--- a/Stock Selection/OPEN POSITION.xlsx
+++ b/Stock Selection/OPEN POSITION.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q101"/>
+  <dimension ref="A1:Q107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,7 +522,7 @@
     <row r="2">
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="n">
-        <v>1744916452</v>
+        <v>1554741910</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.4245</v>
+        <v>0.3495</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45751.74230173611</v>
+        <v>45623.74951116898</v>
       </c>
       <c r="G2" t="n">
-        <v>17.54</v>
+        <v>15.3</v>
       </c>
       <c r="H2" t="n">
-        <v>21.42</v>
+        <v>21.3</v>
       </c>
       <c r="I2" t="n">
-        <v>7.45</v>
+        <v>5.35</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -564,18 +564,18 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.64</v>
+        <v>2.09</v>
       </c>
       <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="n">
-        <v>1817264187</v>
+        <v>1825032378</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -584,19 +584,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4757</v>
+        <v>0.2894</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45789.64859377315</v>
+        <v>45792.76093177083</v>
       </c>
       <c r="G3" t="n">
-        <v>42.02</v>
+        <v>34.55</v>
       </c>
       <c r="H3" t="n">
-        <v>40.45</v>
+        <v>32.31</v>
       </c>
       <c r="I3" t="n">
-        <v>19.99</v>
+        <v>10</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -613,18 +613,18 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.75</v>
+        <v>-0.65</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="n">
-        <v>1566610015</v>
+        <v>1594315903</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -633,19 +633,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9385</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45632.87667083334</v>
+        <v>45659.42644752315</v>
       </c>
       <c r="G4" t="n">
-        <v>21.31</v>
+        <v>16.425</v>
       </c>
       <c r="H4" t="n">
-        <v>16.74</v>
+        <v>15.394</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>17.11</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -662,18 +662,18 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-4.29</v>
+        <v>0.24</v>
       </c>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="n">
-        <v>1644796307</v>
+        <v>1653137218</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0.277</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45693.85501710648</v>
+        <v>45699.85152199074</v>
       </c>
       <c r="G5" t="n">
-        <v>20.36</v>
+        <v>36.1</v>
       </c>
       <c r="H5" t="n">
-        <v>21.8</v>
+        <v>36.44</v>
       </c>
       <c r="I5" t="n">
-        <v>20.36</v>
+        <v>10</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -711,18 +711,18 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.44</v>
+        <v>0.09</v>
       </c>
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="n">
-        <v>1582737192</v>
+        <v>1729617775</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.001</v>
+        <v>0.0907</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45645.90143930555</v>
+        <v>45744.71339734954</v>
       </c>
       <c r="G6" t="n">
-        <v>524.4299999999999</v>
+        <v>165.35</v>
       </c>
       <c r="H6" t="n">
-        <v>569.85</v>
+        <v>197.55</v>
       </c>
       <c r="I6" t="n">
-        <v>0.52</v>
+        <v>15</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -760,18 +760,18 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.05</v>
+        <v>2.92</v>
       </c>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="n">
-        <v>1422773288</v>
+        <v>1796453499</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -780,19 +780,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.483</v>
+        <v>0.6422</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45518.84428523148</v>
+        <v>45777.64668229167</v>
       </c>
       <c r="G7" t="n">
-        <v>51.24</v>
+        <v>15.57</v>
       </c>
       <c r="H7" t="n">
-        <v>59.27</v>
+        <v>17.88</v>
       </c>
       <c r="I7" t="n">
-        <v>24.75</v>
+        <v>10</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -809,18 +809,18 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.88</v>
+        <v>1.48</v>
       </c>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>1727563010</v>
+        <v>1648735305</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0.4576</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45743.76106726852</v>
+        <v>45695.85530675926</v>
       </c>
       <c r="G8" t="n">
-        <v>46.11</v>
+        <v>21.85</v>
       </c>
       <c r="H8" t="n">
-        <v>47.59</v>
+        <v>17.3</v>
       </c>
       <c r="I8" t="n">
-        <v>46.11</v>
+        <v>10</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -858,14 +858,14 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.48</v>
+        <v>-2.08</v>
       </c>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>1599455288</v>
+        <v>1635194117</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -878,16 +878,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.2195</v>
+        <v>0.2479</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45663.73750263889</v>
+        <v>45687.85228493056</v>
       </c>
       <c r="G9" t="n">
-        <v>45.55</v>
+        <v>40.33</v>
       </c>
       <c r="H9" t="n">
-        <v>36.07</v>
+        <v>36.44</v>
       </c>
       <c r="I9" t="n">
         <v>10</v>
@@ -907,18 +907,18 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.08</v>
+        <v>-0.97</v>
       </c>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
-        <v>1381417257</v>
+        <v>1642762235</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0.1572</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45484.67877329861</v>
+        <v>45692.86612574074</v>
       </c>
       <c r="G10" t="n">
-        <v>16.374</v>
+        <v>127.16</v>
       </c>
       <c r="H10" t="n">
-        <v>15.238</v>
+        <v>139.38</v>
       </c>
       <c r="I10" t="n">
-        <v>17.9</v>
+        <v>19.99</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -956,18 +956,18 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.8100000000000001</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
-        <v>1644789287</v>
+        <v>1511085920</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -976,19 +976,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.0813</v>
+        <v>0.0761</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45693.85123056713</v>
+        <v>45593.7262774074</v>
       </c>
       <c r="G11" t="n">
-        <v>129.08</v>
+        <v>196.9</v>
       </c>
       <c r="H11" t="n">
-        <v>139.68</v>
+        <v>197.55</v>
       </c>
       <c r="I11" t="n">
-        <v>10.49</v>
+        <v>14.98</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -1005,18 +1005,18 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.87</v>
+        <v>0.05</v>
       </c>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>1729617775</v>
+        <v>1830410729</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1025,19 +1025,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.0907</v>
+        <v>0.297</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>45744.71339734954</v>
+        <v>45796.82476561343</v>
       </c>
       <c r="G12" t="n">
-        <v>165.35</v>
+        <v>33.66</v>
       </c>
       <c r="H12" t="n">
-        <v>196.16</v>
+        <v>32.31</v>
       </c>
       <c r="I12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -1054,18 +1054,18 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.79</v>
+        <v>-0.4</v>
       </c>
       <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>1554741910</v>
+        <v>1414752069</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1074,19 +1074,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.3495</v>
+        <v>0.1933</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>45623.74951116898</v>
+        <v>45511.86049193287</v>
       </c>
       <c r="G13" t="n">
-        <v>15.3</v>
+        <v>77.53</v>
       </c>
       <c r="H13" t="n">
-        <v>21.42</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>5.35</v>
+        <v>14.99</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -1103,18 +1103,18 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.14</v>
+        <v>-1.84</v>
       </c>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="n">
-        <v>1621495187</v>
+        <v>1712850989</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.2318</v>
+        <v>0.1244</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>45678.83178196759</v>
+        <v>45734.85576775463</v>
       </c>
       <c r="G14" t="n">
-        <v>43.27</v>
+        <v>160.64</v>
       </c>
       <c r="H14" t="n">
-        <v>36.07</v>
+        <v>172.84</v>
       </c>
       <c r="I14" t="n">
-        <v>10.03</v>
+        <v>19.98</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -1152,18 +1152,18 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.67</v>
+        <v>1.52</v>
       </c>
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="n">
-        <v>1701100027</v>
+        <v>1811432805</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.7812</v>
+        <v>0.0856</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>45727.87202070602</v>
+        <v>45785.66143211805</v>
       </c>
       <c r="G15" t="n">
-        <v>19.2</v>
+        <v>128.46</v>
       </c>
       <c r="H15" t="n">
-        <v>16.74</v>
+        <v>155.71</v>
       </c>
       <c r="I15" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1201,14 +1201,14 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.92</v>
+        <v>2.33</v>
       </c>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="n">
-        <v>1744767540</v>
+        <v>1582714896</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.643</v>
+        <v>0.4847</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>45751.72316712963</v>
+        <v>45645.89066263889</v>
       </c>
       <c r="G16" t="n">
-        <v>15.55</v>
+        <v>20.62</v>
       </c>
       <c r="H16" t="n">
-        <v>16.74</v>
+        <v>17.3</v>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1250,18 +1250,18 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.76</v>
+        <v>-1.6</v>
       </c>
       <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="n">
-        <v>1653137218</v>
+        <v>1843477272</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1270,19 +1270,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.277</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>45699.85152199074</v>
+        <v>45804.66725678241</v>
       </c>
       <c r="G17" t="n">
-        <v>36.1</v>
+        <v>17.86</v>
       </c>
       <c r="H17" t="n">
-        <v>36.07</v>
+        <v>17.88</v>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>17.86</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1299,18 +1299,18 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
-        <v>1806978791</v>
+        <v>1566610015</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.0867</v>
+        <v>0.9385</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45783.83109655092</v>
+        <v>45632.87667083334</v>
       </c>
       <c r="G18" t="n">
-        <v>126.78</v>
+        <v>21.31</v>
       </c>
       <c r="H18" t="n">
-        <v>156.44</v>
+        <v>17.3</v>
       </c>
       <c r="I18" t="n">
-        <v>10.99</v>
+        <v>20</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1348,18 +1348,18 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.57</v>
+        <v>-3.76</v>
       </c>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="n">
-        <v>1582708979</v>
+        <v>1499061783</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1368,19 +1368,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.0769</v>
+        <v>0.0001</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45645.88746980324</v>
+        <v>45582.73996892361</v>
       </c>
       <c r="G19" t="n">
-        <v>195.11</v>
+        <v>232.2</v>
       </c>
       <c r="H19" t="n">
-        <v>196.16</v>
+        <v>200.14</v>
       </c>
       <c r="I19" t="n">
-        <v>15</v>
+        <v>0.02</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1397,18 +1397,18 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
-        <v>1662993636</v>
+        <v>1824482557</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1417,19 +1417,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0.2641</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45706.87026833333</v>
+        <v>45792.64805195602</v>
       </c>
       <c r="G20" t="n">
-        <v>20.65</v>
+        <v>56.78</v>
       </c>
       <c r="H20" t="n">
-        <v>21.8</v>
+        <v>59.59</v>
       </c>
       <c r="I20" t="n">
-        <v>20.65</v>
+        <v>15</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1446,18 +1446,18 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.15</v>
+        <v>0.74</v>
       </c>
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="n">
-        <v>1824482557</v>
+        <v>1378901781</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BOTZ.L</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1466,19 +1466,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.2641</v>
+        <v>1</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45792.64805195602</v>
+        <v>45482.71294556713</v>
       </c>
       <c r="G21" t="n">
-        <v>56.78</v>
+        <v>20.58</v>
       </c>
       <c r="H21" t="n">
-        <v>59.27</v>
+        <v>20.66</v>
       </c>
       <c r="I21" t="n">
-        <v>15</v>
+        <v>20.58</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1495,18 +1495,18 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.65</v>
+        <v>0.08</v>
       </c>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="n">
-        <v>1631475148</v>
+        <v>1582737192</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1515,19 +1515,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.2592</v>
+        <v>0.001</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>45685.83625201389</v>
+        <v>45645.90143930555</v>
       </c>
       <c r="G22" t="n">
-        <v>38.58</v>
+        <v>524.4299999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>36.07</v>
+        <v>573.11</v>
       </c>
       <c r="I22" t="n">
-        <v>10</v>
+        <v>0.52</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -1544,18 +1544,18 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.65</v>
+        <v>0.05</v>
       </c>
       <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="n">
-        <v>1727591551</v>
+        <v>1727564345</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0.3274</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>45743.77389555555</v>
+        <v>45743.76175270833</v>
       </c>
       <c r="G23" t="n">
-        <v>72.87</v>
+        <v>30.54</v>
       </c>
       <c r="H23" t="n">
-        <v>72.06</v>
+        <v>30.02</v>
       </c>
       <c r="I23" t="n">
-        <v>72.87</v>
+        <v>10</v>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -1593,18 +1593,18 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.17</v>
       </c>
       <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="n">
-        <v>1554741956</v>
+        <v>1450043624</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0.0231</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45623.74952237269</v>
+        <v>45544.65163525463</v>
       </c>
       <c r="G24" t="n">
-        <v>15.3</v>
+        <v>147.48</v>
       </c>
       <c r="H24" t="n">
-        <v>21.42</v>
+        <v>142.76</v>
       </c>
       <c r="I24" t="n">
-        <v>15.3</v>
+        <v>3.41</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1642,18 +1642,18 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>6.12</v>
+        <v>-0.11</v>
       </c>
       <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="n">
-        <v>1606697510</v>
+        <v>1744930699</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>BND</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1662,19 +1662,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.0295</v>
+        <v>1</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>45667.68664726852</v>
+        <v>45751.74534789352</v>
       </c>
       <c r="G25" t="n">
-        <v>507.68</v>
+        <v>74.13</v>
       </c>
       <c r="H25" t="n">
-        <v>569.85</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>14.98</v>
+        <v>74.13</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -1691,18 +1691,18 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.83</v>
+        <v>-1.62</v>
       </c>
       <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="n">
-        <v>1511085920</v>
+        <v>1666457581</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1711,19 +1711,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.0761</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>45593.7262774074</v>
+        <v>45708.68135159722</v>
       </c>
       <c r="G26" t="n">
-        <v>196.9</v>
+        <v>38.23</v>
       </c>
       <c r="H26" t="n">
-        <v>196.16</v>
+        <v>32.31</v>
       </c>
       <c r="I26" t="n">
-        <v>14.98</v>
+        <v>19.98</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -1740,18 +1740,18 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.05</v>
+        <v>-3.09</v>
       </c>
       <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="n">
-        <v>1378901781</v>
+        <v>1358151307</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BOTZ.L</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1760,19 +1760,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0.1081</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>45482.71294556713</v>
+        <v>45460.88529052083</v>
       </c>
       <c r="G27" t="n">
-        <v>20.58</v>
+        <v>165.93</v>
       </c>
       <c r="H27" t="n">
-        <v>20.135</v>
+        <v>131.35</v>
       </c>
       <c r="I27" t="n">
-        <v>20.58</v>
+        <v>17.94</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -1789,18 +1789,18 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.44</v>
+        <v>-3.73</v>
       </c>
       <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="n">
-        <v>1495551484</v>
+        <v>1754302454</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1809,19 +1809,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.1914</v>
+        <v>0.3673</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>45580.70648087963</v>
+        <v>45755.88025324074</v>
       </c>
       <c r="G28" t="n">
-        <v>135.82</v>
+        <v>27.17</v>
       </c>
       <c r="H28" t="n">
-        <v>136.57</v>
+        <v>36.44</v>
       </c>
       <c r="I28" t="n">
-        <v>26</v>
+        <v>9.98</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -1838,18 +1838,18 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0.14</v>
+        <v>3.4</v>
       </c>
       <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
-        <v>1754304266</v>
+        <v>1559802942</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1858,19 +1858,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.7137</v>
+        <v>0.2585</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>45755.88055112268</v>
+        <v>45628.85929152778</v>
       </c>
       <c r="G29" t="n">
-        <v>14</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>16.74</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>9.99</v>
+        <v>19.99</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -1887,18 +1887,18 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.96</v>
+        <v>-2.41</v>
       </c>
       <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
-        <v>1701098878</v>
+        <v>1824476420</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1907,19 +1907,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.0383</v>
+        <v>0.1548</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45727.87167594907</v>
+        <v>45792.64714148148</v>
       </c>
       <c r="G30" t="n">
-        <v>139.41</v>
+        <v>129.17</v>
       </c>
       <c r="H30" t="n">
-        <v>156.44</v>
+        <v>131.35</v>
       </c>
       <c r="I30" t="n">
-        <v>5.34</v>
+        <v>20</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -1936,14 +1936,14 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0.65</v>
+        <v>0.33</v>
       </c>
       <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="n">
-        <v>1811475599</v>
+        <v>1811475646</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1956,19 +1956,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.7256</v>
+        <v>1</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45785.66972070602</v>
+        <v>45785.66973634259</v>
       </c>
       <c r="G31" t="n">
         <v>12.75</v>
       </c>
       <c r="H31" t="n">
-        <v>13.67</v>
+        <v>13.54</v>
       </c>
       <c r="I31" t="n">
-        <v>10.51</v>
+        <v>14.49</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1985,18 +1985,18 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.62</v>
+        <v>0.77</v>
       </c>
       <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="n">
-        <v>1666451221</v>
+        <v>1599449649</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2005,19 +2005,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.0001</v>
+        <v>0.4145</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45708.68022634259</v>
+        <v>45663.73562525463</v>
       </c>
       <c r="G32" t="n">
-        <v>43</v>
+        <v>24.11</v>
       </c>
       <c r="H32" t="n">
-        <v>43.41</v>
+        <v>17.3</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>9.99</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -2034,18 +2034,18 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>-2.82</v>
       </c>
       <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="n">
-        <v>1648737122</v>
+        <v>1843469729</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2054,19 +2054,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.0269</v>
+        <v>0.0956</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45695.85619950231</v>
+        <v>45804.66615450232</v>
       </c>
       <c r="G33" t="n">
-        <v>408.33</v>
+        <v>156.9</v>
       </c>
       <c r="H33" t="n">
-        <v>454.92</v>
+        <v>155.71</v>
       </c>
       <c r="I33" t="n">
-        <v>10.98</v>
+        <v>15</v>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -2083,18 +2083,18 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.26</v>
+        <v>-0.11</v>
       </c>
       <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="n">
-        <v>1806980496</v>
+        <v>1599448103</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2103,19 +2103,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>0.2839</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45783.83190503472</v>
+        <v>45663.73506711805</v>
       </c>
       <c r="G34" t="n">
-        <v>16.12</v>
+        <v>52.83</v>
       </c>
       <c r="H34" t="n">
-        <v>17.62</v>
+        <v>59.59</v>
       </c>
       <c r="I34" t="n">
-        <v>16.12</v>
+        <v>15</v>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
@@ -2132,18 +2132,18 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>1582714896</v>
+        <v>1582735114</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2152,19 +2152,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.4847</v>
+        <v>0.0003</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>45645.89066263889</v>
+        <v>45645.90076803241</v>
       </c>
       <c r="G35" t="n">
-        <v>20.62</v>
+        <v>130.51</v>
       </c>
       <c r="H35" t="n">
-        <v>16.74</v>
+        <v>143.97</v>
       </c>
       <c r="I35" t="n">
-        <v>9.99</v>
+        <v>0.04</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
@@ -2181,18 +2181,18 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>-1.88</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>1499061783</v>
+        <v>1633116336</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2201,19 +2201,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.0001</v>
+        <v>1</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45582.73996892361</v>
+        <v>45686.83272234954</v>
       </c>
       <c r="G36" t="n">
-        <v>232.2</v>
+        <v>44.24</v>
       </c>
       <c r="H36" t="n">
-        <v>201.23</v>
+        <v>47.61</v>
       </c>
       <c r="I36" t="n">
-        <v>0.02</v>
+        <v>44.24</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -2230,18 +2230,18 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
-        <v>1825032062</v>
+        <v>1381375440</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2250,19 +2250,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.3559</v>
+        <v>0.1057</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>45792.76080334491</v>
+        <v>45484.67118315972</v>
       </c>
       <c r="G37" t="n">
-        <v>28.09</v>
+        <v>189.11</v>
       </c>
       <c r="H37" t="n">
-        <v>29.51</v>
+        <v>197.55</v>
       </c>
       <c r="I37" t="n">
-        <v>10</v>
+        <v>19.99</v>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
@@ -2279,18 +2279,18 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.5</v>
+        <v>0.89</v>
       </c>
       <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>1554742887</v>
+        <v>1806980482</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2299,19 +2299,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.2406</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45623.74993112269</v>
+        <v>45783.83189613426</v>
       </c>
       <c r="G38" t="n">
-        <v>178.48</v>
+        <v>16.12</v>
       </c>
       <c r="H38" t="n">
-        <v>196.16</v>
+        <v>17.88</v>
       </c>
       <c r="I38" t="n">
-        <v>14.99</v>
+        <v>3.88</v>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
@@ -2328,18 +2328,18 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.49</v>
+        <v>0.42</v>
       </c>
       <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
-        <v>1642762235</v>
+        <v>1680991980</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2348,19 +2348,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.1572</v>
+        <v>0.1958</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45692.86612574074</v>
+        <v>45716.8556621875</v>
       </c>
       <c r="G39" t="n">
-        <v>127.16</v>
+        <v>178.67</v>
       </c>
       <c r="H39" t="n">
-        <v>136.57</v>
+        <v>197.55</v>
       </c>
       <c r="I39" t="n">
-        <v>19.99</v>
+        <v>34.98</v>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -2377,18 +2377,18 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1.48</v>
+        <v>3.7</v>
       </c>
       <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="n">
-        <v>1680993370</v>
+        <v>1843470413</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2397,19 +2397,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>0.4729</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>45716.85638861111</v>
+        <v>45804.66637251157</v>
       </c>
       <c r="G40" t="n">
-        <v>44.49</v>
+        <v>42.29</v>
       </c>
       <c r="H40" t="n">
-        <v>47.59</v>
+        <v>42.18</v>
       </c>
       <c r="I40" t="n">
-        <v>44.49</v>
+        <v>20</v>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
@@ -2426,18 +2426,18 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>3.1</v>
+        <v>-0.05</v>
       </c>
       <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="n">
-        <v>1532661507</v>
+        <v>1662993636</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2446,19 +2446,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.06809999999999999</v>
+        <v>1</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45608.74251107639</v>
+        <v>45706.87026833333</v>
       </c>
       <c r="G41" t="n">
-        <v>190.67</v>
+        <v>20.65</v>
       </c>
       <c r="H41" t="n">
-        <v>196.16</v>
+        <v>22.18</v>
       </c>
       <c r="I41" t="n">
-        <v>12.98</v>
+        <v>20.65</v>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
@@ -2475,18 +2475,18 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.38</v>
+        <v>1.53</v>
       </c>
       <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="n">
-        <v>1744930699</v>
+        <v>1481609355</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2495,19 +2495,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0.107</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>45751.74534789352</v>
+        <v>45568.7734872338</v>
       </c>
       <c r="G42" t="n">
-        <v>74.13</v>
+        <v>140.18</v>
       </c>
       <c r="H42" t="n">
-        <v>72.06</v>
+        <v>142.76</v>
       </c>
       <c r="I42" t="n">
-        <v>74.13</v>
+        <v>15</v>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -2524,18 +2524,18 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>-2.07</v>
+        <v>0.28</v>
       </c>
       <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="n">
-        <v>1776193271</v>
+        <v>1744767540</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2544,16 +2544,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.6724</v>
+        <v>0.643</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>45764.85451520833</v>
+        <v>45751.72316712963</v>
       </c>
       <c r="G43" t="n">
-        <v>14.87</v>
+        <v>15.55</v>
       </c>
       <c r="H43" t="n">
-        <v>17.62</v>
+        <v>17.3</v>
       </c>
       <c r="I43" t="n">
         <v>10</v>
@@ -2573,18 +2573,18 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.85</v>
+        <v>1.12</v>
       </c>
       <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
-        <v>1461331124</v>
+        <v>1817256440</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2593,19 +2593,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.3922</v>
+        <v>0.2267</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45553.65374138889</v>
+        <v>45789.64787115741</v>
       </c>
       <c r="G44" t="n">
-        <v>50.99</v>
+        <v>44.1</v>
       </c>
       <c r="H44" t="n">
-        <v>59.27</v>
+        <v>43.88</v>
       </c>
       <c r="I44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -2622,18 +2622,18 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>3.25</v>
+        <v>-0.05</v>
       </c>
       <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>1712849726</v>
+        <v>1843468958</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2642,19 +2642,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.0861</v>
+        <v>0.2208</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>45734.85489405093</v>
+        <v>45804.66597149306</v>
       </c>
       <c r="G45" t="n">
-        <v>127.72</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>156.44</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -2671,18 +2671,18 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.47</v>
+        <v>0.02</v>
       </c>
       <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>1806977521</v>
+        <v>1532661507</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2691,19 +2691,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.3367</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>45783.8305750463</v>
+        <v>45608.74251107639</v>
       </c>
       <c r="G46" t="n">
-        <v>29.7</v>
+        <v>190.67</v>
       </c>
       <c r="H46" t="n">
-        <v>36.07</v>
+        <v>197.55</v>
       </c>
       <c r="I46" t="n">
-        <v>10</v>
+        <v>12.98</v>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -2720,18 +2720,18 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.14</v>
+        <v>0.47</v>
       </c>
       <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>1666461140</v>
+        <v>1583696868</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>BOTZ.L</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2740,19 +2740,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.2651</v>
+        <v>0.5</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>45708.68207092593</v>
+        <v>45646.60053979167</v>
       </c>
       <c r="G47" t="n">
-        <v>37.7</v>
+        <v>20.645</v>
       </c>
       <c r="H47" t="n">
-        <v>36.07</v>
+        <v>20.66</v>
       </c>
       <c r="I47" t="n">
-        <v>9.99</v>
+        <v>10.32</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -2769,18 +2769,18 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>-0.43</v>
+        <v>0.01</v>
       </c>
       <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>1648740228</v>
+        <v>1712849726</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2789,19 +2789,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.0538</v>
+        <v>0.0861</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>45695.85792408565</v>
+        <v>45734.85489405093</v>
       </c>
       <c r="G48" t="n">
-        <v>185.82</v>
+        <v>127.72</v>
       </c>
       <c r="H48" t="n">
-        <v>170.83</v>
+        <v>155.71</v>
       </c>
       <c r="I48" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -2818,18 +2818,18 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>-0.8100000000000001</v>
+        <v>2.41</v>
       </c>
       <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
-        <v>1806980482</v>
+        <v>1582723120</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2838,19 +2838,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.2406</v>
+        <v>0.3755</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45783.83189613426</v>
+        <v>45645.89511640046</v>
       </c>
       <c r="G49" t="n">
-        <v>16.12</v>
+        <v>53.26</v>
       </c>
       <c r="H49" t="n">
-        <v>17.62</v>
+        <v>59.59</v>
       </c>
       <c r="I49" t="n">
-        <v>3.88</v>
+        <v>20</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
@@ -2867,18 +2867,18 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
-        <v>1594315903</v>
+        <v>1806979127</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0.6361</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>45659.42644752315</v>
+        <v>45783.83125244213</v>
       </c>
       <c r="G50" t="n">
-        <v>16.425</v>
+        <v>15.72</v>
       </c>
       <c r="H50" t="n">
-        <v>15.238</v>
+        <v>17.3</v>
       </c>
       <c r="I50" t="n">
-        <v>17.11</v>
+        <v>10</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -2916,18 +2916,18 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>-0.02</v>
+        <v>1</v>
       </c>
       <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>1666459270</v>
+        <v>1727591551</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>BND</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2939,16 +2939,16 @@
         <v>1</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>45708.68166530092</v>
+        <v>45743.77389555555</v>
       </c>
       <c r="G51" t="n">
-        <v>17.18</v>
+        <v>72.87</v>
       </c>
       <c r="H51" t="n">
-        <v>21.42</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>17.18</v>
+        <v>72.87</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -2965,18 +2965,18 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>4.24</v>
+        <v>-0.36</v>
       </c>
       <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
-        <v>1559802942</v>
+        <v>1666459270</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2985,19 +2985,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.2585</v>
+        <v>1</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>45628.85929152778</v>
+        <v>45708.68166530092</v>
       </c>
       <c r="G52" t="n">
-        <v>77.34999999999999</v>
+        <v>17.18</v>
       </c>
       <c r="H52" t="n">
-        <v>66.91</v>
+        <v>21.3</v>
       </c>
       <c r="I52" t="n">
-        <v>19.99</v>
+        <v>17.18</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
@@ -3014,18 +3014,18 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>-2.69</v>
+        <v>4.12</v>
       </c>
       <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="n">
-        <v>1644788775</v>
+        <v>1648740228</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3034,19 +3034,19 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.0538</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>45693.85093391204</v>
+        <v>45695.85792408565</v>
       </c>
       <c r="G53" t="n">
-        <v>144.94</v>
+        <v>185.82</v>
       </c>
       <c r="H53" t="n">
-        <v>130.1</v>
+        <v>172.84</v>
       </c>
       <c r="I53" t="n">
-        <v>10.99</v>
+        <v>10</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
@@ -3063,18 +3063,18 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>-1.13</v>
+        <v>-0.7</v>
       </c>
       <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="n">
-        <v>1680994777</v>
+        <v>1631475148</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3083,19 +3083,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.7278</v>
+        <v>0.2592</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>45716.85705375</v>
+        <v>45685.83625201389</v>
       </c>
       <c r="G54" t="n">
-        <v>20.6</v>
+        <v>38.58</v>
       </c>
       <c r="H54" t="n">
-        <v>16.74</v>
+        <v>36.44</v>
       </c>
       <c r="I54" t="n">
-        <v>14.99</v>
+        <v>10</v>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
@@ -3112,18 +3112,18 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>-2.81</v>
+        <v>-0.55</v>
       </c>
       <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="n">
-        <v>1517510856</v>
+        <v>1644796307</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3132,19 +3132,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.0602</v>
+        <v>1</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>45597.61014849537</v>
+        <v>45693.85501710648</v>
       </c>
       <c r="G55" t="n">
-        <v>166.03</v>
+        <v>20.36</v>
       </c>
       <c r="H55" t="n">
-        <v>130.1</v>
+        <v>22.18</v>
       </c>
       <c r="I55" t="n">
-        <v>10</v>
+        <v>20.36</v>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
@@ -3161,14 +3161,14 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>-2.17</v>
+        <v>1.82</v>
       </c>
       <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="n">
-        <v>1563288050</v>
+        <v>1517510856</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -3181,16 +3181,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.0626</v>
+        <v>0.0602</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>45630.85583428241</v>
+        <v>45597.61014849537</v>
       </c>
       <c r="G56" t="n">
-        <v>159.74</v>
+        <v>166.03</v>
       </c>
       <c r="H56" t="n">
-        <v>130.1</v>
+        <v>131.35</v>
       </c>
       <c r="I56" t="n">
         <v>10</v>
@@ -3210,18 +3210,18 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>-1.86</v>
+        <v>-2.09</v>
       </c>
       <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="n">
-        <v>1744879358</v>
+        <v>1680993370</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3230,19 +3230,19 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.2701</v>
+        <v>1</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45751.73925940973</v>
+        <v>45716.85638861111</v>
       </c>
       <c r="G57" t="n">
-        <v>148.09</v>
+        <v>44.49</v>
       </c>
       <c r="H57" t="n">
-        <v>196.16</v>
+        <v>47.61</v>
       </c>
       <c r="I57" t="n">
-        <v>40</v>
+        <v>44.49</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
@@ -3259,18 +3259,18 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>12.98</v>
+        <v>3.12</v>
       </c>
       <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
-        <v>1817256440</v>
+        <v>1843474191</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3279,19 +3279,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.2267</v>
+        <v>0.9372</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45789.64787115741</v>
+        <v>45804.66699503472</v>
       </c>
       <c r="G58" t="n">
-        <v>44.1</v>
+        <v>21.33</v>
       </c>
       <c r="H58" t="n">
-        <v>43.41</v>
+        <v>21.3</v>
       </c>
       <c r="I58" t="n">
-        <v>10</v>
+        <v>19.99</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
@@ -3308,18 +3308,18 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>-0.16</v>
+        <v>-0.03</v>
       </c>
       <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="n">
-        <v>1635194117</v>
+        <v>1422773288</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3328,19 +3328,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.2479</v>
+        <v>0.483</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>45687.85228493056</v>
+        <v>45518.84428523148</v>
       </c>
       <c r="G59" t="n">
-        <v>40.33</v>
+        <v>51.24</v>
       </c>
       <c r="H59" t="n">
-        <v>36.07</v>
+        <v>59.59</v>
       </c>
       <c r="I59" t="n">
-        <v>10</v>
+        <v>24.75</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
@@ -3357,18 +3357,18 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>-1.06</v>
+        <v>4.03</v>
       </c>
       <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="n">
-        <v>1811475646</v>
+        <v>1744916452</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3377,19 +3377,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>0.4245</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45785.66973634259</v>
+        <v>45751.74230173611</v>
       </c>
       <c r="G60" t="n">
-        <v>12.75</v>
+        <v>17.54</v>
       </c>
       <c r="H60" t="n">
-        <v>13.67</v>
+        <v>21.3</v>
       </c>
       <c r="I60" t="n">
-        <v>14.49</v>
+        <v>7.45</v>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
@@ -3406,18 +3406,18 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>0.84</v>
+        <v>1.59</v>
       </c>
       <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="n">
-        <v>1796453499</v>
+        <v>1824475555</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3426,19 +3426,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.6422</v>
+        <v>1</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>45777.64668229167</v>
+        <v>45792.64702015046</v>
       </c>
       <c r="G61" t="n">
-        <v>15.57</v>
+        <v>21.66</v>
       </c>
       <c r="H61" t="n">
-        <v>17.62</v>
+        <v>22.18</v>
       </c>
       <c r="I61" t="n">
-        <v>10</v>
+        <v>21.66</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
@@ -3455,18 +3455,18 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>1.32</v>
+        <v>0.52</v>
       </c>
       <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="n">
-        <v>1824476420</v>
+        <v>1806980496</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3475,19 +3475,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.1548</v>
+        <v>1</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>45792.64714148148</v>
+        <v>45783.83190503472</v>
       </c>
       <c r="G62" t="n">
-        <v>129.17</v>
+        <v>16.12</v>
       </c>
       <c r="H62" t="n">
-        <v>130.1</v>
+        <v>17.88</v>
       </c>
       <c r="I62" t="n">
-        <v>20</v>
+        <v>16.12</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
@@ -3504,18 +3504,18 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>0.14</v>
+        <v>1.76</v>
       </c>
       <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="n">
-        <v>1582735114</v>
+        <v>1599435465</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3524,19 +3524,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.0003</v>
+        <v>0.0289</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>45645.90076803241</v>
+        <v>45663.73115600694</v>
       </c>
       <c r="G63" t="n">
-        <v>130.51</v>
+        <v>517.7</v>
       </c>
       <c r="H63" t="n">
-        <v>145.39</v>
+        <v>573.11</v>
       </c>
       <c r="I63" t="n">
-        <v>0.04</v>
+        <v>14.96</v>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
@@ -3553,18 +3553,18 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="n">
-        <v>1830408508</v>
+        <v>1559803221</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3573,19 +3573,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.5793</v>
+        <v>0.092</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>45796.82346997685</v>
+        <v>45628.85951927083</v>
       </c>
       <c r="G64" t="n">
-        <v>17.26</v>
+        <v>162.85</v>
       </c>
       <c r="H64" t="n">
-        <v>16.74</v>
+        <v>131.35</v>
       </c>
       <c r="I64" t="n">
-        <v>10</v>
+        <v>14.98</v>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
@@ -3602,18 +3602,18 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>-0.3</v>
+        <v>-2.9</v>
       </c>
       <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="n">
-        <v>1680991980</v>
+        <v>1666451221</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3622,19 +3622,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.1958</v>
+        <v>0.0001</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>45716.8556621875</v>
+        <v>45708.68022634259</v>
       </c>
       <c r="G65" t="n">
-        <v>178.67</v>
+        <v>43</v>
       </c>
       <c r="H65" t="n">
-        <v>196.16</v>
+        <v>43.88</v>
       </c>
       <c r="I65" t="n">
-        <v>34.98</v>
+        <v>0</v>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
@@ -3651,18 +3651,18 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="n">
-        <v>1414752069</v>
+        <v>1701100481</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3671,16 +3671,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.1933</v>
+        <v>0.0873</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>45511.86049193287</v>
+        <v>45727.87214378472</v>
       </c>
       <c r="G66" t="n">
-        <v>77.53</v>
+        <v>171.67</v>
       </c>
       <c r="H66" t="n">
-        <v>66.91</v>
+        <v>197.55</v>
       </c>
       <c r="I66" t="n">
         <v>14.99</v>
@@ -3700,18 +3700,18 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>-2.06</v>
+        <v>2.26</v>
       </c>
       <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="n">
-        <v>1599449649</v>
+        <v>1599455288</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3720,19 +3720,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.4145</v>
+        <v>0.2195</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>45663.73562525463</v>
+        <v>45663.73750263889</v>
       </c>
       <c r="G67" t="n">
-        <v>24.11</v>
+        <v>45.55</v>
       </c>
       <c r="H67" t="n">
-        <v>16.74</v>
+        <v>36.44</v>
       </c>
       <c r="I67" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
@@ -3749,18 +3749,18 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>-3.05</v>
+        <v>-2</v>
       </c>
       <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="n">
-        <v>1559803221</v>
+        <v>1811475599</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3769,19 +3769,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.092</v>
+        <v>0.7256</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>45628.85951927083</v>
+        <v>45785.66972070602</v>
       </c>
       <c r="G68" t="n">
-        <v>162.85</v>
+        <v>12.75</v>
       </c>
       <c r="H68" t="n">
-        <v>130.1</v>
+        <v>13.54</v>
       </c>
       <c r="I68" t="n">
-        <v>14.98</v>
+        <v>10.51</v>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
@@ -3798,18 +3798,18 @@
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>-3.01</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="n">
-        <v>1358151307</v>
+        <v>1727563010</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3818,19 +3818,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.1081</v>
+        <v>1</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>45460.88529052083</v>
+        <v>45743.76106726852</v>
       </c>
       <c r="G69" t="n">
-        <v>165.93</v>
+        <v>46.11</v>
       </c>
       <c r="H69" t="n">
-        <v>130.1</v>
+        <v>47.61</v>
       </c>
       <c r="I69" t="n">
-        <v>17.94</v>
+        <v>46.11</v>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
@@ -3847,18 +3847,18 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>-3.87</v>
+        <v>1.5</v>
       </c>
       <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="n">
-        <v>1754302454</v>
+        <v>1644789287</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3867,19 +3867,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.3673</v>
+        <v>0.0813</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>45755.88025324074</v>
+        <v>45693.85123056713</v>
       </c>
       <c r="G70" t="n">
-        <v>27.17</v>
+        <v>129.08</v>
       </c>
       <c r="H70" t="n">
-        <v>36.07</v>
+        <v>142.76</v>
       </c>
       <c r="I70" t="n">
-        <v>9.98</v>
+        <v>10.49</v>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
@@ -3896,18 +3896,18 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>3.27</v>
+        <v>1.12</v>
       </c>
       <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="n">
-        <v>1712850989</v>
+        <v>1621495187</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3916,19 +3916,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.1244</v>
+        <v>0.2318</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>45734.85576775463</v>
+        <v>45678.83178196759</v>
       </c>
       <c r="G71" t="n">
-        <v>160.64</v>
+        <v>43.27</v>
       </c>
       <c r="H71" t="n">
-        <v>170.83</v>
+        <v>36.44</v>
       </c>
       <c r="I71" t="n">
-        <v>19.98</v>
+        <v>10.03</v>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
@@ -3945,18 +3945,18 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>1.27</v>
+        <v>-1.58</v>
       </c>
       <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="n">
-        <v>1744916497</v>
+        <v>1644788775</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3965,19 +3965,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>45751.74231563658</v>
+        <v>45693.85093391204</v>
       </c>
       <c r="G72" t="n">
-        <v>17.54</v>
+        <v>144.94</v>
       </c>
       <c r="H72" t="n">
-        <v>21.42</v>
+        <v>131.35</v>
       </c>
       <c r="I72" t="n">
-        <v>17.54</v>
+        <v>10.99</v>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -3994,18 +3994,18 @@
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>3.88</v>
+        <v>-1.03</v>
       </c>
       <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="n">
-        <v>1830410729</v>
+        <v>1495551484</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4014,19 +4014,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.297</v>
+        <v>0.1914</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45796.82476561343</v>
+        <v>45580.70648087963</v>
       </c>
       <c r="G73" t="n">
-        <v>33.66</v>
+        <v>135.82</v>
       </c>
       <c r="H73" t="n">
-        <v>31.67</v>
+        <v>139.38</v>
       </c>
       <c r="I73" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
@@ -4043,18 +4043,18 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>-0.59</v>
+        <v>0.68</v>
       </c>
       <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="n">
-        <v>1824475555</v>
+        <v>1830408508</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4063,19 +4063,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>0.5793</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45792.64702015046</v>
+        <v>45796.82346997685</v>
       </c>
       <c r="G74" t="n">
-        <v>21.66</v>
+        <v>17.26</v>
       </c>
       <c r="H74" t="n">
-        <v>21.8</v>
+        <v>17.3</v>
       </c>
       <c r="I74" t="n">
-        <v>21.66</v>
+        <v>10</v>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
@@ -4092,18 +4092,18 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>0.14</v>
+        <v>0.02</v>
       </c>
       <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="n">
-        <v>1648733962</v>
+        <v>1563288050</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4112,19 +4112,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.081</v>
+        <v>0.0626</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>45695.85463682871</v>
+        <v>45630.85583428241</v>
       </c>
       <c r="G75" t="n">
-        <v>129.56</v>
+        <v>159.74</v>
       </c>
       <c r="H75" t="n">
-        <v>139.68</v>
+        <v>131.35</v>
       </c>
       <c r="I75" t="n">
-        <v>10.49</v>
+        <v>10</v>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
@@ -4141,14 +4141,14 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>0.82</v>
+        <v>-1.78</v>
       </c>
       <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="n">
-        <v>1806979127</v>
+        <v>1701100027</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -4161,19 +4161,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.6361</v>
+        <v>0.7812</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>45783.83125244213</v>
+        <v>45727.87202070602</v>
       </c>
       <c r="G76" t="n">
-        <v>15.72</v>
+        <v>19.2</v>
       </c>
       <c r="H76" t="n">
-        <v>16.74</v>
+        <v>17.3</v>
       </c>
       <c r="I76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
@@ -4190,18 +4190,18 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>0.65</v>
+        <v>-1.49</v>
       </c>
       <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="n">
-        <v>1582723120</v>
+        <v>1744929368</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4210,19 +4210,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.3755</v>
+        <v>0.0192</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>45645.89511640046</v>
+        <v>45751.74500871528</v>
       </c>
       <c r="G77" t="n">
-        <v>53.26</v>
+        <v>324.48</v>
       </c>
       <c r="H77" t="n">
-        <v>59.27</v>
+        <v>358.47</v>
       </c>
       <c r="I77" t="n">
-        <v>20</v>
+        <v>6.23</v>
       </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
@@ -4239,18 +4239,18 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>2.26</v>
+        <v>0.65</v>
       </c>
       <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="n">
-        <v>1662995258</v>
+        <v>1599431096</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4259,19 +4259,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.2943</v>
+        <v>0.1013</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>45706.87121422453</v>
+        <v>45663.73014731482</v>
       </c>
       <c r="G78" t="n">
-        <v>67.97</v>
+        <v>148.02</v>
       </c>
       <c r="H78" t="n">
-        <v>66.91</v>
+        <v>131.35</v>
       </c>
       <c r="I78" t="n">
-        <v>20</v>
+        <v>14.99</v>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
@@ -4288,18 +4288,18 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>-0.31</v>
+        <v>-1.68</v>
       </c>
       <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="n">
-        <v>1559803984</v>
+        <v>1554742887</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4308,19 +4308,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.1076</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>45628.86014383102</v>
+        <v>45623.74993112269</v>
       </c>
       <c r="G79" t="n">
-        <v>139.4</v>
+        <v>178.48</v>
       </c>
       <c r="H79" t="n">
-        <v>139.68</v>
+        <v>197.55</v>
       </c>
       <c r="I79" t="n">
-        <v>15</v>
+        <v>14.99</v>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
@@ -4337,18 +4337,18 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>0.03</v>
+        <v>1.6</v>
       </c>
       <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="n">
-        <v>1633116336</v>
+        <v>1666459175</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4357,19 +4357,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>0.1641</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>45686.83272234954</v>
+        <v>45708.68165298611</v>
       </c>
       <c r="G80" t="n">
-        <v>44.24</v>
+        <v>17.18</v>
       </c>
       <c r="H80" t="n">
-        <v>47.59</v>
+        <v>21.3</v>
       </c>
       <c r="I80" t="n">
-        <v>44.24</v>
+        <v>2.82</v>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
@@ -4386,18 +4386,18 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>3.35</v>
+        <v>0.68</v>
       </c>
       <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="n">
-        <v>1727564345</v>
+        <v>1824477589</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4406,16 +4406,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.3274</v>
+        <v>0.2344</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>45743.76175270833</v>
+        <v>45792.64732982639</v>
       </c>
       <c r="G81" t="n">
-        <v>30.54</v>
+        <v>42.66</v>
       </c>
       <c r="H81" t="n">
-        <v>29.51</v>
+        <v>43.88</v>
       </c>
       <c r="I81" t="n">
         <v>10</v>
@@ -4435,18 +4435,18 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>-0.34</v>
+        <v>0.29</v>
       </c>
       <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="n">
-        <v>1533882988</v>
+        <v>1381417257</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BOTZ.L</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4455,19 +4455,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>45609.60769543982</v>
+        <v>45484.67877329861</v>
       </c>
       <c r="G82" t="n">
-        <v>21.905</v>
+        <v>16.374</v>
       </c>
       <c r="H82" t="n">
-        <v>20.135</v>
+        <v>15.394</v>
       </c>
       <c r="I82" t="n">
-        <v>10.95</v>
+        <v>17.9</v>
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
@@ -4484,18 +4484,18 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>-0.88</v>
+        <v>-0.55</v>
       </c>
       <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="n">
-        <v>1599431096</v>
+        <v>1806977521</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4504,19 +4504,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.1013</v>
+        <v>0.3367</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>45663.73014731482</v>
+        <v>45783.8305750463</v>
       </c>
       <c r="G83" t="n">
-        <v>148.02</v>
+        <v>29.7</v>
       </c>
       <c r="H83" t="n">
-        <v>130.1</v>
+        <v>36.44</v>
       </c>
       <c r="I83" t="n">
-        <v>14.99</v>
+        <v>10</v>
       </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
@@ -4533,18 +4533,18 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>-1.81</v>
+        <v>2.27</v>
       </c>
       <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="n">
-        <v>1381375440</v>
+        <v>1727574394</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4553,19 +4553,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.1057</v>
+        <v>1</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>45484.67118315972</v>
+        <v>45743.76658678241</v>
       </c>
       <c r="G84" t="n">
-        <v>189.11</v>
+        <v>21.13</v>
       </c>
       <c r="H84" t="n">
-        <v>196.16</v>
+        <v>22.18</v>
       </c>
       <c r="I84" t="n">
-        <v>19.99</v>
+        <v>21.13</v>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
@@ -4582,18 +4582,18 @@
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>0.74</v>
+        <v>1.05</v>
       </c>
       <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="n">
-        <v>1481609355</v>
+        <v>1461331124</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4602,19 +4602,19 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.107</v>
+        <v>0.3922</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>45568.7734872338</v>
+        <v>45553.65374138889</v>
       </c>
       <c r="G85" t="n">
-        <v>140.18</v>
+        <v>50.99</v>
       </c>
       <c r="H85" t="n">
-        <v>139.68</v>
+        <v>59.59</v>
       </c>
       <c r="I85" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
@@ -4631,18 +4631,18 @@
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>-0.05</v>
+        <v>3.37</v>
       </c>
       <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="n">
-        <v>1450043624</v>
+        <v>1744879358</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4651,19 +4651,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.0231</v>
+        <v>0.2701</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>45544.65163525463</v>
+        <v>45751.73925940973</v>
       </c>
       <c r="G86" t="n">
-        <v>147.48</v>
+        <v>148.09</v>
       </c>
       <c r="H86" t="n">
-        <v>139.68</v>
+        <v>197.55</v>
       </c>
       <c r="I86" t="n">
-        <v>3.41</v>
+        <v>40</v>
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
@@ -4680,18 +4680,18 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>-0.18</v>
+        <v>13.36</v>
       </c>
       <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="n">
-        <v>1701100481</v>
+        <v>1662995258</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4700,19 +4700,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.0873</v>
+        <v>0.2943</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>45727.87214378472</v>
+        <v>45706.87121422453</v>
       </c>
       <c r="G87" t="n">
-        <v>171.67</v>
+        <v>67.97</v>
       </c>
       <c r="H87" t="n">
-        <v>196.16</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>14.99</v>
+        <v>20</v>
       </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
@@ -4729,18 +4729,18 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>2.13</v>
+        <v>0.02</v>
       </c>
       <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="n">
-        <v>1744929368</v>
+        <v>1817264187</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4749,19 +4749,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.0192</v>
+        <v>0.4757</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>45751.74500871528</v>
+        <v>45789.64859377315</v>
       </c>
       <c r="G88" t="n">
-        <v>324.48</v>
+        <v>42.02</v>
       </c>
       <c r="H88" t="n">
-        <v>357</v>
+        <v>42.18</v>
       </c>
       <c r="I88" t="n">
-        <v>6.23</v>
+        <v>19.99</v>
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
@@ -4778,18 +4778,18 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>0.62</v>
+        <v>0.08</v>
       </c>
       <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="n">
-        <v>1825032378</v>
+        <v>1754304266</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4798,19 +4798,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.2894</v>
+        <v>0.7137</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>45792.76093177083</v>
+        <v>45755.88055112268</v>
       </c>
       <c r="G89" t="n">
-        <v>34.55</v>
+        <v>14</v>
       </c>
       <c r="H89" t="n">
-        <v>31.67</v>
+        <v>17.3</v>
       </c>
       <c r="I89" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
@@ -4827,18 +4827,18 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>-0.83</v>
+        <v>2.36</v>
       </c>
       <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="n">
-        <v>1666457581</v>
+        <v>1554741956</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4847,19 +4847,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.5227000000000001</v>
+        <v>1</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>45708.68135159722</v>
+        <v>45623.74952237269</v>
       </c>
       <c r="G90" t="n">
-        <v>38.23</v>
+        <v>15.3</v>
       </c>
       <c r="H90" t="n">
-        <v>31.67</v>
+        <v>21.3</v>
       </c>
       <c r="I90" t="n">
-        <v>19.98</v>
+        <v>15.3</v>
       </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
@@ -4876,18 +4876,18 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>-3.43</v>
+        <v>6</v>
       </c>
       <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="n">
-        <v>1648735305</v>
+        <v>1701098878</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4896,19 +4896,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.4576</v>
+        <v>0.0383</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>45695.85530675926</v>
+        <v>45727.87167594907</v>
       </c>
       <c r="G91" t="n">
-        <v>21.85</v>
+        <v>139.41</v>
       </c>
       <c r="H91" t="n">
-        <v>16.74</v>
+        <v>155.71</v>
       </c>
       <c r="I91" t="n">
-        <v>10</v>
+        <v>5.34</v>
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
@@ -4925,14 +4925,14 @@
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>-2.34</v>
+        <v>0.62</v>
       </c>
       <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="n">
-        <v>1811432805</v>
+        <v>1806978791</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -4945,19 +4945,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.0856</v>
+        <v>0.0867</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>45785.66143211805</v>
+        <v>45783.83109655092</v>
       </c>
       <c r="G92" t="n">
-        <v>128.46</v>
+        <v>126.78</v>
       </c>
       <c r="H92" t="n">
-        <v>156.44</v>
+        <v>155.71</v>
       </c>
       <c r="I92" t="n">
-        <v>11</v>
+        <v>10.99</v>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
@@ -4974,18 +4974,18 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>2.39</v>
+        <v>2.51</v>
       </c>
       <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="n">
-        <v>1583696868</v>
+        <v>1582708979</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BOTZ.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4994,19 +4994,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.5</v>
+        <v>0.0769</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>45646.60053979167</v>
+        <v>45645.88746980324</v>
       </c>
       <c r="G93" t="n">
-        <v>20.645</v>
+        <v>195.11</v>
       </c>
       <c r="H93" t="n">
-        <v>20.135</v>
+        <v>197.55</v>
       </c>
       <c r="I93" t="n">
-        <v>10.32</v>
+        <v>15</v>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
@@ -5023,18 +5023,18 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>-0.25</v>
+        <v>0.19</v>
       </c>
       <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="n">
-        <v>1666459175</v>
+        <v>1559803984</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5043,19 +5043,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.1641</v>
+        <v>0.1076</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>45708.68165298611</v>
+        <v>45628.86014383102</v>
       </c>
       <c r="G94" t="n">
-        <v>17.18</v>
+        <v>139.4</v>
       </c>
       <c r="H94" t="n">
-        <v>21.42</v>
+        <v>142.76</v>
       </c>
       <c r="I94" t="n">
-        <v>2.82</v>
+        <v>15</v>
       </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
@@ -5072,18 +5072,18 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>0.7</v>
+        <v>0.36</v>
       </c>
       <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="n">
-        <v>1599448103</v>
+        <v>1666461140</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5092,19 +5092,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.2839</v>
+        <v>0.2651</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>45663.73506711805</v>
+        <v>45708.68207092593</v>
       </c>
       <c r="G95" t="n">
-        <v>52.83</v>
+        <v>37.7</v>
       </c>
       <c r="H95" t="n">
-        <v>59.27</v>
+        <v>36.44</v>
       </c>
       <c r="I95" t="n">
-        <v>15</v>
+        <v>9.99</v>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -5121,7 +5121,7 @@
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>1.83</v>
+        <v>-0.33</v>
       </c>
       <c r="Q95" t="inlineStr"/>
     </row>
@@ -5150,7 +5150,7 @@
         <v>34.78</v>
       </c>
       <c r="H96" t="n">
-        <v>29.51</v>
+        <v>30.02</v>
       </c>
       <c r="I96" t="n">
         <v>10</v>
@@ -5170,18 +5170,18 @@
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>-1.52</v>
+        <v>-1.37</v>
       </c>
       <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="n">
-        <v>1824477589</v>
+        <v>1648737122</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5190,19 +5190,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.2344</v>
+        <v>0.0269</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>45792.64732982639</v>
+        <v>45695.85619950231</v>
       </c>
       <c r="G97" t="n">
-        <v>42.66</v>
+        <v>408.33</v>
       </c>
       <c r="H97" t="n">
-        <v>43.41</v>
+        <v>460.45</v>
       </c>
       <c r="I97" t="n">
-        <v>10</v>
+        <v>10.98</v>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
@@ -5219,18 +5219,18 @@
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>0.18</v>
+        <v>1.41</v>
       </c>
       <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="n">
-        <v>1727574394</v>
+        <v>1648733962</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5239,19 +5239,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1</v>
+        <v>0.081</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>45743.76658678241</v>
+        <v>45695.85463682871</v>
       </c>
       <c r="G98" t="n">
-        <v>21.13</v>
+        <v>129.56</v>
       </c>
       <c r="H98" t="n">
-        <v>21.8</v>
+        <v>142.76</v>
       </c>
       <c r="I98" t="n">
-        <v>21.13</v>
+        <v>10.49</v>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
@@ -5268,18 +5268,18 @@
         <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>0.67</v>
+        <v>1.07</v>
       </c>
       <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="n">
-        <v>1517514880</v>
+        <v>1680994777</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5288,19 +5288,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.0231</v>
+        <v>0.7278</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>45597.61087239583</v>
+        <v>45716.85705375</v>
       </c>
       <c r="G99" t="n">
-        <v>409.38</v>
+        <v>20.6</v>
       </c>
       <c r="H99" t="n">
-        <v>454.92</v>
+        <v>17.3</v>
       </c>
       <c r="I99" t="n">
-        <v>9.460000000000001</v>
+        <v>14.99</v>
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
@@ -5317,18 +5317,18 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>1.05</v>
+        <v>-2.4</v>
       </c>
       <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="n">
-        <v>1599435465</v>
+        <v>1517514880</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5337,19 +5337,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.0289</v>
+        <v>0.0231</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>45663.73115600694</v>
+        <v>45597.61087239583</v>
       </c>
       <c r="G100" t="n">
-        <v>517.7</v>
+        <v>409.38</v>
       </c>
       <c r="H100" t="n">
-        <v>569.85</v>
+        <v>460.45</v>
       </c>
       <c r="I100" t="n">
-        <v>14.96</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
@@ -5366,27 +5366,45 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>1.51</v>
+        <v>1.18</v>
       </c>
       <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
+      <c r="B101" t="n">
+        <v>1776193271</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>BCS</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>0.6724</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>45764.85451520833</v>
+      </c>
+      <c r="G101" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="H101" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="I101" t="n">
+        <v>10</v>
+      </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
       <c r="M101" t="n">
         <v>0</v>
       </c>
@@ -5397,9 +5415,285 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>45.65</v>
+        <v>2.02</v>
       </c>
       <c r="Q101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="n">
+        <v>1744916497</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ING</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>45751.74231563658</v>
+      </c>
+      <c r="G102" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="H102" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="I102" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="Q102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="n">
+        <v>1825032062</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>AGIO</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>45792.76080334491</v>
+      </c>
+      <c r="G103" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="H103" t="n">
+        <v>30.02</v>
+      </c>
+      <c r="I103" t="n">
+        <v>10</v>
+      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="Q103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="n">
+        <v>1533882988</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>BOTZ.L</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>45609.60769543982</v>
+      </c>
+      <c r="G104" t="n">
+        <v>21.905</v>
+      </c>
+      <c r="H104" t="n">
+        <v>20.66</v>
+      </c>
+      <c r="I104" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="Q104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="n">
+        <v>1843477152</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>BCS</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0.1198</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>45804.66724922453</v>
+      </c>
+      <c r="G105" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="H105" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="I105" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="n">
+        <v>1606697510</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0.0295</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>45667.68664726852</v>
+      </c>
+      <c r="G106" t="n">
+        <v>507.68</v>
+      </c>
+      <c r="H106" t="n">
+        <v>573.11</v>
+      </c>
+      <c r="I106" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>62.79</v>
+      </c>
+      <c r="Q107" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Stock Selection/OPEN POSITION.xlsx
+++ b/Stock Selection/OPEN POSITION.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q107"/>
+  <dimension ref="A1:Q110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,7 +544,7 @@
         <v>15.3</v>
       </c>
       <c r="H2" t="n">
-        <v>21.3</v>
+        <v>20.97</v>
       </c>
       <c r="I2" t="n">
         <v>5.35</v>
@@ -564,7 +564,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="Q2" t="inlineStr"/>
     </row>
@@ -593,7 +593,7 @@
         <v>34.55</v>
       </c>
       <c r="H3" t="n">
-        <v>32.31</v>
+        <v>31.46</v>
       </c>
       <c r="I3" t="n">
         <v>10</v>
@@ -613,7 +613,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.65</v>
+        <v>-0.9</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
@@ -642,7 +642,7 @@
         <v>16.425</v>
       </c>
       <c r="H4" t="n">
-        <v>15.394</v>
+        <v>15.382</v>
       </c>
       <c r="I4" t="n">
         <v>17.11</v>
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="Q4" t="inlineStr"/>
     </row>
@@ -691,7 +691,7 @@
         <v>36.1</v>
       </c>
       <c r="H5" t="n">
-        <v>36.44</v>
+        <v>36.95</v>
       </c>
       <c r="I5" t="n">
         <v>10</v>
@@ -711,7 +711,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="Q5" t="inlineStr"/>
     </row>
@@ -740,7 +740,7 @@
         <v>165.35</v>
       </c>
       <c r="H6" t="n">
-        <v>197.55</v>
+        <v>196.05</v>
       </c>
       <c r="I6" t="n">
         <v>15</v>
@@ -760,7 +760,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="Q6" t="inlineStr"/>
     </row>
@@ -789,7 +789,7 @@
         <v>15.57</v>
       </c>
       <c r="H7" t="n">
-        <v>17.88</v>
+        <v>17.63</v>
       </c>
       <c r="I7" t="n">
         <v>10</v>
@@ -809,7 +809,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="Q7" t="inlineStr"/>
     </row>
@@ -838,7 +838,7 @@
         <v>21.85</v>
       </c>
       <c r="H8" t="n">
-        <v>17.3</v>
+        <v>17.17</v>
       </c>
       <c r="I8" t="n">
         <v>10</v>
@@ -858,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.08</v>
+        <v>-2.14</v>
       </c>
       <c r="Q8" t="inlineStr"/>
     </row>
@@ -887,7 +887,7 @@
         <v>40.33</v>
       </c>
       <c r="H9" t="n">
-        <v>36.44</v>
+        <v>36.95</v>
       </c>
       <c r="I9" t="n">
         <v>10</v>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.97</v>
+        <v>-0.84</v>
       </c>
       <c r="Q9" t="inlineStr"/>
     </row>
@@ -936,7 +936,7 @@
         <v>127.16</v>
       </c>
       <c r="H10" t="n">
-        <v>139.38</v>
+        <v>137.42</v>
       </c>
       <c r="I10" t="n">
         <v>19.99</v>
@@ -956,7 +956,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.92</v>
+        <v>1.61</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
@@ -985,7 +985,7 @@
         <v>196.9</v>
       </c>
       <c r="H11" t="n">
-        <v>197.55</v>
+        <v>196.05</v>
       </c>
       <c r="I11" t="n">
         <v>14.98</v>
@@ -1005,7 +1005,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="Q11" t="inlineStr"/>
     </row>
@@ -1034,7 +1034,7 @@
         <v>33.66</v>
       </c>
       <c r="H12" t="n">
-        <v>32.31</v>
+        <v>31.46</v>
       </c>
       <c r="I12" t="n">
         <v>10</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4</v>
+        <v>-0.66</v>
       </c>
       <c r="Q12" t="inlineStr"/>
     </row>
@@ -1083,7 +1083,7 @@
         <v>77.53</v>
       </c>
       <c r="H13" t="n">
-        <v>68.01000000000001</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="I13" t="n">
         <v>14.99</v>
@@ -1103,7 +1103,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.84</v>
+        <v>-2</v>
       </c>
       <c r="Q13" t="inlineStr"/>
     </row>
@@ -1132,7 +1132,7 @@
         <v>160.64</v>
       </c>
       <c r="H14" t="n">
-        <v>172.84</v>
+        <v>172.3</v>
       </c>
       <c r="I14" t="n">
         <v>19.98</v>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="Q14" t="inlineStr"/>
     </row>
@@ -1181,7 +1181,7 @@
         <v>128.46</v>
       </c>
       <c r="H15" t="n">
-        <v>155.71</v>
+        <v>156.05</v>
       </c>
       <c r="I15" t="n">
         <v>11</v>
@@ -1201,7 +1201,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="Q15" t="inlineStr"/>
     </row>
@@ -1230,7 +1230,7 @@
         <v>20.62</v>
       </c>
       <c r="H16" t="n">
-        <v>17.3</v>
+        <v>17.17</v>
       </c>
       <c r="I16" t="n">
         <v>9.99</v>
@@ -1250,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.6</v>
+        <v>-1.67</v>
       </c>
       <c r="Q16" t="inlineStr"/>
     </row>
@@ -1279,7 +1279,7 @@
         <v>17.86</v>
       </c>
       <c r="H17" t="n">
-        <v>17.88</v>
+        <v>17.63</v>
       </c>
       <c r="I17" t="n">
         <v>17.86</v>
@@ -1299,7 +1299,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.02</v>
+        <v>-0.23</v>
       </c>
       <c r="Q17" t="inlineStr"/>
     </row>
@@ -1328,7 +1328,7 @@
         <v>21.31</v>
       </c>
       <c r="H18" t="n">
-        <v>17.3</v>
+        <v>17.17</v>
       </c>
       <c r="I18" t="n">
         <v>20</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.76</v>
+        <v>-3.89</v>
       </c>
       <c r="Q18" t="inlineStr"/>
     </row>
@@ -1377,7 +1377,7 @@
         <v>232.2</v>
       </c>
       <c r="H19" t="n">
-        <v>200.14</v>
+        <v>200.41</v>
       </c>
       <c r="I19" t="n">
         <v>0.02</v>
@@ -1426,7 +1426,7 @@
         <v>56.78</v>
       </c>
       <c r="H20" t="n">
-        <v>59.59</v>
+        <v>59.48</v>
       </c>
       <c r="I20" t="n">
         <v>15</v>
@@ -1446,7 +1446,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="Q20" t="inlineStr"/>
     </row>
@@ -1475,7 +1475,7 @@
         <v>20.58</v>
       </c>
       <c r="H21" t="n">
-        <v>20.66</v>
+        <v>20.41</v>
       </c>
       <c r="I21" t="n">
         <v>20.58</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.08</v>
+        <v>-0.17</v>
       </c>
       <c r="Q21" t="inlineStr"/>
     </row>
@@ -1524,7 +1524,7 @@
         <v>524.4299999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>573.11</v>
+        <v>575.73</v>
       </c>
       <c r="I22" t="n">
         <v>0.52</v>
@@ -1544,7 +1544,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="Q22" t="inlineStr"/>
     </row>
@@ -1573,7 +1573,7 @@
         <v>30.54</v>
       </c>
       <c r="H23" t="n">
-        <v>30.02</v>
+        <v>30.82</v>
       </c>
       <c r="I23" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.17</v>
+        <v>0.09</v>
       </c>
       <c r="Q23" t="inlineStr"/>
     </row>
@@ -1622,7 +1622,7 @@
         <v>147.48</v>
       </c>
       <c r="H24" t="n">
-        <v>142.76</v>
+        <v>142.67</v>
       </c>
       <c r="I24" t="n">
         <v>3.41</v>
@@ -1671,7 +1671,7 @@
         <v>74.13</v>
       </c>
       <c r="H25" t="n">
-        <v>72.51000000000001</v>
+        <v>72.38</v>
       </c>
       <c r="I25" t="n">
         <v>74.13</v>
@@ -1691,7 +1691,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.62</v>
+        <v>-1.75</v>
       </c>
       <c r="Q25" t="inlineStr"/>
     </row>
@@ -1720,7 +1720,7 @@
         <v>38.23</v>
       </c>
       <c r="H26" t="n">
-        <v>32.31</v>
+        <v>31.46</v>
       </c>
       <c r="I26" t="n">
         <v>19.98</v>
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-3.09</v>
+        <v>-3.54</v>
       </c>
       <c r="Q26" t="inlineStr"/>
     </row>
@@ -1769,7 +1769,7 @@
         <v>165.93</v>
       </c>
       <c r="H27" t="n">
-        <v>131.35</v>
+        <v>130.65</v>
       </c>
       <c r="I27" t="n">
         <v>17.94</v>
@@ -1789,7 +1789,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>-3.73</v>
+        <v>-3.81</v>
       </c>
       <c r="Q27" t="inlineStr"/>
     </row>
@@ -1818,7 +1818,7 @@
         <v>27.17</v>
       </c>
       <c r="H28" t="n">
-        <v>36.44</v>
+        <v>36.95</v>
       </c>
       <c r="I28" t="n">
         <v>9.98</v>
@@ -1838,7 +1838,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3.4</v>
+        <v>3.59</v>
       </c>
       <c r="Q28" t="inlineStr"/>
     </row>
@@ -1867,7 +1867,7 @@
         <v>77.34999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>68.01000000000001</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="I29" t="n">
         <v>19.99</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>-2.41</v>
+        <v>-2.62</v>
       </c>
       <c r="Q29" t="inlineStr"/>
     </row>
@@ -1916,7 +1916,7 @@
         <v>129.17</v>
       </c>
       <c r="H30" t="n">
-        <v>131.35</v>
+        <v>130.65</v>
       </c>
       <c r="I30" t="n">
         <v>20</v>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="Q30" t="inlineStr"/>
     </row>
@@ -1965,7 +1965,7 @@
         <v>12.75</v>
       </c>
       <c r="H31" t="n">
-        <v>13.54</v>
+        <v>13.26</v>
       </c>
       <c r="I31" t="n">
         <v>14.49</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.77</v>
+        <v>0.4</v>
       </c>
       <c r="Q31" t="inlineStr"/>
     </row>
@@ -2014,7 +2014,7 @@
         <v>24.11</v>
       </c>
       <c r="H32" t="n">
-        <v>17.3</v>
+        <v>17.17</v>
       </c>
       <c r="I32" t="n">
         <v>9.99</v>
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>-2.82</v>
+        <v>-2.87</v>
       </c>
       <c r="Q32" t="inlineStr"/>
     </row>
@@ -2063,7 +2063,7 @@
         <v>156.9</v>
       </c>
       <c r="H33" t="n">
-        <v>155.71</v>
+        <v>156.05</v>
       </c>
       <c r="I33" t="n">
         <v>15</v>
@@ -2083,7 +2083,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="Q33" t="inlineStr"/>
     </row>
@@ -2112,7 +2112,7 @@
         <v>52.83</v>
       </c>
       <c r="H34" t="n">
-        <v>59.59</v>
+        <v>59.48</v>
       </c>
       <c r="I34" t="n">
         <v>15</v>
@@ -2132,7 +2132,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="Q34" t="inlineStr"/>
     </row>
@@ -2161,7 +2161,7 @@
         <v>130.51</v>
       </c>
       <c r="H35" t="n">
-        <v>143.97</v>
+        <v>143.07</v>
       </c>
       <c r="I35" t="n">
         <v>0.04</v>
@@ -2188,11 +2188,11 @@
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>1633116336</v>
+        <v>1845429980</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2204,16 +2204,16 @@
         <v>1</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45686.83272234954</v>
+        <v>45805.66181400463</v>
       </c>
       <c r="G36" t="n">
-        <v>44.24</v>
+        <v>13.27</v>
       </c>
       <c r="H36" t="n">
-        <v>47.61</v>
+        <v>13.26</v>
       </c>
       <c r="I36" t="n">
-        <v>44.24</v>
+        <v>15.09</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -2230,18 +2230,18 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>3.37</v>
+        <v>-0.2</v>
       </c>
       <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
-        <v>1381375440</v>
+        <v>1633116336</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2250,19 +2250,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.1057</v>
+        <v>1</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>45484.67118315972</v>
+        <v>45686.83272234954</v>
       </c>
       <c r="G37" t="n">
-        <v>189.11</v>
+        <v>44.24</v>
       </c>
       <c r="H37" t="n">
-        <v>197.55</v>
+        <v>47.33</v>
       </c>
       <c r="I37" t="n">
-        <v>19.99</v>
+        <v>44.24</v>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
@@ -2279,18 +2279,18 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.89</v>
+        <v>3.09</v>
       </c>
       <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>1806980482</v>
+        <v>1381375440</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2299,19 +2299,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.2406</v>
+        <v>0.1057</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45783.83189613426</v>
+        <v>45484.67118315972</v>
       </c>
       <c r="G38" t="n">
-        <v>16.12</v>
+        <v>189.11</v>
       </c>
       <c r="H38" t="n">
-        <v>17.88</v>
+        <v>196.05</v>
       </c>
       <c r="I38" t="n">
-        <v>3.88</v>
+        <v>19.99</v>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
@@ -2328,18 +2328,18 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.42</v>
+        <v>0.73</v>
       </c>
       <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
-        <v>1680991980</v>
+        <v>1806980482</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2348,19 +2348,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.1958</v>
+        <v>0.2406</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45716.8556621875</v>
+        <v>45783.83189613426</v>
       </c>
       <c r="G39" t="n">
-        <v>178.67</v>
+        <v>16.12</v>
       </c>
       <c r="H39" t="n">
-        <v>197.55</v>
+        <v>17.63</v>
       </c>
       <c r="I39" t="n">
-        <v>34.98</v>
+        <v>3.88</v>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -2377,18 +2377,18 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>3.7</v>
+        <v>0.36</v>
       </c>
       <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="n">
-        <v>1843470413</v>
+        <v>1680991980</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2397,19 +2397,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.4729</v>
+        <v>0.1958</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>45804.66637251157</v>
+        <v>45716.8556621875</v>
       </c>
       <c r="G40" t="n">
-        <v>42.29</v>
+        <v>178.67</v>
       </c>
       <c r="H40" t="n">
-        <v>42.18</v>
+        <v>196.05</v>
       </c>
       <c r="I40" t="n">
-        <v>20</v>
+        <v>34.98</v>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
@@ -2426,18 +2426,18 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>-0.05</v>
+        <v>3.41</v>
       </c>
       <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="n">
-        <v>1662993636</v>
+        <v>1843470413</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2446,19 +2446,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0.4729</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45706.87026833333</v>
+        <v>45804.66637251157</v>
       </c>
       <c r="G41" t="n">
-        <v>20.65</v>
+        <v>42.29</v>
       </c>
       <c r="H41" t="n">
-        <v>22.18</v>
+        <v>42.16</v>
       </c>
       <c r="I41" t="n">
-        <v>20.65</v>
+        <v>20</v>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
@@ -2475,18 +2475,18 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.53</v>
+        <v>-0.06</v>
       </c>
       <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="n">
-        <v>1481609355</v>
+        <v>1662993636</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2495,19 +2495,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.107</v>
+        <v>1</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>45568.7734872338</v>
+        <v>45706.87026833333</v>
       </c>
       <c r="G42" t="n">
-        <v>140.18</v>
+        <v>20.65</v>
       </c>
       <c r="H42" t="n">
-        <v>142.76</v>
+        <v>22.16</v>
       </c>
       <c r="I42" t="n">
-        <v>15</v>
+        <v>20.65</v>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -2524,18 +2524,18 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0.28</v>
+        <v>1.51</v>
       </c>
       <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="n">
-        <v>1744767540</v>
+        <v>1481609355</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2544,19 +2544,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.643</v>
+        <v>0.107</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>45751.72316712963</v>
+        <v>45568.7734872338</v>
       </c>
       <c r="G43" t="n">
-        <v>15.55</v>
+        <v>140.18</v>
       </c>
       <c r="H43" t="n">
-        <v>17.3</v>
+        <v>142.67</v>
       </c>
       <c r="I43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -2573,18 +2573,18 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.12</v>
+        <v>0.27</v>
       </c>
       <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
-        <v>1817256440</v>
+        <v>1744767540</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2593,16 +2593,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.2267</v>
+        <v>0.643</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45789.64787115741</v>
+        <v>45751.72316712963</v>
       </c>
       <c r="G44" t="n">
-        <v>44.1</v>
+        <v>15.55</v>
       </c>
       <c r="H44" t="n">
-        <v>43.88</v>
+        <v>17.17</v>
       </c>
       <c r="I44" t="n">
         <v>10</v>
@@ -2622,18 +2622,18 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>-0.05</v>
+        <v>1.04</v>
       </c>
       <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>1843468958</v>
+        <v>1817256440</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2642,19 +2642,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.2208</v>
+        <v>0.2267</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>45804.66597149306</v>
+        <v>45789.64787115741</v>
       </c>
       <c r="G45" t="n">
-        <v>67.93000000000001</v>
+        <v>44.1</v>
       </c>
       <c r="H45" t="n">
-        <v>68.01000000000001</v>
+        <v>43.27</v>
       </c>
       <c r="I45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -2671,18 +2671,18 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.02</v>
+        <v>-0.19</v>
       </c>
       <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>1532661507</v>
+        <v>1843468958</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2691,19 +2691,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.2208</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>45608.74251107639</v>
+        <v>45804.66597149306</v>
       </c>
       <c r="G46" t="n">
-        <v>190.67</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>197.55</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>12.98</v>
+        <v>15</v>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -2720,18 +2720,18 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.47</v>
+        <v>-0.16</v>
       </c>
       <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>1583696868</v>
+        <v>1532661507</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BOTZ.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2740,19 +2740,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.5</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>45646.60053979167</v>
+        <v>45608.74251107639</v>
       </c>
       <c r="G47" t="n">
-        <v>20.645</v>
+        <v>190.67</v>
       </c>
       <c r="H47" t="n">
-        <v>20.66</v>
+        <v>196.05</v>
       </c>
       <c r="I47" t="n">
-        <v>10.32</v>
+        <v>12.98</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -2769,18 +2769,18 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0.01</v>
+        <v>0.37</v>
       </c>
       <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>1712849726</v>
+        <v>1583696868</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>BOTZ.L</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2789,19 +2789,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.0861</v>
+        <v>0.5</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>45734.85489405093</v>
+        <v>45646.60053979167</v>
       </c>
       <c r="G48" t="n">
-        <v>127.72</v>
+        <v>20.645</v>
       </c>
       <c r="H48" t="n">
-        <v>155.71</v>
+        <v>20.41</v>
       </c>
       <c r="I48" t="n">
-        <v>11</v>
+        <v>10.32</v>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -2818,18 +2818,18 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.41</v>
+        <v>-0.11</v>
       </c>
       <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
-        <v>1582723120</v>
+        <v>1712849726</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2838,19 +2838,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.3755</v>
+        <v>0.0861</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45645.89511640046</v>
+        <v>45734.85489405093</v>
       </c>
       <c r="G49" t="n">
-        <v>53.26</v>
+        <v>127.72</v>
       </c>
       <c r="H49" t="n">
-        <v>59.59</v>
+        <v>156.05</v>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
@@ -2867,18 +2867,18 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
-        <v>1806979127</v>
+        <v>1582723120</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.6361</v>
+        <v>0.3755</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>45783.83125244213</v>
+        <v>45645.89511640046</v>
       </c>
       <c r="G50" t="n">
-        <v>15.72</v>
+        <v>53.26</v>
       </c>
       <c r="H50" t="n">
-        <v>17.3</v>
+        <v>59.48</v>
       </c>
       <c r="I50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -2916,18 +2916,18 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1</v>
+        <v>2.33</v>
       </c>
       <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>1727591551</v>
+        <v>1806979127</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2936,19 +2936,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0.6361</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>45743.77389555555</v>
+        <v>45783.83125244213</v>
       </c>
       <c r="G51" t="n">
-        <v>72.87</v>
+        <v>15.72</v>
       </c>
       <c r="H51" t="n">
-        <v>72.51000000000001</v>
+        <v>17.17</v>
       </c>
       <c r="I51" t="n">
-        <v>72.87</v>
+        <v>10</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -2965,18 +2965,18 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>-0.36</v>
+        <v>0.92</v>
       </c>
       <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
-        <v>1666459270</v>
+        <v>1727591551</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>BND</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2988,16 +2988,16 @@
         <v>1</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>45708.68166530092</v>
+        <v>45743.77389555555</v>
       </c>
       <c r="G52" t="n">
-        <v>17.18</v>
+        <v>72.87</v>
       </c>
       <c r="H52" t="n">
-        <v>21.3</v>
+        <v>72.38</v>
       </c>
       <c r="I52" t="n">
-        <v>17.18</v>
+        <v>72.87</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
@@ -3014,18 +3014,18 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>4.12</v>
+        <v>-0.49</v>
       </c>
       <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="n">
-        <v>1648740228</v>
+        <v>1666459270</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3034,19 +3034,19 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.0538</v>
+        <v>1</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>45695.85792408565</v>
+        <v>45708.68166530092</v>
       </c>
       <c r="G53" t="n">
-        <v>185.82</v>
+        <v>17.18</v>
       </c>
       <c r="H53" t="n">
-        <v>172.84</v>
+        <v>20.97</v>
       </c>
       <c r="I53" t="n">
-        <v>10</v>
+        <v>17.18</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
@@ -3063,18 +3063,18 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>-0.7</v>
+        <v>3.79</v>
       </c>
       <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="n">
-        <v>1631475148</v>
+        <v>1648740228</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3083,16 +3083,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.2592</v>
+        <v>0.0538</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>45685.83625201389</v>
+        <v>45695.85792408565</v>
       </c>
       <c r="G54" t="n">
-        <v>38.58</v>
+        <v>185.82</v>
       </c>
       <c r="H54" t="n">
-        <v>36.44</v>
+        <v>172.3</v>
       </c>
       <c r="I54" t="n">
         <v>10</v>
@@ -3112,18 +3112,18 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>-0.55</v>
+        <v>-0.73</v>
       </c>
       <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="n">
-        <v>1644796307</v>
+        <v>1631475148</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3132,19 +3132,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>0.2592</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>45693.85501710648</v>
+        <v>45685.83625201389</v>
       </c>
       <c r="G55" t="n">
-        <v>20.36</v>
+        <v>38.58</v>
       </c>
       <c r="H55" t="n">
-        <v>22.18</v>
+        <v>36.95</v>
       </c>
       <c r="I55" t="n">
-        <v>20.36</v>
+        <v>10</v>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
@@ -3161,18 +3161,18 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>1.82</v>
+        <v>-0.42</v>
       </c>
       <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="n">
-        <v>1517510856</v>
+        <v>1644796307</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3181,19 +3181,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.0602</v>
+        <v>1</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>45597.61014849537</v>
+        <v>45693.85501710648</v>
       </c>
       <c r="G56" t="n">
-        <v>166.03</v>
+        <v>20.36</v>
       </c>
       <c r="H56" t="n">
-        <v>131.35</v>
+        <v>22.16</v>
       </c>
       <c r="I56" t="n">
-        <v>10</v>
+        <v>20.36</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
@@ -3210,18 +3210,18 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>-2.09</v>
+        <v>1.8</v>
       </c>
       <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="n">
-        <v>1680993370</v>
+        <v>1517510856</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3230,19 +3230,19 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0.0602</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45716.85638861111</v>
+        <v>45597.61014849537</v>
       </c>
       <c r="G57" t="n">
-        <v>44.49</v>
+        <v>166.03</v>
       </c>
       <c r="H57" t="n">
-        <v>47.61</v>
+        <v>130.65</v>
       </c>
       <c r="I57" t="n">
-        <v>44.49</v>
+        <v>10</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
@@ -3259,18 +3259,18 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>3.12</v>
+        <v>-2.13</v>
       </c>
       <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
-        <v>1843474191</v>
+        <v>1680993370</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3279,19 +3279,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.9372</v>
+        <v>1</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45804.66699503472</v>
+        <v>45716.85638861111</v>
       </c>
       <c r="G58" t="n">
-        <v>21.33</v>
+        <v>44.49</v>
       </c>
       <c r="H58" t="n">
-        <v>21.3</v>
+        <v>47.33</v>
       </c>
       <c r="I58" t="n">
-        <v>19.99</v>
+        <v>44.49</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
@@ -3308,18 +3308,18 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>-0.03</v>
+        <v>2.84</v>
       </c>
       <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="n">
-        <v>1422773288</v>
+        <v>1843474191</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3328,19 +3328,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.483</v>
+        <v>0.9372</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>45518.84428523148</v>
+        <v>45804.66699503472</v>
       </c>
       <c r="G59" t="n">
-        <v>51.24</v>
+        <v>21.33</v>
       </c>
       <c r="H59" t="n">
-        <v>59.59</v>
+        <v>20.97</v>
       </c>
       <c r="I59" t="n">
-        <v>24.75</v>
+        <v>19.99</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
@@ -3357,18 +3357,18 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>4.03</v>
+        <v>-0.34</v>
       </c>
       <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="n">
-        <v>1744916452</v>
+        <v>1422773288</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3377,19 +3377,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.4245</v>
+        <v>0.483</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45751.74230173611</v>
+        <v>45518.84428523148</v>
       </c>
       <c r="G60" t="n">
-        <v>17.54</v>
+        <v>51.24</v>
       </c>
       <c r="H60" t="n">
-        <v>21.3</v>
+        <v>59.48</v>
       </c>
       <c r="I60" t="n">
-        <v>7.45</v>
+        <v>24.75</v>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
@@ -3406,18 +3406,18 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>1.59</v>
+        <v>3.98</v>
       </c>
       <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="n">
-        <v>1824475555</v>
+        <v>1744916452</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3426,19 +3426,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>0.4245</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>45792.64702015046</v>
+        <v>45751.74230173611</v>
       </c>
       <c r="G61" t="n">
-        <v>21.66</v>
+        <v>17.54</v>
       </c>
       <c r="H61" t="n">
-        <v>22.18</v>
+        <v>20.97</v>
       </c>
       <c r="I61" t="n">
-        <v>21.66</v>
+        <v>7.45</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
@@ -3455,18 +3455,18 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>0.52</v>
+        <v>1.45</v>
       </c>
       <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="n">
-        <v>1806980496</v>
+        <v>1824475555</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3478,16 +3478,16 @@
         <v>1</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>45783.83190503472</v>
+        <v>45792.64702015046</v>
       </c>
       <c r="G62" t="n">
-        <v>16.12</v>
+        <v>21.66</v>
       </c>
       <c r="H62" t="n">
-        <v>17.88</v>
+        <v>22.16</v>
       </c>
       <c r="I62" t="n">
-        <v>16.12</v>
+        <v>21.66</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
@@ -3504,18 +3504,18 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>1.76</v>
+        <v>0.5</v>
       </c>
       <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="n">
-        <v>1599435465</v>
+        <v>1806980496</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3524,19 +3524,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.0289</v>
+        <v>1</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>45663.73115600694</v>
+        <v>45783.83190503472</v>
       </c>
       <c r="G63" t="n">
-        <v>517.7</v>
+        <v>16.12</v>
       </c>
       <c r="H63" t="n">
-        <v>573.11</v>
+        <v>17.63</v>
       </c>
       <c r="I63" t="n">
-        <v>14.96</v>
+        <v>16.12</v>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
@@ -3553,18 +3553,18 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="n">
-        <v>1559803221</v>
+        <v>1599435465</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3573,19 +3573,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.092</v>
+        <v>0.0289</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>45628.85951927083</v>
+        <v>45663.73115600694</v>
       </c>
       <c r="G64" t="n">
-        <v>162.85</v>
+        <v>517.7</v>
       </c>
       <c r="H64" t="n">
-        <v>131.35</v>
+        <v>575.73</v>
       </c>
       <c r="I64" t="n">
-        <v>14.98</v>
+        <v>14.96</v>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
@@ -3602,18 +3602,18 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>-2.9</v>
+        <v>1.68</v>
       </c>
       <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="n">
-        <v>1666451221</v>
+        <v>1559803221</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3622,19 +3622,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.0001</v>
+        <v>0.092</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>45708.68022634259</v>
+        <v>45628.85951927083</v>
       </c>
       <c r="G65" t="n">
-        <v>43</v>
+        <v>162.85</v>
       </c>
       <c r="H65" t="n">
-        <v>43.88</v>
+        <v>130.65</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>14.98</v>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
@@ -3651,18 +3651,18 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>-2.96</v>
       </c>
       <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="n">
-        <v>1701100481</v>
+        <v>1666451221</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3671,19 +3671,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.0873</v>
+        <v>0.0001</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>45727.87214378472</v>
+        <v>45708.68022634259</v>
       </c>
       <c r="G66" t="n">
-        <v>171.67</v>
+        <v>43</v>
       </c>
       <c r="H66" t="n">
-        <v>197.55</v>
+        <v>43.27</v>
       </c>
       <c r="I66" t="n">
-        <v>14.99</v>
+        <v>0</v>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
@@ -3700,18 +3700,18 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="n">
-        <v>1599455288</v>
+        <v>1701100481</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3720,19 +3720,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.2195</v>
+        <v>0.0873</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>45663.73750263889</v>
+        <v>45727.87214378472</v>
       </c>
       <c r="G67" t="n">
-        <v>45.55</v>
+        <v>171.67</v>
       </c>
       <c r="H67" t="n">
-        <v>36.44</v>
+        <v>196.05</v>
       </c>
       <c r="I67" t="n">
-        <v>10</v>
+        <v>14.99</v>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
@@ -3749,18 +3749,18 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>-2</v>
+        <v>2.13</v>
       </c>
       <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="n">
-        <v>1811475599</v>
+        <v>1599455288</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3769,19 +3769,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.7256</v>
+        <v>0.2195</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>45785.66972070602</v>
+        <v>45663.73750263889</v>
       </c>
       <c r="G68" t="n">
-        <v>12.75</v>
+        <v>45.55</v>
       </c>
       <c r="H68" t="n">
-        <v>13.54</v>
+        <v>36.95</v>
       </c>
       <c r="I68" t="n">
-        <v>10.51</v>
+        <v>10</v>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
@@ -3798,18 +3798,18 @@
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.89</v>
       </c>
       <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="n">
-        <v>1727563010</v>
+        <v>1811475599</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3818,19 +3818,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>0.7256</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>45743.76106726852</v>
+        <v>45785.66972070602</v>
       </c>
       <c r="G69" t="n">
-        <v>46.11</v>
+        <v>12.75</v>
       </c>
       <c r="H69" t="n">
-        <v>47.61</v>
+        <v>13.26</v>
       </c>
       <c r="I69" t="n">
-        <v>46.11</v>
+        <v>10.51</v>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
@@ -3847,18 +3847,18 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="n">
-        <v>1644789287</v>
+        <v>1727563010</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3867,19 +3867,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.0813</v>
+        <v>1</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>45693.85123056713</v>
+        <v>45743.76106726852</v>
       </c>
       <c r="G70" t="n">
-        <v>129.08</v>
+        <v>46.11</v>
       </c>
       <c r="H70" t="n">
-        <v>142.76</v>
+        <v>47.33</v>
       </c>
       <c r="I70" t="n">
-        <v>10.49</v>
+        <v>46.11</v>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
@@ -3896,18 +3896,18 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="n">
-        <v>1621495187</v>
+        <v>1644789287</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3916,19 +3916,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.2318</v>
+        <v>0.0813</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>45678.83178196759</v>
+        <v>45693.85123056713</v>
       </c>
       <c r="G71" t="n">
-        <v>43.27</v>
+        <v>129.08</v>
       </c>
       <c r="H71" t="n">
-        <v>36.44</v>
+        <v>142.67</v>
       </c>
       <c r="I71" t="n">
-        <v>10.03</v>
+        <v>10.49</v>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
@@ -3945,18 +3945,18 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>-1.58</v>
+        <v>1.11</v>
       </c>
       <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="n">
-        <v>1644788775</v>
+        <v>1621495187</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3965,19 +3965,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.2318</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>45693.85093391204</v>
+        <v>45678.83178196759</v>
       </c>
       <c r="G72" t="n">
-        <v>144.94</v>
+        <v>43.27</v>
       </c>
       <c r="H72" t="n">
-        <v>131.35</v>
+        <v>36.95</v>
       </c>
       <c r="I72" t="n">
-        <v>10.99</v>
+        <v>10.03</v>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -3994,18 +3994,18 @@
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>-1.03</v>
+        <v>-1.46</v>
       </c>
       <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="n">
-        <v>1495551484</v>
+        <v>1644788775</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4014,19 +4014,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.1914</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45580.70648087963</v>
+        <v>45693.85093391204</v>
       </c>
       <c r="G73" t="n">
-        <v>135.82</v>
+        <v>144.94</v>
       </c>
       <c r="H73" t="n">
-        <v>139.38</v>
+        <v>130.65</v>
       </c>
       <c r="I73" t="n">
-        <v>26</v>
+        <v>10.99</v>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
@@ -4043,18 +4043,18 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>0.68</v>
+        <v>-1.09</v>
       </c>
       <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="n">
-        <v>1830408508</v>
+        <v>1495551484</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4063,19 +4063,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.5793</v>
+        <v>0.1914</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45796.82346997685</v>
+        <v>45580.70648087963</v>
       </c>
       <c r="G74" t="n">
-        <v>17.26</v>
+        <v>135.82</v>
       </c>
       <c r="H74" t="n">
-        <v>17.3</v>
+        <v>137.42</v>
       </c>
       <c r="I74" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
@@ -4092,18 +4092,18 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>0.02</v>
+        <v>0.3</v>
       </c>
       <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="n">
-        <v>1563288050</v>
+        <v>1830408508</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4112,16 +4112,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.0626</v>
+        <v>0.5793</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>45630.85583428241</v>
+        <v>45796.82346997685</v>
       </c>
       <c r="G75" t="n">
-        <v>159.74</v>
+        <v>17.26</v>
       </c>
       <c r="H75" t="n">
-        <v>131.35</v>
+        <v>17.17</v>
       </c>
       <c r="I75" t="n">
         <v>10</v>
@@ -4141,18 +4141,18 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>-1.78</v>
+        <v>-0.05</v>
       </c>
       <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="n">
-        <v>1701100027</v>
+        <v>1563288050</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4161,19 +4161,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.7812</v>
+        <v>0.0626</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>45727.87202070602</v>
+        <v>45630.85583428241</v>
       </c>
       <c r="G76" t="n">
-        <v>19.2</v>
+        <v>159.74</v>
       </c>
       <c r="H76" t="n">
-        <v>17.3</v>
+        <v>130.65</v>
       </c>
       <c r="I76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
@@ -4190,18 +4190,18 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>-1.49</v>
+        <v>-1.82</v>
       </c>
       <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="n">
-        <v>1744929368</v>
+        <v>1845429956</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4210,19 +4210,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.0192</v>
+        <v>0.6565</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>45751.74500871528</v>
+        <v>45805.66180811343</v>
       </c>
       <c r="G77" t="n">
-        <v>324.48</v>
+        <v>13.275</v>
       </c>
       <c r="H77" t="n">
-        <v>358.47</v>
+        <v>13.26</v>
       </c>
       <c r="I77" t="n">
-        <v>6.23</v>
+        <v>9.91</v>
       </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
@@ -4239,18 +4239,18 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>0.65</v>
+        <v>-0.13</v>
       </c>
       <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="n">
-        <v>1599431096</v>
+        <v>1701100027</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4259,19 +4259,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.1013</v>
+        <v>0.7812</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>45663.73014731482</v>
+        <v>45727.87202070602</v>
       </c>
       <c r="G78" t="n">
-        <v>148.02</v>
+        <v>19.2</v>
       </c>
       <c r="H78" t="n">
-        <v>131.35</v>
+        <v>17.17</v>
       </c>
       <c r="I78" t="n">
-        <v>14.99</v>
+        <v>15</v>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
@@ -4288,18 +4288,18 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>-1.68</v>
+        <v>-1.59</v>
       </c>
       <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="n">
-        <v>1554742887</v>
+        <v>1744929368</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4308,19 +4308,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0192</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>45623.74993112269</v>
+        <v>45751.74500871528</v>
       </c>
       <c r="G79" t="n">
-        <v>178.48</v>
+        <v>324.48</v>
       </c>
       <c r="H79" t="n">
-        <v>197.55</v>
+        <v>359.84</v>
       </c>
       <c r="I79" t="n">
-        <v>14.99</v>
+        <v>6.23</v>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
@@ -4337,18 +4337,18 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>1.6</v>
+        <v>0.68</v>
       </c>
       <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="n">
-        <v>1666459175</v>
+        <v>1599431096</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4357,19 +4357,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.1641</v>
+        <v>0.1013</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>45708.68165298611</v>
+        <v>45663.73014731482</v>
       </c>
       <c r="G80" t="n">
-        <v>17.18</v>
+        <v>148.02</v>
       </c>
       <c r="H80" t="n">
-        <v>21.3</v>
+        <v>130.65</v>
       </c>
       <c r="I80" t="n">
-        <v>2.82</v>
+        <v>14.99</v>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
@@ -4386,18 +4386,18 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>0.68</v>
+        <v>-1.76</v>
       </c>
       <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="n">
-        <v>1824477589</v>
+        <v>1554742887</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4406,19 +4406,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.2344</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>45792.64732982639</v>
+        <v>45623.74993112269</v>
       </c>
       <c r="G81" t="n">
-        <v>42.66</v>
+        <v>178.48</v>
       </c>
       <c r="H81" t="n">
-        <v>43.88</v>
+        <v>196.05</v>
       </c>
       <c r="I81" t="n">
-        <v>10</v>
+        <v>14.99</v>
       </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
@@ -4435,18 +4435,18 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>0.29</v>
+        <v>1.48</v>
       </c>
       <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="n">
-        <v>1381417257</v>
+        <v>1666459175</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4455,19 +4455,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0.1641</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>45484.67877329861</v>
+        <v>45708.68165298611</v>
       </c>
       <c r="G82" t="n">
-        <v>16.374</v>
+        <v>17.18</v>
       </c>
       <c r="H82" t="n">
-        <v>15.394</v>
+        <v>20.97</v>
       </c>
       <c r="I82" t="n">
-        <v>17.9</v>
+        <v>2.82</v>
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
@@ -4484,18 +4484,18 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>-0.55</v>
+        <v>0.62</v>
       </c>
       <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="n">
-        <v>1806977521</v>
+        <v>1824477589</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4504,16 +4504,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.3367</v>
+        <v>0.2344</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>45783.8305750463</v>
+        <v>45792.64732982639</v>
       </c>
       <c r="G83" t="n">
-        <v>29.7</v>
+        <v>42.66</v>
       </c>
       <c r="H83" t="n">
-        <v>36.44</v>
+        <v>43.27</v>
       </c>
       <c r="I83" t="n">
         <v>10</v>
@@ -4533,18 +4533,18 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>2.27</v>
+        <v>0.14</v>
       </c>
       <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="n">
-        <v>1727574394</v>
+        <v>1381417257</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4556,16 +4556,16 @@
         <v>1</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>45743.76658678241</v>
+        <v>45484.67877329861</v>
       </c>
       <c r="G84" t="n">
-        <v>21.13</v>
+        <v>16.374</v>
       </c>
       <c r="H84" t="n">
-        <v>22.18</v>
+        <v>15.382</v>
       </c>
       <c r="I84" t="n">
-        <v>21.13</v>
+        <v>17.9</v>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
@@ -4582,18 +4582,18 @@
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>1.05</v>
+        <v>-0.62</v>
       </c>
       <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="n">
-        <v>1461331124</v>
+        <v>1806977521</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4602,19 +4602,19 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.3922</v>
+        <v>0.3367</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>45553.65374138889</v>
+        <v>45783.8305750463</v>
       </c>
       <c r="G85" t="n">
-        <v>50.99</v>
+        <v>29.7</v>
       </c>
       <c r="H85" t="n">
-        <v>59.59</v>
+        <v>36.95</v>
       </c>
       <c r="I85" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
@@ -4631,18 +4631,18 @@
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>3.37</v>
+        <v>2.44</v>
       </c>
       <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="n">
-        <v>1744879358</v>
+        <v>1727574394</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4651,19 +4651,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.2701</v>
+        <v>1</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>45751.73925940973</v>
+        <v>45743.76658678241</v>
       </c>
       <c r="G86" t="n">
-        <v>148.09</v>
+        <v>21.13</v>
       </c>
       <c r="H86" t="n">
-        <v>197.55</v>
+        <v>22.16</v>
       </c>
       <c r="I86" t="n">
-        <v>40</v>
+        <v>21.13</v>
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
@@ -4680,18 +4680,18 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>13.36</v>
+        <v>1.03</v>
       </c>
       <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="n">
-        <v>1662995258</v>
+        <v>1461331124</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4700,16 +4700,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.2943</v>
+        <v>0.3922</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>45706.87121422453</v>
+        <v>45553.65374138889</v>
       </c>
       <c r="G87" t="n">
-        <v>67.97</v>
+        <v>50.99</v>
       </c>
       <c r="H87" t="n">
-        <v>68.01000000000001</v>
+        <v>59.48</v>
       </c>
       <c r="I87" t="n">
         <v>20</v>
@@ -4729,18 +4729,18 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>0.02</v>
+        <v>3.33</v>
       </c>
       <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="n">
-        <v>1817264187</v>
+        <v>1744879358</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4749,19 +4749,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.4757</v>
+        <v>0.2701</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>45789.64859377315</v>
+        <v>45751.73925940973</v>
       </c>
       <c r="G88" t="n">
-        <v>42.02</v>
+        <v>148.09</v>
       </c>
       <c r="H88" t="n">
-        <v>42.18</v>
+        <v>196.05</v>
       </c>
       <c r="I88" t="n">
-        <v>19.99</v>
+        <v>40</v>
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
@@ -4778,18 +4778,18 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>0.08</v>
+        <v>12.95</v>
       </c>
       <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="n">
-        <v>1754304266</v>
+        <v>1662995258</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4798,19 +4798,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.7137</v>
+        <v>0.2943</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>45755.88055112268</v>
+        <v>45706.87121422453</v>
       </c>
       <c r="G89" t="n">
-        <v>14</v>
+        <v>67.97</v>
       </c>
       <c r="H89" t="n">
-        <v>17.3</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="I89" t="n">
-        <v>9.99</v>
+        <v>20</v>
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
@@ -4827,18 +4827,18 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>2.36</v>
+        <v>-0.22</v>
       </c>
       <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="n">
-        <v>1554741956</v>
+        <v>1817264187</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4847,19 +4847,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>0.4757</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>45623.74952237269</v>
+        <v>45789.64859377315</v>
       </c>
       <c r="G90" t="n">
-        <v>15.3</v>
+        <v>42.02</v>
       </c>
       <c r="H90" t="n">
-        <v>21.3</v>
+        <v>42.16</v>
       </c>
       <c r="I90" t="n">
-        <v>15.3</v>
+        <v>19.99</v>
       </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
@@ -4876,18 +4876,18 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>6</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="n">
-        <v>1701098878</v>
+        <v>1754304266</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4896,19 +4896,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.0383</v>
+        <v>0.7137</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>45727.87167594907</v>
+        <v>45755.88055112268</v>
       </c>
       <c r="G91" t="n">
-        <v>139.41</v>
+        <v>14</v>
       </c>
       <c r="H91" t="n">
-        <v>155.71</v>
+        <v>17.17</v>
       </c>
       <c r="I91" t="n">
-        <v>5.34</v>
+        <v>9.99</v>
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
@@ -4925,18 +4925,18 @@
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>0.62</v>
+        <v>2.26</v>
       </c>
       <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="n">
-        <v>1806978791</v>
+        <v>1554741956</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4945,19 +4945,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.0867</v>
+        <v>1</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>45783.83109655092</v>
+        <v>45623.74952237269</v>
       </c>
       <c r="G92" t="n">
-        <v>126.78</v>
+        <v>15.3</v>
       </c>
       <c r="H92" t="n">
-        <v>155.71</v>
+        <v>20.97</v>
       </c>
       <c r="I92" t="n">
-        <v>10.99</v>
+        <v>15.3</v>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
@@ -4974,18 +4974,18 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>2.51</v>
+        <v>5.67</v>
       </c>
       <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="n">
-        <v>1582708979</v>
+        <v>1701098878</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4994,19 +4994,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.0769</v>
+        <v>0.0383</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>45645.88746980324</v>
+        <v>45727.87167594907</v>
       </c>
       <c r="G93" t="n">
-        <v>195.11</v>
+        <v>139.41</v>
       </c>
       <c r="H93" t="n">
-        <v>197.55</v>
+        <v>156.05</v>
       </c>
       <c r="I93" t="n">
-        <v>15</v>
+        <v>5.34</v>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
@@ -5023,18 +5023,18 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>0.19</v>
+        <v>0.64</v>
       </c>
       <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="n">
-        <v>1559803984</v>
+        <v>1806978791</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5043,19 +5043,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.1076</v>
+        <v>0.0867</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>45628.86014383102</v>
+        <v>45783.83109655092</v>
       </c>
       <c r="G94" t="n">
-        <v>139.4</v>
+        <v>126.78</v>
       </c>
       <c r="H94" t="n">
-        <v>142.76</v>
+        <v>156.05</v>
       </c>
       <c r="I94" t="n">
-        <v>15</v>
+        <v>10.99</v>
       </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
@@ -5072,18 +5072,18 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>0.36</v>
+        <v>2.54</v>
       </c>
       <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="n">
-        <v>1666461140</v>
+        <v>1582708979</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5092,19 +5092,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.2651</v>
+        <v>0.0769</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>45708.68207092593</v>
+        <v>45645.88746980324</v>
       </c>
       <c r="G95" t="n">
-        <v>37.7</v>
+        <v>195.11</v>
       </c>
       <c r="H95" t="n">
-        <v>36.44</v>
+        <v>196.05</v>
       </c>
       <c r="I95" t="n">
-        <v>9.99</v>
+        <v>15</v>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -5121,18 +5121,18 @@
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>-0.33</v>
+        <v>0.08</v>
       </c>
       <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="n">
-        <v>1635194724</v>
+        <v>1559803984</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5141,19 +5141,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.2875</v>
+        <v>0.1076</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>45687.85271734954</v>
+        <v>45628.86014383102</v>
       </c>
       <c r="G96" t="n">
-        <v>34.78</v>
+        <v>139.4</v>
       </c>
       <c r="H96" t="n">
-        <v>30.02</v>
+        <v>142.67</v>
       </c>
       <c r="I96" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
@@ -5170,18 +5170,18 @@
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>-1.37</v>
+        <v>0.35</v>
       </c>
       <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="n">
-        <v>1648737122</v>
+        <v>1666461140</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5190,19 +5190,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.0269</v>
+        <v>0.2651</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>45695.85619950231</v>
+        <v>45708.68207092593</v>
       </c>
       <c r="G97" t="n">
-        <v>408.33</v>
+        <v>37.7</v>
       </c>
       <c r="H97" t="n">
-        <v>460.45</v>
+        <v>36.95</v>
       </c>
       <c r="I97" t="n">
-        <v>10.98</v>
+        <v>9.99</v>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
@@ -5219,18 +5219,18 @@
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>1.41</v>
+        <v>-0.19</v>
       </c>
       <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="n">
-        <v>1648733962</v>
+        <v>1635194724</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5239,19 +5239,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.081</v>
+        <v>0.2875</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>45695.85463682871</v>
+        <v>45687.85271734954</v>
       </c>
       <c r="G98" t="n">
-        <v>129.56</v>
+        <v>34.78</v>
       </c>
       <c r="H98" t="n">
-        <v>142.76</v>
+        <v>30.82</v>
       </c>
       <c r="I98" t="n">
-        <v>10.49</v>
+        <v>10</v>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
@@ -5268,18 +5268,18 @@
         <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>1.07</v>
+        <v>-1.14</v>
       </c>
       <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="n">
-        <v>1680994777</v>
+        <v>1648737122</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5288,19 +5288,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.7278</v>
+        <v>0.0269</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>45716.85705375</v>
+        <v>45695.85619950231</v>
       </c>
       <c r="G99" t="n">
-        <v>20.6</v>
+        <v>408.33</v>
       </c>
       <c r="H99" t="n">
-        <v>17.3</v>
+        <v>457.4</v>
       </c>
       <c r="I99" t="n">
-        <v>14.99</v>
+        <v>10.98</v>
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
@@ -5317,18 +5317,18 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>-2.4</v>
+        <v>1.32</v>
       </c>
       <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="n">
-        <v>1517514880</v>
+        <v>1648733962</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5337,19 +5337,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.0231</v>
+        <v>0.081</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>45597.61087239583</v>
+        <v>45695.85463682871</v>
       </c>
       <c r="G100" t="n">
-        <v>409.38</v>
+        <v>129.56</v>
       </c>
       <c r="H100" t="n">
-        <v>460.45</v>
+        <v>142.67</v>
       </c>
       <c r="I100" t="n">
-        <v>9.460000000000001</v>
+        <v>10.49</v>
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
@@ -5366,18 +5366,18 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="n">
-        <v>1776193271</v>
+        <v>1680994777</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5386,19 +5386,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.6724</v>
+        <v>0.7278</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>45764.85451520833</v>
+        <v>45716.85705375</v>
       </c>
       <c r="G101" t="n">
-        <v>14.87</v>
+        <v>20.6</v>
       </c>
       <c r="H101" t="n">
-        <v>17.88</v>
+        <v>17.17</v>
       </c>
       <c r="I101" t="n">
-        <v>10</v>
+        <v>14.99</v>
       </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -5415,18 +5415,18 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>2.02</v>
+        <v>-2.49</v>
       </c>
       <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="n">
-        <v>1744916497</v>
+        <v>1517514880</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5435,19 +5435,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1</v>
+        <v>0.0231</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>45751.74231563658</v>
+        <v>45597.61087239583</v>
       </c>
       <c r="G102" t="n">
-        <v>17.54</v>
+        <v>409.38</v>
       </c>
       <c r="H102" t="n">
-        <v>21.3</v>
+        <v>457.4</v>
       </c>
       <c r="I102" t="n">
-        <v>17.54</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
@@ -5464,18 +5464,18 @@
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>3.76</v>
+        <v>1.11</v>
       </c>
       <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="n">
-        <v>1825032062</v>
+        <v>1776193271</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5484,16 +5484,16 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.3559</v>
+        <v>0.6724</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>45792.76080334491</v>
+        <v>45764.85451520833</v>
       </c>
       <c r="G103" t="n">
-        <v>28.09</v>
+        <v>14.87</v>
       </c>
       <c r="H103" t="n">
-        <v>30.02</v>
+        <v>17.63</v>
       </c>
       <c r="I103" t="n">
         <v>10</v>
@@ -5513,18 +5513,18 @@
         <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>0.68</v>
+        <v>1.85</v>
       </c>
       <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="n">
-        <v>1533882988</v>
+        <v>1744916497</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BOTZ.L</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5533,19 +5533,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>45609.60769543982</v>
+        <v>45751.74231563658</v>
       </c>
       <c r="G104" t="n">
-        <v>21.905</v>
+        <v>17.54</v>
       </c>
       <c r="H104" t="n">
-        <v>20.66</v>
+        <v>20.97</v>
       </c>
       <c r="I104" t="n">
-        <v>10.95</v>
+        <v>17.54</v>
       </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
@@ -5562,18 +5562,18 @@
         <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>-0.62</v>
+        <v>3.43</v>
       </c>
       <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="n">
-        <v>1843477152</v>
+        <v>1825032062</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5582,19 +5582,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.1198</v>
+        <v>0.3559</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>45804.66724922453</v>
+        <v>45792.76080334491</v>
       </c>
       <c r="G105" t="n">
-        <v>17.86</v>
+        <v>28.09</v>
       </c>
       <c r="H105" t="n">
-        <v>17.88</v>
+        <v>30.82</v>
       </c>
       <c r="I105" t="n">
-        <v>2.14</v>
+        <v>10</v>
       </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
@@ -5611,18 +5611,18 @@
         <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="n">
-        <v>1606697510</v>
+        <v>1533882988</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>BOTZ.L</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5631,19 +5631,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.0295</v>
+        <v>0.5</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>45667.68664726852</v>
+        <v>45609.60769543982</v>
       </c>
       <c r="G106" t="n">
-        <v>507.68</v>
+        <v>21.905</v>
       </c>
       <c r="H106" t="n">
-        <v>573.11</v>
+        <v>20.41</v>
       </c>
       <c r="I106" t="n">
-        <v>14.98</v>
+        <v>10.95</v>
       </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
@@ -5660,27 +5660,45 @@
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>1.93</v>
+        <v>-0.74</v>
       </c>
       <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
+      <c r="B107" t="n">
+        <v>1843477152</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>BCS</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0.1198</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>45804.66724922453</v>
+      </c>
+      <c r="G107" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="H107" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="I107" t="n">
+        <v>2.14</v>
+      </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
       <c r="M107" t="n">
         <v>0</v>
       </c>
@@ -5691,9 +5709,138 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>62.79</v>
+        <v>-0.03</v>
       </c>
       <c r="Q107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="n">
+        <v>1606697510</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0.0295</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>45667.68664726852</v>
+      </c>
+      <c r="G108" t="n">
+        <v>507.68</v>
+      </c>
+      <c r="H108" t="n">
+        <v>575.73</v>
+      </c>
+      <c r="I108" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="n">
+        <v>1845431561</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>AGIO</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>45805.66210755787</v>
+      </c>
+      <c r="G109" t="n">
+        <v>30.57</v>
+      </c>
+      <c r="H109" t="n">
+        <v>30.82</v>
+      </c>
+      <c r="I109" t="n">
+        <v>10</v>
+      </c>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Q109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>53.71</v>
+      </c>
+      <c r="Q110" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Stock Selection/OPEN POSITION.xlsx
+++ b/Stock Selection/OPEN POSITION.xlsx
@@ -522,11 +522,11 @@
     <row r="2">
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="n">
-        <v>1554741910</v>
+        <v>1511085920</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.3495</v>
+        <v>0.0761</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45623.74951116898</v>
+        <v>45593.7262774074</v>
       </c>
       <c r="G2" t="n">
-        <v>15.3</v>
+        <v>196.9</v>
       </c>
       <c r="H2" t="n">
-        <v>20.97</v>
+        <v>193.28</v>
       </c>
       <c r="I2" t="n">
-        <v>5.35</v>
+        <v>14.98</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -564,18 +564,18 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.98</v>
+        <v>-0.27</v>
       </c>
       <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="n">
-        <v>1825032378</v>
+        <v>1642762235</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -584,19 +584,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.2894</v>
+        <v>0.1572</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45792.76093177083</v>
+        <v>45692.86612574074</v>
       </c>
       <c r="G3" t="n">
-        <v>34.55</v>
+        <v>127.16</v>
       </c>
       <c r="H3" t="n">
-        <v>31.46</v>
+        <v>139.03</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>19.99</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -613,18 +613,18 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9</v>
+        <v>1.87</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="n">
-        <v>1594315903</v>
+        <v>1554741956</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -636,16 +636,16 @@
         <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45659.42644752315</v>
+        <v>45623.74952237269</v>
       </c>
       <c r="G4" t="n">
-        <v>16.425</v>
+        <v>15.3</v>
       </c>
       <c r="H4" t="n">
-        <v>15.382</v>
+        <v>21.24</v>
       </c>
       <c r="I4" t="n">
-        <v>17.11</v>
+        <v>15.3</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -662,18 +662,18 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.17</v>
+        <v>5.94</v>
       </c>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="n">
-        <v>1653137218</v>
+        <v>1599449649</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.277</v>
+        <v>0.4145</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45699.85152199074</v>
+        <v>45663.73562525463</v>
       </c>
       <c r="G5" t="n">
-        <v>36.1</v>
+        <v>24.11</v>
       </c>
       <c r="H5" t="n">
-        <v>36.95</v>
+        <v>17</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -711,18 +711,18 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.24</v>
+        <v>-2.94</v>
       </c>
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="n">
-        <v>1729617775</v>
+        <v>1843477152</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0907</v>
+        <v>0.1198</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45744.71339734954</v>
+        <v>45804.66724922453</v>
       </c>
       <c r="G6" t="n">
-        <v>165.35</v>
+        <v>17.86</v>
       </c>
       <c r="H6" t="n">
-        <v>196.05</v>
+        <v>17.82</v>
       </c>
       <c r="I6" t="n">
-        <v>15</v>
+        <v>2.14</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -760,18 +760,18 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.78</v>
+        <v>-0.01</v>
       </c>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="n">
-        <v>1796453499</v>
+        <v>1662995258</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -780,19 +780,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6422</v>
+        <v>0.2943</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45777.64668229167</v>
+        <v>45706.87121422453</v>
       </c>
       <c r="G7" t="n">
-        <v>15.57</v>
+        <v>67.97</v>
       </c>
       <c r="H7" t="n">
-        <v>17.63</v>
+        <v>70.56</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -809,18 +809,18 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.32</v>
+        <v>0.77</v>
       </c>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>1648735305</v>
+        <v>1811475599</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.4576</v>
+        <v>0.7256</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45695.85530675926</v>
+        <v>45785.66972070602</v>
       </c>
       <c r="G8" t="n">
-        <v>21.85</v>
+        <v>12.75</v>
       </c>
       <c r="H8" t="n">
-        <v>17.17</v>
+        <v>13.225</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>10.51</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -858,18 +858,18 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.14</v>
+        <v>0.33</v>
       </c>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>1635194117</v>
+        <v>1599448103</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -878,19 +878,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.2479</v>
+        <v>0.2839</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45687.85228493056</v>
+        <v>45663.73506711805</v>
       </c>
       <c r="G9" t="n">
-        <v>40.33</v>
+        <v>52.83</v>
       </c>
       <c r="H9" t="n">
-        <v>36.95</v>
+        <v>60.5</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -907,18 +907,18 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.84</v>
+        <v>2.18</v>
       </c>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
-        <v>1642762235</v>
+        <v>1776193271</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.1572</v>
+        <v>0.6724</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45692.86612574074</v>
+        <v>45764.85451520833</v>
       </c>
       <c r="G10" t="n">
-        <v>127.16</v>
+        <v>14.87</v>
       </c>
       <c r="H10" t="n">
-        <v>137.42</v>
+        <v>17.82</v>
       </c>
       <c r="I10" t="n">
-        <v>19.99</v>
+        <v>10</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -956,18 +956,18 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.61</v>
+        <v>1.98</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
-        <v>1511085920</v>
+        <v>1817256440</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -976,19 +976,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.0761</v>
+        <v>0.2267</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45593.7262774074</v>
+        <v>45789.64787115741</v>
       </c>
       <c r="G11" t="n">
-        <v>196.9</v>
+        <v>44.1</v>
       </c>
       <c r="H11" t="n">
-        <v>196.05</v>
+        <v>43.82</v>
       </c>
       <c r="I11" t="n">
-        <v>14.98</v>
+        <v>10</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -1005,14 +1005,14 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>1830410729</v>
+        <v>1825032378</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1025,16 +1025,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.297</v>
+        <v>0.2894</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>45796.82476561343</v>
+        <v>45792.76093177083</v>
       </c>
       <c r="G12" t="n">
-        <v>33.66</v>
+        <v>34.55</v>
       </c>
       <c r="H12" t="n">
-        <v>31.46</v>
+        <v>31.09</v>
       </c>
       <c r="I12" t="n">
         <v>10</v>
@@ -1054,18 +1054,18 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.66</v>
+        <v>-1</v>
       </c>
       <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>1414752069</v>
+        <v>1744930699</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>BND</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1074,19 +1074,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.1933</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>45511.86049193287</v>
+        <v>45751.74534789352</v>
       </c>
       <c r="G13" t="n">
-        <v>77.53</v>
+        <v>74.13</v>
       </c>
       <c r="H13" t="n">
-        <v>67.20999999999999</v>
+        <v>72.75</v>
       </c>
       <c r="I13" t="n">
-        <v>14.99</v>
+        <v>74.13</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -1103,18 +1103,18 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-2</v>
+        <v>-1.38</v>
       </c>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="n">
-        <v>1712850989</v>
+        <v>1666457581</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.1244</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>45734.85576775463</v>
+        <v>45708.68135159722</v>
       </c>
       <c r="G14" t="n">
-        <v>160.64</v>
+        <v>38.23</v>
       </c>
       <c r="H14" t="n">
-        <v>172.3</v>
+        <v>31.09</v>
       </c>
       <c r="I14" t="n">
         <v>19.98</v>
@@ -1152,18 +1152,18 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.45</v>
+        <v>-3.73</v>
       </c>
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="n">
-        <v>1811432805</v>
+        <v>1727591551</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>BND</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.0856</v>
+        <v>1</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>45785.66143211805</v>
+        <v>45743.77389555555</v>
       </c>
       <c r="G15" t="n">
-        <v>128.46</v>
+        <v>72.87</v>
       </c>
       <c r="H15" t="n">
-        <v>156.05</v>
+        <v>72.75</v>
       </c>
       <c r="I15" t="n">
-        <v>11</v>
+        <v>72.87</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1201,14 +1201,14 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.36</v>
+        <v>-0.12</v>
       </c>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="n">
-        <v>1582714896</v>
+        <v>1648735305</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.4847</v>
+        <v>0.4576</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>45645.89066263889</v>
+        <v>45695.85530675926</v>
       </c>
       <c r="G16" t="n">
-        <v>20.62</v>
+        <v>21.85</v>
       </c>
       <c r="H16" t="n">
-        <v>17.17</v>
+        <v>17</v>
       </c>
       <c r="I16" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1250,18 +1250,18 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.67</v>
+        <v>-2.22</v>
       </c>
       <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="n">
-        <v>1843477272</v>
+        <v>1606697510</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1270,19 +1270,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0.0295</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>45804.66725678241</v>
+        <v>45667.68664726852</v>
       </c>
       <c r="G17" t="n">
-        <v>17.86</v>
+        <v>507.68</v>
       </c>
       <c r="H17" t="n">
-        <v>17.63</v>
+        <v>582.1799999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>17.86</v>
+        <v>14.98</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1299,18 +1299,18 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.23</v>
+        <v>2.19</v>
       </c>
       <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
-        <v>1566610015</v>
+        <v>1843469729</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9385</v>
+        <v>0.0956</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45632.87667083334</v>
+        <v>45804.66615450232</v>
       </c>
       <c r="G18" t="n">
-        <v>21.31</v>
+        <v>156.9</v>
       </c>
       <c r="H18" t="n">
-        <v>17.17</v>
+        <v>157.86</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1348,18 +1348,18 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.89</v>
+        <v>0.09</v>
       </c>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="n">
-        <v>1499061783</v>
+        <v>1517514880</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1368,19 +1368,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.0001</v>
+        <v>0.0231</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45582.73996892361</v>
+        <v>45597.61087239583</v>
       </c>
       <c r="G19" t="n">
-        <v>232.2</v>
+        <v>409.38</v>
       </c>
       <c r="H19" t="n">
-        <v>200.41</v>
+        <v>459.55</v>
       </c>
       <c r="I19" t="n">
-        <v>0.02</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1397,18 +1397,18 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
-        <v>1824482557</v>
+        <v>1644796307</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1417,19 +1417,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.2641</v>
+        <v>1</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45792.64805195602</v>
+        <v>45693.85501710648</v>
       </c>
       <c r="G20" t="n">
-        <v>56.78</v>
+        <v>20.36</v>
       </c>
       <c r="H20" t="n">
-        <v>59.48</v>
+        <v>22.23</v>
       </c>
       <c r="I20" t="n">
-        <v>15</v>
+        <v>20.36</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1446,14 +1446,14 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.71</v>
+        <v>1.87</v>
       </c>
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="n">
-        <v>1378901781</v>
+        <v>1583696868</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1466,19 +1466,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45482.71294556713</v>
+        <v>45646.60053979167</v>
       </c>
       <c r="G21" t="n">
-        <v>20.58</v>
+        <v>20.645</v>
       </c>
       <c r="H21" t="n">
-        <v>20.41</v>
+        <v>20.25</v>
       </c>
       <c r="I21" t="n">
-        <v>20.58</v>
+        <v>10.32</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1495,18 +1495,18 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.17</v>
+        <v>-0.19</v>
       </c>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="n">
-        <v>1582737192</v>
+        <v>1582723120</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1515,19 +1515,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.001</v>
+        <v>0.3755</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>45645.90143930555</v>
+        <v>45645.89511640046</v>
       </c>
       <c r="G22" t="n">
-        <v>524.4299999999999</v>
+        <v>53.26</v>
       </c>
       <c r="H22" t="n">
-        <v>575.73</v>
+        <v>60.5</v>
       </c>
       <c r="I22" t="n">
-        <v>0.52</v>
+        <v>20</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -1544,18 +1544,18 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.06</v>
+        <v>2.72</v>
       </c>
       <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="n">
-        <v>1727564345</v>
+        <v>1450043624</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.3274</v>
+        <v>0.0231</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>45743.76175270833</v>
+        <v>45544.65163525463</v>
       </c>
       <c r="G23" t="n">
-        <v>30.54</v>
+        <v>147.48</v>
       </c>
       <c r="H23" t="n">
-        <v>30.82</v>
+        <v>143.68</v>
       </c>
       <c r="I23" t="n">
-        <v>10</v>
+        <v>3.41</v>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -1593,18 +1593,18 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0.09</v>
+        <v>-0.09</v>
       </c>
       <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="n">
-        <v>1450043624</v>
+        <v>1806977521</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.0231</v>
+        <v>0.3367</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45544.65163525463</v>
+        <v>45783.8305750463</v>
       </c>
       <c r="G24" t="n">
-        <v>147.48</v>
+        <v>29.7</v>
       </c>
       <c r="H24" t="n">
-        <v>142.67</v>
+        <v>35.39</v>
       </c>
       <c r="I24" t="n">
-        <v>3.41</v>
+        <v>10</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1642,18 +1642,18 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.11</v>
+        <v>1.92</v>
       </c>
       <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="n">
-        <v>1744930699</v>
+        <v>1378901781</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>BOTZ.L</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1665,16 +1665,16 @@
         <v>1</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>45751.74534789352</v>
+        <v>45482.71294556713</v>
       </c>
       <c r="G25" t="n">
-        <v>74.13</v>
+        <v>20.58</v>
       </c>
       <c r="H25" t="n">
-        <v>72.38</v>
+        <v>20.25</v>
       </c>
       <c r="I25" t="n">
-        <v>74.13</v>
+        <v>20.58</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -1691,18 +1691,18 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.75</v>
+        <v>-0.33</v>
       </c>
       <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="n">
-        <v>1666457581</v>
+        <v>1727563010</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1711,19 +1711,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.5227000000000001</v>
+        <v>1</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>45708.68135159722</v>
+        <v>45743.76106726852</v>
       </c>
       <c r="G26" t="n">
-        <v>38.23</v>
+        <v>46.11</v>
       </c>
       <c r="H26" t="n">
-        <v>31.46</v>
+        <v>46.99</v>
       </c>
       <c r="I26" t="n">
-        <v>19.98</v>
+        <v>46.11</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -1740,14 +1740,14 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-3.54</v>
+        <v>0.88</v>
       </c>
       <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="n">
-        <v>1358151307</v>
+        <v>1824476420</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1760,19 +1760,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.1081</v>
+        <v>0.1548</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>45460.88529052083</v>
+        <v>45792.64714148148</v>
       </c>
       <c r="G27" t="n">
-        <v>165.93</v>
+        <v>129.17</v>
       </c>
       <c r="H27" t="n">
-        <v>130.65</v>
+        <v>131.36</v>
       </c>
       <c r="I27" t="n">
-        <v>17.94</v>
+        <v>20</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -1789,18 +1789,18 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>-3.81</v>
+        <v>0.33</v>
       </c>
       <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="n">
-        <v>1754302454</v>
+        <v>1666459175</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1809,19 +1809,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.3673</v>
+        <v>0.1641</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>45755.88025324074</v>
+        <v>45708.68165298611</v>
       </c>
       <c r="G28" t="n">
-        <v>27.17</v>
+        <v>17.18</v>
       </c>
       <c r="H28" t="n">
-        <v>36.95</v>
+        <v>21.24</v>
       </c>
       <c r="I28" t="n">
-        <v>9.98</v>
+        <v>2.82</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -1838,18 +1838,18 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3.59</v>
+        <v>0.67</v>
       </c>
       <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
-        <v>1559802942</v>
+        <v>1701100027</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1858,19 +1858,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.2585</v>
+        <v>0.7812</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>45628.85929152778</v>
+        <v>45727.87202070602</v>
       </c>
       <c r="G29" t="n">
-        <v>77.34999999999999</v>
+        <v>19.2</v>
       </c>
       <c r="H29" t="n">
-        <v>67.20999999999999</v>
+        <v>17</v>
       </c>
       <c r="I29" t="n">
-        <v>19.99</v>
+        <v>15</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -1887,18 +1887,18 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>-2.62</v>
+        <v>-1.72</v>
       </c>
       <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
-        <v>1824476420</v>
+        <v>1744916452</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1907,19 +1907,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.1548</v>
+        <v>0.4245</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45792.64714148148</v>
+        <v>45751.74230173611</v>
       </c>
       <c r="G30" t="n">
-        <v>129.17</v>
+        <v>17.54</v>
       </c>
       <c r="H30" t="n">
-        <v>130.65</v>
+        <v>21.24</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>7.45</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -1936,18 +1936,18 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0.22</v>
+        <v>1.57</v>
       </c>
       <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="n">
-        <v>1811475646</v>
+        <v>1830410729</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1956,19 +1956,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.297</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45785.66973634259</v>
+        <v>45796.82476561343</v>
       </c>
       <c r="G31" t="n">
-        <v>12.75</v>
+        <v>33.66</v>
       </c>
       <c r="H31" t="n">
-        <v>13.26</v>
+        <v>31.09</v>
       </c>
       <c r="I31" t="n">
-        <v>14.49</v>
+        <v>10</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1985,18 +1985,18 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.4</v>
+        <v>-0.77</v>
       </c>
       <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="n">
-        <v>1599449649</v>
+        <v>1648737122</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2005,19 +2005,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.4145</v>
+        <v>0.0269</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45663.73562525463</v>
+        <v>45695.85619950231</v>
       </c>
       <c r="G32" t="n">
-        <v>24.11</v>
+        <v>408.33</v>
       </c>
       <c r="H32" t="n">
-        <v>17.17</v>
+        <v>459.55</v>
       </c>
       <c r="I32" t="n">
-        <v>9.99</v>
+        <v>10.98</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -2034,18 +2034,18 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>-2.87</v>
+        <v>1.38</v>
       </c>
       <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="n">
-        <v>1843469729</v>
+        <v>1582714896</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2054,19 +2054,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.0956</v>
+        <v>0.4847</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45804.66615450232</v>
+        <v>45645.89066263889</v>
       </c>
       <c r="G33" t="n">
-        <v>156.9</v>
+        <v>20.62</v>
       </c>
       <c r="H33" t="n">
-        <v>156.05</v>
+        <v>17</v>
       </c>
       <c r="I33" t="n">
-        <v>15</v>
+        <v>9.99</v>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -2083,18 +2083,18 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>-0.08</v>
+        <v>-1.75</v>
       </c>
       <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="n">
-        <v>1599448103</v>
+        <v>1843468958</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2103,16 +2103,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.2839</v>
+        <v>0.2208</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45663.73506711805</v>
+        <v>45804.66597149306</v>
       </c>
       <c r="G34" t="n">
-        <v>52.83</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>59.48</v>
+        <v>70.56</v>
       </c>
       <c r="I34" t="n">
         <v>15</v>
@@ -2132,18 +2132,18 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.89</v>
+        <v>0.58</v>
       </c>
       <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>1582735114</v>
+        <v>1811432805</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2152,19 +2152,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.0003</v>
+        <v>0.0856</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>45645.90076803241</v>
+        <v>45785.66143211805</v>
       </c>
       <c r="G35" t="n">
-        <v>130.51</v>
+        <v>128.46</v>
       </c>
       <c r="H35" t="n">
-        <v>143.07</v>
+        <v>157.86</v>
       </c>
       <c r="I35" t="n">
-        <v>0.04</v>
+        <v>11</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
@@ -2181,18 +2181,18 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>1845429980</v>
+        <v>1559802942</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2201,19 +2201,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>0.2585</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45805.66181400463</v>
+        <v>45628.85929152778</v>
       </c>
       <c r="G36" t="n">
-        <v>13.27</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>13.26</v>
+        <v>70.56</v>
       </c>
       <c r="I36" t="n">
-        <v>15.09</v>
+        <v>19.99</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -2230,18 +2230,18 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>-0.2</v>
+        <v>-1.75</v>
       </c>
       <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
-        <v>1633116336</v>
+        <v>1644788775</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2250,19 +2250,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>45686.83272234954</v>
+        <v>45693.85093391204</v>
       </c>
       <c r="G37" t="n">
-        <v>44.24</v>
+        <v>144.94</v>
       </c>
       <c r="H37" t="n">
-        <v>47.33</v>
+        <v>131.36</v>
       </c>
       <c r="I37" t="n">
-        <v>44.24</v>
+        <v>10.99</v>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
@@ -2279,18 +2279,18 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3.09</v>
+        <v>-1.03</v>
       </c>
       <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>1381375440</v>
+        <v>1817264187</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2299,16 +2299,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.1057</v>
+        <v>0.4757</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45484.67118315972</v>
+        <v>45789.64859377315</v>
       </c>
       <c r="G38" t="n">
-        <v>189.11</v>
+        <v>42.02</v>
       </c>
       <c r="H38" t="n">
-        <v>196.05</v>
+        <v>41.16</v>
       </c>
       <c r="I38" t="n">
         <v>19.99</v>
@@ -2328,18 +2328,18 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.73</v>
+        <v>-0.41</v>
       </c>
       <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
-        <v>1806980482</v>
+        <v>1666451221</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2348,19 +2348,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.2406</v>
+        <v>0.0001</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45783.83189613426</v>
+        <v>45708.68022634259</v>
       </c>
       <c r="G39" t="n">
-        <v>16.12</v>
+        <v>43</v>
       </c>
       <c r="H39" t="n">
-        <v>17.63</v>
+        <v>43.82</v>
       </c>
       <c r="I39" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -2377,18 +2377,18 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="n">
-        <v>1680991980</v>
+        <v>1701098878</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2397,19 +2397,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.1958</v>
+        <v>0.0383</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>45716.8556621875</v>
+        <v>45727.87167594907</v>
       </c>
       <c r="G40" t="n">
-        <v>178.67</v>
+        <v>139.41</v>
       </c>
       <c r="H40" t="n">
-        <v>196.05</v>
+        <v>157.86</v>
       </c>
       <c r="I40" t="n">
-        <v>34.98</v>
+        <v>5.34</v>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
@@ -2426,18 +2426,18 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>3.41</v>
+        <v>0.71</v>
       </c>
       <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="n">
-        <v>1843470413</v>
+        <v>1806979127</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2446,19 +2446,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.4729</v>
+        <v>0.6361</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45804.66637251157</v>
+        <v>45783.83125244213</v>
       </c>
       <c r="G41" t="n">
-        <v>42.29</v>
+        <v>15.72</v>
       </c>
       <c r="H41" t="n">
-        <v>42.16</v>
+        <v>17</v>
       </c>
       <c r="I41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
@@ -2475,18 +2475,18 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>-0.06</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="n">
-        <v>1662993636</v>
+        <v>1381417257</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2498,16 +2498,16 @@
         <v>1</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>45706.87026833333</v>
+        <v>45484.67877329861</v>
       </c>
       <c r="G42" t="n">
-        <v>20.65</v>
+        <v>16.374</v>
       </c>
       <c r="H42" t="n">
-        <v>22.16</v>
+        <v>15.134</v>
       </c>
       <c r="I42" t="n">
-        <v>20.65</v>
+        <v>17.9</v>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -2524,18 +2524,18 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1.51</v>
+        <v>-0.8</v>
       </c>
       <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="n">
-        <v>1481609355</v>
+        <v>1680993370</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2544,19 +2544,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.107</v>
+        <v>1</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>45568.7734872338</v>
+        <v>45716.85638861111</v>
       </c>
       <c r="G43" t="n">
-        <v>140.18</v>
+        <v>44.49</v>
       </c>
       <c r="H43" t="n">
-        <v>142.67</v>
+        <v>46.99</v>
       </c>
       <c r="I43" t="n">
-        <v>15</v>
+        <v>44.49</v>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -2573,18 +2573,18 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0.27</v>
+        <v>2.5</v>
       </c>
       <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
-        <v>1744767540</v>
+        <v>1533882988</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>BOTZ.L</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2593,19 +2593,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.643</v>
+        <v>0.5</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45751.72316712963</v>
+        <v>45609.60769543982</v>
       </c>
       <c r="G44" t="n">
-        <v>15.55</v>
+        <v>21.905</v>
       </c>
       <c r="H44" t="n">
-        <v>17.17</v>
+        <v>20.25</v>
       </c>
       <c r="I44" t="n">
-        <v>10</v>
+        <v>10.95</v>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -2622,18 +2622,18 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1.04</v>
+        <v>-0.82</v>
       </c>
       <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>1817256440</v>
+        <v>1754302454</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2642,19 +2642,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.2267</v>
+        <v>0.3673</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>45789.64787115741</v>
+        <v>45755.88025324074</v>
       </c>
       <c r="G45" t="n">
-        <v>44.1</v>
+        <v>27.17</v>
       </c>
       <c r="H45" t="n">
-        <v>43.27</v>
+        <v>35.39</v>
       </c>
       <c r="I45" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -2671,18 +2671,18 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>-0.19</v>
+        <v>3.02</v>
       </c>
       <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>1843468958</v>
+        <v>1744879358</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2691,19 +2691,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.2208</v>
+        <v>0.2701</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>45804.66597149306</v>
+        <v>45751.73925940973</v>
       </c>
       <c r="G46" t="n">
-        <v>67.93000000000001</v>
+        <v>148.09</v>
       </c>
       <c r="H46" t="n">
-        <v>67.20999999999999</v>
+        <v>193.28</v>
       </c>
       <c r="I46" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -2720,18 +2720,18 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>-0.16</v>
+        <v>12.2</v>
       </c>
       <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>1532661507</v>
+        <v>1517510856</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2740,19 +2740,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0602</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>45608.74251107639</v>
+        <v>45597.61014849537</v>
       </c>
       <c r="G47" t="n">
-        <v>190.67</v>
+        <v>166.03</v>
       </c>
       <c r="H47" t="n">
-        <v>196.05</v>
+        <v>131.36</v>
       </c>
       <c r="I47" t="n">
-        <v>12.98</v>
+        <v>10</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -2769,18 +2769,18 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0.37</v>
+        <v>-2.09</v>
       </c>
       <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>1583696868</v>
+        <v>1582735114</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BOTZ.L</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2789,19 +2789,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.5</v>
+        <v>0.0003</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>45646.60053979167</v>
+        <v>45645.90076803241</v>
       </c>
       <c r="G48" t="n">
-        <v>20.645</v>
+        <v>130.51</v>
       </c>
       <c r="H48" t="n">
-        <v>20.41</v>
+        <v>143.76</v>
       </c>
       <c r="I48" t="n">
-        <v>10.32</v>
+        <v>0.04</v>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -2818,18 +2818,18 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
-        <v>1712849726</v>
+        <v>1563288050</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2838,19 +2838,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.0861</v>
+        <v>0.0626</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45734.85489405093</v>
+        <v>45630.85583428241</v>
       </c>
       <c r="G49" t="n">
-        <v>127.72</v>
+        <v>159.74</v>
       </c>
       <c r="H49" t="n">
-        <v>156.05</v>
+        <v>131.36</v>
       </c>
       <c r="I49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
@@ -2867,18 +2867,18 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.44</v>
+        <v>-1.78</v>
       </c>
       <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
-        <v>1582723120</v>
+        <v>1599431096</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.3755</v>
+        <v>0.1013</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>45645.89511640046</v>
+        <v>45663.73014731482</v>
       </c>
       <c r="G50" t="n">
-        <v>53.26</v>
+        <v>148.02</v>
       </c>
       <c r="H50" t="n">
-        <v>59.48</v>
+        <v>131.36</v>
       </c>
       <c r="I50" t="n">
-        <v>20</v>
+        <v>14.99</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -2916,18 +2916,18 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.33</v>
+        <v>-1.68</v>
       </c>
       <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>1806979127</v>
+        <v>1845429980</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2936,19 +2936,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.6361</v>
+        <v>1</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>45783.83125244213</v>
+        <v>45805.66181400463</v>
       </c>
       <c r="G51" t="n">
-        <v>15.72</v>
+        <v>13.27</v>
       </c>
       <c r="H51" t="n">
-        <v>17.17</v>
+        <v>13.225</v>
       </c>
       <c r="I51" t="n">
-        <v>10</v>
+        <v>15.09</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -2965,18 +2965,18 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>0.92</v>
+        <v>-0.15</v>
       </c>
       <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
-        <v>1727591551</v>
+        <v>1662993636</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2988,16 +2988,16 @@
         <v>1</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>45743.77389555555</v>
+        <v>45706.87026833333</v>
       </c>
       <c r="G52" t="n">
-        <v>72.87</v>
+        <v>20.65</v>
       </c>
       <c r="H52" t="n">
-        <v>72.38</v>
+        <v>22.23</v>
       </c>
       <c r="I52" t="n">
-        <v>72.87</v>
+        <v>20.65</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
@@ -3014,18 +3014,18 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>-0.49</v>
+        <v>1.58</v>
       </c>
       <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="n">
-        <v>1666459270</v>
+        <v>1806978791</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3034,19 +3034,19 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>0.0867</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>45708.68166530092</v>
+        <v>45783.83109655092</v>
       </c>
       <c r="G53" t="n">
-        <v>17.18</v>
+        <v>126.78</v>
       </c>
       <c r="H53" t="n">
-        <v>20.97</v>
+        <v>157.86</v>
       </c>
       <c r="I53" t="n">
-        <v>17.18</v>
+        <v>10.99</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
@@ -3063,18 +3063,18 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>3.79</v>
+        <v>2.7</v>
       </c>
       <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="n">
-        <v>1648740228</v>
+        <v>1554741910</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3083,19 +3083,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.0538</v>
+        <v>0.3495</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>45695.85792408565</v>
+        <v>45623.74951116898</v>
       </c>
       <c r="G54" t="n">
-        <v>185.82</v>
+        <v>15.3</v>
       </c>
       <c r="H54" t="n">
-        <v>172.3</v>
+        <v>21.24</v>
       </c>
       <c r="I54" t="n">
-        <v>10</v>
+        <v>5.35</v>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
@@ -3112,18 +3112,18 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>-0.73</v>
+        <v>2.07</v>
       </c>
       <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="n">
-        <v>1631475148</v>
+        <v>1648733962</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3132,19 +3132,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.2592</v>
+        <v>0.081</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>45685.83625201389</v>
+        <v>45695.85463682871</v>
       </c>
       <c r="G55" t="n">
-        <v>38.58</v>
+        <v>129.56</v>
       </c>
       <c r="H55" t="n">
-        <v>36.95</v>
+        <v>143.68</v>
       </c>
       <c r="I55" t="n">
-        <v>10</v>
+        <v>10.49</v>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
@@ -3161,18 +3161,18 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>-0.42</v>
+        <v>1.15</v>
       </c>
       <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="n">
-        <v>1644796307</v>
+        <v>1824482557</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3181,19 +3181,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>0.2641</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>45693.85501710648</v>
+        <v>45792.64805195602</v>
       </c>
       <c r="G56" t="n">
-        <v>20.36</v>
+        <v>56.78</v>
       </c>
       <c r="H56" t="n">
-        <v>22.16</v>
+        <v>60.5</v>
       </c>
       <c r="I56" t="n">
-        <v>20.36</v>
+        <v>15</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
@@ -3210,18 +3210,18 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>1.8</v>
+        <v>0.98</v>
       </c>
       <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="n">
-        <v>1517510856</v>
+        <v>1825032062</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3230,16 +3230,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.0602</v>
+        <v>0.3559</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45597.61014849537</v>
+        <v>45792.76080334491</v>
       </c>
       <c r="G57" t="n">
-        <v>166.03</v>
+        <v>28.09</v>
       </c>
       <c r="H57" t="n">
-        <v>130.65</v>
+        <v>31.92</v>
       </c>
       <c r="I57" t="n">
         <v>10</v>
@@ -3259,18 +3259,18 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>-2.13</v>
+        <v>1.36</v>
       </c>
       <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
-        <v>1680993370</v>
+        <v>1811475646</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3282,16 +3282,16 @@
         <v>1</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45716.85638861111</v>
+        <v>45785.66973634259</v>
       </c>
       <c r="G58" t="n">
-        <v>44.49</v>
+        <v>12.75</v>
       </c>
       <c r="H58" t="n">
-        <v>47.33</v>
+        <v>13.225</v>
       </c>
       <c r="I58" t="n">
-        <v>44.49</v>
+        <v>14.49</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
@@ -3308,18 +3308,18 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>2.84</v>
+        <v>0.45</v>
       </c>
       <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="n">
-        <v>1843474191</v>
+        <v>1381375440</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3328,16 +3328,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.9372</v>
+        <v>0.1057</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>45804.66699503472</v>
+        <v>45484.67118315972</v>
       </c>
       <c r="G59" t="n">
-        <v>21.33</v>
+        <v>189.11</v>
       </c>
       <c r="H59" t="n">
-        <v>20.97</v>
+        <v>193.28</v>
       </c>
       <c r="I59" t="n">
         <v>19.99</v>
@@ -3357,18 +3357,18 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>-0.34</v>
+        <v>0.44</v>
       </c>
       <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="n">
-        <v>1422773288</v>
+        <v>1680991980</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3377,19 +3377,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.483</v>
+        <v>0.1958</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45518.84428523148</v>
+        <v>45716.8556621875</v>
       </c>
       <c r="G60" t="n">
-        <v>51.24</v>
+        <v>178.67</v>
       </c>
       <c r="H60" t="n">
-        <v>59.48</v>
+        <v>193.28</v>
       </c>
       <c r="I60" t="n">
-        <v>24.75</v>
+        <v>34.98</v>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
@@ -3406,18 +3406,18 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>3.98</v>
+        <v>2.86</v>
       </c>
       <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="n">
-        <v>1744916452</v>
+        <v>1644789287</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3426,19 +3426,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.4245</v>
+        <v>0.0813</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>45751.74230173611</v>
+        <v>45693.85123056713</v>
       </c>
       <c r="G61" t="n">
-        <v>17.54</v>
+        <v>129.08</v>
       </c>
       <c r="H61" t="n">
-        <v>20.97</v>
+        <v>143.68</v>
       </c>
       <c r="I61" t="n">
-        <v>7.45</v>
+        <v>10.49</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
@@ -3455,18 +3455,18 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="n">
-        <v>1824475555</v>
+        <v>1621495187</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3475,19 +3475,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>0.2318</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>45792.64702015046</v>
+        <v>45678.83178196759</v>
       </c>
       <c r="G62" t="n">
-        <v>21.66</v>
+        <v>43.27</v>
       </c>
       <c r="H62" t="n">
-        <v>22.16</v>
+        <v>35.39</v>
       </c>
       <c r="I62" t="n">
-        <v>21.66</v>
+        <v>10.03</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
@@ -3504,18 +3504,18 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>0.5</v>
+        <v>-1.83</v>
       </c>
       <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="n">
-        <v>1806980496</v>
+        <v>1843474191</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3524,19 +3524,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>0.9372</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>45783.83190503472</v>
+        <v>45804.66699503472</v>
       </c>
       <c r="G63" t="n">
-        <v>16.12</v>
+        <v>21.33</v>
       </c>
       <c r="H63" t="n">
-        <v>17.63</v>
+        <v>21.24</v>
       </c>
       <c r="I63" t="n">
-        <v>16.12</v>
+        <v>19.99</v>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
@@ -3553,18 +3553,18 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>1.51</v>
+        <v>-0.08</v>
       </c>
       <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="n">
-        <v>1599435465</v>
+        <v>1481609355</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3573,19 +3573,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.0289</v>
+        <v>0.107</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>45663.73115600694</v>
+        <v>45568.7734872338</v>
       </c>
       <c r="G64" t="n">
-        <v>517.7</v>
+        <v>140.18</v>
       </c>
       <c r="H64" t="n">
-        <v>575.73</v>
+        <v>143.68</v>
       </c>
       <c r="I64" t="n">
-        <v>14.96</v>
+        <v>15</v>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
@@ -3602,18 +3602,18 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>1.68</v>
+        <v>0.37</v>
       </c>
       <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="n">
-        <v>1559803221</v>
+        <v>1653137218</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3622,19 +3622,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.092</v>
+        <v>0.277</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>45628.85951927083</v>
+        <v>45699.85152199074</v>
       </c>
       <c r="G65" t="n">
-        <v>162.85</v>
+        <v>36.1</v>
       </c>
       <c r="H65" t="n">
-        <v>130.65</v>
+        <v>35.39</v>
       </c>
       <c r="I65" t="n">
-        <v>14.98</v>
+        <v>10</v>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
@@ -3651,18 +3651,18 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>-2.96</v>
+        <v>-0.2</v>
       </c>
       <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="n">
-        <v>1666451221</v>
+        <v>1566610015</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3671,19 +3671,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.0001</v>
+        <v>0.9385</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>45708.68022634259</v>
+        <v>45632.87667083334</v>
       </c>
       <c r="G66" t="n">
-        <v>43</v>
+        <v>21.31</v>
       </c>
       <c r="H66" t="n">
-        <v>43.27</v>
+        <v>17</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
@@ -3700,18 +3700,18 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>-4.05</v>
       </c>
       <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="n">
-        <v>1701100481</v>
+        <v>1599435465</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3720,19 +3720,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.0873</v>
+        <v>0.0289</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>45727.87214378472</v>
+        <v>45663.73115600694</v>
       </c>
       <c r="G67" t="n">
-        <v>171.67</v>
+        <v>517.7</v>
       </c>
       <c r="H67" t="n">
-        <v>196.05</v>
+        <v>582.1799999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>14.99</v>
+        <v>14.96</v>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
@@ -3749,18 +3749,18 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>2.13</v>
+        <v>1.87</v>
       </c>
       <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="n">
-        <v>1599455288</v>
+        <v>1843477272</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3769,19 +3769,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.2195</v>
+        <v>1</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>45663.73750263889</v>
+        <v>45804.66725678241</v>
       </c>
       <c r="G68" t="n">
-        <v>45.55</v>
+        <v>17.86</v>
       </c>
       <c r="H68" t="n">
-        <v>36.95</v>
+        <v>17.82</v>
       </c>
       <c r="I68" t="n">
-        <v>10</v>
+        <v>17.86</v>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
@@ -3798,18 +3798,18 @@
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>-1.89</v>
+        <v>-0.04</v>
       </c>
       <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="n">
-        <v>1811475599</v>
+        <v>1666461140</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3818,19 +3818,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.7256</v>
+        <v>0.2651</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>45785.66972070602</v>
+        <v>45708.68207092593</v>
       </c>
       <c r="G69" t="n">
-        <v>12.75</v>
+        <v>37.7</v>
       </c>
       <c r="H69" t="n">
-        <v>13.26</v>
+        <v>35.39</v>
       </c>
       <c r="I69" t="n">
-        <v>10.51</v>
+        <v>9.99</v>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
@@ -3847,18 +3847,18 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>0.3</v>
+        <v>-0.61</v>
       </c>
       <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="n">
-        <v>1727563010</v>
+        <v>1744929368</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3867,19 +3867,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>0.0192</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>45743.76106726852</v>
+        <v>45751.74500871528</v>
       </c>
       <c r="G70" t="n">
-        <v>46.11</v>
+        <v>324.48</v>
       </c>
       <c r="H70" t="n">
-        <v>47.33</v>
+        <v>365.19</v>
       </c>
       <c r="I70" t="n">
-        <v>46.11</v>
+        <v>6.23</v>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
@@ -3896,18 +3896,18 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>1.22</v>
+        <v>0.78</v>
       </c>
       <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="n">
-        <v>1644789287</v>
+        <v>1358151307</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3916,19 +3916,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.0813</v>
+        <v>0.1081</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>45693.85123056713</v>
+        <v>45460.88529052083</v>
       </c>
       <c r="G71" t="n">
-        <v>129.08</v>
+        <v>165.93</v>
       </c>
       <c r="H71" t="n">
-        <v>142.67</v>
+        <v>131.36</v>
       </c>
       <c r="I71" t="n">
-        <v>10.49</v>
+        <v>17.94</v>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
@@ -3945,18 +3945,18 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>1.11</v>
+        <v>-3.73</v>
       </c>
       <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="n">
-        <v>1621495187</v>
+        <v>1727564345</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3965,19 +3965,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.2318</v>
+        <v>0.3274</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>45678.83178196759</v>
+        <v>45743.76175270833</v>
       </c>
       <c r="G72" t="n">
-        <v>43.27</v>
+        <v>30.54</v>
       </c>
       <c r="H72" t="n">
-        <v>36.95</v>
+        <v>31.92</v>
       </c>
       <c r="I72" t="n">
-        <v>10.03</v>
+        <v>10</v>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -3994,18 +3994,18 @@
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>-1.46</v>
+        <v>0.45</v>
       </c>
       <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="n">
-        <v>1644788775</v>
+        <v>1824475555</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4014,19 +4014,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.07580000000000001</v>
+        <v>1</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45693.85093391204</v>
+        <v>45792.64702015046</v>
       </c>
       <c r="G73" t="n">
-        <v>144.94</v>
+        <v>21.66</v>
       </c>
       <c r="H73" t="n">
-        <v>130.65</v>
+        <v>22.23</v>
       </c>
       <c r="I73" t="n">
-        <v>10.99</v>
+        <v>21.66</v>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
@@ -4043,18 +4043,18 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>-1.09</v>
+        <v>0.57</v>
       </c>
       <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="n">
-        <v>1495551484</v>
+        <v>1701100481</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4063,19 +4063,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.1914</v>
+        <v>0.0873</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45580.70648087963</v>
+        <v>45727.87214378472</v>
       </c>
       <c r="G74" t="n">
-        <v>135.82</v>
+        <v>171.67</v>
       </c>
       <c r="H74" t="n">
-        <v>137.42</v>
+        <v>193.28</v>
       </c>
       <c r="I74" t="n">
-        <v>26</v>
+        <v>14.99</v>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
@@ -4092,18 +4092,18 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>0.3</v>
+        <v>1.88</v>
       </c>
       <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="n">
-        <v>1830408508</v>
+        <v>1744916497</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4112,19 +4112,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.5793</v>
+        <v>1</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>45796.82346997685</v>
+        <v>45751.74231563658</v>
       </c>
       <c r="G75" t="n">
-        <v>17.26</v>
+        <v>17.54</v>
       </c>
       <c r="H75" t="n">
-        <v>17.17</v>
+        <v>21.24</v>
       </c>
       <c r="I75" t="n">
-        <v>10</v>
+        <v>17.54</v>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
@@ -4141,18 +4141,18 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>-0.05</v>
+        <v>3.7</v>
       </c>
       <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="n">
-        <v>1563288050</v>
+        <v>1796453499</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4161,16 +4161,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.0626</v>
+        <v>0.6422</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>45630.85583428241</v>
+        <v>45777.64668229167</v>
       </c>
       <c r="G76" t="n">
-        <v>159.74</v>
+        <v>15.57</v>
       </c>
       <c r="H76" t="n">
-        <v>130.65</v>
+        <v>17.82</v>
       </c>
       <c r="I76" t="n">
         <v>10</v>
@@ -4190,18 +4190,18 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>-1.82</v>
+        <v>1.44</v>
       </c>
       <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="n">
-        <v>1845429956</v>
+        <v>1830408508</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4210,19 +4210,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.6565</v>
+        <v>0.5793</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>45805.66180811343</v>
+        <v>45796.82346997685</v>
       </c>
       <c r="G77" t="n">
-        <v>13.275</v>
+        <v>17.26</v>
       </c>
       <c r="H77" t="n">
-        <v>13.26</v>
+        <v>17</v>
       </c>
       <c r="I77" t="n">
-        <v>9.91</v>
+        <v>10</v>
       </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
@@ -4239,18 +4239,18 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>-0.13</v>
+        <v>-0.15</v>
       </c>
       <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="n">
-        <v>1701100027</v>
+        <v>1635194724</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4259,19 +4259,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.7812</v>
+        <v>0.2875</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>45727.87202070602</v>
+        <v>45687.85271734954</v>
       </c>
       <c r="G78" t="n">
-        <v>19.2</v>
+        <v>34.78</v>
       </c>
       <c r="H78" t="n">
-        <v>17.17</v>
+        <v>31.92</v>
       </c>
       <c r="I78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
@@ -4288,18 +4288,18 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>-1.59</v>
+        <v>-0.82</v>
       </c>
       <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="n">
-        <v>1744929368</v>
+        <v>1582708979</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4308,19 +4308,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.0192</v>
+        <v>0.0769</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>45751.74500871528</v>
+        <v>45645.88746980324</v>
       </c>
       <c r="G79" t="n">
-        <v>324.48</v>
+        <v>195.11</v>
       </c>
       <c r="H79" t="n">
-        <v>359.84</v>
+        <v>193.28</v>
       </c>
       <c r="I79" t="n">
-        <v>6.23</v>
+        <v>15</v>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
@@ -4337,18 +4337,18 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>0.68</v>
+        <v>-0.14</v>
       </c>
       <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="n">
-        <v>1599431096</v>
+        <v>1843470413</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4357,19 +4357,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.1013</v>
+        <v>0.4729</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>45663.73014731482</v>
+        <v>45804.66637251157</v>
       </c>
       <c r="G80" t="n">
-        <v>148.02</v>
+        <v>42.29</v>
       </c>
       <c r="H80" t="n">
-        <v>130.65</v>
+        <v>41.16</v>
       </c>
       <c r="I80" t="n">
-        <v>14.99</v>
+        <v>20</v>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
@@ -4386,18 +4386,18 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>-1.76</v>
+        <v>-0.54</v>
       </c>
       <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="n">
-        <v>1554742887</v>
+        <v>1495551484</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4406,19 +4406,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.1914</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>45623.74993112269</v>
+        <v>45580.70648087963</v>
       </c>
       <c r="G81" t="n">
-        <v>178.48</v>
+        <v>135.82</v>
       </c>
       <c r="H81" t="n">
-        <v>196.05</v>
+        <v>139.03</v>
       </c>
       <c r="I81" t="n">
-        <v>14.99</v>
+        <v>26</v>
       </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
@@ -4435,18 +4435,18 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>1.48</v>
+        <v>0.61</v>
       </c>
       <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="n">
-        <v>1666459175</v>
+        <v>1633116336</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4455,19 +4455,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.1641</v>
+        <v>1</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>45708.68165298611</v>
+        <v>45686.83272234954</v>
       </c>
       <c r="G82" t="n">
-        <v>17.18</v>
+        <v>44.24</v>
       </c>
       <c r="H82" t="n">
-        <v>20.97</v>
+        <v>46.99</v>
       </c>
       <c r="I82" t="n">
-        <v>2.82</v>
+        <v>44.24</v>
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
@@ -4484,18 +4484,18 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>0.62</v>
+        <v>2.75</v>
       </c>
       <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="n">
-        <v>1824477589</v>
+        <v>1554742887</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4504,19 +4504,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.2344</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>45792.64732982639</v>
+        <v>45623.74993112269</v>
       </c>
       <c r="G83" t="n">
-        <v>42.66</v>
+        <v>178.48</v>
       </c>
       <c r="H83" t="n">
-        <v>43.27</v>
+        <v>193.28</v>
       </c>
       <c r="I83" t="n">
-        <v>10</v>
+        <v>14.99</v>
       </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
@@ -4533,14 +4533,14 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>0.14</v>
+        <v>1.25</v>
       </c>
       <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="n">
-        <v>1381417257</v>
+        <v>1594315903</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -4556,16 +4556,16 @@
         <v>1</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>45484.67877329861</v>
+        <v>45659.42644752315</v>
       </c>
       <c r="G84" t="n">
-        <v>16.374</v>
+        <v>16.425</v>
       </c>
       <c r="H84" t="n">
-        <v>15.382</v>
+        <v>15.134</v>
       </c>
       <c r="I84" t="n">
-        <v>17.9</v>
+        <v>17.11</v>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
@@ -4582,18 +4582,18 @@
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>-0.62</v>
+        <v>-0.01</v>
       </c>
       <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="n">
-        <v>1806977521</v>
+        <v>1461331124</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4602,19 +4602,19 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.3367</v>
+        <v>0.3922</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>45783.8305750463</v>
+        <v>45553.65374138889</v>
       </c>
       <c r="G85" t="n">
-        <v>29.7</v>
+        <v>50.99</v>
       </c>
       <c r="H85" t="n">
-        <v>36.95</v>
+        <v>60.5</v>
       </c>
       <c r="I85" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
@@ -4631,18 +4631,18 @@
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>2.44</v>
+        <v>3.73</v>
       </c>
       <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="n">
-        <v>1727574394</v>
+        <v>1806980482</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4651,19 +4651,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>0.2406</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>45743.76658678241</v>
+        <v>45783.83189613426</v>
       </c>
       <c r="G86" t="n">
-        <v>21.13</v>
+        <v>16.12</v>
       </c>
       <c r="H86" t="n">
-        <v>22.16</v>
+        <v>17.82</v>
       </c>
       <c r="I86" t="n">
-        <v>21.13</v>
+        <v>3.88</v>
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
@@ -4680,18 +4680,18 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>1.03</v>
+        <v>0.41</v>
       </c>
       <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="n">
-        <v>1461331124</v>
+        <v>1414752069</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4700,19 +4700,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.3922</v>
+        <v>0.1933</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>45553.65374138889</v>
+        <v>45511.86049193287</v>
       </c>
       <c r="G87" t="n">
-        <v>50.99</v>
+        <v>77.53</v>
       </c>
       <c r="H87" t="n">
-        <v>59.48</v>
+        <v>70.56</v>
       </c>
       <c r="I87" t="n">
-        <v>20</v>
+        <v>14.99</v>
       </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
@@ -4729,18 +4729,18 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>3.33</v>
+        <v>-1.35</v>
       </c>
       <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="n">
-        <v>1744879358</v>
+        <v>1499061783</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4749,19 +4749,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.2701</v>
+        <v>0.0001</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>45751.73925940973</v>
+        <v>45582.73996892361</v>
       </c>
       <c r="G88" t="n">
-        <v>148.09</v>
+        <v>232.2</v>
       </c>
       <c r="H88" t="n">
-        <v>196.05</v>
+        <v>200.85</v>
       </c>
       <c r="I88" t="n">
-        <v>40</v>
+        <v>0.02</v>
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
@@ -4778,18 +4778,18 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>12.95</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="n">
-        <v>1662995258</v>
+        <v>1532661507</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4798,19 +4798,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.2943</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>45706.87121422453</v>
+        <v>45608.74251107639</v>
       </c>
       <c r="G89" t="n">
-        <v>67.97</v>
+        <v>190.67</v>
       </c>
       <c r="H89" t="n">
-        <v>67.20999999999999</v>
+        <v>193.28</v>
       </c>
       <c r="I89" t="n">
-        <v>20</v>
+        <v>12.98</v>
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
@@ -4827,18 +4827,18 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>-0.22</v>
+        <v>0.18</v>
       </c>
       <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="n">
-        <v>1817264187</v>
+        <v>1727574394</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4847,19 +4847,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.4757</v>
+        <v>1</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>45789.64859377315</v>
+        <v>45743.76658678241</v>
       </c>
       <c r="G90" t="n">
-        <v>42.02</v>
+        <v>21.13</v>
       </c>
       <c r="H90" t="n">
-        <v>42.16</v>
+        <v>22.23</v>
       </c>
       <c r="I90" t="n">
-        <v>19.99</v>
+        <v>21.13</v>
       </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
@@ -4876,18 +4876,18 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="n">
-        <v>1754304266</v>
+        <v>1712850989</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4896,19 +4896,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.7137</v>
+        <v>0.1244</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>45755.88055112268</v>
+        <v>45734.85576775463</v>
       </c>
       <c r="G91" t="n">
-        <v>14</v>
+        <v>160.64</v>
       </c>
       <c r="H91" t="n">
-        <v>17.17</v>
+        <v>171.72</v>
       </c>
       <c r="I91" t="n">
-        <v>9.99</v>
+        <v>19.98</v>
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
@@ -4925,18 +4925,18 @@
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>2.26</v>
+        <v>1.38</v>
       </c>
       <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="n">
-        <v>1554741956</v>
+        <v>1744767540</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4945,19 +4945,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>0.643</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>45623.74952237269</v>
+        <v>45751.72316712963</v>
       </c>
       <c r="G92" t="n">
-        <v>15.3</v>
+        <v>15.55</v>
       </c>
       <c r="H92" t="n">
-        <v>20.97</v>
+        <v>17</v>
       </c>
       <c r="I92" t="n">
-        <v>15.3</v>
+        <v>10</v>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
@@ -4974,18 +4974,18 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>5.67</v>
+        <v>0.93</v>
       </c>
       <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="n">
-        <v>1701098878</v>
+        <v>1680994777</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4994,19 +4994,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.0383</v>
+        <v>0.7278</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>45727.87167594907</v>
+        <v>45716.85705375</v>
       </c>
       <c r="G93" t="n">
-        <v>139.41</v>
+        <v>20.6</v>
       </c>
       <c r="H93" t="n">
-        <v>156.05</v>
+        <v>17</v>
       </c>
       <c r="I93" t="n">
-        <v>5.34</v>
+        <v>14.99</v>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
@@ -5023,18 +5023,18 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>0.64</v>
+        <v>-2.62</v>
       </c>
       <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="n">
-        <v>1806978791</v>
+        <v>1635194117</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5043,19 +5043,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.0867</v>
+        <v>0.2479</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>45783.83109655092</v>
+        <v>45687.85228493056</v>
       </c>
       <c r="G94" t="n">
-        <v>126.78</v>
+        <v>40.33</v>
       </c>
       <c r="H94" t="n">
-        <v>156.05</v>
+        <v>35.39</v>
       </c>
       <c r="I94" t="n">
-        <v>10.99</v>
+        <v>10</v>
       </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
@@ -5072,18 +5072,18 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>2.54</v>
+        <v>-1.23</v>
       </c>
       <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="n">
-        <v>1582708979</v>
+        <v>1559803221</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5092,19 +5092,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.0769</v>
+        <v>0.092</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>45645.88746980324</v>
+        <v>45628.85951927083</v>
       </c>
       <c r="G95" t="n">
-        <v>195.11</v>
+        <v>162.85</v>
       </c>
       <c r="H95" t="n">
-        <v>196.05</v>
+        <v>131.36</v>
       </c>
       <c r="I95" t="n">
-        <v>15</v>
+        <v>14.98</v>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -5121,18 +5121,18 @@
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>0.08</v>
+        <v>-2.89</v>
       </c>
       <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="n">
-        <v>1559803984</v>
+        <v>1599455288</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5141,19 +5141,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.1076</v>
+        <v>0.2195</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>45628.86014383102</v>
+        <v>45663.73750263889</v>
       </c>
       <c r="G96" t="n">
-        <v>139.4</v>
+        <v>45.55</v>
       </c>
       <c r="H96" t="n">
-        <v>142.67</v>
+        <v>35.39</v>
       </c>
       <c r="I96" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
@@ -5170,18 +5170,18 @@
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>0.35</v>
+        <v>-2.23</v>
       </c>
       <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="n">
-        <v>1666461140</v>
+        <v>1845431561</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5190,19 +5190,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.2651</v>
+        <v>0.3271</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>45708.68207092593</v>
+        <v>45805.66210755787</v>
       </c>
       <c r="G97" t="n">
-        <v>37.7</v>
+        <v>30.57</v>
       </c>
       <c r="H97" t="n">
-        <v>36.95</v>
+        <v>31.92</v>
       </c>
       <c r="I97" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
@@ -5219,18 +5219,18 @@
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>-0.19</v>
+        <v>0.44</v>
       </c>
       <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="n">
-        <v>1635194724</v>
+        <v>1582737192</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5239,19 +5239,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.2875</v>
+        <v>0.001</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>45687.85271734954</v>
+        <v>45645.90143930555</v>
       </c>
       <c r="G98" t="n">
-        <v>34.78</v>
+        <v>524.4299999999999</v>
       </c>
       <c r="H98" t="n">
-        <v>30.82</v>
+        <v>582.1799999999999</v>
       </c>
       <c r="I98" t="n">
-        <v>10</v>
+        <v>0.52</v>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
@@ -5268,18 +5268,18 @@
         <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>-1.14</v>
+        <v>0.06</v>
       </c>
       <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="n">
-        <v>1648737122</v>
+        <v>1559803984</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5288,19 +5288,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.0269</v>
+        <v>0.1076</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>45695.85619950231</v>
+        <v>45628.86014383102</v>
       </c>
       <c r="G99" t="n">
-        <v>408.33</v>
+        <v>139.4</v>
       </c>
       <c r="H99" t="n">
-        <v>457.4</v>
+        <v>143.68</v>
       </c>
       <c r="I99" t="n">
-        <v>10.98</v>
+        <v>15</v>
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
@@ -5317,18 +5317,18 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>1.32</v>
+        <v>0.46</v>
       </c>
       <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="n">
-        <v>1648733962</v>
+        <v>1666459270</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5337,19 +5337,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.081</v>
+        <v>1</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>45695.85463682871</v>
+        <v>45708.68166530092</v>
       </c>
       <c r="G100" t="n">
-        <v>129.56</v>
+        <v>17.18</v>
       </c>
       <c r="H100" t="n">
-        <v>142.67</v>
+        <v>21.24</v>
       </c>
       <c r="I100" t="n">
-        <v>10.49</v>
+        <v>17.18</v>
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
@@ -5366,18 +5366,18 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>1.07</v>
+        <v>4.06</v>
       </c>
       <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="n">
-        <v>1680994777</v>
+        <v>1824477589</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5386,19 +5386,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.7278</v>
+        <v>0.2344</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>45716.85705375</v>
+        <v>45792.64732982639</v>
       </c>
       <c r="G101" t="n">
-        <v>20.6</v>
+        <v>42.66</v>
       </c>
       <c r="H101" t="n">
-        <v>17.17</v>
+        <v>43.82</v>
       </c>
       <c r="I101" t="n">
-        <v>14.99</v>
+        <v>10</v>
       </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -5415,18 +5415,18 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>-2.49</v>
+        <v>0.27</v>
       </c>
       <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="n">
-        <v>1517514880</v>
+        <v>1648740228</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5435,19 +5435,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.0231</v>
+        <v>0.0538</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>45597.61087239583</v>
+        <v>45695.85792408565</v>
       </c>
       <c r="G102" t="n">
-        <v>409.38</v>
+        <v>185.82</v>
       </c>
       <c r="H102" t="n">
-        <v>457.4</v>
+        <v>171.72</v>
       </c>
       <c r="I102" t="n">
-        <v>9.460000000000001</v>
+        <v>10</v>
       </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
@@ -5464,18 +5464,18 @@
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>1.11</v>
+        <v>-0.76</v>
       </c>
       <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="n">
-        <v>1776193271</v>
+        <v>1712849726</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5484,19 +5484,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.6724</v>
+        <v>0.0861</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>45764.85451520833</v>
+        <v>45734.85489405093</v>
       </c>
       <c r="G103" t="n">
-        <v>14.87</v>
+        <v>127.72</v>
       </c>
       <c r="H103" t="n">
-        <v>17.63</v>
+        <v>157.86</v>
       </c>
       <c r="I103" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
@@ -5513,18 +5513,18 @@
         <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>1.85</v>
+        <v>2.59</v>
       </c>
       <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="n">
-        <v>1744916497</v>
+        <v>1806980496</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5536,16 +5536,16 @@
         <v>1</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>45751.74231563658</v>
+        <v>45783.83190503472</v>
       </c>
       <c r="G104" t="n">
-        <v>17.54</v>
+        <v>16.12</v>
       </c>
       <c r="H104" t="n">
-        <v>20.97</v>
+        <v>17.82</v>
       </c>
       <c r="I104" t="n">
-        <v>17.54</v>
+        <v>16.12</v>
       </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
@@ -5562,18 +5562,18 @@
         <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>3.43</v>
+        <v>1.7</v>
       </c>
       <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="n">
-        <v>1825032062</v>
+        <v>1422773288</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5582,19 +5582,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.3559</v>
+        <v>0.483</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>45792.76080334491</v>
+        <v>45518.84428523148</v>
       </c>
       <c r="G105" t="n">
-        <v>28.09</v>
+        <v>51.24</v>
       </c>
       <c r="H105" t="n">
-        <v>30.82</v>
+        <v>60.5</v>
       </c>
       <c r="I105" t="n">
-        <v>10</v>
+        <v>24.75</v>
       </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
@@ -5611,18 +5611,18 @@
         <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>0.97</v>
+        <v>4.47</v>
       </c>
       <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="n">
-        <v>1533882988</v>
+        <v>1729617775</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BOTZ.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5631,19 +5631,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.5</v>
+        <v>0.0907</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>45609.60769543982</v>
+        <v>45744.71339734954</v>
       </c>
       <c r="G106" t="n">
-        <v>21.905</v>
+        <v>165.35</v>
       </c>
       <c r="H106" t="n">
-        <v>20.41</v>
+        <v>193.28</v>
       </c>
       <c r="I106" t="n">
-        <v>10.95</v>
+        <v>15</v>
       </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
@@ -5660,18 +5660,18 @@
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>-0.74</v>
+        <v>2.53</v>
       </c>
       <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="n">
-        <v>1843477152</v>
+        <v>1631475148</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5680,19 +5680,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.1198</v>
+        <v>0.2592</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>45804.66724922453</v>
+        <v>45685.83625201389</v>
       </c>
       <c r="G107" t="n">
-        <v>17.86</v>
+        <v>38.58</v>
       </c>
       <c r="H107" t="n">
-        <v>17.63</v>
+        <v>35.39</v>
       </c>
       <c r="I107" t="n">
-        <v>2.14</v>
+        <v>10</v>
       </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
@@ -5709,18 +5709,18 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>-0.03</v>
+        <v>-0.83</v>
       </c>
       <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="n">
-        <v>1606697510</v>
+        <v>1754304266</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5729,19 +5729,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.0295</v>
+        <v>0.7137</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>45667.68664726852</v>
+        <v>45755.88055112268</v>
       </c>
       <c r="G108" t="n">
-        <v>507.68</v>
+        <v>14</v>
       </c>
       <c r="H108" t="n">
-        <v>575.73</v>
+        <v>17</v>
       </c>
       <c r="I108" t="n">
-        <v>14.98</v>
+        <v>9.99</v>
       </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
@@ -5758,18 +5758,18 @@
         <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="n">
-        <v>1845431561</v>
+        <v>1845429956</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5778,19 +5778,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.3271</v>
+        <v>0.6565</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>45805.66210755787</v>
+        <v>45805.66180811343</v>
       </c>
       <c r="G109" t="n">
-        <v>30.57</v>
+        <v>13.275</v>
       </c>
       <c r="H109" t="n">
-        <v>30.82</v>
+        <v>13.225</v>
       </c>
       <c r="I109" t="n">
-        <v>10</v>
+        <v>9.91</v>
       </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
@@ -5807,7 +5807,7 @@
         <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="Q109" t="inlineStr"/>
     </row>
@@ -5838,7 +5838,7 @@
         <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>53.71</v>
+        <v>55.77</v>
       </c>
       <c r="Q110" t="inlineStr"/>
     </row>

--- a/Stock Selection/OPEN POSITION.xlsx
+++ b/Stock Selection/OPEN POSITION.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q110"/>
+  <dimension ref="A1:Q124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,11 +522,11 @@
     <row r="2">
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="n">
-        <v>1511085920</v>
+        <v>1666451221</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0761</v>
+        <v>0.0001</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45593.7262774074</v>
+        <v>45708.68022634259</v>
       </c>
       <c r="G2" t="n">
-        <v>196.9</v>
+        <v>43</v>
       </c>
       <c r="H2" t="n">
-        <v>193.28</v>
+        <v>42.37</v>
       </c>
       <c r="I2" t="n">
-        <v>14.98</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -564,18 +564,18 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="n">
-        <v>1642762235</v>
+        <v>1644789287</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -584,19 +584,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.1572</v>
+        <v>0.0813</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45692.86612574074</v>
+        <v>45693.85123056713</v>
       </c>
       <c r="G3" t="n">
-        <v>127.16</v>
+        <v>129.08</v>
       </c>
       <c r="H3" t="n">
-        <v>139.03</v>
+        <v>127.93</v>
       </c>
       <c r="I3" t="n">
-        <v>19.99</v>
+        <v>10.49</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -613,18 +613,18 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.87</v>
+        <v>-0.09</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="n">
-        <v>1554741956</v>
+        <v>1533882988</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>BOTZ.L</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -633,19 +633,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45623.74952237269</v>
+        <v>45609.60769543982</v>
       </c>
       <c r="G4" t="n">
-        <v>15.3</v>
+        <v>21.905</v>
       </c>
       <c r="H4" t="n">
-        <v>21.24</v>
+        <v>20.405</v>
       </c>
       <c r="I4" t="n">
-        <v>15.3</v>
+        <v>10.95</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -662,18 +662,18 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>5.94</v>
+        <v>-0.75</v>
       </c>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="n">
-        <v>1599449649</v>
+        <v>1599435465</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4145</v>
+        <v>0.0289</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45663.73562525463</v>
+        <v>45663.73115600694</v>
       </c>
       <c r="G5" t="n">
-        <v>24.11</v>
+        <v>517.7</v>
       </c>
       <c r="H5" t="n">
-        <v>17</v>
+        <v>538.84</v>
       </c>
       <c r="I5" t="n">
-        <v>9.99</v>
+        <v>14.96</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -711,18 +711,18 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.94</v>
+        <v>0.61</v>
       </c>
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="n">
-        <v>1843477152</v>
+        <v>1880446963</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.1198</v>
+        <v>0.0774</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45804.66724922453</v>
+        <v>45825.89330317129</v>
       </c>
       <c r="G6" t="n">
-        <v>17.86</v>
+        <v>129.25</v>
       </c>
       <c r="H6" t="n">
-        <v>17.82</v>
+        <v>127.93</v>
       </c>
       <c r="I6" t="n">
-        <v>2.14</v>
+        <v>10</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -760,18 +760,18 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="n">
-        <v>1662995258</v>
+        <v>1712850989</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -780,19 +780,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.2943</v>
+        <v>0.0282</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45706.87121422453</v>
+        <v>45734.85576775463</v>
       </c>
       <c r="G7" t="n">
-        <v>67.97</v>
+        <v>160.64</v>
       </c>
       <c r="H7" t="n">
-        <v>70.56</v>
+        <v>173.31</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>4.53</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -809,18 +809,18 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.77</v>
+        <v>0.36</v>
       </c>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>1811475599</v>
+        <v>1880442840</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.7256</v>
+        <v>0.2535</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45785.66972070602</v>
+        <v>45825.89113450232</v>
       </c>
       <c r="G8" t="n">
-        <v>12.75</v>
+        <v>59.15</v>
       </c>
       <c r="H8" t="n">
-        <v>13.225</v>
+        <v>59.49</v>
       </c>
       <c r="I8" t="n">
-        <v>10.51</v>
+        <v>14.99</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -858,18 +858,18 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.33</v>
+        <v>0.09</v>
       </c>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>1599448103</v>
+        <v>1642762235</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -878,19 +878,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.2839</v>
+        <v>0.1572</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45663.73506711805</v>
+        <v>45692.86612574074</v>
       </c>
       <c r="G9" t="n">
-        <v>52.83</v>
+        <v>127.16</v>
       </c>
       <c r="H9" t="n">
-        <v>60.5</v>
+        <v>136.42</v>
       </c>
       <c r="I9" t="n">
-        <v>15</v>
+        <v>19.99</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -907,18 +907,18 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.18</v>
+        <v>1.46</v>
       </c>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
-        <v>1776193271</v>
+        <v>1680994777</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.6724</v>
+        <v>0.7278</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45764.85451520833</v>
+        <v>45716.85705375</v>
       </c>
       <c r="G10" t="n">
-        <v>14.87</v>
+        <v>20.6</v>
       </c>
       <c r="H10" t="n">
-        <v>17.82</v>
+        <v>20.3</v>
       </c>
       <c r="I10" t="n">
-        <v>10</v>
+        <v>14.99</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -956,18 +956,18 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.98</v>
+        <v>-0.22</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
-        <v>1817256440</v>
+        <v>1583696868</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>BOTZ.L</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -976,19 +976,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.2267</v>
+        <v>0.5</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45789.64787115741</v>
+        <v>45646.60053979167</v>
       </c>
       <c r="G11" t="n">
-        <v>44.1</v>
+        <v>20.645</v>
       </c>
       <c r="H11" t="n">
-        <v>43.82</v>
+        <v>20.405</v>
       </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>10.32</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -1005,18 +1005,18 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>1825032378</v>
+        <v>1824477589</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1025,16 +1025,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.2894</v>
+        <v>0.2344</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>45792.76093177083</v>
+        <v>45792.64732982639</v>
       </c>
       <c r="G12" t="n">
-        <v>34.55</v>
+        <v>42.66</v>
       </c>
       <c r="H12" t="n">
-        <v>31.09</v>
+        <v>42.37</v>
       </c>
       <c r="I12" t="n">
         <v>10</v>
@@ -1054,18 +1054,18 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>1744930699</v>
+        <v>1867193336</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1077,16 +1077,16 @@
         <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>45751.74534789352</v>
+        <v>45818.80084483796</v>
       </c>
       <c r="G13" t="n">
-        <v>74.13</v>
+        <v>17.64</v>
       </c>
       <c r="H13" t="n">
-        <v>72.75</v>
+        <v>17.65</v>
       </c>
       <c r="I13" t="n">
-        <v>74.13</v>
+        <v>17.64</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -1103,18 +1103,18 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.38</v>
+        <v>0.01</v>
       </c>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="n">
-        <v>1666457581</v>
+        <v>1796453499</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.6422</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>45708.68135159722</v>
+        <v>45777.64668229167</v>
       </c>
       <c r="G14" t="n">
-        <v>38.23</v>
+        <v>15.57</v>
       </c>
       <c r="H14" t="n">
-        <v>31.09</v>
+        <v>17.65</v>
       </c>
       <c r="I14" t="n">
-        <v>19.98</v>
+        <v>10</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -1152,18 +1152,18 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.73</v>
+        <v>1.33</v>
       </c>
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="n">
-        <v>1727591551</v>
+        <v>1481609355</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.107</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>45743.77389555555</v>
+        <v>45568.7734872338</v>
       </c>
       <c r="G15" t="n">
-        <v>72.87</v>
+        <v>140.18</v>
       </c>
       <c r="H15" t="n">
-        <v>72.75</v>
+        <v>127.93</v>
       </c>
       <c r="I15" t="n">
-        <v>72.87</v>
+        <v>15</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1201,14 +1201,14 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.12</v>
+        <v>-1.31</v>
       </c>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="n">
-        <v>1648735305</v>
+        <v>1744767540</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1221,16 +1221,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.4576</v>
+        <v>0.643</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>45695.85530675926</v>
+        <v>45751.72316712963</v>
       </c>
       <c r="G16" t="n">
-        <v>21.85</v>
+        <v>15.55</v>
       </c>
       <c r="H16" t="n">
-        <v>17</v>
+        <v>20.3</v>
       </c>
       <c r="I16" t="n">
         <v>10</v>
@@ -1250,18 +1250,18 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.22</v>
+        <v>3.05</v>
       </c>
       <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="n">
-        <v>1606697510</v>
+        <v>1633116336</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1270,19 +1270,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.0295</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>45667.68664726852</v>
+        <v>45686.83272234954</v>
       </c>
       <c r="G17" t="n">
-        <v>507.68</v>
+        <v>44.24</v>
       </c>
       <c r="H17" t="n">
-        <v>582.1799999999999</v>
+        <v>48.15</v>
       </c>
       <c r="I17" t="n">
-        <v>14.98</v>
+        <v>44.24</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1299,18 +1299,18 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.19</v>
+        <v>3.91</v>
       </c>
       <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
-        <v>1843469729</v>
+        <v>1824475555</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.0956</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45804.66615450232</v>
+        <v>45792.64702015046</v>
       </c>
       <c r="G18" t="n">
-        <v>156.9</v>
+        <v>21.66</v>
       </c>
       <c r="H18" t="n">
-        <v>157.86</v>
+        <v>21.07</v>
       </c>
       <c r="I18" t="n">
-        <v>15</v>
+        <v>21.66</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1348,18 +1348,18 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.09</v>
+        <v>-0.59</v>
       </c>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="n">
-        <v>1517514880</v>
+        <v>1744929368</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1368,19 +1368,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.0231</v>
+        <v>0.0192</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45597.61087239583</v>
+        <v>45751.74500871528</v>
       </c>
       <c r="G19" t="n">
-        <v>409.38</v>
+        <v>324.48</v>
       </c>
       <c r="H19" t="n">
-        <v>459.55</v>
+        <v>340.31</v>
       </c>
       <c r="I19" t="n">
-        <v>9.460000000000001</v>
+        <v>6.23</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1397,18 +1397,18 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.16</v>
+        <v>0.3</v>
       </c>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
-        <v>1644796307</v>
+        <v>1806980482</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1417,19 +1417,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0.2406</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45693.85501710648</v>
+        <v>45783.83189613426</v>
       </c>
       <c r="G20" t="n">
-        <v>20.36</v>
+        <v>16.12</v>
       </c>
       <c r="H20" t="n">
-        <v>22.23</v>
+        <v>17.65</v>
       </c>
       <c r="I20" t="n">
-        <v>20.36</v>
+        <v>3.88</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1446,18 +1446,18 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.87</v>
+        <v>0.37</v>
       </c>
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="n">
-        <v>1583696868</v>
+        <v>1867193304</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BOTZ.L</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1466,19 +1466,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.5</v>
+        <v>0.1337</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45646.60053979167</v>
+        <v>45818.8008296412</v>
       </c>
       <c r="G21" t="n">
-        <v>20.645</v>
+        <v>17.64</v>
       </c>
       <c r="H21" t="n">
-        <v>20.25</v>
+        <v>17.65</v>
       </c>
       <c r="I21" t="n">
-        <v>10.32</v>
+        <v>2.36</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1495,18 +1495,18 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.19</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="n">
-        <v>1582723120</v>
+        <v>1635194724</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1515,19 +1515,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.3755</v>
+        <v>0.2875</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>45645.89511640046</v>
+        <v>45687.85271734954</v>
       </c>
       <c r="G22" t="n">
-        <v>53.26</v>
+        <v>34.78</v>
       </c>
       <c r="H22" t="n">
-        <v>60.5</v>
+        <v>35.28</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -1544,18 +1544,18 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.72</v>
+        <v>0.14</v>
       </c>
       <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="n">
-        <v>1450043624</v>
+        <v>1554741956</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.0231</v>
+        <v>1</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>45544.65163525463</v>
+        <v>45623.74952237269</v>
       </c>
       <c r="G23" t="n">
-        <v>147.48</v>
+        <v>15.3</v>
       </c>
       <c r="H23" t="n">
-        <v>143.68</v>
+        <v>20.77</v>
       </c>
       <c r="I23" t="n">
-        <v>3.41</v>
+        <v>15.3</v>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -1593,18 +1593,18 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.09</v>
+        <v>5.47</v>
       </c>
       <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="n">
-        <v>1806977521</v>
+        <v>1606697510</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.3367</v>
+        <v>0.0295</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45783.8305750463</v>
+        <v>45667.68664726852</v>
       </c>
       <c r="G24" t="n">
-        <v>29.7</v>
+        <v>507.68</v>
       </c>
       <c r="H24" t="n">
-        <v>35.39</v>
+        <v>538.84</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>14.98</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1642,18 +1642,18 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.92</v>
+        <v>0.92</v>
       </c>
       <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="n">
-        <v>1378901781</v>
+        <v>1843470413</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BOTZ.L</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1662,19 +1662,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0.4729</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>45482.71294556713</v>
+        <v>45804.66637251157</v>
       </c>
       <c r="G25" t="n">
-        <v>20.58</v>
+        <v>42.29</v>
       </c>
       <c r="H25" t="n">
-        <v>20.25</v>
+        <v>43.22</v>
       </c>
       <c r="I25" t="n">
-        <v>20.58</v>
+        <v>20</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -1691,18 +1691,18 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.33</v>
+        <v>0.44</v>
       </c>
       <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="n">
-        <v>1727563010</v>
+        <v>1882278057</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1711,19 +1711,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0.0432</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>45743.76106726852</v>
+        <v>45826.76262912037</v>
       </c>
       <c r="G26" t="n">
-        <v>46.11</v>
+        <v>346.61</v>
       </c>
       <c r="H26" t="n">
-        <v>46.99</v>
+        <v>340.31</v>
       </c>
       <c r="I26" t="n">
-        <v>46.11</v>
+        <v>14.97</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -1740,18 +1740,18 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0.88</v>
+        <v>-0.27</v>
       </c>
       <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="n">
-        <v>1824476420</v>
+        <v>1817256440</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1760,19 +1760,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.1548</v>
+        <v>0.2267</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>45792.64714148148</v>
+        <v>45789.64787115741</v>
       </c>
       <c r="G27" t="n">
-        <v>129.17</v>
+        <v>44.1</v>
       </c>
       <c r="H27" t="n">
-        <v>131.36</v>
+        <v>42.37</v>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -1789,18 +1789,18 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.33</v>
+        <v>-0.39</v>
       </c>
       <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="n">
-        <v>1666459175</v>
+        <v>1582723120</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1809,19 +1809,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.1641</v>
+        <v>0.3755</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>45708.68165298611</v>
+        <v>45645.89511640046</v>
       </c>
       <c r="G28" t="n">
-        <v>17.18</v>
+        <v>53.26</v>
       </c>
       <c r="H28" t="n">
-        <v>21.24</v>
+        <v>59.49</v>
       </c>
       <c r="I28" t="n">
-        <v>2.82</v>
+        <v>20</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -1838,14 +1838,14 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0.67</v>
+        <v>2.34</v>
       </c>
       <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
-        <v>1701100027</v>
+        <v>1830408508</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1858,19 +1858,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.7812</v>
+        <v>0.5793</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>45727.87202070602</v>
+        <v>45796.82346997685</v>
       </c>
       <c r="G29" t="n">
-        <v>19.2</v>
+        <v>17.26</v>
       </c>
       <c r="H29" t="n">
-        <v>17</v>
+        <v>20.3</v>
       </c>
       <c r="I29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -1887,18 +1887,18 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>-1.72</v>
+        <v>1.76</v>
       </c>
       <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
-        <v>1744916452</v>
+        <v>1712849726</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1907,19 +1907,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.4245</v>
+        <v>0.0861</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45751.74230173611</v>
+        <v>45734.85489405093</v>
       </c>
       <c r="G30" t="n">
-        <v>17.54</v>
+        <v>127.72</v>
       </c>
       <c r="H30" t="n">
-        <v>21.24</v>
+        <v>142.34</v>
       </c>
       <c r="I30" t="n">
-        <v>7.45</v>
+        <v>11</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -1936,18 +1936,18 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="n">
-        <v>1830410729</v>
+        <v>1680991980</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1956,19 +1956,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.297</v>
+        <v>0.1066</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45796.82476561343</v>
+        <v>45716.8556621875</v>
       </c>
       <c r="G31" t="n">
-        <v>33.66</v>
+        <v>178.67</v>
       </c>
       <c r="H31" t="n">
-        <v>31.09</v>
+        <v>213.27</v>
       </c>
       <c r="I31" t="n">
-        <v>10</v>
+        <v>19.05</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1985,18 +1985,18 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.77</v>
+        <v>3.69</v>
       </c>
       <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="n">
-        <v>1648737122</v>
+        <v>1811432805</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2005,19 +2005,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.0269</v>
+        <v>0.0856</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45695.85619950231</v>
+        <v>45785.66143211805</v>
       </c>
       <c r="G32" t="n">
-        <v>408.33</v>
+        <v>128.46</v>
       </c>
       <c r="H32" t="n">
-        <v>459.55</v>
+        <v>142.34</v>
       </c>
       <c r="I32" t="n">
-        <v>10.98</v>
+        <v>11</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -2034,18 +2034,18 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="n">
-        <v>1582714896</v>
+        <v>1582737192</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2054,19 +2054,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.4847</v>
+        <v>0.001</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45645.89066263889</v>
+        <v>45645.90143930555</v>
       </c>
       <c r="G33" t="n">
-        <v>20.62</v>
+        <v>524.4299999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>17</v>
+        <v>538.84</v>
       </c>
       <c r="I33" t="n">
-        <v>9.99</v>
+        <v>0.52</v>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -2083,18 +2083,18 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>-1.75</v>
+        <v>0.02</v>
       </c>
       <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="n">
-        <v>1843468958</v>
+        <v>1843474191</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2103,19 +2103,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.2208</v>
+        <v>0.9372</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45804.66597149306</v>
+        <v>45804.66699503472</v>
       </c>
       <c r="G34" t="n">
-        <v>67.93000000000001</v>
+        <v>21.33</v>
       </c>
       <c r="H34" t="n">
-        <v>70.56</v>
+        <v>20.77</v>
       </c>
       <c r="I34" t="n">
-        <v>15</v>
+        <v>19.99</v>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
@@ -2132,18 +2132,18 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.58</v>
+        <v>-0.52</v>
       </c>
       <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>1811432805</v>
+        <v>1744916497</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2152,19 +2152,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.0856</v>
+        <v>1</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>45785.66143211805</v>
+        <v>45751.74231563658</v>
       </c>
       <c r="G35" t="n">
-        <v>128.46</v>
+        <v>17.54</v>
       </c>
       <c r="H35" t="n">
-        <v>157.86</v>
+        <v>20.77</v>
       </c>
       <c r="I35" t="n">
-        <v>11</v>
+        <v>17.54</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
@@ -2181,18 +2181,18 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.51</v>
+        <v>3.23</v>
       </c>
       <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>1559802942</v>
+        <v>1635194117</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2201,19 +2201,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.2585</v>
+        <v>0.2479</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45628.85929152778</v>
+        <v>45687.85228493056</v>
       </c>
       <c r="G36" t="n">
-        <v>77.34999999999999</v>
+        <v>40.33</v>
       </c>
       <c r="H36" t="n">
-        <v>70.56</v>
+        <v>35.26</v>
       </c>
       <c r="I36" t="n">
-        <v>19.99</v>
+        <v>10</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -2230,18 +2230,18 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>-1.75</v>
+        <v>-1.26</v>
       </c>
       <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
-        <v>1644788775</v>
+        <v>1381417257</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2250,19 +2250,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.07580000000000001</v>
+        <v>1</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>45693.85093391204</v>
+        <v>45484.67877329861</v>
       </c>
       <c r="G37" t="n">
-        <v>144.94</v>
+        <v>16.374</v>
       </c>
       <c r="H37" t="n">
-        <v>131.36</v>
+        <v>15.2</v>
       </c>
       <c r="I37" t="n">
-        <v>10.99</v>
+        <v>17.9</v>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
@@ -2279,18 +2279,18 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>-1.03</v>
+        <v>-0.48</v>
       </c>
       <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>1817264187</v>
+        <v>1882281884</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2299,19 +2299,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.4757</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45789.64859377315</v>
+        <v>45826.76479001158</v>
       </c>
       <c r="G38" t="n">
-        <v>42.02</v>
+        <v>138.84</v>
       </c>
       <c r="H38" t="n">
-        <v>41.16</v>
+        <v>138.29</v>
       </c>
       <c r="I38" t="n">
-        <v>19.99</v>
+        <v>10</v>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
@@ -2328,18 +2328,18 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>-0.41</v>
+        <v>-0.04</v>
       </c>
       <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
-        <v>1666451221</v>
+        <v>1880441651</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2348,19 +2348,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.0001</v>
+        <v>1</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45708.68022634259</v>
+        <v>45825.89055887731</v>
       </c>
       <c r="G39" t="n">
-        <v>43</v>
+        <v>21.21</v>
       </c>
       <c r="H39" t="n">
-        <v>43.82</v>
+        <v>21.07</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>21.21</v>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -2377,18 +2377,18 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="n">
-        <v>1701098878</v>
+        <v>1461331124</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2397,19 +2397,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.0383</v>
+        <v>0.3922</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>45727.87167594907</v>
+        <v>45553.65374138889</v>
       </c>
       <c r="G40" t="n">
-        <v>139.41</v>
+        <v>50.99</v>
       </c>
       <c r="H40" t="n">
-        <v>157.86</v>
+        <v>59.49</v>
       </c>
       <c r="I40" t="n">
-        <v>5.34</v>
+        <v>20</v>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
@@ -2426,18 +2426,18 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.71</v>
+        <v>3.33</v>
       </c>
       <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="n">
-        <v>1806979127</v>
+        <v>1867195417</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2446,19 +2446,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.6361</v>
+        <v>0.1044</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45783.83125244213</v>
+        <v>45818.80165224537</v>
       </c>
       <c r="G41" t="n">
-        <v>15.72</v>
+        <v>143.6</v>
       </c>
       <c r="H41" t="n">
-        <v>17</v>
+        <v>138.29</v>
       </c>
       <c r="I41" t="n">
-        <v>10</v>
+        <v>14.99</v>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
@@ -2475,18 +2475,18 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.55</v>
       </c>
       <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="n">
-        <v>1381417257</v>
+        <v>1644788775</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2495,19 +2495,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>45484.67877329861</v>
+        <v>45693.85093391204</v>
       </c>
       <c r="G42" t="n">
-        <v>16.374</v>
+        <v>144.94</v>
       </c>
       <c r="H42" t="n">
-        <v>15.134</v>
+        <v>128.99</v>
       </c>
       <c r="I42" t="n">
-        <v>17.9</v>
+        <v>10.99</v>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -2524,18 +2524,18 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>-0.8</v>
+        <v>-1.21</v>
       </c>
       <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="n">
-        <v>1680993370</v>
+        <v>1754304266</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2544,19 +2544,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>0.7137</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>45716.85638861111</v>
+        <v>45755.88055112268</v>
       </c>
       <c r="G43" t="n">
-        <v>44.49</v>
+        <v>14</v>
       </c>
       <c r="H43" t="n">
-        <v>46.99</v>
+        <v>20.3</v>
       </c>
       <c r="I43" t="n">
-        <v>44.49</v>
+        <v>9.99</v>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -2573,18 +2573,18 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
-        <v>1533882988</v>
+        <v>1559802942</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BOTZ.L</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2593,19 +2593,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.5</v>
+        <v>0.2585</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45609.60769543982</v>
+        <v>45628.85929152778</v>
       </c>
       <c r="G44" t="n">
-        <v>21.905</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>20.25</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>10.95</v>
+        <v>19.99</v>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -2622,18 +2622,18 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>-0.82</v>
+        <v>-1.49</v>
       </c>
       <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>1754302454</v>
+        <v>1880446729</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2642,19 +2642,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.3673</v>
+        <v>0.0772</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>45755.88025324074</v>
+        <v>45825.89315055555</v>
       </c>
       <c r="G45" t="n">
-        <v>27.17</v>
+        <v>129.62</v>
       </c>
       <c r="H45" t="n">
-        <v>35.39</v>
+        <v>128.99</v>
       </c>
       <c r="I45" t="n">
-        <v>9.98</v>
+        <v>10.01</v>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -2671,18 +2671,18 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>3.02</v>
+        <v>-0.05</v>
       </c>
       <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>1744879358</v>
+        <v>1621495187</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2691,19 +2691,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.2701</v>
+        <v>0.2318</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>45751.73925940973</v>
+        <v>45678.83178196759</v>
       </c>
       <c r="G46" t="n">
-        <v>148.09</v>
+        <v>43.27</v>
       </c>
       <c r="H46" t="n">
-        <v>193.28</v>
+        <v>35.26</v>
       </c>
       <c r="I46" t="n">
-        <v>40</v>
+        <v>10.03</v>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -2720,18 +2720,18 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>12.2</v>
+        <v>-1.86</v>
       </c>
       <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>1517510856</v>
+        <v>1867194722</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2740,19 +2740,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.0602</v>
+        <v>1</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>45597.61014849537</v>
+        <v>45818.80135700232</v>
       </c>
       <c r="G47" t="n">
-        <v>166.03</v>
+        <v>21.27</v>
       </c>
       <c r="H47" t="n">
-        <v>131.36</v>
+        <v>21.07</v>
       </c>
       <c r="I47" t="n">
-        <v>10</v>
+        <v>21.27</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -2769,18 +2769,18 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>-2.09</v>
+        <v>-0.2</v>
       </c>
       <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>1582735114</v>
+        <v>1806979127</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2789,19 +2789,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.0003</v>
+        <v>0.6361</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>45645.90076803241</v>
+        <v>45783.83125244213</v>
       </c>
       <c r="G48" t="n">
-        <v>130.51</v>
+        <v>15.72</v>
       </c>
       <c r="H48" t="n">
-        <v>143.76</v>
+        <v>20.3</v>
       </c>
       <c r="I48" t="n">
-        <v>0.04</v>
+        <v>10</v>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -2818,18 +2818,18 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
-        <v>1563288050</v>
+        <v>1776193271</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2838,16 +2838,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.0626</v>
+        <v>0.6724</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45630.85583428241</v>
+        <v>45764.85451520833</v>
       </c>
       <c r="G49" t="n">
-        <v>159.74</v>
+        <v>14.87</v>
       </c>
       <c r="H49" t="n">
-        <v>131.36</v>
+        <v>17.65</v>
       </c>
       <c r="I49" t="n">
         <v>10</v>
@@ -2867,18 +2867,18 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>-1.78</v>
+        <v>1.87</v>
       </c>
       <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
-        <v>1599431096</v>
+        <v>1594315903</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.1013</v>
+        <v>1</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>45663.73014731482</v>
+        <v>45659.42644752315</v>
       </c>
       <c r="G50" t="n">
-        <v>148.02</v>
+        <v>16.425</v>
       </c>
       <c r="H50" t="n">
-        <v>131.36</v>
+        <v>15.2</v>
       </c>
       <c r="I50" t="n">
-        <v>14.99</v>
+        <v>17.11</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -2916,18 +2916,18 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>-1.68</v>
+        <v>0.31</v>
       </c>
       <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>1845429980</v>
+        <v>1680993370</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2939,16 +2939,16 @@
         <v>1</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>45805.66181400463</v>
+        <v>45716.85638861111</v>
       </c>
       <c r="G51" t="n">
-        <v>13.27</v>
+        <v>44.49</v>
       </c>
       <c r="H51" t="n">
-        <v>13.225</v>
+        <v>48.15</v>
       </c>
       <c r="I51" t="n">
-        <v>15.09</v>
+        <v>44.49</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -2965,18 +2965,18 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>-0.15</v>
+        <v>3.66</v>
       </c>
       <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
-        <v>1662993636</v>
+        <v>1701100481</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2985,19 +2985,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>0.0873</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>45706.87026833333</v>
+        <v>45727.87214378472</v>
       </c>
       <c r="G52" t="n">
-        <v>20.65</v>
+        <v>171.67</v>
       </c>
       <c r="H52" t="n">
-        <v>22.23</v>
+        <v>213.27</v>
       </c>
       <c r="I52" t="n">
-        <v>20.65</v>
+        <v>14.99</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
@@ -3014,18 +3014,18 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>1.58</v>
+        <v>3.63</v>
       </c>
       <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="n">
-        <v>1806978791</v>
+        <v>1867197360</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3034,19 +3034,19 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.0867</v>
+        <v>0.0765</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>45783.83109655092</v>
+        <v>45818.80265583334</v>
       </c>
       <c r="G53" t="n">
-        <v>126.78</v>
+        <v>131.96</v>
       </c>
       <c r="H53" t="n">
-        <v>157.86</v>
+        <v>128.99</v>
       </c>
       <c r="I53" t="n">
-        <v>10.99</v>
+        <v>10.09</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
@@ -3063,18 +3063,18 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.7</v>
+        <v>-0.22</v>
       </c>
       <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="n">
-        <v>1554741910</v>
+        <v>1806977521</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3083,19 +3083,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.3495</v>
+        <v>0.3367</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>45623.74951116898</v>
+        <v>45783.8305750463</v>
       </c>
       <c r="G54" t="n">
-        <v>15.3</v>
+        <v>29.7</v>
       </c>
       <c r="H54" t="n">
-        <v>21.24</v>
+        <v>35.26</v>
       </c>
       <c r="I54" t="n">
-        <v>5.35</v>
+        <v>10</v>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
@@ -3112,18 +3112,18 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="n">
-        <v>1648733962</v>
+        <v>1867462173</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3132,19 +3132,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.081</v>
+        <v>0.1284</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>45695.85463682871</v>
+        <v>45818.90866184028</v>
       </c>
       <c r="G55" t="n">
-        <v>129.56</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="H55" t="n">
-        <v>143.68</v>
+        <v>78.31</v>
       </c>
       <c r="I55" t="n">
-        <v>10.49</v>
+        <v>10.01</v>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
@@ -3161,18 +3161,18 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>1.15</v>
+        <v>0.05</v>
       </c>
       <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="n">
-        <v>1824482557</v>
+        <v>1744930699</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BND</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3181,19 +3181,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.2641</v>
+        <v>1</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>45792.64805195602</v>
+        <v>45751.74534789352</v>
       </c>
       <c r="G56" t="n">
-        <v>56.78</v>
+        <v>74.13</v>
       </c>
       <c r="H56" t="n">
-        <v>60.5</v>
+        <v>72.83</v>
       </c>
       <c r="I56" t="n">
-        <v>15</v>
+        <v>74.13</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
@@ -3210,18 +3210,18 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>0.98</v>
+        <v>-1.3</v>
       </c>
       <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="n">
-        <v>1825032062</v>
+        <v>1648733962</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3230,19 +3230,19 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.3559</v>
+        <v>0.081</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45792.76080334491</v>
+        <v>45695.85463682871</v>
       </c>
       <c r="G57" t="n">
-        <v>28.09</v>
+        <v>129.56</v>
       </c>
       <c r="H57" t="n">
-        <v>31.92</v>
+        <v>127.93</v>
       </c>
       <c r="I57" t="n">
-        <v>10</v>
+        <v>10.49</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
@@ -3259,18 +3259,18 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>1.36</v>
+        <v>-0.13</v>
       </c>
       <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
-        <v>1811475646</v>
+        <v>1378901781</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>BOTZ.L</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3282,16 +3282,16 @@
         <v>1</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45785.66973634259</v>
+        <v>45482.71294556713</v>
       </c>
       <c r="G58" t="n">
-        <v>12.75</v>
+        <v>20.58</v>
       </c>
       <c r="H58" t="n">
-        <v>13.225</v>
+        <v>20.405</v>
       </c>
       <c r="I58" t="n">
-        <v>14.49</v>
+        <v>20.58</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
@@ -3308,18 +3308,18 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>0.45</v>
+        <v>-0.17</v>
       </c>
       <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="n">
-        <v>1381375440</v>
+        <v>1599449649</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3328,19 +3328,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.1057</v>
+        <v>0.4145</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>45484.67118315972</v>
+        <v>45663.73562525463</v>
       </c>
       <c r="G59" t="n">
-        <v>189.11</v>
+        <v>24.11</v>
       </c>
       <c r="H59" t="n">
-        <v>193.28</v>
+        <v>20.3</v>
       </c>
       <c r="I59" t="n">
-        <v>19.99</v>
+        <v>9.99</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
@@ -3357,18 +3357,18 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>0.44</v>
+        <v>-1.58</v>
       </c>
       <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="n">
-        <v>1680991980</v>
+        <v>1845429956</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3377,19 +3377,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.1958</v>
+        <v>0.6565</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45716.8556621875</v>
+        <v>45805.66180811343</v>
       </c>
       <c r="G60" t="n">
-        <v>178.67</v>
+        <v>13.275</v>
       </c>
       <c r="H60" t="n">
-        <v>193.28</v>
+        <v>13.07</v>
       </c>
       <c r="I60" t="n">
-        <v>34.98</v>
+        <v>9.91</v>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
@@ -3406,18 +3406,18 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>2.86</v>
+        <v>-0.08</v>
       </c>
       <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="n">
-        <v>1644789287</v>
+        <v>1648735305</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3426,19 +3426,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.0813</v>
+        <v>0.4576</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>45693.85123056713</v>
+        <v>45695.85530675926</v>
       </c>
       <c r="G61" t="n">
-        <v>129.08</v>
+        <v>21.85</v>
       </c>
       <c r="H61" t="n">
-        <v>143.68</v>
+        <v>20.3</v>
       </c>
       <c r="I61" t="n">
-        <v>10.49</v>
+        <v>10</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
@@ -3455,18 +3455,18 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>1.19</v>
+        <v>-0.71</v>
       </c>
       <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="n">
-        <v>1621495187</v>
+        <v>1727591551</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>BND</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3475,19 +3475,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.2318</v>
+        <v>1</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>45678.83178196759</v>
+        <v>45743.77389555555</v>
       </c>
       <c r="G62" t="n">
-        <v>43.27</v>
+        <v>72.87</v>
       </c>
       <c r="H62" t="n">
-        <v>35.39</v>
+        <v>72.83</v>
       </c>
       <c r="I62" t="n">
-        <v>10.03</v>
+        <v>72.87</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
@@ -3504,18 +3504,18 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>-1.83</v>
+        <v>-0.04</v>
       </c>
       <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="n">
-        <v>1843474191</v>
+        <v>1559803221</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3524,19 +3524,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.9372</v>
+        <v>0.092</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>45804.66699503472</v>
+        <v>45628.85951927083</v>
       </c>
       <c r="G63" t="n">
-        <v>21.33</v>
+        <v>162.85</v>
       </c>
       <c r="H63" t="n">
-        <v>21.24</v>
+        <v>128.99</v>
       </c>
       <c r="I63" t="n">
-        <v>19.99</v>
+        <v>14.98</v>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
@@ -3553,18 +3553,18 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>-0.08</v>
+        <v>-3.11</v>
       </c>
       <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="n">
-        <v>1481609355</v>
+        <v>1824476420</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3573,19 +3573,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.107</v>
+        <v>0.1548</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>45568.7734872338</v>
+        <v>45792.64714148148</v>
       </c>
       <c r="G64" t="n">
-        <v>140.18</v>
+        <v>129.17</v>
       </c>
       <c r="H64" t="n">
-        <v>143.68</v>
+        <v>128.99</v>
       </c>
       <c r="I64" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
@@ -3602,18 +3602,18 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>0.37</v>
+        <v>-0.03</v>
       </c>
       <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="n">
-        <v>1653137218</v>
+        <v>1845431561</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3622,16 +3622,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.277</v>
+        <v>0.3271</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>45699.85152199074</v>
+        <v>45805.66210755787</v>
       </c>
       <c r="G65" t="n">
-        <v>36.1</v>
+        <v>30.57</v>
       </c>
       <c r="H65" t="n">
-        <v>35.39</v>
+        <v>35.28</v>
       </c>
       <c r="I65" t="n">
         <v>10</v>
@@ -3651,18 +3651,18 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>-0.2</v>
+        <v>1.54</v>
       </c>
       <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="n">
-        <v>1566610015</v>
+        <v>1806978791</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3671,19 +3671,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.9385</v>
+        <v>0.0867</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>45632.87667083334</v>
+        <v>45783.83109655092</v>
       </c>
       <c r="G66" t="n">
-        <v>21.31</v>
+        <v>126.78</v>
       </c>
       <c r="H66" t="n">
-        <v>17</v>
+        <v>142.34</v>
       </c>
       <c r="I66" t="n">
-        <v>20</v>
+        <v>10.99</v>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
@@ -3700,18 +3700,18 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>-4.05</v>
+        <v>1.35</v>
       </c>
       <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="n">
-        <v>1599435465</v>
+        <v>1517510856</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3720,19 +3720,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.0289</v>
+        <v>0.0602</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>45663.73115600694</v>
+        <v>45597.61014849537</v>
       </c>
       <c r="G67" t="n">
-        <v>517.7</v>
+        <v>166.03</v>
       </c>
       <c r="H67" t="n">
-        <v>582.1799999999999</v>
+        <v>128.99</v>
       </c>
       <c r="I67" t="n">
-        <v>14.96</v>
+        <v>10</v>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
@@ -3749,18 +3749,18 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>1.87</v>
+        <v>-2.23</v>
       </c>
       <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="n">
-        <v>1843477272</v>
+        <v>1358151307</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3769,19 +3769,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>0.1081</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>45804.66725678241</v>
+        <v>45460.88529052083</v>
       </c>
       <c r="G68" t="n">
-        <v>17.86</v>
+        <v>165.93</v>
       </c>
       <c r="H68" t="n">
-        <v>17.82</v>
+        <v>128.99</v>
       </c>
       <c r="I68" t="n">
-        <v>17.86</v>
+        <v>17.94</v>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
@@ -3798,18 +3798,18 @@
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>-0.04</v>
+        <v>-3.99</v>
       </c>
       <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="n">
-        <v>1666461140</v>
+        <v>1727563010</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3818,19 +3818,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.2651</v>
+        <v>1</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>45708.68207092593</v>
+        <v>45743.76106726852</v>
       </c>
       <c r="G69" t="n">
-        <v>37.7</v>
+        <v>46.11</v>
       </c>
       <c r="H69" t="n">
-        <v>35.39</v>
+        <v>48.15</v>
       </c>
       <c r="I69" t="n">
-        <v>9.99</v>
+        <v>46.11</v>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
@@ -3847,18 +3847,18 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>-0.61</v>
+        <v>2.04</v>
       </c>
       <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="n">
-        <v>1744929368</v>
+        <v>1824482557</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3867,19 +3867,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.0192</v>
+        <v>0.2641</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>45751.74500871528</v>
+        <v>45792.64805195602</v>
       </c>
       <c r="G70" t="n">
-        <v>324.48</v>
+        <v>56.78</v>
       </c>
       <c r="H70" t="n">
-        <v>365.19</v>
+        <v>59.49</v>
       </c>
       <c r="I70" t="n">
-        <v>6.23</v>
+        <v>15</v>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
@@ -3896,18 +3896,18 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>0.78</v>
+        <v>0.71</v>
       </c>
       <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="n">
-        <v>1358151307</v>
+        <v>1845429980</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3916,19 +3916,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.1081</v>
+        <v>1</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>45460.88529052083</v>
+        <v>45805.66181400463</v>
       </c>
       <c r="G71" t="n">
-        <v>165.93</v>
+        <v>13.27</v>
       </c>
       <c r="H71" t="n">
-        <v>131.36</v>
+        <v>13.07</v>
       </c>
       <c r="I71" t="n">
-        <v>17.94</v>
+        <v>15.09</v>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
@@ -3945,18 +3945,18 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>-3.73</v>
+        <v>-0.11</v>
       </c>
       <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="n">
-        <v>1727564345</v>
+        <v>1666461140</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3965,19 +3965,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.3274</v>
+        <v>0.2651</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>45743.76175270833</v>
+        <v>45708.68207092593</v>
       </c>
       <c r="G72" t="n">
-        <v>30.54</v>
+        <v>37.7</v>
       </c>
       <c r="H72" t="n">
-        <v>31.92</v>
+        <v>35.26</v>
       </c>
       <c r="I72" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -3994,18 +3994,18 @@
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>0.45</v>
+        <v>-0.64</v>
       </c>
       <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="n">
-        <v>1824475555</v>
+        <v>1631475148</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4014,19 +4014,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>0.2592</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45792.64702015046</v>
+        <v>45685.83625201389</v>
       </c>
       <c r="G73" t="n">
-        <v>21.66</v>
+        <v>38.58</v>
       </c>
       <c r="H73" t="n">
-        <v>22.23</v>
+        <v>35.26</v>
       </c>
       <c r="I73" t="n">
-        <v>21.66</v>
+        <v>10</v>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
@@ -4043,18 +4043,18 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>0.57</v>
+        <v>-0.86</v>
       </c>
       <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="n">
-        <v>1701100481</v>
+        <v>1554741910</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4063,19 +4063,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.0873</v>
+        <v>0.3495</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45727.87214378472</v>
+        <v>45623.74951116898</v>
       </c>
       <c r="G74" t="n">
-        <v>171.67</v>
+        <v>15.3</v>
       </c>
       <c r="H74" t="n">
-        <v>193.28</v>
+        <v>20.77</v>
       </c>
       <c r="I74" t="n">
-        <v>14.99</v>
+        <v>5.35</v>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
@@ -4092,18 +4092,18 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="n">
-        <v>1744916497</v>
+        <v>1599455288</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4112,19 +4112,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>0.2195</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>45751.74231563658</v>
+        <v>45663.73750263889</v>
       </c>
       <c r="G75" t="n">
-        <v>17.54</v>
+        <v>45.55</v>
       </c>
       <c r="H75" t="n">
-        <v>21.24</v>
+        <v>35.26</v>
       </c>
       <c r="I75" t="n">
-        <v>17.54</v>
+        <v>10</v>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
@@ -4141,18 +4141,18 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>3.7</v>
+        <v>-2.26</v>
       </c>
       <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="n">
-        <v>1796453499</v>
+        <v>1869077157</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4161,19 +4161,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.6422</v>
+        <v>0.3061</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>45777.64668229167</v>
+        <v>45819.6742621412</v>
       </c>
       <c r="G76" t="n">
-        <v>15.57</v>
+        <v>13.285</v>
       </c>
       <c r="H76" t="n">
-        <v>17.82</v>
+        <v>13.07</v>
       </c>
       <c r="I76" t="n">
-        <v>10</v>
+        <v>4.69</v>
       </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
@@ -4190,18 +4190,18 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>1.44</v>
+        <v>-0.11</v>
       </c>
       <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="n">
-        <v>1830408508</v>
+        <v>1880445013</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4210,16 +4210,16 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.5793</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>45796.82346997685</v>
+        <v>45825.8922271412</v>
       </c>
       <c r="G77" t="n">
-        <v>17.26</v>
+        <v>139.86</v>
       </c>
       <c r="H77" t="n">
-        <v>17</v>
+        <v>138.29</v>
       </c>
       <c r="I77" t="n">
         <v>10</v>
@@ -4239,18 +4239,18 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>-0.15</v>
+        <v>-0.11</v>
       </c>
       <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="n">
-        <v>1635194724</v>
+        <v>1653137218</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4259,16 +4259,16 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.2875</v>
+        <v>0.277</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>45687.85271734954</v>
+        <v>45699.85152199074</v>
       </c>
       <c r="G78" t="n">
-        <v>34.78</v>
+        <v>36.1</v>
       </c>
       <c r="H78" t="n">
-        <v>31.92</v>
+        <v>35.26</v>
       </c>
       <c r="I78" t="n">
         <v>10</v>
@@ -4288,18 +4288,18 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>-0.82</v>
+        <v>-0.23</v>
       </c>
       <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="n">
-        <v>1582708979</v>
+        <v>1727564345</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4308,19 +4308,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.0769</v>
+        <v>0.3274</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>45645.88746980324</v>
+        <v>45743.76175270833</v>
       </c>
       <c r="G79" t="n">
-        <v>195.11</v>
+        <v>30.54</v>
       </c>
       <c r="H79" t="n">
-        <v>193.28</v>
+        <v>35.28</v>
       </c>
       <c r="I79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
@@ -4337,18 +4337,18 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>-0.14</v>
+        <v>1.55</v>
       </c>
       <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="n">
-        <v>1843470413</v>
+        <v>1563288050</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4357,19 +4357,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.4729</v>
+        <v>0.0626</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>45804.66637251157</v>
+        <v>45630.85583428241</v>
       </c>
       <c r="G80" t="n">
-        <v>42.29</v>
+        <v>159.74</v>
       </c>
       <c r="H80" t="n">
-        <v>41.16</v>
+        <v>128.99</v>
       </c>
       <c r="I80" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
@@ -4386,18 +4386,18 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>-0.54</v>
+        <v>-1.93</v>
       </c>
       <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="n">
-        <v>1495551484</v>
+        <v>1701098878</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4406,19 +4406,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.1914</v>
+        <v>0.0383</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>45580.70648087963</v>
+        <v>45727.87167594907</v>
       </c>
       <c r="G81" t="n">
-        <v>135.82</v>
+        <v>139.41</v>
       </c>
       <c r="H81" t="n">
-        <v>139.03</v>
+        <v>142.34</v>
       </c>
       <c r="I81" t="n">
-        <v>26</v>
+        <v>5.34</v>
       </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
@@ -4435,18 +4435,18 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>0.61</v>
+        <v>0.11</v>
       </c>
       <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="n">
-        <v>1633116336</v>
+        <v>1843477272</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4458,16 +4458,16 @@
         <v>1</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>45686.83272234954</v>
+        <v>45804.66725678241</v>
       </c>
       <c r="G82" t="n">
-        <v>44.24</v>
+        <v>17.86</v>
       </c>
       <c r="H82" t="n">
-        <v>46.99</v>
+        <v>17.65</v>
       </c>
       <c r="I82" t="n">
-        <v>44.24</v>
+        <v>17.86</v>
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
@@ -4484,18 +4484,18 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>2.75</v>
+        <v>-0.21</v>
       </c>
       <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="n">
-        <v>1554742887</v>
+        <v>1666459175</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4504,19 +4504,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.1641</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>45623.74993112269</v>
+        <v>45708.68165298611</v>
       </c>
       <c r="G83" t="n">
-        <v>178.48</v>
+        <v>17.18</v>
       </c>
       <c r="H83" t="n">
-        <v>193.28</v>
+        <v>20.77</v>
       </c>
       <c r="I83" t="n">
-        <v>14.99</v>
+        <v>2.82</v>
       </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
@@ -4533,18 +4533,18 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>1.25</v>
+        <v>0.59</v>
       </c>
       <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="n">
-        <v>1594315903</v>
+        <v>1843468958</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4553,19 +4553,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1</v>
+        <v>0.2208</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>45659.42644752315</v>
+        <v>45804.66597149306</v>
       </c>
       <c r="G84" t="n">
-        <v>16.425</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="H84" t="n">
-        <v>15.134</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>17.11</v>
+        <v>15</v>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
@@ -4582,18 +4582,18 @@
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>-0.01</v>
+        <v>0.8</v>
       </c>
       <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="n">
-        <v>1461331124</v>
+        <v>1744916452</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4602,19 +4602,19 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.3922</v>
+        <v>0.4245</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>45553.65374138889</v>
+        <v>45751.74230173611</v>
       </c>
       <c r="G85" t="n">
-        <v>50.99</v>
+        <v>17.54</v>
       </c>
       <c r="H85" t="n">
-        <v>60.5</v>
+        <v>20.77</v>
       </c>
       <c r="I85" t="n">
-        <v>20</v>
+        <v>7.45</v>
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
@@ -4631,18 +4631,18 @@
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>3.73</v>
+        <v>1.37</v>
       </c>
       <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="n">
-        <v>1806980482</v>
+        <v>1662993636</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4651,19 +4651,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.2406</v>
+        <v>1</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>45783.83189613426</v>
+        <v>45706.87026833333</v>
       </c>
       <c r="G86" t="n">
-        <v>16.12</v>
+        <v>20.65</v>
       </c>
       <c r="H86" t="n">
-        <v>17.82</v>
+        <v>21.07</v>
       </c>
       <c r="I86" t="n">
-        <v>3.88</v>
+        <v>20.65</v>
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
@@ -4680,7 +4680,7 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="Q86" t="inlineStr"/>
     </row>
@@ -4709,7 +4709,7 @@
         <v>77.53</v>
       </c>
       <c r="H87" t="n">
-        <v>70.56</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="I87" t="n">
         <v>14.99</v>
@@ -4729,7 +4729,7 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>-1.35</v>
+        <v>-1.16</v>
       </c>
       <c r="Q87" t="inlineStr"/>
     </row>
@@ -4758,7 +4758,7 @@
         <v>232.2</v>
       </c>
       <c r="H88" t="n">
-        <v>200.85</v>
+        <v>196.61</v>
       </c>
       <c r="I88" t="n">
         <v>0.02</v>
@@ -4785,11 +4785,11 @@
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="n">
-        <v>1532661507</v>
+        <v>1662995258</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4798,19 +4798,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.2943</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>45608.74251107639</v>
+        <v>45706.87121422453</v>
       </c>
       <c r="G89" t="n">
-        <v>190.67</v>
+        <v>67.97</v>
       </c>
       <c r="H89" t="n">
-        <v>193.28</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="I89" t="n">
-        <v>12.98</v>
+        <v>20</v>
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
@@ -4827,18 +4827,18 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>0.18</v>
+        <v>1.06</v>
       </c>
       <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="n">
-        <v>1727574394</v>
+        <v>1880443947</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4847,19 +4847,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>0.1047</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>45743.76658678241</v>
+        <v>45825.891695625</v>
       </c>
       <c r="G90" t="n">
-        <v>21.13</v>
+        <v>142.99</v>
       </c>
       <c r="H90" t="n">
-        <v>22.23</v>
+        <v>142.34</v>
       </c>
       <c r="I90" t="n">
-        <v>21.13</v>
+        <v>14.97</v>
       </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
@@ -4876,18 +4876,18 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>1.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="n">
-        <v>1712850989</v>
+        <v>1867461578</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>BAP</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4896,19 +4896,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.1244</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>45734.85576775463</v>
+        <v>45818.90835071759</v>
       </c>
       <c r="G91" t="n">
-        <v>160.64</v>
+        <v>216.54</v>
       </c>
       <c r="H91" t="n">
-        <v>171.72</v>
+        <v>217.2</v>
       </c>
       <c r="I91" t="n">
-        <v>19.98</v>
+        <v>19.99</v>
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
@@ -4925,18 +4925,18 @@
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>1.38</v>
+        <v>0.06</v>
       </c>
       <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="n">
-        <v>1744767540</v>
+        <v>1648737122</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4945,19 +4945,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.643</v>
+        <v>0.01</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>45751.72316712963</v>
+        <v>45695.85619950231</v>
       </c>
       <c r="G92" t="n">
-        <v>15.55</v>
+        <v>408.33</v>
       </c>
       <c r="H92" t="n">
-        <v>17</v>
+        <v>480</v>
       </c>
       <c r="I92" t="n">
-        <v>10</v>
+        <v>4.08</v>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
@@ -4974,18 +4974,18 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>0.93</v>
+        <v>0.72</v>
       </c>
       <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="n">
-        <v>1680994777</v>
+        <v>1754302454</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4994,19 +4994,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.7278</v>
+        <v>0.3673</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>45716.85705375</v>
+        <v>45755.88025324074</v>
       </c>
       <c r="G93" t="n">
-        <v>20.6</v>
+        <v>27.17</v>
       </c>
       <c r="H93" t="n">
-        <v>17</v>
+        <v>35.26</v>
       </c>
       <c r="I93" t="n">
-        <v>14.99</v>
+        <v>9.98</v>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
@@ -5023,18 +5023,18 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>-2.62</v>
+        <v>2.97</v>
       </c>
       <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="n">
-        <v>1635194117</v>
+        <v>1599448103</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5043,19 +5043,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.2479</v>
+        <v>0.2839</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>45687.85228493056</v>
+        <v>45663.73506711805</v>
       </c>
       <c r="G94" t="n">
-        <v>40.33</v>
+        <v>52.83</v>
       </c>
       <c r="H94" t="n">
-        <v>35.39</v>
+        <v>59.49</v>
       </c>
       <c r="I94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
@@ -5072,14 +5072,14 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>-1.23</v>
+        <v>1.89</v>
       </c>
       <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="n">
-        <v>1559803221</v>
+        <v>1599431096</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -5092,19 +5092,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.092</v>
+        <v>0.1013</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>45628.85951927083</v>
+        <v>45663.73014731482</v>
       </c>
       <c r="G95" t="n">
-        <v>162.85</v>
+        <v>148.02</v>
       </c>
       <c r="H95" t="n">
-        <v>131.36</v>
+        <v>128.99</v>
       </c>
       <c r="I95" t="n">
-        <v>14.98</v>
+        <v>14.99</v>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -5121,18 +5121,18 @@
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>-2.89</v>
+        <v>-1.92</v>
       </c>
       <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="n">
-        <v>1599455288</v>
+        <v>1843477152</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5141,19 +5141,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.2195</v>
+        <v>0.1198</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>45663.73750263889</v>
+        <v>45804.66724922453</v>
       </c>
       <c r="G96" t="n">
-        <v>45.55</v>
+        <v>17.86</v>
       </c>
       <c r="H96" t="n">
-        <v>35.39</v>
+        <v>17.65</v>
       </c>
       <c r="I96" t="n">
-        <v>10</v>
+        <v>2.14</v>
       </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
@@ -5170,18 +5170,18 @@
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>-2.23</v>
+        <v>-0.03</v>
       </c>
       <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="n">
-        <v>1845431561</v>
+        <v>1817264187</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5190,19 +5190,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.3271</v>
+        <v>0.4757</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>45805.66210755787</v>
+        <v>45789.64859377315</v>
       </c>
       <c r="G97" t="n">
-        <v>30.57</v>
+        <v>42.02</v>
       </c>
       <c r="H97" t="n">
-        <v>31.92</v>
+        <v>43.22</v>
       </c>
       <c r="I97" t="n">
-        <v>10</v>
+        <v>19.99</v>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
@@ -5219,18 +5219,18 @@
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>0.44</v>
+        <v>0.57</v>
       </c>
       <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="n">
-        <v>1582737192</v>
+        <v>1582714896</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5239,19 +5239,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.001</v>
+        <v>0.4847</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>45645.90143930555</v>
+        <v>45645.89066263889</v>
       </c>
       <c r="G98" t="n">
-        <v>524.4299999999999</v>
+        <v>20.62</v>
       </c>
       <c r="H98" t="n">
-        <v>582.1799999999999</v>
+        <v>20.3</v>
       </c>
       <c r="I98" t="n">
-        <v>0.52</v>
+        <v>9.99</v>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
@@ -5268,18 +5268,18 @@
         <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>0.06</v>
+        <v>-0.15</v>
       </c>
       <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="n">
-        <v>1559803984</v>
+        <v>1811475599</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5288,19 +5288,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.1076</v>
+        <v>0.7256</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>45628.86014383102</v>
+        <v>45785.66972070602</v>
       </c>
       <c r="G99" t="n">
-        <v>139.4</v>
+        <v>12.75</v>
       </c>
       <c r="H99" t="n">
-        <v>143.68</v>
+        <v>13.07</v>
       </c>
       <c r="I99" t="n">
-        <v>15</v>
+        <v>10.51</v>
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
@@ -5317,18 +5317,18 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="n">
-        <v>1666459270</v>
+        <v>1701100027</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5337,19 +5337,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1</v>
+        <v>0.7812</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>45708.68166530092</v>
+        <v>45727.87202070602</v>
       </c>
       <c r="G100" t="n">
-        <v>17.18</v>
+        <v>19.2</v>
       </c>
       <c r="H100" t="n">
-        <v>21.24</v>
+        <v>20.3</v>
       </c>
       <c r="I100" t="n">
-        <v>17.18</v>
+        <v>15</v>
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
@@ -5366,18 +5366,18 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>4.06</v>
+        <v>0.86</v>
       </c>
       <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="n">
-        <v>1824477589</v>
+        <v>1830410729</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5386,19 +5386,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.2344</v>
+        <v>0.1091</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>45792.64732982639</v>
+        <v>45796.82476561343</v>
       </c>
       <c r="G101" t="n">
-        <v>42.66</v>
+        <v>33.66</v>
       </c>
       <c r="H101" t="n">
-        <v>43.82</v>
+        <v>38.41</v>
       </c>
       <c r="I101" t="n">
-        <v>10</v>
+        <v>3.67</v>
       </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -5415,18 +5415,18 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>0.27</v>
+        <v>0.52</v>
       </c>
       <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="n">
-        <v>1648740228</v>
+        <v>1867458993</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5435,19 +5435,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.0538</v>
+        <v>0.3417</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>45695.85792408565</v>
+        <v>45818.90699613426</v>
       </c>
       <c r="G102" t="n">
-        <v>185.82</v>
+        <v>58.53</v>
       </c>
       <c r="H102" t="n">
-        <v>171.72</v>
+        <v>59.49</v>
       </c>
       <c r="I102" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
@@ -5464,18 +5464,18 @@
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>-0.76</v>
+        <v>0.33</v>
       </c>
       <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="n">
-        <v>1712849726</v>
+        <v>1811475646</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5484,19 +5484,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.0861</v>
+        <v>1</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>45734.85489405093</v>
+        <v>45785.66973634259</v>
       </c>
       <c r="G103" t="n">
-        <v>127.72</v>
+        <v>12.75</v>
       </c>
       <c r="H103" t="n">
-        <v>157.86</v>
+        <v>13.07</v>
       </c>
       <c r="I103" t="n">
-        <v>11</v>
+        <v>14.49</v>
       </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
@@ -5513,18 +5513,18 @@
         <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>2.59</v>
+        <v>0.49</v>
       </c>
       <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="n">
-        <v>1806980496</v>
+        <v>1882283184</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5533,19 +5533,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1</v>
+        <v>0.4835</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>45783.83190503472</v>
+        <v>45826.76569390047</v>
       </c>
       <c r="G104" t="n">
-        <v>16.12</v>
+        <v>20.69</v>
       </c>
       <c r="H104" t="n">
-        <v>17.82</v>
+        <v>20.3</v>
       </c>
       <c r="I104" t="n">
-        <v>16.12</v>
+        <v>10</v>
       </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
@@ -5562,18 +5562,18 @@
         <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>1.7</v>
+        <v>-0.18</v>
       </c>
       <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="n">
-        <v>1422773288</v>
+        <v>1867196288</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5582,19 +5582,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.483</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>45518.84428523148</v>
+        <v>45818.80209099537</v>
       </c>
       <c r="G105" t="n">
-        <v>51.24</v>
+        <v>41.99</v>
       </c>
       <c r="H105" t="n">
-        <v>60.5</v>
+        <v>43.22</v>
       </c>
       <c r="I105" t="n">
-        <v>24.75</v>
+        <v>25</v>
       </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
@@ -5611,14 +5611,14 @@
         <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>4.47</v>
+        <v>0.73</v>
       </c>
       <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="n">
-        <v>1729617775</v>
+        <v>1744879358</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -5631,19 +5631,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.0907</v>
+        <v>0.2701</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>45744.71339734954</v>
+        <v>45751.73925940973</v>
       </c>
       <c r="G106" t="n">
-        <v>165.35</v>
+        <v>148.09</v>
       </c>
       <c r="H106" t="n">
-        <v>193.28</v>
+        <v>213.27</v>
       </c>
       <c r="I106" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
@@ -5660,18 +5660,18 @@
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>2.53</v>
+        <v>17.6</v>
       </c>
       <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="n">
-        <v>1631475148</v>
+        <v>1582735114</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5680,19 +5680,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.2592</v>
+        <v>0.0003</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>45685.83625201389</v>
+        <v>45645.90076803241</v>
       </c>
       <c r="G107" t="n">
-        <v>38.58</v>
+        <v>130.51</v>
       </c>
       <c r="H107" t="n">
-        <v>35.39</v>
+        <v>138.29</v>
       </c>
       <c r="I107" t="n">
-        <v>10</v>
+        <v>0.04</v>
       </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
@@ -5709,18 +5709,18 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>-0.83</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="n">
-        <v>1754304266</v>
+        <v>1422773288</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5729,19 +5729,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.7137</v>
+        <v>0.483</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>45755.88055112268</v>
+        <v>45518.84428523148</v>
       </c>
       <c r="G108" t="n">
-        <v>14</v>
+        <v>51.24</v>
       </c>
       <c r="H108" t="n">
-        <v>17</v>
+        <v>59.49</v>
       </c>
       <c r="I108" t="n">
-        <v>9.99</v>
+        <v>24.75</v>
       </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
@@ -5758,18 +5758,18 @@
         <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>2.14</v>
+        <v>3.98</v>
       </c>
       <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="n">
-        <v>1845429956</v>
+        <v>1450043624</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5778,19 +5778,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.6565</v>
+        <v>0.0231</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>45805.66180811343</v>
+        <v>45544.65163525463</v>
       </c>
       <c r="G109" t="n">
-        <v>13.275</v>
+        <v>147.48</v>
       </c>
       <c r="H109" t="n">
-        <v>13.225</v>
+        <v>127.93</v>
       </c>
       <c r="I109" t="n">
-        <v>9.91</v>
+        <v>3.41</v>
       </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
@@ -5807,27 +5807,45 @@
         <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>-0.1</v>
+        <v>-0.45</v>
       </c>
       <c r="Q109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+      <c r="B110" t="n">
+        <v>1869077178</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>BBVA.MC</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>45819.67426902778</v>
+      </c>
+      <c r="G110" t="n">
+        <v>13.285</v>
+      </c>
+      <c r="H110" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="I110" t="n">
+        <v>15.31</v>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
       <c r="M110" t="n">
         <v>0</v>
       </c>
@@ -5838,9 +5856,673 @@
         <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>55.77</v>
+        <v>-0.33</v>
       </c>
       <c r="Q110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="n">
+        <v>1644796307</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ACI</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>45693.85501710648</v>
+      </c>
+      <c r="G111" t="n">
+        <v>20.36</v>
+      </c>
+      <c r="H111" t="n">
+        <v>21.07</v>
+      </c>
+      <c r="I111" t="n">
+        <v>20.36</v>
+      </c>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="Q111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="n">
+        <v>1729617775</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>0.0907</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>45744.71339734954</v>
+      </c>
+      <c r="G112" t="n">
+        <v>165.35</v>
+      </c>
+      <c r="H112" t="n">
+        <v>213.27</v>
+      </c>
+      <c r="I112" t="n">
+        <v>15</v>
+      </c>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="Q112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="n">
+        <v>1559803984</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>KMB</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0.1076</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>45628.86014383102</v>
+      </c>
+      <c r="G113" t="n">
+        <v>139.4</v>
+      </c>
+      <c r="H113" t="n">
+        <v>127.93</v>
+      </c>
+      <c r="I113" t="n">
+        <v>15</v>
+      </c>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="Q113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="n">
+        <v>1825032062</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>AGIO</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>45792.76080334491</v>
+      </c>
+      <c r="G114" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="H114" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="I114" t="n">
+        <v>10</v>
+      </c>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="n">
+        <v>1843469729</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>FSLR</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>45804.66615450232</v>
+      </c>
+      <c r="G115" t="n">
+        <v>156.9</v>
+      </c>
+      <c r="H115" t="n">
+        <v>142.34</v>
+      </c>
+      <c r="I115" t="n">
+        <v>15</v>
+      </c>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="Q115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="n">
+        <v>1806980496</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>BCS</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>45783.83190503472</v>
+      </c>
+      <c r="G116" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="H116" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="I116" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="n">
+        <v>1495551484</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>INGR</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>0.1914</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>45580.70648087963</v>
+      </c>
+      <c r="G117" t="n">
+        <v>135.82</v>
+      </c>
+      <c r="H117" t="n">
+        <v>136.42</v>
+      </c>
+      <c r="I117" t="n">
+        <v>26</v>
+      </c>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="n">
+        <v>1566610015</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9385</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>45632.87667083334</v>
+      </c>
+      <c r="G118" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="H118" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="I118" t="n">
+        <v>20</v>
+      </c>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="Q118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="n">
+        <v>1727574394</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ACI</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>45743.76658678241</v>
+      </c>
+      <c r="G119" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="H119" t="n">
+        <v>21.07</v>
+      </c>
+      <c r="I119" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="Q119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="n">
+        <v>1666459270</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>ING</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>45708.68166530092</v>
+      </c>
+      <c r="G120" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="H120" t="n">
+        <v>20.77</v>
+      </c>
+      <c r="I120" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="Q120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="n">
+        <v>1867195793</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>EXC</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>0.2339</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>45818.80180457176</v>
+      </c>
+      <c r="G121" t="n">
+        <v>42.74</v>
+      </c>
+      <c r="H121" t="n">
+        <v>42.37</v>
+      </c>
+      <c r="I121" t="n">
+        <v>10</v>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="Q121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="n">
+        <v>1883977086</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>BBVA.MC</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>45827.66106613426</v>
+      </c>
+      <c r="G122" t="n">
+        <v>12.875</v>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="n">
+        <v>1883977044</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>BBVA.MC</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>45827.66105774305</v>
+      </c>
+      <c r="G123" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>71.67</v>
+      </c>
+      <c r="Q124" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Stock Selection/OPEN POSITION.xlsx
+++ b/Stock Selection/OPEN POSITION.xlsx
@@ -544,7 +544,7 @@
         <v>43</v>
       </c>
       <c r="H2" t="n">
-        <v>42.37</v>
+        <v>43.09</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -593,7 +593,7 @@
         <v>129.08</v>
       </c>
       <c r="H3" t="n">
-        <v>127.93</v>
+        <v>129.91</v>
       </c>
       <c r="I3" t="n">
         <v>10.49</v>
@@ -613,7 +613,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
@@ -642,7 +642,7 @@
         <v>21.905</v>
       </c>
       <c r="H4" t="n">
-        <v>20.405</v>
+        <v>20.58</v>
       </c>
       <c r="I4" t="n">
         <v>10.95</v>
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.75</v>
+        <v>-0.66</v>
       </c>
       <c r="Q4" t="inlineStr"/>
     </row>
@@ -691,7 +691,7 @@
         <v>517.7</v>
       </c>
       <c r="H5" t="n">
-        <v>538.84</v>
+        <v>556.39</v>
       </c>
       <c r="I5" t="n">
         <v>14.96</v>
@@ -711,7 +711,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.61</v>
+        <v>1.12</v>
       </c>
       <c r="Q5" t="inlineStr"/>
     </row>
@@ -740,7 +740,7 @@
         <v>129.25</v>
       </c>
       <c r="H6" t="n">
-        <v>127.93</v>
+        <v>129.91</v>
       </c>
       <c r="I6" t="n">
         <v>10</v>
@@ -760,7 +760,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1</v>
+        <v>0.06</v>
       </c>
       <c r="Q6" t="inlineStr"/>
     </row>
@@ -789,7 +789,7 @@
         <v>160.64</v>
       </c>
       <c r="H7" t="n">
-        <v>173.31</v>
+        <v>166.76</v>
       </c>
       <c r="I7" t="n">
         <v>4.53</v>
@@ -809,7 +809,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.36</v>
+        <v>0.17</v>
       </c>
       <c r="Q7" t="inlineStr"/>
     </row>
@@ -838,7 +838,7 @@
         <v>59.15</v>
       </c>
       <c r="H8" t="n">
-        <v>59.49</v>
+        <v>59.93</v>
       </c>
       <c r="I8" t="n">
         <v>14.99</v>
@@ -858,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="Q8" t="inlineStr"/>
     </row>
@@ -887,7 +887,7 @@
         <v>127.16</v>
       </c>
       <c r="H9" t="n">
-        <v>136.42</v>
+        <v>137.47</v>
       </c>
       <c r="I9" t="n">
         <v>19.99</v>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="Q9" t="inlineStr"/>
     </row>
@@ -936,7 +936,7 @@
         <v>20.6</v>
       </c>
       <c r="H10" t="n">
-        <v>20.3</v>
+        <v>18.17</v>
       </c>
       <c r="I10" t="n">
         <v>14.99</v>
@@ -956,18 +956,18 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.22</v>
+        <v>-1.77</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
-        <v>1583696868</v>
+        <v>1888686062</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BOTZ.L</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -976,19 +976,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.5</v>
+        <v>0.2903</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45646.60053979167</v>
+        <v>45831.64964792824</v>
       </c>
       <c r="G11" t="n">
-        <v>20.645</v>
+        <v>34.36</v>
       </c>
       <c r="H11" t="n">
-        <v>20.405</v>
+        <v>34.37</v>
       </c>
       <c r="I11" t="n">
-        <v>10.32</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -1005,18 +1005,18 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.12</v>
+        <v>0.01</v>
       </c>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>1824477589</v>
+        <v>1583696868</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>BOTZ.L</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1025,19 +1025,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.2344</v>
+        <v>0.5</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>45792.64732982639</v>
+        <v>45646.60053979167</v>
       </c>
       <c r="G12" t="n">
-        <v>42.66</v>
+        <v>20.645</v>
       </c>
       <c r="H12" t="n">
-        <v>42.37</v>
+        <v>20.58</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>10.32</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -1054,18 +1054,18 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>1867193336</v>
+        <v>1824477589</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1074,19 +1074,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0.2344</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>45818.80084483796</v>
+        <v>45792.64732982639</v>
       </c>
       <c r="G13" t="n">
-        <v>17.64</v>
+        <v>42.66</v>
       </c>
       <c r="H13" t="n">
-        <v>17.65</v>
+        <v>43.09</v>
       </c>
       <c r="I13" t="n">
-        <v>17.64</v>
+        <v>10</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -1103,14 +1103,14 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="n">
-        <v>1796453499</v>
+        <v>1867193336</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.6422</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>45777.64668229167</v>
+        <v>45818.80084483796</v>
       </c>
       <c r="G14" t="n">
-        <v>15.57</v>
+        <v>17.64</v>
       </c>
       <c r="H14" t="n">
-        <v>17.65</v>
+        <v>18.25</v>
       </c>
       <c r="I14" t="n">
-        <v>10</v>
+        <v>17.64</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -1152,18 +1152,18 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.33</v>
+        <v>0.61</v>
       </c>
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="n">
-        <v>1481609355</v>
+        <v>1796453499</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.107</v>
+        <v>0.6422</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>45568.7734872338</v>
+        <v>45777.64668229167</v>
       </c>
       <c r="G15" t="n">
-        <v>140.18</v>
+        <v>15.57</v>
       </c>
       <c r="H15" t="n">
-        <v>127.93</v>
+        <v>18.25</v>
       </c>
       <c r="I15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1201,18 +1201,18 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.31</v>
+        <v>1.72</v>
       </c>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="n">
-        <v>1744767540</v>
+        <v>1481609355</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.643</v>
+        <v>0.107</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>45751.72316712963</v>
+        <v>45568.7734872338</v>
       </c>
       <c r="G16" t="n">
-        <v>15.55</v>
+        <v>140.18</v>
       </c>
       <c r="H16" t="n">
-        <v>20.3</v>
+        <v>129.91</v>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1250,18 +1250,18 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.05</v>
+        <v>-1.1</v>
       </c>
       <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="n">
-        <v>1633116336</v>
+        <v>1885700231</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1270,19 +1270,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0.0187</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>45686.83272234954</v>
+        <v>45828.65147924769</v>
       </c>
       <c r="G17" t="n">
-        <v>44.24</v>
+        <v>534.86</v>
       </c>
       <c r="H17" t="n">
-        <v>48.15</v>
+        <v>556.39</v>
       </c>
       <c r="I17" t="n">
-        <v>44.24</v>
+        <v>10</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1299,18 +1299,18 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.91</v>
+        <v>0.4</v>
       </c>
       <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
-        <v>1824475555</v>
+        <v>1744767540</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0.643</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45792.64702015046</v>
+        <v>45751.72316712963</v>
       </c>
       <c r="G18" t="n">
-        <v>21.66</v>
+        <v>15.55</v>
       </c>
       <c r="H18" t="n">
-        <v>21.07</v>
+        <v>18.17</v>
       </c>
       <c r="I18" t="n">
-        <v>21.66</v>
+        <v>10</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1348,18 +1348,18 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.59</v>
+        <v>1.68</v>
       </c>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="n">
-        <v>1744929368</v>
+        <v>1633116336</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1368,19 +1368,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.0192</v>
+        <v>1</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45751.74500871528</v>
+        <v>45686.83272234954</v>
       </c>
       <c r="G19" t="n">
-        <v>324.48</v>
+        <v>44.24</v>
       </c>
       <c r="H19" t="n">
-        <v>340.31</v>
+        <v>49.01</v>
       </c>
       <c r="I19" t="n">
-        <v>6.23</v>
+        <v>44.24</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1397,18 +1397,18 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3</v>
+        <v>4.77</v>
       </c>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
-        <v>1806980482</v>
+        <v>1824475555</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1417,19 +1417,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.2406</v>
+        <v>1</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45783.83189613426</v>
+        <v>45792.64702015046</v>
       </c>
       <c r="G20" t="n">
-        <v>16.12</v>
+        <v>21.66</v>
       </c>
       <c r="H20" t="n">
-        <v>17.65</v>
+        <v>21.68</v>
       </c>
       <c r="I20" t="n">
-        <v>3.88</v>
+        <v>21.66</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1446,18 +1446,18 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.37</v>
+        <v>0.02</v>
       </c>
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="n">
-        <v>1867193304</v>
+        <v>1744929368</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1466,19 +1466,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.1337</v>
+        <v>0.0192</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45818.8008296412</v>
+        <v>45751.74500871528</v>
       </c>
       <c r="G21" t="n">
-        <v>17.64</v>
+        <v>324.48</v>
       </c>
       <c r="H21" t="n">
-        <v>17.65</v>
+        <v>351.65</v>
       </c>
       <c r="I21" t="n">
-        <v>2.36</v>
+        <v>6.23</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1495,18 +1495,18 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="n">
-        <v>1635194724</v>
+        <v>1806980482</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1515,19 +1515,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.2875</v>
+        <v>0.2406</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>45687.85271734954</v>
+        <v>45783.83189613426</v>
       </c>
       <c r="G22" t="n">
-        <v>34.78</v>
+        <v>16.12</v>
       </c>
       <c r="H22" t="n">
-        <v>35.28</v>
+        <v>18.25</v>
       </c>
       <c r="I22" t="n">
-        <v>10</v>
+        <v>3.88</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -1544,18 +1544,18 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.14</v>
+        <v>0.51</v>
       </c>
       <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="n">
-        <v>1554741956</v>
+        <v>1867193304</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0.1337</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>45623.74952237269</v>
+        <v>45818.8008296412</v>
       </c>
       <c r="G23" t="n">
-        <v>15.3</v>
+        <v>17.64</v>
       </c>
       <c r="H23" t="n">
-        <v>20.77</v>
+        <v>18.25</v>
       </c>
       <c r="I23" t="n">
-        <v>15.3</v>
+        <v>2.36</v>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -1593,18 +1593,18 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>5.47</v>
+        <v>0.08</v>
       </c>
       <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="n">
-        <v>1606697510</v>
+        <v>1554741956</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.0295</v>
+        <v>1</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45667.68664726852</v>
+        <v>45623.74952237269</v>
       </c>
       <c r="G24" t="n">
-        <v>507.68</v>
+        <v>15.3</v>
       </c>
       <c r="H24" t="n">
-        <v>538.84</v>
+        <v>21.35</v>
       </c>
       <c r="I24" t="n">
-        <v>14.98</v>
+        <v>15.3</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1642,18 +1642,18 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0.92</v>
+        <v>6.05</v>
       </c>
       <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="n">
-        <v>1843470413</v>
+        <v>1606697510</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1662,19 +1662,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.4729</v>
+        <v>0.0295</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>45804.66637251157</v>
+        <v>45667.68664726852</v>
       </c>
       <c r="G25" t="n">
-        <v>42.29</v>
+        <v>507.68</v>
       </c>
       <c r="H25" t="n">
-        <v>43.22</v>
+        <v>556.39</v>
       </c>
       <c r="I25" t="n">
-        <v>20</v>
+        <v>14.98</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -1691,18 +1691,18 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="n">
-        <v>1882278057</v>
+        <v>1883977044</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1711,19 +1711,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.0432</v>
+        <v>0.345</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>45826.76262912037</v>
+        <v>45827.66105774305</v>
       </c>
       <c r="G26" t="n">
-        <v>346.61</v>
+        <v>12.88</v>
       </c>
       <c r="H26" t="n">
-        <v>340.31</v>
+        <v>13.095</v>
       </c>
       <c r="I26" t="n">
-        <v>14.97</v>
+        <v>5.13</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -1740,18 +1740,18 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.27</v>
+        <v>0.09</v>
       </c>
       <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="n">
-        <v>1817256440</v>
+        <v>1843470413</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1760,19 +1760,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.2267</v>
+        <v>0.4729</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>45789.64787115741</v>
+        <v>45804.66637251157</v>
       </c>
       <c r="G27" t="n">
-        <v>44.1</v>
+        <v>42.29</v>
       </c>
       <c r="H27" t="n">
-        <v>42.37</v>
+        <v>44.92</v>
       </c>
       <c r="I27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -1789,18 +1789,18 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.39</v>
+        <v>1.24</v>
       </c>
       <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="n">
-        <v>1582723120</v>
+        <v>1882278057</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1809,19 +1809,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.3755</v>
+        <v>0.0432</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>45645.89511640046</v>
+        <v>45826.76262912037</v>
       </c>
       <c r="G28" t="n">
-        <v>53.26</v>
+        <v>346.61</v>
       </c>
       <c r="H28" t="n">
-        <v>59.49</v>
+        <v>351.65</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>14.97</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -1838,18 +1838,18 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.34</v>
+        <v>0.22</v>
       </c>
       <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
-        <v>1830408508</v>
+        <v>1817256440</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1858,16 +1858,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.5793</v>
+        <v>0.2267</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>45796.82346997685</v>
+        <v>45789.64787115741</v>
       </c>
       <c r="G29" t="n">
-        <v>17.26</v>
+        <v>44.1</v>
       </c>
       <c r="H29" t="n">
-        <v>20.3</v>
+        <v>43.09</v>
       </c>
       <c r="I29" t="n">
         <v>10</v>
@@ -1887,18 +1887,18 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.76</v>
+        <v>-0.23</v>
       </c>
       <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
-        <v>1712849726</v>
+        <v>1582723120</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1907,19 +1907,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.0861</v>
+        <v>0.3755</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45734.85489405093</v>
+        <v>45645.89511640046</v>
       </c>
       <c r="G30" t="n">
-        <v>127.72</v>
+        <v>53.26</v>
       </c>
       <c r="H30" t="n">
-        <v>142.34</v>
+        <v>59.93</v>
       </c>
       <c r="I30" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -1936,18 +1936,18 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.26</v>
+        <v>2.5</v>
       </c>
       <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="n">
-        <v>1680991980</v>
+        <v>1830408508</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1956,19 +1956,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.1066</v>
+        <v>0.5793</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45716.8556621875</v>
+        <v>45796.82346997685</v>
       </c>
       <c r="G31" t="n">
-        <v>178.67</v>
+        <v>17.26</v>
       </c>
       <c r="H31" t="n">
-        <v>213.27</v>
+        <v>18.17</v>
       </c>
       <c r="I31" t="n">
-        <v>19.05</v>
+        <v>10</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1985,14 +1985,14 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>3.69</v>
+        <v>0.53</v>
       </c>
       <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="n">
-        <v>1811432805</v>
+        <v>1712849726</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -2005,16 +2005,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.0856</v>
+        <v>0.0861</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45785.66143211805</v>
+        <v>45734.85489405093</v>
       </c>
       <c r="G32" t="n">
-        <v>128.46</v>
+        <v>127.72</v>
       </c>
       <c r="H32" t="n">
-        <v>142.34</v>
+        <v>150.56</v>
       </c>
       <c r="I32" t="n">
         <v>11</v>
@@ -2034,18 +2034,18 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.18</v>
+        <v>1.96</v>
       </c>
       <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="n">
-        <v>1582737192</v>
+        <v>1680991980</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2054,19 +2054,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.001</v>
+        <v>0.1066</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45645.90143930555</v>
+        <v>45716.8556621875</v>
       </c>
       <c r="G33" t="n">
-        <v>524.4299999999999</v>
+        <v>178.67</v>
       </c>
       <c r="H33" t="n">
-        <v>538.84</v>
+        <v>220.02</v>
       </c>
       <c r="I33" t="n">
-        <v>0.52</v>
+        <v>19.05</v>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -2083,18 +2083,18 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.02</v>
+        <v>4.41</v>
       </c>
       <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="n">
-        <v>1843474191</v>
+        <v>1811432805</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2103,19 +2103,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9372</v>
+        <v>0.0856</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45804.66699503472</v>
+        <v>45785.66143211805</v>
       </c>
       <c r="G34" t="n">
-        <v>21.33</v>
+        <v>128.46</v>
       </c>
       <c r="H34" t="n">
-        <v>20.77</v>
+        <v>150.56</v>
       </c>
       <c r="I34" t="n">
-        <v>19.99</v>
+        <v>11</v>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
@@ -2132,18 +2132,18 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>-0.52</v>
+        <v>1.89</v>
       </c>
       <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>1744916497</v>
+        <v>1582737192</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2152,19 +2152,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>45751.74231563658</v>
+        <v>45645.90143930555</v>
       </c>
       <c r="G35" t="n">
-        <v>17.54</v>
+        <v>524.4299999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>20.77</v>
+        <v>556.39</v>
       </c>
       <c r="I35" t="n">
-        <v>17.54</v>
+        <v>0.52</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
@@ -2181,18 +2181,18 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>3.23</v>
+        <v>0.04</v>
       </c>
       <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>1635194117</v>
+        <v>1843474191</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2201,19 +2201,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.2479</v>
+        <v>0.9372</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45687.85228493056</v>
+        <v>45804.66699503472</v>
       </c>
       <c r="G36" t="n">
-        <v>40.33</v>
+        <v>21.33</v>
       </c>
       <c r="H36" t="n">
-        <v>35.26</v>
+        <v>21.35</v>
       </c>
       <c r="I36" t="n">
-        <v>10</v>
+        <v>19.99</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -2230,18 +2230,18 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>-1.26</v>
+        <v>0.02</v>
       </c>
       <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
-        <v>1381417257</v>
+        <v>1744916497</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2253,16 +2253,16 @@
         <v>1</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>45484.67877329861</v>
+        <v>45751.74231563658</v>
       </c>
       <c r="G37" t="n">
-        <v>16.374</v>
+        <v>17.54</v>
       </c>
       <c r="H37" t="n">
-        <v>15.2</v>
+        <v>21.35</v>
       </c>
       <c r="I37" t="n">
-        <v>17.9</v>
+        <v>17.54</v>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
@@ -2279,18 +2279,18 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>-0.48</v>
+        <v>3.81</v>
       </c>
       <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>1882281884</v>
+        <v>1635194117</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2299,16 +2299,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.2479</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45826.76479001158</v>
+        <v>45687.85228493056</v>
       </c>
       <c r="G38" t="n">
-        <v>138.84</v>
+        <v>40.33</v>
       </c>
       <c r="H38" t="n">
-        <v>138.29</v>
+        <v>34.37</v>
       </c>
       <c r="I38" t="n">
         <v>10</v>
@@ -2328,18 +2328,18 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>-0.04</v>
+        <v>-1.48</v>
       </c>
       <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
-        <v>1880441651</v>
+        <v>1381417257</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2351,16 +2351,16 @@
         <v>1</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45825.89055887731</v>
+        <v>45484.67877329861</v>
       </c>
       <c r="G39" t="n">
-        <v>21.21</v>
+        <v>16.374</v>
       </c>
       <c r="H39" t="n">
-        <v>21.07</v>
+        <v>15.194</v>
       </c>
       <c r="I39" t="n">
-        <v>21.21</v>
+        <v>17.9</v>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -2377,18 +2377,18 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>-0.14</v>
+        <v>-0.34</v>
       </c>
       <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="n">
-        <v>1461331124</v>
+        <v>1882281884</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2397,19 +2397,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.3922</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>45553.65374138889</v>
+        <v>45826.76479001158</v>
       </c>
       <c r="G40" t="n">
-        <v>50.99</v>
+        <v>138.84</v>
       </c>
       <c r="H40" t="n">
-        <v>59.49</v>
+        <v>142.64</v>
       </c>
       <c r="I40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
@@ -2426,18 +2426,18 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>3.33</v>
+        <v>0.27</v>
       </c>
       <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="n">
-        <v>1867195417</v>
+        <v>1880441651</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2446,19 +2446,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.1044</v>
+        <v>1</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45818.80165224537</v>
+        <v>45825.89055887731</v>
       </c>
       <c r="G41" t="n">
-        <v>143.6</v>
+        <v>21.21</v>
       </c>
       <c r="H41" t="n">
-        <v>138.29</v>
+        <v>21.68</v>
       </c>
       <c r="I41" t="n">
-        <v>14.99</v>
+        <v>21.21</v>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
@@ -2475,18 +2475,18 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>-0.55</v>
+        <v>0.47</v>
       </c>
       <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="n">
-        <v>1644788775</v>
+        <v>1461331124</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2495,19 +2495,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.3922</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>45693.85093391204</v>
+        <v>45553.65374138889</v>
       </c>
       <c r="G42" t="n">
-        <v>144.94</v>
+        <v>50.99</v>
       </c>
       <c r="H42" t="n">
-        <v>128.99</v>
+        <v>59.93</v>
       </c>
       <c r="I42" t="n">
-        <v>10.99</v>
+        <v>20</v>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -2524,18 +2524,18 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>-1.21</v>
+        <v>3.5</v>
       </c>
       <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="n">
-        <v>1754304266</v>
+        <v>1867195417</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2544,19 +2544,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.7137</v>
+        <v>0.1044</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>45755.88055112268</v>
+        <v>45818.80165224537</v>
       </c>
       <c r="G43" t="n">
-        <v>14</v>
+        <v>143.6</v>
       </c>
       <c r="H43" t="n">
-        <v>20.3</v>
+        <v>142.64</v>
       </c>
       <c r="I43" t="n">
-        <v>9.99</v>
+        <v>14.99</v>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -2573,18 +2573,18 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>4.5</v>
+        <v>-0.1</v>
       </c>
       <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
-        <v>1559802942</v>
+        <v>1644788775</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2593,19 +2593,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.2585</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45628.85929152778</v>
+        <v>45693.85093391204</v>
       </c>
       <c r="G44" t="n">
-        <v>77.34999999999999</v>
+        <v>144.94</v>
       </c>
       <c r="H44" t="n">
-        <v>71.56999999999999</v>
+        <v>131.06</v>
       </c>
       <c r="I44" t="n">
-        <v>19.99</v>
+        <v>10.99</v>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -2622,18 +2622,18 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>-1.49</v>
+        <v>-1.06</v>
       </c>
       <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>1880446729</v>
+        <v>1754304266</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2642,19 +2642,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.0772</v>
+        <v>0.7137</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>45825.89315055555</v>
+        <v>45755.88055112268</v>
       </c>
       <c r="G45" t="n">
-        <v>129.62</v>
+        <v>14</v>
       </c>
       <c r="H45" t="n">
-        <v>128.99</v>
+        <v>18.17</v>
       </c>
       <c r="I45" t="n">
-        <v>10.01</v>
+        <v>9.99</v>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -2671,18 +2671,18 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>-0.05</v>
+        <v>2.98</v>
       </c>
       <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>1621495187</v>
+        <v>1559802942</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2691,19 +2691,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.2318</v>
+        <v>0.2585</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>45678.83178196759</v>
+        <v>45628.85929152778</v>
       </c>
       <c r="G46" t="n">
-        <v>43.27</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>35.26</v>
+        <v>71.42</v>
       </c>
       <c r="I46" t="n">
-        <v>10.03</v>
+        <v>19.99</v>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -2720,18 +2720,18 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>-1.86</v>
+        <v>-1.53</v>
       </c>
       <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>1867194722</v>
+        <v>1880446729</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2740,19 +2740,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>0.0772</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>45818.80135700232</v>
+        <v>45825.89315055555</v>
       </c>
       <c r="G47" t="n">
-        <v>21.27</v>
+        <v>129.62</v>
       </c>
       <c r="H47" t="n">
-        <v>21.07</v>
+        <v>131.06</v>
       </c>
       <c r="I47" t="n">
-        <v>21.27</v>
+        <v>10.01</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -2769,18 +2769,18 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>-0.2</v>
+        <v>0.11</v>
       </c>
       <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>1806979127</v>
+        <v>1621495187</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2789,19 +2789,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.6361</v>
+        <v>0.2318</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>45783.83125244213</v>
+        <v>45678.83178196759</v>
       </c>
       <c r="G48" t="n">
-        <v>15.72</v>
+        <v>43.27</v>
       </c>
       <c r="H48" t="n">
-        <v>20.3</v>
+        <v>34.37</v>
       </c>
       <c r="I48" t="n">
-        <v>10</v>
+        <v>10.03</v>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -2818,18 +2818,18 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.91</v>
+        <v>-2.06</v>
       </c>
       <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
-        <v>1776193271</v>
+        <v>1867194722</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2838,19 +2838,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.6724</v>
+        <v>1</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45764.85451520833</v>
+        <v>45818.80135700232</v>
       </c>
       <c r="G49" t="n">
-        <v>14.87</v>
+        <v>21.27</v>
       </c>
       <c r="H49" t="n">
-        <v>17.65</v>
+        <v>21.68</v>
       </c>
       <c r="I49" t="n">
-        <v>10</v>
+        <v>21.27</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
@@ -2867,18 +2867,18 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>1.87</v>
+        <v>0.41</v>
       </c>
       <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
-        <v>1594315903</v>
+        <v>1806979127</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0.6361</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>45659.42644752315</v>
+        <v>45783.83125244213</v>
       </c>
       <c r="G50" t="n">
-        <v>16.425</v>
+        <v>15.72</v>
       </c>
       <c r="H50" t="n">
-        <v>15.2</v>
+        <v>18.17</v>
       </c>
       <c r="I50" t="n">
-        <v>17.11</v>
+        <v>10</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -2916,18 +2916,18 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0.31</v>
+        <v>1.56</v>
       </c>
       <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>1680993370</v>
+        <v>1776193271</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2936,19 +2936,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0.6724</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>45716.85638861111</v>
+        <v>45764.85451520833</v>
       </c>
       <c r="G51" t="n">
-        <v>44.49</v>
+        <v>14.87</v>
       </c>
       <c r="H51" t="n">
-        <v>48.15</v>
+        <v>18.25</v>
       </c>
       <c r="I51" t="n">
-        <v>44.49</v>
+        <v>10</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -2965,18 +2965,18 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>3.66</v>
+        <v>2.27</v>
       </c>
       <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
-        <v>1701100481</v>
+        <v>1594315903</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>BATT.AS</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2985,19 +2985,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.0873</v>
+        <v>1</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>45727.87214378472</v>
+        <v>45659.42644752315</v>
       </c>
       <c r="G52" t="n">
-        <v>171.67</v>
+        <v>16.425</v>
       </c>
       <c r="H52" t="n">
-        <v>213.27</v>
+        <v>15.194</v>
       </c>
       <c r="I52" t="n">
-        <v>14.99</v>
+        <v>17.11</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
@@ -3014,18 +3014,18 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>3.63</v>
+        <v>0.45</v>
       </c>
       <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="n">
-        <v>1867197360</v>
+        <v>1680993370</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3034,19 +3034,19 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.0765</v>
+        <v>1</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>45818.80265583334</v>
+        <v>45716.85638861111</v>
       </c>
       <c r="G53" t="n">
-        <v>131.96</v>
+        <v>44.49</v>
       </c>
       <c r="H53" t="n">
-        <v>128.99</v>
+        <v>49.01</v>
       </c>
       <c r="I53" t="n">
-        <v>10.09</v>
+        <v>44.49</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
@@ -3063,18 +3063,18 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>-0.22</v>
+        <v>4.52</v>
       </c>
       <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="n">
-        <v>1806977521</v>
+        <v>1701100481</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3083,19 +3083,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.3367</v>
+        <v>0.0873</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>45783.8305750463</v>
+        <v>45727.87214378472</v>
       </c>
       <c r="G54" t="n">
-        <v>29.7</v>
+        <v>171.67</v>
       </c>
       <c r="H54" t="n">
-        <v>35.26</v>
+        <v>220.02</v>
       </c>
       <c r="I54" t="n">
-        <v>10</v>
+        <v>14.99</v>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
@@ -3112,18 +3112,18 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>1.87</v>
+        <v>4.22</v>
       </c>
       <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="n">
-        <v>1867462173</v>
+        <v>1867197360</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3132,19 +3132,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.1284</v>
+        <v>0.0765</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>45818.90866184028</v>
+        <v>45818.80265583334</v>
       </c>
       <c r="G55" t="n">
-        <v>77.93000000000001</v>
+        <v>131.96</v>
       </c>
       <c r="H55" t="n">
-        <v>78.31</v>
+        <v>131.06</v>
       </c>
       <c r="I55" t="n">
-        <v>10.01</v>
+        <v>10.09</v>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
@@ -3161,18 +3161,18 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="n">
-        <v>1744930699</v>
+        <v>1806977521</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3181,19 +3181,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>0.3367</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>45751.74534789352</v>
+        <v>45783.8305750463</v>
       </c>
       <c r="G56" t="n">
-        <v>74.13</v>
+        <v>29.7</v>
       </c>
       <c r="H56" t="n">
-        <v>72.83</v>
+        <v>34.37</v>
       </c>
       <c r="I56" t="n">
-        <v>74.13</v>
+        <v>10</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
@@ -3210,18 +3210,18 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>-1.3</v>
+        <v>1.57</v>
       </c>
       <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="n">
-        <v>1648733962</v>
+        <v>1867462173</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3230,19 +3230,19 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.081</v>
+        <v>0.1284</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45695.85463682871</v>
+        <v>45818.90866184028</v>
       </c>
       <c r="G57" t="n">
-        <v>129.56</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>127.93</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>10.49</v>
+        <v>10.01</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
@@ -3259,18 +3259,18 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>-0.13</v>
+        <v>0.41</v>
       </c>
       <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
-        <v>1378901781</v>
+        <v>1744930699</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BOTZ.L</t>
+          <t>BND</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3282,16 +3282,16 @@
         <v>1</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45482.71294556713</v>
+        <v>45751.74534789352</v>
       </c>
       <c r="G58" t="n">
-        <v>20.58</v>
+        <v>74.13</v>
       </c>
       <c r="H58" t="n">
-        <v>20.405</v>
+        <v>73.28</v>
       </c>
       <c r="I58" t="n">
-        <v>20.58</v>
+        <v>74.13</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
@@ -3308,18 +3308,18 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>-0.17</v>
+        <v>-0.85</v>
       </c>
       <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="n">
-        <v>1599449649</v>
+        <v>1648733962</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3328,19 +3328,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.4145</v>
+        <v>0.081</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>45663.73562525463</v>
+        <v>45695.85463682871</v>
       </c>
       <c r="G59" t="n">
-        <v>24.11</v>
+        <v>129.56</v>
       </c>
       <c r="H59" t="n">
-        <v>20.3</v>
+        <v>129.91</v>
       </c>
       <c r="I59" t="n">
-        <v>9.99</v>
+        <v>10.49</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
@@ -3357,18 +3357,18 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>-1.58</v>
+        <v>0.03</v>
       </c>
       <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="n">
-        <v>1845429956</v>
+        <v>1378901781</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>BOTZ.L</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3377,19 +3377,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.6565</v>
+        <v>1</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45805.66180811343</v>
+        <v>45482.71294556713</v>
       </c>
       <c r="G60" t="n">
-        <v>13.275</v>
+        <v>20.58</v>
       </c>
       <c r="H60" t="n">
-        <v>13.07</v>
+        <v>20.58</v>
       </c>
       <c r="I60" t="n">
-        <v>9.91</v>
+        <v>20.58</v>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
@@ -3406,14 +3406,14 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="n">
-        <v>1648735305</v>
+        <v>1599449649</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -3426,19 +3426,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.4576</v>
+        <v>0.4145</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>45695.85530675926</v>
+        <v>45663.73562525463</v>
       </c>
       <c r="G61" t="n">
-        <v>21.85</v>
+        <v>24.11</v>
       </c>
       <c r="H61" t="n">
-        <v>20.3</v>
+        <v>18.17</v>
       </c>
       <c r="I61" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
@@ -3455,18 +3455,18 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>-0.71</v>
+        <v>-2.46</v>
       </c>
       <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="n">
-        <v>1727591551</v>
+        <v>1845429956</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3475,19 +3475,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>0.6565</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>45743.77389555555</v>
+        <v>45805.66180811343</v>
       </c>
       <c r="G62" t="n">
-        <v>72.87</v>
+        <v>13.275</v>
       </c>
       <c r="H62" t="n">
-        <v>72.83</v>
+        <v>13.095</v>
       </c>
       <c r="I62" t="n">
-        <v>72.87</v>
+        <v>9.91</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
@@ -3504,18 +3504,18 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="n">
-        <v>1559803221</v>
+        <v>1883977086</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3524,19 +3524,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.092</v>
+        <v>1</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>45628.85951927083</v>
+        <v>45827.66106613426</v>
       </c>
       <c r="G63" t="n">
-        <v>162.85</v>
+        <v>12.875</v>
       </c>
       <c r="H63" t="n">
-        <v>128.99</v>
+        <v>13.095</v>
       </c>
       <c r="I63" t="n">
-        <v>14.98</v>
+        <v>14.86</v>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
@@ -3553,18 +3553,18 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>-3.11</v>
+        <v>0.28</v>
       </c>
       <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="n">
-        <v>1824476420</v>
+        <v>1648735305</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3573,19 +3573,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.1548</v>
+        <v>0.4576</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>45792.64714148148</v>
+        <v>45695.85530675926</v>
       </c>
       <c r="G64" t="n">
-        <v>129.17</v>
+        <v>21.85</v>
       </c>
       <c r="H64" t="n">
-        <v>128.99</v>
+        <v>18.17</v>
       </c>
       <c r="I64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
@@ -3602,18 +3602,18 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>-0.03</v>
+        <v>-1.69</v>
       </c>
       <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="n">
-        <v>1845431561</v>
+        <v>1727591551</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>BND</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3622,19 +3622,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.3271</v>
+        <v>1</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>45805.66210755787</v>
+        <v>45743.77389555555</v>
       </c>
       <c r="G65" t="n">
-        <v>30.57</v>
+        <v>72.87</v>
       </c>
       <c r="H65" t="n">
-        <v>35.28</v>
+        <v>73.28</v>
       </c>
       <c r="I65" t="n">
-        <v>10</v>
+        <v>72.87</v>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
@@ -3651,18 +3651,18 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>1.54</v>
+        <v>0.41</v>
       </c>
       <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="n">
-        <v>1806978791</v>
+        <v>1559803221</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3671,19 +3671,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.0867</v>
+        <v>0.092</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>45783.83109655092</v>
+        <v>45628.85951927083</v>
       </c>
       <c r="G66" t="n">
-        <v>126.78</v>
+        <v>162.85</v>
       </c>
       <c r="H66" t="n">
-        <v>142.34</v>
+        <v>131.06</v>
       </c>
       <c r="I66" t="n">
-        <v>10.99</v>
+        <v>14.98</v>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
@@ -3700,14 +3700,14 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>1.35</v>
+        <v>-2.92</v>
       </c>
       <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="n">
-        <v>1517510856</v>
+        <v>1824476420</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -3720,19 +3720,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.0602</v>
+        <v>0.1548</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>45597.61014849537</v>
+        <v>45792.64714148148</v>
       </c>
       <c r="G67" t="n">
-        <v>166.03</v>
+        <v>129.17</v>
       </c>
       <c r="H67" t="n">
-        <v>128.99</v>
+        <v>131.06</v>
       </c>
       <c r="I67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
@@ -3749,18 +3749,18 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>-2.23</v>
+        <v>0.29</v>
       </c>
       <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="n">
-        <v>1358151307</v>
+        <v>1845431561</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3769,19 +3769,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.1081</v>
+        <v>0.0179</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>45460.88529052083</v>
+        <v>45805.66210755787</v>
       </c>
       <c r="G68" t="n">
-        <v>165.93</v>
+        <v>30.57</v>
       </c>
       <c r="H68" t="n">
-        <v>128.99</v>
+        <v>33.28</v>
       </c>
       <c r="I68" t="n">
-        <v>17.94</v>
+        <v>0.55</v>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
@@ -3798,18 +3798,18 @@
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>-3.99</v>
+        <v>0.05</v>
       </c>
       <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="n">
-        <v>1727563010</v>
+        <v>1806978791</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3818,19 +3818,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>0.0867</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>45743.76106726852</v>
+        <v>45783.83109655092</v>
       </c>
       <c r="G69" t="n">
-        <v>46.11</v>
+        <v>126.78</v>
       </c>
       <c r="H69" t="n">
-        <v>48.15</v>
+        <v>150.56</v>
       </c>
       <c r="I69" t="n">
-        <v>46.11</v>
+        <v>10.99</v>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
@@ -3847,18 +3847,18 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="n">
-        <v>1824482557</v>
+        <v>1517510856</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3867,19 +3867,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.2641</v>
+        <v>0.0602</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>45792.64805195602</v>
+        <v>45597.61014849537</v>
       </c>
       <c r="G70" t="n">
-        <v>56.78</v>
+        <v>166.03</v>
       </c>
       <c r="H70" t="n">
-        <v>59.49</v>
+        <v>131.06</v>
       </c>
       <c r="I70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
@@ -3896,18 +3896,18 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>0.71</v>
+        <v>-2.11</v>
       </c>
       <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="n">
-        <v>1845429980</v>
+        <v>1358151307</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3916,19 +3916,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>0.1081</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>45805.66181400463</v>
+        <v>45460.88529052083</v>
       </c>
       <c r="G71" t="n">
-        <v>13.27</v>
+        <v>165.93</v>
       </c>
       <c r="H71" t="n">
-        <v>13.07</v>
+        <v>131.06</v>
       </c>
       <c r="I71" t="n">
-        <v>15.09</v>
+        <v>17.94</v>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
@@ -3945,18 +3945,18 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>-0.11</v>
+        <v>-3.76</v>
       </c>
       <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="n">
-        <v>1666461140</v>
+        <v>1727563010</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3965,19 +3965,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.2651</v>
+        <v>1</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>45708.68207092593</v>
+        <v>45743.76106726852</v>
       </c>
       <c r="G72" t="n">
-        <v>37.7</v>
+        <v>46.11</v>
       </c>
       <c r="H72" t="n">
-        <v>35.26</v>
+        <v>49.01</v>
       </c>
       <c r="I72" t="n">
-        <v>9.99</v>
+        <v>46.11</v>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -3994,18 +3994,18 @@
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>-0.64</v>
+        <v>2.9</v>
       </c>
       <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="n">
-        <v>1631475148</v>
+        <v>1824482557</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4014,19 +4014,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.2592</v>
+        <v>0.2641</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45685.83625201389</v>
+        <v>45792.64805195602</v>
       </c>
       <c r="G73" t="n">
-        <v>38.58</v>
+        <v>56.78</v>
       </c>
       <c r="H73" t="n">
-        <v>35.26</v>
+        <v>59.93</v>
       </c>
       <c r="I73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
@@ -4043,18 +4043,18 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>-0.86</v>
+        <v>0.83</v>
       </c>
       <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="n">
-        <v>1554741910</v>
+        <v>1845429980</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4063,19 +4063,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.3495</v>
+        <v>1</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45623.74951116898</v>
+        <v>45805.66181400463</v>
       </c>
       <c r="G74" t="n">
-        <v>15.3</v>
+        <v>13.27</v>
       </c>
       <c r="H74" t="n">
-        <v>20.77</v>
+        <v>13.095</v>
       </c>
       <c r="I74" t="n">
-        <v>5.35</v>
+        <v>15.09</v>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
@@ -4092,14 +4092,14 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>1.91</v>
+        <v>0.05</v>
       </c>
       <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="n">
-        <v>1599455288</v>
+        <v>1666461140</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -4112,19 +4112,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.2195</v>
+        <v>0.2651</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>45663.73750263889</v>
+        <v>45708.68207092593</v>
       </c>
       <c r="G75" t="n">
-        <v>45.55</v>
+        <v>37.7</v>
       </c>
       <c r="H75" t="n">
-        <v>35.26</v>
+        <v>34.37</v>
       </c>
       <c r="I75" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
@@ -4141,18 +4141,18 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>-2.26</v>
+        <v>-0.88</v>
       </c>
       <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="n">
-        <v>1869077157</v>
+        <v>1631475148</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4161,19 +4161,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.3061</v>
+        <v>0.2592</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>45819.6742621412</v>
+        <v>45685.83625201389</v>
       </c>
       <c r="G76" t="n">
-        <v>13.285</v>
+        <v>38.58</v>
       </c>
       <c r="H76" t="n">
-        <v>13.07</v>
+        <v>34.37</v>
       </c>
       <c r="I76" t="n">
-        <v>4.69</v>
+        <v>10</v>
       </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
@@ -4190,18 +4190,18 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>-0.11</v>
+        <v>-1.09</v>
       </c>
       <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="n">
-        <v>1880445013</v>
+        <v>1554741910</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4210,19 +4210,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.3495</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>45825.8922271412</v>
+        <v>45623.74951116898</v>
       </c>
       <c r="G77" t="n">
-        <v>139.86</v>
+        <v>15.3</v>
       </c>
       <c r="H77" t="n">
-        <v>138.29</v>
+        <v>21.35</v>
       </c>
       <c r="I77" t="n">
-        <v>10</v>
+        <v>5.35</v>
       </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
@@ -4239,14 +4239,14 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>-0.11</v>
+        <v>2.11</v>
       </c>
       <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="n">
-        <v>1653137218</v>
+        <v>1599455288</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -4259,16 +4259,16 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.277</v>
+        <v>0.2195</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>45699.85152199074</v>
+        <v>45663.73750263889</v>
       </c>
       <c r="G78" t="n">
-        <v>36.1</v>
+        <v>45.55</v>
       </c>
       <c r="H78" t="n">
-        <v>35.26</v>
+        <v>34.37</v>
       </c>
       <c r="I78" t="n">
         <v>10</v>
@@ -4288,18 +4288,18 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>-0.23</v>
+        <v>-2.46</v>
       </c>
       <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="n">
-        <v>1727564345</v>
+        <v>1869077157</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4308,19 +4308,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.3274</v>
+        <v>0.3061</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>45743.76175270833</v>
+        <v>45819.6742621412</v>
       </c>
       <c r="G79" t="n">
-        <v>30.54</v>
+        <v>13.285</v>
       </c>
       <c r="H79" t="n">
-        <v>35.28</v>
+        <v>13.095</v>
       </c>
       <c r="I79" t="n">
-        <v>10</v>
+        <v>4.69</v>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
@@ -4337,18 +4337,18 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>1.55</v>
+        <v>-0.06</v>
       </c>
       <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="n">
-        <v>1563288050</v>
+        <v>1880445013</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4357,16 +4357,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.0626</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>45630.85583428241</v>
+        <v>45825.8922271412</v>
       </c>
       <c r="G80" t="n">
-        <v>159.74</v>
+        <v>139.86</v>
       </c>
       <c r="H80" t="n">
-        <v>128.99</v>
+        <v>142.64</v>
       </c>
       <c r="I80" t="n">
         <v>10</v>
@@ -4386,18 +4386,18 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>-1.93</v>
+        <v>0.2</v>
       </c>
       <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="n">
-        <v>1701098878</v>
+        <v>1653137218</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4406,19 +4406,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.0383</v>
+        <v>0.277</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>45727.87167594907</v>
+        <v>45699.85152199074</v>
       </c>
       <c r="G81" t="n">
-        <v>139.41</v>
+        <v>36.1</v>
       </c>
       <c r="H81" t="n">
-        <v>142.34</v>
+        <v>34.37</v>
       </c>
       <c r="I81" t="n">
-        <v>5.34</v>
+        <v>10</v>
       </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
@@ -4435,18 +4435,18 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>0.11</v>
+        <v>-0.48</v>
       </c>
       <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="n">
-        <v>1843477272</v>
+        <v>1563288050</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4455,19 +4455,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0.0626</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>45804.66725678241</v>
+        <v>45630.85583428241</v>
       </c>
       <c r="G82" t="n">
-        <v>17.86</v>
+        <v>159.74</v>
       </c>
       <c r="H82" t="n">
-        <v>17.65</v>
+        <v>131.06</v>
       </c>
       <c r="I82" t="n">
-        <v>17.86</v>
+        <v>10</v>
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
@@ -4484,18 +4484,18 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>-0.21</v>
+        <v>-1.8</v>
       </c>
       <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="n">
-        <v>1666459175</v>
+        <v>1701098878</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4504,19 +4504,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.1641</v>
+        <v>0.0383</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>45708.68165298611</v>
+        <v>45727.87167594907</v>
       </c>
       <c r="G83" t="n">
-        <v>17.18</v>
+        <v>139.41</v>
       </c>
       <c r="H83" t="n">
-        <v>20.77</v>
+        <v>150.56</v>
       </c>
       <c r="I83" t="n">
-        <v>2.82</v>
+        <v>5.34</v>
       </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
@@ -4533,18 +4533,18 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>0.59</v>
+        <v>0.43</v>
       </c>
       <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="n">
-        <v>1843468958</v>
+        <v>1843477272</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4553,19 +4553,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.2208</v>
+        <v>1</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>45804.66597149306</v>
+        <v>45804.66725678241</v>
       </c>
       <c r="G84" t="n">
-        <v>67.93000000000001</v>
+        <v>17.86</v>
       </c>
       <c r="H84" t="n">
-        <v>71.56999999999999</v>
+        <v>18.25</v>
       </c>
       <c r="I84" t="n">
-        <v>15</v>
+        <v>17.86</v>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
@@ -4582,14 +4582,14 @@
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>0.8</v>
+        <v>0.39</v>
       </c>
       <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="n">
-        <v>1744916452</v>
+        <v>1666459175</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -4602,19 +4602,19 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.4245</v>
+        <v>0.1641</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>45751.74230173611</v>
+        <v>45708.68165298611</v>
       </c>
       <c r="G85" t="n">
-        <v>17.54</v>
+        <v>17.18</v>
       </c>
       <c r="H85" t="n">
-        <v>20.77</v>
+        <v>21.35</v>
       </c>
       <c r="I85" t="n">
-        <v>7.45</v>
+        <v>2.82</v>
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
@@ -4631,18 +4631,18 @@
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>1.37</v>
+        <v>0.68</v>
       </c>
       <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="n">
-        <v>1662993636</v>
+        <v>1843468958</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4651,19 +4651,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>0.2208</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>45706.87026833333</v>
+        <v>45804.66597149306</v>
       </c>
       <c r="G86" t="n">
-        <v>20.65</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="H86" t="n">
-        <v>21.07</v>
+        <v>71.42</v>
       </c>
       <c r="I86" t="n">
-        <v>20.65</v>
+        <v>15</v>
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
@@ -4680,18 +4680,18 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>0.42</v>
+        <v>0.77</v>
       </c>
       <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="n">
-        <v>1414752069</v>
+        <v>1744916452</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4700,19 +4700,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.1933</v>
+        <v>0.4245</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>45511.86049193287</v>
+        <v>45751.74230173611</v>
       </c>
       <c r="G87" t="n">
-        <v>77.53</v>
+        <v>17.54</v>
       </c>
       <c r="H87" t="n">
-        <v>71.56999999999999</v>
+        <v>21.35</v>
       </c>
       <c r="I87" t="n">
-        <v>14.99</v>
+        <v>7.45</v>
       </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
@@ -4729,18 +4729,18 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>-1.16</v>
+        <v>1.61</v>
       </c>
       <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="n">
-        <v>1499061783</v>
+        <v>1662993636</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4749,19 +4749,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.0001</v>
+        <v>1</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>45582.73996892361</v>
+        <v>45706.87026833333</v>
       </c>
       <c r="G88" t="n">
-        <v>232.2</v>
+        <v>20.65</v>
       </c>
       <c r="H88" t="n">
-        <v>196.61</v>
+        <v>21.68</v>
       </c>
       <c r="I88" t="n">
-        <v>0.02</v>
+        <v>20.65</v>
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
@@ -4778,14 +4778,14 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="n">
-        <v>1662995258</v>
+        <v>1414752069</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4798,19 +4798,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.2943</v>
+        <v>0.1933</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>45706.87121422453</v>
+        <v>45511.86049193287</v>
       </c>
       <c r="G89" t="n">
-        <v>67.97</v>
+        <v>77.53</v>
       </c>
       <c r="H89" t="n">
-        <v>71.56999999999999</v>
+        <v>71.42</v>
       </c>
       <c r="I89" t="n">
-        <v>20</v>
+        <v>14.99</v>
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
@@ -4827,18 +4827,18 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>1.06</v>
+        <v>-1.18</v>
       </c>
       <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="n">
-        <v>1880443947</v>
+        <v>1499061783</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4847,19 +4847,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.1047</v>
+        <v>0.0001</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>45825.891695625</v>
+        <v>45582.73996892361</v>
       </c>
       <c r="G90" t="n">
-        <v>142.99</v>
+        <v>232.2</v>
       </c>
       <c r="H90" t="n">
-        <v>142.34</v>
+        <v>200.31</v>
       </c>
       <c r="I90" t="n">
-        <v>14.97</v>
+        <v>0.02</v>
       </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
@@ -4876,18 +4876,18 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="n">
-        <v>1867461578</v>
+        <v>1662995258</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BAP</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4896,19 +4896,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.2943</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>45818.90835071759</v>
+        <v>45706.87121422453</v>
       </c>
       <c r="G91" t="n">
-        <v>216.54</v>
+        <v>67.97</v>
       </c>
       <c r="H91" t="n">
-        <v>217.2</v>
+        <v>71.42</v>
       </c>
       <c r="I91" t="n">
-        <v>19.99</v>
+        <v>20</v>
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
@@ -4925,18 +4925,18 @@
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>0.06</v>
+        <v>1.02</v>
       </c>
       <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="n">
-        <v>1648737122</v>
+        <v>1880443947</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4945,19 +4945,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.01</v>
+        <v>0.1047</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>45695.85619950231</v>
+        <v>45825.891695625</v>
       </c>
       <c r="G92" t="n">
-        <v>408.33</v>
+        <v>142.99</v>
       </c>
       <c r="H92" t="n">
-        <v>480</v>
+        <v>150.56</v>
       </c>
       <c r="I92" t="n">
-        <v>4.08</v>
+        <v>14.97</v>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
@@ -4974,18 +4974,18 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="n">
-        <v>1754302454</v>
+        <v>1867461578</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>BAP</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4994,19 +4994,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.3673</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>45755.88025324074</v>
+        <v>45818.90835071759</v>
       </c>
       <c r="G93" t="n">
-        <v>27.17</v>
+        <v>216.54</v>
       </c>
       <c r="H93" t="n">
-        <v>35.26</v>
+        <v>217.11</v>
       </c>
       <c r="I93" t="n">
-        <v>9.98</v>
+        <v>19.99</v>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
@@ -5023,18 +5023,18 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>2.97</v>
+        <v>0.05</v>
       </c>
       <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="n">
-        <v>1599448103</v>
+        <v>1648737122</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5043,19 +5043,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.2839</v>
+        <v>0.001</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>45663.73506711805</v>
+        <v>45695.85619950231</v>
       </c>
       <c r="G94" t="n">
-        <v>52.83</v>
+        <v>408.33</v>
       </c>
       <c r="H94" t="n">
-        <v>59.49</v>
+        <v>490.22</v>
       </c>
       <c r="I94" t="n">
-        <v>15</v>
+        <v>0.41</v>
       </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
@@ -5072,18 +5072,18 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>1.89</v>
+        <v>0.08</v>
       </c>
       <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="n">
-        <v>1599431096</v>
+        <v>1754302454</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5092,19 +5092,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.1013</v>
+        <v>0.3673</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>45663.73014731482</v>
+        <v>45755.88025324074</v>
       </c>
       <c r="G95" t="n">
-        <v>148.02</v>
+        <v>27.17</v>
       </c>
       <c r="H95" t="n">
-        <v>128.99</v>
+        <v>34.37</v>
       </c>
       <c r="I95" t="n">
-        <v>14.99</v>
+        <v>9.98</v>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -5121,18 +5121,18 @@
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>-1.92</v>
+        <v>2.64</v>
       </c>
       <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="n">
-        <v>1843477152</v>
+        <v>1599448103</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5141,19 +5141,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.1198</v>
+        <v>0.2839</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>45804.66724922453</v>
+        <v>45663.73506711805</v>
       </c>
       <c r="G96" t="n">
-        <v>17.86</v>
+        <v>52.83</v>
       </c>
       <c r="H96" t="n">
-        <v>17.65</v>
+        <v>59.93</v>
       </c>
       <c r="I96" t="n">
-        <v>2.14</v>
+        <v>15</v>
       </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
@@ -5170,18 +5170,18 @@
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>-0.03</v>
+        <v>2.01</v>
       </c>
       <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="n">
-        <v>1817264187</v>
+        <v>1599431096</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5190,19 +5190,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.4757</v>
+        <v>0.1013</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>45789.64859377315</v>
+        <v>45663.73014731482</v>
       </c>
       <c r="G97" t="n">
-        <v>42.02</v>
+        <v>148.02</v>
       </c>
       <c r="H97" t="n">
-        <v>43.22</v>
+        <v>131.06</v>
       </c>
       <c r="I97" t="n">
-        <v>19.99</v>
+        <v>14.99</v>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
@@ -5219,18 +5219,18 @@
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>0.57</v>
+        <v>-1.71</v>
       </c>
       <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="n">
-        <v>1582714896</v>
+        <v>1843477152</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5239,19 +5239,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.4847</v>
+        <v>0.1198</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>45645.89066263889</v>
+        <v>45804.66724922453</v>
       </c>
       <c r="G98" t="n">
-        <v>20.62</v>
+        <v>17.86</v>
       </c>
       <c r="H98" t="n">
-        <v>20.3</v>
+        <v>18.25</v>
       </c>
       <c r="I98" t="n">
-        <v>9.99</v>
+        <v>2.14</v>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
@@ -5268,18 +5268,18 @@
         <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>-0.15</v>
+        <v>0.05</v>
       </c>
       <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="n">
-        <v>1811475599</v>
+        <v>1817264187</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5288,19 +5288,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.7256</v>
+        <v>0.4757</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>45785.66972070602</v>
+        <v>45789.64859377315</v>
       </c>
       <c r="G99" t="n">
-        <v>12.75</v>
+        <v>42.02</v>
       </c>
       <c r="H99" t="n">
-        <v>13.07</v>
+        <v>44.92</v>
       </c>
       <c r="I99" t="n">
-        <v>10.51</v>
+        <v>19.99</v>
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
@@ -5317,14 +5317,14 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>0.36</v>
+        <v>1.38</v>
       </c>
       <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="n">
-        <v>1701100027</v>
+        <v>1582714896</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -5337,19 +5337,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.7812</v>
+        <v>0.4847</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>45727.87202070602</v>
+        <v>45645.89066263889</v>
       </c>
       <c r="G100" t="n">
-        <v>19.2</v>
+        <v>20.62</v>
       </c>
       <c r="H100" t="n">
-        <v>20.3</v>
+        <v>18.17</v>
       </c>
       <c r="I100" t="n">
-        <v>15</v>
+        <v>9.99</v>
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
@@ -5366,18 +5366,18 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>0.86</v>
+        <v>-1.18</v>
       </c>
       <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="n">
-        <v>1830410729</v>
+        <v>1811475599</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5386,19 +5386,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.1091</v>
+        <v>0.7256</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>45796.82476561343</v>
+        <v>45785.66972070602</v>
       </c>
       <c r="G101" t="n">
-        <v>33.66</v>
+        <v>12.75</v>
       </c>
       <c r="H101" t="n">
-        <v>38.41</v>
+        <v>13.095</v>
       </c>
       <c r="I101" t="n">
-        <v>3.67</v>
+        <v>10.51</v>
       </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -5415,18 +5415,18 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="n">
-        <v>1867458993</v>
+        <v>1701100027</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5435,19 +5435,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.3417</v>
+        <v>0.7812</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>45818.90699613426</v>
+        <v>45727.87202070602</v>
       </c>
       <c r="G102" t="n">
-        <v>58.53</v>
+        <v>19.2</v>
       </c>
       <c r="H102" t="n">
-        <v>59.49</v>
+        <v>18.17</v>
       </c>
       <c r="I102" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
@@ -5464,18 +5464,18 @@
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>0.33</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="n">
-        <v>1811475646</v>
+        <v>1830410729</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5484,19 +5484,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1</v>
+        <v>0.1091</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>45785.66973634259</v>
+        <v>45796.82476561343</v>
       </c>
       <c r="G103" t="n">
-        <v>12.75</v>
+        <v>33.66</v>
       </c>
       <c r="H103" t="n">
-        <v>13.07</v>
+        <v>38.46</v>
       </c>
       <c r="I103" t="n">
-        <v>14.49</v>
+        <v>3.67</v>
       </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
@@ -5513,18 +5513,18 @@
         <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>0.49</v>
+        <v>0.53</v>
       </c>
       <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="n">
-        <v>1882283184</v>
+        <v>1867458993</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5533,19 +5533,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.4835</v>
+        <v>0.3417</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>45826.76569390047</v>
+        <v>45818.90699613426</v>
       </c>
       <c r="G104" t="n">
-        <v>20.69</v>
+        <v>58.53</v>
       </c>
       <c r="H104" t="n">
-        <v>20.3</v>
+        <v>59.93</v>
       </c>
       <c r="I104" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
@@ -5562,18 +5562,18 @@
         <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>-0.18</v>
+        <v>0.48</v>
       </c>
       <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="n">
-        <v>1867196288</v>
+        <v>1888700382</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5582,19 +5582,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.5953000000000001</v>
+        <v>1</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>45818.80209099537</v>
+        <v>45831.65144708334</v>
       </c>
       <c r="G105" t="n">
-        <v>41.99</v>
+        <v>47.58</v>
       </c>
       <c r="H105" t="n">
-        <v>43.22</v>
+        <v>49.01</v>
       </c>
       <c r="I105" t="n">
-        <v>25</v>
+        <v>47.58</v>
       </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
@@ -5611,18 +5611,18 @@
         <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>0.73</v>
+        <v>1.43</v>
       </c>
       <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="n">
-        <v>1744879358</v>
+        <v>1811475646</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5631,19 +5631,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.2701</v>
+        <v>1</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>45751.73925940973</v>
+        <v>45785.66973634259</v>
       </c>
       <c r="G106" t="n">
-        <v>148.09</v>
+        <v>12.75</v>
       </c>
       <c r="H106" t="n">
-        <v>213.27</v>
+        <v>13.095</v>
       </c>
       <c r="I106" t="n">
-        <v>40</v>
+        <v>14.49</v>
       </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
@@ -5660,18 +5660,18 @@
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>17.6</v>
+        <v>0.65</v>
       </c>
       <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="n">
-        <v>1582735114</v>
+        <v>1882283184</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5680,19 +5680,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.0003</v>
+        <v>0.4835</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>45645.90076803241</v>
+        <v>45826.76569390047</v>
       </c>
       <c r="G107" t="n">
-        <v>130.51</v>
+        <v>20.69</v>
       </c>
       <c r="H107" t="n">
-        <v>138.29</v>
+        <v>18.17</v>
       </c>
       <c r="I107" t="n">
-        <v>0.04</v>
+        <v>10</v>
       </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
@@ -5709,18 +5709,18 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>-1.21</v>
       </c>
       <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="n">
-        <v>1422773288</v>
+        <v>1867196288</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5729,19 +5729,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.483</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>45518.84428523148</v>
+        <v>45818.80209099537</v>
       </c>
       <c r="G108" t="n">
-        <v>51.24</v>
+        <v>41.99</v>
       </c>
       <c r="H108" t="n">
-        <v>59.49</v>
+        <v>44.92</v>
       </c>
       <c r="I108" t="n">
-        <v>24.75</v>
+        <v>25</v>
       </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
@@ -5758,18 +5758,18 @@
         <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>3.98</v>
+        <v>1.74</v>
       </c>
       <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="n">
-        <v>1450043624</v>
+        <v>1744879358</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5778,19 +5778,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.0231</v>
+        <v>0.2701</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>45544.65163525463</v>
+        <v>45751.73925940973</v>
       </c>
       <c r="G109" t="n">
-        <v>147.48</v>
+        <v>148.09</v>
       </c>
       <c r="H109" t="n">
-        <v>127.93</v>
+        <v>220.02</v>
       </c>
       <c r="I109" t="n">
-        <v>3.41</v>
+        <v>40</v>
       </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
@@ -5807,18 +5807,18 @@
         <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>-0.45</v>
+        <v>19.43</v>
       </c>
       <c r="Q109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="n">
-        <v>1869077178</v>
+        <v>1582735114</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5827,19 +5827,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1</v>
+        <v>0.0003</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>45819.67426902778</v>
+        <v>45645.90076803241</v>
       </c>
       <c r="G110" t="n">
-        <v>13.285</v>
+        <v>130.51</v>
       </c>
       <c r="H110" t="n">
-        <v>13.07</v>
+        <v>142.64</v>
       </c>
       <c r="I110" t="n">
-        <v>15.31</v>
+        <v>0.04</v>
       </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
@@ -5856,18 +5856,18 @@
         <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>-0.33</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="n">
-        <v>1644796307</v>
+        <v>1422773288</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5876,19 +5876,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1</v>
+        <v>0.483</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>45693.85501710648</v>
+        <v>45518.84428523148</v>
       </c>
       <c r="G111" t="n">
-        <v>20.36</v>
+        <v>51.24</v>
       </c>
       <c r="H111" t="n">
-        <v>21.07</v>
+        <v>59.93</v>
       </c>
       <c r="I111" t="n">
-        <v>20.36</v>
+        <v>24.75</v>
       </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
@@ -5905,18 +5905,18 @@
         <v>0</v>
       </c>
       <c r="P111" t="n">
-        <v>0.71</v>
+        <v>4.2</v>
       </c>
       <c r="Q111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="n">
-        <v>1729617775</v>
+        <v>1450043624</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5925,19 +5925,19 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.0907</v>
+        <v>0.0231</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>45744.71339734954</v>
+        <v>45544.65163525463</v>
       </c>
       <c r="G112" t="n">
-        <v>165.35</v>
+        <v>147.48</v>
       </c>
       <c r="H112" t="n">
-        <v>213.27</v>
+        <v>129.91</v>
       </c>
       <c r="I112" t="n">
-        <v>15</v>
+        <v>3.41</v>
       </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
@@ -5954,18 +5954,18 @@
         <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>4.34</v>
+        <v>-0.41</v>
       </c>
       <c r="Q112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="n">
-        <v>1559803984</v>
+        <v>1869077178</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5974,19 +5974,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.1076</v>
+        <v>1</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>45628.86014383102</v>
+        <v>45819.67426902778</v>
       </c>
       <c r="G113" t="n">
-        <v>139.4</v>
+        <v>13.285</v>
       </c>
       <c r="H113" t="n">
-        <v>127.93</v>
+        <v>13.095</v>
       </c>
       <c r="I113" t="n">
-        <v>15</v>
+        <v>15.31</v>
       </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
@@ -6003,18 +6003,18 @@
         <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>-1.23</v>
+        <v>-0.17</v>
       </c>
       <c r="Q113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="n">
-        <v>1825032062</v>
+        <v>1644796307</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6023,19 +6023,19 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.3559</v>
+        <v>1</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>45792.76080334491</v>
+        <v>45693.85501710648</v>
       </c>
       <c r="G114" t="n">
-        <v>28.09</v>
+        <v>20.36</v>
       </c>
       <c r="H114" t="n">
-        <v>35.28</v>
+        <v>21.68</v>
       </c>
       <c r="I114" t="n">
-        <v>10</v>
+        <v>20.36</v>
       </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
@@ -6052,18 +6052,18 @@
         <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>2.56</v>
+        <v>1.32</v>
       </c>
       <c r="Q114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="n">
-        <v>1843469729</v>
+        <v>1729617775</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6072,16 +6072,16 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.0956</v>
+        <v>0.0907</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>45804.66615450232</v>
+        <v>45744.71339734954</v>
       </c>
       <c r="G115" t="n">
-        <v>156.9</v>
+        <v>165.35</v>
       </c>
       <c r="H115" t="n">
-        <v>142.34</v>
+        <v>220.02</v>
       </c>
       <c r="I115" t="n">
         <v>15</v>
@@ -6101,18 +6101,18 @@
         <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>-1.39</v>
+        <v>4.96</v>
       </c>
       <c r="Q115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="n">
-        <v>1806980496</v>
+        <v>1559803984</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6121,19 +6121,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1</v>
+        <v>0.1076</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>45783.83190503472</v>
+        <v>45628.86014383102</v>
       </c>
       <c r="G116" t="n">
-        <v>16.12</v>
+        <v>139.4</v>
       </c>
       <c r="H116" t="n">
-        <v>17.65</v>
+        <v>129.91</v>
       </c>
       <c r="I116" t="n">
-        <v>16.12</v>
+        <v>15</v>
       </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
@@ -6150,18 +6150,18 @@
         <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>1.53</v>
+        <v>-1.02</v>
       </c>
       <c r="Q116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="n">
-        <v>1495551484</v>
+        <v>1843469729</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6170,19 +6170,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.1914</v>
+        <v>0.0956</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>45580.70648087963</v>
+        <v>45804.66615450232</v>
       </c>
       <c r="G117" t="n">
-        <v>135.82</v>
+        <v>156.9</v>
       </c>
       <c r="H117" t="n">
-        <v>136.42</v>
+        <v>150.56</v>
       </c>
       <c r="I117" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
@@ -6199,18 +6199,18 @@
         <v>0</v>
       </c>
       <c r="P117" t="n">
-        <v>0.11</v>
+        <v>-0.61</v>
       </c>
       <c r="Q117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="n">
-        <v>1566610015</v>
+        <v>1806980496</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6219,19 +6219,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9385</v>
+        <v>1</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>45632.87667083334</v>
+        <v>45783.83190503472</v>
       </c>
       <c r="G118" t="n">
-        <v>21.31</v>
+        <v>16.12</v>
       </c>
       <c r="H118" t="n">
-        <v>20.3</v>
+        <v>18.25</v>
       </c>
       <c r="I118" t="n">
-        <v>20</v>
+        <v>16.12</v>
       </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
@@ -6248,18 +6248,18 @@
         <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>-0.95</v>
+        <v>2.13</v>
       </c>
       <c r="Q118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="n">
-        <v>1727574394</v>
+        <v>1495551484</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6268,19 +6268,19 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1</v>
+        <v>0.1914</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>45743.76658678241</v>
+        <v>45580.70648087963</v>
       </c>
       <c r="G119" t="n">
-        <v>21.13</v>
+        <v>135.82</v>
       </c>
       <c r="H119" t="n">
-        <v>21.07</v>
+        <v>137.47</v>
       </c>
       <c r="I119" t="n">
-        <v>21.13</v>
+        <v>26</v>
       </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
@@ -6297,18 +6297,18 @@
         <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>-0.06</v>
+        <v>0.31</v>
       </c>
       <c r="Q119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="n">
-        <v>1666459270</v>
+        <v>1566610015</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6317,19 +6317,19 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1</v>
+        <v>0.9385</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>45708.68166530092</v>
+        <v>45632.87667083334</v>
       </c>
       <c r="G120" t="n">
-        <v>17.18</v>
+        <v>21.31</v>
       </c>
       <c r="H120" t="n">
-        <v>20.77</v>
+        <v>18.17</v>
       </c>
       <c r="I120" t="n">
-        <v>17.18</v>
+        <v>20</v>
       </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
@@ -6346,18 +6346,18 @@
         <v>0</v>
       </c>
       <c r="P120" t="n">
-        <v>3.59</v>
+        <v>-2.95</v>
       </c>
       <c r="Q120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="n">
-        <v>1867195793</v>
+        <v>1727574394</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6366,19 +6366,19 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.2339</v>
+        <v>1</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>45818.80180457176</v>
+        <v>45743.76658678241</v>
       </c>
       <c r="G121" t="n">
-        <v>42.74</v>
+        <v>21.13</v>
       </c>
       <c r="H121" t="n">
-        <v>42.37</v>
+        <v>21.68</v>
       </c>
       <c r="I121" t="n">
-        <v>10</v>
+        <v>21.13</v>
       </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
@@ -6395,18 +6395,18 @@
         <v>0</v>
       </c>
       <c r="P121" t="n">
-        <v>-0.09</v>
+        <v>0.55</v>
       </c>
       <c r="Q121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="n">
-        <v>1883977086</v>
+        <v>1666459270</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6418,14 +6418,16 @@
         <v>1</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>45827.66106613426</v>
+        <v>45708.68166530092</v>
       </c>
       <c r="G122" t="n">
-        <v>12.875</v>
-      </c>
-      <c r="H122" t="inlineStr"/>
+        <v>17.18</v>
+      </c>
+      <c r="H122" t="n">
+        <v>21.35</v>
+      </c>
       <c r="I122" t="n">
-        <v>14.86</v>
+        <v>17.18</v>
       </c>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
@@ -6442,18 +6444,18 @@
         <v>0</v>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="n">
-        <v>1883977044</v>
+        <v>1867195793</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6462,17 +6464,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.345</v>
+        <v>0.2339</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>45827.66105774305</v>
+        <v>45818.80180457176</v>
       </c>
       <c r="G123" t="n">
-        <v>12.88</v>
-      </c>
-      <c r="H123" t="inlineStr"/>
+        <v>42.74</v>
+      </c>
+      <c r="H123" t="n">
+        <v>43.09</v>
+      </c>
       <c r="I123" t="n">
-        <v>5.13</v>
+        <v>10</v>
       </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
@@ -6489,7 +6493,7 @@
         <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="Q123" t="inlineStr"/>
     </row>
@@ -6520,7 +6524,7 @@
         <v>0</v>
       </c>
       <c r="P124" t="n">
-        <v>71.67</v>
+        <v>82.98</v>
       </c>
       <c r="Q124" t="inlineStr"/>
     </row>

--- a/Stock Selection/OPEN POSITION.xlsx
+++ b/Stock Selection/OPEN POSITION.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q124"/>
+  <dimension ref="A1:Q127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,11 +522,11 @@
     <row r="2">
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="n">
-        <v>1666451221</v>
+        <v>1867194722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0001</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45708.68022634259</v>
+        <v>45818.80135700232</v>
       </c>
       <c r="G2" t="n">
-        <v>43</v>
+        <v>21.27</v>
       </c>
       <c r="H2" t="n">
-        <v>43.09</v>
+        <v>20.79</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>21.27</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -564,18 +564,18 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0.48</v>
       </c>
       <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="n">
-        <v>1644789287</v>
+        <v>1811432805</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -584,19 +584,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.0813</v>
+        <v>0.0856</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45693.85123056713</v>
+        <v>45785.66143211805</v>
       </c>
       <c r="G3" t="n">
-        <v>129.08</v>
+        <v>128.46</v>
       </c>
       <c r="H3" t="n">
-        <v>129.91</v>
+        <v>179.46</v>
       </c>
       <c r="I3" t="n">
-        <v>10.49</v>
+        <v>11</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -613,18 +613,18 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.07000000000000001</v>
+        <v>4.36</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="n">
-        <v>1533882988</v>
+        <v>1662995258</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BOTZ.L</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -633,19 +633,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5</v>
+        <v>0.2943</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45609.60769543982</v>
+        <v>45706.87121422453</v>
       </c>
       <c r="G4" t="n">
-        <v>21.905</v>
+        <v>67.97</v>
       </c>
       <c r="H4" t="n">
-        <v>20.58</v>
+        <v>72.84</v>
       </c>
       <c r="I4" t="n">
-        <v>10.95</v>
+        <v>20</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -662,18 +662,18 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.66</v>
+        <v>1.44</v>
       </c>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="n">
-        <v>1599435465</v>
+        <v>1729617775</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.0289</v>
+        <v>0.0546</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45663.73115600694</v>
+        <v>45744.71339734954</v>
       </c>
       <c r="G5" t="n">
-        <v>517.7</v>
+        <v>165.35</v>
       </c>
       <c r="H5" t="n">
-        <v>556.39</v>
+        <v>240.32</v>
       </c>
       <c r="I5" t="n">
-        <v>14.96</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -711,18 +711,18 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.12</v>
+        <v>4.09</v>
       </c>
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="n">
-        <v>1880446963</v>
+        <v>1824475555</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0774</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45825.89330317129</v>
+        <v>45792.64702015046</v>
       </c>
       <c r="G6" t="n">
-        <v>129.25</v>
+        <v>21.66</v>
       </c>
       <c r="H6" t="n">
-        <v>129.91</v>
+        <v>20.79</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>21.66</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -760,18 +760,18 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.06</v>
+        <v>-0.87</v>
       </c>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="n">
-        <v>1712850989</v>
+        <v>1882278057</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -780,19 +780,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.0282</v>
+        <v>0.0432</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45734.85576775463</v>
+        <v>45826.76262912037</v>
       </c>
       <c r="G7" t="n">
-        <v>160.64</v>
+        <v>346.61</v>
       </c>
       <c r="H7" t="n">
-        <v>166.76</v>
+        <v>355.29</v>
       </c>
       <c r="I7" t="n">
-        <v>4.53</v>
+        <v>14.97</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -809,18 +809,18 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>1880442840</v>
+        <v>1867193304</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.2535</v>
+        <v>0.1337</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45825.89113450232</v>
+        <v>45818.8008296412</v>
       </c>
       <c r="G8" t="n">
-        <v>59.15</v>
+        <v>17.64</v>
       </c>
       <c r="H8" t="n">
-        <v>59.93</v>
+        <v>19.46</v>
       </c>
       <c r="I8" t="n">
-        <v>14.99</v>
+        <v>2.36</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -858,18 +858,18 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>1642762235</v>
+        <v>1461331124</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -878,19 +878,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.1572</v>
+        <v>0.3922</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45692.86612574074</v>
+        <v>45553.65374138889</v>
       </c>
       <c r="G9" t="n">
-        <v>127.16</v>
+        <v>50.99</v>
       </c>
       <c r="H9" t="n">
-        <v>137.47</v>
+        <v>59.79</v>
       </c>
       <c r="I9" t="n">
-        <v>19.99</v>
+        <v>20</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -907,18 +907,18 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.62</v>
+        <v>3.45</v>
       </c>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
-        <v>1680994777</v>
+        <v>1582735114</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.7278</v>
+        <v>0.0003</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45716.85705375</v>
+        <v>45645.90076803241</v>
       </c>
       <c r="G10" t="n">
-        <v>20.6</v>
+        <v>130.51</v>
       </c>
       <c r="H10" t="n">
-        <v>18.17</v>
+        <v>147.68</v>
       </c>
       <c r="I10" t="n">
-        <v>14.99</v>
+        <v>0.04</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -956,18 +956,18 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.77</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
-        <v>1888686062</v>
+        <v>1599448103</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -976,19 +976,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.2903</v>
+        <v>0.2839</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45831.64964792824</v>
+        <v>45663.73506711805</v>
       </c>
       <c r="G11" t="n">
-        <v>34.36</v>
+        <v>52.83</v>
       </c>
       <c r="H11" t="n">
-        <v>34.37</v>
+        <v>59.79</v>
       </c>
       <c r="I11" t="n">
-        <v>9.970000000000001</v>
+        <v>15</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -1005,18 +1005,18 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.01</v>
+        <v>1.97</v>
       </c>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>1583696868</v>
+        <v>1888686062</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BOTZ.L</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1025,19 +1025,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.5</v>
+        <v>0.2903</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>45646.60053979167</v>
+        <v>45831.64964792824</v>
       </c>
       <c r="G12" t="n">
-        <v>20.645</v>
+        <v>34.36</v>
       </c>
       <c r="H12" t="n">
-        <v>20.58</v>
+        <v>32.28</v>
       </c>
       <c r="I12" t="n">
-        <v>10.32</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -1054,18 +1054,18 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.03</v>
+        <v>-0.6</v>
       </c>
       <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>1824477589</v>
+        <v>1843474191</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1074,19 +1074,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.2344</v>
+        <v>0.9372</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>45792.64732982639</v>
+        <v>45804.66699503472</v>
       </c>
       <c r="G13" t="n">
-        <v>42.66</v>
+        <v>21.33</v>
       </c>
       <c r="H13" t="n">
-        <v>43.09</v>
+        <v>23.81</v>
       </c>
       <c r="I13" t="n">
-        <v>10</v>
+        <v>19.99</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -1103,18 +1103,18 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="n">
-        <v>1867193336</v>
+        <v>1744916452</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0.4245</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>45818.80084483796</v>
+        <v>45751.74230173611</v>
       </c>
       <c r="G14" t="n">
-        <v>17.64</v>
+        <v>17.54</v>
       </c>
       <c r="H14" t="n">
-        <v>18.25</v>
+        <v>23.81</v>
       </c>
       <c r="I14" t="n">
-        <v>17.64</v>
+        <v>7.45</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -1152,18 +1152,18 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.61</v>
+        <v>2.66</v>
       </c>
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="n">
-        <v>1796453499</v>
+        <v>1845429980</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.6422</v>
+        <v>1</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>45777.64668229167</v>
+        <v>45805.66181400463</v>
       </c>
       <c r="G15" t="n">
-        <v>15.57</v>
+        <v>13.27</v>
       </c>
       <c r="H15" t="n">
-        <v>18.25</v>
+        <v>12.805</v>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>15.09</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1201,18 +1201,18 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.72</v>
+        <v>-0.12</v>
       </c>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="n">
-        <v>1481609355</v>
+        <v>1358151307</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.107</v>
+        <v>0.1081</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>45568.7734872338</v>
+        <v>45460.88529052083</v>
       </c>
       <c r="G16" t="n">
-        <v>140.18</v>
+        <v>165.93</v>
       </c>
       <c r="H16" t="n">
-        <v>129.91</v>
+        <v>145.63</v>
       </c>
       <c r="I16" t="n">
-        <v>15</v>
+        <v>17.94</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1250,18 +1250,18 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1</v>
+        <v>-2.19</v>
       </c>
       <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="n">
-        <v>1885700231</v>
+        <v>1499061783</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1270,19 +1270,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.0187</v>
+        <v>0.0001</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>45828.65147924769</v>
+        <v>45582.73996892361</v>
       </c>
       <c r="G17" t="n">
-        <v>534.86</v>
+        <v>232.2</v>
       </c>
       <c r="H17" t="n">
-        <v>556.39</v>
+        <v>214.18</v>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>0.02</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1299,18 +1299,18 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
-        <v>1744767540</v>
+        <v>1754302454</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.643</v>
+        <v>0.3673</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45751.72316712963</v>
+        <v>45755.88025324074</v>
       </c>
       <c r="G18" t="n">
-        <v>15.55</v>
+        <v>27.17</v>
       </c>
       <c r="H18" t="n">
-        <v>18.17</v>
+        <v>32.28</v>
       </c>
       <c r="I18" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1348,18 +1348,18 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="n">
-        <v>1633116336</v>
+        <v>1923224670</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1368,19 +1368,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0.2583</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45686.83272234954</v>
+        <v>45853.65359685185</v>
       </c>
       <c r="G19" t="n">
-        <v>44.24</v>
+        <v>58.05</v>
       </c>
       <c r="H19" t="n">
-        <v>49.01</v>
+        <v>59.79</v>
       </c>
       <c r="I19" t="n">
-        <v>44.24</v>
+        <v>14.99</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1397,18 +1397,18 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>4.77</v>
+        <v>0.45</v>
       </c>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
-        <v>1824475555</v>
+        <v>1599449649</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1417,19 +1417,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0.4145</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45792.64702015046</v>
+        <v>45663.73562525463</v>
       </c>
       <c r="G20" t="n">
-        <v>21.66</v>
+        <v>24.11</v>
       </c>
       <c r="H20" t="n">
-        <v>21.68</v>
+        <v>19.19</v>
       </c>
       <c r="I20" t="n">
-        <v>21.66</v>
+        <v>9.99</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1446,18 +1446,18 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.02</v>
+        <v>-2.04</v>
       </c>
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="n">
-        <v>1744929368</v>
+        <v>1869077178</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1466,19 +1466,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.0192</v>
+        <v>1</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45751.74500871528</v>
+        <v>45819.67426902778</v>
       </c>
       <c r="G21" t="n">
-        <v>324.48</v>
+        <v>13.285</v>
       </c>
       <c r="H21" t="n">
-        <v>351.65</v>
+        <v>12.805</v>
       </c>
       <c r="I21" t="n">
-        <v>6.23</v>
+        <v>15.31</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1495,18 +1495,18 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.52</v>
+        <v>-0.34</v>
       </c>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="n">
-        <v>1806980482</v>
+        <v>1806978791</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1515,19 +1515,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.2406</v>
+        <v>0.0867</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>45783.83189613426</v>
+        <v>45783.83109655092</v>
       </c>
       <c r="G22" t="n">
-        <v>16.12</v>
+        <v>126.78</v>
       </c>
       <c r="H22" t="n">
-        <v>18.25</v>
+        <v>179.46</v>
       </c>
       <c r="I22" t="n">
-        <v>3.88</v>
+        <v>10.99</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -1544,14 +1544,14 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.51</v>
+        <v>4.57</v>
       </c>
       <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="n">
-        <v>1867193304</v>
+        <v>1796453499</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.1337</v>
+        <v>0.6422</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>45818.8008296412</v>
+        <v>45777.64668229167</v>
       </c>
       <c r="G23" t="n">
-        <v>17.64</v>
+        <v>15.57</v>
       </c>
       <c r="H23" t="n">
-        <v>18.25</v>
+        <v>19.46</v>
       </c>
       <c r="I23" t="n">
-        <v>2.36</v>
+        <v>10</v>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -1593,18 +1593,18 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0.08</v>
+        <v>2.5</v>
       </c>
       <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="n">
-        <v>1554741956</v>
+        <v>1895465445</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0.2987</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45623.74952237269</v>
+        <v>45834.6539484375</v>
       </c>
       <c r="G24" t="n">
-        <v>15.3</v>
+        <v>33.47</v>
       </c>
       <c r="H24" t="n">
-        <v>21.35</v>
+        <v>32.28</v>
       </c>
       <c r="I24" t="n">
-        <v>15.3</v>
+        <v>10</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1642,18 +1642,18 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>6.05</v>
+        <v>-0.36</v>
       </c>
       <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="n">
-        <v>1606697510</v>
+        <v>1712849726</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1662,19 +1662,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.0295</v>
+        <v>0.0861</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>45667.68664726852</v>
+        <v>45734.85489405093</v>
       </c>
       <c r="G25" t="n">
-        <v>507.68</v>
+        <v>127.72</v>
       </c>
       <c r="H25" t="n">
-        <v>556.39</v>
+        <v>179.46</v>
       </c>
       <c r="I25" t="n">
-        <v>14.98</v>
+        <v>11</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -1691,14 +1691,14 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.43</v>
+        <v>4.45</v>
       </c>
       <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="n">
-        <v>1883977044</v>
+        <v>1883977086</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1711,19 +1711,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.345</v>
+        <v>1</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>45827.66105774305</v>
+        <v>45827.66106613426</v>
       </c>
       <c r="G26" t="n">
-        <v>12.88</v>
+        <v>12.875</v>
       </c>
       <c r="H26" t="n">
-        <v>13.095</v>
+        <v>12.805</v>
       </c>
       <c r="I26" t="n">
-        <v>5.13</v>
+        <v>14.86</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -1740,18 +1740,18 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="n">
-        <v>1843470413</v>
+        <v>1867195793</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1760,19 +1760,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.4729</v>
+        <v>0.2339</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>45804.66637251157</v>
+        <v>45818.80180457176</v>
       </c>
       <c r="G27" t="n">
-        <v>42.29</v>
+        <v>42.74</v>
       </c>
       <c r="H27" t="n">
-        <v>44.92</v>
+        <v>43.48</v>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -1789,18 +1789,18 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.24</v>
+        <v>0.17</v>
       </c>
       <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="n">
-        <v>1882278057</v>
+        <v>1867196288</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1809,19 +1809,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.0432</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>45826.76262912037</v>
+        <v>45818.80209099537</v>
       </c>
       <c r="G28" t="n">
-        <v>346.61</v>
+        <v>41.99</v>
       </c>
       <c r="H28" t="n">
-        <v>351.65</v>
+        <v>44.95</v>
       </c>
       <c r="I28" t="n">
-        <v>14.97</v>
+        <v>25</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -1838,18 +1838,18 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0.22</v>
+        <v>1.76</v>
       </c>
       <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
-        <v>1817256440</v>
+        <v>1666459175</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1858,19 +1858,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.2267</v>
+        <v>0.1641</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>45789.64787115741</v>
+        <v>45708.68165298611</v>
       </c>
       <c r="G29" t="n">
-        <v>44.1</v>
+        <v>17.18</v>
       </c>
       <c r="H29" t="n">
-        <v>43.09</v>
+        <v>23.81</v>
       </c>
       <c r="I29" t="n">
-        <v>10</v>
+        <v>2.82</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -1887,18 +1887,18 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.23</v>
+        <v>1.09</v>
       </c>
       <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
-        <v>1582723120</v>
+        <v>1554741956</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1907,19 +1907,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.3755</v>
+        <v>1</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45645.89511640046</v>
+        <v>45623.74952237269</v>
       </c>
       <c r="G30" t="n">
-        <v>53.26</v>
+        <v>15.3</v>
       </c>
       <c r="H30" t="n">
-        <v>59.93</v>
+        <v>23.81</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>15.3</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -1936,18 +1936,18 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.5</v>
+        <v>8.51</v>
       </c>
       <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="n">
-        <v>1830408508</v>
+        <v>1880446963</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1956,16 +1956,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.5793</v>
+        <v>0.0774</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45796.82346997685</v>
+        <v>45825.89330317129</v>
       </c>
       <c r="G31" t="n">
-        <v>17.26</v>
+        <v>129.25</v>
       </c>
       <c r="H31" t="n">
-        <v>18.17</v>
+        <v>127.64</v>
       </c>
       <c r="I31" t="n">
         <v>10</v>
@@ -1985,18 +1985,18 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.53</v>
+        <v>-0.12</v>
       </c>
       <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="n">
-        <v>1712849726</v>
+        <v>1923250768</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2005,19 +2005,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.0861</v>
+        <v>0.87</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45734.85489405093</v>
+        <v>45853.65447396991</v>
       </c>
       <c r="G32" t="n">
-        <v>127.72</v>
+        <v>12.76</v>
       </c>
       <c r="H32" t="n">
-        <v>150.56</v>
+        <v>12.805</v>
       </c>
       <c r="I32" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -2034,18 +2034,18 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.96</v>
+        <v>0.02</v>
       </c>
       <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="n">
-        <v>1680991980</v>
+        <v>1495551484</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2054,19 +2054,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.1066</v>
+        <v>0.1914</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45716.8556621875</v>
+        <v>45580.70648087963</v>
       </c>
       <c r="G33" t="n">
-        <v>178.67</v>
+        <v>135.82</v>
       </c>
       <c r="H33" t="n">
-        <v>220.02</v>
+        <v>134.04</v>
       </c>
       <c r="I33" t="n">
-        <v>19.05</v>
+        <v>26</v>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -2083,18 +2083,18 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>4.41</v>
+        <v>-0.34</v>
       </c>
       <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="n">
-        <v>1811432805</v>
+        <v>1845429956</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2103,19 +2103,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.0856</v>
+        <v>0.6565</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45785.66143211805</v>
+        <v>45805.66180811343</v>
       </c>
       <c r="G34" t="n">
-        <v>128.46</v>
+        <v>13.275</v>
       </c>
       <c r="H34" t="n">
-        <v>150.56</v>
+        <v>12.805</v>
       </c>
       <c r="I34" t="n">
-        <v>11</v>
+        <v>9.91</v>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
@@ -2132,18 +2132,18 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.89</v>
+        <v>-0.08</v>
       </c>
       <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>1582737192</v>
+        <v>1806979127</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2152,19 +2152,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.001</v>
+        <v>0.6361</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>45645.90143930555</v>
+        <v>45783.83125244213</v>
       </c>
       <c r="G35" t="n">
-        <v>524.4299999999999</v>
+        <v>15.72</v>
       </c>
       <c r="H35" t="n">
-        <v>556.39</v>
+        <v>19.19</v>
       </c>
       <c r="I35" t="n">
-        <v>0.52</v>
+        <v>10</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
@@ -2181,18 +2181,18 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.04</v>
+        <v>2.21</v>
       </c>
       <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>1843474191</v>
+        <v>1811475599</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2201,19 +2201,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9372</v>
+        <v>0.7256</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45804.66699503472</v>
+        <v>45785.66972070602</v>
       </c>
       <c r="G36" t="n">
-        <v>21.33</v>
+        <v>12.75</v>
       </c>
       <c r="H36" t="n">
-        <v>21.35</v>
+        <v>12.805</v>
       </c>
       <c r="I36" t="n">
-        <v>19.99</v>
+        <v>10.51</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -2230,18 +2230,18 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.02</v>
+        <v>0.35</v>
       </c>
       <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
-        <v>1744916497</v>
+        <v>1880445013</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2250,19 +2250,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>45751.74231563658</v>
+        <v>45825.8922271412</v>
       </c>
       <c r="G37" t="n">
-        <v>17.54</v>
+        <v>139.86</v>
       </c>
       <c r="H37" t="n">
-        <v>21.35</v>
+        <v>147.68</v>
       </c>
       <c r="I37" t="n">
-        <v>17.54</v>
+        <v>10</v>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
@@ -2279,14 +2279,14 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3.81</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>1635194117</v>
+        <v>1666461140</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2299,19 +2299,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.2479</v>
+        <v>0.2651</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45687.85228493056</v>
+        <v>45708.68207092593</v>
       </c>
       <c r="G38" t="n">
-        <v>40.33</v>
+        <v>37.7</v>
       </c>
       <c r="H38" t="n">
-        <v>34.37</v>
+        <v>32.28</v>
       </c>
       <c r="I38" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
@@ -2328,18 +2328,18 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>-1.48</v>
+        <v>-1.43</v>
       </c>
       <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
-        <v>1381417257</v>
+        <v>1923271589</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2348,19 +2348,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>0.4478</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45484.67877329861</v>
+        <v>45853.65794861111</v>
       </c>
       <c r="G39" t="n">
-        <v>16.374</v>
+        <v>44.66</v>
       </c>
       <c r="H39" t="n">
-        <v>15.194</v>
+        <v>44.95</v>
       </c>
       <c r="I39" t="n">
-        <v>17.9</v>
+        <v>20</v>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -2377,18 +2377,18 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>-0.34</v>
+        <v>0.13</v>
       </c>
       <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="n">
-        <v>1882281884</v>
+        <v>1599455288</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2397,16 +2397,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.2195</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>45826.76479001158</v>
+        <v>45663.73750263889</v>
       </c>
       <c r="G40" t="n">
-        <v>138.84</v>
+        <v>45.55</v>
       </c>
       <c r="H40" t="n">
-        <v>142.64</v>
+        <v>32.28</v>
       </c>
       <c r="I40" t="n">
         <v>10</v>
@@ -2426,18 +2426,18 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.27</v>
+        <v>-2.91</v>
       </c>
       <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="n">
-        <v>1880441651</v>
+        <v>1867461578</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>BAP</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2446,19 +2446,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45825.89055887731</v>
+        <v>45818.90835071759</v>
       </c>
       <c r="G41" t="n">
-        <v>21.21</v>
+        <v>216.54</v>
       </c>
       <c r="H41" t="n">
-        <v>21.68</v>
+        <v>235.66</v>
       </c>
       <c r="I41" t="n">
-        <v>21.21</v>
+        <v>19.99</v>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
@@ -2475,18 +2475,18 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.47</v>
+        <v>1.76</v>
       </c>
       <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="n">
-        <v>1461331124</v>
+        <v>1666459270</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2495,19 +2495,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.3922</v>
+        <v>1</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>45553.65374138889</v>
+        <v>45708.68166530092</v>
       </c>
       <c r="G42" t="n">
-        <v>50.99</v>
+        <v>17.18</v>
       </c>
       <c r="H42" t="n">
-        <v>59.93</v>
+        <v>23.81</v>
       </c>
       <c r="I42" t="n">
-        <v>20</v>
+        <v>17.18</v>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -2524,18 +2524,18 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>3.5</v>
+        <v>6.63</v>
       </c>
       <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="n">
-        <v>1867195417</v>
+        <v>1817264187</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2544,19 +2544,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.1044</v>
+        <v>0.4757</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>45818.80165224537</v>
+        <v>45789.64859377315</v>
       </c>
       <c r="G43" t="n">
-        <v>143.6</v>
+        <v>42.02</v>
       </c>
       <c r="H43" t="n">
-        <v>142.64</v>
+        <v>44.95</v>
       </c>
       <c r="I43" t="n">
-        <v>14.99</v>
+        <v>19.99</v>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -2573,18 +2573,18 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>-0.1</v>
+        <v>1.39</v>
       </c>
       <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
-        <v>1644788775</v>
+        <v>1566610015</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2593,19 +2593,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.9385</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45693.85093391204</v>
+        <v>45632.87667083334</v>
       </c>
       <c r="G44" t="n">
-        <v>144.94</v>
+        <v>21.31</v>
       </c>
       <c r="H44" t="n">
-        <v>131.06</v>
+        <v>19.19</v>
       </c>
       <c r="I44" t="n">
-        <v>10.99</v>
+        <v>20</v>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -2622,18 +2622,18 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>-1.06</v>
+        <v>-1.99</v>
       </c>
       <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>1754304266</v>
+        <v>1701098878</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2642,19 +2642,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.7137</v>
+        <v>0.0383</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>45755.88055112268</v>
+        <v>45727.87167594907</v>
       </c>
       <c r="G45" t="n">
-        <v>14</v>
+        <v>139.41</v>
       </c>
       <c r="H45" t="n">
-        <v>18.17</v>
+        <v>179.46</v>
       </c>
       <c r="I45" t="n">
-        <v>9.99</v>
+        <v>5.34</v>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -2671,18 +2671,18 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.98</v>
+        <v>1.53</v>
       </c>
       <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>1559802942</v>
+        <v>1888700382</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2691,19 +2691,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.2585</v>
+        <v>1</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>45628.85929152778</v>
+        <v>45831.65144708334</v>
       </c>
       <c r="G46" t="n">
-        <v>77.34999999999999</v>
+        <v>47.58</v>
       </c>
       <c r="H46" t="n">
-        <v>71.42</v>
+        <v>51.22</v>
       </c>
       <c r="I46" t="n">
-        <v>19.99</v>
+        <v>47.58</v>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -2720,14 +2720,14 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>-1.53</v>
+        <v>3.64</v>
       </c>
       <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>1880446729</v>
+        <v>1867197360</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2740,19 +2740,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.0772</v>
+        <v>0.0765</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>45825.89315055555</v>
+        <v>45818.80265583334</v>
       </c>
       <c r="G47" t="n">
-        <v>129.62</v>
+        <v>131.96</v>
       </c>
       <c r="H47" t="n">
-        <v>131.06</v>
+        <v>145.63</v>
       </c>
       <c r="I47" t="n">
-        <v>10.01</v>
+        <v>10.09</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -2769,18 +2769,18 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0.11</v>
+        <v>1.05</v>
       </c>
       <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>1621495187</v>
+        <v>1712850989</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2789,19 +2789,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.2318</v>
+        <v>0.0282</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>45678.83178196759</v>
+        <v>45734.85576775463</v>
       </c>
       <c r="G48" t="n">
-        <v>43.27</v>
+        <v>160.64</v>
       </c>
       <c r="H48" t="n">
-        <v>34.37</v>
+        <v>190.27</v>
       </c>
       <c r="I48" t="n">
-        <v>10.03</v>
+        <v>4.53</v>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -2818,18 +2818,18 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>-2.06</v>
+        <v>0.84</v>
       </c>
       <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
-        <v>1867194722</v>
+        <v>1563288050</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2838,19 +2838,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0.0626</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45818.80135700232</v>
+        <v>45630.85583428241</v>
       </c>
       <c r="G49" t="n">
-        <v>21.27</v>
+        <v>159.74</v>
       </c>
       <c r="H49" t="n">
-        <v>21.68</v>
+        <v>145.63</v>
       </c>
       <c r="I49" t="n">
-        <v>21.27</v>
+        <v>10</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
@@ -2867,18 +2867,18 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0.41</v>
+        <v>-0.88</v>
       </c>
       <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
-        <v>1806979127</v>
+        <v>1744916497</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.6361</v>
+        <v>1</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>45783.83125244213</v>
+        <v>45751.74231563658</v>
       </c>
       <c r="G50" t="n">
-        <v>15.72</v>
+        <v>17.54</v>
       </c>
       <c r="H50" t="n">
-        <v>18.17</v>
+        <v>23.81</v>
       </c>
       <c r="I50" t="n">
-        <v>10</v>
+        <v>17.54</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -2916,18 +2916,18 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1.56</v>
+        <v>6.27</v>
       </c>
       <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>1776193271</v>
+        <v>1845431561</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2936,19 +2936,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.6724</v>
+        <v>0.0179</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>45764.85451520833</v>
+        <v>45805.66210755787</v>
       </c>
       <c r="G51" t="n">
-        <v>14.87</v>
+        <v>30.57</v>
       </c>
       <c r="H51" t="n">
-        <v>18.25</v>
+        <v>40.39</v>
       </c>
       <c r="I51" t="n">
-        <v>10</v>
+        <v>0.55</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -2965,18 +2965,18 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.27</v>
+        <v>0.17</v>
       </c>
       <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
-        <v>1594315903</v>
+        <v>1648737122</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BATT.AS</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2985,19 +2985,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>45659.42644752315</v>
+        <v>45695.85619950231</v>
       </c>
       <c r="G52" t="n">
-        <v>16.425</v>
+        <v>408.33</v>
       </c>
       <c r="H52" t="n">
-        <v>15.194</v>
+        <v>505.96</v>
       </c>
       <c r="I52" t="n">
-        <v>17.11</v>
+        <v>0.41</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
@@ -3014,18 +3014,18 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
       <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="n">
-        <v>1680993370</v>
+        <v>1923246263</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3037,16 +3037,16 @@
         <v>1</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>45716.85638861111</v>
+        <v>45853.6538128125</v>
       </c>
       <c r="G53" t="n">
-        <v>44.49</v>
+        <v>21.17</v>
       </c>
       <c r="H53" t="n">
-        <v>49.01</v>
+        <v>20.79</v>
       </c>
       <c r="I53" t="n">
-        <v>44.49</v>
+        <v>21.17</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
@@ -3063,18 +3063,18 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>4.52</v>
+        <v>-0.38</v>
       </c>
       <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="n">
-        <v>1701100481</v>
+        <v>1621495187</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3083,19 +3083,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.0873</v>
+        <v>0.2318</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>45727.87214378472</v>
+        <v>45678.83178196759</v>
       </c>
       <c r="G54" t="n">
-        <v>171.67</v>
+        <v>43.27</v>
       </c>
       <c r="H54" t="n">
-        <v>220.02</v>
+        <v>32.28</v>
       </c>
       <c r="I54" t="n">
-        <v>14.99</v>
+        <v>10.03</v>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
@@ -3112,18 +3112,18 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>4.22</v>
+        <v>-2.55</v>
       </c>
       <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="n">
-        <v>1867197360</v>
+        <v>1867462173</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3132,19 +3132,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.0765</v>
+        <v>0.1284</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>45818.80265583334</v>
+        <v>45818.90866184028</v>
       </c>
       <c r="G55" t="n">
-        <v>131.96</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="H55" t="n">
-        <v>131.06</v>
+        <v>95.97</v>
       </c>
       <c r="I55" t="n">
-        <v>10.09</v>
+        <v>10.01</v>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
@@ -3161,18 +3161,18 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>-0.06</v>
+        <v>2.31</v>
       </c>
       <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="n">
-        <v>1806977521</v>
+        <v>1811475646</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3181,19 +3181,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.3367</v>
+        <v>1</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>45783.8305750463</v>
+        <v>45785.66973634259</v>
       </c>
       <c r="G56" t="n">
-        <v>29.7</v>
+        <v>12.75</v>
       </c>
       <c r="H56" t="n">
-        <v>34.37</v>
+        <v>12.805</v>
       </c>
       <c r="I56" t="n">
-        <v>10</v>
+        <v>14.49</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
@@ -3210,18 +3210,18 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>1.57</v>
+        <v>0.48</v>
       </c>
       <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="n">
-        <v>1867462173</v>
+        <v>1644789287</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3230,19 +3230,19 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.1284</v>
+        <v>0.0813</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45818.90866184028</v>
+        <v>45693.85123056713</v>
       </c>
       <c r="G57" t="n">
-        <v>77.93000000000001</v>
+        <v>129.08</v>
       </c>
       <c r="H57" t="n">
-        <v>81.15000000000001</v>
+        <v>127.64</v>
       </c>
       <c r="I57" t="n">
-        <v>10.01</v>
+        <v>10.49</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
@@ -3259,18 +3259,18 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>0.41</v>
+        <v>-0.11</v>
       </c>
       <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
-        <v>1744930699</v>
+        <v>1928218937</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3282,16 +3282,16 @@
         <v>1</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45751.74534789352</v>
+        <v>45855.75970359953</v>
       </c>
       <c r="G58" t="n">
-        <v>74.13</v>
+        <v>20.24</v>
       </c>
       <c r="H58" t="n">
-        <v>73.28</v>
+        <v>20.79</v>
       </c>
       <c r="I58" t="n">
-        <v>74.13</v>
+        <v>20.24</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
@@ -3308,18 +3308,18 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>-0.85</v>
+        <v>0.55</v>
       </c>
       <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="n">
-        <v>1648733962</v>
+        <v>1701100027</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3328,19 +3328,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.081</v>
+        <v>0.7812</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>45695.85463682871</v>
+        <v>45727.87202070602</v>
       </c>
       <c r="G59" t="n">
-        <v>129.56</v>
+        <v>19.2</v>
       </c>
       <c r="H59" t="n">
-        <v>129.91</v>
+        <v>19.19</v>
       </c>
       <c r="I59" t="n">
-        <v>10.49</v>
+        <v>15</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
@@ -3357,18 +3357,18 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="n">
-        <v>1378901781</v>
+        <v>1882281884</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BOTZ.L</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3377,19 +3377,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45482.71294556713</v>
+        <v>45826.76479001158</v>
       </c>
       <c r="G60" t="n">
-        <v>20.58</v>
+        <v>138.84</v>
       </c>
       <c r="H60" t="n">
-        <v>20.58</v>
+        <v>147.68</v>
       </c>
       <c r="I60" t="n">
-        <v>20.58</v>
+        <v>10</v>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
@@ -3406,18 +3406,18 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="n">
-        <v>1599449649</v>
+        <v>1727574394</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3426,19 +3426,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.4145</v>
+        <v>1</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>45663.73562525463</v>
+        <v>45743.76658678241</v>
       </c>
       <c r="G61" t="n">
-        <v>24.11</v>
+        <v>21.13</v>
       </c>
       <c r="H61" t="n">
-        <v>18.17</v>
+        <v>20.79</v>
       </c>
       <c r="I61" t="n">
-        <v>9.99</v>
+        <v>21.13</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
@@ -3455,18 +3455,18 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>-2.46</v>
+        <v>-0.34</v>
       </c>
       <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="n">
-        <v>1845429956</v>
+        <v>1414752069</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3475,19 +3475,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.6565</v>
+        <v>0.1933</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>45805.66180811343</v>
+        <v>45511.86049193287</v>
       </c>
       <c r="G62" t="n">
-        <v>13.275</v>
+        <v>77.53</v>
       </c>
       <c r="H62" t="n">
-        <v>13.095</v>
+        <v>72.84</v>
       </c>
       <c r="I62" t="n">
-        <v>9.91</v>
+        <v>14.99</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
@@ -3504,18 +3504,18 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>0.03</v>
+        <v>-0.91</v>
       </c>
       <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="n">
-        <v>1883977086</v>
+        <v>1830408508</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3524,19 +3524,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>0.5793</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>45827.66106613426</v>
+        <v>45796.82346997685</v>
       </c>
       <c r="G63" t="n">
-        <v>12.875</v>
+        <v>17.26</v>
       </c>
       <c r="H63" t="n">
-        <v>13.095</v>
+        <v>19.19</v>
       </c>
       <c r="I63" t="n">
-        <v>14.86</v>
+        <v>10</v>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
@@ -3553,14 +3553,14 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>0.28</v>
+        <v>1.12</v>
       </c>
       <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="n">
-        <v>1648735305</v>
+        <v>1582714896</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -3573,19 +3573,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.4576</v>
+        <v>0.4847</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>45695.85530675926</v>
+        <v>45645.89066263889</v>
       </c>
       <c r="G64" t="n">
-        <v>21.85</v>
+        <v>20.62</v>
       </c>
       <c r="H64" t="n">
-        <v>18.17</v>
+        <v>19.19</v>
       </c>
       <c r="I64" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
@@ -3602,18 +3602,18 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>-1.69</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="n">
-        <v>1727591551</v>
+        <v>1880441651</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3625,16 +3625,16 @@
         <v>1</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>45743.77389555555</v>
+        <v>45825.89055887731</v>
       </c>
       <c r="G65" t="n">
-        <v>72.87</v>
+        <v>21.21</v>
       </c>
       <c r="H65" t="n">
-        <v>73.28</v>
+        <v>20.79</v>
       </c>
       <c r="I65" t="n">
-        <v>72.87</v>
+        <v>21.21</v>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
@@ -3651,18 +3651,18 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>0.41</v>
+        <v>-0.42</v>
       </c>
       <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="n">
-        <v>1559803221</v>
+        <v>1680994777</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3671,19 +3671,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.092</v>
+        <v>0.7278</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>45628.85951927083</v>
+        <v>45716.85705375</v>
       </c>
       <c r="G66" t="n">
-        <v>162.85</v>
+        <v>20.6</v>
       </c>
       <c r="H66" t="n">
-        <v>131.06</v>
+        <v>19.19</v>
       </c>
       <c r="I66" t="n">
-        <v>14.98</v>
+        <v>14.99</v>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
@@ -3700,18 +3700,18 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>-2.92</v>
+        <v>-1.02</v>
       </c>
       <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="n">
-        <v>1824476420</v>
+        <v>1744767540</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3720,19 +3720,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.1548</v>
+        <v>0.643</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>45792.64714148148</v>
+        <v>45751.72316712963</v>
       </c>
       <c r="G67" t="n">
-        <v>129.17</v>
+        <v>15.55</v>
       </c>
       <c r="H67" t="n">
-        <v>131.06</v>
+        <v>19.19</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
@@ -3749,18 +3749,18 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>0.29</v>
+        <v>2.34</v>
       </c>
       <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="n">
-        <v>1845431561</v>
+        <v>1843477152</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3769,19 +3769,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.0179</v>
+        <v>0.1198</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>45805.66210755787</v>
+        <v>45804.66724922453</v>
       </c>
       <c r="G68" t="n">
-        <v>30.57</v>
+        <v>17.86</v>
       </c>
       <c r="H68" t="n">
-        <v>33.28</v>
+        <v>19.46</v>
       </c>
       <c r="I68" t="n">
-        <v>0.55</v>
+        <v>2.14</v>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
@@ -3798,18 +3798,18 @@
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>0.05</v>
+        <v>0.19</v>
       </c>
       <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="n">
-        <v>1806978791</v>
+        <v>1559802942</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3818,19 +3818,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.0867</v>
+        <v>0.2585</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>45783.83109655092</v>
+        <v>45628.85929152778</v>
       </c>
       <c r="G69" t="n">
-        <v>126.78</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>150.56</v>
+        <v>72.84</v>
       </c>
       <c r="I69" t="n">
-        <v>10.99</v>
+        <v>19.99</v>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
@@ -3847,18 +3847,18 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>2.06</v>
+        <v>-1.16</v>
       </c>
       <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="n">
-        <v>1517510856</v>
+        <v>1653137218</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3867,16 +3867,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.0602</v>
+        <v>0.277</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>45597.61014849537</v>
+        <v>45699.85152199074</v>
       </c>
       <c r="G70" t="n">
-        <v>166.03</v>
+        <v>36.1</v>
       </c>
       <c r="H70" t="n">
-        <v>131.06</v>
+        <v>32.28</v>
       </c>
       <c r="I70" t="n">
         <v>10</v>
@@ -3896,18 +3896,18 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>-2.11</v>
+        <v>-1.06</v>
       </c>
       <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="n">
-        <v>1358151307</v>
+        <v>1883977044</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3916,19 +3916,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.1081</v>
+        <v>0.345</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>45460.88529052083</v>
+        <v>45827.66105774305</v>
       </c>
       <c r="G71" t="n">
-        <v>165.93</v>
+        <v>12.88</v>
       </c>
       <c r="H71" t="n">
-        <v>131.06</v>
+        <v>12.805</v>
       </c>
       <c r="I71" t="n">
-        <v>17.94</v>
+        <v>5.13</v>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
@@ -3945,18 +3945,18 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>-3.76</v>
+        <v>0.03</v>
       </c>
       <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="n">
-        <v>1727563010</v>
+        <v>1923258249</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3968,16 +3968,16 @@
         <v>1</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>45743.76106726852</v>
+        <v>45853.65576626157</v>
       </c>
       <c r="G72" t="n">
-        <v>46.11</v>
+        <v>19.41</v>
       </c>
       <c r="H72" t="n">
-        <v>49.01</v>
+        <v>19.19</v>
       </c>
       <c r="I72" t="n">
-        <v>46.11</v>
+        <v>19.41</v>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -3994,18 +3994,18 @@
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>2.9</v>
+        <v>-0.22</v>
       </c>
       <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="n">
-        <v>1824482557</v>
+        <v>1635194117</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4014,19 +4014,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.2641</v>
+        <v>0.2479</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45792.64805195602</v>
+        <v>45687.85228493056</v>
       </c>
       <c r="G73" t="n">
-        <v>56.78</v>
+        <v>40.33</v>
       </c>
       <c r="H73" t="n">
-        <v>59.93</v>
+        <v>32.28</v>
       </c>
       <c r="I73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
@@ -4043,18 +4043,18 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>0.83</v>
+        <v>-2</v>
       </c>
       <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="n">
-        <v>1845429980</v>
+        <v>1843477272</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4066,16 +4066,16 @@
         <v>1</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45805.66181400463</v>
+        <v>45804.66725678241</v>
       </c>
       <c r="G74" t="n">
-        <v>13.27</v>
+        <v>17.86</v>
       </c>
       <c r="H74" t="n">
-        <v>13.095</v>
+        <v>19.46</v>
       </c>
       <c r="I74" t="n">
-        <v>15.09</v>
+        <v>17.86</v>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
@@ -4092,18 +4092,18 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>0.05</v>
+        <v>1.6</v>
       </c>
       <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="n">
-        <v>1666461140</v>
+        <v>1744929368</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4112,19 +4112,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.2651</v>
+        <v>0.0192</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>45708.68207092593</v>
+        <v>45751.74500871528</v>
       </c>
       <c r="G75" t="n">
-        <v>37.7</v>
+        <v>324.48</v>
       </c>
       <c r="H75" t="n">
-        <v>34.37</v>
+        <v>355.29</v>
       </c>
       <c r="I75" t="n">
-        <v>9.99</v>
+        <v>6.23</v>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
@@ -4141,18 +4141,18 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>-0.88</v>
+        <v>0.59</v>
       </c>
       <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="n">
-        <v>1631475148</v>
+        <v>1662993636</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4161,19 +4161,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.2592</v>
+        <v>1</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>45685.83625201389</v>
+        <v>45706.87026833333</v>
       </c>
       <c r="G76" t="n">
-        <v>38.58</v>
+        <v>20.65</v>
       </c>
       <c r="H76" t="n">
-        <v>34.37</v>
+        <v>20.79</v>
       </c>
       <c r="I76" t="n">
-        <v>10</v>
+        <v>20.65</v>
       </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
@@ -4190,18 +4190,18 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>-1.09</v>
+        <v>0.14</v>
       </c>
       <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="n">
-        <v>1554741910</v>
+        <v>1895460914</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4210,19 +4210,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.3495</v>
+        <v>0.0781</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>45623.74951116898</v>
+        <v>45834.65311391203</v>
       </c>
       <c r="G77" t="n">
-        <v>15.3</v>
+        <v>128.09</v>
       </c>
       <c r="H77" t="n">
-        <v>21.35</v>
+        <v>127.64</v>
       </c>
       <c r="I77" t="n">
-        <v>5.35</v>
+        <v>10</v>
       </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
@@ -4239,18 +4239,18 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>2.11</v>
+        <v>-0.03</v>
       </c>
       <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="n">
-        <v>1599455288</v>
+        <v>1824476420</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4259,19 +4259,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.2195</v>
+        <v>0.1548</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>45663.73750263889</v>
+        <v>45792.64714148148</v>
       </c>
       <c r="G78" t="n">
-        <v>45.55</v>
+        <v>129.17</v>
       </c>
       <c r="H78" t="n">
-        <v>34.37</v>
+        <v>145.63</v>
       </c>
       <c r="I78" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
@@ -4288,18 +4288,18 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>-2.46</v>
+        <v>2.54</v>
       </c>
       <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="n">
-        <v>1869077157</v>
+        <v>1880443947</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4308,19 +4308,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.3061</v>
+        <v>0.1047</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>45819.6742621412</v>
+        <v>45825.891695625</v>
       </c>
       <c r="G79" t="n">
-        <v>13.285</v>
+        <v>142.99</v>
       </c>
       <c r="H79" t="n">
-        <v>13.095</v>
+        <v>179.46</v>
       </c>
       <c r="I79" t="n">
-        <v>4.69</v>
+        <v>14.97</v>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
@@ -4337,18 +4337,18 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>-0.06</v>
+        <v>3.82</v>
       </c>
       <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="n">
-        <v>1880445013</v>
+        <v>1867193336</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4357,19 +4357,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.07149999999999999</v>
+        <v>1</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>45825.8922271412</v>
+        <v>45818.80084483796</v>
       </c>
       <c r="G80" t="n">
-        <v>139.86</v>
+        <v>17.64</v>
       </c>
       <c r="H80" t="n">
-        <v>142.64</v>
+        <v>19.46</v>
       </c>
       <c r="I80" t="n">
-        <v>10</v>
+        <v>17.64</v>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
@@ -4386,18 +4386,18 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>0.2</v>
+        <v>1.82</v>
       </c>
       <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="n">
-        <v>1653137218</v>
+        <v>1450043624</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4406,19 +4406,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.277</v>
+        <v>0.0231</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>45699.85152199074</v>
+        <v>45544.65163525463</v>
       </c>
       <c r="G81" t="n">
-        <v>36.1</v>
+        <v>147.48</v>
       </c>
       <c r="H81" t="n">
-        <v>34.37</v>
+        <v>127.64</v>
       </c>
       <c r="I81" t="n">
-        <v>10</v>
+        <v>3.41</v>
       </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
@@ -4435,18 +4435,18 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>-0.48</v>
+        <v>-0.46</v>
       </c>
       <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="n">
-        <v>1563288050</v>
+        <v>1642762235</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4455,19 +4455,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.0626</v>
+        <v>0.1572</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>45630.85583428241</v>
+        <v>45692.86612574074</v>
       </c>
       <c r="G82" t="n">
-        <v>159.74</v>
+        <v>127.16</v>
       </c>
       <c r="H82" t="n">
-        <v>131.06</v>
+        <v>134.04</v>
       </c>
       <c r="I82" t="n">
-        <v>10</v>
+        <v>19.99</v>
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
@@ -4484,18 +4484,18 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>-1.8</v>
+        <v>1.08</v>
       </c>
       <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="n">
-        <v>1701098878</v>
+        <v>1559803221</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4504,19 +4504,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.0383</v>
+        <v>0.092</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>45727.87167594907</v>
+        <v>45628.85951927083</v>
       </c>
       <c r="G83" t="n">
-        <v>139.41</v>
+        <v>162.85</v>
       </c>
       <c r="H83" t="n">
-        <v>150.56</v>
+        <v>145.63</v>
       </c>
       <c r="I83" t="n">
-        <v>5.34</v>
+        <v>14.98</v>
       </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
@@ -4533,18 +4533,18 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>0.43</v>
+        <v>-1.58</v>
       </c>
       <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="n">
-        <v>1843477272</v>
+        <v>1830410729</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4553,19 +4553,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1</v>
+        <v>0.1091</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>45804.66725678241</v>
+        <v>45796.82476561343</v>
       </c>
       <c r="G84" t="n">
-        <v>17.86</v>
+        <v>33.66</v>
       </c>
       <c r="H84" t="n">
-        <v>18.25</v>
+        <v>36.8</v>
       </c>
       <c r="I84" t="n">
-        <v>17.86</v>
+        <v>3.67</v>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
@@ -4582,18 +4582,18 @@
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>0.39</v>
+        <v>0.34</v>
       </c>
       <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="n">
-        <v>1666459175</v>
+        <v>1843469729</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4602,19 +4602,19 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.1641</v>
+        <v>0.0956</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>45708.68165298611</v>
+        <v>45804.66615450232</v>
       </c>
       <c r="G85" t="n">
-        <v>17.18</v>
+        <v>156.9</v>
       </c>
       <c r="H85" t="n">
-        <v>21.35</v>
+        <v>179.46</v>
       </c>
       <c r="I85" t="n">
-        <v>2.82</v>
+        <v>15</v>
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
@@ -4631,18 +4631,18 @@
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>0.68</v>
+        <v>2.16</v>
       </c>
       <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="n">
-        <v>1843468958</v>
+        <v>1481609355</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4651,16 +4651,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.2208</v>
+        <v>0.107</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>45804.66597149306</v>
+        <v>45568.7734872338</v>
       </c>
       <c r="G86" t="n">
-        <v>67.93000000000001</v>
+        <v>140.18</v>
       </c>
       <c r="H86" t="n">
-        <v>71.42</v>
+        <v>127.64</v>
       </c>
       <c r="I86" t="n">
         <v>15</v>
@@ -4680,18 +4680,18 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>0.77</v>
+        <v>-1.34</v>
       </c>
       <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="n">
-        <v>1744916452</v>
+        <v>1727563010</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4700,19 +4700,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.4245</v>
+        <v>1</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>45751.74230173611</v>
+        <v>45743.76106726852</v>
       </c>
       <c r="G87" t="n">
-        <v>17.54</v>
+        <v>46.11</v>
       </c>
       <c r="H87" t="n">
-        <v>21.35</v>
+        <v>51.22</v>
       </c>
       <c r="I87" t="n">
-        <v>7.45</v>
+        <v>46.11</v>
       </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
@@ -4729,18 +4729,18 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>1.61</v>
+        <v>5.11</v>
       </c>
       <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="n">
-        <v>1662993636</v>
+        <v>1806980482</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4749,19 +4749,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>0.2406</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>45706.87026833333</v>
+        <v>45783.83189613426</v>
       </c>
       <c r="G88" t="n">
-        <v>20.65</v>
+        <v>16.12</v>
       </c>
       <c r="H88" t="n">
-        <v>21.68</v>
+        <v>19.46</v>
       </c>
       <c r="I88" t="n">
-        <v>20.65</v>
+        <v>3.88</v>
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
@@ -4778,18 +4778,18 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>1.03</v>
+        <v>0.8</v>
       </c>
       <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="n">
-        <v>1414752069</v>
+        <v>1644796307</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4798,19 +4798,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.1933</v>
+        <v>1</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>45511.86049193287</v>
+        <v>45693.85501710648</v>
       </c>
       <c r="G89" t="n">
-        <v>77.53</v>
+        <v>20.36</v>
       </c>
       <c r="H89" t="n">
-        <v>71.42</v>
+        <v>20.79</v>
       </c>
       <c r="I89" t="n">
-        <v>14.99</v>
+        <v>20.36</v>
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
@@ -4827,18 +4827,18 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>-1.18</v>
+        <v>0.43</v>
       </c>
       <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="n">
-        <v>1499061783</v>
+        <v>1880446729</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4847,19 +4847,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.0001</v>
+        <v>0.0772</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>45582.73996892361</v>
+        <v>45825.89315055555</v>
       </c>
       <c r="G90" t="n">
-        <v>232.2</v>
+        <v>129.62</v>
       </c>
       <c r="H90" t="n">
-        <v>200.31</v>
+        <v>145.63</v>
       </c>
       <c r="I90" t="n">
-        <v>0.02</v>
+        <v>10.01</v>
       </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
@@ -4876,18 +4876,18 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="n">
-        <v>1662995258</v>
+        <v>1923258184</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4896,19 +4896,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.2943</v>
+        <v>0.0298</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>45706.87121422453</v>
+        <v>45853.6557568287</v>
       </c>
       <c r="G91" t="n">
-        <v>67.97</v>
+        <v>19.43</v>
       </c>
       <c r="H91" t="n">
-        <v>71.42</v>
+        <v>19.19</v>
       </c>
       <c r="I91" t="n">
-        <v>20</v>
+        <v>0.58</v>
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
@@ -4925,18 +4925,18 @@
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>1.02</v>
+        <v>-0.01</v>
       </c>
       <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="n">
-        <v>1880443947</v>
+        <v>1806980496</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4945,19 +4945,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.1047</v>
+        <v>1</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>45825.891695625</v>
+        <v>45783.83190503472</v>
       </c>
       <c r="G92" t="n">
-        <v>142.99</v>
+        <v>16.12</v>
       </c>
       <c r="H92" t="n">
-        <v>150.56</v>
+        <v>19.46</v>
       </c>
       <c r="I92" t="n">
-        <v>14.97</v>
+        <v>16.12</v>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
@@ -4974,18 +4974,18 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>0.79</v>
+        <v>3.34</v>
       </c>
       <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="n">
-        <v>1867461578</v>
+        <v>1631475148</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BAP</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4994,19 +4994,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.2592</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>45818.90835071759</v>
+        <v>45685.83625201389</v>
       </c>
       <c r="G93" t="n">
-        <v>216.54</v>
+        <v>38.58</v>
       </c>
       <c r="H93" t="n">
-        <v>217.11</v>
+        <v>32.28</v>
       </c>
       <c r="I93" t="n">
-        <v>19.99</v>
+        <v>10</v>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
@@ -5023,18 +5023,18 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>0.05</v>
+        <v>-1.63</v>
       </c>
       <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="n">
-        <v>1648737122</v>
+        <v>1843468958</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5043,19 +5043,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.001</v>
+        <v>0.2208</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>45695.85619950231</v>
+        <v>45804.66597149306</v>
       </c>
       <c r="G94" t="n">
-        <v>408.33</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="H94" t="n">
-        <v>490.22</v>
+        <v>72.84</v>
       </c>
       <c r="I94" t="n">
-        <v>0.41</v>
+        <v>15</v>
       </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
@@ -5072,18 +5072,18 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>0.08</v>
+        <v>1.08</v>
       </c>
       <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="n">
-        <v>1754302454</v>
+        <v>1666451221</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5092,19 +5092,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.3673</v>
+        <v>0.0001</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>45755.88025324074</v>
+        <v>45708.68022634259</v>
       </c>
       <c r="G95" t="n">
-        <v>27.17</v>
+        <v>43</v>
       </c>
       <c r="H95" t="n">
-        <v>34.37</v>
+        <v>43.48</v>
       </c>
       <c r="I95" t="n">
-        <v>9.98</v>
+        <v>0</v>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -5121,18 +5121,18 @@
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="n">
-        <v>1599448103</v>
+        <v>1776193271</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5141,19 +5141,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.2839</v>
+        <v>0.6724</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>45663.73506711805</v>
+        <v>45764.85451520833</v>
       </c>
       <c r="G96" t="n">
-        <v>52.83</v>
+        <v>14.87</v>
       </c>
       <c r="H96" t="n">
-        <v>59.93</v>
+        <v>19.46</v>
       </c>
       <c r="I96" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
@@ -5170,18 +5170,18 @@
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>2.01</v>
+        <v>3.08</v>
       </c>
       <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="n">
-        <v>1599431096</v>
+        <v>1824482557</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5190,19 +5190,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.1013</v>
+        <v>0.2641</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>45663.73014731482</v>
+        <v>45792.64805195602</v>
       </c>
       <c r="G97" t="n">
-        <v>148.02</v>
+        <v>56.78</v>
       </c>
       <c r="H97" t="n">
-        <v>131.06</v>
+        <v>59.79</v>
       </c>
       <c r="I97" t="n">
-        <v>14.99</v>
+        <v>15</v>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
@@ -5219,18 +5219,18 @@
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>-1.71</v>
+        <v>0.79</v>
       </c>
       <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="n">
-        <v>1843477152</v>
+        <v>1754304266</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5239,19 +5239,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.1198</v>
+        <v>0.7137</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>45804.66724922453</v>
+        <v>45755.88055112268</v>
       </c>
       <c r="G98" t="n">
-        <v>17.86</v>
+        <v>14</v>
       </c>
       <c r="H98" t="n">
-        <v>18.25</v>
+        <v>19.19</v>
       </c>
       <c r="I98" t="n">
-        <v>2.14</v>
+        <v>9.99</v>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
@@ -5268,18 +5268,18 @@
         <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>0.05</v>
+        <v>3.71</v>
       </c>
       <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="n">
-        <v>1817264187</v>
+        <v>1867195417</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5288,19 +5288,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.4757</v>
+        <v>0.1044</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>45789.64859377315</v>
+        <v>45818.80165224537</v>
       </c>
       <c r="G99" t="n">
-        <v>42.02</v>
+        <v>143.6</v>
       </c>
       <c r="H99" t="n">
-        <v>44.92</v>
+        <v>147.68</v>
       </c>
       <c r="I99" t="n">
-        <v>19.99</v>
+        <v>14.99</v>
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
@@ -5317,18 +5317,18 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>1.38</v>
+        <v>0.43</v>
       </c>
       <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="n">
-        <v>1582714896</v>
+        <v>1843470413</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5337,19 +5337,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.4847</v>
+        <v>0.4729</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>45645.89066263889</v>
+        <v>45804.66637251157</v>
       </c>
       <c r="G100" t="n">
-        <v>20.62</v>
+        <v>42.29</v>
       </c>
       <c r="H100" t="n">
-        <v>18.17</v>
+        <v>44.95</v>
       </c>
       <c r="I100" t="n">
-        <v>9.99</v>
+        <v>20</v>
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
@@ -5366,18 +5366,18 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>-1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="n">
-        <v>1811475599</v>
+        <v>1559803984</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5386,19 +5386,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.7256</v>
+        <v>0.1076</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>45785.66972070602</v>
+        <v>45628.86014383102</v>
       </c>
       <c r="G101" t="n">
-        <v>12.75</v>
+        <v>139.4</v>
       </c>
       <c r="H101" t="n">
-        <v>13.095</v>
+        <v>127.64</v>
       </c>
       <c r="I101" t="n">
-        <v>10.51</v>
+        <v>15</v>
       </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -5415,18 +5415,18 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>0.47</v>
+        <v>-1.27</v>
       </c>
       <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="n">
-        <v>1701100027</v>
+        <v>1648733962</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5435,19 +5435,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.7812</v>
+        <v>0.081</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>45727.87202070602</v>
+        <v>45695.85463682871</v>
       </c>
       <c r="G102" t="n">
-        <v>19.2</v>
+        <v>129.56</v>
       </c>
       <c r="H102" t="n">
-        <v>18.17</v>
+        <v>127.64</v>
       </c>
       <c r="I102" t="n">
-        <v>15</v>
+        <v>10.49</v>
       </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
@@ -5464,18 +5464,18 @@
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.15</v>
       </c>
       <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="n">
-        <v>1830410729</v>
+        <v>1882283184</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5484,19 +5484,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.1091</v>
+        <v>0.4835</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>45796.82476561343</v>
+        <v>45826.76569390047</v>
       </c>
       <c r="G103" t="n">
-        <v>33.66</v>
+        <v>20.69</v>
       </c>
       <c r="H103" t="n">
-        <v>38.46</v>
+        <v>19.19</v>
       </c>
       <c r="I103" t="n">
-        <v>3.67</v>
+        <v>10</v>
       </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
@@ -5513,18 +5513,18 @@
         <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>0.53</v>
+        <v>-0.72</v>
       </c>
       <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="n">
-        <v>1867458993</v>
+        <v>1923259795</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5533,19 +5533,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.3417</v>
+        <v>0.4424</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>45818.90699613426</v>
+        <v>45853.65609353009</v>
       </c>
       <c r="G104" t="n">
-        <v>58.53</v>
+        <v>22.59</v>
       </c>
       <c r="H104" t="n">
-        <v>59.93</v>
+        <v>23.81</v>
       </c>
       <c r="I104" t="n">
-        <v>20</v>
+        <v>9.99</v>
       </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
@@ -5562,18 +5562,18 @@
         <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="n">
-        <v>1888700382</v>
+        <v>1744879358</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5582,19 +5582,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1</v>
+        <v>0.2701</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>45831.65144708334</v>
+        <v>45751.73925940973</v>
       </c>
       <c r="G105" t="n">
-        <v>47.58</v>
+        <v>148.09</v>
       </c>
       <c r="H105" t="n">
-        <v>49.01</v>
+        <v>240.32</v>
       </c>
       <c r="I105" t="n">
-        <v>47.58</v>
+        <v>40</v>
       </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
@@ -5611,18 +5611,18 @@
         <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>1.43</v>
+        <v>24.91</v>
       </c>
       <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="n">
-        <v>1811475646</v>
+        <v>1517510856</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5631,19 +5631,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1</v>
+        <v>0.0602</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>45785.66973634259</v>
+        <v>45597.61014849537</v>
       </c>
       <c r="G106" t="n">
-        <v>12.75</v>
+        <v>166.03</v>
       </c>
       <c r="H106" t="n">
-        <v>13.095</v>
+        <v>145.63</v>
       </c>
       <c r="I106" t="n">
-        <v>14.49</v>
+        <v>10</v>
       </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
@@ -5660,18 +5660,18 @@
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>0.65</v>
+        <v>-1.23</v>
       </c>
       <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="n">
-        <v>1882283184</v>
+        <v>1869077157</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5680,19 +5680,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.4835</v>
+        <v>0.3061</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>45826.76569390047</v>
+        <v>45819.6742621412</v>
       </c>
       <c r="G107" t="n">
-        <v>20.69</v>
+        <v>13.285</v>
       </c>
       <c r="H107" t="n">
-        <v>18.17</v>
+        <v>12.805</v>
       </c>
       <c r="I107" t="n">
-        <v>10</v>
+        <v>4.69</v>
       </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
@@ -5709,18 +5709,18 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>-1.21</v>
+        <v>-0.11</v>
       </c>
       <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="n">
-        <v>1867196288</v>
+        <v>1806977521</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5729,19 +5729,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.3367</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>45818.80209099537</v>
+        <v>45783.8305750463</v>
       </c>
       <c r="G108" t="n">
-        <v>41.99</v>
+        <v>29.7</v>
       </c>
       <c r="H108" t="n">
-        <v>44.92</v>
+        <v>32.28</v>
       </c>
       <c r="I108" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
@@ -5758,18 +5758,18 @@
         <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>1.74</v>
+        <v>0.87</v>
       </c>
       <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="n">
-        <v>1744879358</v>
+        <v>1644788775</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5778,19 +5778,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.2701</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>45751.73925940973</v>
+        <v>45693.85093391204</v>
       </c>
       <c r="G109" t="n">
-        <v>148.09</v>
+        <v>144.94</v>
       </c>
       <c r="H109" t="n">
-        <v>220.02</v>
+        <v>145.63</v>
       </c>
       <c r="I109" t="n">
-        <v>40</v>
+        <v>10.99</v>
       </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
@@ -5807,18 +5807,18 @@
         <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>19.43</v>
+        <v>0.05</v>
       </c>
       <c r="Q109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="n">
-        <v>1582735114</v>
+        <v>1926287328</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5827,19 +5827,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.0003</v>
+        <v>0.5476</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>45645.90076803241</v>
+        <v>45854.82177967593</v>
       </c>
       <c r="G110" t="n">
-        <v>130.51</v>
+        <v>18.26</v>
       </c>
       <c r="H110" t="n">
-        <v>142.64</v>
+        <v>19.19</v>
       </c>
       <c r="I110" t="n">
-        <v>0.04</v>
+        <v>10</v>
       </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
@@ -5856,18 +5856,18 @@
         <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="Q110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="n">
-        <v>1422773288</v>
+        <v>1824477589</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5876,19 +5876,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.483</v>
+        <v>0.2344</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>45518.84428523148</v>
+        <v>45792.64732982639</v>
       </c>
       <c r="G111" t="n">
-        <v>51.24</v>
+        <v>42.66</v>
       </c>
       <c r="H111" t="n">
-        <v>59.93</v>
+        <v>43.48</v>
       </c>
       <c r="I111" t="n">
-        <v>24.75</v>
+        <v>10</v>
       </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
@@ -5905,18 +5905,18 @@
         <v>0</v>
       </c>
       <c r="P111" t="n">
-        <v>4.2</v>
+        <v>0.19</v>
       </c>
       <c r="Q111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="n">
-        <v>1450043624</v>
+        <v>1633116336</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5925,19 +5925,19 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.0231</v>
+        <v>1</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>45544.65163525463</v>
+        <v>45686.83272234954</v>
       </c>
       <c r="G112" t="n">
-        <v>147.48</v>
+        <v>44.24</v>
       </c>
       <c r="H112" t="n">
-        <v>129.91</v>
+        <v>51.22</v>
       </c>
       <c r="I112" t="n">
-        <v>3.41</v>
+        <v>44.24</v>
       </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
@@ -5954,18 +5954,18 @@
         <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>-0.41</v>
+        <v>6.98</v>
       </c>
       <c r="Q112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="n">
-        <v>1869077178</v>
+        <v>1727591551</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>BND</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5977,16 +5977,16 @@
         <v>1</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>45819.67426902778</v>
+        <v>45743.77389555555</v>
       </c>
       <c r="G113" t="n">
-        <v>13.285</v>
+        <v>72.87</v>
       </c>
       <c r="H113" t="n">
-        <v>13.095</v>
+        <v>73.02</v>
       </c>
       <c r="I113" t="n">
-        <v>15.31</v>
+        <v>72.87</v>
       </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
@@ -6003,18 +6003,18 @@
         <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>-0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Q113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="n">
-        <v>1644796307</v>
+        <v>1422773288</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6023,19 +6023,19 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1</v>
+        <v>0.483</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>45693.85501710648</v>
+        <v>45518.84428523148</v>
       </c>
       <c r="G114" t="n">
-        <v>20.36</v>
+        <v>51.24</v>
       </c>
       <c r="H114" t="n">
-        <v>21.68</v>
+        <v>59.79</v>
       </c>
       <c r="I114" t="n">
-        <v>20.36</v>
+        <v>24.75</v>
       </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
@@ -6052,18 +6052,18 @@
         <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>1.32</v>
+        <v>4.13</v>
       </c>
       <c r="Q114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="n">
-        <v>1729617775</v>
+        <v>1817256440</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6072,19 +6072,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.0907</v>
+        <v>0.2267</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>45744.71339734954</v>
+        <v>45789.64787115741</v>
       </c>
       <c r="G115" t="n">
-        <v>165.35</v>
+        <v>44.1</v>
       </c>
       <c r="H115" t="n">
-        <v>220.02</v>
+        <v>43.48</v>
       </c>
       <c r="I115" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
@@ -6101,18 +6101,18 @@
         <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>4.96</v>
+        <v>-0.14</v>
       </c>
       <c r="Q115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="n">
-        <v>1559803984</v>
+        <v>1582723120</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6121,19 +6121,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.1076</v>
+        <v>0.3755</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>45628.86014383102</v>
+        <v>45645.89511640046</v>
       </c>
       <c r="G116" t="n">
-        <v>139.4</v>
+        <v>53.26</v>
       </c>
       <c r="H116" t="n">
-        <v>129.91</v>
+        <v>59.79</v>
       </c>
       <c r="I116" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
@@ -6150,18 +6150,18 @@
         <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>-1.02</v>
+        <v>2.45</v>
       </c>
       <c r="Q116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="n">
-        <v>1843469729</v>
+        <v>1880442840</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6170,19 +6170,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.0956</v>
+        <v>0.2535</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>45804.66615450232</v>
+        <v>45825.89113450232</v>
       </c>
       <c r="G117" t="n">
-        <v>156.9</v>
+        <v>59.15</v>
       </c>
       <c r="H117" t="n">
-        <v>150.56</v>
+        <v>59.79</v>
       </c>
       <c r="I117" t="n">
-        <v>15</v>
+        <v>14.99</v>
       </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
@@ -6199,18 +6199,18 @@
         <v>0</v>
       </c>
       <c r="P117" t="n">
-        <v>-0.61</v>
+        <v>0.17</v>
       </c>
       <c r="Q117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="n">
-        <v>1806980496</v>
+        <v>1867458993</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6219,19 +6219,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1</v>
+        <v>0.3417</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>45783.83190503472</v>
+        <v>45818.90699613426</v>
       </c>
       <c r="G118" t="n">
-        <v>16.12</v>
+        <v>58.53</v>
       </c>
       <c r="H118" t="n">
-        <v>18.25</v>
+        <v>59.79</v>
       </c>
       <c r="I118" t="n">
-        <v>16.12</v>
+        <v>20</v>
       </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
@@ -6248,18 +6248,18 @@
         <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>2.13</v>
+        <v>0.43</v>
       </c>
       <c r="Q118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="n">
-        <v>1495551484</v>
+        <v>1744930699</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>BND</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6268,19 +6268,19 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.1914</v>
+        <v>1</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>45580.70648087963</v>
+        <v>45751.74534789352</v>
       </c>
       <c r="G119" t="n">
-        <v>135.82</v>
+        <v>74.13</v>
       </c>
       <c r="H119" t="n">
-        <v>137.47</v>
+        <v>73.02</v>
       </c>
       <c r="I119" t="n">
-        <v>26</v>
+        <v>74.13</v>
       </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
@@ -6297,18 +6297,18 @@
         <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>0.31</v>
+        <v>-1.11</v>
       </c>
       <c r="Q119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="n">
-        <v>1566610015</v>
+        <v>1932757037</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6317,19 +6317,19 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.9385</v>
+        <v>0.2511</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>45632.87667083334</v>
+        <v>45859.74017836805</v>
       </c>
       <c r="G120" t="n">
-        <v>21.31</v>
+        <v>39.85</v>
       </c>
       <c r="H120" t="n">
-        <v>18.17</v>
+        <v>40.39</v>
       </c>
       <c r="I120" t="n">
-        <v>20</v>
+        <v>10.01</v>
       </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
@@ -6346,18 +6346,18 @@
         <v>0</v>
       </c>
       <c r="P120" t="n">
-        <v>-2.95</v>
+        <v>0.13</v>
       </c>
       <c r="Q120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="n">
-        <v>1727574394</v>
+        <v>1680993370</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6369,16 +6369,16 @@
         <v>1</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>45743.76658678241</v>
+        <v>45716.85638861111</v>
       </c>
       <c r="G121" t="n">
-        <v>21.13</v>
+        <v>44.49</v>
       </c>
       <c r="H121" t="n">
-        <v>21.68</v>
+        <v>51.22</v>
       </c>
       <c r="I121" t="n">
-        <v>21.13</v>
+        <v>44.49</v>
       </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
@@ -6395,14 +6395,14 @@
         <v>0</v>
       </c>
       <c r="P121" t="n">
-        <v>0.55</v>
+        <v>6.73</v>
       </c>
       <c r="Q121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="n">
-        <v>1666459270</v>
+        <v>1554741910</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -6415,19 +6415,19 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1</v>
+        <v>0.3495</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>45708.68166530092</v>
+        <v>45623.74951116898</v>
       </c>
       <c r="G122" t="n">
-        <v>17.18</v>
+        <v>15.3</v>
       </c>
       <c r="H122" t="n">
-        <v>21.35</v>
+        <v>23.81</v>
       </c>
       <c r="I122" t="n">
-        <v>17.18</v>
+        <v>5.35</v>
       </c>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
@@ -6444,18 +6444,18 @@
         <v>0</v>
       </c>
       <c r="P122" t="n">
-        <v>4.17</v>
+        <v>2.97</v>
       </c>
       <c r="Q122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="n">
-        <v>1867195793</v>
+        <v>1648735305</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6464,16 +6464,16 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.2339</v>
+        <v>0.4576</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>45818.80180457176</v>
+        <v>45695.85530675926</v>
       </c>
       <c r="G123" t="n">
-        <v>42.74</v>
+        <v>21.85</v>
       </c>
       <c r="H123" t="n">
-        <v>43.09</v>
+        <v>19.19</v>
       </c>
       <c r="I123" t="n">
         <v>10</v>
@@ -6493,27 +6493,45 @@
         <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>0.08</v>
+        <v>-1.22</v>
       </c>
       <c r="Q123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
+      <c r="B124" t="n">
+        <v>1885700231</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>0.0081</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>45828.65147924769</v>
+      </c>
+      <c r="G124" t="n">
+        <v>534.86</v>
+      </c>
+      <c r="H124" t="n">
+        <v>561</v>
+      </c>
+      <c r="I124" t="n">
+        <v>4.33</v>
+      </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
       <c r="M124" t="n">
         <v>0</v>
       </c>
@@ -6524,9 +6542,138 @@
         <v>0</v>
       </c>
       <c r="P124" t="n">
-        <v>82.98</v>
+        <v>0.21</v>
       </c>
       <c r="Q124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="n">
+        <v>1923256224</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>YPF</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>0.6457000000000001</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>45853.65543140046</v>
+      </c>
+      <c r="G125" t="n">
+        <v>30.97</v>
+      </c>
+      <c r="H125" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="I125" t="n">
+        <v>20</v>
+      </c>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="Q125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="n">
+        <v>1599431096</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0.1013</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>45663.73014731482</v>
+      </c>
+      <c r="G126" t="n">
+        <v>148.02</v>
+      </c>
+      <c r="H126" t="n">
+        <v>145.63</v>
+      </c>
+      <c r="I126" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="Q126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>131.45</v>
+      </c>
+      <c r="Q127" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Stock Selection/OPEN POSITION.xlsx
+++ b/Stock Selection/OPEN POSITION.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q127"/>
+  <dimension ref="A1:Q114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,11 +522,11 @@
     <row r="2">
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="n">
-        <v>1867194722</v>
+        <v>1744916452</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.4245</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45818.80135700232</v>
+        <v>45751.74230173611</v>
       </c>
       <c r="G2" t="n">
-        <v>21.27</v>
+        <v>17.54</v>
       </c>
       <c r="H2" t="n">
-        <v>20.79</v>
+        <v>24.87</v>
       </c>
       <c r="I2" t="n">
-        <v>21.27</v>
+        <v>7.45</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -564,18 +564,18 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.48</v>
+        <v>3.11</v>
       </c>
       <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="n">
-        <v>1811432805</v>
+        <v>1923271589</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -584,19 +584,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.0856</v>
+        <v>0.4478</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45785.66143211805</v>
+        <v>45853.65794861111</v>
       </c>
       <c r="G3" t="n">
-        <v>128.46</v>
+        <v>44.66</v>
       </c>
       <c r="H3" t="n">
-        <v>179.46</v>
+        <v>49.41</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -613,18 +613,18 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.36</v>
+        <v>2.13</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="n">
-        <v>1662995258</v>
+        <v>1843477152</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -633,19 +633,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.2943</v>
+        <v>0.1198</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45706.87121422453</v>
+        <v>45804.66724922453</v>
       </c>
       <c r="G4" t="n">
-        <v>67.97</v>
+        <v>17.86</v>
       </c>
       <c r="H4" t="n">
-        <v>72.84</v>
+        <v>20.27</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>2.14</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -662,18 +662,18 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.44</v>
+        <v>0.29</v>
       </c>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="n">
-        <v>1729617775</v>
+        <v>1869077178</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.0546</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45744.71339734954</v>
+        <v>45819.67426902778</v>
       </c>
       <c r="G5" t="n">
-        <v>165.35</v>
+        <v>13.285</v>
       </c>
       <c r="H5" t="n">
-        <v>240.32</v>
+        <v>16.515</v>
       </c>
       <c r="I5" t="n">
-        <v>9.029999999999999</v>
+        <v>15.31</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -711,7 +711,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>4.09</v>
+        <v>3.92</v>
       </c>
       <c r="Q5" t="inlineStr"/>
     </row>
@@ -740,7 +740,7 @@
         <v>21.66</v>
       </c>
       <c r="H6" t="n">
-        <v>20.79</v>
+        <v>19.17</v>
       </c>
       <c r="I6" t="n">
         <v>21.66</v>
@@ -760,18 +760,18 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.87</v>
+        <v>-2.49</v>
       </c>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="n">
-        <v>1882278057</v>
+        <v>1554741956</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -780,19 +780,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.0432</v>
+        <v>0.0495</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45826.76262912037</v>
+        <v>45623.74952237269</v>
       </c>
       <c r="G7" t="n">
-        <v>346.61</v>
+        <v>15.3</v>
       </c>
       <c r="H7" t="n">
-        <v>355.29</v>
+        <v>24.87</v>
       </c>
       <c r="I7" t="n">
-        <v>14.97</v>
+        <v>0.76</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -809,18 +809,18 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>1867193304</v>
+        <v>1631475148</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.1337</v>
+        <v>0.2592</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45818.8008296412</v>
+        <v>45685.83625201389</v>
       </c>
       <c r="G8" t="n">
-        <v>17.64</v>
+        <v>38.58</v>
       </c>
       <c r="H8" t="n">
-        <v>19.46</v>
+        <v>32.92</v>
       </c>
       <c r="I8" t="n">
-        <v>2.36</v>
+        <v>10</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -858,18 +858,18 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.24</v>
+        <v>-1.47</v>
       </c>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>1461331124</v>
+        <v>1817264187</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -878,19 +878,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.3922</v>
+        <v>0.4757</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45553.65374138889</v>
+        <v>45789.64859377315</v>
       </c>
       <c r="G9" t="n">
-        <v>50.99</v>
+        <v>42.02</v>
       </c>
       <c r="H9" t="n">
-        <v>59.79</v>
+        <v>49.41</v>
       </c>
       <c r="I9" t="n">
-        <v>20</v>
+        <v>19.99</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -907,18 +907,18 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.45</v>
+        <v>3.51</v>
       </c>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
-        <v>1582735114</v>
+        <v>1843468958</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.0003</v>
+        <v>0.0669</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45645.90076803241</v>
+        <v>45804.66597149306</v>
       </c>
       <c r="G10" t="n">
-        <v>130.51</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>147.68</v>
+        <v>75.44</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04</v>
+        <v>4.54</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -956,18 +956,18 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
-        <v>1599448103</v>
+        <v>1559803221</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -976,19 +976,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.2839</v>
+        <v>0.092</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45663.73506711805</v>
+        <v>45628.85951927083</v>
       </c>
       <c r="G11" t="n">
-        <v>52.83</v>
+        <v>162.85</v>
       </c>
       <c r="H11" t="n">
-        <v>59.79</v>
+        <v>150.32</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>14.98</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -1005,18 +1005,18 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.97</v>
+        <v>-1.15</v>
       </c>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>1888686062</v>
+        <v>1882278057</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1025,19 +1025,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.2903</v>
+        <v>0.0432</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>45831.64964792824</v>
+        <v>45826.76262912037</v>
       </c>
       <c r="G12" t="n">
-        <v>34.36</v>
+        <v>346.61</v>
       </c>
       <c r="H12" t="n">
-        <v>32.28</v>
+        <v>344.31</v>
       </c>
       <c r="I12" t="n">
-        <v>9.970000000000001</v>
+        <v>14.97</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -1054,18 +1054,18 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6</v>
+        <v>-0.1</v>
       </c>
       <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>1843474191</v>
+        <v>1882283184</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1074,19 +1074,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9372</v>
+        <v>0.4835</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>45804.66699503472</v>
+        <v>45826.76569390047</v>
       </c>
       <c r="G13" t="n">
-        <v>21.33</v>
+        <v>20.69</v>
       </c>
       <c r="H13" t="n">
-        <v>23.81</v>
+        <v>20.48</v>
       </c>
       <c r="I13" t="n">
-        <v>19.99</v>
+        <v>10</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -1103,18 +1103,18 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.32</v>
+        <v>-0.1</v>
       </c>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="n">
-        <v>1744916452</v>
+        <v>1928218937</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.4245</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>45751.74230173611</v>
+        <v>45855.75970359953</v>
       </c>
       <c r="G14" t="n">
-        <v>17.54</v>
+        <v>20.24</v>
       </c>
       <c r="H14" t="n">
-        <v>23.81</v>
+        <v>19.17</v>
       </c>
       <c r="I14" t="n">
-        <v>7.45</v>
+        <v>20.24</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -1152,18 +1152,18 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.66</v>
+        <v>-1.07</v>
       </c>
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="n">
-        <v>1845429980</v>
+        <v>1806980482</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.2406</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>45805.66181400463</v>
+        <v>45783.83189613426</v>
       </c>
       <c r="G15" t="n">
-        <v>13.27</v>
+        <v>16.12</v>
       </c>
       <c r="H15" t="n">
-        <v>12.805</v>
+        <v>20.27</v>
       </c>
       <c r="I15" t="n">
-        <v>15.09</v>
+        <v>3.88</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1201,18 +1201,18 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.12</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="n">
-        <v>1358151307</v>
+        <v>1845429956</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.1081</v>
+        <v>0.4821</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>45460.88529052083</v>
+        <v>45805.66180811343</v>
       </c>
       <c r="G16" t="n">
-        <v>165.93</v>
+        <v>13.275</v>
       </c>
       <c r="H16" t="n">
-        <v>145.63</v>
+        <v>16.515</v>
       </c>
       <c r="I16" t="n">
-        <v>17.94</v>
+        <v>7.28</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1250,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.19</v>
+        <v>1.99</v>
       </c>
       <c r="Q16" t="inlineStr"/>
     </row>
@@ -1279,7 +1279,7 @@
         <v>232.2</v>
       </c>
       <c r="H17" t="n">
-        <v>214.18</v>
+        <v>231.63</v>
       </c>
       <c r="I17" t="n">
         <v>0.02</v>
@@ -1306,11 +1306,11 @@
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
-        <v>1754302454</v>
+        <v>1599448103</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.3673</v>
+        <v>0.2839</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45755.88025324074</v>
+        <v>45663.73506711805</v>
       </c>
       <c r="G18" t="n">
-        <v>27.17</v>
+        <v>52.83</v>
       </c>
       <c r="H18" t="n">
-        <v>32.28</v>
+        <v>65.81</v>
       </c>
       <c r="I18" t="n">
-        <v>9.98</v>
+        <v>15</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1348,14 +1348,14 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.88</v>
+        <v>3.68</v>
       </c>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="n">
-        <v>1923224670</v>
+        <v>1880442840</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1368,16 +1368,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.2583</v>
+        <v>0.2535</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45853.65359685185</v>
+        <v>45825.89113450232</v>
       </c>
       <c r="G19" t="n">
-        <v>58.05</v>
+        <v>59.15</v>
       </c>
       <c r="H19" t="n">
-        <v>59.79</v>
+        <v>65.81</v>
       </c>
       <c r="I19" t="n">
         <v>14.99</v>
@@ -1397,18 +1397,18 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.45</v>
+        <v>1.69</v>
       </c>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
-        <v>1599449649</v>
+        <v>1729617775</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1417,19 +1417,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.4145</v>
+        <v>0.0546</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45663.73562525463</v>
+        <v>45744.71339734954</v>
       </c>
       <c r="G20" t="n">
-        <v>24.11</v>
+        <v>165.35</v>
       </c>
       <c r="H20" t="n">
-        <v>19.19</v>
+        <v>239.01</v>
       </c>
       <c r="I20" t="n">
-        <v>9.99</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1446,18 +1446,18 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.04</v>
+        <v>4.02</v>
       </c>
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="n">
-        <v>1869077178</v>
+        <v>1867193336</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1469,16 +1469,16 @@
         <v>1</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45819.67426902778</v>
+        <v>45818.80084483796</v>
       </c>
       <c r="G21" t="n">
-        <v>13.285</v>
+        <v>17.64</v>
       </c>
       <c r="H21" t="n">
-        <v>12.805</v>
+        <v>20.27</v>
       </c>
       <c r="I21" t="n">
-        <v>15.31</v>
+        <v>17.64</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1495,18 +1495,18 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.34</v>
+        <v>2.63</v>
       </c>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="n">
-        <v>1806978791</v>
+        <v>1727591551</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>BND</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1515,19 +1515,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.0867</v>
+        <v>1</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>45783.83109655092</v>
+        <v>45743.77389555555</v>
       </c>
       <c r="G22" t="n">
-        <v>126.78</v>
+        <v>72.87</v>
       </c>
       <c r="H22" t="n">
-        <v>179.46</v>
+        <v>73.42</v>
       </c>
       <c r="I22" t="n">
-        <v>10.99</v>
+        <v>72.87</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -1544,18 +1544,18 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>4.57</v>
+        <v>0.55</v>
       </c>
       <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="n">
-        <v>1796453499</v>
+        <v>1824476420</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.6422</v>
+        <v>0.1548</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>45777.64668229167</v>
+        <v>45792.64714148148</v>
       </c>
       <c r="G23" t="n">
-        <v>15.57</v>
+        <v>129.17</v>
       </c>
       <c r="H23" t="n">
-        <v>19.46</v>
+        <v>150.32</v>
       </c>
       <c r="I23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -1593,18 +1593,18 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.5</v>
+        <v>3.27</v>
       </c>
       <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="n">
-        <v>1895465445</v>
+        <v>1867194722</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.2987</v>
+        <v>1</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45834.6539484375</v>
+        <v>45818.80135700232</v>
       </c>
       <c r="G24" t="n">
-        <v>33.47</v>
+        <v>21.27</v>
       </c>
       <c r="H24" t="n">
-        <v>32.28</v>
+        <v>19.17</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>21.27</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1642,18 +1642,18 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.36</v>
+        <v>-2.1</v>
       </c>
       <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="n">
-        <v>1712849726</v>
+        <v>1662993636</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1662,19 +1662,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.0861</v>
+        <v>1</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>45734.85489405093</v>
+        <v>45706.87026833333</v>
       </c>
       <c r="G25" t="n">
-        <v>127.72</v>
+        <v>20.65</v>
       </c>
       <c r="H25" t="n">
-        <v>179.46</v>
+        <v>19.17</v>
       </c>
       <c r="I25" t="n">
-        <v>11</v>
+        <v>20.65</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -1691,18 +1691,18 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>4.45</v>
+        <v>-1.48</v>
       </c>
       <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="n">
-        <v>1883977086</v>
+        <v>1621495187</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1711,19 +1711,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0.2318</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>45827.66106613426</v>
+        <v>45678.83178196759</v>
       </c>
       <c r="G26" t="n">
-        <v>12.875</v>
+        <v>43.27</v>
       </c>
       <c r="H26" t="n">
-        <v>12.805</v>
+        <v>32.92</v>
       </c>
       <c r="I26" t="n">
-        <v>14.86</v>
+        <v>10.03</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -1740,18 +1740,18 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0.11</v>
+        <v>-2.4</v>
       </c>
       <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="n">
-        <v>1867195793</v>
+        <v>1972092684</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1760,19 +1760,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.2339</v>
+        <v>1</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>45818.80180457176</v>
+        <v>45882.68269449074</v>
       </c>
       <c r="G27" t="n">
-        <v>42.74</v>
+        <v>18.8</v>
       </c>
       <c r="H27" t="n">
-        <v>43.48</v>
+        <v>19.17</v>
       </c>
       <c r="I27" t="n">
-        <v>10</v>
+        <v>18.8</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -1789,18 +1789,18 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.17</v>
+        <v>0.37</v>
       </c>
       <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="n">
-        <v>1867196288</v>
+        <v>1845431561</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1809,19 +1809,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.0179</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>45818.80209099537</v>
+        <v>45805.66210755787</v>
       </c>
       <c r="G28" t="n">
-        <v>41.99</v>
+        <v>30.57</v>
       </c>
       <c r="H28" t="n">
-        <v>44.95</v>
+        <v>37.01</v>
       </c>
       <c r="I28" t="n">
-        <v>25</v>
+        <v>0.55</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -1838,18 +1838,18 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.76</v>
+        <v>0.11</v>
       </c>
       <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
-        <v>1666459175</v>
+        <v>1867458993</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1858,19 +1858,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.1641</v>
+        <v>0.3417</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>45708.68165298611</v>
+        <v>45818.90699613426</v>
       </c>
       <c r="G29" t="n">
-        <v>17.18</v>
+        <v>58.53</v>
       </c>
       <c r="H29" t="n">
-        <v>23.81</v>
+        <v>65.81</v>
       </c>
       <c r="I29" t="n">
-        <v>2.82</v>
+        <v>20</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -1887,18 +1887,18 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.09</v>
+        <v>2.49</v>
       </c>
       <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
-        <v>1554741956</v>
+        <v>1754302454</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1907,19 +1907,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0.3673</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45623.74952237269</v>
+        <v>45755.88025324074</v>
       </c>
       <c r="G30" t="n">
-        <v>15.3</v>
+        <v>27.17</v>
       </c>
       <c r="H30" t="n">
-        <v>23.81</v>
+        <v>32.92</v>
       </c>
       <c r="I30" t="n">
-        <v>15.3</v>
+        <v>9.98</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -1936,18 +1936,18 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>8.51</v>
+        <v>2.11</v>
       </c>
       <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="n">
-        <v>1880446963</v>
+        <v>1955448954</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1956,19 +1956,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.0774</v>
+        <v>0.3236</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45825.89330317129</v>
+        <v>45873.64722828704</v>
       </c>
       <c r="G31" t="n">
-        <v>129.25</v>
+        <v>30.93</v>
       </c>
       <c r="H31" t="n">
-        <v>127.64</v>
+        <v>37.01</v>
       </c>
       <c r="I31" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1985,18 +1985,18 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.12</v>
+        <v>1.97</v>
       </c>
       <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="n">
-        <v>1923250768</v>
+        <v>1975988073</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2005,19 +2005,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.87</v>
+        <v>0.0469</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45853.65447396991</v>
+        <v>45884.6572796875</v>
       </c>
       <c r="G32" t="n">
-        <v>12.76</v>
+        <v>319.83</v>
       </c>
       <c r="H32" t="n">
-        <v>12.805</v>
+        <v>317.43</v>
       </c>
       <c r="I32" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -2034,18 +2034,18 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.02</v>
+        <v>-0.11</v>
       </c>
       <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="n">
-        <v>1495551484</v>
+        <v>1883977044</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2054,19 +2054,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.1914</v>
+        <v>0.345</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45580.70648087963</v>
+        <v>45827.66105774305</v>
       </c>
       <c r="G33" t="n">
-        <v>135.82</v>
+        <v>12.88</v>
       </c>
       <c r="H33" t="n">
-        <v>134.04</v>
+        <v>16.515</v>
       </c>
       <c r="I33" t="n">
-        <v>26</v>
+        <v>5.13</v>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -2083,18 +2083,18 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>-0.34</v>
+        <v>1.51</v>
       </c>
       <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="n">
-        <v>1845429956</v>
+        <v>1495551484</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2103,19 +2103,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.6565</v>
+        <v>0.1914</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45805.66180811343</v>
+        <v>45580.70648087963</v>
       </c>
       <c r="G34" t="n">
-        <v>13.275</v>
+        <v>135.82</v>
       </c>
       <c r="H34" t="n">
-        <v>12.805</v>
+        <v>125.74</v>
       </c>
       <c r="I34" t="n">
-        <v>9.91</v>
+        <v>26</v>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
@@ -2132,18 +2132,18 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>-0.08</v>
+        <v>-1.93</v>
       </c>
       <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>1806979127</v>
+        <v>1582735114</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2152,19 +2152,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.6361</v>
+        <v>0.0003</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>45783.83125244213</v>
+        <v>45645.90076803241</v>
       </c>
       <c r="G35" t="n">
-        <v>15.72</v>
+        <v>130.51</v>
       </c>
       <c r="H35" t="n">
-        <v>19.19</v>
+        <v>148.15</v>
       </c>
       <c r="I35" t="n">
-        <v>10</v>
+        <v>0.04</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
@@ -2181,18 +2181,18 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>1811475599</v>
+        <v>1811432805</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2201,19 +2201,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.7256</v>
+        <v>0.0467</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45785.66972070602</v>
+        <v>45785.66143211805</v>
       </c>
       <c r="G36" t="n">
-        <v>12.75</v>
+        <v>128.46</v>
       </c>
       <c r="H36" t="n">
-        <v>12.805</v>
+        <v>199.86</v>
       </c>
       <c r="I36" t="n">
-        <v>10.51</v>
+        <v>6</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -2230,18 +2230,18 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.35</v>
+        <v>3.33</v>
       </c>
       <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
-        <v>1880445013</v>
+        <v>1843477272</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2250,19 +2250,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.07149999999999999</v>
+        <v>1</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>45825.8922271412</v>
+        <v>45804.66725678241</v>
       </c>
       <c r="G37" t="n">
-        <v>139.86</v>
+        <v>17.86</v>
       </c>
       <c r="H37" t="n">
-        <v>147.68</v>
+        <v>20.27</v>
       </c>
       <c r="I37" t="n">
-        <v>10</v>
+        <v>17.86</v>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
@@ -2279,18 +2279,18 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.41</v>
       </c>
       <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>1666461140</v>
+        <v>1666459270</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2299,19 +2299,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.2651</v>
+        <v>1</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45708.68207092593</v>
+        <v>45708.68166530092</v>
       </c>
       <c r="G38" t="n">
-        <v>37.7</v>
+        <v>17.18</v>
       </c>
       <c r="H38" t="n">
-        <v>32.28</v>
+        <v>24.87</v>
       </c>
       <c r="I38" t="n">
-        <v>9.99</v>
+        <v>17.18</v>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
@@ -2328,18 +2328,18 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>-1.43</v>
+        <v>7.69</v>
       </c>
       <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
-        <v>1923271589</v>
+        <v>1599449649</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2348,19 +2348,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.4478</v>
+        <v>0.4145</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45853.65794861111</v>
+        <v>45663.73562525463</v>
       </c>
       <c r="G39" t="n">
-        <v>44.66</v>
+        <v>24.11</v>
       </c>
       <c r="H39" t="n">
-        <v>44.95</v>
+        <v>20.48</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>9.99</v>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -2377,18 +2377,18 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.13</v>
+        <v>-1.5</v>
       </c>
       <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="n">
-        <v>1599455288</v>
+        <v>1882281884</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2397,16 +2397,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.2195</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>45663.73750263889</v>
+        <v>45826.76479001158</v>
       </c>
       <c r="G40" t="n">
-        <v>45.55</v>
+        <v>138.84</v>
       </c>
       <c r="H40" t="n">
-        <v>32.28</v>
+        <v>148.15</v>
       </c>
       <c r="I40" t="n">
         <v>10</v>
@@ -2426,18 +2426,18 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>-2.91</v>
+        <v>0.67</v>
       </c>
       <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="n">
-        <v>1867461578</v>
+        <v>1923256224</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BAP</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2446,19 +2446,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.6457000000000001</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45818.90835071759</v>
+        <v>45853.65543140046</v>
       </c>
       <c r="G41" t="n">
-        <v>216.54</v>
+        <v>30.97</v>
       </c>
       <c r="H41" t="n">
-        <v>235.66</v>
+        <v>32.92</v>
       </c>
       <c r="I41" t="n">
-        <v>19.99</v>
+        <v>20</v>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
@@ -2475,18 +2475,18 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.76</v>
+        <v>1.26</v>
       </c>
       <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="n">
-        <v>1666459270</v>
+        <v>1653137218</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2495,19 +2495,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0.277</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>45708.68166530092</v>
+        <v>45699.85152199074</v>
       </c>
       <c r="G42" t="n">
-        <v>17.18</v>
+        <v>36.1</v>
       </c>
       <c r="H42" t="n">
-        <v>23.81</v>
+        <v>32.92</v>
       </c>
       <c r="I42" t="n">
-        <v>17.18</v>
+        <v>10</v>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -2524,18 +2524,18 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>6.63</v>
+        <v>-0.88</v>
       </c>
       <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="n">
-        <v>1817264187</v>
+        <v>1976499401</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2544,19 +2544,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.4757</v>
+        <v>0.8064</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>45789.64859377315</v>
+        <v>45884.83731814815</v>
       </c>
       <c r="G43" t="n">
-        <v>42.02</v>
+        <v>49.6</v>
       </c>
       <c r="H43" t="n">
-        <v>44.95</v>
+        <v>49.63</v>
       </c>
       <c r="I43" t="n">
-        <v>19.99</v>
+        <v>40</v>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -2573,14 +2573,14 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.39</v>
+        <v>0.02</v>
       </c>
       <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
-        <v>1566610015</v>
+        <v>1830408508</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2593,19 +2593,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9385</v>
+        <v>0.5793</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45632.87667083334</v>
+        <v>45796.82346997685</v>
       </c>
       <c r="G44" t="n">
-        <v>21.31</v>
+        <v>17.26</v>
       </c>
       <c r="H44" t="n">
-        <v>19.19</v>
+        <v>20.48</v>
       </c>
       <c r="I44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -2622,18 +2622,18 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>-1.99</v>
+        <v>1.86</v>
       </c>
       <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>1701098878</v>
+        <v>1888686062</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2642,19 +2642,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.0383</v>
+        <v>0.2903</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>45727.87167594907</v>
+        <v>45831.64964792824</v>
       </c>
       <c r="G45" t="n">
-        <v>139.41</v>
+        <v>34.36</v>
       </c>
       <c r="H45" t="n">
-        <v>179.46</v>
+        <v>32.92</v>
       </c>
       <c r="I45" t="n">
-        <v>5.34</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -2671,18 +2671,18 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.53</v>
+        <v>-0.41</v>
       </c>
       <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>1888700382</v>
+        <v>1867462173</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2691,19 +2691,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>45831.65144708334</v>
+        <v>45818.90866184028</v>
       </c>
       <c r="G46" t="n">
-        <v>47.58</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>51.22</v>
+        <v>93.67</v>
       </c>
       <c r="I46" t="n">
-        <v>47.58</v>
+        <v>0.65</v>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -2720,14 +2720,14 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>3.64</v>
+        <v>0.14</v>
       </c>
       <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>1867197360</v>
+        <v>1563288050</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2740,19 +2740,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.0765</v>
+        <v>0.0626</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>45818.80265583334</v>
+        <v>45630.85583428241</v>
       </c>
       <c r="G47" t="n">
-        <v>131.96</v>
+        <v>159.74</v>
       </c>
       <c r="H47" t="n">
-        <v>145.63</v>
+        <v>150.32</v>
       </c>
       <c r="I47" t="n">
-        <v>10.09</v>
+        <v>10</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -2769,18 +2769,18 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1.05</v>
+        <v>-0.59</v>
       </c>
       <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>1712850989</v>
+        <v>1642762235</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2789,19 +2789,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.0282</v>
+        <v>0.1572</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>45734.85576775463</v>
+        <v>45692.86612574074</v>
       </c>
       <c r="G48" t="n">
-        <v>160.64</v>
+        <v>127.16</v>
       </c>
       <c r="H48" t="n">
-        <v>190.27</v>
+        <v>125.74</v>
       </c>
       <c r="I48" t="n">
-        <v>4.53</v>
+        <v>19.99</v>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -2818,18 +2818,18 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0.84</v>
+        <v>-0.22</v>
       </c>
       <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
-        <v>1563288050</v>
+        <v>1754304266</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2838,19 +2838,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.0626</v>
+        <v>0.7137</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45630.85583428241</v>
+        <v>45755.88055112268</v>
       </c>
       <c r="G49" t="n">
-        <v>159.74</v>
+        <v>14</v>
       </c>
       <c r="H49" t="n">
-        <v>145.63</v>
+        <v>20.48</v>
       </c>
       <c r="I49" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
@@ -2867,14 +2867,14 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>-0.88</v>
+        <v>4.63</v>
       </c>
       <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
-        <v>1744916497</v>
+        <v>1923259795</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0.4424</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>45751.74231563658</v>
+        <v>45853.65609353009</v>
       </c>
       <c r="G50" t="n">
-        <v>17.54</v>
+        <v>22.59</v>
       </c>
       <c r="H50" t="n">
-        <v>23.81</v>
+        <v>24.87</v>
       </c>
       <c r="I50" t="n">
-        <v>17.54</v>
+        <v>9.99</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -2916,18 +2916,18 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>6.27</v>
+        <v>1.01</v>
       </c>
       <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>1845431561</v>
+        <v>1845429980</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2936,19 +2936,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.0179</v>
+        <v>1</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>45805.66210755787</v>
+        <v>45805.66181400463</v>
       </c>
       <c r="G51" t="n">
-        <v>30.57</v>
+        <v>13.27</v>
       </c>
       <c r="H51" t="n">
-        <v>40.39</v>
+        <v>16.515</v>
       </c>
       <c r="I51" t="n">
-        <v>0.55</v>
+        <v>15.09</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -2965,18 +2965,18 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>0.17</v>
+        <v>4.14</v>
       </c>
       <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
-        <v>1648737122</v>
+        <v>1680993370</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2985,19 +2985,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.001</v>
+        <v>1</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>45695.85619950231</v>
+        <v>45716.85638861111</v>
       </c>
       <c r="G52" t="n">
-        <v>408.33</v>
+        <v>44.49</v>
       </c>
       <c r="H52" t="n">
-        <v>505.96</v>
+        <v>51.35</v>
       </c>
       <c r="I52" t="n">
-        <v>0.41</v>
+        <v>44.49</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
@@ -3014,18 +3014,18 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>0.1</v>
+        <v>6.86</v>
       </c>
       <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="n">
-        <v>1923246263</v>
+        <v>1701100027</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3034,19 +3034,19 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>0.7812</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>45853.6538128125</v>
+        <v>45727.87202070602</v>
       </c>
       <c r="G53" t="n">
-        <v>21.17</v>
+        <v>19.2</v>
       </c>
       <c r="H53" t="n">
-        <v>20.79</v>
+        <v>20.48</v>
       </c>
       <c r="I53" t="n">
-        <v>21.17</v>
+        <v>15</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
@@ -3063,18 +3063,18 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>-0.38</v>
+        <v>1</v>
       </c>
       <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="n">
-        <v>1621495187</v>
+        <v>1644796307</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3083,19 +3083,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.2318</v>
+        <v>1</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>45678.83178196759</v>
+        <v>45693.85501710648</v>
       </c>
       <c r="G54" t="n">
-        <v>43.27</v>
+        <v>20.36</v>
       </c>
       <c r="H54" t="n">
-        <v>32.28</v>
+        <v>19.17</v>
       </c>
       <c r="I54" t="n">
-        <v>10.03</v>
+        <v>20.36</v>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
@@ -3112,18 +3112,18 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>-2.55</v>
+        <v>-1.19</v>
       </c>
       <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="n">
-        <v>1867462173</v>
+        <v>1806979127</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3132,19 +3132,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.1284</v>
+        <v>0.6361</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>45818.90866184028</v>
+        <v>45783.83125244213</v>
       </c>
       <c r="G55" t="n">
-        <v>77.93000000000001</v>
+        <v>15.72</v>
       </c>
       <c r="H55" t="n">
-        <v>95.97</v>
+        <v>20.48</v>
       </c>
       <c r="I55" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
@@ -3161,18 +3161,18 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.31</v>
+        <v>3.03</v>
       </c>
       <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="n">
-        <v>1811475646</v>
+        <v>1843474191</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3181,19 +3181,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>0.9372</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>45785.66973634259</v>
+        <v>45804.66699503472</v>
       </c>
       <c r="G56" t="n">
-        <v>12.75</v>
+        <v>21.33</v>
       </c>
       <c r="H56" t="n">
-        <v>12.805</v>
+        <v>24.87</v>
       </c>
       <c r="I56" t="n">
-        <v>14.49</v>
+        <v>19.99</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
@@ -3210,18 +3210,18 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>0.48</v>
+        <v>3.32</v>
       </c>
       <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="n">
-        <v>1644789287</v>
+        <v>1883977086</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3230,19 +3230,19 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.0813</v>
+        <v>1</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45693.85123056713</v>
+        <v>45827.66106613426</v>
       </c>
       <c r="G57" t="n">
-        <v>129.08</v>
+        <v>12.875</v>
       </c>
       <c r="H57" t="n">
-        <v>127.64</v>
+        <v>16.515</v>
       </c>
       <c r="I57" t="n">
-        <v>10.49</v>
+        <v>14.86</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
@@ -3259,18 +3259,18 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>-0.11</v>
+        <v>4.37</v>
       </c>
       <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
-        <v>1928218937</v>
+        <v>1932757037</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3279,19 +3279,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>0.2511</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45855.75970359953</v>
+        <v>45859.74017836805</v>
       </c>
       <c r="G58" t="n">
-        <v>20.24</v>
+        <v>39.85</v>
       </c>
       <c r="H58" t="n">
-        <v>20.79</v>
+        <v>37.01</v>
       </c>
       <c r="I58" t="n">
-        <v>20.24</v>
+        <v>10.01</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
@@ -3308,18 +3308,18 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>0.55</v>
+        <v>-0.72</v>
       </c>
       <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="n">
-        <v>1701100027</v>
+        <v>1744930699</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>BND</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3328,19 +3328,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.7812</v>
+        <v>1</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>45727.87202070602</v>
+        <v>45751.74534789352</v>
       </c>
       <c r="G59" t="n">
-        <v>19.2</v>
+        <v>74.13</v>
       </c>
       <c r="H59" t="n">
-        <v>19.19</v>
+        <v>73.42</v>
       </c>
       <c r="I59" t="n">
-        <v>15</v>
+        <v>74.13</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
@@ -3357,18 +3357,18 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>-0.01</v>
+        <v>-0.71</v>
       </c>
       <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="n">
-        <v>1882281884</v>
+        <v>1923246263</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3377,19 +3377,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.07199999999999999</v>
+        <v>1</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45826.76479001158</v>
+        <v>45853.6538128125</v>
       </c>
       <c r="G60" t="n">
-        <v>138.84</v>
+        <v>21.17</v>
       </c>
       <c r="H60" t="n">
-        <v>147.68</v>
+        <v>19.17</v>
       </c>
       <c r="I60" t="n">
-        <v>10</v>
+        <v>21.17</v>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
@@ -3406,18 +3406,18 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>0.63</v>
+        <v>-2</v>
       </c>
       <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="n">
-        <v>1727574394</v>
+        <v>1648735305</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3426,19 +3426,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>0.4576</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>45743.76658678241</v>
+        <v>45695.85530675926</v>
       </c>
       <c r="G61" t="n">
-        <v>21.13</v>
+        <v>21.85</v>
       </c>
       <c r="H61" t="n">
-        <v>20.79</v>
+        <v>20.48</v>
       </c>
       <c r="I61" t="n">
-        <v>21.13</v>
+        <v>10</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
@@ -3455,18 +3455,18 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>-0.34</v>
+        <v>-0.63</v>
       </c>
       <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="n">
-        <v>1414752069</v>
+        <v>1744929368</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3475,19 +3475,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.1933</v>
+        <v>0.0192</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>45511.86049193287</v>
+        <v>45751.74500871528</v>
       </c>
       <c r="G62" t="n">
-        <v>77.53</v>
+        <v>324.48</v>
       </c>
       <c r="H62" t="n">
-        <v>72.84</v>
+        <v>344.31</v>
       </c>
       <c r="I62" t="n">
-        <v>14.99</v>
+        <v>6.23</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
@@ -3504,18 +3504,18 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>-0.91</v>
+        <v>0.38</v>
       </c>
       <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="n">
-        <v>1830408508</v>
+        <v>1867196288</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3524,19 +3524,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.5793</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>45796.82346997685</v>
+        <v>45818.80209099537</v>
       </c>
       <c r="G63" t="n">
-        <v>17.26</v>
+        <v>41.99</v>
       </c>
       <c r="H63" t="n">
-        <v>19.19</v>
+        <v>49.41</v>
       </c>
       <c r="I63" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
@@ -3553,18 +3553,18 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>1.12</v>
+        <v>4.41</v>
       </c>
       <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="n">
-        <v>1582714896</v>
+        <v>1666459175</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3573,19 +3573,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.4847</v>
+        <v>0.1641</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>45645.89066263889</v>
+        <v>45708.68165298611</v>
       </c>
       <c r="G64" t="n">
-        <v>20.62</v>
+        <v>17.18</v>
       </c>
       <c r="H64" t="n">
-        <v>19.19</v>
+        <v>24.87</v>
       </c>
       <c r="I64" t="n">
-        <v>9.99</v>
+        <v>2.82</v>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
@@ -3602,18 +3602,18 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>-0.6899999999999999</v>
+        <v>1.26</v>
       </c>
       <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="n">
-        <v>1880441651</v>
+        <v>1582723120</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3622,19 +3622,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>0.3755</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>45825.89055887731</v>
+        <v>45645.89511640046</v>
       </c>
       <c r="G65" t="n">
-        <v>21.21</v>
+        <v>53.26</v>
       </c>
       <c r="H65" t="n">
-        <v>20.79</v>
+        <v>65.81</v>
       </c>
       <c r="I65" t="n">
-        <v>21.21</v>
+        <v>20</v>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
@@ -3651,18 +3651,18 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>-0.42</v>
+        <v>4.71</v>
       </c>
       <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="n">
-        <v>1680994777</v>
+        <v>1880445013</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3671,19 +3671,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.7278</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>45716.85705375</v>
+        <v>45825.8922271412</v>
       </c>
       <c r="G66" t="n">
-        <v>20.6</v>
+        <v>139.86</v>
       </c>
       <c r="H66" t="n">
-        <v>19.19</v>
+        <v>148.15</v>
       </c>
       <c r="I66" t="n">
-        <v>14.99</v>
+        <v>10</v>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
@@ -3700,14 +3700,14 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>-1.02</v>
+        <v>0.59</v>
       </c>
       <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="n">
-        <v>1744767540</v>
+        <v>1923258249</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -3720,19 +3720,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.643</v>
+        <v>1</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>45751.72316712963</v>
+        <v>45853.65576626157</v>
       </c>
       <c r="G67" t="n">
-        <v>15.55</v>
+        <v>19.41</v>
       </c>
       <c r="H67" t="n">
-        <v>19.19</v>
+        <v>20.48</v>
       </c>
       <c r="I67" t="n">
-        <v>10</v>
+        <v>19.41</v>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
@@ -3749,18 +3749,18 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>2.34</v>
+        <v>1.07</v>
       </c>
       <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="n">
-        <v>1843477152</v>
+        <v>1843470413</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3769,19 +3769,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.1198</v>
+        <v>0.4729</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>45804.66724922453</v>
+        <v>45804.66637251157</v>
       </c>
       <c r="G68" t="n">
-        <v>17.86</v>
+        <v>42.29</v>
       </c>
       <c r="H68" t="n">
-        <v>19.46</v>
+        <v>49.41</v>
       </c>
       <c r="I68" t="n">
-        <v>2.14</v>
+        <v>20</v>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
@@ -3798,18 +3798,18 @@
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>0.19</v>
+        <v>3.37</v>
       </c>
       <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="n">
-        <v>1559802942</v>
+        <v>1869077157</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3818,19 +3818,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.2585</v>
+        <v>0.3061</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>45628.85929152778</v>
+        <v>45819.6742621412</v>
       </c>
       <c r="G69" t="n">
-        <v>77.34999999999999</v>
+        <v>13.285</v>
       </c>
       <c r="H69" t="n">
-        <v>72.84</v>
+        <v>16.515</v>
       </c>
       <c r="I69" t="n">
-        <v>19.99</v>
+        <v>4.69</v>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
@@ -3847,18 +3847,18 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>-1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="n">
-        <v>1653137218</v>
+        <v>1824477589</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3867,16 +3867,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.277</v>
+        <v>0.2344</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>45699.85152199074</v>
+        <v>45792.64732982639</v>
       </c>
       <c r="G70" t="n">
-        <v>36.1</v>
+        <v>42.66</v>
       </c>
       <c r="H70" t="n">
-        <v>32.28</v>
+        <v>44.56</v>
       </c>
       <c r="I70" t="n">
         <v>10</v>
@@ -3896,18 +3896,18 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>-1.06</v>
+        <v>0.44</v>
       </c>
       <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="n">
-        <v>1883977044</v>
+        <v>1517510856</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3916,19 +3916,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.345</v>
+        <v>0.0602</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>45827.66105774305</v>
+        <v>45597.61014849537</v>
       </c>
       <c r="G71" t="n">
-        <v>12.88</v>
+        <v>166.03</v>
       </c>
       <c r="H71" t="n">
-        <v>12.805</v>
+        <v>150.32</v>
       </c>
       <c r="I71" t="n">
-        <v>5.13</v>
+        <v>10</v>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
@@ -3945,18 +3945,18 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>0.03</v>
+        <v>-0.95</v>
       </c>
       <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="n">
-        <v>1923258249</v>
+        <v>1666461140</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3965,19 +3965,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>0.2651</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>45853.65576626157</v>
+        <v>45708.68207092593</v>
       </c>
       <c r="G72" t="n">
-        <v>19.41</v>
+        <v>37.7</v>
       </c>
       <c r="H72" t="n">
-        <v>19.19</v>
+        <v>32.92</v>
       </c>
       <c r="I72" t="n">
-        <v>19.41</v>
+        <v>9.99</v>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -3994,18 +3994,18 @@
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>-0.22</v>
+        <v>-1.26</v>
       </c>
       <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="n">
-        <v>1635194117</v>
+        <v>1817256440</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4014,16 +4014,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.2479</v>
+        <v>0.2267</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45687.85228493056</v>
+        <v>45789.64787115741</v>
       </c>
       <c r="G73" t="n">
-        <v>40.33</v>
+        <v>44.1</v>
       </c>
       <c r="H73" t="n">
-        <v>32.28</v>
+        <v>44.56</v>
       </c>
       <c r="I73" t="n">
         <v>10</v>
@@ -4043,18 +4043,18 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>-2</v>
+        <v>0.1</v>
       </c>
       <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="n">
-        <v>1843477272</v>
+        <v>1888700382</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4066,16 +4066,16 @@
         <v>1</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45804.66725678241</v>
+        <v>45831.65144708334</v>
       </c>
       <c r="G74" t="n">
-        <v>17.86</v>
+        <v>47.58</v>
       </c>
       <c r="H74" t="n">
-        <v>19.46</v>
+        <v>51.35</v>
       </c>
       <c r="I74" t="n">
-        <v>17.86</v>
+        <v>47.58</v>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
@@ -4092,18 +4092,18 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>1.6</v>
+        <v>3.77</v>
       </c>
       <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="n">
-        <v>1744929368</v>
+        <v>1867193304</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4112,19 +4112,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.0192</v>
+        <v>0.1337</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>45751.74500871528</v>
+        <v>45818.8008296412</v>
       </c>
       <c r="G75" t="n">
-        <v>324.48</v>
+        <v>17.64</v>
       </c>
       <c r="H75" t="n">
-        <v>355.29</v>
+        <v>20.27</v>
       </c>
       <c r="I75" t="n">
-        <v>6.23</v>
+        <v>2.36</v>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
@@ -4141,18 +4141,18 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>0.59</v>
+        <v>0.35</v>
       </c>
       <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="n">
-        <v>1662993636</v>
+        <v>1880446729</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4161,19 +4161,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>0.0772</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>45706.87026833333</v>
+        <v>45825.89315055555</v>
       </c>
       <c r="G76" t="n">
-        <v>20.65</v>
+        <v>129.62</v>
       </c>
       <c r="H76" t="n">
-        <v>20.79</v>
+        <v>150.32</v>
       </c>
       <c r="I76" t="n">
-        <v>20.65</v>
+        <v>10.01</v>
       </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
@@ -4190,18 +4190,18 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>0.14</v>
+        <v>1.59</v>
       </c>
       <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="n">
-        <v>1895460914</v>
+        <v>1358151307</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4210,19 +4210,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.0781</v>
+        <v>0.1081</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>45834.65311391203</v>
+        <v>45460.88529052083</v>
       </c>
       <c r="G77" t="n">
-        <v>128.09</v>
+        <v>165.93</v>
       </c>
       <c r="H77" t="n">
-        <v>127.64</v>
+        <v>150.32</v>
       </c>
       <c r="I77" t="n">
-        <v>10</v>
+        <v>17.94</v>
       </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
@@ -4239,18 +4239,18 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>-0.03</v>
+        <v>-1.68</v>
       </c>
       <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="n">
-        <v>1824476420</v>
+        <v>1744916497</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4259,19 +4259,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.1548</v>
+        <v>1</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>45792.64714148148</v>
+        <v>45751.74231563658</v>
       </c>
       <c r="G78" t="n">
-        <v>129.17</v>
+        <v>17.54</v>
       </c>
       <c r="H78" t="n">
-        <v>145.63</v>
+        <v>24.87</v>
       </c>
       <c r="I78" t="n">
-        <v>20</v>
+        <v>17.54</v>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
@@ -4288,18 +4288,18 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>2.54</v>
+        <v>7.33</v>
       </c>
       <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="n">
-        <v>1880443947</v>
+        <v>1926287328</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4308,19 +4308,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.1047</v>
+        <v>0.5476</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>45825.891695625</v>
+        <v>45854.82177967593</v>
       </c>
       <c r="G79" t="n">
-        <v>142.99</v>
+        <v>18.26</v>
       </c>
       <c r="H79" t="n">
-        <v>179.46</v>
+        <v>20.48</v>
       </c>
       <c r="I79" t="n">
-        <v>14.97</v>
+        <v>10</v>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
@@ -4337,14 +4337,14 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>3.82</v>
+        <v>1.21</v>
       </c>
       <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="n">
-        <v>1867193336</v>
+        <v>1796453499</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -4357,19 +4357,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>45818.80084483796</v>
+        <v>45777.64668229167</v>
       </c>
       <c r="G80" t="n">
-        <v>17.64</v>
+        <v>15.57</v>
       </c>
       <c r="H80" t="n">
-        <v>19.46</v>
+        <v>20.27</v>
       </c>
       <c r="I80" t="n">
-        <v>17.64</v>
+        <v>8.01</v>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
@@ -4386,18 +4386,18 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>1.82</v>
+        <v>2.42</v>
       </c>
       <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="n">
-        <v>1450043624</v>
+        <v>1806977521</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4406,19 +4406,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.0231</v>
+        <v>0.3367</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>45544.65163525463</v>
+        <v>45783.8305750463</v>
       </c>
       <c r="G81" t="n">
-        <v>147.48</v>
+        <v>29.7</v>
       </c>
       <c r="H81" t="n">
-        <v>127.64</v>
+        <v>32.92</v>
       </c>
       <c r="I81" t="n">
-        <v>3.41</v>
+        <v>10</v>
       </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
@@ -4435,18 +4435,18 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>-0.46</v>
+        <v>1.08</v>
       </c>
       <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="n">
-        <v>1642762235</v>
+        <v>1867195793</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4455,19 +4455,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.1572</v>
+        <v>0.2339</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>45692.86612574074</v>
+        <v>45818.80180457176</v>
       </c>
       <c r="G82" t="n">
-        <v>127.16</v>
+        <v>42.74</v>
       </c>
       <c r="H82" t="n">
-        <v>134.04</v>
+        <v>44.56</v>
       </c>
       <c r="I82" t="n">
-        <v>19.99</v>
+        <v>10</v>
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
@@ -4484,14 +4484,14 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>1.08</v>
+        <v>0.42</v>
       </c>
       <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="n">
-        <v>1559803221</v>
+        <v>1644788775</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -4504,19 +4504,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.092</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>45628.85951927083</v>
+        <v>45693.85093391204</v>
       </c>
       <c r="G83" t="n">
-        <v>162.85</v>
+        <v>144.94</v>
       </c>
       <c r="H83" t="n">
-        <v>145.63</v>
+        <v>150.32</v>
       </c>
       <c r="I83" t="n">
-        <v>14.98</v>
+        <v>10.99</v>
       </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
@@ -4533,18 +4533,18 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>-1.58</v>
+        <v>0.4</v>
       </c>
       <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="n">
-        <v>1830410729</v>
+        <v>1566610015</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4553,19 +4553,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.1091</v>
+        <v>0.9385</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>45796.82476561343</v>
+        <v>45632.87667083334</v>
       </c>
       <c r="G84" t="n">
-        <v>33.66</v>
+        <v>21.31</v>
       </c>
       <c r="H84" t="n">
-        <v>36.8</v>
+        <v>20.48</v>
       </c>
       <c r="I84" t="n">
-        <v>3.67</v>
+        <v>20</v>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
@@ -4582,18 +4582,18 @@
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>0.34</v>
+        <v>-0.78</v>
       </c>
       <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="n">
-        <v>1843469729</v>
+        <v>1970057305</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4602,19 +4602,19 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.0956</v>
+        <v>0.2789</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>45804.66615450232</v>
+        <v>45881.70511172454</v>
       </c>
       <c r="G85" t="n">
-        <v>156.9</v>
+        <v>35.88</v>
       </c>
       <c r="H85" t="n">
-        <v>179.46</v>
+        <v>37.01</v>
       </c>
       <c r="I85" t="n">
-        <v>15</v>
+        <v>10.01</v>
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
@@ -4631,18 +4631,18 @@
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>2.16</v>
+        <v>0.31</v>
       </c>
       <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="n">
-        <v>1481609355</v>
+        <v>1744767540</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4651,19 +4651,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.107</v>
+        <v>0.643</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>45568.7734872338</v>
+        <v>45751.72316712963</v>
       </c>
       <c r="G86" t="n">
-        <v>140.18</v>
+        <v>15.55</v>
       </c>
       <c r="H86" t="n">
-        <v>127.64</v>
+        <v>20.48</v>
       </c>
       <c r="I86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
@@ -4680,18 +4680,18 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>-1.34</v>
+        <v>3.17</v>
       </c>
       <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="n">
-        <v>1727563010</v>
+        <v>1923250768</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4700,19 +4700,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>45743.76106726852</v>
+        <v>45853.65447396991</v>
       </c>
       <c r="G87" t="n">
-        <v>46.11</v>
+        <v>12.76</v>
       </c>
       <c r="H87" t="n">
-        <v>51.22</v>
+        <v>16.515</v>
       </c>
       <c r="I87" t="n">
-        <v>46.11</v>
+        <v>13</v>
       </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
@@ -4729,18 +4729,18 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>5.11</v>
+        <v>3.73</v>
       </c>
       <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="n">
-        <v>1806980482</v>
+        <v>1712850989</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4749,19 +4749,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.2406</v>
+        <v>0.0282</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>45783.83189613426</v>
+        <v>45734.85576775463</v>
       </c>
       <c r="G88" t="n">
-        <v>16.12</v>
+        <v>160.64</v>
       </c>
       <c r="H88" t="n">
-        <v>19.46</v>
+        <v>203.88</v>
       </c>
       <c r="I88" t="n">
-        <v>3.88</v>
+        <v>4.53</v>
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
@@ -4778,18 +4778,18 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>0.8</v>
+        <v>1.22</v>
       </c>
       <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="n">
-        <v>1644796307</v>
+        <v>1727563010</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4801,16 +4801,16 @@
         <v>1</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>45693.85501710648</v>
+        <v>45743.76106726852</v>
       </c>
       <c r="G89" t="n">
-        <v>20.36</v>
+        <v>46.11</v>
       </c>
       <c r="H89" t="n">
-        <v>20.79</v>
+        <v>51.35</v>
       </c>
       <c r="I89" t="n">
-        <v>20.36</v>
+        <v>46.11</v>
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
@@ -4827,18 +4827,18 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>0.43</v>
+        <v>5.24</v>
       </c>
       <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="n">
-        <v>1880446729</v>
+        <v>1824482557</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4847,19 +4847,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.0772</v>
+        <v>0.2641</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>45825.89315055555</v>
+        <v>45792.64805195602</v>
       </c>
       <c r="G90" t="n">
-        <v>129.62</v>
+        <v>56.78</v>
       </c>
       <c r="H90" t="n">
-        <v>145.63</v>
+        <v>65.81</v>
       </c>
       <c r="I90" t="n">
-        <v>10.01</v>
+        <v>15</v>
       </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
@@ -4876,18 +4876,18 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>1.23</v>
+        <v>2.38</v>
       </c>
       <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="n">
-        <v>1923258184</v>
+        <v>1867197360</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4896,19 +4896,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.0298</v>
+        <v>0.0765</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>45853.6557568287</v>
+        <v>45818.80265583334</v>
       </c>
       <c r="G91" t="n">
-        <v>19.43</v>
+        <v>131.96</v>
       </c>
       <c r="H91" t="n">
-        <v>19.19</v>
+        <v>150.32</v>
       </c>
       <c r="I91" t="n">
-        <v>0.58</v>
+        <v>10.09</v>
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
@@ -4925,18 +4925,18 @@
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>-0.01</v>
+        <v>1.41</v>
       </c>
       <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="n">
-        <v>1806980496</v>
+        <v>1635194117</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4945,19 +4945,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>0.2479</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>45783.83190503472</v>
+        <v>45687.85228493056</v>
       </c>
       <c r="G92" t="n">
-        <v>16.12</v>
+        <v>40.33</v>
       </c>
       <c r="H92" t="n">
-        <v>19.46</v>
+        <v>32.92</v>
       </c>
       <c r="I92" t="n">
-        <v>16.12</v>
+        <v>10</v>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
@@ -4974,18 +4974,18 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>3.34</v>
+        <v>-1.84</v>
       </c>
       <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="n">
-        <v>1631475148</v>
+        <v>1599431096</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4994,19 +4994,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.2592</v>
+        <v>0.1013</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>45685.83625201389</v>
+        <v>45663.73014731482</v>
       </c>
       <c r="G93" t="n">
-        <v>38.58</v>
+        <v>148.02</v>
       </c>
       <c r="H93" t="n">
-        <v>32.28</v>
+        <v>150.32</v>
       </c>
       <c r="I93" t="n">
-        <v>10</v>
+        <v>14.99</v>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
@@ -5023,18 +5023,18 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>-1.63</v>
+        <v>0.24</v>
       </c>
       <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="n">
-        <v>1843468958</v>
+        <v>1885700231</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5043,19 +5043,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.2208</v>
+        <v>0.0081</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>45804.66597149306</v>
+        <v>45828.65147924769</v>
       </c>
       <c r="G94" t="n">
-        <v>67.93000000000001</v>
+        <v>534.86</v>
       </c>
       <c r="H94" t="n">
-        <v>72.84</v>
+        <v>581.5700000000001</v>
       </c>
       <c r="I94" t="n">
-        <v>15</v>
+        <v>4.33</v>
       </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
@@ -5072,18 +5072,18 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>1.08</v>
+        <v>0.38</v>
       </c>
       <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="n">
-        <v>1666451221</v>
+        <v>1880443947</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5092,19 +5092,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.0001</v>
+        <v>0.1047</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>45708.68022634259</v>
+        <v>45825.891695625</v>
       </c>
       <c r="G95" t="n">
-        <v>43</v>
+        <v>142.99</v>
       </c>
       <c r="H95" t="n">
-        <v>43.48</v>
+        <v>199.86</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>14.97</v>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -5121,18 +5121,18 @@
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="n">
-        <v>1776193271</v>
+        <v>1923224670</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5141,19 +5141,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.6724</v>
+        <v>0.2583</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>45764.85451520833</v>
+        <v>45853.65359685185</v>
       </c>
       <c r="G96" t="n">
-        <v>14.87</v>
+        <v>58.05</v>
       </c>
       <c r="H96" t="n">
-        <v>19.46</v>
+        <v>65.81</v>
       </c>
       <c r="I96" t="n">
-        <v>10</v>
+        <v>14.99</v>
       </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
@@ -5170,18 +5170,18 @@
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>3.08</v>
+        <v>2.01</v>
       </c>
       <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="n">
-        <v>1824482557</v>
+        <v>1867195417</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5190,19 +5190,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.2641</v>
+        <v>0.1044</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>45792.64805195602</v>
+        <v>45818.80165224537</v>
       </c>
       <c r="G97" t="n">
-        <v>56.78</v>
+        <v>143.6</v>
       </c>
       <c r="H97" t="n">
-        <v>59.79</v>
+        <v>148.15</v>
       </c>
       <c r="I97" t="n">
-        <v>15</v>
+        <v>14.99</v>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
@@ -5219,14 +5219,14 @@
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>0.79</v>
+        <v>0.48</v>
       </c>
       <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="n">
-        <v>1754304266</v>
+        <v>1680994777</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -5239,19 +5239,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.7137</v>
+        <v>0.7278</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>45755.88055112268</v>
+        <v>45716.85705375</v>
       </c>
       <c r="G98" t="n">
-        <v>14</v>
+        <v>20.6</v>
       </c>
       <c r="H98" t="n">
-        <v>19.19</v>
+        <v>20.48</v>
       </c>
       <c r="I98" t="n">
-        <v>9.99</v>
+        <v>14.99</v>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
@@ -5268,18 +5268,18 @@
         <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>3.71</v>
+        <v>-0.08</v>
       </c>
       <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="n">
-        <v>1867195417</v>
+        <v>1880441651</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5288,19 +5288,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.1044</v>
+        <v>1</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>45818.80165224537</v>
+        <v>45825.89055887731</v>
       </c>
       <c r="G99" t="n">
-        <v>143.6</v>
+        <v>21.21</v>
       </c>
       <c r="H99" t="n">
-        <v>147.68</v>
+        <v>19.17</v>
       </c>
       <c r="I99" t="n">
-        <v>14.99</v>
+        <v>21.21</v>
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
@@ -5317,18 +5317,18 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>0.43</v>
+        <v>-2.04</v>
       </c>
       <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="n">
-        <v>1843470413</v>
+        <v>1461331124</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5337,19 +5337,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.4729</v>
+        <v>0.3752</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>45804.66637251157</v>
+        <v>45553.65374138889</v>
       </c>
       <c r="G100" t="n">
-        <v>42.29</v>
+        <v>50.99</v>
       </c>
       <c r="H100" t="n">
-        <v>44.95</v>
+        <v>65.81</v>
       </c>
       <c r="I100" t="n">
-        <v>20</v>
+        <v>19.13</v>
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
@@ -5366,18 +5366,18 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>1.26</v>
+        <v>5.56</v>
       </c>
       <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="n">
-        <v>1559803984</v>
+        <v>1666451221</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5386,19 +5386,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.1076</v>
+        <v>0.0001</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>45628.86014383102</v>
+        <v>45708.68022634259</v>
       </c>
       <c r="G101" t="n">
-        <v>139.4</v>
+        <v>43</v>
       </c>
       <c r="H101" t="n">
-        <v>127.64</v>
+        <v>44.56</v>
       </c>
       <c r="I101" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -5415,18 +5415,18 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>-1.27</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="n">
-        <v>1648733962</v>
+        <v>1806980496</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5435,19 +5435,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.081</v>
+        <v>1</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>45695.85463682871</v>
+        <v>45783.83190503472</v>
       </c>
       <c r="G102" t="n">
-        <v>129.56</v>
+        <v>16.12</v>
       </c>
       <c r="H102" t="n">
-        <v>127.64</v>
+        <v>20.27</v>
       </c>
       <c r="I102" t="n">
-        <v>10.49</v>
+        <v>16.12</v>
       </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
@@ -5464,18 +5464,18 @@
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>-0.15</v>
+        <v>4.15</v>
       </c>
       <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="n">
-        <v>1882283184</v>
+        <v>1867461578</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>BAP</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5484,19 +5484,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.4835</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>45826.76569390047</v>
+        <v>45818.90835071759</v>
       </c>
       <c r="G103" t="n">
-        <v>20.69</v>
+        <v>216.54</v>
       </c>
       <c r="H103" t="n">
-        <v>19.19</v>
+        <v>251.42</v>
       </c>
       <c r="I103" t="n">
-        <v>10</v>
+        <v>19.99</v>
       </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
@@ -5513,18 +5513,18 @@
         <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>-0.72</v>
+        <v>3.22</v>
       </c>
       <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="n">
-        <v>1923259795</v>
+        <v>1830410729</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5533,19 +5533,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.4424</v>
+        <v>0.1091</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>45853.65609353009</v>
+        <v>45796.82476561343</v>
       </c>
       <c r="G104" t="n">
-        <v>22.59</v>
+        <v>33.66</v>
       </c>
       <c r="H104" t="n">
-        <v>23.81</v>
+        <v>31.13</v>
       </c>
       <c r="I104" t="n">
-        <v>9.99</v>
+        <v>3.67</v>
       </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
@@ -5562,18 +5562,18 @@
         <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>0.54</v>
+        <v>-0.27</v>
       </c>
       <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="n">
-        <v>1744879358</v>
+        <v>1599455288</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5582,19 +5582,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.2701</v>
+        <v>0.2195</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>45751.73925940973</v>
+        <v>45663.73750263889</v>
       </c>
       <c r="G105" t="n">
-        <v>148.09</v>
+        <v>45.55</v>
       </c>
       <c r="H105" t="n">
-        <v>240.32</v>
+        <v>32.92</v>
       </c>
       <c r="I105" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
@@ -5611,18 +5611,18 @@
         <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>24.91</v>
+        <v>-2.77</v>
       </c>
       <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="n">
-        <v>1517510856</v>
+        <v>1744879358</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5631,19 +5631,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.0602</v>
+        <v>0.2701</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>45597.61014849537</v>
+        <v>45751.73925940973</v>
       </c>
       <c r="G106" t="n">
-        <v>166.03</v>
+        <v>148.09</v>
       </c>
       <c r="H106" t="n">
-        <v>145.63</v>
+        <v>239.01</v>
       </c>
       <c r="I106" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
@@ -5660,18 +5660,18 @@
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>-1.23</v>
+        <v>24.56</v>
       </c>
       <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="n">
-        <v>1869077157</v>
+        <v>1923258184</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5680,19 +5680,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.3061</v>
+        <v>0.0298</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>45819.6742621412</v>
+        <v>45853.6557568287</v>
       </c>
       <c r="G107" t="n">
-        <v>13.285</v>
+        <v>19.43</v>
       </c>
       <c r="H107" t="n">
-        <v>12.805</v>
+        <v>20.48</v>
       </c>
       <c r="I107" t="n">
-        <v>4.69</v>
+        <v>0.58</v>
       </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
@@ -5709,18 +5709,18 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>-0.11</v>
+        <v>0.03</v>
       </c>
       <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="n">
-        <v>1806977521</v>
+        <v>1648737122</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5729,19 +5729,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.3367</v>
+        <v>0.001</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>45783.8305750463</v>
+        <v>45695.85619950231</v>
       </c>
       <c r="G108" t="n">
-        <v>29.7</v>
+        <v>408.33</v>
       </c>
       <c r="H108" t="n">
-        <v>32.28</v>
+        <v>520.01</v>
       </c>
       <c r="I108" t="n">
-        <v>10</v>
+        <v>0.41</v>
       </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
@@ -5758,18 +5758,18 @@
         <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>0.87</v>
+        <v>0.11</v>
       </c>
       <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="n">
-        <v>1644788775</v>
+        <v>1895465445</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5778,19 +5778,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.2987</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>45693.85093391204</v>
+        <v>45834.6539484375</v>
       </c>
       <c r="G109" t="n">
-        <v>144.94</v>
+        <v>33.47</v>
       </c>
       <c r="H109" t="n">
-        <v>145.63</v>
+        <v>32.92</v>
       </c>
       <c r="I109" t="n">
-        <v>10.99</v>
+        <v>10</v>
       </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
@@ -5807,18 +5807,18 @@
         <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>0.05</v>
+        <v>-0.17</v>
       </c>
       <c r="Q109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="n">
-        <v>1926287328</v>
+        <v>1727574394</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5827,19 +5827,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.5476</v>
+        <v>1</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>45854.82177967593</v>
+        <v>45743.76658678241</v>
       </c>
       <c r="G110" t="n">
-        <v>18.26</v>
+        <v>21.13</v>
       </c>
       <c r="H110" t="n">
-        <v>19.19</v>
+        <v>19.17</v>
       </c>
       <c r="I110" t="n">
-        <v>10</v>
+        <v>21.13</v>
       </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
@@ -5856,18 +5856,18 @@
         <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>0.51</v>
+        <v>-1.96</v>
       </c>
       <c r="Q110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="n">
-        <v>1824477589</v>
+        <v>1843469729</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5876,19 +5876,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.2344</v>
+        <v>0.0956</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>45792.64732982639</v>
+        <v>45804.66615450232</v>
       </c>
       <c r="G111" t="n">
-        <v>42.66</v>
+        <v>156.9</v>
       </c>
       <c r="H111" t="n">
-        <v>43.48</v>
+        <v>199.86</v>
       </c>
       <c r="I111" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
@@ -5905,7 +5905,7 @@
         <v>0</v>
       </c>
       <c r="P111" t="n">
-        <v>0.19</v>
+        <v>4.11</v>
       </c>
       <c r="Q111" t="inlineStr"/>
     </row>
@@ -5934,7 +5934,7 @@
         <v>44.24</v>
       </c>
       <c r="H112" t="n">
-        <v>51.22</v>
+        <v>51.35</v>
       </c>
       <c r="I112" t="n">
         <v>44.24</v>
@@ -5954,18 +5954,18 @@
         <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>6.98</v>
+        <v>7.11</v>
       </c>
       <c r="Q112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="n">
-        <v>1727591551</v>
+        <v>1582714896</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5974,19 +5974,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1</v>
+        <v>0.4847</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>45743.77389555555</v>
+        <v>45645.89066263889</v>
       </c>
       <c r="G113" t="n">
-        <v>72.87</v>
+        <v>20.62</v>
       </c>
       <c r="H113" t="n">
-        <v>73.02</v>
+        <v>20.48</v>
       </c>
       <c r="I113" t="n">
-        <v>72.87</v>
+        <v>9.99</v>
       </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
@@ -6003,45 +6003,27 @@
         <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>0.15</v>
+        <v>-0.06</v>
       </c>
       <c r="Q113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
-      <c r="B114" t="n">
-        <v>1422773288</v>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E114" t="n">
-        <v>0.483</v>
-      </c>
-      <c r="F114" s="2" t="n">
-        <v>45518.84428523148</v>
-      </c>
-      <c r="G114" t="n">
-        <v>51.24</v>
-      </c>
-      <c r="H114" t="n">
-        <v>59.79</v>
-      </c>
-      <c r="I114" t="n">
-        <v>24.75</v>
-      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
-      <c r="L114" t="n">
-        <v>0</v>
-      </c>
+      <c r="L114" t="inlineStr"/>
       <c r="M114" t="n">
         <v>0</v>
       </c>
@@ -6052,628 +6034,9 @@
         <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>4.13</v>
+        <v>161.44</v>
       </c>
       <c r="Q114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr"/>
-      <c r="B115" t="n">
-        <v>1817256440</v>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>EXC</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E115" t="n">
-        <v>0.2267</v>
-      </c>
-      <c r="F115" s="2" t="n">
-        <v>45789.64787115741</v>
-      </c>
-      <c r="G115" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="H115" t="n">
-        <v>43.48</v>
-      </c>
-      <c r="I115" t="n">
-        <v>10</v>
-      </c>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" t="n">
-        <v>0</v>
-      </c>
-      <c r="N115" t="n">
-        <v>0</v>
-      </c>
-      <c r="O115" t="n">
-        <v>0</v>
-      </c>
-      <c r="P115" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="Q115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr"/>
-      <c r="B116" t="n">
-        <v>1582723120</v>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E116" t="n">
-        <v>0.3755</v>
-      </c>
-      <c r="F116" s="2" t="n">
-        <v>45645.89511640046</v>
-      </c>
-      <c r="G116" t="n">
-        <v>53.26</v>
-      </c>
-      <c r="H116" t="n">
-        <v>59.79</v>
-      </c>
-      <c r="I116" t="n">
-        <v>20</v>
-      </c>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" t="n">
-        <v>0</v>
-      </c>
-      <c r="N116" t="n">
-        <v>0</v>
-      </c>
-      <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q116" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr"/>
-      <c r="B117" t="n">
-        <v>1880442840</v>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E117" t="n">
-        <v>0.2535</v>
-      </c>
-      <c r="F117" s="2" t="n">
-        <v>45825.89113450232</v>
-      </c>
-      <c r="G117" t="n">
-        <v>59.15</v>
-      </c>
-      <c r="H117" t="n">
-        <v>59.79</v>
-      </c>
-      <c r="I117" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" t="n">
-        <v>0</v>
-      </c>
-      <c r="N117" t="n">
-        <v>0</v>
-      </c>
-      <c r="O117" t="n">
-        <v>0</v>
-      </c>
-      <c r="P117" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="Q117" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr"/>
-      <c r="B118" t="n">
-        <v>1867458993</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E118" t="n">
-        <v>0.3417</v>
-      </c>
-      <c r="F118" s="2" t="n">
-        <v>45818.90699613426</v>
-      </c>
-      <c r="G118" t="n">
-        <v>58.53</v>
-      </c>
-      <c r="H118" t="n">
-        <v>59.79</v>
-      </c>
-      <c r="I118" t="n">
-        <v>20</v>
-      </c>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="n">
-        <v>0</v>
-      </c>
-      <c r="M118" t="n">
-        <v>0</v>
-      </c>
-      <c r="N118" t="n">
-        <v>0</v>
-      </c>
-      <c r="O118" t="n">
-        <v>0</v>
-      </c>
-      <c r="P118" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="Q118" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr"/>
-      <c r="B119" t="n">
-        <v>1744930699</v>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>BND</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E119" t="n">
-        <v>1</v>
-      </c>
-      <c r="F119" s="2" t="n">
-        <v>45751.74534789352</v>
-      </c>
-      <c r="G119" t="n">
-        <v>74.13</v>
-      </c>
-      <c r="H119" t="n">
-        <v>73.02</v>
-      </c>
-      <c r="I119" t="n">
-        <v>74.13</v>
-      </c>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="n">
-        <v>0</v>
-      </c>
-      <c r="M119" t="n">
-        <v>0</v>
-      </c>
-      <c r="N119" t="n">
-        <v>0</v>
-      </c>
-      <c r="O119" t="n">
-        <v>0</v>
-      </c>
-      <c r="P119" t="n">
-        <v>-1.11</v>
-      </c>
-      <c r="Q119" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr"/>
-      <c r="B120" t="n">
-        <v>1932757037</v>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>AGIO</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E120" t="n">
-        <v>0.2511</v>
-      </c>
-      <c r="F120" s="2" t="n">
-        <v>45859.74017836805</v>
-      </c>
-      <c r="G120" t="n">
-        <v>39.85</v>
-      </c>
-      <c r="H120" t="n">
-        <v>40.39</v>
-      </c>
-      <c r="I120" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="n">
-        <v>0</v>
-      </c>
-      <c r="M120" t="n">
-        <v>0</v>
-      </c>
-      <c r="N120" t="n">
-        <v>0</v>
-      </c>
-      <c r="O120" t="n">
-        <v>0</v>
-      </c>
-      <c r="P120" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="Q120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr"/>
-      <c r="B121" t="n">
-        <v>1680993370</v>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>VWO</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E121" t="n">
-        <v>1</v>
-      </c>
-      <c r="F121" s="2" t="n">
-        <v>45716.85638861111</v>
-      </c>
-      <c r="G121" t="n">
-        <v>44.49</v>
-      </c>
-      <c r="H121" t="n">
-        <v>51.22</v>
-      </c>
-      <c r="I121" t="n">
-        <v>44.49</v>
-      </c>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="n">
-        <v>0</v>
-      </c>
-      <c r="M121" t="n">
-        <v>0</v>
-      </c>
-      <c r="N121" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" t="n">
-        <v>0</v>
-      </c>
-      <c r="P121" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="Q121" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr"/>
-      <c r="B122" t="n">
-        <v>1554741910</v>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>ING</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E122" t="n">
-        <v>0.3495</v>
-      </c>
-      <c r="F122" s="2" t="n">
-        <v>45623.74951116898</v>
-      </c>
-      <c r="G122" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="H122" t="n">
-        <v>23.81</v>
-      </c>
-      <c r="I122" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="n">
-        <v>0</v>
-      </c>
-      <c r="M122" t="n">
-        <v>0</v>
-      </c>
-      <c r="N122" t="n">
-        <v>0</v>
-      </c>
-      <c r="O122" t="n">
-        <v>0</v>
-      </c>
-      <c r="P122" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Q122" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr"/>
-      <c r="B123" t="n">
-        <v>1648735305</v>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>APA</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E123" t="n">
-        <v>0.4576</v>
-      </c>
-      <c r="F123" s="2" t="n">
-        <v>45695.85530675926</v>
-      </c>
-      <c r="G123" t="n">
-        <v>21.85</v>
-      </c>
-      <c r="H123" t="n">
-        <v>19.19</v>
-      </c>
-      <c r="I123" t="n">
-        <v>10</v>
-      </c>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="n">
-        <v>0</v>
-      </c>
-      <c r="M123" t="n">
-        <v>0</v>
-      </c>
-      <c r="N123" t="n">
-        <v>0</v>
-      </c>
-      <c r="O123" t="n">
-        <v>0</v>
-      </c>
-      <c r="P123" t="n">
-        <v>-1.22</v>
-      </c>
-      <c r="Q123" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr"/>
-      <c r="B124" t="n">
-        <v>1885700231</v>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E124" t="n">
-        <v>0.0081</v>
-      </c>
-      <c r="F124" s="2" t="n">
-        <v>45828.65147924769</v>
-      </c>
-      <c r="G124" t="n">
-        <v>534.86</v>
-      </c>
-      <c r="H124" t="n">
-        <v>561</v>
-      </c>
-      <c r="I124" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="n">
-        <v>0</v>
-      </c>
-      <c r="M124" t="n">
-        <v>0</v>
-      </c>
-      <c r="N124" t="n">
-        <v>0</v>
-      </c>
-      <c r="O124" t="n">
-        <v>0</v>
-      </c>
-      <c r="P124" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="Q124" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr"/>
-      <c r="B125" t="n">
-        <v>1923256224</v>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>YPF</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E125" t="n">
-        <v>0.6457000000000001</v>
-      </c>
-      <c r="F125" s="2" t="n">
-        <v>45853.65543140046</v>
-      </c>
-      <c r="G125" t="n">
-        <v>30.97</v>
-      </c>
-      <c r="H125" t="n">
-        <v>32.28</v>
-      </c>
-      <c r="I125" t="n">
-        <v>20</v>
-      </c>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" t="n">
-        <v>0</v>
-      </c>
-      <c r="N125" t="n">
-        <v>0</v>
-      </c>
-      <c r="O125" t="n">
-        <v>0</v>
-      </c>
-      <c r="P125" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="Q125" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr"/>
-      <c r="B126" t="n">
-        <v>1599431096</v>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="E126" t="n">
-        <v>0.1013</v>
-      </c>
-      <c r="F126" s="2" t="n">
-        <v>45663.73014731482</v>
-      </c>
-      <c r="G126" t="n">
-        <v>148.02</v>
-      </c>
-      <c r="H126" t="n">
-        <v>145.63</v>
-      </c>
-      <c r="I126" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" t="n">
-        <v>0</v>
-      </c>
-      <c r="N126" t="n">
-        <v>0</v>
-      </c>
-      <c r="O126" t="n">
-        <v>0</v>
-      </c>
-      <c r="P126" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="Q126" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr"/>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="n">
-        <v>0</v>
-      </c>
-      <c r="N127" t="n">
-        <v>0</v>
-      </c>
-      <c r="O127" t="n">
-        <v>0</v>
-      </c>
-      <c r="P127" t="n">
-        <v>131.45</v>
-      </c>
-      <c r="Q127" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Stock Selection/OPEN POSITION.xlsx
+++ b/Stock Selection/OPEN POSITION.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q114"/>
+  <dimension ref="A1:Q142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,11 +522,11 @@
     <row r="2">
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="n">
-        <v>1744916452</v>
+        <v>1867458993</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.4245</v>
+        <v>0.3417</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45751.74230173611</v>
+        <v>45818.90699613426</v>
       </c>
       <c r="G2" t="n">
-        <v>17.54</v>
+        <v>58.53</v>
       </c>
       <c r="H2" t="n">
-        <v>24.87</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>7.45</v>
+        <v>20</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -564,18 +564,18 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>3.11</v>
+        <v>2.38</v>
       </c>
       <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="n">
-        <v>1923271589</v>
+        <v>1869077157</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -584,19 +584,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4478</v>
+        <v>0.3061</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45853.65794861111</v>
+        <v>45819.6742621412</v>
       </c>
       <c r="G3" t="n">
-        <v>44.66</v>
+        <v>13.285</v>
       </c>
       <c r="H3" t="n">
-        <v>49.41</v>
+        <v>16.025</v>
       </c>
       <c r="I3" t="n">
-        <v>20</v>
+        <v>4.69</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -613,18 +613,18 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.13</v>
+        <v>1.09</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="n">
-        <v>1843477152</v>
+        <v>1582723120</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -633,19 +633,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1198</v>
+        <v>0.3755</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45804.66724922453</v>
+        <v>45645.89511640046</v>
       </c>
       <c r="G4" t="n">
-        <v>17.86</v>
+        <v>53.26</v>
       </c>
       <c r="H4" t="n">
-        <v>20.27</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>2.14</v>
+        <v>20</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -662,14 +662,14 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.29</v>
+        <v>4.6</v>
       </c>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="n">
-        <v>1869077178</v>
+        <v>1923250768</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45819.67426902778</v>
+        <v>45853.65447396991</v>
       </c>
       <c r="G5" t="n">
-        <v>13.285</v>
+        <v>12.76</v>
       </c>
       <c r="H5" t="n">
-        <v>16.515</v>
+        <v>16.025</v>
       </c>
       <c r="I5" t="n">
-        <v>15.31</v>
+        <v>13</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -711,18 +711,18 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.92</v>
+        <v>3.44</v>
       </c>
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="n">
-        <v>1824475555</v>
+        <v>2002501482</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0.0526</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45792.64702015046</v>
+        <v>45902.65588916666</v>
       </c>
       <c r="G6" t="n">
-        <v>21.66</v>
+        <v>190.17</v>
       </c>
       <c r="H6" t="n">
-        <v>19.17</v>
+        <v>210.26</v>
       </c>
       <c r="I6" t="n">
-        <v>21.66</v>
+        <v>10</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -760,18 +760,18 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.49</v>
+        <v>1.06</v>
       </c>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="n">
-        <v>1554741956</v>
+        <v>1993384302</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -780,19 +780,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.0495</v>
+        <v>0.1347</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45623.74952237269</v>
+        <v>45896.66850298611</v>
       </c>
       <c r="G7" t="n">
-        <v>15.3</v>
+        <v>74.23</v>
       </c>
       <c r="H7" t="n">
-        <v>24.87</v>
+        <v>70.22</v>
       </c>
       <c r="I7" t="n">
-        <v>0.76</v>
+        <v>10</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -809,18 +809,18 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.47</v>
+        <v>-0.54</v>
       </c>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>1631475148</v>
+        <v>1680993370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.2592</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45685.83625201389</v>
+        <v>45716.85638861111</v>
       </c>
       <c r="G8" t="n">
-        <v>38.58</v>
+        <v>44.49</v>
       </c>
       <c r="H8" t="n">
-        <v>32.92</v>
+        <v>54.49</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>44.49</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -858,18 +858,18 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.47</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>1817264187</v>
+        <v>1976499401</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -878,19 +878,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.4757</v>
+        <v>0.8064</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45789.64859377315</v>
+        <v>45884.83731814815</v>
       </c>
       <c r="G9" t="n">
-        <v>42.02</v>
+        <v>49.6</v>
       </c>
       <c r="H9" t="n">
-        <v>49.41</v>
+        <v>49.16</v>
       </c>
       <c r="I9" t="n">
-        <v>19.99</v>
+        <v>40</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -907,18 +907,18 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.51</v>
+        <v>-0.36</v>
       </c>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
-        <v>1843468958</v>
+        <v>1631475148</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.0669</v>
+        <v>0.2592</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45804.66597149306</v>
+        <v>45685.83625201389</v>
       </c>
       <c r="G10" t="n">
-        <v>67.93000000000001</v>
+        <v>38.58</v>
       </c>
       <c r="H10" t="n">
-        <v>75.44</v>
+        <v>27.15</v>
       </c>
       <c r="I10" t="n">
-        <v>4.54</v>
+        <v>10</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -956,18 +956,18 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.51</v>
+        <v>-2.96</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
-        <v>1559803221</v>
+        <v>1744916497</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -976,19 +976,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.092</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45628.85951927083</v>
+        <v>45751.74231563658</v>
       </c>
       <c r="G11" t="n">
-        <v>162.85</v>
+        <v>17.54</v>
       </c>
       <c r="H11" t="n">
-        <v>150.32</v>
+        <v>25.33</v>
       </c>
       <c r="I11" t="n">
-        <v>14.98</v>
+        <v>17.54</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -1005,18 +1005,18 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.15</v>
+        <v>7.79</v>
       </c>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>1882278057</v>
+        <v>1666459270</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1025,19 +1025,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.0432</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>45826.76262912037</v>
+        <v>45708.68166530092</v>
       </c>
       <c r="G12" t="n">
-        <v>346.61</v>
+        <v>17.18</v>
       </c>
       <c r="H12" t="n">
-        <v>344.31</v>
+        <v>25.33</v>
       </c>
       <c r="I12" t="n">
-        <v>14.97</v>
+        <v>17.18</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -1054,18 +1054,18 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1</v>
+        <v>8.15</v>
       </c>
       <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>1882283184</v>
+        <v>1882281884</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.4835</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>45826.76569390047</v>
+        <v>45826.76479001158</v>
       </c>
       <c r="G13" t="n">
-        <v>20.69</v>
+        <v>138.84</v>
       </c>
       <c r="H13" t="n">
-        <v>20.48</v>
+        <v>148.1</v>
       </c>
       <c r="I13" t="n">
         <v>10</v>
@@ -1103,18 +1103,18 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1</v>
+        <v>0.66</v>
       </c>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="n">
-        <v>1928218937</v>
+        <v>1888686062</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0.2903</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>45855.75970359953</v>
+        <v>45831.64964792824</v>
       </c>
       <c r="G14" t="n">
-        <v>20.24</v>
+        <v>34.36</v>
       </c>
       <c r="H14" t="n">
-        <v>19.17</v>
+        <v>27.15</v>
       </c>
       <c r="I14" t="n">
-        <v>20.24</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -1152,18 +1152,18 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.07</v>
+        <v>-2.09</v>
       </c>
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="n">
-        <v>1806980482</v>
+        <v>1972092684</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.2406</v>
+        <v>1</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>45783.83189613426</v>
+        <v>45882.68269449074</v>
       </c>
       <c r="G15" t="n">
-        <v>16.12</v>
+        <v>18.8</v>
       </c>
       <c r="H15" t="n">
-        <v>20.27</v>
+        <v>18.4</v>
       </c>
       <c r="I15" t="n">
-        <v>3.88</v>
+        <v>18.8</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1201,14 +1201,14 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>-0.4</v>
       </c>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="n">
-        <v>1845429956</v>
+        <v>1845429980</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.4821</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>45805.66180811343</v>
+        <v>45805.66181400463</v>
       </c>
       <c r="G16" t="n">
-        <v>13.275</v>
+        <v>13.27</v>
       </c>
       <c r="H16" t="n">
-        <v>16.515</v>
+        <v>16.025</v>
       </c>
       <c r="I16" t="n">
-        <v>7.28</v>
+        <v>15.09</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1250,18 +1250,18 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.99</v>
+        <v>3.81</v>
       </c>
       <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="n">
-        <v>1499061783</v>
+        <v>1845429956</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1270,19 +1270,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.0001</v>
+        <v>0.4821</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>45582.73996892361</v>
+        <v>45805.66180811343</v>
       </c>
       <c r="G17" t="n">
-        <v>232.2</v>
+        <v>13.275</v>
       </c>
       <c r="H17" t="n">
-        <v>231.63</v>
+        <v>16.025</v>
       </c>
       <c r="I17" t="n">
-        <v>0.02</v>
+        <v>7.28</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1299,18 +1299,18 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
-        <v>1599448103</v>
+        <v>1729617775</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.2839</v>
+        <v>0.0546</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45663.73506711805</v>
+        <v>45744.71339734954</v>
       </c>
       <c r="G18" t="n">
-        <v>52.83</v>
+        <v>165.35</v>
       </c>
       <c r="H18" t="n">
-        <v>65.81</v>
+        <v>262.31</v>
       </c>
       <c r="I18" t="n">
-        <v>15</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1348,18 +1348,18 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.68</v>
+        <v>5.29</v>
       </c>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="n">
-        <v>1880442840</v>
+        <v>1712850989</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1368,19 +1368,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.2535</v>
+        <v>0.0002</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45825.89113450232</v>
+        <v>45734.85576775463</v>
       </c>
       <c r="G19" t="n">
-        <v>59.15</v>
+        <v>160.64</v>
       </c>
       <c r="H19" t="n">
-        <v>65.81</v>
+        <v>249.34</v>
       </c>
       <c r="I19" t="n">
-        <v>14.99</v>
+        <v>0.03</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1397,18 +1397,18 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.69</v>
+        <v>0.02</v>
       </c>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
-        <v>1729617775</v>
+        <v>2025662892</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1417,19 +1417,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.0546</v>
+        <v>0.8196</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45744.71339734954</v>
+        <v>45915.72913914352</v>
       </c>
       <c r="G20" t="n">
-        <v>165.35</v>
+        <v>24.39</v>
       </c>
       <c r="H20" t="n">
-        <v>239.01</v>
+        <v>24.73</v>
       </c>
       <c r="I20" t="n">
-        <v>9.029999999999999</v>
+        <v>19.99</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1446,18 +1446,18 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>4.02</v>
+        <v>0.28</v>
       </c>
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="n">
-        <v>1867193336</v>
+        <v>1995249699</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1466,19 +1466,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0.4888</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45818.80084483796</v>
+        <v>45897.61086020833</v>
       </c>
       <c r="G21" t="n">
-        <v>17.64</v>
+        <v>87.16500000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>20.27</v>
+        <v>87.7</v>
       </c>
       <c r="I21" t="n">
-        <v>17.64</v>
+        <v>49.99</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1495,18 +1495,18 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="n">
-        <v>1727591551</v>
+        <v>1727563010</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1518,16 +1518,16 @@
         <v>1</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>45743.77389555555</v>
+        <v>45743.76106726852</v>
       </c>
       <c r="G22" t="n">
-        <v>72.87</v>
+        <v>46.11</v>
       </c>
       <c r="H22" t="n">
-        <v>73.42</v>
+        <v>54.49</v>
       </c>
       <c r="I22" t="n">
-        <v>72.87</v>
+        <v>46.11</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -1544,18 +1544,18 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.55</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="n">
-        <v>1824476420</v>
+        <v>1982273555</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.1548</v>
+        <v>0.0439</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>45792.64714148148</v>
+        <v>45889.64957444445</v>
       </c>
       <c r="G23" t="n">
-        <v>129.17</v>
+        <v>228</v>
       </c>
       <c r="H23" t="n">
-        <v>150.32</v>
+        <v>262.31</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>10.01</v>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -1593,18 +1593,18 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>3.27</v>
+        <v>1.51</v>
       </c>
       <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="n">
-        <v>1867194722</v>
+        <v>1495551484</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0.1914</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45818.80135700232</v>
+        <v>45580.70648087963</v>
       </c>
       <c r="G24" t="n">
-        <v>21.27</v>
+        <v>135.82</v>
       </c>
       <c r="H24" t="n">
-        <v>19.17</v>
+        <v>123.49</v>
       </c>
       <c r="I24" t="n">
-        <v>21.27</v>
+        <v>26</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1642,18 +1642,18 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.1</v>
+        <v>-2.36</v>
       </c>
       <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="n">
-        <v>1662993636</v>
+        <v>1744916452</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1662,19 +1662,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0.4245</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>45706.87026833333</v>
+        <v>45751.74230173611</v>
       </c>
       <c r="G25" t="n">
-        <v>20.65</v>
+        <v>17.54</v>
       </c>
       <c r="H25" t="n">
-        <v>19.17</v>
+        <v>25.33</v>
       </c>
       <c r="I25" t="n">
-        <v>20.65</v>
+        <v>7.45</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -1691,14 +1691,14 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.48</v>
+        <v>3.3</v>
       </c>
       <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="n">
-        <v>1621495187</v>
+        <v>1653137218</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1711,19 +1711,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.2318</v>
+        <v>0.277</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>45678.83178196759</v>
+        <v>45699.85152199074</v>
       </c>
       <c r="G26" t="n">
-        <v>43.27</v>
+        <v>36.1</v>
       </c>
       <c r="H26" t="n">
-        <v>32.92</v>
+        <v>27.15</v>
       </c>
       <c r="I26" t="n">
-        <v>10.03</v>
+        <v>10</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -1740,18 +1740,18 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.4</v>
+        <v>-2.48</v>
       </c>
       <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="n">
-        <v>1972092684</v>
+        <v>1744930699</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>BND</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1763,16 +1763,16 @@
         <v>1</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>45882.68269449074</v>
+        <v>45751.74534789352</v>
       </c>
       <c r="G27" t="n">
-        <v>18.8</v>
+        <v>74.13</v>
       </c>
       <c r="H27" t="n">
-        <v>19.17</v>
+        <v>74.58</v>
       </c>
       <c r="I27" t="n">
-        <v>18.8</v>
+        <v>74.13</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -1789,18 +1789,18 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.37</v>
+        <v>0.45</v>
       </c>
       <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="n">
-        <v>1845431561</v>
+        <v>1830408508</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1809,19 +1809,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.0179</v>
+        <v>0.5793</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>45805.66210755787</v>
+        <v>45796.82346997685</v>
       </c>
       <c r="G28" t="n">
-        <v>30.57</v>
+        <v>17.26</v>
       </c>
       <c r="H28" t="n">
-        <v>37.01</v>
+        <v>24.13</v>
       </c>
       <c r="I28" t="n">
-        <v>0.55</v>
+        <v>10</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -1838,18 +1838,18 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0.11</v>
+        <v>3.98</v>
       </c>
       <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
-        <v>1867458993</v>
+        <v>1867197360</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1858,19 +1858,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.3417</v>
+        <v>0.0765</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>45818.90699613426</v>
+        <v>45818.80265583334</v>
       </c>
       <c r="G29" t="n">
-        <v>58.53</v>
+        <v>131.96</v>
       </c>
       <c r="H29" t="n">
-        <v>65.81</v>
+        <v>141.21</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>10.09</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -1887,18 +1887,18 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.49</v>
+        <v>0.71</v>
       </c>
       <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
-        <v>1754302454</v>
+        <v>1843477272</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1907,19 +1907,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.3673</v>
+        <v>1</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45755.88025324074</v>
+        <v>45804.66725678241</v>
       </c>
       <c r="G30" t="n">
-        <v>27.17</v>
+        <v>17.86</v>
       </c>
       <c r="H30" t="n">
-        <v>32.92</v>
+        <v>20.75</v>
       </c>
       <c r="I30" t="n">
-        <v>9.98</v>
+        <v>17.86</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -1936,18 +1936,18 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.11</v>
+        <v>2.89</v>
       </c>
       <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="n">
-        <v>1955448954</v>
+        <v>1599455288</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1956,19 +1956,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.3236</v>
+        <v>0.2195</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45873.64722828704</v>
+        <v>45663.73750263889</v>
       </c>
       <c r="G31" t="n">
-        <v>30.93</v>
+        <v>45.55</v>
       </c>
       <c r="H31" t="n">
-        <v>37.01</v>
+        <v>27.15</v>
       </c>
       <c r="I31" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1985,18 +1985,18 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.97</v>
+        <v>-4.04</v>
       </c>
       <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="n">
-        <v>1975988073</v>
+        <v>1923258249</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2005,19 +2005,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.0469</v>
+        <v>1</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45884.6572796875</v>
+        <v>45853.65576626157</v>
       </c>
       <c r="G32" t="n">
-        <v>319.83</v>
+        <v>19.41</v>
       </c>
       <c r="H32" t="n">
-        <v>317.43</v>
+        <v>24.13</v>
       </c>
       <c r="I32" t="n">
-        <v>15</v>
+        <v>19.41</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -2034,18 +2034,18 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>-0.11</v>
+        <v>4.72</v>
       </c>
       <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="n">
-        <v>1883977044</v>
+        <v>2017852950</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2054,19 +2054,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.345</v>
+        <v>1</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45827.66105774305</v>
+        <v>45910.65507498843</v>
       </c>
       <c r="G33" t="n">
-        <v>12.88</v>
+        <v>37.44</v>
       </c>
       <c r="H33" t="n">
-        <v>16.515</v>
+        <v>37.8</v>
       </c>
       <c r="I33" t="n">
-        <v>5.13</v>
+        <v>37.44</v>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -2083,18 +2083,18 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.51</v>
+        <v>0.36</v>
       </c>
       <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="n">
-        <v>1495551484</v>
+        <v>1635194117</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2103,19 +2103,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.1914</v>
+        <v>0.2479</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45580.70648087963</v>
+        <v>45687.85228493056</v>
       </c>
       <c r="G34" t="n">
-        <v>135.82</v>
+        <v>40.33</v>
       </c>
       <c r="H34" t="n">
-        <v>125.74</v>
+        <v>27.15</v>
       </c>
       <c r="I34" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
@@ -2132,18 +2132,18 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>-1.93</v>
+        <v>-3.27</v>
       </c>
       <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>1582735114</v>
+        <v>1997552824</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2152,19 +2152,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.0003</v>
+        <v>0.0429</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>45645.90076803241</v>
+        <v>45898.65627293981</v>
       </c>
       <c r="G35" t="n">
-        <v>130.51</v>
+        <v>233.17</v>
       </c>
       <c r="H35" t="n">
-        <v>148.15</v>
+        <v>262.31</v>
       </c>
       <c r="I35" t="n">
-        <v>0.04</v>
+        <v>10</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
@@ -2181,18 +2181,18 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>1811432805</v>
+        <v>1806977521</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2201,19 +2201,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.0467</v>
+        <v>0.3367</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45785.66143211805</v>
+        <v>45783.8305750463</v>
       </c>
       <c r="G36" t="n">
-        <v>128.46</v>
+        <v>29.7</v>
       </c>
       <c r="H36" t="n">
-        <v>199.86</v>
+        <v>27.15</v>
       </c>
       <c r="I36" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -2230,18 +2230,18 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>3.33</v>
+        <v>-0.86</v>
       </c>
       <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
-        <v>1843477272</v>
+        <v>1997561527</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2250,19 +2250,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0.1498</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>45804.66725678241</v>
+        <v>45898.65748991898</v>
       </c>
       <c r="G37" t="n">
-        <v>17.86</v>
+        <v>66.73</v>
       </c>
       <c r="H37" t="n">
-        <v>20.27</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>17.86</v>
+        <v>10</v>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
@@ -2279,18 +2279,18 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.41</v>
+        <v>-0.19</v>
       </c>
       <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>1666459270</v>
+        <v>1701100027</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2299,19 +2299,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0.7812</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45708.68166530092</v>
+        <v>45727.87202070602</v>
       </c>
       <c r="G38" t="n">
-        <v>17.18</v>
+        <v>19.2</v>
       </c>
       <c r="H38" t="n">
-        <v>24.87</v>
+        <v>24.13</v>
       </c>
       <c r="I38" t="n">
-        <v>17.18</v>
+        <v>15</v>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
@@ -2328,18 +2328,18 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>7.69</v>
+        <v>3.85</v>
       </c>
       <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
-        <v>1599449649</v>
+        <v>1817264187</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2348,19 +2348,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.4145</v>
+        <v>0.4757</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45663.73562525463</v>
+        <v>45789.64859377315</v>
       </c>
       <c r="G39" t="n">
-        <v>24.11</v>
+        <v>42.02</v>
       </c>
       <c r="H39" t="n">
-        <v>20.48</v>
+        <v>51.79</v>
       </c>
       <c r="I39" t="n">
-        <v>9.99</v>
+        <v>19.99</v>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -2377,18 +2377,18 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>-1.5</v>
+        <v>4.65</v>
       </c>
       <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="n">
-        <v>1882281884</v>
+        <v>1824482557</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2397,19 +2397,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.2641</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>45826.76479001158</v>
+        <v>45792.64805195602</v>
       </c>
       <c r="G40" t="n">
-        <v>138.84</v>
+        <v>56.78</v>
       </c>
       <c r="H40" t="n">
-        <v>148.15</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
@@ -2426,18 +2426,18 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.67</v>
+        <v>2.3</v>
       </c>
       <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="n">
-        <v>1923256224</v>
+        <v>1648735305</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2446,19 +2446,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.4576</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45853.65543140046</v>
+        <v>45695.85530675926</v>
       </c>
       <c r="G41" t="n">
-        <v>30.97</v>
+        <v>21.85</v>
       </c>
       <c r="H41" t="n">
-        <v>32.92</v>
+        <v>24.13</v>
       </c>
       <c r="I41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
@@ -2475,18 +2475,18 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="n">
-        <v>1653137218</v>
+        <v>1880442840</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2495,19 +2495,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.277</v>
+        <v>0.2535</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>45699.85152199074</v>
+        <v>45825.89113450232</v>
       </c>
       <c r="G42" t="n">
-        <v>36.1</v>
+        <v>59.15</v>
       </c>
       <c r="H42" t="n">
-        <v>32.92</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>10</v>
+        <v>14.99</v>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -2524,18 +2524,18 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>-0.88</v>
+        <v>1.62</v>
       </c>
       <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="n">
-        <v>1976499401</v>
+        <v>1880446729</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2544,19 +2544,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.8064</v>
+        <v>0.0772</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>45884.83731814815</v>
+        <v>45825.89315055555</v>
       </c>
       <c r="G43" t="n">
-        <v>49.6</v>
+        <v>129.62</v>
       </c>
       <c r="H43" t="n">
-        <v>49.63</v>
+        <v>141.21</v>
       </c>
       <c r="I43" t="n">
-        <v>40</v>
+        <v>10.01</v>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -2573,18 +2573,18 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0.02</v>
+        <v>0.89</v>
       </c>
       <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
-        <v>1830408508</v>
+        <v>1867195793</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2593,16 +2593,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.5793</v>
+        <v>0.2339</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45796.82346997685</v>
+        <v>45818.80180457176</v>
       </c>
       <c r="G44" t="n">
-        <v>17.26</v>
+        <v>42.74</v>
       </c>
       <c r="H44" t="n">
-        <v>20.48</v>
+        <v>43.22</v>
       </c>
       <c r="I44" t="n">
         <v>10</v>
@@ -2622,18 +2622,18 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1.86</v>
+        <v>0.11</v>
       </c>
       <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>1888686062</v>
+        <v>1867193304</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2642,19 +2642,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.2903</v>
+        <v>0.1337</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>45831.64964792824</v>
+        <v>45818.8008296412</v>
       </c>
       <c r="G45" t="n">
-        <v>34.36</v>
+        <v>17.64</v>
       </c>
       <c r="H45" t="n">
-        <v>32.92</v>
+        <v>20.75</v>
       </c>
       <c r="I45" t="n">
-        <v>9.970000000000001</v>
+        <v>2.36</v>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -2671,18 +2671,18 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>-0.41</v>
+        <v>0.41</v>
       </c>
       <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>1867462173</v>
+        <v>1563288050</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2691,19 +2691,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0626</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>45818.90866184028</v>
+        <v>45630.85583428241</v>
       </c>
       <c r="G46" t="n">
-        <v>77.93000000000001</v>
+        <v>159.74</v>
       </c>
       <c r="H46" t="n">
-        <v>93.67</v>
+        <v>141.21</v>
       </c>
       <c r="I46" t="n">
-        <v>0.65</v>
+        <v>10</v>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -2720,18 +2720,18 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.14</v>
+        <v>-1.16</v>
       </c>
       <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>1563288050</v>
+        <v>1923256224</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2740,19 +2740,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.0626</v>
+        <v>0.6457000000000001</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>45630.85583428241</v>
+        <v>45853.65543140046</v>
       </c>
       <c r="G47" t="n">
-        <v>159.74</v>
+        <v>30.97</v>
       </c>
       <c r="H47" t="n">
-        <v>150.32</v>
+        <v>27.15</v>
       </c>
       <c r="I47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -2769,18 +2769,18 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>-0.59</v>
+        <v>-2.47</v>
       </c>
       <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>1642762235</v>
+        <v>2020498366</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>BBAR</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2789,19 +2789,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.1572</v>
+        <v>1</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>45692.86612574074</v>
+        <v>45911.68945292824</v>
       </c>
       <c r="G48" t="n">
-        <v>127.16</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>125.74</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>19.99</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -2818,18 +2818,18 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>-0.22</v>
+        <v>-1.02</v>
       </c>
       <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
-        <v>1754304266</v>
+        <v>1970057305</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2838,19 +2838,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.7137</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45755.88055112268</v>
+        <v>45881.70511172454</v>
       </c>
       <c r="G49" t="n">
-        <v>14</v>
+        <v>35.88</v>
       </c>
       <c r="H49" t="n">
-        <v>20.48</v>
+        <v>36.4</v>
       </c>
       <c r="I49" t="n">
-        <v>9.99</v>
+        <v>2.57</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
@@ -2867,18 +2867,18 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>4.63</v>
+        <v>0.03</v>
       </c>
       <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
-        <v>1923259795</v>
+        <v>1997485943</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.4424</v>
+        <v>0.5157</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>45853.65609353009</v>
+        <v>45898.65185685185</v>
       </c>
       <c r="G50" t="n">
-        <v>22.59</v>
+        <v>19.39</v>
       </c>
       <c r="H50" t="n">
-        <v>24.87</v>
+        <v>20.75</v>
       </c>
       <c r="I50" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -2916,18 +2916,18 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1.01</v>
+        <v>0.7</v>
       </c>
       <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>1845429980</v>
+        <v>1981010841</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2936,19 +2936,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0.0425</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>45805.66181400463</v>
+        <v>45888.84617734954</v>
       </c>
       <c r="G51" t="n">
-        <v>13.27</v>
+        <v>235.53</v>
       </c>
       <c r="H51" t="n">
-        <v>16.515</v>
+        <v>262.31</v>
       </c>
       <c r="I51" t="n">
-        <v>15.09</v>
+        <v>10.01</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -2965,18 +2965,18 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>4.14</v>
+        <v>1.14</v>
       </c>
       <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
-        <v>1680993370</v>
+        <v>1499061783</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2985,19 +2985,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>0.0001</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>45716.85638861111</v>
+        <v>45582.73996892361</v>
       </c>
       <c r="G52" t="n">
-        <v>44.49</v>
+        <v>232.2</v>
       </c>
       <c r="H52" t="n">
-        <v>51.35</v>
+        <v>238.81</v>
       </c>
       <c r="I52" t="n">
-        <v>44.49</v>
+        <v>0.02</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
@@ -3014,18 +3014,18 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>6.86</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="n">
-        <v>1701100027</v>
+        <v>1754302454</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3034,19 +3034,19 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.7812</v>
+        <v>0.3673</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>45727.87202070602</v>
+        <v>45755.88025324074</v>
       </c>
       <c r="G53" t="n">
-        <v>19.2</v>
+        <v>27.17</v>
       </c>
       <c r="H53" t="n">
-        <v>20.48</v>
+        <v>27.15</v>
       </c>
       <c r="I53" t="n">
-        <v>15</v>
+        <v>9.98</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
@@ -3063,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>1</v>
+        <v>-0.01</v>
       </c>
       <c r="Q53" t="inlineStr"/>
     </row>
@@ -3092,7 +3092,7 @@
         <v>20.36</v>
       </c>
       <c r="H54" t="n">
-        <v>19.17</v>
+        <v>18.4</v>
       </c>
       <c r="I54" t="n">
         <v>20.36</v>
@@ -3112,14 +3112,14 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>-1.19</v>
+        <v>-1.96</v>
       </c>
       <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="n">
-        <v>1806979127</v>
+        <v>1744767540</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -3132,16 +3132,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.6361</v>
+        <v>0.643</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>45783.83125244213</v>
+        <v>45751.72316712963</v>
       </c>
       <c r="G55" t="n">
-        <v>15.72</v>
+        <v>15.55</v>
       </c>
       <c r="H55" t="n">
-        <v>20.48</v>
+        <v>24.13</v>
       </c>
       <c r="I55" t="n">
         <v>10</v>
@@ -3161,18 +3161,18 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>3.03</v>
+        <v>5.52</v>
       </c>
       <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="n">
-        <v>1843474191</v>
+        <v>1806980482</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3181,19 +3181,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.9372</v>
+        <v>0.2406</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>45804.66699503472</v>
+        <v>45783.83189613426</v>
       </c>
       <c r="G56" t="n">
-        <v>21.33</v>
+        <v>16.12</v>
       </c>
       <c r="H56" t="n">
-        <v>24.87</v>
+        <v>20.75</v>
       </c>
       <c r="I56" t="n">
-        <v>19.99</v>
+        <v>3.88</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
@@ -3210,18 +3210,18 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>3.32</v>
+        <v>1.11</v>
       </c>
       <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="n">
-        <v>1883977086</v>
+        <v>1885700231</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3230,19 +3230,19 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0.0081</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45827.66106613426</v>
+        <v>45828.65147924769</v>
       </c>
       <c r="G57" t="n">
-        <v>12.875</v>
+        <v>534.86</v>
       </c>
       <c r="H57" t="n">
-        <v>16.515</v>
+        <v>598.13</v>
       </c>
       <c r="I57" t="n">
-        <v>14.86</v>
+        <v>4.33</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
@@ -3259,18 +3259,18 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>4.37</v>
+        <v>0.51</v>
       </c>
       <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
-        <v>1932757037</v>
+        <v>1867196288</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3279,19 +3279,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.2511</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45859.74017836805</v>
+        <v>45818.80209099537</v>
       </c>
       <c r="G58" t="n">
-        <v>39.85</v>
+        <v>41.99</v>
       </c>
       <c r="H58" t="n">
-        <v>37.01</v>
+        <v>51.79</v>
       </c>
       <c r="I58" t="n">
-        <v>10.01</v>
+        <v>25</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
@@ -3308,18 +3308,18 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>-0.72</v>
+        <v>5.83</v>
       </c>
       <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="n">
-        <v>1744930699</v>
+        <v>1843469729</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3328,19 +3328,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0.0423</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>45751.74534789352</v>
+        <v>45804.66615450232</v>
       </c>
       <c r="G59" t="n">
-        <v>74.13</v>
+        <v>156.9</v>
       </c>
       <c r="H59" t="n">
-        <v>73.42</v>
+        <v>210.26</v>
       </c>
       <c r="I59" t="n">
-        <v>74.13</v>
+        <v>6.64</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
@@ -3357,18 +3357,18 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>-0.71</v>
+        <v>2.25</v>
       </c>
       <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="n">
-        <v>1923246263</v>
+        <v>1923258184</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3377,19 +3377,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>0.0298</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45853.6538128125</v>
+        <v>45853.6557568287</v>
       </c>
       <c r="G60" t="n">
-        <v>21.17</v>
+        <v>19.43</v>
       </c>
       <c r="H60" t="n">
-        <v>19.17</v>
+        <v>24.13</v>
       </c>
       <c r="I60" t="n">
-        <v>21.17</v>
+        <v>0.58</v>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
@@ -3406,14 +3406,14 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>-2</v>
+        <v>0.14</v>
       </c>
       <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="n">
-        <v>1648735305</v>
+        <v>2017777441</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -3426,16 +3426,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.4576</v>
+        <v>0.4582</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>45695.85530675926</v>
+        <v>45910.64656457176</v>
       </c>
       <c r="G61" t="n">
-        <v>21.85</v>
+        <v>21.82</v>
       </c>
       <c r="H61" t="n">
-        <v>20.48</v>
+        <v>24.13</v>
       </c>
       <c r="I61" t="n">
         <v>10</v>
@@ -3455,18 +3455,18 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>-0.63</v>
+        <v>1.06</v>
       </c>
       <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="n">
-        <v>1744929368</v>
+        <v>1993443280</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>BBVA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3475,19 +3475,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.0192</v>
+        <v>1</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>45751.74500871528</v>
+        <v>45896.67387811343</v>
       </c>
       <c r="G62" t="n">
-        <v>324.48</v>
+        <v>17.97</v>
       </c>
       <c r="H62" t="n">
-        <v>344.31</v>
+        <v>18.99</v>
       </c>
       <c r="I62" t="n">
-        <v>6.23</v>
+        <v>17.97</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
@@ -3504,18 +3504,18 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>0.38</v>
+        <v>1.02</v>
       </c>
       <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="n">
-        <v>1867196288</v>
+        <v>1727591551</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>BND</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3524,19 +3524,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.5953000000000001</v>
+        <v>1</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>45818.80209099537</v>
+        <v>45743.77389555555</v>
       </c>
       <c r="G63" t="n">
-        <v>41.99</v>
+        <v>72.87</v>
       </c>
       <c r="H63" t="n">
-        <v>49.41</v>
+        <v>74.58</v>
       </c>
       <c r="I63" t="n">
-        <v>25</v>
+        <v>72.87</v>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
@@ -3553,18 +3553,18 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>4.41</v>
+        <v>1.71</v>
       </c>
       <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="n">
-        <v>1666459175</v>
+        <v>1599449649</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3573,19 +3573,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.1641</v>
+        <v>0.0377</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>45708.68165298611</v>
+        <v>45663.73562525463</v>
       </c>
       <c r="G64" t="n">
-        <v>17.18</v>
+        <v>24.11</v>
       </c>
       <c r="H64" t="n">
-        <v>24.87</v>
+        <v>24.13</v>
       </c>
       <c r="I64" t="n">
-        <v>2.82</v>
+        <v>0.91</v>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
@@ -3602,18 +3602,18 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="n">
-        <v>1582723120</v>
+        <v>1978487977</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3622,19 +3622,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.3755</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>45645.89511640046</v>
+        <v>45887.66311905093</v>
       </c>
       <c r="G65" t="n">
-        <v>53.26</v>
+        <v>127.06</v>
       </c>
       <c r="H65" t="n">
-        <v>65.81</v>
+        <v>123.49</v>
       </c>
       <c r="I65" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
@@ -3651,18 +3651,18 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>4.71</v>
+        <v>-0.28</v>
       </c>
       <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="n">
-        <v>1880445013</v>
+        <v>1642762235</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3671,19 +3671,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.1572</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>45825.8922271412</v>
+        <v>45692.86612574074</v>
       </c>
       <c r="G66" t="n">
-        <v>139.86</v>
+        <v>127.16</v>
       </c>
       <c r="H66" t="n">
-        <v>148.15</v>
+        <v>123.49</v>
       </c>
       <c r="I66" t="n">
-        <v>10</v>
+        <v>19.99</v>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
@@ -3700,18 +3700,18 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>0.59</v>
+        <v>-0.58</v>
       </c>
       <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="n">
-        <v>1923258249</v>
+        <v>1830410729</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3720,19 +3720,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>0.1091</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>45853.65576626157</v>
+        <v>45796.82476561343</v>
       </c>
       <c r="G67" t="n">
-        <v>19.41</v>
+        <v>33.66</v>
       </c>
       <c r="H67" t="n">
-        <v>20.48</v>
+        <v>33.1</v>
       </c>
       <c r="I67" t="n">
-        <v>19.41</v>
+        <v>3.67</v>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
@@ -3749,18 +3749,18 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>1.07</v>
+        <v>-0.06</v>
       </c>
       <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="n">
-        <v>1843470413</v>
+        <v>1662993636</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3769,19 +3769,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.4729</v>
+        <v>1</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>45804.66637251157</v>
+        <v>45706.87026833333</v>
       </c>
       <c r="G68" t="n">
-        <v>42.29</v>
+        <v>20.65</v>
       </c>
       <c r="H68" t="n">
-        <v>49.41</v>
+        <v>18.4</v>
       </c>
       <c r="I68" t="n">
-        <v>20</v>
+        <v>20.65</v>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
@@ -3798,14 +3798,14 @@
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>3.37</v>
+        <v>-2.25</v>
       </c>
       <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="n">
-        <v>1869077157</v>
+        <v>1883977044</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -3818,19 +3818,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.3061</v>
+        <v>0.345</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>45819.6742621412</v>
+        <v>45827.66105774305</v>
       </c>
       <c r="G69" t="n">
-        <v>13.285</v>
+        <v>12.88</v>
       </c>
       <c r="H69" t="n">
-        <v>16.515</v>
+        <v>16.025</v>
       </c>
       <c r="I69" t="n">
-        <v>4.69</v>
+        <v>5.13</v>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
@@ -3847,18 +3847,18 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="n">
-        <v>1824477589</v>
+        <v>1986476926</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3867,19 +3867,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.2344</v>
+        <v>1</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>45792.64732982639</v>
+        <v>45891.66490212963</v>
       </c>
       <c r="G70" t="n">
-        <v>42.66</v>
+        <v>34.44</v>
       </c>
       <c r="H70" t="n">
-        <v>44.56</v>
+        <v>37.8</v>
       </c>
       <c r="I70" t="n">
-        <v>10</v>
+        <v>34.44</v>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
@@ -3896,18 +3896,18 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>0.44</v>
+        <v>3.36</v>
       </c>
       <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="n">
-        <v>1517510856</v>
+        <v>1867462173</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3916,19 +3916,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.0602</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>45597.61014849537</v>
+        <v>45818.90866184028</v>
       </c>
       <c r="G71" t="n">
-        <v>166.03</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="H71" t="n">
-        <v>150.32</v>
+        <v>101.74</v>
       </c>
       <c r="I71" t="n">
-        <v>10</v>
+        <v>0.65</v>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
@@ -3945,18 +3945,18 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>-0.95</v>
+        <v>0.2</v>
       </c>
       <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="n">
-        <v>1666461140</v>
+        <v>1843474191</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3965,19 +3965,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.2651</v>
+        <v>0.9372</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>45708.68207092593</v>
+        <v>45804.66699503472</v>
       </c>
       <c r="G72" t="n">
-        <v>37.7</v>
+        <v>21.33</v>
       </c>
       <c r="H72" t="n">
-        <v>32.92</v>
+        <v>25.33</v>
       </c>
       <c r="I72" t="n">
-        <v>9.99</v>
+        <v>19.99</v>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -3994,18 +3994,18 @@
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>-1.26</v>
+        <v>3.75</v>
       </c>
       <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="n">
-        <v>1817256440</v>
+        <v>1599448103</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4014,19 +4014,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.2267</v>
+        <v>0.2839</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45789.64787115741</v>
+        <v>45663.73506711805</v>
       </c>
       <c r="G73" t="n">
-        <v>44.1</v>
+        <v>52.83</v>
       </c>
       <c r="H73" t="n">
-        <v>44.56</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
@@ -4043,18 +4043,18 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>0.1</v>
+        <v>3.6</v>
       </c>
       <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="n">
-        <v>1888700382</v>
+        <v>1923271589</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4063,19 +4063,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>0.4478</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45831.65144708334</v>
+        <v>45853.65794861111</v>
       </c>
       <c r="G74" t="n">
-        <v>47.58</v>
+        <v>44.66</v>
       </c>
       <c r="H74" t="n">
-        <v>51.35</v>
+        <v>51.79</v>
       </c>
       <c r="I74" t="n">
-        <v>47.58</v>
+        <v>20</v>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
@@ -4092,18 +4092,18 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>3.77</v>
+        <v>3.19</v>
       </c>
       <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="n">
-        <v>1867193304</v>
+        <v>1923224670</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4112,19 +4112,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.1337</v>
+        <v>0.2583</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>45818.8008296412</v>
+        <v>45853.65359685185</v>
       </c>
       <c r="G75" t="n">
-        <v>17.64</v>
+        <v>58.05</v>
       </c>
       <c r="H75" t="n">
-        <v>20.27</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>2.36</v>
+        <v>14.99</v>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
@@ -4141,18 +4141,18 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>0.35</v>
+        <v>1.93</v>
       </c>
       <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="n">
-        <v>1880446729</v>
+        <v>2025661832</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4161,19 +4161,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.0772</v>
+        <v>0.3235</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>45825.89315055555</v>
+        <v>45915.72870862269</v>
       </c>
       <c r="G76" t="n">
-        <v>129.62</v>
+        <v>61.81</v>
       </c>
       <c r="H76" t="n">
-        <v>150.32</v>
+        <v>61.04</v>
       </c>
       <c r="I76" t="n">
-        <v>10.01</v>
+        <v>20</v>
       </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
@@ -4190,18 +4190,18 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>1.59</v>
+        <v>-0.25</v>
       </c>
       <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="n">
-        <v>1358151307</v>
+        <v>1744929368</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4210,19 +4210,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.1081</v>
+        <v>0.0192</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>45460.88529052083</v>
+        <v>45751.74500871528</v>
       </c>
       <c r="G77" t="n">
-        <v>165.93</v>
+        <v>324.48</v>
       </c>
       <c r="H77" t="n">
-        <v>150.32</v>
+        <v>345.85</v>
       </c>
       <c r="I77" t="n">
-        <v>17.94</v>
+        <v>6.23</v>
       </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
@@ -4239,18 +4239,18 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>-1.68</v>
+        <v>0.41</v>
       </c>
       <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="n">
-        <v>1744916497</v>
+        <v>1993444707</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>BBAR</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4259,19 +4259,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>0.8051</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>45751.74231563658</v>
+        <v>45896.6743321875</v>
       </c>
       <c r="G78" t="n">
-        <v>17.54</v>
+        <v>12.42</v>
       </c>
       <c r="H78" t="n">
-        <v>24.87</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>17.54</v>
+        <v>10</v>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
@@ -4288,18 +4288,18 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>7.33</v>
+        <v>-2.87</v>
       </c>
       <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="n">
-        <v>1926287328</v>
+        <v>1993382859</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4308,19 +4308,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.5476</v>
+        <v>0.0779</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>45854.82177967593</v>
+        <v>45896.66809304398</v>
       </c>
       <c r="G79" t="n">
-        <v>18.26</v>
+        <v>128.25</v>
       </c>
       <c r="H79" t="n">
-        <v>20.48</v>
+        <v>123.49</v>
       </c>
       <c r="I79" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
@@ -4337,18 +4337,18 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>1.21</v>
+        <v>-0.37</v>
       </c>
       <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="n">
-        <v>1796453499</v>
+        <v>1975988073</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4357,19 +4357,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.0469</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>45777.64668229167</v>
+        <v>45884.6572796875</v>
       </c>
       <c r="G80" t="n">
-        <v>15.57</v>
+        <v>319.83</v>
       </c>
       <c r="H80" t="n">
-        <v>20.27</v>
+        <v>320.42</v>
       </c>
       <c r="I80" t="n">
-        <v>8.01</v>
+        <v>15</v>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
@@ -4386,18 +4386,18 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>2.42</v>
+        <v>0.03</v>
       </c>
       <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="n">
-        <v>1806977521</v>
+        <v>1817256440</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4406,16 +4406,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.3367</v>
+        <v>0.2267</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>45783.8305750463</v>
+        <v>45789.64787115741</v>
       </c>
       <c r="G81" t="n">
-        <v>29.7</v>
+        <v>44.1</v>
       </c>
       <c r="H81" t="n">
-        <v>32.92</v>
+        <v>43.22</v>
       </c>
       <c r="I81" t="n">
         <v>10</v>
@@ -4435,18 +4435,18 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>1.08</v>
+        <v>-0.2</v>
       </c>
       <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="n">
-        <v>1867195793</v>
+        <v>1978489328</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4455,19 +4455,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.2339</v>
+        <v>1</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>45818.80180457176</v>
+        <v>45887.6634622338</v>
       </c>
       <c r="G82" t="n">
-        <v>42.74</v>
+        <v>34.58</v>
       </c>
       <c r="H82" t="n">
-        <v>44.56</v>
+        <v>37.8</v>
       </c>
       <c r="I82" t="n">
-        <v>10</v>
+        <v>34.58</v>
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
@@ -4484,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>0.42</v>
+        <v>3.22</v>
       </c>
       <c r="Q82" t="inlineStr"/>
     </row>
@@ -4513,7 +4513,7 @@
         <v>144.94</v>
       </c>
       <c r="H83" t="n">
-        <v>150.32</v>
+        <v>141.21</v>
       </c>
       <c r="I83" t="n">
         <v>10.99</v>
@@ -4533,18 +4533,18 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>0.4</v>
+        <v>-0.29</v>
       </c>
       <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="n">
-        <v>1566610015</v>
+        <v>1880441651</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4553,19 +4553,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.9385</v>
+        <v>1</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>45632.87667083334</v>
+        <v>45825.89055887731</v>
       </c>
       <c r="G84" t="n">
-        <v>21.31</v>
+        <v>21.21</v>
       </c>
       <c r="H84" t="n">
-        <v>20.48</v>
+        <v>18.4</v>
       </c>
       <c r="I84" t="n">
-        <v>20</v>
+        <v>21.21</v>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
@@ -4582,18 +4582,18 @@
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>-0.78</v>
+        <v>-2.81</v>
       </c>
       <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="n">
-        <v>1970057305</v>
+        <v>1984829391</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4602,16 +4602,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.2789</v>
+        <v>0.0512</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>45881.70511172454</v>
+        <v>45890.71798858796</v>
       </c>
       <c r="G85" t="n">
-        <v>35.88</v>
+        <v>195.52</v>
       </c>
       <c r="H85" t="n">
-        <v>37.01</v>
+        <v>210.26</v>
       </c>
       <c r="I85" t="n">
         <v>10.01</v>
@@ -4631,18 +4631,18 @@
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>0.31</v>
+        <v>0.76</v>
       </c>
       <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="n">
-        <v>1744767540</v>
+        <v>1843468958</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4651,19 +4651,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.643</v>
+        <v>0.0669</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>45751.72316712963</v>
+        <v>45804.66597149306</v>
       </c>
       <c r="G86" t="n">
-        <v>15.55</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="H86" t="n">
-        <v>20.48</v>
+        <v>70.22</v>
       </c>
       <c r="I86" t="n">
-        <v>10</v>
+        <v>4.54</v>
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
@@ -4680,18 +4680,18 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>3.17</v>
+        <v>0.16</v>
       </c>
       <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="n">
-        <v>1923250768</v>
+        <v>1843470413</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4700,19 +4700,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.87</v>
+        <v>0.4729</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>45853.65447396991</v>
+        <v>45804.66637251157</v>
       </c>
       <c r="G87" t="n">
-        <v>12.76</v>
+        <v>42.29</v>
       </c>
       <c r="H87" t="n">
-        <v>16.515</v>
+        <v>51.79</v>
       </c>
       <c r="I87" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
@@ -4729,18 +4729,18 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>3.73</v>
+        <v>4.49</v>
       </c>
       <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="n">
-        <v>1712850989</v>
+        <v>1599431096</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4749,19 +4749,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.0282</v>
+        <v>0.1013</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>45734.85576775463</v>
+        <v>45663.73014731482</v>
       </c>
       <c r="G88" t="n">
-        <v>160.64</v>
+        <v>148.02</v>
       </c>
       <c r="H88" t="n">
-        <v>203.88</v>
+        <v>141.21</v>
       </c>
       <c r="I88" t="n">
-        <v>4.53</v>
+        <v>14.99</v>
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
@@ -4778,18 +4778,18 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>1.22</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="n">
-        <v>1727563010</v>
+        <v>1926287328</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4798,19 +4798,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>0.5476</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>45743.76106726852</v>
+        <v>45854.82177967593</v>
       </c>
       <c r="G89" t="n">
-        <v>46.11</v>
+        <v>18.26</v>
       </c>
       <c r="H89" t="n">
-        <v>51.35</v>
+        <v>24.13</v>
       </c>
       <c r="I89" t="n">
-        <v>46.11</v>
+        <v>10</v>
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
@@ -4827,18 +4827,18 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>5.24</v>
+        <v>3.21</v>
       </c>
       <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="n">
-        <v>1824482557</v>
+        <v>2020498309</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BBAR</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4847,19 +4847,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.2641</v>
+        <v>0.0131</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>45792.64805195602</v>
+        <v>45911.68944190972</v>
       </c>
       <c r="G90" t="n">
-        <v>56.78</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="H90" t="n">
-        <v>65.81</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="I90" t="n">
-        <v>15</v>
+        <v>0.13</v>
       </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
@@ -4876,18 +4876,18 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>2.38</v>
+        <v>-0.01</v>
       </c>
       <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="n">
-        <v>1867197360</v>
+        <v>1997500170</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>JKS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4896,19 +4896,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.0765</v>
+        <v>0.4466</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>45818.80265583334</v>
+        <v>45898.65406594907</v>
       </c>
       <c r="G91" t="n">
-        <v>131.96</v>
+        <v>22.39</v>
       </c>
       <c r="H91" t="n">
-        <v>150.32</v>
+        <v>25.17</v>
       </c>
       <c r="I91" t="n">
-        <v>10.09</v>
+        <v>10</v>
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
@@ -4925,18 +4925,18 @@
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="n">
-        <v>1635194117</v>
+        <v>1727574394</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4945,19 +4945,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.2479</v>
+        <v>1</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>45687.85228493056</v>
+        <v>45743.76658678241</v>
       </c>
       <c r="G92" t="n">
-        <v>40.33</v>
+        <v>21.13</v>
       </c>
       <c r="H92" t="n">
-        <v>32.92</v>
+        <v>18.4</v>
       </c>
       <c r="I92" t="n">
-        <v>10</v>
+        <v>21.13</v>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
@@ -4974,18 +4974,18 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>-1.84</v>
+        <v>-2.73</v>
       </c>
       <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="n">
-        <v>1599431096</v>
+        <v>1666461140</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4994,19 +4994,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.1013</v>
+        <v>0.2651</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>45663.73014731482</v>
+        <v>45708.68207092593</v>
       </c>
       <c r="G93" t="n">
-        <v>148.02</v>
+        <v>37.7</v>
       </c>
       <c r="H93" t="n">
-        <v>150.32</v>
+        <v>27.15</v>
       </c>
       <c r="I93" t="n">
-        <v>14.99</v>
+        <v>9.99</v>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
@@ -5023,18 +5023,18 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>0.24</v>
+        <v>-2.79</v>
       </c>
       <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="n">
-        <v>1885700231</v>
+        <v>1824477589</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5043,19 +5043,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.0081</v>
+        <v>0.2344</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>45828.65147924769</v>
+        <v>45792.64732982639</v>
       </c>
       <c r="G94" t="n">
-        <v>534.86</v>
+        <v>42.66</v>
       </c>
       <c r="H94" t="n">
-        <v>581.5700000000001</v>
+        <v>43.22</v>
       </c>
       <c r="I94" t="n">
-        <v>4.33</v>
+        <v>10</v>
       </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
@@ -5072,18 +5072,18 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>0.38</v>
+        <v>0.13</v>
       </c>
       <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="n">
-        <v>1880443947</v>
+        <v>1582735114</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5092,19 +5092,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.1047</v>
+        <v>0.0003</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>45825.891695625</v>
+        <v>45645.90076803241</v>
       </c>
       <c r="G95" t="n">
-        <v>142.99</v>
+        <v>130.51</v>
       </c>
       <c r="H95" t="n">
-        <v>199.86</v>
+        <v>148.1</v>
       </c>
       <c r="I95" t="n">
-        <v>14.97</v>
+        <v>0.04</v>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -5121,18 +5121,18 @@
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>5.96</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="n">
-        <v>1923224670</v>
+        <v>1806980496</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5141,19 +5141,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.2583</v>
+        <v>1</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>45853.65359685185</v>
+        <v>45783.83190503472</v>
       </c>
       <c r="G96" t="n">
-        <v>58.05</v>
+        <v>16.12</v>
       </c>
       <c r="H96" t="n">
-        <v>65.81</v>
+        <v>20.75</v>
       </c>
       <c r="I96" t="n">
-        <v>14.99</v>
+        <v>16.12</v>
       </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
@@ -5170,14 +5170,14 @@
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>2.01</v>
+        <v>4.63</v>
       </c>
       <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="n">
-        <v>1867195417</v>
+        <v>1880445013</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -5190,19 +5190,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.1044</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>45818.80165224537</v>
+        <v>45825.8922271412</v>
       </c>
       <c r="G97" t="n">
-        <v>143.6</v>
+        <v>139.86</v>
       </c>
       <c r="H97" t="n">
-        <v>148.15</v>
+        <v>148.1</v>
       </c>
       <c r="I97" t="n">
-        <v>14.99</v>
+        <v>10</v>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
@@ -5219,18 +5219,18 @@
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>0.48</v>
+        <v>0.59</v>
       </c>
       <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="n">
-        <v>1680994777</v>
+        <v>2002503461</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5239,19 +5239,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.7278</v>
+        <v>0.0439</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>45716.85705375</v>
+        <v>45902.65623520833</v>
       </c>
       <c r="G98" t="n">
-        <v>20.6</v>
+        <v>227.95</v>
       </c>
       <c r="H98" t="n">
-        <v>20.48</v>
+        <v>262.31</v>
       </c>
       <c r="I98" t="n">
-        <v>14.99</v>
+        <v>10.01</v>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
@@ -5268,18 +5268,18 @@
         <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>-0.08</v>
+        <v>1.51</v>
       </c>
       <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="n">
-        <v>1880441651</v>
+        <v>1895465445</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5288,19 +5288,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1</v>
+        <v>0.2987</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>45825.89055887731</v>
+        <v>45834.6539484375</v>
       </c>
       <c r="G99" t="n">
-        <v>21.21</v>
+        <v>33.47</v>
       </c>
       <c r="H99" t="n">
-        <v>19.17</v>
+        <v>27.15</v>
       </c>
       <c r="I99" t="n">
-        <v>21.21</v>
+        <v>10</v>
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
@@ -5317,18 +5317,18 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>-2.04</v>
+        <v>-1.89</v>
       </c>
       <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="n">
-        <v>1461331124</v>
+        <v>1843477152</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5337,19 +5337,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.3752</v>
+        <v>0.1198</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>45553.65374138889</v>
+        <v>45804.66724922453</v>
       </c>
       <c r="G100" t="n">
-        <v>50.99</v>
+        <v>17.86</v>
       </c>
       <c r="H100" t="n">
-        <v>65.81</v>
+        <v>20.75</v>
       </c>
       <c r="I100" t="n">
-        <v>19.13</v>
+        <v>2.14</v>
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
@@ -5366,18 +5366,18 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>5.56</v>
+        <v>0.35</v>
       </c>
       <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="n">
-        <v>1666451221</v>
+        <v>1358151307</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5386,19 +5386,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.0001</v>
+        <v>0.1081</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>45708.68022634259</v>
+        <v>45460.88529052083</v>
       </c>
       <c r="G101" t="n">
-        <v>43</v>
+        <v>165.93</v>
       </c>
       <c r="H101" t="n">
-        <v>44.56</v>
+        <v>141.21</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>17.94</v>
       </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -5415,18 +5415,18 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>-2.67</v>
       </c>
       <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="n">
-        <v>1806980496</v>
+        <v>1923259795</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5435,19 +5435,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1</v>
+        <v>0.4424</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>45783.83190503472</v>
+        <v>45853.65609353009</v>
       </c>
       <c r="G102" t="n">
-        <v>16.12</v>
+        <v>22.59</v>
       </c>
       <c r="H102" t="n">
-        <v>20.27</v>
+        <v>25.33</v>
       </c>
       <c r="I102" t="n">
-        <v>16.12</v>
+        <v>9.99</v>
       </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
@@ -5464,7 +5464,7 @@
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>4.15</v>
+        <v>1.22</v>
       </c>
       <c r="Q102" t="inlineStr"/>
     </row>
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.0023</v>
       </c>
       <c r="F103" s="2" t="n">
         <v>45818.90835071759</v>
@@ -5493,10 +5493,10 @@
         <v>216.54</v>
       </c>
       <c r="H103" t="n">
-        <v>251.42</v>
+        <v>278.14</v>
       </c>
       <c r="I103" t="n">
-        <v>19.99</v>
+        <v>0.5</v>
       </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
@@ -5513,18 +5513,18 @@
         <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>3.22</v>
+        <v>0.14</v>
       </c>
       <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="n">
-        <v>1830410729</v>
+        <v>1989207013</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>JKS</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5533,19 +5533,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.1091</v>
+        <v>0.4133</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>45796.82476561343</v>
+        <v>45894.65354606482</v>
       </c>
       <c r="G104" t="n">
-        <v>33.66</v>
+        <v>24.19</v>
       </c>
       <c r="H104" t="n">
-        <v>31.13</v>
+        <v>25.17</v>
       </c>
       <c r="I104" t="n">
-        <v>3.67</v>
+        <v>10</v>
       </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
@@ -5562,18 +5562,18 @@
         <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>-0.27</v>
+        <v>0.4</v>
       </c>
       <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="n">
-        <v>1599455288</v>
+        <v>1997498400</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5582,16 +5582,16 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.2195</v>
+        <v>0.0507</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>45663.73750263889</v>
+        <v>45898.65380736111</v>
       </c>
       <c r="G105" t="n">
-        <v>45.55</v>
+        <v>197.26</v>
       </c>
       <c r="H105" t="n">
-        <v>32.92</v>
+        <v>210.26</v>
       </c>
       <c r="I105" t="n">
         <v>10</v>
@@ -5611,18 +5611,18 @@
         <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>-2.77</v>
+        <v>0.66</v>
       </c>
       <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="n">
-        <v>1744879358</v>
+        <v>1559803221</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5631,19 +5631,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.2701</v>
+        <v>0.092</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>45751.73925940973</v>
+        <v>45628.85951927083</v>
       </c>
       <c r="G106" t="n">
-        <v>148.09</v>
+        <v>162.85</v>
       </c>
       <c r="H106" t="n">
-        <v>239.01</v>
+        <v>141.21</v>
       </c>
       <c r="I106" t="n">
-        <v>40</v>
+        <v>14.98</v>
       </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
@@ -5660,18 +5660,18 @@
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>24.56</v>
+        <v>-1.99</v>
       </c>
       <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="n">
-        <v>1923258184</v>
+        <v>1824476420</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5680,19 +5680,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.0298</v>
+        <v>0.1548</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>45853.6557568287</v>
+        <v>45792.64714148148</v>
       </c>
       <c r="G107" t="n">
-        <v>19.43</v>
+        <v>129.17</v>
       </c>
       <c r="H107" t="n">
-        <v>20.48</v>
+        <v>141.21</v>
       </c>
       <c r="I107" t="n">
-        <v>0.58</v>
+        <v>20</v>
       </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
@@ -5709,18 +5709,18 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>0.03</v>
+        <v>1.86</v>
       </c>
       <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="n">
-        <v>1648737122</v>
+        <v>1666451221</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5729,19 +5729,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.001</v>
+        <v>0.0001</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>45695.85619950231</v>
+        <v>45708.68022634259</v>
       </c>
       <c r="G108" t="n">
-        <v>408.33</v>
+        <v>43</v>
       </c>
       <c r="H108" t="n">
-        <v>520.01</v>
+        <v>43.22</v>
       </c>
       <c r="I108" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
@@ -5758,18 +5758,18 @@
         <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="n">
-        <v>1895465445</v>
+        <v>1744879358</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5778,19 +5778,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.2987</v>
+        <v>0.2701</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>45834.6539484375</v>
+        <v>45751.73925940973</v>
       </c>
       <c r="G109" t="n">
-        <v>33.47</v>
+        <v>148.09</v>
       </c>
       <c r="H109" t="n">
-        <v>32.92</v>
+        <v>262.31</v>
       </c>
       <c r="I109" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
@@ -5807,18 +5807,18 @@
         <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>-0.17</v>
+        <v>30.85</v>
       </c>
       <c r="Q109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="n">
-        <v>1727574394</v>
+        <v>1666459175</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5827,19 +5827,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1</v>
+        <v>0.1641</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>45743.76658678241</v>
+        <v>45708.68165298611</v>
       </c>
       <c r="G110" t="n">
-        <v>21.13</v>
+        <v>17.18</v>
       </c>
       <c r="H110" t="n">
-        <v>19.17</v>
+        <v>25.33</v>
       </c>
       <c r="I110" t="n">
-        <v>21.13</v>
+        <v>2.82</v>
       </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
@@ -5856,18 +5856,18 @@
         <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>-1.96</v>
+        <v>1.34</v>
       </c>
       <c r="Q110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="n">
-        <v>1843469729</v>
+        <v>1883977086</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5876,19 +5876,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.0956</v>
+        <v>1</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>45804.66615450232</v>
+        <v>45827.66106613426</v>
       </c>
       <c r="G111" t="n">
-        <v>156.9</v>
+        <v>12.875</v>
       </c>
       <c r="H111" t="n">
-        <v>199.86</v>
+        <v>16.025</v>
       </c>
       <c r="I111" t="n">
-        <v>15</v>
+        <v>14.86</v>
       </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
@@ -5905,14 +5905,14 @@
         <v>0</v>
       </c>
       <c r="P111" t="n">
-        <v>4.11</v>
+        <v>4.04</v>
       </c>
       <c r="Q111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="n">
-        <v>1633116336</v>
+        <v>1888700382</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -5928,16 +5928,16 @@
         <v>1</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>45686.83272234954</v>
+        <v>45831.65144708334</v>
       </c>
       <c r="G112" t="n">
-        <v>44.24</v>
+        <v>47.58</v>
       </c>
       <c r="H112" t="n">
-        <v>51.35</v>
+        <v>54.49</v>
       </c>
       <c r="I112" t="n">
-        <v>44.24</v>
+        <v>47.58</v>
       </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
@@ -5954,18 +5954,18 @@
         <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>7.11</v>
+        <v>6.91</v>
       </c>
       <c r="Q112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="n">
-        <v>1582714896</v>
+        <v>1867195417</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5974,19 +5974,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.4847</v>
+        <v>0.1044</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>45645.89066263889</v>
+        <v>45818.80165224537</v>
       </c>
       <c r="G113" t="n">
-        <v>20.62</v>
+        <v>143.6</v>
       </c>
       <c r="H113" t="n">
-        <v>20.48</v>
+        <v>148.1</v>
       </c>
       <c r="I113" t="n">
-        <v>9.99</v>
+        <v>14.99</v>
       </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
@@ -6003,27 +6003,45 @@
         <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>-0.06</v>
+        <v>0.47</v>
       </c>
       <c r="Q113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
+      <c r="B114" t="n">
+        <v>1869077178</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>BBVA.MC</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>45819.67426902778</v>
+      </c>
+      <c r="G114" t="n">
+        <v>13.285</v>
+      </c>
+      <c r="H114" t="n">
+        <v>16.025</v>
+      </c>
+      <c r="I114" t="n">
+        <v>15.31</v>
+      </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
       <c r="M114" t="n">
         <v>0</v>
       </c>
@@ -6034,9 +6052,1363 @@
         <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>161.44</v>
+        <v>3.59</v>
       </c>
       <c r="Q114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="n">
+        <v>1461331124</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>0.3752</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>45553.65374138889</v>
+      </c>
+      <c r="G115" t="n">
+        <v>50.99</v>
+      </c>
+      <c r="H115" t="n">
+        <v>65.51000000000001</v>
+      </c>
+      <c r="I115" t="n">
+        <v>19.13</v>
+      </c>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="Q115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="n">
+        <v>1923246263</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ACI</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>45853.6538128125</v>
+      </c>
+      <c r="G116" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="H116" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="I116" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>-2.77</v>
+      </c>
+      <c r="Q116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="n">
+        <v>1806979127</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>0.6361</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>45783.83125244213</v>
+      </c>
+      <c r="G117" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="H117" t="n">
+        <v>24.13</v>
+      </c>
+      <c r="I117" t="n">
+        <v>10</v>
+      </c>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="Q117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="n">
+        <v>2017778050</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>YPF</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>45910.64665976852</v>
+      </c>
+      <c r="G118" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="H118" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="I118" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="Q118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="n">
+        <v>2027639997</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>0.1558</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>45916.65703747685</v>
+      </c>
+      <c r="G119" t="n">
+        <v>64.18000000000001</v>
+      </c>
+      <c r="H119" t="n">
+        <v>65.51000000000001</v>
+      </c>
+      <c r="I119" t="n">
+        <v>10</v>
+      </c>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="Q119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="n">
+        <v>2000138014</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>BTCE.DE</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>0.1017</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>45901.57795706019</v>
+      </c>
+      <c r="G120" t="n">
+        <v>83.47499999999999</v>
+      </c>
+      <c r="H120" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="I120" t="n">
+        <v>10</v>
+      </c>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="Q120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="n">
+        <v>1995846726</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>NEE</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>0.1372</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>45897.72549582176</v>
+      </c>
+      <c r="G121" t="n">
+        <v>72.94</v>
+      </c>
+      <c r="H121" t="n">
+        <v>70.22</v>
+      </c>
+      <c r="I121" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="Q121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="n">
+        <v>1982267978</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>45889.64851537037</v>
+      </c>
+      <c r="G122" t="n">
+        <v>303.76</v>
+      </c>
+      <c r="H122" t="n">
+        <v>320.42</v>
+      </c>
+      <c r="I122" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="n">
+        <v>1517510856</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>0.0602</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>45597.61014849537</v>
+      </c>
+      <c r="G123" t="n">
+        <v>166.03</v>
+      </c>
+      <c r="H123" t="n">
+        <v>141.21</v>
+      </c>
+      <c r="I123" t="n">
+        <v>10</v>
+      </c>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="Q123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="n">
+        <v>1880443947</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>FSLR</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>0.1047</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>45825.891695625</v>
+      </c>
+      <c r="G124" t="n">
+        <v>142.99</v>
+      </c>
+      <c r="H124" t="n">
+        <v>210.26</v>
+      </c>
+      <c r="I124" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="Q124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="n">
+        <v>1648737122</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>45695.85619950231</v>
+      </c>
+      <c r="G125" t="n">
+        <v>408.33</v>
+      </c>
+      <c r="H125" t="n">
+        <v>509.58</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="n">
+        <v>1882278057</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0.0432</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>45826.76262912037</v>
+      </c>
+      <c r="G126" t="n">
+        <v>346.61</v>
+      </c>
+      <c r="H126" t="n">
+        <v>345.85</v>
+      </c>
+      <c r="I126" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="Q126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="n">
+        <v>1983186744</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>YPF</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>45889.85904239583</v>
+      </c>
+      <c r="G127" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="H127" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="I127" t="n">
+        <v>10</v>
+      </c>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="Q127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="n">
+        <v>1867193336</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>BCS</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>45818.80084483796</v>
+      </c>
+      <c r="G128" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="H128" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="I128" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="Q128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="n">
+        <v>1867194722</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ACI</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>45818.80135700232</v>
+      </c>
+      <c r="G129" t="n">
+        <v>21.27</v>
+      </c>
+      <c r="H129" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="I129" t="n">
+        <v>21.27</v>
+      </c>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>-2.87</v>
+      </c>
+      <c r="Q129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="n">
+        <v>1554741956</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ING</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>45623.74952237269</v>
+      </c>
+      <c r="G130" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H130" t="n">
+        <v>25.33</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="Q130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" t="n">
+        <v>1928218937</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ACI</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>1</v>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>45855.75970359953</v>
+      </c>
+      <c r="G131" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="H131" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="I131" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="Q131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="n">
+        <v>2017847675</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>AGIO</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>0.2767</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>45910.65426635417</v>
+      </c>
+      <c r="G132" t="n">
+        <v>36.17</v>
+      </c>
+      <c r="H132" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="I132" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="Q132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="n">
+        <v>1680994777</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>0.7278</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>45716.85705375</v>
+      </c>
+      <c r="G133" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="H133" t="n">
+        <v>24.13</v>
+      </c>
+      <c r="I133" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Q133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="n">
+        <v>1997562259</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ING</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>0.6323</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>45898.65762083334</v>
+      </c>
+      <c r="G134" t="n">
+        <v>23.72</v>
+      </c>
+      <c r="H134" t="n">
+        <v>25.33</v>
+      </c>
+      <c r="I134" t="n">
+        <v>15</v>
+      </c>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Q134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="n">
+        <v>1633116336</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>VWO</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>45686.83272234954</v>
+      </c>
+      <c r="G135" t="n">
+        <v>44.24</v>
+      </c>
+      <c r="H135" t="n">
+        <v>54.49</v>
+      </c>
+      <c r="I135" t="n">
+        <v>44.24</v>
+      </c>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="Q135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="n">
+        <v>1796453499</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>BCS</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>0.5145999999999999</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>45777.64668229167</v>
+      </c>
+      <c r="G136" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="H136" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="I136" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Q136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="n">
+        <v>1824475555</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>ACI</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>1</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>45792.64702015046</v>
+      </c>
+      <c r="G137" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="H137" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="I137" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-3.26</v>
+      </c>
+      <c r="Q137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="n">
+        <v>1621495187</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>YPF</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>0.2318</v>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>45678.83178196759</v>
+      </c>
+      <c r="G138" t="n">
+        <v>43.27</v>
+      </c>
+      <c r="H138" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="I138" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>-3.74</v>
+      </c>
+      <c r="Q138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="n">
+        <v>2029950407</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>PHGP.L</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>0.1453</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>45917.66293982639</v>
+      </c>
+      <c r="G139" t="n">
+        <v>250.56</v>
+      </c>
+      <c r="H139" t="n">
+        <v>251</v>
+      </c>
+      <c r="I139" t="n">
+        <v>49.99</v>
+      </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="Q139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="n">
+        <v>1754304266</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>0.7137</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>45755.88055112268</v>
+      </c>
+      <c r="G140" t="n">
+        <v>14</v>
+      </c>
+      <c r="H140" t="n">
+        <v>24.13</v>
+      </c>
+      <c r="I140" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="Q140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="n">
+        <v>1882283184</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>0.4835</v>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>45826.76569390047</v>
+      </c>
+      <c r="G141" t="n">
+        <v>20.69</v>
+      </c>
+      <c r="H141" t="n">
+        <v>24.13</v>
+      </c>
+      <c r="I141" t="n">
+        <v>10</v>
+      </c>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>184.93</v>
+      </c>
+      <c r="Q142" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Stock Selection/OPEN POSITION.xlsx
+++ b/Stock Selection/OPEN POSITION.xlsx
@@ -544,7 +544,7 @@
         <v>58.53</v>
       </c>
       <c r="H2" t="n">
-        <v>65.51000000000001</v>
+        <v>63.95</v>
       </c>
       <c r="I2" t="n">
         <v>20</v>
@@ -564,7 +564,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="Q2" t="inlineStr"/>
     </row>
@@ -593,7 +593,7 @@
         <v>13.285</v>
       </c>
       <c r="H3" t="n">
-        <v>16.025</v>
+        <v>16.205</v>
       </c>
       <c r="I3" t="n">
         <v>4.69</v>
@@ -613,7 +613,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
@@ -642,7 +642,7 @@
         <v>53.26</v>
       </c>
       <c r="H4" t="n">
-        <v>65.51000000000001</v>
+        <v>63.95</v>
       </c>
       <c r="I4" t="n">
         <v>20</v>
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>4.6</v>
+        <v>4.01</v>
       </c>
       <c r="Q4" t="inlineStr"/>
     </row>
@@ -691,7 +691,7 @@
         <v>12.76</v>
       </c>
       <c r="H5" t="n">
-        <v>16.025</v>
+        <v>16.205</v>
       </c>
       <c r="I5" t="n">
         <v>13</v>
@@ -711,7 +711,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.44</v>
+        <v>3.54</v>
       </c>
       <c r="Q5" t="inlineStr"/>
     </row>
@@ -740,7 +740,7 @@
         <v>190.17</v>
       </c>
       <c r="H6" t="n">
-        <v>210.26</v>
+        <v>208.95</v>
       </c>
       <c r="I6" t="n">
         <v>10</v>
@@ -760,7 +760,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.06</v>
+        <v>0.99</v>
       </c>
       <c r="Q6" t="inlineStr"/>
     </row>
@@ -789,7 +789,7 @@
         <v>74.23</v>
       </c>
       <c r="H7" t="n">
-        <v>70.22</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="I7" t="n">
         <v>10</v>
@@ -809,7 +809,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.54</v>
+        <v>-0.47</v>
       </c>
       <c r="Q7" t="inlineStr"/>
     </row>
@@ -838,7 +838,7 @@
         <v>44.49</v>
       </c>
       <c r="H8" t="n">
-        <v>54.49</v>
+        <v>54.27</v>
       </c>
       <c r="I8" t="n">
         <v>44.49</v>
@@ -858,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>10</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Q8" t="inlineStr"/>
     </row>
@@ -887,7 +887,7 @@
         <v>49.6</v>
       </c>
       <c r="H9" t="n">
-        <v>49.16</v>
+        <v>49.82</v>
       </c>
       <c r="I9" t="n">
         <v>40</v>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.36</v>
+        <v>0.17</v>
       </c>
       <c r="Q9" t="inlineStr"/>
     </row>
@@ -936,7 +936,7 @@
         <v>38.58</v>
       </c>
       <c r="H10" t="n">
-        <v>27.15</v>
+        <v>24.44</v>
       </c>
       <c r="I10" t="n">
         <v>10</v>
@@ -956,7 +956,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.96</v>
+        <v>-3.67</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
@@ -985,7 +985,7 @@
         <v>17.54</v>
       </c>
       <c r="H11" t="n">
-        <v>25.33</v>
+        <v>25.31</v>
       </c>
       <c r="I11" t="n">
         <v>17.54</v>
@@ -1005,7 +1005,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>7.79</v>
+        <v>7.77</v>
       </c>
       <c r="Q11" t="inlineStr"/>
     </row>
@@ -1034,7 +1034,7 @@
         <v>17.18</v>
       </c>
       <c r="H12" t="n">
-        <v>25.33</v>
+        <v>25.31</v>
       </c>
       <c r="I12" t="n">
         <v>17.18</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>8.15</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="Q12" t="inlineStr"/>
     </row>
@@ -1083,7 +1083,7 @@
         <v>138.84</v>
       </c>
       <c r="H13" t="n">
-        <v>148.1</v>
+        <v>145.15</v>
       </c>
       <c r="I13" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.66</v>
+        <v>0.45</v>
       </c>
       <c r="Q13" t="inlineStr"/>
     </row>
@@ -1132,7 +1132,7 @@
         <v>34.36</v>
       </c>
       <c r="H14" t="n">
-        <v>27.15</v>
+        <v>24.44</v>
       </c>
       <c r="I14" t="n">
         <v>9.970000000000001</v>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.09</v>
+        <v>-2.88</v>
       </c>
       <c r="Q14" t="inlineStr"/>
     </row>
@@ -1181,7 +1181,7 @@
         <v>18.8</v>
       </c>
       <c r="H15" t="n">
-        <v>18.4</v>
+        <v>18.31</v>
       </c>
       <c r="I15" t="n">
         <v>18.8</v>
@@ -1201,7 +1201,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4</v>
+        <v>-0.49</v>
       </c>
       <c r="Q15" t="inlineStr"/>
     </row>
@@ -1230,7 +1230,7 @@
         <v>13.27</v>
       </c>
       <c r="H16" t="n">
-        <v>16.025</v>
+        <v>16.205</v>
       </c>
       <c r="I16" t="n">
         <v>15.09</v>
@@ -1250,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.81</v>
+        <v>3.92</v>
       </c>
       <c r="Q16" t="inlineStr"/>
     </row>
@@ -1279,7 +1279,7 @@
         <v>13.275</v>
       </c>
       <c r="H17" t="n">
-        <v>16.025</v>
+        <v>16.205</v>
       </c>
       <c r="I17" t="n">
         <v>7.28</v>
@@ -1299,7 +1299,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="Q17" t="inlineStr"/>
     </row>
@@ -1328,7 +1328,7 @@
         <v>165.35</v>
       </c>
       <c r="H18" t="n">
-        <v>262.31</v>
+        <v>268.11</v>
       </c>
       <c r="I18" t="n">
         <v>9.029999999999999</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>5.29</v>
+        <v>5.61</v>
       </c>
       <c r="Q18" t="inlineStr"/>
     </row>
@@ -1377,7 +1377,7 @@
         <v>160.64</v>
       </c>
       <c r="H19" t="n">
-        <v>249.34</v>
+        <v>252.1</v>
       </c>
       <c r="I19" t="n">
         <v>0.03</v>
@@ -1426,7 +1426,7 @@
         <v>24.39</v>
       </c>
       <c r="H20" t="n">
-        <v>24.73</v>
+        <v>24.56</v>
       </c>
       <c r="I20" t="n">
         <v>19.99</v>
@@ -1446,7 +1446,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.28</v>
+        <v>0.14</v>
       </c>
       <c r="Q20" t="inlineStr"/>
     </row>
@@ -1475,7 +1475,7 @@
         <v>87.16500000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>87.7</v>
+        <v>89.47</v>
       </c>
       <c r="I21" t="n">
         <v>49.99</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.31</v>
       </c>
       <c r="Q21" t="inlineStr"/>
     </row>
@@ -1524,7 +1524,7 @@
         <v>46.11</v>
       </c>
       <c r="H22" t="n">
-        <v>54.49</v>
+        <v>54.27</v>
       </c>
       <c r="I22" t="n">
         <v>46.11</v>
@@ -1544,7 +1544,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>8.380000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="Q22" t="inlineStr"/>
     </row>
@@ -1573,7 +1573,7 @@
         <v>228</v>
       </c>
       <c r="H23" t="n">
-        <v>262.31</v>
+        <v>268.11</v>
       </c>
       <c r="I23" t="n">
         <v>10.01</v>
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.51</v>
+        <v>1.76</v>
       </c>
       <c r="Q23" t="inlineStr"/>
     </row>
@@ -1622,7 +1622,7 @@
         <v>135.82</v>
       </c>
       <c r="H24" t="n">
-        <v>123.49</v>
+        <v>123.6</v>
       </c>
       <c r="I24" t="n">
         <v>26</v>
@@ -1642,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.36</v>
+        <v>-2.34</v>
       </c>
       <c r="Q24" t="inlineStr"/>
     </row>
@@ -1671,7 +1671,7 @@
         <v>17.54</v>
       </c>
       <c r="H25" t="n">
-        <v>25.33</v>
+        <v>25.31</v>
       </c>
       <c r="I25" t="n">
         <v>7.45</v>
@@ -1691,7 +1691,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="Q25" t="inlineStr"/>
     </row>
@@ -1720,7 +1720,7 @@
         <v>36.1</v>
       </c>
       <c r="H26" t="n">
-        <v>27.15</v>
+        <v>24.44</v>
       </c>
       <c r="I26" t="n">
         <v>10</v>
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.48</v>
+        <v>-3.23</v>
       </c>
       <c r="Q26" t="inlineStr"/>
     </row>
@@ -1769,7 +1769,7 @@
         <v>74.13</v>
       </c>
       <c r="H27" t="n">
-        <v>74.58</v>
+        <v>74.39</v>
       </c>
       <c r="I27" t="n">
         <v>74.13</v>
@@ -1789,7 +1789,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.45</v>
+        <v>0.26</v>
       </c>
       <c r="Q27" t="inlineStr"/>
     </row>
@@ -1818,7 +1818,7 @@
         <v>17.26</v>
       </c>
       <c r="H28" t="n">
-        <v>24.13</v>
+        <v>23.89</v>
       </c>
       <c r="I28" t="n">
         <v>10</v>
@@ -1838,7 +1838,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3.98</v>
+        <v>3.84</v>
       </c>
       <c r="Q28" t="inlineStr"/>
     </row>
@@ -1867,7 +1867,7 @@
         <v>131.96</v>
       </c>
       <c r="H29" t="n">
-        <v>141.21</v>
+        <v>140.69</v>
       </c>
       <c r="I29" t="n">
         <v>10.09</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="Q29" t="inlineStr"/>
     </row>
@@ -1916,7 +1916,7 @@
         <v>17.86</v>
       </c>
       <c r="H30" t="n">
-        <v>20.75</v>
+        <v>21.02</v>
       </c>
       <c r="I30" t="n">
         <v>17.86</v>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.89</v>
+        <v>3.16</v>
       </c>
       <c r="Q30" t="inlineStr"/>
     </row>
@@ -1965,7 +1965,7 @@
         <v>45.55</v>
       </c>
       <c r="H31" t="n">
-        <v>27.15</v>
+        <v>24.44</v>
       </c>
       <c r="I31" t="n">
         <v>10</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>-4.04</v>
+        <v>-4.64</v>
       </c>
       <c r="Q31" t="inlineStr"/>
     </row>
@@ -2014,7 +2014,7 @@
         <v>19.41</v>
       </c>
       <c r="H32" t="n">
-        <v>24.13</v>
+        <v>23.89</v>
       </c>
       <c r="I32" t="n">
         <v>19.41</v>
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>4.72</v>
+        <v>4.48</v>
       </c>
       <c r="Q32" t="inlineStr"/>
     </row>
@@ -2063,7 +2063,7 @@
         <v>37.44</v>
       </c>
       <c r="H33" t="n">
-        <v>37.8</v>
+        <v>37.98</v>
       </c>
       <c r="I33" t="n">
         <v>37.44</v>
@@ -2083,7 +2083,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.36</v>
+        <v>0.54</v>
       </c>
       <c r="Q33" t="inlineStr"/>
     </row>
@@ -2112,7 +2112,7 @@
         <v>40.33</v>
       </c>
       <c r="H34" t="n">
-        <v>27.15</v>
+        <v>24.44</v>
       </c>
       <c r="I34" t="n">
         <v>10</v>
@@ -2132,7 +2132,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>-3.27</v>
+        <v>-3.94</v>
       </c>
       <c r="Q34" t="inlineStr"/>
     </row>
@@ -2161,7 +2161,7 @@
         <v>233.17</v>
       </c>
       <c r="H35" t="n">
-        <v>262.31</v>
+        <v>268.11</v>
       </c>
       <c r="I35" t="n">
         <v>10</v>
@@ -2181,7 +2181,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="Q35" t="inlineStr"/>
     </row>
@@ -2210,7 +2210,7 @@
         <v>29.7</v>
       </c>
       <c r="H36" t="n">
-        <v>27.15</v>
+        <v>24.44</v>
       </c>
       <c r="I36" t="n">
         <v>10</v>
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>-0.86</v>
+        <v>-1.77</v>
       </c>
       <c r="Q36" t="inlineStr"/>
     </row>
@@ -2259,7 +2259,7 @@
         <v>66.73</v>
       </c>
       <c r="H37" t="n">
-        <v>65.51000000000001</v>
+        <v>63.95</v>
       </c>
       <c r="I37" t="n">
         <v>10</v>
@@ -2279,7 +2279,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>-0.19</v>
+        <v>-0.42</v>
       </c>
       <c r="Q37" t="inlineStr"/>
     </row>
@@ -2308,7 +2308,7 @@
         <v>19.2</v>
       </c>
       <c r="H38" t="n">
-        <v>24.13</v>
+        <v>23.89</v>
       </c>
       <c r="I38" t="n">
         <v>15</v>
@@ -2328,7 +2328,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>3.85</v>
+        <v>3.66</v>
       </c>
       <c r="Q38" t="inlineStr"/>
     </row>
@@ -2357,7 +2357,7 @@
         <v>42.02</v>
       </c>
       <c r="H39" t="n">
-        <v>51.79</v>
+        <v>51.49</v>
       </c>
       <c r="I39" t="n">
         <v>19.99</v>
@@ -2377,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="Q39" t="inlineStr"/>
     </row>
@@ -2406,7 +2406,7 @@
         <v>56.78</v>
       </c>
       <c r="H40" t="n">
-        <v>65.51000000000001</v>
+        <v>63.95</v>
       </c>
       <c r="I40" t="n">
         <v>15</v>
@@ -2426,7 +2426,7 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="Q40" t="inlineStr"/>
     </row>
@@ -2455,7 +2455,7 @@
         <v>21.85</v>
       </c>
       <c r="H41" t="n">
-        <v>24.13</v>
+        <v>23.89</v>
       </c>
       <c r="I41" t="n">
         <v>10</v>
@@ -2475,7 +2475,7 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.04</v>
+        <v>0.93</v>
       </c>
       <c r="Q41" t="inlineStr"/>
     </row>
@@ -2504,7 +2504,7 @@
         <v>59.15</v>
       </c>
       <c r="H42" t="n">
-        <v>65.51000000000001</v>
+        <v>63.95</v>
       </c>
       <c r="I42" t="n">
         <v>14.99</v>
@@ -2524,7 +2524,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="Q42" t="inlineStr"/>
     </row>
@@ -2553,7 +2553,7 @@
         <v>129.62</v>
       </c>
       <c r="H43" t="n">
-        <v>141.21</v>
+        <v>140.69</v>
       </c>
       <c r="I43" t="n">
         <v>10.01</v>
@@ -2573,7 +2573,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="Q43" t="inlineStr"/>
     </row>
@@ -2602,7 +2602,7 @@
         <v>42.74</v>
       </c>
       <c r="H44" t="n">
-        <v>43.22</v>
+        <v>43.1</v>
       </c>
       <c r="I44" t="n">
         <v>10</v>
@@ -2622,7 +2622,7 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="Q44" t="inlineStr"/>
     </row>
@@ -2651,7 +2651,7 @@
         <v>17.64</v>
       </c>
       <c r="H45" t="n">
-        <v>20.75</v>
+        <v>21.02</v>
       </c>
       <c r="I45" t="n">
         <v>2.36</v>
@@ -2671,7 +2671,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.41</v>
+        <v>0.45</v>
       </c>
       <c r="Q45" t="inlineStr"/>
     </row>
@@ -2700,7 +2700,7 @@
         <v>159.74</v>
       </c>
       <c r="H46" t="n">
-        <v>141.21</v>
+        <v>140.69</v>
       </c>
       <c r="I46" t="n">
         <v>10</v>
@@ -2720,7 +2720,7 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>-1.16</v>
+        <v>-1.19</v>
       </c>
       <c r="Q46" t="inlineStr"/>
     </row>
@@ -2749,7 +2749,7 @@
         <v>30.97</v>
       </c>
       <c r="H47" t="n">
-        <v>27.15</v>
+        <v>24.44</v>
       </c>
       <c r="I47" t="n">
         <v>20</v>
@@ -2769,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>-2.47</v>
+        <v>-4.22</v>
       </c>
       <c r="Q47" t="inlineStr"/>
     </row>
@@ -2798,7 +2798,7 @@
         <v>9.880000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>8.859999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="I48" t="n">
         <v>9.880000000000001</v>
@@ -2818,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>-1.02</v>
+        <v>-1.6</v>
       </c>
       <c r="Q48" t="inlineStr"/>
     </row>
@@ -2847,7 +2847,7 @@
         <v>35.88</v>
       </c>
       <c r="H49" t="n">
-        <v>36.4</v>
+        <v>37.73</v>
       </c>
       <c r="I49" t="n">
         <v>2.57</v>
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0.03</v>
+        <v>0.13</v>
       </c>
       <c r="Q49" t="inlineStr"/>
     </row>
@@ -2896,7 +2896,7 @@
         <v>19.39</v>
       </c>
       <c r="H50" t="n">
-        <v>20.75</v>
+        <v>21.02</v>
       </c>
       <c r="I50" t="n">
         <v>10</v>
@@ -2916,7 +2916,7 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0.7</v>
+        <v>0.84</v>
       </c>
       <c r="Q50" t="inlineStr"/>
     </row>
@@ -2945,7 +2945,7 @@
         <v>235.53</v>
       </c>
       <c r="H51" t="n">
-        <v>262.31</v>
+        <v>268.11</v>
       </c>
       <c r="I51" t="n">
         <v>10.01</v>
@@ -2965,7 +2965,7 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="Q51" t="inlineStr"/>
     </row>
@@ -2994,7 +2994,7 @@
         <v>232.2</v>
       </c>
       <c r="H52" t="n">
-        <v>238.81</v>
+        <v>237.85</v>
       </c>
       <c r="I52" t="n">
         <v>0.02</v>
@@ -3043,7 +3043,7 @@
         <v>27.17</v>
       </c>
       <c r="H53" t="n">
-        <v>27.15</v>
+        <v>24.44</v>
       </c>
       <c r="I53" t="n">
         <v>9.98</v>
@@ -3063,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>-0.01</v>
+        <v>-1</v>
       </c>
       <c r="Q53" t="inlineStr"/>
     </row>
@@ -3092,7 +3092,7 @@
         <v>20.36</v>
       </c>
       <c r="H54" t="n">
-        <v>18.4</v>
+        <v>18.31</v>
       </c>
       <c r="I54" t="n">
         <v>20.36</v>
@@ -3112,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>-1.96</v>
+        <v>-2.05</v>
       </c>
       <c r="Q54" t="inlineStr"/>
     </row>
@@ -3141,7 +3141,7 @@
         <v>15.55</v>
       </c>
       <c r="H55" t="n">
-        <v>24.13</v>
+        <v>23.89</v>
       </c>
       <c r="I55" t="n">
         <v>10</v>
@@ -3161,7 +3161,7 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>5.52</v>
+        <v>5.36</v>
       </c>
       <c r="Q55" t="inlineStr"/>
     </row>
@@ -3190,7 +3190,7 @@
         <v>16.12</v>
       </c>
       <c r="H56" t="n">
-        <v>20.75</v>
+        <v>21.02</v>
       </c>
       <c r="I56" t="n">
         <v>3.88</v>
@@ -3210,7 +3210,7 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="Q56" t="inlineStr"/>
     </row>
@@ -3239,7 +3239,7 @@
         <v>534.86</v>
       </c>
       <c r="H57" t="n">
-        <v>598.13</v>
+        <v>586.48</v>
       </c>
       <c r="I57" t="n">
         <v>4.33</v>
@@ -3259,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>0.51</v>
+        <v>0.42</v>
       </c>
       <c r="Q57" t="inlineStr"/>
     </row>
@@ -3288,7 +3288,7 @@
         <v>41.99</v>
       </c>
       <c r="H58" t="n">
-        <v>51.79</v>
+        <v>51.49</v>
       </c>
       <c r="I58" t="n">
         <v>25</v>
@@ -3308,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>5.83</v>
+        <v>5.65</v>
       </c>
       <c r="Q58" t="inlineStr"/>
     </row>
@@ -3337,7 +3337,7 @@
         <v>156.9</v>
       </c>
       <c r="H59" t="n">
-        <v>210.26</v>
+        <v>208.95</v>
       </c>
       <c r="I59" t="n">
         <v>6.64</v>
@@ -3357,7 +3357,7 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q59" t="inlineStr"/>
     </row>
@@ -3386,7 +3386,7 @@
         <v>19.43</v>
       </c>
       <c r="H60" t="n">
-        <v>24.13</v>
+        <v>23.89</v>
       </c>
       <c r="I60" t="n">
         <v>0.58</v>
@@ -3406,7 +3406,7 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="Q60" t="inlineStr"/>
     </row>
@@ -3435,7 +3435,7 @@
         <v>21.82</v>
       </c>
       <c r="H61" t="n">
-        <v>24.13</v>
+        <v>23.89</v>
       </c>
       <c r="I61" t="n">
         <v>10</v>
@@ -3455,7 +3455,7 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>1.06</v>
+        <v>0.95</v>
       </c>
       <c r="Q61" t="inlineStr"/>
     </row>
@@ -3484,7 +3484,7 @@
         <v>17.97</v>
       </c>
       <c r="H62" t="n">
-        <v>18.99</v>
+        <v>19.1</v>
       </c>
       <c r="I62" t="n">
         <v>17.97</v>
@@ -3504,7 +3504,7 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="Q62" t="inlineStr"/>
     </row>
@@ -3533,7 +3533,7 @@
         <v>72.87</v>
       </c>
       <c r="H63" t="n">
-        <v>74.58</v>
+        <v>74.39</v>
       </c>
       <c r="I63" t="n">
         <v>72.87</v>
@@ -3553,7 +3553,7 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="Q63" t="inlineStr"/>
     </row>
@@ -3582,7 +3582,7 @@
         <v>24.11</v>
       </c>
       <c r="H64" t="n">
-        <v>24.13</v>
+        <v>23.89</v>
       </c>
       <c r="I64" t="n">
         <v>0.91</v>
@@ -3602,7 +3602,7 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="Q64" t="inlineStr"/>
     </row>
@@ -3631,7 +3631,7 @@
         <v>127.06</v>
       </c>
       <c r="H65" t="n">
-        <v>123.49</v>
+        <v>123.6</v>
       </c>
       <c r="I65" t="n">
         <v>10</v>
@@ -3651,7 +3651,7 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="Q65" t="inlineStr"/>
     </row>
@@ -3680,7 +3680,7 @@
         <v>127.16</v>
       </c>
       <c r="H66" t="n">
-        <v>123.49</v>
+        <v>123.6</v>
       </c>
       <c r="I66" t="n">
         <v>19.99</v>
@@ -3700,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>-0.58</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="Q66" t="inlineStr"/>
     </row>
@@ -3729,7 +3729,7 @@
         <v>33.66</v>
       </c>
       <c r="H67" t="n">
-        <v>33.1</v>
+        <v>32.44</v>
       </c>
       <c r="I67" t="n">
         <v>3.67</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>-0.06</v>
+        <v>-0.13</v>
       </c>
       <c r="Q67" t="inlineStr"/>
     </row>
@@ -3778,7 +3778,7 @@
         <v>20.65</v>
       </c>
       <c r="H68" t="n">
-        <v>18.4</v>
+        <v>18.31</v>
       </c>
       <c r="I68" t="n">
         <v>20.65</v>
@@ -3798,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>-2.25</v>
+        <v>-2.34</v>
       </c>
       <c r="Q68" t="inlineStr"/>
     </row>
@@ -3827,7 +3827,7 @@
         <v>12.88</v>
       </c>
       <c r="H69" t="n">
-        <v>16.025</v>
+        <v>16.205</v>
       </c>
       <c r="I69" t="n">
         <v>5.13</v>
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="Q69" t="inlineStr"/>
     </row>
@@ -3876,7 +3876,7 @@
         <v>34.44</v>
       </c>
       <c r="H70" t="n">
-        <v>37.8</v>
+        <v>37.98</v>
       </c>
       <c r="I70" t="n">
         <v>34.44</v>
@@ -3896,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>3.36</v>
+        <v>3.54</v>
       </c>
       <c r="Q70" t="inlineStr"/>
     </row>
@@ -3925,7 +3925,7 @@
         <v>77.93000000000001</v>
       </c>
       <c r="H71" t="n">
-        <v>101.74</v>
+        <v>102.41</v>
       </c>
       <c r="I71" t="n">
         <v>0.65</v>
@@ -3945,7 +3945,7 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="Q71" t="inlineStr"/>
     </row>
@@ -3974,7 +3974,7 @@
         <v>21.33</v>
       </c>
       <c r="H72" t="n">
-        <v>25.33</v>
+        <v>25.31</v>
       </c>
       <c r="I72" t="n">
         <v>19.99</v>
@@ -3994,7 +3994,7 @@
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="Q72" t="inlineStr"/>
     </row>
@@ -4023,7 +4023,7 @@
         <v>52.83</v>
       </c>
       <c r="H73" t="n">
-        <v>65.51000000000001</v>
+        <v>63.95</v>
       </c>
       <c r="I73" t="n">
         <v>15</v>
@@ -4043,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>3.6</v>
+        <v>3.16</v>
       </c>
       <c r="Q73" t="inlineStr"/>
     </row>
@@ -4072,7 +4072,7 @@
         <v>44.66</v>
       </c>
       <c r="H74" t="n">
-        <v>51.79</v>
+        <v>51.49</v>
       </c>
       <c r="I74" t="n">
         <v>20</v>
@@ -4092,7 +4092,7 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>3.19</v>
+        <v>3.06</v>
       </c>
       <c r="Q74" t="inlineStr"/>
     </row>
@@ -4121,7 +4121,7 @@
         <v>58.05</v>
       </c>
       <c r="H75" t="n">
-        <v>65.51000000000001</v>
+        <v>63.95</v>
       </c>
       <c r="I75" t="n">
         <v>14.99</v>
@@ -4141,7 +4141,7 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>1.93</v>
+        <v>1.53</v>
       </c>
       <c r="Q75" t="inlineStr"/>
     </row>
@@ -4170,7 +4170,7 @@
         <v>61.81</v>
       </c>
       <c r="H76" t="n">
-        <v>61.04</v>
+        <v>61.37</v>
       </c>
       <c r="I76" t="n">
         <v>20</v>
@@ -4190,7 +4190,7 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>-0.25</v>
+        <v>-0.15</v>
       </c>
       <c r="Q76" t="inlineStr"/>
     </row>
@@ -4219,7 +4219,7 @@
         <v>324.48</v>
       </c>
       <c r="H77" t="n">
-        <v>345.85</v>
+        <v>338.11</v>
       </c>
       <c r="I77" t="n">
         <v>6.23</v>
@@ -4239,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>0.41</v>
+        <v>0.26</v>
       </c>
       <c r="Q77" t="inlineStr"/>
     </row>
@@ -4268,7 +4268,7 @@
         <v>12.42</v>
       </c>
       <c r="H78" t="n">
-        <v>8.859999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="I78" t="n">
         <v>10</v>
@@ -4288,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>-2.87</v>
+        <v>-3.33</v>
       </c>
       <c r="Q78" t="inlineStr"/>
     </row>
@@ -4317,7 +4317,7 @@
         <v>128.25</v>
       </c>
       <c r="H79" t="n">
-        <v>123.49</v>
+        <v>123.6</v>
       </c>
       <c r="I79" t="n">
         <v>9.99</v>
@@ -4337,7 +4337,7 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>-0.37</v>
+        <v>-0.36</v>
       </c>
       <c r="Q79" t="inlineStr"/>
     </row>
@@ -4366,7 +4366,7 @@
         <v>319.83</v>
       </c>
       <c r="H80" t="n">
-        <v>320.42</v>
+        <v>342.82</v>
       </c>
       <c r="I80" t="n">
         <v>15</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>0.03</v>
+        <v>1.08</v>
       </c>
       <c r="Q80" t="inlineStr"/>
     </row>
@@ -4415,7 +4415,7 @@
         <v>44.1</v>
       </c>
       <c r="H81" t="n">
-        <v>43.22</v>
+        <v>43.1</v>
       </c>
       <c r="I81" t="n">
         <v>10</v>
@@ -4435,7 +4435,7 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>-0.2</v>
+        <v>-0.23</v>
       </c>
       <c r="Q81" t="inlineStr"/>
     </row>
@@ -4464,7 +4464,7 @@
         <v>34.58</v>
       </c>
       <c r="H82" t="n">
-        <v>37.8</v>
+        <v>37.98</v>
       </c>
       <c r="I82" t="n">
         <v>34.58</v>
@@ -4484,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="Q82" t="inlineStr"/>
     </row>
@@ -4513,7 +4513,7 @@
         <v>144.94</v>
       </c>
       <c r="H83" t="n">
-        <v>141.21</v>
+        <v>140.69</v>
       </c>
       <c r="I83" t="n">
         <v>10.99</v>
@@ -4533,7 +4533,7 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>-0.29</v>
+        <v>-0.33</v>
       </c>
       <c r="Q83" t="inlineStr"/>
     </row>
@@ -4562,7 +4562,7 @@
         <v>21.21</v>
       </c>
       <c r="H84" t="n">
-        <v>18.4</v>
+        <v>18.31</v>
       </c>
       <c r="I84" t="n">
         <v>21.21</v>
@@ -4582,7 +4582,7 @@
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>-2.81</v>
+        <v>-2.9</v>
       </c>
       <c r="Q84" t="inlineStr"/>
     </row>
@@ -4611,7 +4611,7 @@
         <v>195.52</v>
       </c>
       <c r="H85" t="n">
-        <v>210.26</v>
+        <v>208.95</v>
       </c>
       <c r="I85" t="n">
         <v>10.01</v>
@@ -4631,7 +4631,7 @@
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>0.76</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q85" t="inlineStr"/>
     </row>
@@ -4660,7 +4660,7 @@
         <v>67.93000000000001</v>
       </c>
       <c r="H86" t="n">
-        <v>70.22</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="I86" t="n">
         <v>4.54</v>
@@ -4680,7 +4680,7 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="Q86" t="inlineStr"/>
     </row>
@@ -4709,7 +4709,7 @@
         <v>42.29</v>
       </c>
       <c r="H87" t="n">
-        <v>51.79</v>
+        <v>51.49</v>
       </c>
       <c r="I87" t="n">
         <v>20</v>
@@ -4729,7 +4729,7 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>4.49</v>
+        <v>4.35</v>
       </c>
       <c r="Q87" t="inlineStr"/>
     </row>
@@ -4758,7 +4758,7 @@
         <v>148.02</v>
       </c>
       <c r="H88" t="n">
-        <v>141.21</v>
+        <v>140.69</v>
       </c>
       <c r="I88" t="n">
         <v>14.99</v>
@@ -4778,7 +4778,7 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.74</v>
       </c>
       <c r="Q88" t="inlineStr"/>
     </row>
@@ -4807,7 +4807,7 @@
         <v>18.26</v>
       </c>
       <c r="H89" t="n">
-        <v>24.13</v>
+        <v>23.89</v>
       </c>
       <c r="I89" t="n">
         <v>10</v>
@@ -4827,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="Q89" t="inlineStr"/>
     </row>
@@ -4856,7 +4856,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="H90" t="n">
-        <v>8.859999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="I90" t="n">
         <v>0.13</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="Q90" t="inlineStr"/>
     </row>
@@ -4905,7 +4905,7 @@
         <v>22.39</v>
       </c>
       <c r="H91" t="n">
-        <v>25.17</v>
+        <v>23.96</v>
       </c>
       <c r="I91" t="n">
         <v>10</v>
@@ -4925,7 +4925,7 @@
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>1.24</v>
+        <v>0.7</v>
       </c>
       <c r="Q91" t="inlineStr"/>
     </row>
@@ -4954,7 +4954,7 @@
         <v>21.13</v>
       </c>
       <c r="H92" t="n">
-        <v>18.4</v>
+        <v>18.31</v>
       </c>
       <c r="I92" t="n">
         <v>21.13</v>
@@ -4974,7 +4974,7 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>-2.73</v>
+        <v>-2.82</v>
       </c>
       <c r="Q92" t="inlineStr"/>
     </row>
@@ -5003,7 +5003,7 @@
         <v>37.7</v>
       </c>
       <c r="H93" t="n">
-        <v>27.15</v>
+        <v>24.44</v>
       </c>
       <c r="I93" t="n">
         <v>9.99</v>
@@ -5023,7 +5023,7 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>-2.79</v>
+        <v>-3.51</v>
       </c>
       <c r="Q93" t="inlineStr"/>
     </row>
@@ -5052,7 +5052,7 @@
         <v>42.66</v>
       </c>
       <c r="H94" t="n">
-        <v>43.22</v>
+        <v>43.1</v>
       </c>
       <c r="I94" t="n">
         <v>10</v>
@@ -5072,7 +5072,7 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="Q94" t="inlineStr"/>
     </row>
@@ -5101,7 +5101,7 @@
         <v>130.51</v>
       </c>
       <c r="H95" t="n">
-        <v>148.1</v>
+        <v>145.15</v>
       </c>
       <c r="I95" t="n">
         <v>0.04</v>
@@ -5150,7 +5150,7 @@
         <v>16.12</v>
       </c>
       <c r="H96" t="n">
-        <v>20.75</v>
+        <v>21.02</v>
       </c>
       <c r="I96" t="n">
         <v>16.12</v>
@@ -5170,7 +5170,7 @@
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>4.63</v>
+        <v>4.9</v>
       </c>
       <c r="Q96" t="inlineStr"/>
     </row>
@@ -5199,7 +5199,7 @@
         <v>139.86</v>
       </c>
       <c r="H97" t="n">
-        <v>148.1</v>
+        <v>145.15</v>
       </c>
       <c r="I97" t="n">
         <v>10</v>
@@ -5219,7 +5219,7 @@
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>0.59</v>
+        <v>0.38</v>
       </c>
       <c r="Q97" t="inlineStr"/>
     </row>
@@ -5248,7 +5248,7 @@
         <v>227.95</v>
       </c>
       <c r="H98" t="n">
-        <v>262.31</v>
+        <v>268.11</v>
       </c>
       <c r="I98" t="n">
         <v>10.01</v>
@@ -5268,7 +5268,7 @@
         <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>1.51</v>
+        <v>1.76</v>
       </c>
       <c r="Q98" t="inlineStr"/>
     </row>
@@ -5297,7 +5297,7 @@
         <v>33.47</v>
       </c>
       <c r="H99" t="n">
-        <v>27.15</v>
+        <v>24.44</v>
       </c>
       <c r="I99" t="n">
         <v>10</v>
@@ -5317,7 +5317,7 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>-1.89</v>
+        <v>-2.7</v>
       </c>
       <c r="Q99" t="inlineStr"/>
     </row>
@@ -5346,7 +5346,7 @@
         <v>17.86</v>
       </c>
       <c r="H100" t="n">
-        <v>20.75</v>
+        <v>21.02</v>
       </c>
       <c r="I100" t="n">
         <v>2.14</v>
@@ -5366,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="Q100" t="inlineStr"/>
     </row>
@@ -5395,7 +5395,7 @@
         <v>165.93</v>
       </c>
       <c r="H101" t="n">
-        <v>141.21</v>
+        <v>140.69</v>
       </c>
       <c r="I101" t="n">
         <v>17.94</v>
@@ -5415,7 +5415,7 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>-2.67</v>
+        <v>-2.72</v>
       </c>
       <c r="Q101" t="inlineStr"/>
     </row>
@@ -5444,7 +5444,7 @@
         <v>22.59</v>
       </c>
       <c r="H102" t="n">
-        <v>25.33</v>
+        <v>25.31</v>
       </c>
       <c r="I102" t="n">
         <v>9.99</v>
@@ -5464,7 +5464,7 @@
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Q102" t="inlineStr"/>
     </row>
@@ -5493,7 +5493,7 @@
         <v>216.54</v>
       </c>
       <c r="H103" t="n">
-        <v>278.14</v>
+        <v>261.65</v>
       </c>
       <c r="I103" t="n">
         <v>0.5</v>
@@ -5513,7 +5513,7 @@
         <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="Q103" t="inlineStr"/>
     </row>
@@ -5542,7 +5542,7 @@
         <v>24.19</v>
       </c>
       <c r="H104" t="n">
-        <v>25.17</v>
+        <v>23.96</v>
       </c>
       <c r="I104" t="n">
         <v>10</v>
@@ -5562,7 +5562,7 @@
         <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="Q104" t="inlineStr"/>
     </row>
@@ -5591,7 +5591,7 @@
         <v>197.26</v>
       </c>
       <c r="H105" t="n">
-        <v>210.26</v>
+        <v>208.95</v>
       </c>
       <c r="I105" t="n">
         <v>10</v>
@@ -5611,7 +5611,7 @@
         <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>0.66</v>
+        <v>0.59</v>
       </c>
       <c r="Q105" t="inlineStr"/>
     </row>
@@ -5640,7 +5640,7 @@
         <v>162.85</v>
       </c>
       <c r="H106" t="n">
-        <v>141.21</v>
+        <v>140.69</v>
       </c>
       <c r="I106" t="n">
         <v>14.98</v>
@@ -5660,7 +5660,7 @@
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>-1.99</v>
+        <v>-2.04</v>
       </c>
       <c r="Q106" t="inlineStr"/>
     </row>
@@ -5689,7 +5689,7 @@
         <v>129.17</v>
       </c>
       <c r="H107" t="n">
-        <v>141.21</v>
+        <v>140.69</v>
       </c>
       <c r="I107" t="n">
         <v>20</v>
@@ -5709,7 +5709,7 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="Q107" t="inlineStr"/>
     </row>
@@ -5738,7 +5738,7 @@
         <v>43</v>
       </c>
       <c r="H108" t="n">
-        <v>43.22</v>
+        <v>43.1</v>
       </c>
       <c r="I108" t="n">
         <v>0</v>
@@ -5787,7 +5787,7 @@
         <v>148.09</v>
       </c>
       <c r="H109" t="n">
-        <v>262.31</v>
+        <v>268.11</v>
       </c>
       <c r="I109" t="n">
         <v>40</v>
@@ -5807,7 +5807,7 @@
         <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>30.85</v>
+        <v>32.42</v>
       </c>
       <c r="Q109" t="inlineStr"/>
     </row>
@@ -5836,7 +5836,7 @@
         <v>17.18</v>
       </c>
       <c r="H110" t="n">
-        <v>25.33</v>
+        <v>25.31</v>
       </c>
       <c r="I110" t="n">
         <v>2.82</v>
@@ -5856,7 +5856,7 @@
         <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Q110" t="inlineStr"/>
     </row>
@@ -5885,7 +5885,7 @@
         <v>12.875</v>
       </c>
       <c r="H111" t="n">
-        <v>16.025</v>
+        <v>16.205</v>
       </c>
       <c r="I111" t="n">
         <v>14.86</v>
@@ -5905,7 +5905,7 @@
         <v>0</v>
       </c>
       <c r="P111" t="n">
-        <v>4.04</v>
+        <v>4.15</v>
       </c>
       <c r="Q111" t="inlineStr"/>
     </row>
@@ -5934,7 +5934,7 @@
         <v>47.58</v>
       </c>
       <c r="H112" t="n">
-        <v>54.49</v>
+        <v>54.27</v>
       </c>
       <c r="I112" t="n">
         <v>47.58</v>
@@ -5954,7 +5954,7 @@
         <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>6.91</v>
+        <v>6.69</v>
       </c>
       <c r="Q112" t="inlineStr"/>
     </row>
@@ -5983,7 +5983,7 @@
         <v>143.6</v>
       </c>
       <c r="H113" t="n">
-        <v>148.1</v>
+        <v>145.15</v>
       </c>
       <c r="I113" t="n">
         <v>14.99</v>
@@ -6003,7 +6003,7 @@
         <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>0.47</v>
+        <v>0.16</v>
       </c>
       <c r="Q113" t="inlineStr"/>
     </row>
@@ -6032,7 +6032,7 @@
         <v>13.285</v>
       </c>
       <c r="H114" t="n">
-        <v>16.025</v>
+        <v>16.205</v>
       </c>
       <c r="I114" t="n">
         <v>15.31</v>
@@ -6052,7 +6052,7 @@
         <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>3.59</v>
+        <v>3.7</v>
       </c>
       <c r="Q114" t="inlineStr"/>
     </row>
@@ -6081,7 +6081,7 @@
         <v>50.99</v>
       </c>
       <c r="H115" t="n">
-        <v>65.51000000000001</v>
+        <v>63.95</v>
       </c>
       <c r="I115" t="n">
         <v>19.13</v>
@@ -6101,7 +6101,7 @@
         <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>5.45</v>
+        <v>4.86</v>
       </c>
       <c r="Q115" t="inlineStr"/>
     </row>
@@ -6130,7 +6130,7 @@
         <v>21.17</v>
       </c>
       <c r="H116" t="n">
-        <v>18.4</v>
+        <v>18.31</v>
       </c>
       <c r="I116" t="n">
         <v>21.17</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>-2.77</v>
+        <v>-2.86</v>
       </c>
       <c r="Q116" t="inlineStr"/>
     </row>
@@ -6179,7 +6179,7 @@
         <v>15.72</v>
       </c>
       <c r="H117" t="n">
-        <v>24.13</v>
+        <v>23.89</v>
       </c>
       <c r="I117" t="n">
         <v>10</v>
@@ -6199,7 +6199,7 @@
         <v>0</v>
       </c>
       <c r="P117" t="n">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="Q117" t="inlineStr"/>
     </row>
@@ -6228,7 +6228,7 @@
         <v>27.91</v>
       </c>
       <c r="H118" t="n">
-        <v>27.15</v>
+        <v>24.44</v>
       </c>
       <c r="I118" t="n">
         <v>10.08</v>
@@ -6248,7 +6248,7 @@
         <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>-0.28</v>
+        <v>-1.25</v>
       </c>
       <c r="Q118" t="inlineStr"/>
     </row>
@@ -6277,7 +6277,7 @@
         <v>64.18000000000001</v>
       </c>
       <c r="H119" t="n">
-        <v>65.51000000000001</v>
+        <v>63.95</v>
       </c>
       <c r="I119" t="n">
         <v>10</v>
@@ -6297,7 +6297,7 @@
         <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>0.21</v>
+        <v>-0.04</v>
       </c>
       <c r="Q119" t="inlineStr"/>
     </row>
@@ -6326,7 +6326,7 @@
         <v>83.47499999999999</v>
       </c>
       <c r="H120" t="n">
-        <v>87.7</v>
+        <v>89.47</v>
       </c>
       <c r="I120" t="n">
         <v>10</v>
@@ -6346,7 +6346,7 @@
         <v>0</v>
       </c>
       <c r="P120" t="n">
-        <v>0.52</v>
+        <v>0.67</v>
       </c>
       <c r="Q120" t="inlineStr"/>
     </row>
@@ -6375,7 +6375,7 @@
         <v>72.94</v>
       </c>
       <c r="H121" t="n">
-        <v>70.22</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="I121" t="n">
         <v>10.01</v>
@@ -6395,7 +6395,7 @@
         <v>0</v>
       </c>
       <c r="P121" t="n">
-        <v>-0.38</v>
+        <v>-0.3</v>
       </c>
       <c r="Q121" t="inlineStr"/>
     </row>
@@ -6424,7 +6424,7 @@
         <v>303.76</v>
       </c>
       <c r="H122" t="n">
-        <v>320.42</v>
+        <v>342.82</v>
       </c>
       <c r="I122" t="n">
         <v>10.02</v>
@@ -6444,7 +6444,7 @@
         <v>0</v>
       </c>
       <c r="P122" t="n">
-        <v>0.55</v>
+        <v>1.29</v>
       </c>
       <c r="Q122" t="inlineStr"/>
     </row>
@@ -6473,7 +6473,7 @@
         <v>166.03</v>
       </c>
       <c r="H123" t="n">
-        <v>141.21</v>
+        <v>140.69</v>
       </c>
       <c r="I123" t="n">
         <v>10</v>
@@ -6493,7 +6493,7 @@
         <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>-1.5</v>
+        <v>-1.53</v>
       </c>
       <c r="Q123" t="inlineStr"/>
     </row>
@@ -6522,7 +6522,7 @@
         <v>142.99</v>
       </c>
       <c r="H124" t="n">
-        <v>210.26</v>
+        <v>208.95</v>
       </c>
       <c r="I124" t="n">
         <v>14.97</v>
@@ -6542,7 +6542,7 @@
         <v>0</v>
       </c>
       <c r="P124" t="n">
-        <v>7.04</v>
+        <v>6.91</v>
       </c>
       <c r="Q124" t="inlineStr"/>
     </row>
@@ -6571,7 +6571,7 @@
         <v>408.33</v>
       </c>
       <c r="H125" t="n">
-        <v>509.58</v>
+        <v>508.36</v>
       </c>
       <c r="I125" t="n">
         <v>0.41</v>
@@ -6620,7 +6620,7 @@
         <v>346.61</v>
       </c>
       <c r="H126" t="n">
-        <v>345.85</v>
+        <v>338.11</v>
       </c>
       <c r="I126" t="n">
         <v>14.97</v>
@@ -6640,7 +6640,7 @@
         <v>0</v>
       </c>
       <c r="P126" t="n">
-        <v>-0.03</v>
+        <v>-0.36</v>
       </c>
       <c r="Q126" t="inlineStr"/>
     </row>
@@ -6669,7 +6669,7 @@
         <v>31.61</v>
       </c>
       <c r="H127" t="n">
-        <v>27.15</v>
+        <v>24.44</v>
       </c>
       <c r="I127" t="n">
         <v>10</v>
@@ -6689,7 +6689,7 @@
         <v>0</v>
       </c>
       <c r="P127" t="n">
-        <v>-1.42</v>
+        <v>-2.27</v>
       </c>
       <c r="Q127" t="inlineStr"/>
     </row>
@@ -6718,7 +6718,7 @@
         <v>17.64</v>
       </c>
       <c r="H128" t="n">
-        <v>20.75</v>
+        <v>21.02</v>
       </c>
       <c r="I128" t="n">
         <v>17.64</v>
@@ -6738,7 +6738,7 @@
         <v>0</v>
       </c>
       <c r="P128" t="n">
-        <v>3.11</v>
+        <v>3.38</v>
       </c>
       <c r="Q128" t="inlineStr"/>
     </row>
@@ -6767,7 +6767,7 @@
         <v>21.27</v>
       </c>
       <c r="H129" t="n">
-        <v>18.4</v>
+        <v>18.31</v>
       </c>
       <c r="I129" t="n">
         <v>21.27</v>
@@ -6787,7 +6787,7 @@
         <v>0</v>
       </c>
       <c r="P129" t="n">
-        <v>-2.87</v>
+        <v>-2.96</v>
       </c>
       <c r="Q129" t="inlineStr"/>
     </row>
@@ -6816,7 +6816,7 @@
         <v>15.3</v>
       </c>
       <c r="H130" t="n">
-        <v>25.33</v>
+        <v>25.31</v>
       </c>
       <c r="I130" t="n">
         <v>0.76</v>
@@ -6865,7 +6865,7 @@
         <v>20.24</v>
       </c>
       <c r="H131" t="n">
-        <v>18.4</v>
+        <v>18.31</v>
       </c>
       <c r="I131" t="n">
         <v>20.24</v>
@@ -6885,7 +6885,7 @@
         <v>0</v>
       </c>
       <c r="P131" t="n">
-        <v>-1.84</v>
+        <v>-1.93</v>
       </c>
       <c r="Q131" t="inlineStr"/>
     </row>
@@ -6914,7 +6914,7 @@
         <v>36.17</v>
       </c>
       <c r="H132" t="n">
-        <v>36.4</v>
+        <v>37.73</v>
       </c>
       <c r="I132" t="n">
         <v>10.01</v>
@@ -6934,7 +6934,7 @@
         <v>0</v>
       </c>
       <c r="P132" t="n">
-        <v>0.06</v>
+        <v>0.43</v>
       </c>
       <c r="Q132" t="inlineStr"/>
     </row>
@@ -6963,7 +6963,7 @@
         <v>20.6</v>
       </c>
       <c r="H133" t="n">
-        <v>24.13</v>
+        <v>23.89</v>
       </c>
       <c r="I133" t="n">
         <v>14.99</v>
@@ -6983,7 +6983,7 @@
         <v>0</v>
       </c>
       <c r="P133" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="Q133" t="inlineStr"/>
     </row>
@@ -7012,7 +7012,7 @@
         <v>23.72</v>
       </c>
       <c r="H134" t="n">
-        <v>25.33</v>
+        <v>25.31</v>
       </c>
       <c r="I134" t="n">
         <v>15</v>
@@ -7032,7 +7032,7 @@
         <v>0</v>
       </c>
       <c r="P134" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Q134" t="inlineStr"/>
     </row>
@@ -7061,7 +7061,7 @@
         <v>44.24</v>
       </c>
       <c r="H135" t="n">
-        <v>54.49</v>
+        <v>54.27</v>
       </c>
       <c r="I135" t="n">
         <v>44.24</v>
@@ -7081,7 +7081,7 @@
         <v>0</v>
       </c>
       <c r="P135" t="n">
-        <v>10.25</v>
+        <v>10.03</v>
       </c>
       <c r="Q135" t="inlineStr"/>
     </row>
@@ -7110,7 +7110,7 @@
         <v>15.57</v>
       </c>
       <c r="H136" t="n">
-        <v>20.75</v>
+        <v>21.02</v>
       </c>
       <c r="I136" t="n">
         <v>8.01</v>
@@ -7130,7 +7130,7 @@
         <v>0</v>
       </c>
       <c r="P136" t="n">
-        <v>2.67</v>
+        <v>2.81</v>
       </c>
       <c r="Q136" t="inlineStr"/>
     </row>
@@ -7159,7 +7159,7 @@
         <v>21.66</v>
       </c>
       <c r="H137" t="n">
-        <v>18.4</v>
+        <v>18.31</v>
       </c>
       <c r="I137" t="n">
         <v>21.66</v>
@@ -7179,7 +7179,7 @@
         <v>0</v>
       </c>
       <c r="P137" t="n">
-        <v>-3.26</v>
+        <v>-3.35</v>
       </c>
       <c r="Q137" t="inlineStr"/>
     </row>
@@ -7208,7 +7208,7 @@
         <v>43.27</v>
       </c>
       <c r="H138" t="n">
-        <v>27.15</v>
+        <v>24.44</v>
       </c>
       <c r="I138" t="n">
         <v>10.03</v>
@@ -7228,7 +7228,7 @@
         <v>0</v>
       </c>
       <c r="P138" t="n">
-        <v>-3.74</v>
+        <v>-4.36</v>
       </c>
       <c r="Q138" t="inlineStr"/>
     </row>
@@ -7257,7 +7257,7 @@
         <v>250.56</v>
       </c>
       <c r="H139" t="n">
-        <v>251</v>
+        <v>249.81</v>
       </c>
       <c r="I139" t="n">
         <v>49.99</v>
@@ -7277,7 +7277,7 @@
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>-0.4</v>
+        <v>-1.02</v>
       </c>
       <c r="Q139" t="inlineStr"/>
     </row>
@@ -7306,7 +7306,7 @@
         <v>14</v>
       </c>
       <c r="H140" t="n">
-        <v>24.13</v>
+        <v>23.89</v>
       </c>
       <c r="I140" t="n">
         <v>9.99</v>
@@ -7326,7 +7326,7 @@
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>7.23</v>
+        <v>7.06</v>
       </c>
       <c r="Q140" t="inlineStr"/>
     </row>
@@ -7355,7 +7355,7 @@
         <v>20.69</v>
       </c>
       <c r="H141" t="n">
-        <v>24.13</v>
+        <v>23.89</v>
       </c>
       <c r="I141" t="n">
         <v>10</v>
@@ -7375,7 +7375,7 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="Q141" t="inlineStr"/>
     </row>
@@ -7406,7 +7406,7 @@
         <v>0</v>
       </c>
       <c r="P142" t="n">
-        <v>184.93</v>
+        <v>169.67</v>
       </c>
       <c r="Q142" t="inlineStr"/>
     </row>

--- a/Stock Selection/OPEN POSITION.xlsx
+++ b/Stock Selection/OPEN POSITION.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q142"/>
+  <dimension ref="A1:Q147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,7 +522,7 @@
     <row r="2">
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="n">
-        <v>1867458993</v>
+        <v>1461331124</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.3417</v>
+        <v>0.3752</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45818.90699613426</v>
+        <v>45553.65374138889</v>
       </c>
       <c r="G2" t="n">
-        <v>58.53</v>
+        <v>50.99</v>
       </c>
       <c r="H2" t="n">
-        <v>63.95</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>19.13</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -564,18 +564,18 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.85</v>
+        <v>5.52</v>
       </c>
       <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="n">
-        <v>1869077157</v>
+        <v>1843474191</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -584,19 +584,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.3061</v>
+        <v>0.9372</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45819.6742621412</v>
+        <v>45804.66699503472</v>
       </c>
       <c r="G3" t="n">
-        <v>13.285</v>
+        <v>21.33</v>
       </c>
       <c r="H3" t="n">
-        <v>16.205</v>
+        <v>25.77</v>
       </c>
       <c r="I3" t="n">
-        <v>4.69</v>
+        <v>19.99</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -613,18 +613,18 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.13</v>
+        <v>4.16</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="n">
-        <v>1582723120</v>
+        <v>2000138014</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -633,19 +633,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.3755</v>
+        <v>0.1017</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45645.89511640046</v>
+        <v>45901.57795706019</v>
       </c>
       <c r="G4" t="n">
-        <v>53.26</v>
+        <v>83.47499999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>63.95</v>
+        <v>92.845</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -662,18 +662,18 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>4.01</v>
+        <v>1.03</v>
       </c>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="n">
-        <v>1923250768</v>
+        <v>1843477272</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45853.65447396991</v>
+        <v>45804.66725678241</v>
       </c>
       <c r="G5" t="n">
-        <v>12.76</v>
+        <v>17.86</v>
       </c>
       <c r="H5" t="n">
-        <v>16.205</v>
+        <v>20.97</v>
       </c>
       <c r="I5" t="n">
-        <v>13</v>
+        <v>17.86</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -711,18 +711,18 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.54</v>
+        <v>3.11</v>
       </c>
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="n">
-        <v>2002501482</v>
+        <v>1843470413</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0526</v>
+        <v>0.4515</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45902.65588916666</v>
+        <v>45804.66637251157</v>
       </c>
       <c r="G6" t="n">
-        <v>190.17</v>
+        <v>42.29</v>
       </c>
       <c r="H6" t="n">
-        <v>208.95</v>
+        <v>52</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>19.09</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -760,18 +760,18 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.99</v>
+        <v>4.39</v>
       </c>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="n">
-        <v>1993384302</v>
+        <v>1981010841</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -780,19 +780,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.1347</v>
+        <v>0.0425</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45896.66850298611</v>
+        <v>45888.84617734954</v>
       </c>
       <c r="G7" t="n">
-        <v>74.23</v>
+        <v>235.53</v>
       </c>
       <c r="H7" t="n">
-        <v>70.73999999999999</v>
+        <v>292.04</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -809,18 +809,18 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.47</v>
+        <v>2.4</v>
       </c>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>1680993370</v>
+        <v>1976499401</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0.8064</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45716.85638861111</v>
+        <v>45884.83731814815</v>
       </c>
       <c r="G8" t="n">
-        <v>44.49</v>
+        <v>49.6</v>
       </c>
       <c r="H8" t="n">
-        <v>54.27</v>
+        <v>50.35</v>
       </c>
       <c r="I8" t="n">
-        <v>44.49</v>
+        <v>40</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -858,18 +858,18 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>9.779999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>1976499401</v>
+        <v>1997561527</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -878,19 +878,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.8064</v>
+        <v>0.1498</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45884.83731814815</v>
+        <v>45898.65748991898</v>
       </c>
       <c r="G9" t="n">
-        <v>49.6</v>
+        <v>66.73</v>
       </c>
       <c r="H9" t="n">
-        <v>49.82</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -907,18 +907,18 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
-        <v>1631475148</v>
+        <v>1883977086</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.2592</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45685.83625201389</v>
+        <v>45827.66106613426</v>
       </c>
       <c r="G10" t="n">
-        <v>38.58</v>
+        <v>12.875</v>
       </c>
       <c r="H10" t="n">
-        <v>24.44</v>
+        <v>16.435</v>
       </c>
       <c r="I10" t="n">
-        <v>10</v>
+        <v>14.86</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -956,18 +956,18 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.67</v>
+        <v>4.34</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
-        <v>1744916497</v>
+        <v>1642762235</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -976,19 +976,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0.1572</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45751.74231563658</v>
+        <v>45692.86612574074</v>
       </c>
       <c r="G11" t="n">
-        <v>17.54</v>
+        <v>127.16</v>
       </c>
       <c r="H11" t="n">
-        <v>25.31</v>
+        <v>120.6</v>
       </c>
       <c r="I11" t="n">
-        <v>17.54</v>
+        <v>19.99</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -1005,18 +1005,18 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>7.77</v>
+        <v>-1.03</v>
       </c>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>1666459270</v>
+        <v>2060620530</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>BLX</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1025,19 +1025,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0.2207</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>45708.68166530092</v>
+        <v>45932.89856876157</v>
       </c>
       <c r="G12" t="n">
-        <v>17.18</v>
+        <v>45.28</v>
       </c>
       <c r="H12" t="n">
-        <v>25.31</v>
+        <v>44.99</v>
       </c>
       <c r="I12" t="n">
-        <v>17.18</v>
+        <v>9.99</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -1054,18 +1054,18 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>8.130000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>1882281884</v>
+        <v>2047814173</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>IAPD.AS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1074,19 +1074,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.5688</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>45826.76479001158</v>
+        <v>45926.6592943287</v>
       </c>
       <c r="G13" t="n">
-        <v>138.84</v>
+        <v>22.46</v>
       </c>
       <c r="H13" t="n">
-        <v>145.15</v>
+        <v>22.9</v>
       </c>
       <c r="I13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -1103,18 +1103,18 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.45</v>
+        <v>0.22</v>
       </c>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="n">
-        <v>1888686062</v>
+        <v>1923258184</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.2903</v>
+        <v>0.0298</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>45831.64964792824</v>
+        <v>45853.6557568287</v>
       </c>
       <c r="G14" t="n">
-        <v>34.36</v>
+        <v>19.43</v>
       </c>
       <c r="H14" t="n">
-        <v>24.44</v>
+        <v>24.53</v>
       </c>
       <c r="I14" t="n">
-        <v>9.970000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -1152,18 +1152,18 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.88</v>
+        <v>0.15</v>
       </c>
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="n">
-        <v>1972092684</v>
+        <v>1621495187</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.2318</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>45882.68269449074</v>
+        <v>45678.83178196759</v>
       </c>
       <c r="G15" t="n">
-        <v>18.8</v>
+        <v>43.27</v>
       </c>
       <c r="H15" t="n">
-        <v>18.31</v>
+        <v>24.14</v>
       </c>
       <c r="I15" t="n">
-        <v>18.8</v>
+        <v>10.03</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1201,18 +1201,18 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.49</v>
+        <v>-4.43</v>
       </c>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="n">
-        <v>1845429980</v>
+        <v>1882278057</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0.0432</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>45805.66181400463</v>
+        <v>45826.76262912037</v>
       </c>
       <c r="G16" t="n">
-        <v>13.27</v>
+        <v>346.61</v>
       </c>
       <c r="H16" t="n">
-        <v>16.205</v>
+        <v>349.84</v>
       </c>
       <c r="I16" t="n">
-        <v>15.09</v>
+        <v>14.97</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1250,18 +1250,18 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.92</v>
+        <v>0.14</v>
       </c>
       <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="n">
-        <v>1845429956</v>
+        <v>2017852950</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1270,19 +1270,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.4821</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>45805.66180811343</v>
+        <v>45910.65507498843</v>
       </c>
       <c r="G17" t="n">
-        <v>13.275</v>
+        <v>37.44</v>
       </c>
       <c r="H17" t="n">
-        <v>16.205</v>
+        <v>43.52</v>
       </c>
       <c r="I17" t="n">
-        <v>7.28</v>
+        <v>37.44</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1299,18 +1299,18 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.88</v>
+        <v>6.08</v>
       </c>
       <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
-        <v>1729617775</v>
+        <v>1867458993</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.0546</v>
+        <v>0.3417</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45744.71339734954</v>
+        <v>45818.90699613426</v>
       </c>
       <c r="G18" t="n">
-        <v>165.35</v>
+        <v>58.53</v>
       </c>
       <c r="H18" t="n">
-        <v>268.11</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>9.029999999999999</v>
+        <v>20</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1348,18 +1348,18 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>5.61</v>
+        <v>2.45</v>
       </c>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="n">
-        <v>1712850989</v>
+        <v>1744879358</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1368,19 +1368,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.0002</v>
+        <v>0.1247</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45734.85576775463</v>
+        <v>45751.73925940973</v>
       </c>
       <c r="G19" t="n">
-        <v>160.64</v>
+        <v>148.09</v>
       </c>
       <c r="H19" t="n">
-        <v>252.1</v>
+        <v>292.04</v>
       </c>
       <c r="I19" t="n">
-        <v>0.03</v>
+        <v>18.47</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1397,14 +1397,14 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.02</v>
+        <v>17.95</v>
       </c>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
-        <v>2025662892</v>
+        <v>2042971604</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1417,19 +1417,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.8196</v>
+        <v>0.3901</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45915.72913914352</v>
+        <v>45924.70406969907</v>
       </c>
       <c r="G20" t="n">
-        <v>24.39</v>
+        <v>25.66</v>
       </c>
       <c r="H20" t="n">
-        <v>24.56</v>
+        <v>24.73</v>
       </c>
       <c r="I20" t="n">
-        <v>19.99</v>
+        <v>10.01</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1446,18 +1446,18 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.14</v>
+        <v>-0.36</v>
       </c>
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="n">
-        <v>1995249699</v>
+        <v>1744930699</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BTCE.DE</t>
+          <t>BND</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1466,19 +1466,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.4888</v>
+        <v>1</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45897.61086020833</v>
+        <v>45751.74534789352</v>
       </c>
       <c r="G21" t="n">
-        <v>87.16500000000001</v>
+        <v>74.13</v>
       </c>
       <c r="H21" t="n">
-        <v>89.47</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>49.99</v>
+        <v>74.13</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1495,18 +1495,18 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.31</v>
+        <v>0.16</v>
       </c>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="n">
-        <v>1727563010</v>
+        <v>1824475555</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1518,16 +1518,16 @@
         <v>1</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>45743.76106726852</v>
+        <v>45792.64702015046</v>
       </c>
       <c r="G22" t="n">
-        <v>46.11</v>
+        <v>21.66</v>
       </c>
       <c r="H22" t="n">
-        <v>54.27</v>
+        <v>17.37</v>
       </c>
       <c r="I22" t="n">
-        <v>46.11</v>
+        <v>21.66</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -1544,18 +1544,18 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>8.16</v>
+        <v>-4.29</v>
       </c>
       <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="n">
-        <v>1982273555</v>
+        <v>1997485943</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.0439</v>
+        <v>0.5157</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>45889.64957444445</v>
+        <v>45898.65185685185</v>
       </c>
       <c r="G23" t="n">
-        <v>228</v>
+        <v>19.39</v>
       </c>
       <c r="H23" t="n">
-        <v>268.11</v>
+        <v>20.97</v>
       </c>
       <c r="I23" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -1593,18 +1593,18 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.76</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="n">
-        <v>1495551484</v>
+        <v>1993444707</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>BBAR</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.1914</v>
+        <v>0.8051</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45580.70648087963</v>
+        <v>45896.6743321875</v>
       </c>
       <c r="G24" t="n">
-        <v>135.82</v>
+        <v>12.42</v>
       </c>
       <c r="H24" t="n">
-        <v>123.6</v>
+        <v>8.31</v>
       </c>
       <c r="I24" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1642,18 +1642,18 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.34</v>
+        <v>-3.31</v>
       </c>
       <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="n">
-        <v>1744916452</v>
+        <v>1644788775</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1662,19 +1662,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.4245</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>45751.74230173611</v>
+        <v>45693.85093391204</v>
       </c>
       <c r="G25" t="n">
-        <v>17.54</v>
+        <v>144.94</v>
       </c>
       <c r="H25" t="n">
-        <v>25.31</v>
+        <v>141.96</v>
       </c>
       <c r="I25" t="n">
-        <v>7.45</v>
+        <v>10.99</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -1691,18 +1691,18 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3.29</v>
+        <v>-0.23</v>
       </c>
       <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="n">
-        <v>1653137218</v>
+        <v>1806980482</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1711,19 +1711,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.277</v>
+        <v>0.2406</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>45699.85152199074</v>
+        <v>45783.83189613426</v>
       </c>
       <c r="G26" t="n">
-        <v>36.1</v>
+        <v>16.12</v>
       </c>
       <c r="H26" t="n">
-        <v>24.44</v>
+        <v>20.97</v>
       </c>
       <c r="I26" t="n">
-        <v>10</v>
+        <v>3.88</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -1740,18 +1740,18 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-3.23</v>
+        <v>1.17</v>
       </c>
       <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="n">
-        <v>1744930699</v>
+        <v>2060645660</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1760,19 +1760,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0.1027</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>45751.74534789352</v>
+        <v>45932.90186543982</v>
       </c>
       <c r="G27" t="n">
-        <v>74.13</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>74.39</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>74.13</v>
+        <v>10.01</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -1789,14 +1789,14 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.26</v>
+        <v>0.02</v>
       </c>
       <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="n">
-        <v>1830408508</v>
+        <v>2060619876</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1809,16 +1809,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.5793</v>
+        <v>0.4178</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>45796.82346997685</v>
+        <v>45932.89807736111</v>
       </c>
       <c r="G28" t="n">
-        <v>17.26</v>
+        <v>23.93</v>
       </c>
       <c r="H28" t="n">
-        <v>23.89</v>
+        <v>24.53</v>
       </c>
       <c r="I28" t="n">
         <v>10</v>
@@ -1838,18 +1838,18 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3.84</v>
+        <v>0.25</v>
       </c>
       <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
-        <v>1867197360</v>
+        <v>2017847675</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1858,19 +1858,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.0765</v>
+        <v>0.2767</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>45818.80265583334</v>
+        <v>45910.65426635417</v>
       </c>
       <c r="G29" t="n">
-        <v>131.96</v>
+        <v>36.17</v>
       </c>
       <c r="H29" t="n">
-        <v>140.69</v>
+        <v>40.46</v>
       </c>
       <c r="I29" t="n">
-        <v>10.09</v>
+        <v>10.01</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -1887,18 +1887,18 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0.67</v>
+        <v>1.19</v>
       </c>
       <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
-        <v>1843477272</v>
+        <v>1843469729</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1907,19 +1907,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0.0423</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45804.66725678241</v>
+        <v>45804.66615450232</v>
       </c>
       <c r="G30" t="n">
-        <v>17.86</v>
+        <v>156.9</v>
       </c>
       <c r="H30" t="n">
-        <v>21.02</v>
+        <v>229.42</v>
       </c>
       <c r="I30" t="n">
-        <v>17.86</v>
+        <v>6.64</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -1936,18 +1936,18 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.16</v>
+        <v>3.06</v>
       </c>
       <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="n">
-        <v>1599455288</v>
+        <v>2029950407</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>PHGP.L</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1956,19 +1956,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.2195</v>
+        <v>0.1453</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45663.73750263889</v>
+        <v>45917.66293982639</v>
       </c>
       <c r="G31" t="n">
-        <v>45.55</v>
+        <v>250.56</v>
       </c>
       <c r="H31" t="n">
-        <v>24.44</v>
+        <v>268.4</v>
       </c>
       <c r="I31" t="n">
-        <v>10</v>
+        <v>49.99</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1985,18 +1985,18 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>-4.64</v>
+        <v>2.33</v>
       </c>
       <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="n">
-        <v>1923258249</v>
+        <v>1599448103</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2005,19 +2005,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0.2839</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45853.65576626157</v>
+        <v>45663.73506711805</v>
       </c>
       <c r="G32" t="n">
-        <v>19.41</v>
+        <v>52.83</v>
       </c>
       <c r="H32" t="n">
-        <v>23.89</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>19.41</v>
+        <v>15</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -2034,18 +2034,18 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>4.48</v>
+        <v>3.66</v>
       </c>
       <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="n">
-        <v>2017852950</v>
+        <v>1701100027</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2054,19 +2054,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>0.5043</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45910.65507498843</v>
+        <v>45727.87202070602</v>
       </c>
       <c r="G33" t="n">
-        <v>37.44</v>
+        <v>19.2</v>
       </c>
       <c r="H33" t="n">
-        <v>37.98</v>
+        <v>24.53</v>
       </c>
       <c r="I33" t="n">
-        <v>37.44</v>
+        <v>9.68</v>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -2083,18 +2083,18 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.54</v>
+        <v>2.69</v>
       </c>
       <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="n">
-        <v>1635194117</v>
+        <v>1982267978</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2103,19 +2103,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.2479</v>
+        <v>0.033</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45687.85228493056</v>
+        <v>45889.64851537037</v>
       </c>
       <c r="G34" t="n">
-        <v>40.33</v>
+        <v>303.76</v>
       </c>
       <c r="H34" t="n">
-        <v>24.44</v>
+        <v>379.97</v>
       </c>
       <c r="I34" t="n">
-        <v>10</v>
+        <v>10.02</v>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
@@ -2132,18 +2132,18 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>-3.94</v>
+        <v>2.52</v>
       </c>
       <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>1997552824</v>
+        <v>1754302454</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2152,19 +2152,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.0429</v>
+        <v>0.3673</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>45898.65627293981</v>
+        <v>45755.88025324074</v>
       </c>
       <c r="G35" t="n">
-        <v>233.17</v>
+        <v>27.17</v>
       </c>
       <c r="H35" t="n">
-        <v>268.11</v>
+        <v>24.14</v>
       </c>
       <c r="I35" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
@@ -2181,18 +2181,18 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.5</v>
+        <v>-1.11</v>
       </c>
       <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>1806977521</v>
+        <v>1997562259</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2201,19 +2201,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.3367</v>
+        <v>0.6323</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45783.8305750463</v>
+        <v>45898.65762083334</v>
       </c>
       <c r="G36" t="n">
-        <v>29.7</v>
+        <v>23.72</v>
       </c>
       <c r="H36" t="n">
-        <v>24.44</v>
+        <v>25.77</v>
       </c>
       <c r="I36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -2230,18 +2230,18 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>-1.77</v>
+        <v>1.29</v>
       </c>
       <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
-        <v>1997561527</v>
+        <v>1830408508</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2250,16 +2250,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.1498</v>
+        <v>0.5793</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>45898.65748991898</v>
+        <v>45796.82346997685</v>
       </c>
       <c r="G37" t="n">
-        <v>66.73</v>
+        <v>17.26</v>
       </c>
       <c r="H37" t="n">
-        <v>63.95</v>
+        <v>24.53</v>
       </c>
       <c r="I37" t="n">
         <v>10</v>
@@ -2279,14 +2279,14 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>-0.42</v>
+        <v>4.21</v>
       </c>
       <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>1701100027</v>
+        <v>1754304266</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2299,19 +2299,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.7812</v>
+        <v>0.7137</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45727.87202070602</v>
+        <v>45755.88055112268</v>
       </c>
       <c r="G38" t="n">
-        <v>19.2</v>
+        <v>14</v>
       </c>
       <c r="H38" t="n">
-        <v>23.89</v>
+        <v>24.53</v>
       </c>
       <c r="I38" t="n">
-        <v>15</v>
+        <v>9.99</v>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
@@ -2328,18 +2328,18 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>3.66</v>
+        <v>7.52</v>
       </c>
       <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
-        <v>1817264187</v>
+        <v>1653137218</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2348,19 +2348,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.4757</v>
+        <v>0.277</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45789.64859377315</v>
+        <v>45699.85152199074</v>
       </c>
       <c r="G39" t="n">
-        <v>42.02</v>
+        <v>36.1</v>
       </c>
       <c r="H39" t="n">
-        <v>51.49</v>
+        <v>24.14</v>
       </c>
       <c r="I39" t="n">
-        <v>19.99</v>
+        <v>10</v>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -2377,18 +2377,18 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>4.5</v>
+        <v>-3.31</v>
       </c>
       <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="n">
-        <v>1824482557</v>
+        <v>1631475148</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2397,19 +2397,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.2641</v>
+        <v>0.2592</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>45792.64805195602</v>
+        <v>45685.83625201389</v>
       </c>
       <c r="G40" t="n">
-        <v>56.78</v>
+        <v>38.58</v>
       </c>
       <c r="H40" t="n">
-        <v>63.95</v>
+        <v>24.14</v>
       </c>
       <c r="I40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
@@ -2426,18 +2426,18 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.89</v>
+        <v>-3.74</v>
       </c>
       <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="n">
-        <v>1648735305</v>
+        <v>2047825292</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>BLX</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2446,19 +2446,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.4576</v>
+        <v>0.3157</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45695.85530675926</v>
+        <v>45926.66222740741</v>
       </c>
       <c r="G41" t="n">
-        <v>21.85</v>
+        <v>47.56</v>
       </c>
       <c r="H41" t="n">
-        <v>23.89</v>
+        <v>44.99</v>
       </c>
       <c r="I41" t="n">
-        <v>10</v>
+        <v>15.01</v>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
@@ -2475,18 +2475,18 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.93</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="n">
-        <v>1880442840</v>
+        <v>2047762608</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BBAR</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2495,19 +2495,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.2535</v>
+        <v>1</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>45825.89113450232</v>
+        <v>45926.65281253472</v>
       </c>
       <c r="G42" t="n">
-        <v>59.15</v>
+        <v>9.27</v>
       </c>
       <c r="H42" t="n">
-        <v>63.95</v>
+        <v>8.31</v>
       </c>
       <c r="I42" t="n">
-        <v>14.99</v>
+        <v>9.27</v>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -2524,18 +2524,18 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1.22</v>
+        <v>-0.96</v>
       </c>
       <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="n">
-        <v>1880446729</v>
+        <v>1923246263</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2544,19 +2544,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.0772</v>
+        <v>1</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>45825.89315055555</v>
+        <v>45853.6538128125</v>
       </c>
       <c r="G43" t="n">
-        <v>129.62</v>
+        <v>21.17</v>
       </c>
       <c r="H43" t="n">
-        <v>140.69</v>
+        <v>17.37</v>
       </c>
       <c r="I43" t="n">
-        <v>10.01</v>
+        <v>21.17</v>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -2573,18 +2573,18 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0.85</v>
+        <v>-3.8</v>
       </c>
       <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
-        <v>1867195793</v>
+        <v>1495551484</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2593,19 +2593,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.2339</v>
+        <v>0.1914</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45818.80180457176</v>
+        <v>45580.70648087963</v>
       </c>
       <c r="G44" t="n">
-        <v>42.74</v>
+        <v>135.82</v>
       </c>
       <c r="H44" t="n">
-        <v>43.1</v>
+        <v>120.6</v>
       </c>
       <c r="I44" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -2622,18 +2622,18 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0.08</v>
+        <v>-2.92</v>
       </c>
       <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>1867193304</v>
+        <v>1845429980</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2642,19 +2642,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.1337</v>
+        <v>1</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>45818.8008296412</v>
+        <v>45805.66181400463</v>
       </c>
       <c r="G45" t="n">
-        <v>17.64</v>
+        <v>13.27</v>
       </c>
       <c r="H45" t="n">
-        <v>21.02</v>
+        <v>16.435</v>
       </c>
       <c r="I45" t="n">
-        <v>2.36</v>
+        <v>15.09</v>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -2671,18 +2671,18 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.45</v>
+        <v>4.11</v>
       </c>
       <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>1563288050</v>
+        <v>2017777441</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2691,16 +2691,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.0626</v>
+        <v>0.4582</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>45630.85583428241</v>
+        <v>45910.64656457176</v>
       </c>
       <c r="G46" t="n">
-        <v>159.74</v>
+        <v>21.82</v>
       </c>
       <c r="H46" t="n">
-        <v>140.69</v>
+        <v>24.53</v>
       </c>
       <c r="I46" t="n">
         <v>10</v>
@@ -2720,18 +2720,18 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>-1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>1923256224</v>
+        <v>1869077157</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2740,19 +2740,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.3061</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>45853.65543140046</v>
+        <v>45819.6742621412</v>
       </c>
       <c r="G47" t="n">
-        <v>30.97</v>
+        <v>13.285</v>
       </c>
       <c r="H47" t="n">
-        <v>24.44</v>
+        <v>16.435</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>4.69</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -2769,18 +2769,18 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>-4.22</v>
+        <v>1.19</v>
       </c>
       <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>2020498366</v>
+        <v>2042867993</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BBAR</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2789,19 +2789,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0.2639</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>45911.68945292824</v>
+        <v>45924.68015445602</v>
       </c>
       <c r="G48" t="n">
-        <v>9.880000000000001</v>
+        <v>37.93</v>
       </c>
       <c r="H48" t="n">
-        <v>8.279999999999999</v>
+        <v>40.46</v>
       </c>
       <c r="I48" t="n">
-        <v>9.880000000000001</v>
+        <v>10.01</v>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -2818,18 +2818,18 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>-1.6</v>
+        <v>0.67</v>
       </c>
       <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
-        <v>1970057305</v>
+        <v>1986476926</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2838,19 +2838,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.07149999999999999</v>
+        <v>1</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45881.70511172454</v>
+        <v>45891.66490212963</v>
       </c>
       <c r="G49" t="n">
-        <v>35.88</v>
+        <v>34.44</v>
       </c>
       <c r="H49" t="n">
-        <v>37.73</v>
+        <v>43.52</v>
       </c>
       <c r="I49" t="n">
-        <v>2.57</v>
+        <v>34.44</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
@@ -2867,18 +2867,18 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0.13</v>
+        <v>9.08</v>
       </c>
       <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
-        <v>1997485943</v>
+        <v>1824476420</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.5157</v>
+        <v>0.1548</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>45898.65185685185</v>
+        <v>45792.64714148148</v>
       </c>
       <c r="G50" t="n">
-        <v>19.39</v>
+        <v>129.17</v>
       </c>
       <c r="H50" t="n">
-        <v>21.02</v>
+        <v>141.96</v>
       </c>
       <c r="I50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -2916,18 +2916,18 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0.84</v>
+        <v>1.98</v>
       </c>
       <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>1981010841</v>
+        <v>1997498400</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2936,19 +2936,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.0425</v>
+        <v>0.0507</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>45888.84617734954</v>
+        <v>45898.65380736111</v>
       </c>
       <c r="G51" t="n">
-        <v>235.53</v>
+        <v>197.26</v>
       </c>
       <c r="H51" t="n">
-        <v>268.11</v>
+        <v>229.42</v>
       </c>
       <c r="I51" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -2965,18 +2965,18 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
-        <v>1499061783</v>
+        <v>1882283184</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2985,19 +2985,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.0001</v>
+        <v>0.4835</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>45582.73996892361</v>
+        <v>45826.76569390047</v>
       </c>
       <c r="G52" t="n">
-        <v>232.2</v>
+        <v>20.69</v>
       </c>
       <c r="H52" t="n">
-        <v>237.85</v>
+        <v>24.53</v>
       </c>
       <c r="I52" t="n">
-        <v>0.02</v>
+        <v>10</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
@@ -3014,18 +3014,18 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="n">
-        <v>1754302454</v>
+        <v>1499061783</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3034,19 +3034,19 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.3673</v>
+        <v>0.0001</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>45755.88025324074</v>
+        <v>45582.73996892361</v>
       </c>
       <c r="G53" t="n">
-        <v>27.17</v>
+        <v>232.2</v>
       </c>
       <c r="H53" t="n">
-        <v>24.44</v>
+        <v>258.02</v>
       </c>
       <c r="I53" t="n">
-        <v>9.98</v>
+        <v>0.02</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
@@ -3063,18 +3063,18 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>-1</v>
+        <v>0.01</v>
       </c>
       <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="n">
-        <v>1644796307</v>
+        <v>2045989132</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3083,19 +3083,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>0.2034</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>45693.85501710648</v>
+        <v>45925.79891365741</v>
       </c>
       <c r="G54" t="n">
-        <v>20.36</v>
+        <v>49.16</v>
       </c>
       <c r="H54" t="n">
-        <v>18.31</v>
+        <v>50.35</v>
       </c>
       <c r="I54" t="n">
-        <v>20.36</v>
+        <v>10</v>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
@@ -3112,18 +3112,18 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>-2.05</v>
+        <v>0.24</v>
       </c>
       <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="n">
-        <v>1744767540</v>
+        <v>1599431096</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3132,19 +3132,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.643</v>
+        <v>0.1013</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>45751.72316712963</v>
+        <v>45663.73014731482</v>
       </c>
       <c r="G55" t="n">
-        <v>15.55</v>
+        <v>148.02</v>
       </c>
       <c r="H55" t="n">
-        <v>23.89</v>
+        <v>141.96</v>
       </c>
       <c r="I55" t="n">
-        <v>10</v>
+        <v>14.99</v>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
@@ -3161,18 +3161,18 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>5.36</v>
+        <v>-0.61</v>
       </c>
       <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="n">
-        <v>1806980482</v>
+        <v>2047762508</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>BBAR</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3181,19 +3181,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.2406</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>45783.83189613426</v>
+        <v>45926.65279332176</v>
       </c>
       <c r="G56" t="n">
-        <v>16.12</v>
+        <v>9.27</v>
       </c>
       <c r="H56" t="n">
-        <v>21.02</v>
+        <v>8.31</v>
       </c>
       <c r="I56" t="n">
-        <v>3.88</v>
+        <v>0.73</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
@@ -3210,18 +3210,18 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>1.18</v>
+        <v>-0.08</v>
       </c>
       <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="n">
-        <v>1885700231</v>
+        <v>1880441651</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3230,19 +3230,19 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.0081</v>
+        <v>1</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45828.65147924769</v>
+        <v>45825.89055887731</v>
       </c>
       <c r="G57" t="n">
-        <v>534.86</v>
+        <v>21.21</v>
       </c>
       <c r="H57" t="n">
-        <v>586.48</v>
+        <v>17.37</v>
       </c>
       <c r="I57" t="n">
-        <v>4.33</v>
+        <v>21.21</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
@@ -3259,18 +3259,18 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>0.42</v>
+        <v>-3.84</v>
       </c>
       <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
-        <v>1867196288</v>
+        <v>1926287328</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3279,19 +3279,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.5476</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45818.80209099537</v>
+        <v>45854.82177967593</v>
       </c>
       <c r="G58" t="n">
-        <v>41.99</v>
+        <v>18.26</v>
       </c>
       <c r="H58" t="n">
-        <v>51.49</v>
+        <v>24.53</v>
       </c>
       <c r="I58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
@@ -3308,18 +3308,18 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>5.65</v>
+        <v>3.43</v>
       </c>
       <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="n">
-        <v>1843469729</v>
+        <v>1923271589</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3328,19 +3328,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.0423</v>
+        <v>0.4478</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>45804.66615450232</v>
+        <v>45853.65794861111</v>
       </c>
       <c r="G59" t="n">
-        <v>156.9</v>
+        <v>44.66</v>
       </c>
       <c r="H59" t="n">
-        <v>208.95</v>
+        <v>52</v>
       </c>
       <c r="I59" t="n">
-        <v>6.64</v>
+        <v>20</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
@@ -3357,18 +3357,18 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>2.2</v>
+        <v>3.29</v>
       </c>
       <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="n">
-        <v>1923258184</v>
+        <v>1869077178</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3377,19 +3377,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.0298</v>
+        <v>1</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45853.6557568287</v>
+        <v>45819.67426902778</v>
       </c>
       <c r="G60" t="n">
-        <v>19.43</v>
+        <v>13.285</v>
       </c>
       <c r="H60" t="n">
-        <v>23.89</v>
+        <v>16.435</v>
       </c>
       <c r="I60" t="n">
-        <v>0.58</v>
+        <v>15.31</v>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
@@ -3406,18 +3406,18 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>0.13</v>
+        <v>3.89</v>
       </c>
       <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="n">
-        <v>2017777441</v>
+        <v>1712850989</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3426,19 +3426,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.4582</v>
+        <v>0.0002</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>45910.64656457176</v>
+        <v>45734.85576775463</v>
       </c>
       <c r="G61" t="n">
-        <v>21.82</v>
+        <v>160.64</v>
       </c>
       <c r="H61" t="n">
-        <v>23.89</v>
+        <v>245.35</v>
       </c>
       <c r="I61" t="n">
-        <v>10</v>
+        <v>0.03</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
@@ -3455,18 +3455,18 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>0.95</v>
+        <v>0.02</v>
       </c>
       <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="n">
-        <v>1993443280</v>
+        <v>1867193336</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BBVA</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3478,16 +3478,16 @@
         <v>1</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>45896.67387811343</v>
+        <v>45818.80084483796</v>
       </c>
       <c r="G62" t="n">
-        <v>17.97</v>
+        <v>17.64</v>
       </c>
       <c r="H62" t="n">
-        <v>19.1</v>
+        <v>20.97</v>
       </c>
       <c r="I62" t="n">
-        <v>17.97</v>
+        <v>17.64</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
@@ -3504,18 +3504,18 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>1.13</v>
+        <v>3.33</v>
       </c>
       <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="n">
-        <v>1727591551</v>
+        <v>1744916452</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3524,19 +3524,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>0.4245</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>45743.77389555555</v>
+        <v>45751.74230173611</v>
       </c>
       <c r="G63" t="n">
-        <v>72.87</v>
+        <v>17.54</v>
       </c>
       <c r="H63" t="n">
-        <v>74.39</v>
+        <v>25.77</v>
       </c>
       <c r="I63" t="n">
-        <v>72.87</v>
+        <v>7.45</v>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
@@ -3553,18 +3553,18 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>1.52</v>
+        <v>3.49</v>
       </c>
       <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="n">
-        <v>1599449649</v>
+        <v>2035163256</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3573,19 +3573,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.0377</v>
+        <v>0.0951</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>45663.73562525463</v>
+        <v>45919.66675122685</v>
       </c>
       <c r="G64" t="n">
-        <v>24.11</v>
+        <v>88.91</v>
       </c>
       <c r="H64" t="n">
-        <v>23.89</v>
+        <v>92.845</v>
       </c>
       <c r="I64" t="n">
-        <v>0.91</v>
+        <v>9.99</v>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
@@ -3602,18 +3602,18 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>-0.01</v>
+        <v>0.32</v>
       </c>
       <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="n">
-        <v>1978487977</v>
+        <v>2042867331</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>JKS</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3622,16 +3622,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.3941</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>45887.66311905093</v>
+        <v>45924.67994332176</v>
       </c>
       <c r="G65" t="n">
-        <v>127.06</v>
+        <v>25.37</v>
       </c>
       <c r="H65" t="n">
-        <v>123.6</v>
+        <v>24.6</v>
       </c>
       <c r="I65" t="n">
         <v>10</v>
@@ -3651,18 +3651,18 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>-0.27</v>
+        <v>-0.31</v>
       </c>
       <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="n">
-        <v>1642762235</v>
+        <v>1824482557</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3671,19 +3671,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.1572</v>
+        <v>0.2641</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>45692.86612574074</v>
+        <v>45792.64805195602</v>
       </c>
       <c r="G66" t="n">
-        <v>127.16</v>
+        <v>56.78</v>
       </c>
       <c r="H66" t="n">
-        <v>123.6</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>19.99</v>
+        <v>15</v>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
@@ -3700,18 +3700,18 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>-0.5600000000000001</v>
+        <v>2.35</v>
       </c>
       <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="n">
-        <v>1830410729</v>
+        <v>1680993370</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3720,19 +3720,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.1091</v>
+        <v>1</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>45796.82476561343</v>
+        <v>45716.85638861111</v>
       </c>
       <c r="G67" t="n">
-        <v>33.66</v>
+        <v>44.49</v>
       </c>
       <c r="H67" t="n">
-        <v>32.44</v>
+        <v>54.78</v>
       </c>
       <c r="I67" t="n">
-        <v>3.67</v>
+        <v>44.49</v>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
@@ -3749,14 +3749,14 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>-0.13</v>
+        <v>10.29</v>
       </c>
       <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="n">
-        <v>1662993636</v>
+        <v>1727574394</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -3772,16 +3772,16 @@
         <v>1</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>45706.87026833333</v>
+        <v>45743.76658678241</v>
       </c>
       <c r="G68" t="n">
-        <v>20.65</v>
+        <v>21.13</v>
       </c>
       <c r="H68" t="n">
-        <v>18.31</v>
+        <v>17.37</v>
       </c>
       <c r="I68" t="n">
-        <v>20.65</v>
+        <v>21.13</v>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
@@ -3798,18 +3798,18 @@
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>-2.34</v>
+        <v>-3.76</v>
       </c>
       <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="n">
-        <v>1883977044</v>
+        <v>1666461140</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3818,19 +3818,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.345</v>
+        <v>0.2651</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>45827.66105774305</v>
+        <v>45708.68207092593</v>
       </c>
       <c r="G69" t="n">
-        <v>12.88</v>
+        <v>37.7</v>
       </c>
       <c r="H69" t="n">
-        <v>16.205</v>
+        <v>24.14</v>
       </c>
       <c r="I69" t="n">
-        <v>5.13</v>
+        <v>9.99</v>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
@@ -3847,18 +3847,18 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>1.43</v>
+        <v>-3.59</v>
       </c>
       <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="n">
-        <v>1986476926</v>
+        <v>1559803221</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3867,19 +3867,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>0.092</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>45891.66490212963</v>
+        <v>45628.85951927083</v>
       </c>
       <c r="G70" t="n">
-        <v>34.44</v>
+        <v>162.85</v>
       </c>
       <c r="H70" t="n">
-        <v>37.98</v>
+        <v>141.96</v>
       </c>
       <c r="I70" t="n">
-        <v>34.44</v>
+        <v>14.98</v>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
@@ -3896,18 +3896,18 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>3.54</v>
+        <v>-1.92</v>
       </c>
       <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="n">
-        <v>1867462173</v>
+        <v>2048501554</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>JKS</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3916,19 +3916,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.4118</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>45818.90866184028</v>
+        <v>45926.83927949074</v>
       </c>
       <c r="G71" t="n">
-        <v>77.93000000000001</v>
+        <v>24.28</v>
       </c>
       <c r="H71" t="n">
-        <v>102.41</v>
+        <v>24.6</v>
       </c>
       <c r="I71" t="n">
-        <v>0.65</v>
+        <v>10</v>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
@@ -3945,14 +3945,14 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="n">
-        <v>1843474191</v>
+        <v>1923259795</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -3965,19 +3965,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9372</v>
+        <v>0.4424</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>45804.66699503472</v>
+        <v>45853.65609353009</v>
       </c>
       <c r="G72" t="n">
-        <v>21.33</v>
+        <v>22.59</v>
       </c>
       <c r="H72" t="n">
-        <v>25.31</v>
+        <v>25.77</v>
       </c>
       <c r="I72" t="n">
-        <v>19.99</v>
+        <v>9.99</v>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -3994,18 +3994,18 @@
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>3.73</v>
+        <v>1.41</v>
       </c>
       <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="n">
-        <v>1599448103</v>
+        <v>2017778050</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4014,19 +4014,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.2839</v>
+        <v>0.3611</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45663.73506711805</v>
+        <v>45910.64665976852</v>
       </c>
       <c r="G73" t="n">
-        <v>52.83</v>
+        <v>27.91</v>
       </c>
       <c r="H73" t="n">
-        <v>63.95</v>
+        <v>24.14</v>
       </c>
       <c r="I73" t="n">
-        <v>15</v>
+        <v>10.08</v>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
@@ -4043,18 +4043,18 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>3.16</v>
+        <v>-1.36</v>
       </c>
       <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="n">
-        <v>1923271589</v>
+        <v>1867194722</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4063,19 +4063,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.4478</v>
+        <v>1</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45853.65794861111</v>
+        <v>45818.80135700232</v>
       </c>
       <c r="G74" t="n">
-        <v>44.66</v>
+        <v>21.27</v>
       </c>
       <c r="H74" t="n">
-        <v>51.49</v>
+        <v>17.37</v>
       </c>
       <c r="I74" t="n">
-        <v>20</v>
+        <v>21.27</v>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
@@ -4092,18 +4092,18 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>3.06</v>
+        <v>-3.9</v>
       </c>
       <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="n">
-        <v>1923224670</v>
+        <v>2042979139</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4112,19 +4112,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.2583</v>
+        <v>0.3128</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>45853.65359685185</v>
+        <v>45924.70564383102</v>
       </c>
       <c r="G75" t="n">
-        <v>58.05</v>
+        <v>32</v>
       </c>
       <c r="H75" t="n">
-        <v>63.95</v>
+        <v>31.75</v>
       </c>
       <c r="I75" t="n">
-        <v>14.99</v>
+        <v>10.01</v>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
@@ -4141,18 +4141,18 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>1.53</v>
+        <v>-0.08</v>
       </c>
       <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="n">
-        <v>2025661832</v>
+        <v>1582723120</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4161,16 +4161,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.3235</v>
+        <v>0.3755</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>45915.72870862269</v>
+        <v>45645.89511640046</v>
       </c>
       <c r="G76" t="n">
-        <v>61.81</v>
+        <v>53.26</v>
       </c>
       <c r="H76" t="n">
-        <v>61.37</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="I76" t="n">
         <v>20</v>
@@ -4190,18 +4190,18 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>-0.15</v>
+        <v>4.67</v>
       </c>
       <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="n">
-        <v>1744929368</v>
+        <v>2035164705</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>PHGP.L</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4210,19 +4210,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.0192</v>
+        <v>0.032</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>45751.74500871528</v>
+        <v>45919.6670447338</v>
       </c>
       <c r="G77" t="n">
-        <v>324.48</v>
+        <v>252.81</v>
       </c>
       <c r="H77" t="n">
-        <v>338.11</v>
+        <v>268.4</v>
       </c>
       <c r="I77" t="n">
-        <v>6.23</v>
+        <v>10.97</v>
       </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
@@ -4239,18 +4239,18 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>0.26</v>
+        <v>0.55</v>
       </c>
       <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="n">
-        <v>1993444707</v>
+        <v>1888700382</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BBAR</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4259,19 +4259,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.8051</v>
+        <v>1</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>45896.6743321875</v>
+        <v>45831.65144708334</v>
       </c>
       <c r="G78" t="n">
-        <v>12.42</v>
+        <v>47.58</v>
       </c>
       <c r="H78" t="n">
-        <v>8.279999999999999</v>
+        <v>54.78</v>
       </c>
       <c r="I78" t="n">
-        <v>10</v>
+        <v>47.58</v>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
@@ -4288,18 +4288,18 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>-3.33</v>
+        <v>7.2</v>
       </c>
       <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="n">
-        <v>1993382859</v>
+        <v>1982273555</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4308,19 +4308,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.0779</v>
+        <v>0.0439</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>45896.66809304398</v>
+        <v>45889.64957444445</v>
       </c>
       <c r="G79" t="n">
-        <v>128.25</v>
+        <v>228</v>
       </c>
       <c r="H79" t="n">
-        <v>123.6</v>
+        <v>292.04</v>
       </c>
       <c r="I79" t="n">
-        <v>9.99</v>
+        <v>10.01</v>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
@@ -4337,18 +4337,18 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>-0.36</v>
+        <v>2.81</v>
       </c>
       <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="n">
-        <v>1975988073</v>
+        <v>1993382859</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4357,19 +4357,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.0469</v>
+        <v>0.0779</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>45884.6572796875</v>
+        <v>45896.66809304398</v>
       </c>
       <c r="G80" t="n">
-        <v>319.83</v>
+        <v>128.25</v>
       </c>
       <c r="H80" t="n">
-        <v>342.82</v>
+        <v>120.6</v>
       </c>
       <c r="I80" t="n">
-        <v>15</v>
+        <v>9.99</v>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
@@ -4386,18 +4386,18 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>1.08</v>
+        <v>-0.6</v>
       </c>
       <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="n">
-        <v>1817256440</v>
+        <v>1970057305</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4406,19 +4406,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.2267</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>45789.64787115741</v>
+        <v>45881.70511172454</v>
       </c>
       <c r="G81" t="n">
-        <v>44.1</v>
+        <v>35.88</v>
       </c>
       <c r="H81" t="n">
-        <v>43.1</v>
+        <v>40.46</v>
       </c>
       <c r="I81" t="n">
-        <v>10</v>
+        <v>2.57</v>
       </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
@@ -4435,18 +4435,18 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>-0.23</v>
+        <v>0.32</v>
       </c>
       <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="n">
-        <v>1978489328</v>
+        <v>1880446729</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4455,19 +4455,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0.0772</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>45887.6634622338</v>
+        <v>45825.89315055555</v>
       </c>
       <c r="G82" t="n">
-        <v>34.58</v>
+        <v>129.62</v>
       </c>
       <c r="H82" t="n">
-        <v>37.98</v>
+        <v>141.96</v>
       </c>
       <c r="I82" t="n">
-        <v>34.58</v>
+        <v>10.01</v>
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
@@ -4484,18 +4484,18 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>3.4</v>
+        <v>0.95</v>
       </c>
       <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="n">
-        <v>1644788775</v>
+        <v>1796453499</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4504,19 +4504,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>45693.85093391204</v>
+        <v>45777.64668229167</v>
       </c>
       <c r="G83" t="n">
-        <v>144.94</v>
+        <v>15.57</v>
       </c>
       <c r="H83" t="n">
-        <v>140.69</v>
+        <v>20.97</v>
       </c>
       <c r="I83" t="n">
-        <v>10.99</v>
+        <v>8.01</v>
       </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
@@ -4533,18 +4533,18 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>-0.33</v>
+        <v>2.78</v>
       </c>
       <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="n">
-        <v>1880441651</v>
+        <v>1806979127</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4553,19 +4553,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1</v>
+        <v>0.6361</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>45825.89055887731</v>
+        <v>45783.83125244213</v>
       </c>
       <c r="G84" t="n">
-        <v>21.21</v>
+        <v>15.72</v>
       </c>
       <c r="H84" t="n">
-        <v>18.31</v>
+        <v>24.53</v>
       </c>
       <c r="I84" t="n">
-        <v>21.21</v>
+        <v>10</v>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
@@ -4582,18 +4582,18 @@
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>-2.9</v>
+        <v>5.6</v>
       </c>
       <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="n">
-        <v>1984829391</v>
+        <v>2048539334</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4602,19 +4602,19 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.0512</v>
+        <v>1</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>45890.71798858796</v>
+        <v>45926.85025574074</v>
       </c>
       <c r="G85" t="n">
-        <v>195.52</v>
+        <v>42.2</v>
       </c>
       <c r="H85" t="n">
-        <v>208.95</v>
+        <v>43.52</v>
       </c>
       <c r="I85" t="n">
-        <v>10.01</v>
+        <v>42.2</v>
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
@@ -4631,18 +4631,18 @@
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.32</v>
       </c>
       <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="n">
-        <v>1843468958</v>
+        <v>2045991969</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4651,19 +4651,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.0669</v>
+        <v>0.4928</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>45804.66597149306</v>
+        <v>45925.80038483796</v>
       </c>
       <c r="G86" t="n">
-        <v>67.93000000000001</v>
+        <v>20.29</v>
       </c>
       <c r="H86" t="n">
-        <v>70.73999999999999</v>
+        <v>20.97</v>
       </c>
       <c r="I86" t="n">
-        <v>4.54</v>
+        <v>10</v>
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
@@ -4680,18 +4680,18 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="n">
-        <v>1843470413</v>
+        <v>1923250768</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4700,19 +4700,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.4729</v>
+        <v>0.87</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>45804.66637251157</v>
+        <v>45853.65447396991</v>
       </c>
       <c r="G87" t="n">
-        <v>42.29</v>
+        <v>12.76</v>
       </c>
       <c r="H87" t="n">
-        <v>51.49</v>
+        <v>16.435</v>
       </c>
       <c r="I87" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
@@ -4729,18 +4729,18 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>4.35</v>
+        <v>3.7</v>
       </c>
       <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="n">
-        <v>1599431096</v>
+        <v>1895465445</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4749,19 +4749,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.1013</v>
+        <v>0.2987</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>45663.73014731482</v>
+        <v>45834.6539484375</v>
       </c>
       <c r="G88" t="n">
-        <v>148.02</v>
+        <v>33.47</v>
       </c>
       <c r="H88" t="n">
-        <v>140.69</v>
+        <v>24.14</v>
       </c>
       <c r="I88" t="n">
-        <v>14.99</v>
+        <v>10</v>
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
@@ -4778,18 +4778,18 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>-0.74</v>
+        <v>-2.79</v>
       </c>
       <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="n">
-        <v>1926287328</v>
+        <v>1845429956</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4798,19 +4798,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.5476</v>
+        <v>0.4821</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>45854.82177967593</v>
+        <v>45805.66180811343</v>
       </c>
       <c r="G89" t="n">
-        <v>18.26</v>
+        <v>13.275</v>
       </c>
       <c r="H89" t="n">
-        <v>23.89</v>
+        <v>16.435</v>
       </c>
       <c r="I89" t="n">
-        <v>10</v>
+        <v>7.28</v>
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
@@ -4827,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>3.08</v>
+        <v>1.98</v>
       </c>
       <c r="Q89" t="inlineStr"/>
     </row>
@@ -4856,7 +4856,7 @@
         <v>9.890000000000001</v>
       </c>
       <c r="H90" t="n">
-        <v>8.279999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="I90" t="n">
         <v>0.13</v>
@@ -4883,11 +4883,11 @@
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="n">
-        <v>1997500170</v>
+        <v>1867196288</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>JKS</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4896,19 +4896,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.4466</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>45898.65406594907</v>
+        <v>45818.80209099537</v>
       </c>
       <c r="G91" t="n">
-        <v>22.39</v>
+        <v>41.99</v>
       </c>
       <c r="H91" t="n">
-        <v>23.96</v>
+        <v>52</v>
       </c>
       <c r="I91" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
@@ -4925,18 +4925,18 @@
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>0.7</v>
+        <v>5.96</v>
       </c>
       <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="n">
-        <v>1727574394</v>
+        <v>2027639997</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4945,19 +4945,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>0.1558</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>45743.76658678241</v>
+        <v>45916.65703747685</v>
       </c>
       <c r="G92" t="n">
-        <v>21.13</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="H92" t="n">
-        <v>18.31</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="I92" t="n">
-        <v>21.13</v>
+        <v>10</v>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
@@ -4974,14 +4974,14 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>-2.82</v>
+        <v>0.24</v>
       </c>
       <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="n">
-        <v>1666461140</v>
+        <v>1983186744</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -4994,19 +4994,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.2651</v>
+        <v>0.3162</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>45708.68207092593</v>
+        <v>45889.85904239583</v>
       </c>
       <c r="G93" t="n">
-        <v>37.7</v>
+        <v>31.61</v>
       </c>
       <c r="H93" t="n">
-        <v>24.44</v>
+        <v>24.14</v>
       </c>
       <c r="I93" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
@@ -5023,18 +5023,18 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>-3.51</v>
+        <v>-2.37</v>
       </c>
       <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="n">
-        <v>1824477589</v>
+        <v>1978489328</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5043,19 +5043,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.2344</v>
+        <v>1</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>45792.64732982639</v>
+        <v>45887.6634622338</v>
       </c>
       <c r="G94" t="n">
-        <v>42.66</v>
+        <v>34.58</v>
       </c>
       <c r="H94" t="n">
-        <v>43.1</v>
+        <v>43.52</v>
       </c>
       <c r="I94" t="n">
-        <v>10</v>
+        <v>34.58</v>
       </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
@@ -5072,18 +5072,18 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>0.1</v>
+        <v>8.94</v>
       </c>
       <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="n">
-        <v>1582735114</v>
+        <v>1995249699</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5092,19 +5092,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.0003</v>
+        <v>0.4888</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>45645.90076803241</v>
+        <v>45897.61086020833</v>
       </c>
       <c r="G95" t="n">
-        <v>130.51</v>
+        <v>87.16500000000001</v>
       </c>
       <c r="H95" t="n">
-        <v>145.15</v>
+        <v>92.845</v>
       </c>
       <c r="I95" t="n">
-        <v>0.04</v>
+        <v>49.99</v>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -5121,18 +5121,18 @@
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="n">
-        <v>1806980496</v>
+        <v>1830410729</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5141,19 +5141,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>0.1091</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>45783.83190503472</v>
+        <v>45796.82476561343</v>
       </c>
       <c r="G96" t="n">
-        <v>16.12</v>
+        <v>33.66</v>
       </c>
       <c r="H96" t="n">
-        <v>21.02</v>
+        <v>31.75</v>
       </c>
       <c r="I96" t="n">
-        <v>16.12</v>
+        <v>3.67</v>
       </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
@@ -5170,18 +5170,18 @@
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>4.9</v>
+        <v>-0.21</v>
       </c>
       <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="n">
-        <v>1880445013</v>
+        <v>1662993636</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5190,19 +5190,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.07149999999999999</v>
+        <v>1</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>45825.8922271412</v>
+        <v>45706.87026833333</v>
       </c>
       <c r="G97" t="n">
-        <v>139.86</v>
+        <v>20.65</v>
       </c>
       <c r="H97" t="n">
-        <v>145.15</v>
+        <v>17.37</v>
       </c>
       <c r="I97" t="n">
-        <v>10</v>
+        <v>20.65</v>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
@@ -5219,18 +5219,18 @@
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>0.38</v>
+        <v>-3.28</v>
       </c>
       <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="n">
-        <v>2002503461</v>
+        <v>1806977521</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5239,19 +5239,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.0439</v>
+        <v>0.3367</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>45902.65623520833</v>
+        <v>45783.8305750463</v>
       </c>
       <c r="G98" t="n">
-        <v>227.95</v>
+        <v>29.7</v>
       </c>
       <c r="H98" t="n">
-        <v>268.11</v>
+        <v>24.14</v>
       </c>
       <c r="I98" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
@@ -5268,18 +5268,18 @@
         <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>1.76</v>
+        <v>-1.87</v>
       </c>
       <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="n">
-        <v>1895465445</v>
+        <v>2050990570</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>BLX</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5288,19 +5288,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.2987</v>
+        <v>0.2121</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>45834.6539484375</v>
+        <v>45929.65780017361</v>
       </c>
       <c r="G99" t="n">
-        <v>33.47</v>
+        <v>47</v>
       </c>
       <c r="H99" t="n">
-        <v>24.44</v>
+        <v>44.99</v>
       </c>
       <c r="I99" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
@@ -5317,18 +5317,18 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>-2.7</v>
+        <v>-0.43</v>
       </c>
       <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="n">
-        <v>1843477152</v>
+        <v>1883977044</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5337,19 +5337,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.1198</v>
+        <v>0.345</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>45804.66724922453</v>
+        <v>45827.66105774305</v>
       </c>
       <c r="G100" t="n">
-        <v>17.86</v>
+        <v>12.88</v>
       </c>
       <c r="H100" t="n">
-        <v>21.02</v>
+        <v>16.435</v>
       </c>
       <c r="I100" t="n">
-        <v>2.14</v>
+        <v>5.13</v>
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
@@ -5366,18 +5366,18 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>0.38</v>
+        <v>1.49</v>
       </c>
       <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="n">
-        <v>1358151307</v>
+        <v>2050940197</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5386,19 +5386,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.1081</v>
+        <v>0.3238</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>45460.88529052083</v>
+        <v>45929.65257815972</v>
       </c>
       <c r="G101" t="n">
-        <v>165.93</v>
+        <v>30.91</v>
       </c>
       <c r="H101" t="n">
-        <v>140.69</v>
+        <v>31.75</v>
       </c>
       <c r="I101" t="n">
-        <v>17.94</v>
+        <v>10.01</v>
       </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -5415,18 +5415,18 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>-2.72</v>
+        <v>0.27</v>
       </c>
       <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="n">
-        <v>1923259795</v>
+        <v>1923256224</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5435,19 +5435,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.4424</v>
+        <v>0.6457000000000001</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>45853.65609353009</v>
+        <v>45853.65543140046</v>
       </c>
       <c r="G102" t="n">
-        <v>22.59</v>
+        <v>30.97</v>
       </c>
       <c r="H102" t="n">
-        <v>25.31</v>
+        <v>24.14</v>
       </c>
       <c r="I102" t="n">
-        <v>9.99</v>
+        <v>20</v>
       </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
@@ -5464,18 +5464,18 @@
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>1.21</v>
+        <v>-4.41</v>
       </c>
       <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="n">
-        <v>1867461578</v>
+        <v>1923224670</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BAP</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5484,19 +5484,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.0023</v>
+        <v>0.2583</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>45818.90835071759</v>
+        <v>45853.65359685185</v>
       </c>
       <c r="G103" t="n">
-        <v>216.54</v>
+        <v>58.05</v>
       </c>
       <c r="H103" t="n">
-        <v>261.65</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5</v>
+        <v>14.99</v>
       </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
@@ -5513,18 +5513,18 @@
         <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>0.1</v>
+        <v>1.98</v>
       </c>
       <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="n">
-        <v>1989207013</v>
+        <v>1880443947</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>JKS</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5533,19 +5533,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.4133</v>
+        <v>0.1047</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>45894.65354606482</v>
+        <v>45825.891695625</v>
       </c>
       <c r="G104" t="n">
-        <v>24.19</v>
+        <v>142.99</v>
       </c>
       <c r="H104" t="n">
-        <v>23.96</v>
+        <v>229.42</v>
       </c>
       <c r="I104" t="n">
-        <v>10</v>
+        <v>14.97</v>
       </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
@@ -5562,18 +5562,18 @@
         <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>-0.1</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="n">
-        <v>1997498400</v>
+        <v>1843477152</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5582,19 +5582,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.0507</v>
+        <v>0.1198</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>45898.65380736111</v>
+        <v>45804.66724922453</v>
       </c>
       <c r="G105" t="n">
-        <v>197.26</v>
+        <v>17.86</v>
       </c>
       <c r="H105" t="n">
-        <v>208.95</v>
+        <v>20.97</v>
       </c>
       <c r="I105" t="n">
-        <v>10</v>
+        <v>2.14</v>
       </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
@@ -5611,18 +5611,18 @@
         <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>0.59</v>
+        <v>0.37</v>
       </c>
       <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="n">
-        <v>1559803221</v>
+        <v>2002501482</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5631,19 +5631,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.092</v>
+        <v>0.0526</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>45628.85951927083</v>
+        <v>45902.65588916666</v>
       </c>
       <c r="G106" t="n">
-        <v>162.85</v>
+        <v>190.17</v>
       </c>
       <c r="H106" t="n">
-        <v>140.69</v>
+        <v>229.42</v>
       </c>
       <c r="I106" t="n">
-        <v>14.98</v>
+        <v>10</v>
       </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
@@ -5660,18 +5660,18 @@
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>-2.04</v>
+        <v>2.07</v>
       </c>
       <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="n">
-        <v>1824476420</v>
+        <v>1867462173</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5680,19 +5680,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.1548</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>45792.64714148148</v>
+        <v>45818.90866184028</v>
       </c>
       <c r="G107" t="n">
-        <v>129.17</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="H107" t="n">
-        <v>140.69</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="I107" t="n">
-        <v>20</v>
+        <v>0.65</v>
       </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
@@ -5709,18 +5709,18 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>1.78</v>
+        <v>0.17</v>
       </c>
       <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="n">
-        <v>1666451221</v>
+        <v>2025662892</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5729,19 +5729,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.0001</v>
+        <v>0.8196</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>45708.68022634259</v>
+        <v>45915.72913914352</v>
       </c>
       <c r="G108" t="n">
-        <v>43</v>
+        <v>24.39</v>
       </c>
       <c r="H108" t="n">
-        <v>43.1</v>
+        <v>24.73</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>19.99</v>
       </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
@@ -5758,18 +5758,18 @@
         <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="n">
-        <v>1744879358</v>
+        <v>1358151307</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5778,19 +5778,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.2701</v>
+        <v>0.1081</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>45751.73925940973</v>
+        <v>45460.88529052083</v>
       </c>
       <c r="G109" t="n">
-        <v>148.09</v>
+        <v>165.93</v>
       </c>
       <c r="H109" t="n">
-        <v>268.11</v>
+        <v>141.96</v>
       </c>
       <c r="I109" t="n">
-        <v>40</v>
+        <v>17.94</v>
       </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
@@ -5807,18 +5807,18 @@
         <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>32.42</v>
+        <v>-2.58</v>
       </c>
       <c r="Q109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="n">
-        <v>1666459175</v>
+        <v>1972092684</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5827,19 +5827,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.1641</v>
+        <v>1</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>45708.68165298611</v>
+        <v>45882.68269449074</v>
       </c>
       <c r="G110" t="n">
-        <v>17.18</v>
+        <v>18.8</v>
       </c>
       <c r="H110" t="n">
-        <v>25.31</v>
+        <v>17.37</v>
       </c>
       <c r="I110" t="n">
-        <v>2.82</v>
+        <v>18.8</v>
       </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
@@ -5856,18 +5856,18 @@
         <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>1.33</v>
+        <v>-1.43</v>
       </c>
       <c r="Q110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="n">
-        <v>1883977086</v>
+        <v>1997552824</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5876,19 +5876,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1</v>
+        <v>0.0429</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>45827.66106613426</v>
+        <v>45898.65627293981</v>
       </c>
       <c r="G111" t="n">
-        <v>12.875</v>
+        <v>233.17</v>
       </c>
       <c r="H111" t="n">
-        <v>16.205</v>
+        <v>292.04</v>
       </c>
       <c r="I111" t="n">
-        <v>14.86</v>
+        <v>10</v>
       </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
@@ -5905,18 +5905,18 @@
         <v>0</v>
       </c>
       <c r="P111" t="n">
-        <v>4.15</v>
+        <v>2.53</v>
       </c>
       <c r="Q111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="n">
-        <v>1888700382</v>
+        <v>1727591551</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>BND</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5928,16 +5928,16 @@
         <v>1</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>45831.65144708334</v>
+        <v>45743.77389555555</v>
       </c>
       <c r="G112" t="n">
-        <v>47.58</v>
+        <v>72.87</v>
       </c>
       <c r="H112" t="n">
-        <v>54.27</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="I112" t="n">
-        <v>47.58</v>
+        <v>72.87</v>
       </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
@@ -5954,18 +5954,18 @@
         <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>6.69</v>
+        <v>1.42</v>
       </c>
       <c r="Q112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="n">
-        <v>1867195417</v>
+        <v>1644796307</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5974,19 +5974,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.1044</v>
+        <v>1</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>45818.80165224537</v>
+        <v>45693.85501710648</v>
       </c>
       <c r="G113" t="n">
-        <v>143.6</v>
+        <v>20.36</v>
       </c>
       <c r="H113" t="n">
-        <v>145.15</v>
+        <v>17.37</v>
       </c>
       <c r="I113" t="n">
-        <v>14.99</v>
+        <v>20.36</v>
       </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
@@ -6003,18 +6003,18 @@
         <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>0.16</v>
+        <v>-2.99</v>
       </c>
       <c r="Q113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="n">
-        <v>1869077178</v>
+        <v>1517510856</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6023,19 +6023,19 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1</v>
+        <v>0.0602</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>45819.67426902778</v>
+        <v>45597.61014849537</v>
       </c>
       <c r="G114" t="n">
-        <v>13.285</v>
+        <v>166.03</v>
       </c>
       <c r="H114" t="n">
-        <v>16.205</v>
+        <v>141.96</v>
       </c>
       <c r="I114" t="n">
-        <v>15.31</v>
+        <v>10</v>
       </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
@@ -6052,18 +6052,18 @@
         <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>3.7</v>
+        <v>-1.45</v>
       </c>
       <c r="Q114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="n">
-        <v>1461331124</v>
+        <v>2045993574</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6072,19 +6072,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.3752</v>
+        <v>0.5753</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>45553.65374138889</v>
+        <v>45925.80108013889</v>
       </c>
       <c r="G115" t="n">
-        <v>50.99</v>
+        <v>17.38</v>
       </c>
       <c r="H115" t="n">
-        <v>63.95</v>
+        <v>17.37</v>
       </c>
       <c r="I115" t="n">
-        <v>19.13</v>
+        <v>10</v>
       </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
@@ -6101,18 +6101,18 @@
         <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>4.86</v>
+        <v>-0.01</v>
       </c>
       <c r="Q115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="n">
-        <v>1923246263</v>
+        <v>1923258249</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6124,16 +6124,16 @@
         <v>1</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>45853.6538128125</v>
+        <v>45853.65576626157</v>
       </c>
       <c r="G116" t="n">
-        <v>21.17</v>
+        <v>19.41</v>
       </c>
       <c r="H116" t="n">
-        <v>18.31</v>
+        <v>24.53</v>
       </c>
       <c r="I116" t="n">
-        <v>21.17</v>
+        <v>19.41</v>
       </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
@@ -6150,18 +6150,18 @@
         <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>-2.86</v>
+        <v>5.12</v>
       </c>
       <c r="Q116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="n">
-        <v>1806979127</v>
+        <v>1599455288</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6170,16 +6170,16 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.6361</v>
+        <v>0.2195</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>45783.83125244213</v>
+        <v>45663.73750263889</v>
       </c>
       <c r="G117" t="n">
-        <v>15.72</v>
+        <v>45.55</v>
       </c>
       <c r="H117" t="n">
-        <v>23.89</v>
+        <v>24.14</v>
       </c>
       <c r="I117" t="n">
         <v>10</v>
@@ -6199,18 +6199,18 @@
         <v>0</v>
       </c>
       <c r="P117" t="n">
-        <v>5.2</v>
+        <v>-4.7</v>
       </c>
       <c r="Q117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="n">
-        <v>2017778050</v>
+        <v>1867461578</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>BAP</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6219,19 +6219,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.3611</v>
+        <v>0.0023</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>45910.64665976852</v>
+        <v>45818.90835071759</v>
       </c>
       <c r="G118" t="n">
-        <v>27.91</v>
+        <v>216.54</v>
       </c>
       <c r="H118" t="n">
-        <v>24.44</v>
+        <v>266.11</v>
       </c>
       <c r="I118" t="n">
-        <v>10.08</v>
+        <v>0.5</v>
       </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
@@ -6248,18 +6248,18 @@
         <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>-1.25</v>
+        <v>0.11</v>
       </c>
       <c r="Q118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="n">
-        <v>2027639997</v>
+        <v>1867193304</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6268,19 +6268,19 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.1558</v>
+        <v>0.1337</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>45916.65703747685</v>
+        <v>45818.8008296412</v>
       </c>
       <c r="G119" t="n">
-        <v>64.18000000000001</v>
+        <v>17.64</v>
       </c>
       <c r="H119" t="n">
-        <v>63.95</v>
+        <v>20.97</v>
       </c>
       <c r="I119" t="n">
-        <v>10</v>
+        <v>2.36</v>
       </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
@@ -6297,18 +6297,18 @@
         <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>-0.04</v>
+        <v>0.44</v>
       </c>
       <c r="Q119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="n">
-        <v>2000138014</v>
+        <v>2002503461</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>BTCE.DE</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6317,19 +6317,19 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.1017</v>
+        <v>0.0439</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>45901.57795706019</v>
+        <v>45902.65623520833</v>
       </c>
       <c r="G120" t="n">
-        <v>83.47499999999999</v>
+        <v>227.95</v>
       </c>
       <c r="H120" t="n">
-        <v>89.47</v>
+        <v>292.04</v>
       </c>
       <c r="I120" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
@@ -6346,18 +6346,18 @@
         <v>0</v>
       </c>
       <c r="P120" t="n">
-        <v>0.67</v>
+        <v>2.81</v>
       </c>
       <c r="Q120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="n">
-        <v>1995846726</v>
+        <v>2025661832</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6366,19 +6366,19 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.1372</v>
+        <v>0.3235</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>45897.72549582176</v>
+        <v>45915.72870862269</v>
       </c>
       <c r="G121" t="n">
-        <v>72.94</v>
+        <v>61.81</v>
       </c>
       <c r="H121" t="n">
-        <v>70.73999999999999</v>
+        <v>59.61</v>
       </c>
       <c r="I121" t="n">
-        <v>10.01</v>
+        <v>20</v>
       </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
@@ -6395,18 +6395,18 @@
         <v>0</v>
       </c>
       <c r="P121" t="n">
-        <v>-0.3</v>
+        <v>-0.72</v>
       </c>
       <c r="Q121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="n">
-        <v>1982267978</v>
+        <v>2042956616</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6415,19 +6415,19 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.033</v>
+        <v>0.1592</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>45889.64851537037</v>
+        <v>45924.69943638889</v>
       </c>
       <c r="G122" t="n">
-        <v>303.76</v>
+        <v>62.88</v>
       </c>
       <c r="H122" t="n">
-        <v>342.82</v>
+        <v>59.61</v>
       </c>
       <c r="I122" t="n">
-        <v>10.02</v>
+        <v>10.01</v>
       </c>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
@@ -6444,18 +6444,18 @@
         <v>0</v>
       </c>
       <c r="P122" t="n">
-        <v>1.29</v>
+        <v>-0.52</v>
       </c>
       <c r="Q122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="n">
-        <v>1517510856</v>
+        <v>1978487977</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6464,16 +6464,16 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.0602</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>45597.61014849537</v>
+        <v>45887.66311905093</v>
       </c>
       <c r="G123" t="n">
-        <v>166.03</v>
+        <v>127.06</v>
       </c>
       <c r="H123" t="n">
-        <v>140.69</v>
+        <v>120.6</v>
       </c>
       <c r="I123" t="n">
         <v>10</v>
@@ -6493,18 +6493,18 @@
         <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>-1.53</v>
+        <v>-0.51</v>
       </c>
       <c r="Q123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="n">
-        <v>1880443947</v>
+        <v>1744916497</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6513,19 +6513,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.1047</v>
+        <v>1</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>45825.891695625</v>
+        <v>45751.74231563658</v>
       </c>
       <c r="G124" t="n">
-        <v>142.99</v>
+        <v>17.54</v>
       </c>
       <c r="H124" t="n">
-        <v>208.95</v>
+        <v>25.77</v>
       </c>
       <c r="I124" t="n">
-        <v>14.97</v>
+        <v>17.54</v>
       </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
@@ -6542,18 +6542,18 @@
         <v>0</v>
       </c>
       <c r="P124" t="n">
-        <v>6.91</v>
+        <v>8.23</v>
       </c>
       <c r="Q124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="n">
-        <v>1648737122</v>
+        <v>1727563010</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6562,19 +6562,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.001</v>
+        <v>1</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>45695.85619950231</v>
+        <v>45743.76106726852</v>
       </c>
       <c r="G125" t="n">
-        <v>408.33</v>
+        <v>46.11</v>
       </c>
       <c r="H125" t="n">
-        <v>508.36</v>
+        <v>54.78</v>
       </c>
       <c r="I125" t="n">
-        <v>0.41</v>
+        <v>46.11</v>
       </c>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
@@ -6591,18 +6591,18 @@
         <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>0.1</v>
+        <v>8.67</v>
       </c>
       <c r="Q125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="n">
-        <v>1882278057</v>
+        <v>1997500170</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>JKS</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6611,19 +6611,19 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.0432</v>
+        <v>0.4466</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>45826.76262912037</v>
+        <v>45898.65406594907</v>
       </c>
       <c r="G126" t="n">
-        <v>346.61</v>
+        <v>22.39</v>
       </c>
       <c r="H126" t="n">
-        <v>338.11</v>
+        <v>24.6</v>
       </c>
       <c r="I126" t="n">
-        <v>14.97</v>
+        <v>10</v>
       </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
@@ -6640,18 +6640,18 @@
         <v>0</v>
       </c>
       <c r="P126" t="n">
-        <v>-0.36</v>
+        <v>0.99</v>
       </c>
       <c r="Q126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="n">
-        <v>1983186744</v>
+        <v>1744929368</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6660,19 +6660,19 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.3162</v>
+        <v>0.0192</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>45889.85904239583</v>
+        <v>45751.74500871528</v>
       </c>
       <c r="G127" t="n">
-        <v>31.61</v>
+        <v>324.48</v>
       </c>
       <c r="H127" t="n">
-        <v>24.44</v>
+        <v>349.84</v>
       </c>
       <c r="I127" t="n">
-        <v>10</v>
+        <v>6.23</v>
       </c>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
@@ -6689,14 +6689,14 @@
         <v>0</v>
       </c>
       <c r="P127" t="n">
-        <v>-2.27</v>
+        <v>0.49</v>
       </c>
       <c r="Q127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="n">
-        <v>1867193336</v>
+        <v>1806980496</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -6712,16 +6712,16 @@
         <v>1</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>45818.80084483796</v>
+        <v>45783.83190503472</v>
       </c>
       <c r="G128" t="n">
-        <v>17.64</v>
+        <v>16.12</v>
       </c>
       <c r="H128" t="n">
-        <v>21.02</v>
+        <v>20.97</v>
       </c>
       <c r="I128" t="n">
-        <v>17.64</v>
+        <v>16.12</v>
       </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
@@ -6738,18 +6738,18 @@
         <v>0</v>
       </c>
       <c r="P128" t="n">
-        <v>3.38</v>
+        <v>4.85</v>
       </c>
       <c r="Q128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="n">
-        <v>1867194722</v>
+        <v>2060617471</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6758,19 +6758,19 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1</v>
+        <v>0.2255</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>45818.80135700232</v>
+        <v>45932.89647650463</v>
       </c>
       <c r="G129" t="n">
-        <v>21.27</v>
+        <v>44.35</v>
       </c>
       <c r="H129" t="n">
-        <v>18.31</v>
+        <v>44.83</v>
       </c>
       <c r="I129" t="n">
-        <v>21.27</v>
+        <v>10</v>
       </c>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
@@ -6787,18 +6787,18 @@
         <v>0</v>
       </c>
       <c r="P129" t="n">
-        <v>-2.96</v>
+        <v>0.11</v>
       </c>
       <c r="Q129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="n">
-        <v>1554741956</v>
+        <v>2060624552</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6807,19 +6807,19 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.0495</v>
+        <v>0.1676</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>45623.74952237269</v>
+        <v>45932.90130990741</v>
       </c>
       <c r="G130" t="n">
-        <v>15.3</v>
+        <v>59.7</v>
       </c>
       <c r="H130" t="n">
-        <v>25.31</v>
+        <v>59.61</v>
       </c>
       <c r="I130" t="n">
-        <v>0.76</v>
+        <v>10.01</v>
       </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
@@ -6836,18 +6836,18 @@
         <v>0</v>
       </c>
       <c r="P130" t="n">
-        <v>0.49</v>
+        <v>-0.02</v>
       </c>
       <c r="Q130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="n">
-        <v>1928218937</v>
+        <v>1880442840</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6856,19 +6856,19 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1</v>
+        <v>0.2535</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>45855.75970359953</v>
+        <v>45825.89113450232</v>
       </c>
       <c r="G131" t="n">
-        <v>20.24</v>
+        <v>59.15</v>
       </c>
       <c r="H131" t="n">
-        <v>18.31</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>20.24</v>
+        <v>14.99</v>
       </c>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
@@ -6885,14 +6885,14 @@
         <v>0</v>
       </c>
       <c r="P131" t="n">
-        <v>-1.93</v>
+        <v>1.67</v>
       </c>
       <c r="Q131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="n">
-        <v>2017847675</v>
+        <v>2045990228</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -6905,19 +6905,19 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.2767</v>
+        <v>0.2718</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>45910.65426635417</v>
+        <v>45925.79958348379</v>
       </c>
       <c r="G132" t="n">
-        <v>36.17</v>
+        <v>36.75</v>
       </c>
       <c r="H132" t="n">
-        <v>37.73</v>
+        <v>40.46</v>
       </c>
       <c r="I132" t="n">
-        <v>10.01</v>
+        <v>9.99</v>
       </c>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
@@ -6934,18 +6934,18 @@
         <v>0</v>
       </c>
       <c r="P132" t="n">
-        <v>0.43</v>
+        <v>1.01</v>
       </c>
       <c r="Q132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="n">
-        <v>1680994777</v>
+        <v>1867197360</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6954,19 +6954,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.7278</v>
+        <v>0.0765</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>45716.85705375</v>
+        <v>45818.80265583334</v>
       </c>
       <c r="G133" t="n">
-        <v>20.6</v>
+        <v>131.96</v>
       </c>
       <c r="H133" t="n">
-        <v>23.89</v>
+        <v>141.96</v>
       </c>
       <c r="I133" t="n">
-        <v>14.99</v>
+        <v>10.09</v>
       </c>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
@@ -6983,18 +6983,18 @@
         <v>0</v>
       </c>
       <c r="P133" t="n">
-        <v>2.4</v>
+        <v>0.77</v>
       </c>
       <c r="Q133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="n">
-        <v>1997562259</v>
+        <v>2020498366</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>BBAR</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -7003,19 +7003,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.6323</v>
+        <v>1</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>45898.65762083334</v>
+        <v>45911.68945292824</v>
       </c>
       <c r="G134" t="n">
-        <v>23.72</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="H134" t="n">
-        <v>25.31</v>
+        <v>8.31</v>
       </c>
       <c r="I134" t="n">
-        <v>15</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
@@ -7032,18 +7032,18 @@
         <v>0</v>
       </c>
       <c r="P134" t="n">
-        <v>1</v>
+        <v>-1.57</v>
       </c>
       <c r="Q134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="n">
-        <v>1633116336</v>
+        <v>1563288050</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7052,19 +7052,19 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1</v>
+        <v>0.0626</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>45686.83272234954</v>
+        <v>45630.85583428241</v>
       </c>
       <c r="G135" t="n">
-        <v>44.24</v>
+        <v>159.74</v>
       </c>
       <c r="H135" t="n">
-        <v>54.27</v>
+        <v>141.96</v>
       </c>
       <c r="I135" t="n">
-        <v>44.24</v>
+        <v>10</v>
       </c>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
@@ -7081,18 +7081,18 @@
         <v>0</v>
       </c>
       <c r="P135" t="n">
-        <v>10.03</v>
+        <v>-1.11</v>
       </c>
       <c r="Q135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="n">
-        <v>1796453499</v>
+        <v>1666459270</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7101,19 +7101,19 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.5636</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>45777.64668229167</v>
+        <v>45708.68166530092</v>
       </c>
       <c r="G136" t="n">
-        <v>15.57</v>
+        <v>17.18</v>
       </c>
       <c r="H136" t="n">
-        <v>21.02</v>
+        <v>25.77</v>
       </c>
       <c r="I136" t="n">
-        <v>8.01</v>
+        <v>9.68</v>
       </c>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
@@ -7130,18 +7130,18 @@
         <v>0</v>
       </c>
       <c r="P136" t="n">
-        <v>2.81</v>
+        <v>4.84</v>
       </c>
       <c r="Q136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="n">
-        <v>1824475555</v>
+        <v>1984829391</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7150,19 +7150,19 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1</v>
+        <v>0.0512</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>45792.64702015046</v>
+        <v>45890.71798858796</v>
       </c>
       <c r="G137" t="n">
-        <v>21.66</v>
+        <v>195.52</v>
       </c>
       <c r="H137" t="n">
-        <v>18.31</v>
+        <v>229.42</v>
       </c>
       <c r="I137" t="n">
-        <v>21.66</v>
+        <v>10.01</v>
       </c>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
@@ -7179,18 +7179,18 @@
         <v>0</v>
       </c>
       <c r="P137" t="n">
-        <v>-3.35</v>
+        <v>1.74</v>
       </c>
       <c r="Q137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="n">
-        <v>1621495187</v>
+        <v>1975988073</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7199,19 +7199,19 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.2318</v>
+        <v>0.0469</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>45678.83178196759</v>
+        <v>45884.6572796875</v>
       </c>
       <c r="G138" t="n">
-        <v>43.27</v>
+        <v>319.83</v>
       </c>
       <c r="H138" t="n">
-        <v>24.44</v>
+        <v>379.97</v>
       </c>
       <c r="I138" t="n">
-        <v>10.03</v>
+        <v>15</v>
       </c>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
@@ -7228,18 +7228,18 @@
         <v>0</v>
       </c>
       <c r="P138" t="n">
-        <v>-4.36</v>
+        <v>2.82</v>
       </c>
       <c r="Q138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="n">
-        <v>2029950407</v>
+        <v>1989207013</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>PHGP.L</t>
+          <t>JKS</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7248,19 +7248,19 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.1453</v>
+        <v>0.4133</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>45917.66293982639</v>
+        <v>45894.65354606482</v>
       </c>
       <c r="G139" t="n">
-        <v>250.56</v>
+        <v>24.19</v>
       </c>
       <c r="H139" t="n">
-        <v>249.81</v>
+        <v>24.6</v>
       </c>
       <c r="I139" t="n">
-        <v>49.99</v>
+        <v>10</v>
       </c>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
@@ -7277,14 +7277,14 @@
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>-1.02</v>
+        <v>0.17</v>
       </c>
       <c r="Q139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="n">
-        <v>1754304266</v>
+        <v>1744767540</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -7297,19 +7297,19 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.7137</v>
+        <v>0.643</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>45755.88055112268</v>
+        <v>45751.72316712963</v>
       </c>
       <c r="G140" t="n">
-        <v>14</v>
+        <v>15.55</v>
       </c>
       <c r="H140" t="n">
-        <v>23.89</v>
+        <v>24.53</v>
       </c>
       <c r="I140" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
@@ -7326,18 +7326,18 @@
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>7.06</v>
+        <v>5.77</v>
       </c>
       <c r="Q140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="n">
-        <v>1882283184</v>
+        <v>1635194117</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -7346,16 +7346,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.4835</v>
+        <v>0.2479</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>45826.76569390047</v>
+        <v>45687.85228493056</v>
       </c>
       <c r="G141" t="n">
-        <v>20.69</v>
+        <v>40.33</v>
       </c>
       <c r="H141" t="n">
-        <v>23.89</v>
+        <v>24.14</v>
       </c>
       <c r="I141" t="n">
         <v>10</v>
@@ -7375,27 +7375,45 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>1.55</v>
+        <v>-4.02</v>
       </c>
       <c r="Q141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr"/>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
+      <c r="B142" t="n">
+        <v>1888686062</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>YPF</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>45831.64964792824</v>
+      </c>
+      <c r="G142" t="n">
+        <v>34.36</v>
+      </c>
+      <c r="H142" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="I142" t="n">
+        <v>9.970000000000001</v>
+      </c>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
       <c r="M142" t="n">
         <v>0</v>
       </c>
@@ -7406,9 +7424,236 @@
         <v>0</v>
       </c>
       <c r="P142" t="n">
-        <v>169.67</v>
+        <v>-2.96</v>
       </c>
       <c r="Q142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
+      <c r="B143" t="n">
+        <v>1648737122</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>45695.85619950231</v>
+      </c>
+      <c r="G143" t="n">
+        <v>408.33</v>
+      </c>
+      <c r="H143" t="n">
+        <v>517.23</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+      <c r="B144" t="n">
+        <v>2050937088</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>BTCE.DE</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>45929.65204666667</v>
+      </c>
+      <c r="G144" t="n">
+        <v>86.06999999999999</v>
+      </c>
+      <c r="H144" t="n">
+        <v>92.845</v>
+      </c>
+      <c r="I144" t="n">
+        <v>10</v>
+      </c>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="Q144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
+      <c r="B145" t="n">
+        <v>2047758738</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>0.0365</v>
+      </c>
+      <c r="F145" s="2" t="n">
+        <v>45926.65183609954</v>
+      </c>
+      <c r="G145" t="n">
+        <v>274.22</v>
+      </c>
+      <c r="H145" t="n">
+        <v>292.04</v>
+      </c>
+      <c r="I145" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="Q145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
+      <c r="B146" t="n">
+        <v>1928218937</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>ACI</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>45855.75970359953</v>
+      </c>
+      <c r="G146" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="H146" t="n">
+        <v>17.37</v>
+      </c>
+      <c r="I146" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" t="n">
+        <v>-2.87</v>
+      </c>
+      <c r="Q146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr"/>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" t="n">
+        <v>166.02</v>
+      </c>
+      <c r="Q147" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Stock Selection/OPEN POSITION.xlsx
+++ b/Stock Selection/OPEN POSITION.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q147"/>
+  <dimension ref="A1:Q164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,11 +522,11 @@
     <row r="2">
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="n">
-        <v>1461331124</v>
+        <v>2025662892</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.3752</v>
+        <v>0.8196</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45553.65374138889</v>
+        <v>45915.72913914352</v>
       </c>
       <c r="G2" t="n">
-        <v>50.99</v>
+        <v>24.39</v>
       </c>
       <c r="H2" t="n">
-        <v>65.70999999999999</v>
+        <v>22.87</v>
       </c>
       <c r="I2" t="n">
-        <v>19.13</v>
+        <v>19.99</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -564,18 +564,18 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>5.52</v>
+        <v>-1.25</v>
       </c>
       <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="n">
-        <v>1843474191</v>
+        <v>1461331124</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -584,19 +584,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9372</v>
+        <v>0.3752</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45804.66699503472</v>
+        <v>45553.65374138889</v>
       </c>
       <c r="G3" t="n">
-        <v>21.33</v>
+        <v>50.99</v>
       </c>
       <c r="H3" t="n">
-        <v>25.77</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>19.99</v>
+        <v>19.13</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -613,18 +613,18 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.16</v>
+        <v>4.98</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="n">
-        <v>2000138014</v>
+        <v>1599431096</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BTCE.DE</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -633,19 +633,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1017</v>
+        <v>0.1013</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45901.57795706019</v>
+        <v>45663.73014731482</v>
       </c>
       <c r="G4" t="n">
-        <v>83.47499999999999</v>
+        <v>148.02</v>
       </c>
       <c r="H4" t="n">
-        <v>92.845</v>
+        <v>152.68</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>14.99</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -662,18 +662,18 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.03</v>
+        <v>0.48</v>
       </c>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="n">
-        <v>1843477272</v>
+        <v>2091063412</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0.4089</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45804.66725678241</v>
+        <v>45945.66023149306</v>
       </c>
       <c r="G5" t="n">
-        <v>17.86</v>
+        <v>24.44</v>
       </c>
       <c r="H5" t="n">
-        <v>20.97</v>
+        <v>24.41</v>
       </c>
       <c r="I5" t="n">
-        <v>17.86</v>
+        <v>9.99</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -711,18 +711,18 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.11</v>
+        <v>-0.01</v>
       </c>
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="n">
-        <v>1843470413</v>
+        <v>1754302454</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.4515</v>
+        <v>0.3673</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45804.66637251157</v>
+        <v>45755.88025324074</v>
       </c>
       <c r="G6" t="n">
-        <v>42.29</v>
+        <v>27.17</v>
       </c>
       <c r="H6" t="n">
-        <v>52</v>
+        <v>26.35</v>
       </c>
       <c r="I6" t="n">
-        <v>19.09</v>
+        <v>9.98</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -760,18 +760,18 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>4.39</v>
+        <v>-0.3</v>
       </c>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="n">
-        <v>1981010841</v>
+        <v>1995249699</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -780,19 +780,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.0425</v>
+        <v>0.3888</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45888.84617734954</v>
+        <v>45897.61086020833</v>
       </c>
       <c r="G7" t="n">
-        <v>235.53</v>
+        <v>87.16500000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>292.04</v>
+        <v>84.605</v>
       </c>
       <c r="I7" t="n">
-        <v>10.01</v>
+        <v>39.77</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -809,18 +809,18 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.4</v>
+        <v>-1.57</v>
       </c>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>1976499401</v>
+        <v>1845429980</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.8064</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45884.83731814815</v>
+        <v>45805.66181400463</v>
       </c>
       <c r="G8" t="n">
-        <v>49.6</v>
+        <v>13.27</v>
       </c>
       <c r="H8" t="n">
-        <v>50.35</v>
+        <v>15.685</v>
       </c>
       <c r="I8" t="n">
-        <v>40</v>
+        <v>15.09</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -858,18 +858,18 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6</v>
+        <v>3.12</v>
       </c>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>1997561527</v>
+        <v>1869077178</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -878,19 +878,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.1498</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45898.65748991898</v>
+        <v>45819.67426902778</v>
       </c>
       <c r="G9" t="n">
-        <v>66.73</v>
+        <v>13.285</v>
       </c>
       <c r="H9" t="n">
-        <v>65.70999999999999</v>
+        <v>15.685</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>15.31</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -907,18 +907,18 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.16</v>
+        <v>2.9</v>
       </c>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
-        <v>1883977086</v>
+        <v>1923258249</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -930,16 +930,16 @@
         <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45827.66106613426</v>
+        <v>45853.65576626157</v>
       </c>
       <c r="G10" t="n">
-        <v>12.875</v>
+        <v>19.41</v>
       </c>
       <c r="H10" t="n">
-        <v>16.435</v>
+        <v>23</v>
       </c>
       <c r="I10" t="n">
-        <v>14.86</v>
+        <v>19.41</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -956,18 +956,18 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>4.34</v>
+        <v>3.59</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
-        <v>1642762235</v>
+        <v>1517510856</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -976,19 +976,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.1572</v>
+        <v>0.0602</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45692.86612574074</v>
+        <v>45597.61014849537</v>
       </c>
       <c r="G11" t="n">
-        <v>127.16</v>
+        <v>166.03</v>
       </c>
       <c r="H11" t="n">
-        <v>120.6</v>
+        <v>152.68</v>
       </c>
       <c r="I11" t="n">
-        <v>19.99</v>
+        <v>10</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -1005,18 +1005,18 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.03</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>2060620530</v>
+        <v>1806977521</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BLX</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1025,19 +1025,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.2207</v>
+        <v>0.3367</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>45932.89856876157</v>
+        <v>45783.8305750463</v>
       </c>
       <c r="G12" t="n">
-        <v>45.28</v>
+        <v>29.7</v>
       </c>
       <c r="H12" t="n">
-        <v>44.99</v>
+        <v>26.35</v>
       </c>
       <c r="I12" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -1054,18 +1054,18 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.06</v>
+        <v>-1.13</v>
       </c>
       <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>2047814173</v>
+        <v>1701100027</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IAPD.AS</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1074,19 +1074,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.5688</v>
+        <v>0.5043</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>45926.6592943287</v>
+        <v>45727.87202070602</v>
       </c>
       <c r="G13" t="n">
-        <v>22.46</v>
+        <v>19.2</v>
       </c>
       <c r="H13" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="I13" t="n">
-        <v>15</v>
+        <v>9.68</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -1103,18 +1103,18 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.22</v>
+        <v>1.92</v>
       </c>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="n">
-        <v>1923258184</v>
+        <v>1997552824</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.0298</v>
+        <v>0.0429</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>45853.6557568287</v>
+        <v>45898.65627293981</v>
       </c>
       <c r="G14" t="n">
-        <v>19.43</v>
+        <v>233.17</v>
       </c>
       <c r="H14" t="n">
-        <v>24.53</v>
+        <v>300.11</v>
       </c>
       <c r="I14" t="n">
-        <v>0.58</v>
+        <v>10</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -1152,18 +1152,18 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.15</v>
+        <v>2.87</v>
       </c>
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="n">
-        <v>1621495187</v>
+        <v>2042979139</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.2318</v>
+        <v>0.3128</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>45678.83178196759</v>
+        <v>45924.70564383102</v>
       </c>
       <c r="G15" t="n">
-        <v>43.27</v>
+        <v>32</v>
       </c>
       <c r="H15" t="n">
-        <v>24.14</v>
+        <v>31.67</v>
       </c>
       <c r="I15" t="n">
-        <v>10.03</v>
+        <v>10.01</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1201,18 +1201,18 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-4.43</v>
+        <v>-0.1</v>
       </c>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="n">
-        <v>1882278057</v>
+        <v>2060617471</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.0432</v>
+        <v>0.2255</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>45826.76262912037</v>
+        <v>45932.89647650463</v>
       </c>
       <c r="G16" t="n">
-        <v>346.61</v>
+        <v>44.35</v>
       </c>
       <c r="H16" t="n">
-        <v>349.84</v>
+        <v>41.02</v>
       </c>
       <c r="I16" t="n">
-        <v>14.97</v>
+        <v>10</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1250,18 +1250,18 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.14</v>
+        <v>-0.75</v>
       </c>
       <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="n">
-        <v>2017852950</v>
+        <v>2042956616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1270,19 +1270,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0.1592</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>45910.65507498843</v>
+        <v>45924.69943638889</v>
       </c>
       <c r="G17" t="n">
-        <v>37.44</v>
+        <v>62.88</v>
       </c>
       <c r="H17" t="n">
-        <v>43.52</v>
+        <v>60.36</v>
       </c>
       <c r="I17" t="n">
-        <v>37.44</v>
+        <v>10.01</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1299,18 +1299,18 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>6.08</v>
+        <v>-0.4</v>
       </c>
       <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
-        <v>1867458993</v>
+        <v>2025661832</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1319,16 +1319,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.3417</v>
+        <v>0.3235</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45818.90699613426</v>
+        <v>45915.72870862269</v>
       </c>
       <c r="G18" t="n">
-        <v>58.53</v>
+        <v>61.81</v>
       </c>
       <c r="H18" t="n">
-        <v>65.70999999999999</v>
+        <v>60.36</v>
       </c>
       <c r="I18" t="n">
         <v>20</v>
@@ -1348,18 +1348,18 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.45</v>
+        <v>-0.47</v>
       </c>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="n">
-        <v>1744879358</v>
+        <v>2017777441</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1368,19 +1368,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.1247</v>
+        <v>0.4582</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45751.73925940973</v>
+        <v>45910.64656457176</v>
       </c>
       <c r="G19" t="n">
-        <v>148.09</v>
+        <v>21.82</v>
       </c>
       <c r="H19" t="n">
-        <v>292.04</v>
+        <v>23</v>
       </c>
       <c r="I19" t="n">
-        <v>18.47</v>
+        <v>10</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1397,18 +1397,18 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>17.95</v>
+        <v>0.54</v>
       </c>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
-        <v>2042971604</v>
+        <v>2071864157</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>PHGP.L</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1417,19 +1417,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.3901</v>
+        <v>0.0291</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45924.70406969907</v>
+        <v>45938.58107210648</v>
       </c>
       <c r="G20" t="n">
-        <v>25.66</v>
+        <v>280.19</v>
       </c>
       <c r="H20" t="n">
-        <v>24.73</v>
+        <v>295.87</v>
       </c>
       <c r="I20" t="n">
-        <v>10.01</v>
+        <v>10.99</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1446,18 +1446,18 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.36</v>
+        <v>0.51</v>
       </c>
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="n">
-        <v>1744930699</v>
+        <v>1582723120</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1466,19 +1466,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0.3755</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45751.74534789352</v>
+        <v>45645.89511640046</v>
       </c>
       <c r="G21" t="n">
-        <v>74.13</v>
+        <v>53.26</v>
       </c>
       <c r="H21" t="n">
-        <v>74.29000000000001</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>74.13</v>
+        <v>20</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1495,18 +1495,18 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.16</v>
+        <v>4.13</v>
       </c>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="n">
-        <v>1824475555</v>
+        <v>1883977044</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1515,19 +1515,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0.345</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>45792.64702015046</v>
+        <v>45827.66105774305</v>
       </c>
       <c r="G22" t="n">
-        <v>21.66</v>
+        <v>12.88</v>
       </c>
       <c r="H22" t="n">
-        <v>17.37</v>
+        <v>15.685</v>
       </c>
       <c r="I22" t="n">
-        <v>21.66</v>
+        <v>5.13</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -1544,18 +1544,18 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.29</v>
+        <v>1.15</v>
       </c>
       <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="n">
-        <v>1997485943</v>
+        <v>2000138014</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1564,16 +1564,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.5157</v>
+        <v>0.1017</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>45898.65185685185</v>
+        <v>45901.57795706019</v>
       </c>
       <c r="G23" t="n">
-        <v>19.39</v>
+        <v>83.47499999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>20.97</v>
+        <v>84.605</v>
       </c>
       <c r="I23" t="n">
         <v>10</v>
@@ -1593,18 +1593,18 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="n">
-        <v>1993444707</v>
+        <v>1880446729</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BBAR</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.8051</v>
+        <v>0.0772</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45896.6743321875</v>
+        <v>45825.89315055555</v>
       </c>
       <c r="G24" t="n">
-        <v>12.42</v>
+        <v>129.62</v>
       </c>
       <c r="H24" t="n">
-        <v>8.31</v>
+        <v>152.68</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1642,14 +1642,14 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.31</v>
+        <v>1.78</v>
       </c>
       <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="n">
-        <v>1644788775</v>
+        <v>1867197360</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1662,19 +1662,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.0765</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>45693.85093391204</v>
+        <v>45818.80265583334</v>
       </c>
       <c r="G25" t="n">
-        <v>144.94</v>
+        <v>131.96</v>
       </c>
       <c r="H25" t="n">
-        <v>141.96</v>
+        <v>152.68</v>
       </c>
       <c r="I25" t="n">
-        <v>10.99</v>
+        <v>10.09</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -1691,18 +1691,18 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.23</v>
+        <v>1.59</v>
       </c>
       <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="n">
-        <v>1806980482</v>
+        <v>1984829391</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1711,19 +1711,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.2406</v>
+        <v>0.0512</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>45783.83189613426</v>
+        <v>45890.71798858796</v>
       </c>
       <c r="G26" t="n">
-        <v>16.12</v>
+        <v>195.52</v>
       </c>
       <c r="H26" t="n">
-        <v>20.97</v>
+        <v>237.16</v>
       </c>
       <c r="I26" t="n">
-        <v>3.88</v>
+        <v>10.01</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -1740,18 +1740,18 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.17</v>
+        <v>2.13</v>
       </c>
       <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="n">
-        <v>2060645660</v>
+        <v>1599448103</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1760,19 +1760,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.1027</v>
+        <v>0.2839</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>45932.90186543982</v>
+        <v>45663.73506711805</v>
       </c>
       <c r="G27" t="n">
-        <v>97.43000000000001</v>
+        <v>52.83</v>
       </c>
       <c r="H27" t="n">
-        <v>97.70999999999999</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>10.01</v>
+        <v>15</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -1789,18 +1789,18 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.02</v>
+        <v>3.24</v>
       </c>
       <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="n">
-        <v>2060619876</v>
+        <v>1806980482</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1809,19 +1809,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.4178</v>
+        <v>0.2406</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>45932.89807736111</v>
+        <v>45783.83189613426</v>
       </c>
       <c r="G28" t="n">
-        <v>23.93</v>
+        <v>16.12</v>
       </c>
       <c r="H28" t="n">
-        <v>24.53</v>
+        <v>19.95</v>
       </c>
       <c r="I28" t="n">
-        <v>10</v>
+        <v>3.88</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -1838,18 +1838,18 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0.25</v>
+        <v>0.92</v>
       </c>
       <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
-        <v>2017847675</v>
+        <v>2076201130</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1858,19 +1858,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.2767</v>
+        <v>0.499</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>45910.65426635417</v>
+        <v>45939.75708394676</v>
       </c>
       <c r="G29" t="n">
-        <v>36.17</v>
+        <v>20.04</v>
       </c>
       <c r="H29" t="n">
-        <v>40.46</v>
+        <v>19.95</v>
       </c>
       <c r="I29" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -1887,18 +1887,18 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.19</v>
+        <v>-0.04</v>
       </c>
       <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
-        <v>1843469729</v>
+        <v>2047814173</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>IAPD.AS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1907,19 +1907,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.0423</v>
+        <v>0.5688</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45804.66615450232</v>
+        <v>45926.6592943287</v>
       </c>
       <c r="G30" t="n">
-        <v>156.9</v>
+        <v>22.46</v>
       </c>
       <c r="H30" t="n">
-        <v>229.42</v>
+        <v>23.005</v>
       </c>
       <c r="I30" t="n">
-        <v>6.64</v>
+        <v>15</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -1936,18 +1936,18 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.06</v>
+        <v>0.19</v>
       </c>
       <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="n">
-        <v>2029950407</v>
+        <v>2035163256</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PHGP.L</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1956,19 +1956,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.1453</v>
+        <v>0.0951</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45917.66293982639</v>
+        <v>45919.66675122685</v>
       </c>
       <c r="G31" t="n">
-        <v>250.56</v>
+        <v>88.91</v>
       </c>
       <c r="H31" t="n">
-        <v>268.4</v>
+        <v>84.605</v>
       </c>
       <c r="I31" t="n">
-        <v>49.99</v>
+        <v>9.99</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1985,18 +1985,18 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.33</v>
+        <v>-0.65</v>
       </c>
       <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="n">
-        <v>1599448103</v>
+        <v>1972092684</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2005,19 +2005,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.2839</v>
+        <v>1</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45663.73506711805</v>
+        <v>45882.68269449074</v>
       </c>
       <c r="G32" t="n">
-        <v>52.83</v>
+        <v>18.8</v>
       </c>
       <c r="H32" t="n">
-        <v>65.70999999999999</v>
+        <v>19.24</v>
       </c>
       <c r="I32" t="n">
-        <v>15</v>
+        <v>18.8</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -2034,18 +2034,18 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>3.66</v>
+        <v>0.44</v>
       </c>
       <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="n">
-        <v>1701100027</v>
+        <v>1727563010</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2054,19 +2054,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.5043</v>
+        <v>1</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45727.87202070602</v>
+        <v>45743.76106726852</v>
       </c>
       <c r="G33" t="n">
-        <v>19.2</v>
+        <v>46.11</v>
       </c>
       <c r="H33" t="n">
-        <v>24.53</v>
+        <v>54.52</v>
       </c>
       <c r="I33" t="n">
-        <v>9.68</v>
+        <v>46.11</v>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -2083,18 +2083,18 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.69</v>
+        <v>8.41</v>
       </c>
       <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="n">
-        <v>1982267978</v>
+        <v>1744930699</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>BND</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2103,19 +2103,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.033</v>
+        <v>1</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45889.64851537037</v>
+        <v>45751.74534789352</v>
       </c>
       <c r="G34" t="n">
-        <v>303.76</v>
+        <v>74.13</v>
       </c>
       <c r="H34" t="n">
-        <v>379.97</v>
+        <v>74.97</v>
       </c>
       <c r="I34" t="n">
-        <v>10.02</v>
+        <v>74.13</v>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
@@ -2132,18 +2132,18 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.52</v>
+        <v>0.84</v>
       </c>
       <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>1754302454</v>
+        <v>1997485943</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2152,19 +2152,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.3673</v>
+        <v>0.5157</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>45755.88025324074</v>
+        <v>45898.65185685185</v>
       </c>
       <c r="G35" t="n">
-        <v>27.17</v>
+        <v>19.39</v>
       </c>
       <c r="H35" t="n">
-        <v>24.14</v>
+        <v>19.95</v>
       </c>
       <c r="I35" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
@@ -2181,18 +2181,18 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>-1.11</v>
+        <v>0.29</v>
       </c>
       <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>1997562259</v>
+        <v>2060619876</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2201,19 +2201,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.6323</v>
+        <v>0.4178</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45898.65762083334</v>
+        <v>45932.89807736111</v>
       </c>
       <c r="G36" t="n">
-        <v>23.72</v>
+        <v>23.93</v>
       </c>
       <c r="H36" t="n">
-        <v>25.77</v>
+        <v>23</v>
       </c>
       <c r="I36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -2230,18 +2230,18 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.29</v>
+        <v>-0.39</v>
       </c>
       <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
-        <v>1830408508</v>
+        <v>1744916452</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2250,19 +2250,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.5793</v>
+        <v>0.4245</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>45796.82346997685</v>
+        <v>45751.74230173611</v>
       </c>
       <c r="G37" t="n">
-        <v>17.26</v>
+        <v>17.54</v>
       </c>
       <c r="H37" t="n">
-        <v>24.53</v>
+        <v>24.41</v>
       </c>
       <c r="I37" t="n">
-        <v>10</v>
+        <v>7.45</v>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
@@ -2279,18 +2279,18 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>4.21</v>
+        <v>2.91</v>
       </c>
       <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>1754304266</v>
+        <v>2091104996</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>BLX</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2299,19 +2299,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.7137</v>
+        <v>0.2189</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45755.88055112268</v>
+        <v>45945.66391778935</v>
       </c>
       <c r="G38" t="n">
-        <v>14</v>
+        <v>45.76</v>
       </c>
       <c r="H38" t="n">
-        <v>24.53</v>
+        <v>44.62</v>
       </c>
       <c r="I38" t="n">
-        <v>9.99</v>
+        <v>10.02</v>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
@@ -2328,18 +2328,18 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>7.52</v>
+        <v>-0.25</v>
       </c>
       <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
-        <v>1653137218</v>
+        <v>1843477152</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2348,19 +2348,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.277</v>
+        <v>0.1198</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45699.85152199074</v>
+        <v>45804.66724922453</v>
       </c>
       <c r="G39" t="n">
-        <v>36.1</v>
+        <v>17.86</v>
       </c>
       <c r="H39" t="n">
-        <v>24.14</v>
+        <v>19.95</v>
       </c>
       <c r="I39" t="n">
-        <v>10</v>
+        <v>2.14</v>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -2377,18 +2377,18 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>-3.31</v>
+        <v>0.25</v>
       </c>
       <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="n">
-        <v>1631475148</v>
+        <v>1982273555</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2397,19 +2397,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.2592</v>
+        <v>0.0439</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>45685.83625201389</v>
+        <v>45889.64957444445</v>
       </c>
       <c r="G40" t="n">
-        <v>38.58</v>
+        <v>228</v>
       </c>
       <c r="H40" t="n">
-        <v>24.14</v>
+        <v>300.11</v>
       </c>
       <c r="I40" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
@@ -2426,18 +2426,18 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>-3.74</v>
+        <v>3.16</v>
       </c>
       <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="n">
-        <v>2047825292</v>
+        <v>2060624552</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BLX</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2446,19 +2446,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.3157</v>
+        <v>0.1676</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45926.66222740741</v>
+        <v>45932.90130990741</v>
       </c>
       <c r="G41" t="n">
-        <v>47.56</v>
+        <v>59.7</v>
       </c>
       <c r="H41" t="n">
-        <v>44.99</v>
+        <v>60.36</v>
       </c>
       <c r="I41" t="n">
-        <v>15.01</v>
+        <v>10.01</v>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
@@ -2475,18 +2475,18 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="n">
-        <v>2047762608</v>
+        <v>1923224670</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BBAR</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2495,19 +2495,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0.2583</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>45926.65281253472</v>
+        <v>45853.65359685185</v>
       </c>
       <c r="G42" t="n">
-        <v>9.27</v>
+        <v>58.05</v>
       </c>
       <c r="H42" t="n">
-        <v>8.31</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>9.27</v>
+        <v>14.99</v>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -2524,14 +2524,14 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>-0.96</v>
+        <v>1.61</v>
       </c>
       <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="n">
-        <v>1923246263</v>
+        <v>1662993636</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2547,16 +2547,16 @@
         <v>1</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>45853.6538128125</v>
+        <v>45706.87026833333</v>
       </c>
       <c r="G43" t="n">
-        <v>21.17</v>
+        <v>20.65</v>
       </c>
       <c r="H43" t="n">
-        <v>17.37</v>
+        <v>19.24</v>
       </c>
       <c r="I43" t="n">
-        <v>21.17</v>
+        <v>20.65</v>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -2573,18 +2573,18 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>-3.8</v>
+        <v>-1.41</v>
       </c>
       <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
-        <v>1495551484</v>
+        <v>2078840482</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2593,19 +2593,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.1914</v>
+        <v>0.4336</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45580.70648087963</v>
+        <v>45940.66718949074</v>
       </c>
       <c r="G44" t="n">
-        <v>135.82</v>
+        <v>23.06</v>
       </c>
       <c r="H44" t="n">
-        <v>120.6</v>
+        <v>23</v>
       </c>
       <c r="I44" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -2622,18 +2622,18 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>-2.92</v>
+        <v>-0.03</v>
       </c>
       <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>1845429980</v>
+        <v>2080269311</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2645,16 +2645,16 @@
         <v>1</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>45805.66181400463</v>
+        <v>45940.886384375</v>
       </c>
       <c r="G45" t="n">
-        <v>13.27</v>
+        <v>52.53</v>
       </c>
       <c r="H45" t="n">
-        <v>16.435</v>
+        <v>54.52</v>
       </c>
       <c r="I45" t="n">
-        <v>15.09</v>
+        <v>52.53</v>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -2671,18 +2671,18 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>4.11</v>
+        <v>1.99</v>
       </c>
       <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>2017777441</v>
+        <v>2047762508</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>BBAR</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2691,19 +2691,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.4582</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>45910.64656457176</v>
+        <v>45926.65279332176</v>
       </c>
       <c r="G46" t="n">
-        <v>21.82</v>
+        <v>9.27</v>
       </c>
       <c r="H46" t="n">
-        <v>24.53</v>
+        <v>9.49</v>
       </c>
       <c r="I46" t="n">
-        <v>10</v>
+        <v>0.73</v>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -2720,18 +2720,18 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.24</v>
+        <v>0.02</v>
       </c>
       <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>1869077157</v>
+        <v>2091105918</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>IAPD.AS</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2740,19 +2740,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.3061</v>
+        <v>0.5535</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>45819.6742621412</v>
+        <v>45945.66408168981</v>
       </c>
       <c r="G47" t="n">
-        <v>13.285</v>
+        <v>23.185</v>
       </c>
       <c r="H47" t="n">
-        <v>16.435</v>
+        <v>23.005</v>
       </c>
       <c r="I47" t="n">
-        <v>4.69</v>
+        <v>15</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -2769,18 +2769,18 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1.19</v>
+        <v>-0.22</v>
       </c>
       <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>2042867993</v>
+        <v>1744879358</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2789,19 +2789,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.2639</v>
+        <v>0.0247</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>45924.68015445602</v>
+        <v>45751.73925940973</v>
       </c>
       <c r="G48" t="n">
-        <v>37.93</v>
+        <v>148.09</v>
       </c>
       <c r="H48" t="n">
-        <v>40.46</v>
+        <v>300.11</v>
       </c>
       <c r="I48" t="n">
-        <v>10.01</v>
+        <v>3.66</v>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -2818,18 +2818,18 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0.67</v>
+        <v>3.75</v>
       </c>
       <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
-        <v>1986476926</v>
+        <v>1978487977</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2838,19 +2838,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45891.66490212963</v>
+        <v>45887.66311905093</v>
       </c>
       <c r="G49" t="n">
-        <v>34.44</v>
+        <v>127.06</v>
       </c>
       <c r="H49" t="n">
-        <v>43.52</v>
+        <v>120.39</v>
       </c>
       <c r="I49" t="n">
-        <v>34.44</v>
+        <v>10</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
@@ -2867,18 +2867,18 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>9.08</v>
+        <v>-0.53</v>
       </c>
       <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
-        <v>1824476420</v>
+        <v>1644796307</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.1548</v>
+        <v>1</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>45792.64714148148</v>
+        <v>45693.85501710648</v>
       </c>
       <c r="G50" t="n">
-        <v>129.17</v>
+        <v>20.36</v>
       </c>
       <c r="H50" t="n">
-        <v>141.96</v>
+        <v>19.24</v>
       </c>
       <c r="I50" t="n">
-        <v>20</v>
+        <v>20.36</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -2916,18 +2916,18 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1.98</v>
+        <v>-1.12</v>
       </c>
       <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>1997498400</v>
+        <v>2091064900</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2936,19 +2936,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.0507</v>
+        <v>0.4294</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>45898.65380736111</v>
+        <v>45945.66049490741</v>
       </c>
       <c r="G51" t="n">
-        <v>197.26</v>
+        <v>23.32</v>
       </c>
       <c r="H51" t="n">
-        <v>229.42</v>
+        <v>22.87</v>
       </c>
       <c r="I51" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -2965,18 +2965,18 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>1.63</v>
+        <v>-0.19</v>
       </c>
       <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
-        <v>1882283184</v>
+        <v>1495551484</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2985,19 +2985,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.4835</v>
+        <v>0.1914</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>45826.76569390047</v>
+        <v>45580.70648087963</v>
       </c>
       <c r="G52" t="n">
-        <v>20.69</v>
+        <v>135.82</v>
       </c>
       <c r="H52" t="n">
-        <v>24.53</v>
+        <v>120.39</v>
       </c>
       <c r="I52" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
@@ -3014,18 +3014,18 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>1.86</v>
+        <v>-2.96</v>
       </c>
       <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="n">
-        <v>1499061783</v>
+        <v>1599455288</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3034,19 +3034,19 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.0001</v>
+        <v>0.2195</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>45582.73996892361</v>
+        <v>45663.73750263889</v>
       </c>
       <c r="G53" t="n">
-        <v>232.2</v>
+        <v>45.55</v>
       </c>
       <c r="H53" t="n">
-        <v>258.02</v>
+        <v>26.35</v>
       </c>
       <c r="I53" t="n">
-        <v>0.02</v>
+        <v>10</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
@@ -3063,18 +3063,18 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>0.01</v>
+        <v>-4.22</v>
       </c>
       <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="n">
-        <v>2045989132</v>
+        <v>1888700382</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3083,19 +3083,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.2034</v>
+        <v>1</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>45925.79891365741</v>
+        <v>45831.65144708334</v>
       </c>
       <c r="G54" t="n">
-        <v>49.16</v>
+        <v>47.58</v>
       </c>
       <c r="H54" t="n">
-        <v>50.35</v>
+        <v>54.52</v>
       </c>
       <c r="I54" t="n">
-        <v>10</v>
+        <v>47.58</v>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
@@ -3112,18 +3112,18 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>0.24</v>
+        <v>6.94</v>
       </c>
       <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="n">
-        <v>1599431096</v>
+        <v>1997562259</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3132,19 +3132,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.1013</v>
+        <v>0.6323</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>45663.73014731482</v>
+        <v>45898.65762083334</v>
       </c>
       <c r="G55" t="n">
-        <v>148.02</v>
+        <v>23.72</v>
       </c>
       <c r="H55" t="n">
-        <v>141.96</v>
+        <v>24.41</v>
       </c>
       <c r="I55" t="n">
-        <v>14.99</v>
+        <v>15</v>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
@@ -3161,18 +3161,18 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>-0.61</v>
+        <v>0.43</v>
       </c>
       <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="n">
-        <v>2047762508</v>
+        <v>1845429956</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BBAR</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3181,19 +3181,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.4821</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>45926.65279332176</v>
+        <v>45805.66180811343</v>
       </c>
       <c r="G56" t="n">
-        <v>9.27</v>
+        <v>13.275</v>
       </c>
       <c r="H56" t="n">
-        <v>8.31</v>
+        <v>15.685</v>
       </c>
       <c r="I56" t="n">
-        <v>0.73</v>
+        <v>7.28</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
@@ -3210,18 +3210,18 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>-0.08</v>
+        <v>1.5</v>
       </c>
       <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="n">
-        <v>1880441651</v>
+        <v>1867462173</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3230,19 +3230,19 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45825.89055887731</v>
+        <v>45818.90866184028</v>
       </c>
       <c r="G57" t="n">
-        <v>21.21</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>17.37</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>21.21</v>
+        <v>0.65</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
@@ -3259,18 +3259,18 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>-3.84</v>
+        <v>0.16</v>
       </c>
       <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
-        <v>1926287328</v>
+        <v>2091086432</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3279,19 +3279,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.5476</v>
+        <v>0.1657</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45854.82177967593</v>
+        <v>45945.66072645834</v>
       </c>
       <c r="G58" t="n">
-        <v>18.26</v>
+        <v>60.4</v>
       </c>
       <c r="H58" t="n">
-        <v>24.53</v>
+        <v>60.36</v>
       </c>
       <c r="I58" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
@@ -3308,18 +3308,18 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>3.43</v>
+        <v>-0.01</v>
       </c>
       <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="n">
-        <v>1923271589</v>
+        <v>2091099618</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>BBAR</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3328,19 +3328,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.4478</v>
+        <v>0.0373</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>45853.65794861111</v>
+        <v>45945.66309922453</v>
       </c>
       <c r="G59" t="n">
-        <v>44.66</v>
+        <v>9.68</v>
       </c>
       <c r="H59" t="n">
-        <v>52</v>
+        <v>9.49</v>
       </c>
       <c r="I59" t="n">
-        <v>20</v>
+        <v>0.36</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
@@ -3357,18 +3357,18 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>3.29</v>
+        <v>-0.01</v>
       </c>
       <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="n">
-        <v>1869077178</v>
+        <v>1923271589</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3377,19 +3377,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>0.4478</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45819.67426902778</v>
+        <v>45853.65794861111</v>
       </c>
       <c r="G60" t="n">
-        <v>13.285</v>
+        <v>44.66</v>
       </c>
       <c r="H60" t="n">
-        <v>16.435</v>
+        <v>56.33</v>
       </c>
       <c r="I60" t="n">
-        <v>15.31</v>
+        <v>20</v>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
@@ -3406,18 +3406,18 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>3.89</v>
+        <v>5.22</v>
       </c>
       <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="n">
-        <v>1712850989</v>
+        <v>1653137218</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3426,19 +3426,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.0002</v>
+        <v>0.277</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>45734.85576775463</v>
+        <v>45699.85152199074</v>
       </c>
       <c r="G61" t="n">
-        <v>160.64</v>
+        <v>36.1</v>
       </c>
       <c r="H61" t="n">
-        <v>245.35</v>
+        <v>26.35</v>
       </c>
       <c r="I61" t="n">
-        <v>0.03</v>
+        <v>10</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
@@ -3455,18 +3455,18 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>0.02</v>
+        <v>-2.7</v>
       </c>
       <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="n">
-        <v>1867193336</v>
+        <v>1635194117</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3475,19 +3475,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>0.2479</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>45818.80084483796</v>
+        <v>45687.85228493056</v>
       </c>
       <c r="G62" t="n">
-        <v>17.64</v>
+        <v>40.33</v>
       </c>
       <c r="H62" t="n">
-        <v>20.97</v>
+        <v>26.35</v>
       </c>
       <c r="I62" t="n">
-        <v>17.64</v>
+        <v>10</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
@@ -3504,18 +3504,18 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>3.33</v>
+        <v>-3.47</v>
       </c>
       <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="n">
-        <v>1744916452</v>
+        <v>2091099733</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>BBAR</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3524,19 +3524,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.4245</v>
+        <v>1</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>45751.74230173611</v>
+        <v>45945.6631174537</v>
       </c>
       <c r="G63" t="n">
-        <v>17.54</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="H63" t="n">
-        <v>25.77</v>
+        <v>9.49</v>
       </c>
       <c r="I63" t="n">
-        <v>7.45</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
@@ -3553,18 +3553,18 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>3.49</v>
+        <v>-0.13</v>
       </c>
       <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="n">
-        <v>2035163256</v>
+        <v>2078838036</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BTCE.DE</t>
+          <t>JKS</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3573,19 +3573,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.0951</v>
+        <v>0.43</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>45919.66675122685</v>
+        <v>45940.66691300926</v>
       </c>
       <c r="G64" t="n">
-        <v>88.91</v>
+        <v>23.37</v>
       </c>
       <c r="H64" t="n">
-        <v>92.845</v>
+        <v>23.8</v>
       </c>
       <c r="I64" t="n">
-        <v>9.99</v>
+        <v>10.05</v>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
@@ -3602,18 +3602,18 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>0.32</v>
+        <v>0.18</v>
       </c>
       <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="n">
-        <v>2042867331</v>
+        <v>2065634230</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>JKS</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3622,19 +3622,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.3941</v>
+        <v>0.7849</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>45924.67994332176</v>
+        <v>45936.60990405093</v>
       </c>
       <c r="G65" t="n">
-        <v>25.37</v>
+        <v>16.28</v>
       </c>
       <c r="H65" t="n">
-        <v>24.6</v>
+        <v>15.685</v>
       </c>
       <c r="I65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
@@ -3651,18 +3651,18 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>-0.31</v>
+        <v>-0.71</v>
       </c>
       <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="n">
-        <v>1824482557</v>
+        <v>2035164705</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>PHGP.L</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3671,19 +3671,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.2641</v>
+        <v>0.032</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>45792.64805195602</v>
+        <v>45919.6670447338</v>
       </c>
       <c r="G66" t="n">
-        <v>56.78</v>
+        <v>252.81</v>
       </c>
       <c r="H66" t="n">
-        <v>65.70999999999999</v>
+        <v>295.87</v>
       </c>
       <c r="I66" t="n">
-        <v>15</v>
+        <v>10.97</v>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
@@ -3700,18 +3700,18 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>2.35</v>
+        <v>1.68</v>
       </c>
       <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="n">
-        <v>1680993370</v>
+        <v>2045989132</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3720,19 +3720,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>0.2034</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>45716.85638861111</v>
+        <v>45925.79891365741</v>
       </c>
       <c r="G67" t="n">
-        <v>44.49</v>
+        <v>49.16</v>
       </c>
       <c r="H67" t="n">
-        <v>54.78</v>
+        <v>47.7</v>
       </c>
       <c r="I67" t="n">
-        <v>44.49</v>
+        <v>10</v>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
@@ -3749,18 +3749,18 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>10.29</v>
+        <v>-0.3</v>
       </c>
       <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="n">
-        <v>1727574394</v>
+        <v>2047762608</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>BBAR</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3772,16 +3772,16 @@
         <v>1</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>45743.76658678241</v>
+        <v>45926.65281253472</v>
       </c>
       <c r="G68" t="n">
-        <v>21.13</v>
+        <v>9.27</v>
       </c>
       <c r="H68" t="n">
-        <v>17.37</v>
+        <v>9.49</v>
       </c>
       <c r="I68" t="n">
-        <v>21.13</v>
+        <v>9.27</v>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
@@ -3798,18 +3798,18 @@
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>-3.76</v>
+        <v>0.22</v>
       </c>
       <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="n">
-        <v>1666461140</v>
+        <v>2060645660</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3818,19 +3818,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.2651</v>
+        <v>0.1027</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>45708.68207092593</v>
+        <v>45932.90186543982</v>
       </c>
       <c r="G69" t="n">
-        <v>37.7</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>24.14</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>9.99</v>
+        <v>10.01</v>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
@@ -3847,18 +3847,18 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>-3.59</v>
+        <v>-0.13</v>
       </c>
       <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="n">
-        <v>1559803221</v>
+        <v>2017852950</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3867,19 +3867,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.092</v>
+        <v>1</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>45628.85951927083</v>
+        <v>45910.65507498843</v>
       </c>
       <c r="G70" t="n">
-        <v>162.85</v>
+        <v>37.44</v>
       </c>
       <c r="H70" t="n">
-        <v>141.96</v>
+        <v>49.16</v>
       </c>
       <c r="I70" t="n">
-        <v>14.98</v>
+        <v>37.44</v>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
@@ -3896,18 +3896,18 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>-1.92</v>
+        <v>11.72</v>
       </c>
       <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="n">
-        <v>2048501554</v>
+        <v>2029950407</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>JKS</t>
+          <t>PHGP.L</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3916,19 +3916,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.4118</v>
+        <v>0.1453</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>45926.83927949074</v>
+        <v>45917.66293982639</v>
       </c>
       <c r="G71" t="n">
-        <v>24.28</v>
+        <v>250.56</v>
       </c>
       <c r="H71" t="n">
-        <v>24.6</v>
+        <v>295.87</v>
       </c>
       <c r="I71" t="n">
-        <v>10</v>
+        <v>49.99</v>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
@@ -3945,18 +3945,18 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>0.13</v>
+        <v>7.45</v>
       </c>
       <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="n">
-        <v>1923259795</v>
+        <v>1631475148</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3965,19 +3965,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.4424</v>
+        <v>0.2592</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>45853.65609353009</v>
+        <v>45685.83625201389</v>
       </c>
       <c r="G72" t="n">
-        <v>22.59</v>
+        <v>38.58</v>
       </c>
       <c r="H72" t="n">
-        <v>25.77</v>
+        <v>26.35</v>
       </c>
       <c r="I72" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -3994,18 +3994,18 @@
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>1.41</v>
+        <v>-3.17</v>
       </c>
       <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="n">
-        <v>2017778050</v>
+        <v>1830410729</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4014,19 +4014,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.3611</v>
+        <v>0.1091</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45910.64665976852</v>
+        <v>45796.82476561343</v>
       </c>
       <c r="G73" t="n">
-        <v>27.91</v>
+        <v>33.66</v>
       </c>
       <c r="H73" t="n">
-        <v>24.14</v>
+        <v>31.67</v>
       </c>
       <c r="I73" t="n">
-        <v>10.08</v>
+        <v>3.67</v>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
@@ -4043,18 +4043,18 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>-1.36</v>
+        <v>-0.21</v>
       </c>
       <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="n">
-        <v>1867194722</v>
+        <v>1727591551</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>BND</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4066,16 +4066,16 @@
         <v>1</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45818.80135700232</v>
+        <v>45743.77389555555</v>
       </c>
       <c r="G74" t="n">
-        <v>21.27</v>
+        <v>72.87</v>
       </c>
       <c r="H74" t="n">
-        <v>17.37</v>
+        <v>74.97</v>
       </c>
       <c r="I74" t="n">
-        <v>21.27</v>
+        <v>72.87</v>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
@@ -4092,18 +4092,18 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>-3.9</v>
+        <v>2.1</v>
       </c>
       <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="n">
-        <v>2042979139</v>
+        <v>1744916497</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4112,19 +4112,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.3128</v>
+        <v>1</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>45924.70564383102</v>
+        <v>45751.74231563658</v>
       </c>
       <c r="G75" t="n">
-        <v>32</v>
+        <v>17.54</v>
       </c>
       <c r="H75" t="n">
-        <v>31.75</v>
+        <v>24.41</v>
       </c>
       <c r="I75" t="n">
-        <v>10.01</v>
+        <v>17.54</v>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
@@ -4141,18 +4141,18 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>-0.08</v>
+        <v>6.87</v>
       </c>
       <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="n">
-        <v>1582723120</v>
+        <v>1867193336</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4161,19 +4161,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.3755</v>
+        <v>1</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>45645.89511640046</v>
+        <v>45818.80084483796</v>
       </c>
       <c r="G76" t="n">
-        <v>53.26</v>
+        <v>17.64</v>
       </c>
       <c r="H76" t="n">
-        <v>65.70999999999999</v>
+        <v>19.95</v>
       </c>
       <c r="I76" t="n">
-        <v>20</v>
+        <v>17.64</v>
       </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
@@ -4190,18 +4190,18 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>4.67</v>
+        <v>2.31</v>
       </c>
       <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="n">
-        <v>2035164705</v>
+        <v>1986476926</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PHGP.L</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4210,19 +4210,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.032</v>
+        <v>1</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>45919.6670447338</v>
+        <v>45891.66490212963</v>
       </c>
       <c r="G77" t="n">
-        <v>252.81</v>
+        <v>34.44</v>
       </c>
       <c r="H77" t="n">
-        <v>268.4</v>
+        <v>49.16</v>
       </c>
       <c r="I77" t="n">
-        <v>10.97</v>
+        <v>34.44</v>
       </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
@@ -4239,18 +4239,18 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>0.55</v>
+        <v>14.72</v>
       </c>
       <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="n">
-        <v>1888700382</v>
+        <v>2091115227</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4259,19 +4259,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>0.376</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>45831.65144708334</v>
+        <v>45945.66604186343</v>
       </c>
       <c r="G78" t="n">
-        <v>47.58</v>
+        <v>26.59</v>
       </c>
       <c r="H78" t="n">
-        <v>54.78</v>
+        <v>26.35</v>
       </c>
       <c r="I78" t="n">
-        <v>47.58</v>
+        <v>10</v>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
@@ -4288,18 +4288,18 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>7.2</v>
+        <v>-0.09</v>
       </c>
       <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="n">
-        <v>1982273555</v>
+        <v>1563288050</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4308,19 +4308,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.0439</v>
+        <v>0.0626</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>45889.64957444445</v>
+        <v>45630.85583428241</v>
       </c>
       <c r="G79" t="n">
-        <v>228</v>
+        <v>159.74</v>
       </c>
       <c r="H79" t="n">
-        <v>292.04</v>
+        <v>152.68</v>
       </c>
       <c r="I79" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
@@ -4337,18 +4337,18 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>2.81</v>
+        <v>-0.44</v>
       </c>
       <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="n">
-        <v>1993382859</v>
+        <v>1806980496</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4357,19 +4357,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.0779</v>
+        <v>1</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>45896.66809304398</v>
+        <v>45783.83190503472</v>
       </c>
       <c r="G80" t="n">
-        <v>128.25</v>
+        <v>16.12</v>
       </c>
       <c r="H80" t="n">
-        <v>120.6</v>
+        <v>19.95</v>
       </c>
       <c r="I80" t="n">
-        <v>9.99</v>
+        <v>16.12</v>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
@@ -4386,18 +4386,18 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>-0.6</v>
+        <v>3.83</v>
       </c>
       <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="n">
-        <v>1970057305</v>
+        <v>2072487323</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4406,19 +4406,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.4062</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>45881.70511172454</v>
+        <v>45938.67565716435</v>
       </c>
       <c r="G81" t="n">
-        <v>35.88</v>
+        <v>24.64</v>
       </c>
       <c r="H81" t="n">
-        <v>40.46</v>
+        <v>22.87</v>
       </c>
       <c r="I81" t="n">
-        <v>2.57</v>
+        <v>10.01</v>
       </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
@@ -4435,18 +4435,18 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>0.32</v>
+        <v>-0.72</v>
       </c>
       <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="n">
-        <v>1880446729</v>
+        <v>2042867331</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>JKS</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4455,19 +4455,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.0772</v>
+        <v>0.3941</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>45825.89315055555</v>
+        <v>45924.67994332176</v>
       </c>
       <c r="G82" t="n">
-        <v>129.62</v>
+        <v>25.37</v>
       </c>
       <c r="H82" t="n">
-        <v>141.96</v>
+        <v>23.8</v>
       </c>
       <c r="I82" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
@@ -4484,18 +4484,18 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>0.95</v>
+        <v>-0.62</v>
       </c>
       <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="n">
-        <v>1796453499</v>
+        <v>2042971604</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4504,19 +4504,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.3901</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>45777.64668229167</v>
+        <v>45924.70406969907</v>
       </c>
       <c r="G83" t="n">
-        <v>15.57</v>
+        <v>25.66</v>
       </c>
       <c r="H83" t="n">
-        <v>20.97</v>
+        <v>22.87</v>
       </c>
       <c r="I83" t="n">
-        <v>8.01</v>
+        <v>10.01</v>
       </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
@@ -4533,18 +4533,18 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>2.78</v>
+        <v>-1.09</v>
       </c>
       <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="n">
-        <v>1806979127</v>
+        <v>1976499401</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4553,19 +4553,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.6361</v>
+        <v>0.8064</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>45783.83125244213</v>
+        <v>45884.83731814815</v>
       </c>
       <c r="G84" t="n">
-        <v>15.72</v>
+        <v>49.6</v>
       </c>
       <c r="H84" t="n">
-        <v>24.53</v>
+        <v>47.7</v>
       </c>
       <c r="I84" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
@@ -4582,18 +4582,18 @@
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>5.6</v>
+        <v>-1.53</v>
       </c>
       <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="n">
-        <v>2048539334</v>
+        <v>1997500170</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>JKS</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4602,19 +4602,19 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>0.4466</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>45926.85025574074</v>
+        <v>45898.65406594907</v>
       </c>
       <c r="G85" t="n">
-        <v>42.2</v>
+        <v>22.39</v>
       </c>
       <c r="H85" t="n">
-        <v>43.52</v>
+        <v>23.8</v>
       </c>
       <c r="I85" t="n">
-        <v>42.2</v>
+        <v>10</v>
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
@@ -4631,18 +4631,18 @@
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>1.32</v>
+        <v>0.63</v>
       </c>
       <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="n">
-        <v>2045991969</v>
+        <v>2080281129</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>JKS</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4651,19 +4651,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.4928</v>
+        <v>0.462</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>45925.80038483796</v>
+        <v>45940.89117050926</v>
       </c>
       <c r="G86" t="n">
-        <v>20.29</v>
+        <v>21.73</v>
       </c>
       <c r="H86" t="n">
-        <v>20.97</v>
+        <v>23.8</v>
       </c>
       <c r="I86" t="n">
-        <v>10</v>
+        <v>10.04</v>
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
@@ -4680,18 +4680,18 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>0.33</v>
+        <v>0.96</v>
       </c>
       <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="n">
-        <v>1923250768</v>
+        <v>1882283184</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4700,19 +4700,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.87</v>
+        <v>0.4835</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>45853.65447396991</v>
+        <v>45826.76569390047</v>
       </c>
       <c r="G87" t="n">
-        <v>12.76</v>
+        <v>20.69</v>
       </c>
       <c r="H87" t="n">
-        <v>16.435</v>
+        <v>23</v>
       </c>
       <c r="I87" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
@@ -4729,18 +4729,18 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>3.7</v>
+        <v>1.12</v>
       </c>
       <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="n">
-        <v>1895465445</v>
+        <v>1997498400</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4749,16 +4749,16 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.2987</v>
+        <v>0.0507</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>45834.6539484375</v>
+        <v>45898.65380736111</v>
       </c>
       <c r="G88" t="n">
-        <v>33.47</v>
+        <v>197.26</v>
       </c>
       <c r="H88" t="n">
-        <v>24.14</v>
+        <v>237.16</v>
       </c>
       <c r="I88" t="n">
         <v>10</v>
@@ -4778,18 +4778,18 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>-2.79</v>
+        <v>2.02</v>
       </c>
       <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="n">
-        <v>1845429956</v>
+        <v>1880443947</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4798,19 +4798,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.4821</v>
+        <v>0.1047</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>45805.66180811343</v>
+        <v>45825.891695625</v>
       </c>
       <c r="G89" t="n">
-        <v>13.275</v>
+        <v>142.99</v>
       </c>
       <c r="H89" t="n">
-        <v>16.435</v>
+        <v>237.16</v>
       </c>
       <c r="I89" t="n">
-        <v>7.28</v>
+        <v>14.97</v>
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
@@ -4827,18 +4827,18 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>1.98</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="n">
-        <v>2020498309</v>
+        <v>1843477272</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BBAR</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4847,19 +4847,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.0131</v>
+        <v>1</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>45911.68944190972</v>
+        <v>45804.66725678241</v>
       </c>
       <c r="G90" t="n">
-        <v>9.890000000000001</v>
+        <v>17.86</v>
       </c>
       <c r="H90" t="n">
-        <v>8.31</v>
+        <v>19.95</v>
       </c>
       <c r="I90" t="n">
-        <v>0.13</v>
+        <v>17.86</v>
       </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
@@ -4876,18 +4876,18 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>-0.02</v>
+        <v>2.09</v>
       </c>
       <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="n">
-        <v>1867196288</v>
+        <v>2066994664</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4896,19 +4896,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.067</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>45818.80209099537</v>
+        <v>45936.87431893519</v>
       </c>
       <c r="G91" t="n">
-        <v>41.99</v>
+        <v>149.19</v>
       </c>
       <c r="H91" t="n">
-        <v>52</v>
+        <v>143.25</v>
       </c>
       <c r="I91" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
@@ -4925,18 +4925,18 @@
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>5.96</v>
+        <v>-0.4</v>
       </c>
       <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="n">
-        <v>2027639997</v>
+        <v>1830408508</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4945,16 +4945,16 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.1558</v>
+        <v>0.5793</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>45916.65703747685</v>
+        <v>45796.82346997685</v>
       </c>
       <c r="G92" t="n">
-        <v>64.18000000000001</v>
+        <v>17.26</v>
       </c>
       <c r="H92" t="n">
-        <v>65.70999999999999</v>
+        <v>23</v>
       </c>
       <c r="I92" t="n">
         <v>10</v>
@@ -4974,18 +4974,18 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>0.24</v>
+        <v>3.32</v>
       </c>
       <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="n">
-        <v>1983186744</v>
+        <v>1923258184</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4994,19 +4994,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.3162</v>
+        <v>0.0298</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>45889.85904239583</v>
+        <v>45853.6557568287</v>
       </c>
       <c r="G93" t="n">
-        <v>31.61</v>
+        <v>19.43</v>
       </c>
       <c r="H93" t="n">
-        <v>24.14</v>
+        <v>23</v>
       </c>
       <c r="I93" t="n">
-        <v>10</v>
+        <v>0.58</v>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
@@ -5023,18 +5023,18 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>-2.37</v>
+        <v>0.11</v>
       </c>
       <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="n">
-        <v>1978489328</v>
+        <v>1666461140</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5043,19 +5043,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>0.2651</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>45887.6634622338</v>
+        <v>45708.68207092593</v>
       </c>
       <c r="G94" t="n">
-        <v>34.58</v>
+        <v>37.7</v>
       </c>
       <c r="H94" t="n">
-        <v>43.52</v>
+        <v>26.35</v>
       </c>
       <c r="I94" t="n">
-        <v>34.58</v>
+        <v>9.99</v>
       </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
@@ -5072,18 +5072,18 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>8.94</v>
+        <v>-3</v>
       </c>
       <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="n">
-        <v>1995249699</v>
+        <v>2078907475</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BTCE.DE</t>
+          <t>PHGP.L</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5092,19 +5092,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.4888</v>
+        <v>0.0537</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>45897.61086020833</v>
+        <v>45940.67644164352</v>
       </c>
       <c r="G95" t="n">
-        <v>87.16500000000001</v>
+        <v>278.84</v>
       </c>
       <c r="H95" t="n">
-        <v>92.845</v>
+        <v>295.87</v>
       </c>
       <c r="I95" t="n">
-        <v>49.99</v>
+        <v>19.99</v>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -5121,18 +5121,18 @@
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>3.03</v>
+        <v>1.24</v>
       </c>
       <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="n">
-        <v>1830410729</v>
+        <v>2080281858</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5141,19 +5141,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.1091</v>
+        <v>0.4547</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>45796.82476561343</v>
+        <v>45940.89146028935</v>
       </c>
       <c r="G96" t="n">
-        <v>33.66</v>
+        <v>21.99</v>
       </c>
       <c r="H96" t="n">
-        <v>31.75</v>
+        <v>23</v>
       </c>
       <c r="I96" t="n">
-        <v>3.67</v>
+        <v>10</v>
       </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
@@ -5170,14 +5170,14 @@
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>-0.21</v>
+        <v>0.46</v>
       </c>
       <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="n">
-        <v>1662993636</v>
+        <v>2045993574</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -5190,19 +5190,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>0.5753</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>45706.87026833333</v>
+        <v>45925.80108013889</v>
       </c>
       <c r="G97" t="n">
-        <v>20.65</v>
+        <v>17.38</v>
       </c>
       <c r="H97" t="n">
-        <v>17.37</v>
+        <v>19.24</v>
       </c>
       <c r="I97" t="n">
-        <v>20.65</v>
+        <v>10</v>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
@@ -5219,18 +5219,18 @@
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>-3.28</v>
+        <v>1.07</v>
       </c>
       <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="n">
-        <v>1806977521</v>
+        <v>2050990570</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>BLX</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5239,19 +5239,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.3367</v>
+        <v>0.2121</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>45783.8305750463</v>
+        <v>45929.65780017361</v>
       </c>
       <c r="G98" t="n">
-        <v>29.7</v>
+        <v>47</v>
       </c>
       <c r="H98" t="n">
-        <v>24.14</v>
+        <v>44.62</v>
       </c>
       <c r="I98" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
@@ -5268,18 +5268,18 @@
         <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>-1.87</v>
+        <v>-0.51</v>
       </c>
       <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="n">
-        <v>2050990570</v>
+        <v>1981010841</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BLX</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5288,19 +5288,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.2121</v>
+        <v>0.0425</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>45929.65780017361</v>
+        <v>45888.84617734954</v>
       </c>
       <c r="G99" t="n">
-        <v>47</v>
+        <v>235.53</v>
       </c>
       <c r="H99" t="n">
-        <v>44.99</v>
+        <v>300.11</v>
       </c>
       <c r="I99" t="n">
-        <v>9.970000000000001</v>
+        <v>10.01</v>
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
@@ -5317,18 +5317,18 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>-0.43</v>
+        <v>2.74</v>
       </c>
       <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="n">
-        <v>1883977044</v>
+        <v>1880442840</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5337,19 +5337,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.345</v>
+        <v>0.2535</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>45827.66105774305</v>
+        <v>45825.89113450232</v>
       </c>
       <c r="G100" t="n">
-        <v>12.88</v>
+        <v>59.15</v>
       </c>
       <c r="H100" t="n">
-        <v>16.435</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="I100" t="n">
-        <v>5.13</v>
+        <v>14.99</v>
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
@@ -5366,18 +5366,18 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="n">
-        <v>2050940197</v>
+        <v>1993382859</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5386,19 +5386,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.3238</v>
+        <v>0.0779</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>45929.65257815972</v>
+        <v>45896.66809304398</v>
       </c>
       <c r="G101" t="n">
-        <v>30.91</v>
+        <v>128.25</v>
       </c>
       <c r="H101" t="n">
-        <v>31.75</v>
+        <v>120.39</v>
       </c>
       <c r="I101" t="n">
-        <v>10.01</v>
+        <v>9.99</v>
       </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -5415,18 +5415,18 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>0.27</v>
+        <v>-0.61</v>
       </c>
       <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="n">
-        <v>1923256224</v>
+        <v>1754304266</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5435,19 +5435,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.7137</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>45853.65543140046</v>
+        <v>45755.88055112268</v>
       </c>
       <c r="G102" t="n">
-        <v>30.97</v>
+        <v>14</v>
       </c>
       <c r="H102" t="n">
-        <v>24.14</v>
+        <v>23</v>
       </c>
       <c r="I102" t="n">
-        <v>20</v>
+        <v>9.99</v>
       </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
@@ -5464,14 +5464,14 @@
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>-4.41</v>
+        <v>6.43</v>
       </c>
       <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="n">
-        <v>1923224670</v>
+        <v>1997561527</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -5484,19 +5484,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.2583</v>
+        <v>0.1498</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>45853.65359685185</v>
+        <v>45898.65748991898</v>
       </c>
       <c r="G103" t="n">
-        <v>58.05</v>
+        <v>66.73</v>
       </c>
       <c r="H103" t="n">
-        <v>65.70999999999999</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="I103" t="n">
-        <v>14.99</v>
+        <v>10</v>
       </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
@@ -5513,14 +5513,14 @@
         <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>1.98</v>
+        <v>-0.37</v>
       </c>
       <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="n">
-        <v>1880443947</v>
+        <v>1843469729</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -5533,19 +5533,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.1047</v>
+        <v>0.0423</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>45825.891695625</v>
+        <v>45804.66615450232</v>
       </c>
       <c r="G104" t="n">
-        <v>142.99</v>
+        <v>156.9</v>
       </c>
       <c r="H104" t="n">
-        <v>229.42</v>
+        <v>237.16</v>
       </c>
       <c r="I104" t="n">
-        <v>14.97</v>
+        <v>6.64</v>
       </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
@@ -5562,18 +5562,18 @@
         <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>9.050000000000001</v>
+        <v>3.39</v>
       </c>
       <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="n">
-        <v>1843477152</v>
+        <v>1867194722</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5582,19 +5582,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.1198</v>
+        <v>1</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>45804.66724922453</v>
+        <v>45818.80135700232</v>
       </c>
       <c r="G105" t="n">
-        <v>17.86</v>
+        <v>21.27</v>
       </c>
       <c r="H105" t="n">
-        <v>20.97</v>
+        <v>19.24</v>
       </c>
       <c r="I105" t="n">
-        <v>2.14</v>
+        <v>21.27</v>
       </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
@@ -5611,18 +5611,18 @@
         <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>0.37</v>
+        <v>-2.03</v>
       </c>
       <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="n">
-        <v>2002501482</v>
+        <v>1926287328</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5631,16 +5631,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.0526</v>
+        <v>0.5476</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>45902.65588916666</v>
+        <v>45854.82177967593</v>
       </c>
       <c r="G106" t="n">
-        <v>190.17</v>
+        <v>18.26</v>
       </c>
       <c r="H106" t="n">
-        <v>229.42</v>
+        <v>23</v>
       </c>
       <c r="I106" t="n">
         <v>10</v>
@@ -5660,18 +5660,18 @@
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>2.07</v>
+        <v>2.59</v>
       </c>
       <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="n">
-        <v>1867462173</v>
+        <v>1923259795</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5680,19 +5680,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.4424</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>45818.90866184028</v>
+        <v>45853.65609353009</v>
       </c>
       <c r="G107" t="n">
-        <v>77.93000000000001</v>
+        <v>22.59</v>
       </c>
       <c r="H107" t="n">
-        <v>97.70999999999999</v>
+        <v>24.41</v>
       </c>
       <c r="I107" t="n">
-        <v>0.65</v>
+        <v>9.99</v>
       </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
@@ -5709,18 +5709,18 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>0.17</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="n">
-        <v>2025662892</v>
+        <v>1642762235</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5729,16 +5729,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.8196</v>
+        <v>0.1572</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>45915.72913914352</v>
+        <v>45692.86612574074</v>
       </c>
       <c r="G108" t="n">
-        <v>24.39</v>
+        <v>127.16</v>
       </c>
       <c r="H108" t="n">
-        <v>24.73</v>
+        <v>120.39</v>
       </c>
       <c r="I108" t="n">
         <v>19.99</v>
@@ -5758,18 +5758,18 @@
         <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>0.28</v>
+        <v>-1.06</v>
       </c>
       <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="n">
-        <v>1358151307</v>
+        <v>2065642904</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>IAPD.AS</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5778,19 +5778,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.1081</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>45460.88529052083</v>
+        <v>45936.61247836806</v>
       </c>
       <c r="G109" t="n">
-        <v>165.93</v>
+        <v>22.935</v>
       </c>
       <c r="H109" t="n">
-        <v>141.96</v>
+        <v>23.005</v>
       </c>
       <c r="I109" t="n">
-        <v>17.94</v>
+        <v>15</v>
       </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
@@ -5807,18 +5807,18 @@
         <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>-2.58</v>
+        <v>-0.12</v>
       </c>
       <c r="Q109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="n">
-        <v>1972092684</v>
+        <v>2045990228</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5827,19 +5827,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1</v>
+        <v>0.0839</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>45882.68269449074</v>
+        <v>45925.79958348379</v>
       </c>
       <c r="G110" t="n">
-        <v>18.8</v>
+        <v>36.75</v>
       </c>
       <c r="H110" t="n">
-        <v>17.37</v>
+        <v>41.28</v>
       </c>
       <c r="I110" t="n">
-        <v>18.8</v>
+        <v>3.08</v>
       </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
@@ -5856,18 +5856,18 @@
         <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>-1.43</v>
+        <v>0.38</v>
       </c>
       <c r="Q110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="n">
-        <v>1997552824</v>
+        <v>1666459270</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5876,19 +5876,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.0429</v>
+        <v>0.5636</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>45898.65627293981</v>
+        <v>45708.68166530092</v>
       </c>
       <c r="G111" t="n">
-        <v>233.17</v>
+        <v>17.18</v>
       </c>
       <c r="H111" t="n">
-        <v>292.04</v>
+        <v>24.41</v>
       </c>
       <c r="I111" t="n">
-        <v>10</v>
+        <v>9.68</v>
       </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
@@ -5905,18 +5905,18 @@
         <v>0</v>
       </c>
       <c r="P111" t="n">
-        <v>2.53</v>
+        <v>4.08</v>
       </c>
       <c r="Q111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="n">
-        <v>1727591551</v>
+        <v>2047825292</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>BLX</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5925,19 +5925,19 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1</v>
+        <v>0.3157</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>45743.77389555555</v>
+        <v>45926.66222740741</v>
       </c>
       <c r="G112" t="n">
-        <v>72.87</v>
+        <v>47.56</v>
       </c>
       <c r="H112" t="n">
-        <v>74.29000000000001</v>
+        <v>44.62</v>
       </c>
       <c r="I112" t="n">
-        <v>72.87</v>
+        <v>15.01</v>
       </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
@@ -5954,18 +5954,18 @@
         <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>1.42</v>
+        <v>-0.92</v>
       </c>
       <c r="Q112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="n">
-        <v>1644796307</v>
+        <v>2066990620</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5974,19 +5974,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1</v>
+        <v>0.1541</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>45693.85501710648</v>
+        <v>45936.87171386574</v>
       </c>
       <c r="G113" t="n">
-        <v>20.36</v>
+        <v>64.88</v>
       </c>
       <c r="H113" t="n">
-        <v>17.37</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="I113" t="n">
-        <v>20.36</v>
+        <v>10</v>
       </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
@@ -6003,18 +6003,18 @@
         <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>-2.99</v>
+        <v>-0.1</v>
       </c>
       <c r="Q113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="n">
-        <v>1517510856</v>
+        <v>1824475555</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6023,19 +6023,19 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.0602</v>
+        <v>1</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>45597.61014849537</v>
+        <v>45792.64702015046</v>
       </c>
       <c r="G114" t="n">
-        <v>166.03</v>
+        <v>21.66</v>
       </c>
       <c r="H114" t="n">
-        <v>141.96</v>
+        <v>19.24</v>
       </c>
       <c r="I114" t="n">
-        <v>10</v>
+        <v>21.66</v>
       </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
@@ -6052,18 +6052,18 @@
         <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>-1.45</v>
+        <v>-2.42</v>
       </c>
       <c r="Q114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="n">
-        <v>2045993574</v>
+        <v>2020498309</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>BBAR</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6072,19 +6072,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.5753</v>
+        <v>0.0131</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>45925.80108013889</v>
+        <v>45911.68944190972</v>
       </c>
       <c r="G115" t="n">
-        <v>17.38</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="H115" t="n">
-        <v>17.37</v>
+        <v>9.49</v>
       </c>
       <c r="I115" t="n">
-        <v>10</v>
+        <v>0.13</v>
       </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
@@ -6108,11 +6108,11 @@
     <row r="116">
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="n">
-        <v>1923258249</v>
+        <v>2017778050</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6121,19 +6121,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1</v>
+        <v>0.3611</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>45853.65576626157</v>
+        <v>45910.64665976852</v>
       </c>
       <c r="G116" t="n">
-        <v>19.41</v>
+        <v>27.91</v>
       </c>
       <c r="H116" t="n">
-        <v>24.53</v>
+        <v>26.35</v>
       </c>
       <c r="I116" t="n">
-        <v>19.41</v>
+        <v>10.08</v>
       </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
@@ -6150,14 +6150,14 @@
         <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>5.12</v>
+        <v>-0.57</v>
       </c>
       <c r="Q116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="n">
-        <v>1599455288</v>
+        <v>1621495187</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -6170,19 +6170,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.2195</v>
+        <v>0.2318</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>45663.73750263889</v>
+        <v>45678.83178196759</v>
       </c>
       <c r="G117" t="n">
-        <v>45.55</v>
+        <v>43.27</v>
       </c>
       <c r="H117" t="n">
-        <v>24.14</v>
+        <v>26.35</v>
       </c>
       <c r="I117" t="n">
-        <v>10</v>
+        <v>10.03</v>
       </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
@@ -6199,18 +6199,18 @@
         <v>0</v>
       </c>
       <c r="P117" t="n">
-        <v>-4.7</v>
+        <v>-3.92</v>
       </c>
       <c r="Q117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="n">
-        <v>1867461578</v>
+        <v>1880441651</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>BAP</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6219,19 +6219,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.0023</v>
+        <v>1</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>45818.90835071759</v>
+        <v>45825.89055887731</v>
       </c>
       <c r="G118" t="n">
-        <v>216.54</v>
+        <v>21.21</v>
       </c>
       <c r="H118" t="n">
-        <v>266.11</v>
+        <v>19.24</v>
       </c>
       <c r="I118" t="n">
-        <v>0.5</v>
+        <v>21.21</v>
       </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
@@ -6248,18 +6248,18 @@
         <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>0.11</v>
+        <v>-1.97</v>
       </c>
       <c r="Q118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="n">
-        <v>1867193304</v>
+        <v>1989207013</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>JKS</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6268,19 +6268,19 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.1337</v>
+        <v>0.4133</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>45818.8008296412</v>
+        <v>45894.65354606482</v>
       </c>
       <c r="G119" t="n">
-        <v>17.64</v>
+        <v>24.19</v>
       </c>
       <c r="H119" t="n">
-        <v>20.97</v>
+        <v>23.8</v>
       </c>
       <c r="I119" t="n">
-        <v>2.36</v>
+        <v>10</v>
       </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
@@ -6297,18 +6297,18 @@
         <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>0.44</v>
+        <v>-0.16</v>
       </c>
       <c r="Q119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="n">
-        <v>2002503461</v>
+        <v>2091302201</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6317,19 +6317,19 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.0439</v>
+        <v>0.099</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>45902.65623520833</v>
+        <v>45945.68849447917</v>
       </c>
       <c r="G120" t="n">
-        <v>227.95</v>
+        <v>86.41</v>
       </c>
       <c r="H120" t="n">
-        <v>292.04</v>
+        <v>84.605</v>
       </c>
       <c r="I120" t="n">
-        <v>10.01</v>
+        <v>9.99</v>
       </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
@@ -6346,18 +6346,18 @@
         <v>0</v>
       </c>
       <c r="P120" t="n">
-        <v>2.81</v>
+        <v>-0.27</v>
       </c>
       <c r="Q120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="n">
-        <v>2025661832</v>
+        <v>1869077157</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6366,19 +6366,19 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.3235</v>
+        <v>0.3061</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>45915.72870862269</v>
+        <v>45819.6742621412</v>
       </c>
       <c r="G121" t="n">
-        <v>61.81</v>
+        <v>13.285</v>
       </c>
       <c r="H121" t="n">
-        <v>59.61</v>
+        <v>15.685</v>
       </c>
       <c r="I121" t="n">
-        <v>20</v>
+        <v>4.69</v>
       </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
@@ -6395,18 +6395,18 @@
         <v>0</v>
       </c>
       <c r="P121" t="n">
-        <v>-0.72</v>
+        <v>0.88</v>
       </c>
       <c r="Q121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="n">
-        <v>2042956616</v>
+        <v>1867193304</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6415,19 +6415,19 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.1592</v>
+        <v>0.1337</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>45924.69943638889</v>
+        <v>45818.8008296412</v>
       </c>
       <c r="G122" t="n">
-        <v>62.88</v>
+        <v>17.64</v>
       </c>
       <c r="H122" t="n">
-        <v>59.61</v>
+        <v>19.95</v>
       </c>
       <c r="I122" t="n">
-        <v>10.01</v>
+        <v>2.36</v>
       </c>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
@@ -6444,18 +6444,18 @@
         <v>0</v>
       </c>
       <c r="P122" t="n">
-        <v>-0.52</v>
+        <v>0.31</v>
       </c>
       <c r="Q122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="n">
-        <v>1978487977</v>
+        <v>1923246263</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6464,19 +6464,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.07870000000000001</v>
+        <v>1</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>45887.66311905093</v>
+        <v>45853.6538128125</v>
       </c>
       <c r="G123" t="n">
-        <v>127.06</v>
+        <v>21.17</v>
       </c>
       <c r="H123" t="n">
-        <v>120.6</v>
+        <v>19.24</v>
       </c>
       <c r="I123" t="n">
-        <v>10</v>
+        <v>21.17</v>
       </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
@@ -6493,18 +6493,18 @@
         <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>-0.51</v>
+        <v>-1.93</v>
       </c>
       <c r="Q123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="n">
-        <v>1744916497</v>
+        <v>1559803221</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6513,19 +6513,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1</v>
+        <v>0.092</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>45751.74231563658</v>
+        <v>45628.85951927083</v>
       </c>
       <c r="G124" t="n">
-        <v>17.54</v>
+        <v>162.85</v>
       </c>
       <c r="H124" t="n">
-        <v>25.77</v>
+        <v>152.68</v>
       </c>
       <c r="I124" t="n">
-        <v>17.54</v>
+        <v>14.98</v>
       </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
@@ -6542,18 +6542,18 @@
         <v>0</v>
       </c>
       <c r="P124" t="n">
-        <v>8.23</v>
+        <v>-0.93</v>
       </c>
       <c r="Q124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="n">
-        <v>1727563010</v>
+        <v>1644788775</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6562,19 +6562,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>45743.76106726852</v>
+        <v>45693.85093391204</v>
       </c>
       <c r="G125" t="n">
-        <v>46.11</v>
+        <v>144.94</v>
       </c>
       <c r="H125" t="n">
-        <v>54.78</v>
+        <v>152.68</v>
       </c>
       <c r="I125" t="n">
-        <v>46.11</v>
+        <v>10.99</v>
       </c>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
@@ -6591,18 +6591,18 @@
         <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>8.67</v>
+        <v>0.58</v>
       </c>
       <c r="Q125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="n">
-        <v>1997500170</v>
+        <v>2091093343</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>JKS</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6611,16 +6611,16 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.4466</v>
+        <v>0.2366</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>45898.65406594907</v>
+        <v>45945.66190688658</v>
       </c>
       <c r="G126" t="n">
-        <v>22.39</v>
+        <v>42.25</v>
       </c>
       <c r="H126" t="n">
-        <v>24.6</v>
+        <v>41.02</v>
       </c>
       <c r="I126" t="n">
         <v>10</v>
@@ -6640,18 +6640,18 @@
         <v>0</v>
       </c>
       <c r="P126" t="n">
-        <v>0.99</v>
+        <v>-0.29</v>
       </c>
       <c r="Q126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="n">
-        <v>1744929368</v>
+        <v>2072501999</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6660,19 +6660,19 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.0192</v>
+        <v>0.0121</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>45751.74500871528</v>
+        <v>45938.67873797454</v>
       </c>
       <c r="G127" t="n">
-        <v>324.48</v>
+        <v>844.9</v>
       </c>
       <c r="H127" t="n">
-        <v>349.84</v>
+        <v>877.2</v>
       </c>
       <c r="I127" t="n">
-        <v>6.23</v>
+        <v>11.95</v>
       </c>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
@@ -6689,14 +6689,14 @@
         <v>0</v>
       </c>
       <c r="P127" t="n">
-        <v>0.49</v>
+        <v>0.37</v>
       </c>
       <c r="Q127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="n">
-        <v>1806980496</v>
+        <v>2045991969</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -6709,19 +6709,19 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1</v>
+        <v>0.4928</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>45783.83190503472</v>
+        <v>45925.80038483796</v>
       </c>
       <c r="G128" t="n">
-        <v>16.12</v>
+        <v>20.29</v>
       </c>
       <c r="H128" t="n">
-        <v>20.97</v>
+        <v>19.95</v>
       </c>
       <c r="I128" t="n">
-        <v>16.12</v>
+        <v>10</v>
       </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
@@ -6738,18 +6738,18 @@
         <v>0</v>
       </c>
       <c r="P128" t="n">
-        <v>4.85</v>
+        <v>-0.17</v>
       </c>
       <c r="Q128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="n">
-        <v>2060617471</v>
+        <v>1680993370</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6758,19 +6758,19 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.2255</v>
+        <v>1</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>45932.89647650463</v>
+        <v>45716.85638861111</v>
       </c>
       <c r="G129" t="n">
-        <v>44.35</v>
+        <v>44.49</v>
       </c>
       <c r="H129" t="n">
-        <v>44.83</v>
+        <v>54.52</v>
       </c>
       <c r="I129" t="n">
-        <v>10</v>
+        <v>44.49</v>
       </c>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
@@ -6787,18 +6787,18 @@
         <v>0</v>
       </c>
       <c r="P129" t="n">
-        <v>0.11</v>
+        <v>10.03</v>
       </c>
       <c r="Q129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="n">
-        <v>2060624552</v>
+        <v>2050940197</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6807,16 +6807,16 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.1676</v>
+        <v>0.3238</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>45932.90130990741</v>
+        <v>45929.65257815972</v>
       </c>
       <c r="G130" t="n">
-        <v>59.7</v>
+        <v>30.91</v>
       </c>
       <c r="H130" t="n">
-        <v>59.61</v>
+        <v>31.67</v>
       </c>
       <c r="I130" t="n">
         <v>10.01</v>
@@ -6836,18 +6836,18 @@
         <v>0</v>
       </c>
       <c r="P130" t="n">
-        <v>-0.02</v>
+        <v>0.24</v>
       </c>
       <c r="Q130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="n">
-        <v>1880442840</v>
+        <v>2066988146</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6856,19 +6856,19 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.2535</v>
+        <v>0.102</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>45825.89113450232</v>
+        <v>45936.870276875</v>
       </c>
       <c r="G131" t="n">
-        <v>59.15</v>
+        <v>98.06</v>
       </c>
       <c r="H131" t="n">
-        <v>65.70999999999999</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="I131" t="n">
-        <v>14.99</v>
+        <v>10</v>
       </c>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
@@ -6885,18 +6885,18 @@
         <v>0</v>
       </c>
       <c r="P131" t="n">
-        <v>1.67</v>
+        <v>-0.19</v>
       </c>
       <c r="Q131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="n">
-        <v>2045990228</v>
+        <v>2020498366</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>BBAR</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6905,19 +6905,19 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.2718</v>
+        <v>1</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>45925.79958348379</v>
+        <v>45911.68945292824</v>
       </c>
       <c r="G132" t="n">
-        <v>36.75</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="H132" t="n">
-        <v>40.46</v>
+        <v>9.49</v>
       </c>
       <c r="I132" t="n">
-        <v>9.99</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
@@ -6934,18 +6934,18 @@
         <v>0</v>
       </c>
       <c r="P132" t="n">
-        <v>1.01</v>
+        <v>-0.39</v>
       </c>
       <c r="Q132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="n">
-        <v>1867197360</v>
+        <v>2027639997</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6954,19 +6954,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.0765</v>
+        <v>0.1558</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>45818.80265583334</v>
+        <v>45916.65703747685</v>
       </c>
       <c r="G133" t="n">
-        <v>131.96</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="H133" t="n">
-        <v>141.96</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="I133" t="n">
-        <v>10.09</v>
+        <v>10</v>
       </c>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
@@ -6983,18 +6983,18 @@
         <v>0</v>
       </c>
       <c r="P133" t="n">
-        <v>0.77</v>
+        <v>0.01</v>
       </c>
       <c r="Q133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="n">
-        <v>2020498366</v>
+        <v>1358151307</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>BBAR</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -7003,19 +7003,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1</v>
+        <v>0.1081</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>45911.68945292824</v>
+        <v>45460.88529052083</v>
       </c>
       <c r="G134" t="n">
-        <v>9.880000000000001</v>
+        <v>165.93</v>
       </c>
       <c r="H134" t="n">
-        <v>8.31</v>
+        <v>152.68</v>
       </c>
       <c r="I134" t="n">
-        <v>9.880000000000001</v>
+        <v>17.94</v>
       </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
@@ -7032,18 +7032,18 @@
         <v>0</v>
       </c>
       <c r="P134" t="n">
-        <v>-1.57</v>
+        <v>-1.43</v>
       </c>
       <c r="Q134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="n">
-        <v>1563288050</v>
+        <v>2091123728</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>SQM</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7052,19 +7052,19 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.0626</v>
+        <v>0.4406</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>45630.85583428241</v>
+        <v>45945.66748809028</v>
       </c>
       <c r="G135" t="n">
-        <v>159.74</v>
+        <v>45.28</v>
       </c>
       <c r="H135" t="n">
-        <v>141.96</v>
+        <v>44.38</v>
       </c>
       <c r="I135" t="n">
-        <v>10</v>
+        <v>19.95</v>
       </c>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
@@ -7081,18 +7081,18 @@
         <v>0</v>
       </c>
       <c r="P135" t="n">
-        <v>-1.11</v>
+        <v>-0.4</v>
       </c>
       <c r="Q135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="n">
-        <v>1666459270</v>
+        <v>1883977086</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7101,19 +7101,19 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.5636</v>
+        <v>1</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>45708.68166530092</v>
+        <v>45827.66106613426</v>
       </c>
       <c r="G136" t="n">
-        <v>17.18</v>
+        <v>12.875</v>
       </c>
       <c r="H136" t="n">
-        <v>25.77</v>
+        <v>15.685</v>
       </c>
       <c r="I136" t="n">
-        <v>9.68</v>
+        <v>14.86</v>
       </c>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
@@ -7130,18 +7130,18 @@
         <v>0</v>
       </c>
       <c r="P136" t="n">
-        <v>4.84</v>
+        <v>3.35</v>
       </c>
       <c r="Q136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="n">
-        <v>1984829391</v>
+        <v>1993444707</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>BBAR</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7150,19 +7150,19 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.0512</v>
+        <v>0.8051</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>45890.71798858796</v>
+        <v>45896.6743321875</v>
       </c>
       <c r="G137" t="n">
-        <v>195.52</v>
+        <v>12.42</v>
       </c>
       <c r="H137" t="n">
-        <v>229.42</v>
+        <v>9.49</v>
       </c>
       <c r="I137" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
@@ -7179,18 +7179,18 @@
         <v>0</v>
       </c>
       <c r="P137" t="n">
-        <v>1.74</v>
+        <v>-2.36</v>
       </c>
       <c r="Q137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="n">
-        <v>1975988073</v>
+        <v>2066989908</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7199,19 +7199,19 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.0469</v>
+        <v>0.3946</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>45884.6572796875</v>
+        <v>45936.87125002315</v>
       </c>
       <c r="G138" t="n">
-        <v>319.83</v>
+        <v>25.34</v>
       </c>
       <c r="H138" t="n">
-        <v>379.97</v>
+        <v>24.41</v>
       </c>
       <c r="I138" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
@@ -7228,18 +7228,18 @@
         <v>0</v>
       </c>
       <c r="P138" t="n">
-        <v>2.82</v>
+        <v>-0.37</v>
       </c>
       <c r="Q138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="n">
-        <v>1989207013</v>
+        <v>1888686062</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>JKS</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7248,19 +7248,19 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.4133</v>
+        <v>0.2903</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>45894.65354606482</v>
+        <v>45831.64964792824</v>
       </c>
       <c r="G139" t="n">
-        <v>24.19</v>
+        <v>34.36</v>
       </c>
       <c r="H139" t="n">
-        <v>24.6</v>
+        <v>26.35</v>
       </c>
       <c r="I139" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
@@ -7277,18 +7277,18 @@
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>0.17</v>
+        <v>-2.32</v>
       </c>
       <c r="Q139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="n">
-        <v>1744767540</v>
+        <v>1867458993</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7297,19 +7297,19 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.643</v>
+        <v>0.3417</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>45751.72316712963</v>
+        <v>45818.90699613426</v>
       </c>
       <c r="G140" t="n">
-        <v>15.55</v>
+        <v>58.53</v>
       </c>
       <c r="H140" t="n">
-        <v>24.53</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="I140" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
@@ -7326,14 +7326,14 @@
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>5.77</v>
+        <v>1.96</v>
       </c>
       <c r="Q140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="n">
-        <v>1635194117</v>
+        <v>1983186744</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -7346,16 +7346,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.2479</v>
+        <v>0.3162</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>45687.85228493056</v>
+        <v>45889.85904239583</v>
       </c>
       <c r="G141" t="n">
-        <v>40.33</v>
+        <v>31.61</v>
       </c>
       <c r="H141" t="n">
-        <v>24.14</v>
+        <v>26.35</v>
       </c>
       <c r="I141" t="n">
         <v>10</v>
@@ -7375,18 +7375,18 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>-4.02</v>
+        <v>-1.67</v>
       </c>
       <c r="Q141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="n">
-        <v>1888686062</v>
+        <v>1923250768</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7395,19 +7395,19 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.2903</v>
+        <v>0.87</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>45831.64964792824</v>
+        <v>45853.65447396991</v>
       </c>
       <c r="G142" t="n">
-        <v>34.36</v>
+        <v>12.76</v>
       </c>
       <c r="H142" t="n">
-        <v>24.14</v>
+        <v>15.685</v>
       </c>
       <c r="I142" t="n">
-        <v>9.970000000000001</v>
+        <v>13</v>
       </c>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
@@ -7424,18 +7424,18 @@
         <v>0</v>
       </c>
       <c r="P142" t="n">
-        <v>-2.96</v>
+        <v>2.84</v>
       </c>
       <c r="Q142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="n">
-        <v>1648737122</v>
+        <v>1796453499</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -7444,19 +7444,19 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.001</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>45695.85619950231</v>
+        <v>45777.64668229167</v>
       </c>
       <c r="G143" t="n">
-        <v>408.33</v>
+        <v>15.57</v>
       </c>
       <c r="H143" t="n">
-        <v>517.23</v>
+        <v>19.95</v>
       </c>
       <c r="I143" t="n">
-        <v>0.41</v>
+        <v>8.01</v>
       </c>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
@@ -7473,18 +7473,18 @@
         <v>0</v>
       </c>
       <c r="P143" t="n">
-        <v>0.11</v>
+        <v>2.26</v>
       </c>
       <c r="Q143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="n">
-        <v>2050937088</v>
+        <v>2079414382</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>BTCE.DE</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7493,19 +7493,19 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.0984</v>
+        <v>0.0351</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>45929.65204666667</v>
+        <v>45940.73297075232</v>
       </c>
       <c r="G144" t="n">
-        <v>86.06999999999999</v>
+        <v>285.2</v>
       </c>
       <c r="H144" t="n">
-        <v>92.845</v>
+        <v>300.11</v>
       </c>
       <c r="I144" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
@@ -7522,18 +7522,18 @@
         <v>0</v>
       </c>
       <c r="P144" t="n">
-        <v>0.67</v>
+        <v>0.52</v>
       </c>
       <c r="Q144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="n">
-        <v>2047758738</v>
+        <v>2050937088</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -7542,19 +7542,19 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.0365</v>
+        <v>0.0984</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>45926.65183609954</v>
+        <v>45929.65204666667</v>
       </c>
       <c r="G145" t="n">
-        <v>274.22</v>
+        <v>86.06999999999999</v>
       </c>
       <c r="H145" t="n">
-        <v>292.04</v>
+        <v>84.605</v>
       </c>
       <c r="I145" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
@@ -7571,18 +7571,18 @@
         <v>0</v>
       </c>
       <c r="P145" t="n">
-        <v>0.65</v>
+        <v>-0.34</v>
       </c>
       <c r="Q145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="n">
-        <v>1928218937</v>
+        <v>2048539334</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7594,16 +7594,16 @@
         <v>1</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>45855.75970359953</v>
+        <v>45926.85025574074</v>
       </c>
       <c r="G146" t="n">
-        <v>20.24</v>
+        <v>42.2</v>
       </c>
       <c r="H146" t="n">
-        <v>17.37</v>
+        <v>49.16</v>
       </c>
       <c r="I146" t="n">
-        <v>20.24</v>
+        <v>42.2</v>
       </c>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
@@ -7620,27 +7620,45 @@
         <v>0</v>
       </c>
       <c r="P146" t="n">
-        <v>-2.87</v>
+        <v>6.96</v>
       </c>
       <c r="Q146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr"/>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
+      <c r="B147" t="n">
+        <v>1824482557</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>0.2641</v>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>45792.64805195602</v>
+      </c>
+      <c r="G147" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="H147" t="n">
+        <v>64.26000000000001</v>
+      </c>
+      <c r="I147" t="n">
+        <v>15</v>
+      </c>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
       <c r="M147" t="n">
         <v>0</v>
       </c>
@@ -7651,9 +7669,824 @@
         <v>0</v>
       </c>
       <c r="P147" t="n">
-        <v>166.02</v>
+        <v>1.97</v>
       </c>
       <c r="Q147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr"/>
+      <c r="B148" t="n">
+        <v>1744767540</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>45751.72316712963</v>
+      </c>
+      <c r="G148" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="H148" t="n">
+        <v>23</v>
+      </c>
+      <c r="I148" t="n">
+        <v>10</v>
+      </c>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="Q148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr"/>
+      <c r="B149" t="n">
+        <v>2002501482</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>FSLR</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>45902.65588916666</v>
+      </c>
+      <c r="G149" t="n">
+        <v>190.17</v>
+      </c>
+      <c r="H149" t="n">
+        <v>237.16</v>
+      </c>
+      <c r="I149" t="n">
+        <v>10</v>
+      </c>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+      <c r="B150" t="n">
+        <v>2002503461</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>0.0439</v>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>45902.65623520833</v>
+      </c>
+      <c r="G150" t="n">
+        <v>227.95</v>
+      </c>
+      <c r="H150" t="n">
+        <v>300.11</v>
+      </c>
+      <c r="I150" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="Q150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+      <c r="B151" t="n">
+        <v>1727574394</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>ACI</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>1</v>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>45743.76658678241</v>
+      </c>
+      <c r="G151" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="H151" t="n">
+        <v>19.24</v>
+      </c>
+      <c r="I151" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="Q151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr"/>
+      <c r="B152" t="n">
+        <v>1843474191</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>ING</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>0.9372</v>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>45804.66699503472</v>
+      </c>
+      <c r="G152" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="H152" t="n">
+        <v>24.41</v>
+      </c>
+      <c r="I152" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" t="n">
+        <v>0</v>
+      </c>
+      <c r="N152" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Q152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="n">
+        <v>1928218937</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>ACI</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>1</v>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>45855.75970359953</v>
+      </c>
+      <c r="G153" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="H153" t="n">
+        <v>19.24</v>
+      </c>
+      <c r="I153" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" t="n">
+        <v>1895465445</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>YPF</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>45834.6539484375</v>
+      </c>
+      <c r="G154" t="n">
+        <v>33.47</v>
+      </c>
+      <c r="H154" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="I154" t="n">
+        <v>10</v>
+      </c>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="Q154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="n">
+        <v>1923256224</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>YPF</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>0.6457000000000001</v>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>45853.65543140046</v>
+      </c>
+      <c r="G155" t="n">
+        <v>30.97</v>
+      </c>
+      <c r="H155" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="I155" t="n">
+        <v>20</v>
+      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" t="n">
+        <v>0</v>
+      </c>
+      <c r="N155" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="n">
+        <v>-2.99</v>
+      </c>
+      <c r="Q155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="n">
+        <v>1806979127</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>0.6361</v>
+      </c>
+      <c r="F156" s="2" t="n">
+        <v>45783.83125244213</v>
+      </c>
+      <c r="G156" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="H156" t="n">
+        <v>23</v>
+      </c>
+      <c r="I156" t="n">
+        <v>10</v>
+      </c>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="Q156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="n">
+        <v>2065818035</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>JKS</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>0.3984</v>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>45936.64826241898</v>
+      </c>
+      <c r="G157" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="H157" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="I157" t="n">
+        <v>10</v>
+      </c>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="Q157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" t="n">
+        <v>1867196288</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>0.5568</v>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>45818.80209099537</v>
+      </c>
+      <c r="G158" t="n">
+        <v>41.99</v>
+      </c>
+      <c r="H158" t="n">
+        <v>56.33</v>
+      </c>
+      <c r="I158" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="Q158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="n">
+        <v>2060620530</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>BLX</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>0.2207</v>
+      </c>
+      <c r="F159" s="2" t="n">
+        <v>45932.89856876157</v>
+      </c>
+      <c r="G159" t="n">
+        <v>45.28</v>
+      </c>
+      <c r="H159" t="n">
+        <v>44.62</v>
+      </c>
+      <c r="I159" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="Q159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="n">
+        <v>2048501554</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>JKS</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>0.4118</v>
+      </c>
+      <c r="F160" s="2" t="n">
+        <v>45926.83927949074</v>
+      </c>
+      <c r="G160" t="n">
+        <v>24.28</v>
+      </c>
+      <c r="H160" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="I160" t="n">
+        <v>10</v>
+      </c>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="Q160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="n">
+        <v>2047758738</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>0.0365</v>
+      </c>
+      <c r="F161" s="2" t="n">
+        <v>45926.65183609954</v>
+      </c>
+      <c r="G161" t="n">
+        <v>274.22</v>
+      </c>
+      <c r="H161" t="n">
+        <v>300.11</v>
+      </c>
+      <c r="I161" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="Q161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="n">
+        <v>1824476420</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>0.1548</v>
+      </c>
+      <c r="F162" s="2" t="n">
+        <v>45792.64714148148</v>
+      </c>
+      <c r="G162" t="n">
+        <v>129.17</v>
+      </c>
+      <c r="H162" t="n">
+        <v>152.68</v>
+      </c>
+      <c r="I162" t="n">
+        <v>20</v>
+      </c>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="Q162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="n">
+        <v>2095264263</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>SQM</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>0.2252</v>
+      </c>
+      <c r="F163" s="2" t="n">
+        <v>45946.74280237268</v>
+      </c>
+      <c r="G163" t="n">
+        <v>44.39</v>
+      </c>
+      <c r="H163" t="n">
+        <v>44.38</v>
+      </c>
+      <c r="I163" t="n">
+        <v>10</v>
+      </c>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="Q163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="n">
+        <v>158.27</v>
+      </c>
+      <c r="Q164" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Stock Selection/OPEN POSITION.xlsx
+++ b/Stock Selection/OPEN POSITION.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q164"/>
+  <dimension ref="A1:Q166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,11 +522,11 @@
     <row r="2">
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="n">
-        <v>2025662892</v>
+        <v>1883977044</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.8196</v>
+        <v>0.345</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45915.72913914352</v>
+        <v>45827.66105774305</v>
       </c>
       <c r="G2" t="n">
-        <v>24.39</v>
+        <v>12.88</v>
       </c>
       <c r="H2" t="n">
-        <v>22.87</v>
+        <v>16.645</v>
       </c>
       <c r="I2" t="n">
-        <v>19.99</v>
+        <v>5.13</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -564,18 +564,18 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.25</v>
+        <v>1.54</v>
       </c>
       <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="n">
-        <v>1461331124</v>
+        <v>1882283184</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -584,19 +584,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.3752</v>
+        <v>0.4835</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45553.65374138889</v>
+        <v>45826.76569390047</v>
       </c>
       <c r="G3" t="n">
-        <v>50.99</v>
+        <v>20.69</v>
       </c>
       <c r="H3" t="n">
-        <v>64.26000000000001</v>
+        <v>22.51</v>
       </c>
       <c r="I3" t="n">
-        <v>19.13</v>
+        <v>10</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -613,18 +613,18 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.98</v>
+        <v>0.88</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="n">
-        <v>1599431096</v>
+        <v>2091105918</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>IAPD.AS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -633,19 +633,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1013</v>
+        <v>0.5535</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45663.73014731482</v>
+        <v>45945.66408168981</v>
       </c>
       <c r="G4" t="n">
-        <v>148.02</v>
+        <v>23.185</v>
       </c>
       <c r="H4" t="n">
-        <v>152.68</v>
+        <v>22.975</v>
       </c>
       <c r="I4" t="n">
-        <v>14.99</v>
+        <v>15</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -662,18 +662,18 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.48</v>
+        <v>-0.23</v>
       </c>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="n">
-        <v>2091063412</v>
+        <v>1986476926</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4089</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45945.66023149306</v>
+        <v>45891.66490212963</v>
       </c>
       <c r="G5" t="n">
-        <v>24.44</v>
+        <v>34.44</v>
       </c>
       <c r="H5" t="n">
-        <v>24.41</v>
+        <v>46.95</v>
       </c>
       <c r="I5" t="n">
-        <v>9.99</v>
+        <v>34.44</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -711,18 +711,18 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.01</v>
+        <v>12.51</v>
       </c>
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="n">
-        <v>1754302454</v>
+        <v>1843477152</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.3673</v>
+        <v>0.1198</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45755.88025324074</v>
+        <v>45804.66724922453</v>
       </c>
       <c r="G6" t="n">
-        <v>27.17</v>
+        <v>17.86</v>
       </c>
       <c r="H6" t="n">
-        <v>26.35</v>
+        <v>19.34</v>
       </c>
       <c r="I6" t="n">
-        <v>9.98</v>
+        <v>2.14</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -760,18 +760,18 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3</v>
+        <v>0.18</v>
       </c>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="n">
-        <v>1995249699</v>
+        <v>1993444707</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BTCE.DE</t>
+          <t>BBAR</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -780,19 +780,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.3888</v>
+        <v>0.8051</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45897.61086020833</v>
+        <v>45896.6743321875</v>
       </c>
       <c r="G7" t="n">
-        <v>87.16500000000001</v>
+        <v>12.42</v>
       </c>
       <c r="H7" t="n">
-        <v>84.605</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>39.77</v>
+        <v>10</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -809,18 +809,18 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.57</v>
+        <v>-2.45</v>
       </c>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>1845429980</v>
+        <v>1867458993</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0.3417</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45805.66181400463</v>
+        <v>45818.90699613426</v>
       </c>
       <c r="G8" t="n">
-        <v>13.27</v>
+        <v>58.53</v>
       </c>
       <c r="H8" t="n">
-        <v>15.685</v>
+        <v>65</v>
       </c>
       <c r="I8" t="n">
-        <v>15.09</v>
+        <v>20</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -858,18 +858,18 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.12</v>
+        <v>2.21</v>
       </c>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>1869077178</v>
+        <v>2065818035</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>JKS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -878,19 +878,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0.3984</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45819.67426902778</v>
+        <v>45936.64826241898</v>
       </c>
       <c r="G9" t="n">
-        <v>13.285</v>
+        <v>25.1</v>
       </c>
       <c r="H9" t="n">
-        <v>15.685</v>
+        <v>23.11</v>
       </c>
       <c r="I9" t="n">
-        <v>15.31</v>
+        <v>10</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -907,18 +907,18 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.9</v>
+        <v>-0.79</v>
       </c>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
-        <v>1923258249</v>
+        <v>1644796307</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -930,16 +930,16 @@
         <v>1</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45853.65576626157</v>
+        <v>45693.85501710648</v>
       </c>
       <c r="G10" t="n">
-        <v>19.41</v>
+        <v>20.36</v>
       </c>
       <c r="H10" t="n">
-        <v>23</v>
+        <v>19.75</v>
       </c>
       <c r="I10" t="n">
-        <v>19.41</v>
+        <v>20.36</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -956,18 +956,18 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>3.59</v>
+        <v>-0.61</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
-        <v>1517510856</v>
+        <v>2091064900</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -976,19 +976,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.0602</v>
+        <v>0.4294</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45597.61014849537</v>
+        <v>45945.66049490741</v>
       </c>
       <c r="G11" t="n">
-        <v>166.03</v>
+        <v>23.32</v>
       </c>
       <c r="H11" t="n">
-        <v>152.68</v>
+        <v>23.11</v>
       </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -1005,18 +1005,18 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>1806977521</v>
+        <v>1701100027</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1025,19 +1025,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.3367</v>
+        <v>0.5043</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>45783.8305750463</v>
+        <v>45727.87202070602</v>
       </c>
       <c r="G12" t="n">
-        <v>29.7</v>
+        <v>19.2</v>
       </c>
       <c r="H12" t="n">
-        <v>26.35</v>
+        <v>22.51</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>9.68</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -1054,18 +1054,18 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.13</v>
+        <v>1.67</v>
       </c>
       <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>1701100027</v>
+        <v>2025661832</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1074,19 +1074,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.5043</v>
+        <v>0.3235</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>45727.87202070602</v>
+        <v>45915.72870862269</v>
       </c>
       <c r="G13" t="n">
-        <v>19.2</v>
+        <v>61.81</v>
       </c>
       <c r="H13" t="n">
-        <v>23</v>
+        <v>61.52</v>
       </c>
       <c r="I13" t="n">
-        <v>9.68</v>
+        <v>20</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -1103,18 +1103,18 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.92</v>
+        <v>-0.1</v>
       </c>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="n">
-        <v>1997552824</v>
+        <v>1461331124</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.0429</v>
+        <v>0.3752</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>45898.65627293981</v>
+        <v>45553.65374138889</v>
       </c>
       <c r="G14" t="n">
-        <v>233.17</v>
+        <v>50.99</v>
       </c>
       <c r="H14" t="n">
-        <v>300.11</v>
+        <v>65</v>
       </c>
       <c r="I14" t="n">
-        <v>10</v>
+        <v>19.13</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -1152,18 +1152,18 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.87</v>
+        <v>5.26</v>
       </c>
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="n">
-        <v>2042979139</v>
+        <v>1923224670</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.3128</v>
+        <v>0.2583</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>45924.70564383102</v>
+        <v>45853.65359685185</v>
       </c>
       <c r="G15" t="n">
-        <v>32</v>
+        <v>58.05</v>
       </c>
       <c r="H15" t="n">
-        <v>31.67</v>
+        <v>65</v>
       </c>
       <c r="I15" t="n">
-        <v>10.01</v>
+        <v>14.99</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1201,18 +1201,18 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1</v>
+        <v>1.8</v>
       </c>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="n">
-        <v>2060617471</v>
+        <v>2047825292</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>BLX</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.2255</v>
+        <v>0.3157</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>45932.89647650463</v>
+        <v>45926.66222740741</v>
       </c>
       <c r="G16" t="n">
-        <v>44.35</v>
+        <v>47.56</v>
       </c>
       <c r="H16" t="n">
-        <v>41.02</v>
+        <v>44.72</v>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
+        <v>15.01</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1250,18 +1250,18 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.75</v>
+        <v>-0.89</v>
       </c>
       <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="n">
-        <v>2042956616</v>
+        <v>1806980482</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1270,19 +1270,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.1592</v>
+        <v>0.2406</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>45924.69943638889</v>
+        <v>45783.83189613426</v>
       </c>
       <c r="G17" t="n">
-        <v>62.88</v>
+        <v>16.12</v>
       </c>
       <c r="H17" t="n">
-        <v>60.36</v>
+        <v>19.34</v>
       </c>
       <c r="I17" t="n">
-        <v>10.01</v>
+        <v>3.88</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1299,18 +1299,18 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4</v>
+        <v>0.77</v>
       </c>
       <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
-        <v>2025661832</v>
+        <v>1744916497</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.3235</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45915.72870862269</v>
+        <v>45751.74231563658</v>
       </c>
       <c r="G18" t="n">
-        <v>61.81</v>
+        <v>17.54</v>
       </c>
       <c r="H18" t="n">
-        <v>60.36</v>
+        <v>24.06</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>17.54</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1348,14 +1348,14 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.47</v>
+        <v>6.52</v>
       </c>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="n">
-        <v>2017777441</v>
+        <v>2078840482</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1368,16 +1368,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.4582</v>
+        <v>0.4336</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45910.64656457176</v>
+        <v>45940.66718949074</v>
       </c>
       <c r="G19" t="n">
-        <v>21.82</v>
+        <v>23.06</v>
       </c>
       <c r="H19" t="n">
-        <v>23</v>
+        <v>22.51</v>
       </c>
       <c r="I19" t="n">
         <v>10</v>
@@ -1397,14 +1397,14 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.54</v>
+        <v>-0.24</v>
       </c>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
-        <v>2071864157</v>
+        <v>2078907475</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1417,19 +1417,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.0291</v>
+        <v>0.0537</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45938.58107210648</v>
+        <v>45940.67644164352</v>
       </c>
       <c r="G20" t="n">
-        <v>280.19</v>
+        <v>278.84</v>
       </c>
       <c r="H20" t="n">
-        <v>295.87</v>
+        <v>294.76</v>
       </c>
       <c r="I20" t="n">
-        <v>10.99</v>
+        <v>19.99</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1446,18 +1446,18 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.51</v>
+        <v>1.17</v>
       </c>
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="n">
-        <v>1582723120</v>
+        <v>1888700382</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1466,19 +1466,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.3755</v>
+        <v>1</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45645.89511640046</v>
+        <v>45831.65144708334</v>
       </c>
       <c r="G21" t="n">
-        <v>53.26</v>
+        <v>47.58</v>
       </c>
       <c r="H21" t="n">
-        <v>64.26000000000001</v>
+        <v>54.39</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>47.58</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1495,18 +1495,18 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>4.13</v>
+        <v>6.81</v>
       </c>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="n">
-        <v>1883977044</v>
+        <v>2091086432</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1515,19 +1515,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.345</v>
+        <v>0.1657</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>45827.66105774305</v>
+        <v>45945.66072645834</v>
       </c>
       <c r="G22" t="n">
-        <v>12.88</v>
+        <v>60.4</v>
       </c>
       <c r="H22" t="n">
-        <v>15.685</v>
+        <v>61.52</v>
       </c>
       <c r="I22" t="n">
-        <v>5.13</v>
+        <v>10.01</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -1544,18 +1544,18 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.15</v>
+        <v>0.18</v>
       </c>
       <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="n">
-        <v>2000138014</v>
+        <v>1978487977</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BTCE.DE</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1564,16 +1564,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.1017</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>45901.57795706019</v>
+        <v>45887.66311905093</v>
       </c>
       <c r="G23" t="n">
-        <v>83.47499999999999</v>
+        <v>127.06</v>
       </c>
       <c r="H23" t="n">
-        <v>84.605</v>
+        <v>121.13</v>
       </c>
       <c r="I23" t="n">
         <v>10</v>
@@ -1593,18 +1593,18 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.01</v>
+        <v>-0.47</v>
       </c>
       <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="n">
-        <v>1880446729</v>
+        <v>1843469729</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.0772</v>
+        <v>0.0423</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45825.89315055555</v>
+        <v>45804.66615450232</v>
       </c>
       <c r="G24" t="n">
-        <v>129.62</v>
+        <v>156.9</v>
       </c>
       <c r="H24" t="n">
-        <v>152.68</v>
+        <v>231.77</v>
       </c>
       <c r="I24" t="n">
-        <v>10.01</v>
+        <v>6.64</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1642,18 +1642,18 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.78</v>
+        <v>3.16</v>
       </c>
       <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="n">
-        <v>1867197360</v>
+        <v>2020498309</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>BBAR</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1662,19 +1662,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.0765</v>
+        <v>0.0131</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>45818.80265583334</v>
+        <v>45911.68944190972</v>
       </c>
       <c r="G25" t="n">
-        <v>131.96</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>152.68</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>10.09</v>
+        <v>0.13</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -1691,18 +1691,18 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.59</v>
+        <v>-0.01</v>
       </c>
       <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="n">
-        <v>1984829391</v>
+        <v>1845429980</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1711,19 +1711,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.0512</v>
+        <v>1</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>45890.71798858796</v>
+        <v>45805.66181400463</v>
       </c>
       <c r="G26" t="n">
-        <v>195.52</v>
+        <v>13.27</v>
       </c>
       <c r="H26" t="n">
-        <v>237.16</v>
+        <v>16.645</v>
       </c>
       <c r="I26" t="n">
-        <v>10.01</v>
+        <v>15.09</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -1740,18 +1740,18 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.13</v>
+        <v>4.24</v>
       </c>
       <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="n">
-        <v>1599448103</v>
+        <v>1997562259</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1760,16 +1760,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.2839</v>
+        <v>0.6323</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>45663.73506711805</v>
+        <v>45898.65762083334</v>
       </c>
       <c r="G27" t="n">
-        <v>52.83</v>
+        <v>23.72</v>
       </c>
       <c r="H27" t="n">
-        <v>64.26000000000001</v>
+        <v>24.06</v>
       </c>
       <c r="I27" t="n">
         <v>15</v>
@@ -1789,18 +1789,18 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>3.24</v>
+        <v>0.21</v>
       </c>
       <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="n">
-        <v>1806980482</v>
+        <v>2035164705</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>PHGP.L</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1809,19 +1809,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.2406</v>
+        <v>0.032</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>45783.83189613426</v>
+        <v>45919.6670447338</v>
       </c>
       <c r="G28" t="n">
-        <v>16.12</v>
+        <v>252.81</v>
       </c>
       <c r="H28" t="n">
-        <v>19.95</v>
+        <v>294.76</v>
       </c>
       <c r="I28" t="n">
-        <v>3.88</v>
+        <v>10.97</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -1838,18 +1838,18 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0.92</v>
+        <v>1.64</v>
       </c>
       <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
-        <v>2076201130</v>
+        <v>1923250768</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1858,19 +1858,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.499</v>
+        <v>0.87</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>45939.75708394676</v>
+        <v>45853.65447396991</v>
       </c>
       <c r="G29" t="n">
-        <v>20.04</v>
+        <v>12.76</v>
       </c>
       <c r="H29" t="n">
-        <v>19.95</v>
+        <v>16.645</v>
       </c>
       <c r="I29" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -1887,18 +1887,18 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.04</v>
+        <v>3.82</v>
       </c>
       <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
-        <v>2047814173</v>
+        <v>2047762608</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IAPD.AS</t>
+          <t>BBAR</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1907,19 +1907,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.5688</v>
+        <v>1</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45926.6592943287</v>
+        <v>45926.65281253472</v>
       </c>
       <c r="G30" t="n">
-        <v>22.46</v>
+        <v>9.27</v>
       </c>
       <c r="H30" t="n">
-        <v>23.005</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>15</v>
+        <v>9.27</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -1936,18 +1936,18 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
       <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="n">
-        <v>2035163256</v>
+        <v>1830408508</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BTCE.DE</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1956,19 +1956,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.0951</v>
+        <v>0.5793</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45919.66675122685</v>
+        <v>45796.82346997685</v>
       </c>
       <c r="G31" t="n">
-        <v>88.91</v>
+        <v>17.26</v>
       </c>
       <c r="H31" t="n">
-        <v>84.605</v>
+        <v>22.51</v>
       </c>
       <c r="I31" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1985,18 +1985,18 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.65</v>
+        <v>3.04</v>
       </c>
       <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="n">
-        <v>1972092684</v>
+        <v>2060620530</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>BLX</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2005,19 +2005,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0.2207</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45882.68269449074</v>
+        <v>45932.89856876157</v>
       </c>
       <c r="G32" t="n">
-        <v>18.8</v>
+        <v>45.28</v>
       </c>
       <c r="H32" t="n">
-        <v>19.24</v>
+        <v>44.72</v>
       </c>
       <c r="I32" t="n">
-        <v>18.8</v>
+        <v>9.99</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -2034,18 +2034,18 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.44</v>
+        <v>-0.12</v>
       </c>
       <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="n">
-        <v>1727563010</v>
+        <v>2071864157</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>PHGP.L</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2054,19 +2054,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>0.0291</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45743.76106726852</v>
+        <v>45938.58107210648</v>
       </c>
       <c r="G33" t="n">
-        <v>46.11</v>
+        <v>280.19</v>
       </c>
       <c r="H33" t="n">
-        <v>54.52</v>
+        <v>294.76</v>
       </c>
       <c r="I33" t="n">
-        <v>46.11</v>
+        <v>10.99</v>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -2083,18 +2083,18 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>8.41</v>
+        <v>0.48</v>
       </c>
       <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="n">
-        <v>1744930699</v>
+        <v>2091063412</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2103,19 +2103,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>0.4089</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45751.74534789352</v>
+        <v>45945.66023149306</v>
       </c>
       <c r="G34" t="n">
-        <v>74.13</v>
+        <v>24.44</v>
       </c>
       <c r="H34" t="n">
-        <v>74.97</v>
+        <v>24.06</v>
       </c>
       <c r="I34" t="n">
-        <v>74.13</v>
+        <v>9.99</v>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
@@ -2132,18 +2132,18 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.84</v>
+        <v>-0.15</v>
       </c>
       <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>1997485943</v>
+        <v>2066994664</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2152,16 +2152,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.5157</v>
+        <v>0.067</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>45898.65185685185</v>
+        <v>45936.87431893519</v>
       </c>
       <c r="G35" t="n">
-        <v>19.39</v>
+        <v>149.19</v>
       </c>
       <c r="H35" t="n">
-        <v>19.95</v>
+        <v>145.14</v>
       </c>
       <c r="I35" t="n">
         <v>10</v>
@@ -2181,18 +2181,18 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.29</v>
+        <v>-0.28</v>
       </c>
       <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>2060619876</v>
+        <v>1883977086</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2201,19 +2201,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.4178</v>
+        <v>1</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45932.89807736111</v>
+        <v>45827.66106613426</v>
       </c>
       <c r="G36" t="n">
-        <v>23.93</v>
+        <v>12.875</v>
       </c>
       <c r="H36" t="n">
-        <v>23</v>
+        <v>16.645</v>
       </c>
       <c r="I36" t="n">
-        <v>10</v>
+        <v>14.86</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -2230,18 +2230,18 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>-0.39</v>
+        <v>4.47</v>
       </c>
       <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
-        <v>1744916452</v>
+        <v>1582723120</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2250,19 +2250,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.4245</v>
+        <v>0.3755</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>45751.74230173611</v>
+        <v>45645.89511640046</v>
       </c>
       <c r="G37" t="n">
-        <v>17.54</v>
+        <v>53.26</v>
       </c>
       <c r="H37" t="n">
-        <v>24.41</v>
+        <v>65</v>
       </c>
       <c r="I37" t="n">
-        <v>7.45</v>
+        <v>20</v>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
@@ -2279,18 +2279,18 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.91</v>
+        <v>4.41</v>
       </c>
       <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>2091104996</v>
+        <v>1824476420</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BLX</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2299,19 +2299,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.2189</v>
+        <v>0.1548</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45945.66391778935</v>
+        <v>45792.64714148148</v>
       </c>
       <c r="G38" t="n">
-        <v>45.76</v>
+        <v>129.17</v>
       </c>
       <c r="H38" t="n">
-        <v>44.62</v>
+        <v>153.77</v>
       </c>
       <c r="I38" t="n">
-        <v>10.02</v>
+        <v>20</v>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
@@ -2328,18 +2328,18 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>-0.25</v>
+        <v>3.8</v>
       </c>
       <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
-        <v>1843477152</v>
+        <v>2065642904</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>IAPD.AS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2348,19 +2348,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.1198</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45804.66724922453</v>
+        <v>45936.61247836806</v>
       </c>
       <c r="G39" t="n">
-        <v>17.86</v>
+        <v>22.935</v>
       </c>
       <c r="H39" t="n">
-        <v>19.95</v>
+        <v>22.975</v>
       </c>
       <c r="I39" t="n">
-        <v>2.14</v>
+        <v>15</v>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -2377,18 +2377,18 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.25</v>
+        <v>-0.14</v>
       </c>
       <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="n">
-        <v>1982273555</v>
+        <v>1806977521</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2397,19 +2397,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.0439</v>
+        <v>0.3367</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>45889.64957444445</v>
+        <v>45783.8305750463</v>
       </c>
       <c r="G40" t="n">
-        <v>228</v>
+        <v>29.7</v>
       </c>
       <c r="H40" t="n">
-        <v>300.11</v>
+        <v>26.02</v>
       </c>
       <c r="I40" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
@@ -2426,18 +2426,18 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>3.16</v>
+        <v>-1.24</v>
       </c>
       <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="n">
-        <v>2060624552</v>
+        <v>1997561527</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2446,19 +2446,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.1676</v>
+        <v>0.1498</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45932.90130990741</v>
+        <v>45898.65748991898</v>
       </c>
       <c r="G41" t="n">
-        <v>59.7</v>
+        <v>66.73</v>
       </c>
       <c r="H41" t="n">
-        <v>60.36</v>
+        <v>65</v>
       </c>
       <c r="I41" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
@@ -2475,18 +2475,18 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.11</v>
+        <v>-0.26</v>
       </c>
       <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="n">
-        <v>1923224670</v>
+        <v>1843477272</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2495,19 +2495,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.2583</v>
+        <v>1</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>45853.65359685185</v>
+        <v>45804.66725678241</v>
       </c>
       <c r="G42" t="n">
-        <v>58.05</v>
+        <v>17.86</v>
       </c>
       <c r="H42" t="n">
-        <v>64.26000000000001</v>
+        <v>19.34</v>
       </c>
       <c r="I42" t="n">
-        <v>14.99</v>
+        <v>17.86</v>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -2524,18 +2524,18 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="n">
-        <v>1662993636</v>
+        <v>1997500170</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>JKS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2544,19 +2544,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>0.4466</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>45706.87026833333</v>
+        <v>45898.65406594907</v>
       </c>
       <c r="G43" t="n">
-        <v>20.65</v>
+        <v>22.39</v>
       </c>
       <c r="H43" t="n">
-        <v>19.24</v>
+        <v>23.11</v>
       </c>
       <c r="I43" t="n">
-        <v>20.65</v>
+        <v>10</v>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -2573,18 +2573,18 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>-1.41</v>
+        <v>0.32</v>
       </c>
       <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
-        <v>2078840482</v>
+        <v>1599455288</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2593,16 +2593,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.4336</v>
+        <v>0.2195</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45940.66718949074</v>
+        <v>45663.73750263889</v>
       </c>
       <c r="G44" t="n">
-        <v>23.06</v>
+        <v>45.55</v>
       </c>
       <c r="H44" t="n">
-        <v>23</v>
+        <v>26.02</v>
       </c>
       <c r="I44" t="n">
         <v>10</v>
@@ -2622,18 +2622,18 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>-0.03</v>
+        <v>-4.29</v>
       </c>
       <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>2080269311</v>
+        <v>2029950407</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>PHGP.L</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2642,19 +2642,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0.1453</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>45940.886384375</v>
+        <v>45917.66293982639</v>
       </c>
       <c r="G45" t="n">
-        <v>52.53</v>
+        <v>250.56</v>
       </c>
       <c r="H45" t="n">
-        <v>54.52</v>
+        <v>294.76</v>
       </c>
       <c r="I45" t="n">
-        <v>52.53</v>
+        <v>49.99</v>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -2671,18 +2671,18 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.99</v>
+        <v>7.27</v>
       </c>
       <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>2047762508</v>
+        <v>2027639997</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BBAR</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2691,19 +2691,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.1558</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>45926.65279332176</v>
+        <v>45916.65703747685</v>
       </c>
       <c r="G46" t="n">
-        <v>9.27</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>9.49</v>
+        <v>65</v>
       </c>
       <c r="I46" t="n">
-        <v>0.73</v>
+        <v>10</v>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -2720,18 +2720,18 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.02</v>
+        <v>0.13</v>
       </c>
       <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>2091105918</v>
+        <v>1926287328</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IAPD.AS</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2740,19 +2740,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.5535</v>
+        <v>0.5476</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>45945.66408168981</v>
+        <v>45854.82177967593</v>
       </c>
       <c r="G47" t="n">
-        <v>23.185</v>
+        <v>18.26</v>
       </c>
       <c r="H47" t="n">
-        <v>23.005</v>
+        <v>22.51</v>
       </c>
       <c r="I47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -2769,18 +2769,18 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>-0.22</v>
+        <v>2.33</v>
       </c>
       <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>1744879358</v>
+        <v>1995249699</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2789,19 +2789,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.0247</v>
+        <v>0.3888</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>45751.73925940973</v>
+        <v>45897.61086020833</v>
       </c>
       <c r="G48" t="n">
-        <v>148.09</v>
+        <v>87.16500000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>300.11</v>
+        <v>81.605</v>
       </c>
       <c r="I48" t="n">
-        <v>3.66</v>
+        <v>39.77</v>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -2818,18 +2818,18 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>3.75</v>
+        <v>-2.92</v>
       </c>
       <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
-        <v>1978487977</v>
+        <v>2060619876</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2838,16 +2838,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.4178</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45887.66311905093</v>
+        <v>45932.89807736111</v>
       </c>
       <c r="G49" t="n">
-        <v>127.06</v>
+        <v>23.93</v>
       </c>
       <c r="H49" t="n">
-        <v>120.39</v>
+        <v>22.51</v>
       </c>
       <c r="I49" t="n">
         <v>10</v>
@@ -2867,18 +2867,18 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>-0.53</v>
+        <v>-0.6</v>
       </c>
       <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
-        <v>1644796307</v>
+        <v>2080281129</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>JKS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0.462</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>45693.85501710648</v>
+        <v>45940.89117050926</v>
       </c>
       <c r="G50" t="n">
-        <v>20.36</v>
+        <v>21.73</v>
       </c>
       <c r="H50" t="n">
-        <v>19.24</v>
+        <v>23.11</v>
       </c>
       <c r="I50" t="n">
-        <v>20.36</v>
+        <v>10.04</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -2916,18 +2916,18 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>-1.12</v>
+        <v>0.64</v>
       </c>
       <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>2091064900</v>
+        <v>2066988146</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2936,19 +2936,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.4294</v>
+        <v>0.102</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>45945.66049490741</v>
+        <v>45936.870276875</v>
       </c>
       <c r="G51" t="n">
-        <v>23.32</v>
+        <v>98.06</v>
       </c>
       <c r="H51" t="n">
-        <v>22.87</v>
+        <v>97.06</v>
       </c>
       <c r="I51" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -2965,18 +2965,18 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>-0.19</v>
+        <v>-0.1</v>
       </c>
       <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
-        <v>1495551484</v>
+        <v>1895465445</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2985,19 +2985,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.1914</v>
+        <v>0.2987</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>45580.70648087963</v>
+        <v>45834.6539484375</v>
       </c>
       <c r="G52" t="n">
-        <v>135.82</v>
+        <v>33.47</v>
       </c>
       <c r="H52" t="n">
-        <v>120.39</v>
+        <v>26.02</v>
       </c>
       <c r="I52" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
@@ -3014,14 +3014,14 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>-2.96</v>
+        <v>-2.23</v>
       </c>
       <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="n">
-        <v>1599455288</v>
+        <v>1754302454</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -3034,19 +3034,19 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.2195</v>
+        <v>0.3673</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>45663.73750263889</v>
+        <v>45755.88025324074</v>
       </c>
       <c r="G53" t="n">
-        <v>45.55</v>
+        <v>27.17</v>
       </c>
       <c r="H53" t="n">
-        <v>26.35</v>
+        <v>26.02</v>
       </c>
       <c r="I53" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
@@ -3063,18 +3063,18 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>-4.22</v>
+        <v>-0.42</v>
       </c>
       <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="n">
-        <v>1888700382</v>
+        <v>2091093343</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3083,19 +3083,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>0.2366</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>45831.65144708334</v>
+        <v>45945.66190688658</v>
       </c>
       <c r="G54" t="n">
-        <v>47.58</v>
+        <v>42.25</v>
       </c>
       <c r="H54" t="n">
-        <v>54.52</v>
+        <v>40.9</v>
       </c>
       <c r="I54" t="n">
-        <v>47.58</v>
+        <v>10</v>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
@@ -3112,18 +3112,18 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>6.94</v>
+        <v>-0.32</v>
       </c>
       <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="n">
-        <v>1997562259</v>
+        <v>1981010841</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3132,19 +3132,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.6323</v>
+        <v>0.0425</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>45898.65762083334</v>
+        <v>45888.84617734954</v>
       </c>
       <c r="G55" t="n">
-        <v>23.72</v>
+        <v>235.53</v>
       </c>
       <c r="H55" t="n">
-        <v>24.41</v>
+        <v>295.11</v>
       </c>
       <c r="I55" t="n">
-        <v>15</v>
+        <v>10.01</v>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
@@ -3161,18 +3161,18 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>0.43</v>
+        <v>2.53</v>
       </c>
       <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="n">
-        <v>1845429956</v>
+        <v>2048501554</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>JKS</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3181,19 +3181,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.4821</v>
+        <v>0.4118</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>45805.66180811343</v>
+        <v>45926.83927949074</v>
       </c>
       <c r="G56" t="n">
-        <v>13.275</v>
+        <v>24.28</v>
       </c>
       <c r="H56" t="n">
-        <v>15.685</v>
+        <v>23.11</v>
       </c>
       <c r="I56" t="n">
-        <v>7.28</v>
+        <v>10</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
@@ -3210,18 +3210,18 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>1.5</v>
+        <v>-0.48</v>
       </c>
       <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="n">
-        <v>1867462173</v>
+        <v>1869077157</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3230,19 +3230,19 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.3061</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45818.90866184028</v>
+        <v>45819.6742621412</v>
       </c>
       <c r="G57" t="n">
-        <v>77.93000000000001</v>
+        <v>13.285</v>
       </c>
       <c r="H57" t="n">
-        <v>96.20999999999999</v>
+        <v>16.645</v>
       </c>
       <c r="I57" t="n">
-        <v>0.65</v>
+        <v>4.69</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
@@ -3259,18 +3259,18 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>0.16</v>
+        <v>1.23</v>
       </c>
       <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
-        <v>2091086432</v>
+        <v>2000138014</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3279,19 +3279,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.1657</v>
+        <v>0.1017</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45945.66072645834</v>
+        <v>45901.57795706019</v>
       </c>
       <c r="G58" t="n">
-        <v>60.4</v>
+        <v>83.47499999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>60.36</v>
+        <v>81.605</v>
       </c>
       <c r="I58" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
@@ -3308,18 +3308,18 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>-0.01</v>
+        <v>-0.36</v>
       </c>
       <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="n">
-        <v>2091099618</v>
+        <v>2095264263</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BBAR</t>
+          <t>SQM</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3328,19 +3328,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.0373</v>
+        <v>0.2252</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>45945.66309922453</v>
+        <v>45946.74280237268</v>
       </c>
       <c r="G59" t="n">
-        <v>9.68</v>
+        <v>44.39</v>
       </c>
       <c r="H59" t="n">
-        <v>9.49</v>
+        <v>43.69</v>
       </c>
       <c r="I59" t="n">
-        <v>0.36</v>
+        <v>10</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
@@ -3357,18 +3357,18 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>-0.01</v>
+        <v>-0.16</v>
       </c>
       <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="n">
-        <v>1923271589</v>
+        <v>1621495187</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3377,19 +3377,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.4478</v>
+        <v>0.2318</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45853.65794861111</v>
+        <v>45678.83178196759</v>
       </c>
       <c r="G60" t="n">
-        <v>44.66</v>
+        <v>43.27</v>
       </c>
       <c r="H60" t="n">
-        <v>56.33</v>
+        <v>26.02</v>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>10.03</v>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
@@ -3406,18 +3406,18 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>5.22</v>
+        <v>-4</v>
       </c>
       <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="n">
-        <v>1653137218</v>
+        <v>2042979139</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3426,19 +3426,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.277</v>
+        <v>0.3128</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>45699.85152199074</v>
+        <v>45924.70564383102</v>
       </c>
       <c r="G61" t="n">
-        <v>36.1</v>
+        <v>32</v>
       </c>
       <c r="H61" t="n">
-        <v>26.35</v>
+        <v>31.63</v>
       </c>
       <c r="I61" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
@@ -3455,18 +3455,18 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>-2.7</v>
+        <v>-0.12</v>
       </c>
       <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="n">
-        <v>1635194117</v>
+        <v>1666459270</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3475,19 +3475,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.2479</v>
+        <v>0.5636</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>45687.85228493056</v>
+        <v>45708.68166530092</v>
       </c>
       <c r="G62" t="n">
-        <v>40.33</v>
+        <v>17.18</v>
       </c>
       <c r="H62" t="n">
-        <v>26.35</v>
+        <v>24.06</v>
       </c>
       <c r="I62" t="n">
-        <v>10</v>
+        <v>9.68</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
@@ -3504,18 +3504,18 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>-3.47</v>
+        <v>3.88</v>
       </c>
       <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="n">
-        <v>2091099733</v>
+        <v>1662993636</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BBAR</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3527,16 +3527,16 @@
         <v>1</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>45945.6631174537</v>
+        <v>45706.87026833333</v>
       </c>
       <c r="G63" t="n">
-        <v>9.619999999999999</v>
+        <v>20.65</v>
       </c>
       <c r="H63" t="n">
-        <v>9.49</v>
+        <v>19.75</v>
       </c>
       <c r="I63" t="n">
-        <v>9.619999999999999</v>
+        <v>20.65</v>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
@@ -3553,18 +3553,18 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>-0.13</v>
+        <v>-0.9</v>
       </c>
       <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="n">
-        <v>2078838036</v>
+        <v>1517510856</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>JKS</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3573,19 +3573,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.43</v>
+        <v>0.0602</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>45940.66691300926</v>
+        <v>45597.61014849537</v>
       </c>
       <c r="G64" t="n">
-        <v>23.37</v>
+        <v>166.03</v>
       </c>
       <c r="H64" t="n">
-        <v>23.8</v>
+        <v>153.77</v>
       </c>
       <c r="I64" t="n">
-        <v>10.05</v>
+        <v>10</v>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
@@ -3602,18 +3602,18 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>0.18</v>
+        <v>-0.74</v>
       </c>
       <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="n">
-        <v>2065634230</v>
+        <v>1923258249</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3622,19 +3622,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.7849</v>
+        <v>1</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>45936.60990405093</v>
+        <v>45853.65576626157</v>
       </c>
       <c r="G65" t="n">
-        <v>16.28</v>
+        <v>19.41</v>
       </c>
       <c r="H65" t="n">
-        <v>15.685</v>
+        <v>22.51</v>
       </c>
       <c r="I65" t="n">
-        <v>15</v>
+        <v>19.41</v>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
@@ -3651,18 +3651,18 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>-0.71</v>
+        <v>3.1</v>
       </c>
       <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="n">
-        <v>2035164705</v>
+        <v>2060617471</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>PHGP.L</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3671,19 +3671,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.032</v>
+        <v>0.2255</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>45919.6670447338</v>
+        <v>45932.89647650463</v>
       </c>
       <c r="G66" t="n">
-        <v>252.81</v>
+        <v>44.35</v>
       </c>
       <c r="H66" t="n">
-        <v>295.87</v>
+        <v>40.9</v>
       </c>
       <c r="I66" t="n">
-        <v>10.97</v>
+        <v>10</v>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
@@ -3700,18 +3700,18 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>1.68</v>
+        <v>-0.78</v>
       </c>
       <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="n">
-        <v>2045989132</v>
+        <v>1744916452</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3720,19 +3720,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.2034</v>
+        <v>0.4245</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>45925.79891365741</v>
+        <v>45751.74230173611</v>
       </c>
       <c r="G67" t="n">
-        <v>49.16</v>
+        <v>17.54</v>
       </c>
       <c r="H67" t="n">
-        <v>47.7</v>
+        <v>24.06</v>
       </c>
       <c r="I67" t="n">
-        <v>10</v>
+        <v>7.45</v>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
@@ -3749,18 +3749,18 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>-0.3</v>
+        <v>2.76</v>
       </c>
       <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="n">
-        <v>2047762608</v>
+        <v>2066989908</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BBAR</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3769,19 +3769,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>0.3946</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>45926.65281253472</v>
+        <v>45936.87125002315</v>
       </c>
       <c r="G68" t="n">
-        <v>9.27</v>
+        <v>25.34</v>
       </c>
       <c r="H68" t="n">
-        <v>9.49</v>
+        <v>24.06</v>
       </c>
       <c r="I68" t="n">
-        <v>9.27</v>
+        <v>10</v>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
@@ -3798,18 +3798,18 @@
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>0.22</v>
+        <v>-0.51</v>
       </c>
       <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="n">
-        <v>2060645660</v>
+        <v>1358151307</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3818,19 +3818,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.1027</v>
+        <v>0.1081</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>45932.90186543982</v>
+        <v>45460.88529052083</v>
       </c>
       <c r="G69" t="n">
-        <v>97.43000000000001</v>
+        <v>165.93</v>
       </c>
       <c r="H69" t="n">
-        <v>96.20999999999999</v>
+        <v>153.77</v>
       </c>
       <c r="I69" t="n">
-        <v>10.01</v>
+        <v>17.94</v>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
@@ -3847,18 +3847,18 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>-0.13</v>
+        <v>-1.31</v>
       </c>
       <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="n">
-        <v>2017852950</v>
+        <v>1888686062</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3867,19 +3867,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>0.2903</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>45910.65507498843</v>
+        <v>45831.64964792824</v>
       </c>
       <c r="G70" t="n">
-        <v>37.44</v>
+        <v>34.36</v>
       </c>
       <c r="H70" t="n">
-        <v>49.16</v>
+        <v>26.02</v>
       </c>
       <c r="I70" t="n">
-        <v>37.44</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
@@ -3896,18 +3896,18 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>11.72</v>
+        <v>-2.42</v>
       </c>
       <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="n">
-        <v>2029950407</v>
+        <v>2091115227</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PHGP.L</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3916,19 +3916,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.1453</v>
+        <v>0.376</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>45917.66293982639</v>
+        <v>45945.66604186343</v>
       </c>
       <c r="G71" t="n">
-        <v>250.56</v>
+        <v>26.59</v>
       </c>
       <c r="H71" t="n">
-        <v>295.87</v>
+        <v>26.02</v>
       </c>
       <c r="I71" t="n">
-        <v>49.99</v>
+        <v>10</v>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
@@ -3945,18 +3945,18 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>7.45</v>
+        <v>-0.22</v>
       </c>
       <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="n">
-        <v>1631475148</v>
+        <v>1982273555</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3965,19 +3965,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.2592</v>
+        <v>0.0439</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>45685.83625201389</v>
+        <v>45889.64957444445</v>
       </c>
       <c r="G72" t="n">
-        <v>38.58</v>
+        <v>228</v>
       </c>
       <c r="H72" t="n">
-        <v>26.35</v>
+        <v>295.11</v>
       </c>
       <c r="I72" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -3994,18 +3994,18 @@
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>-3.17</v>
+        <v>2.95</v>
       </c>
       <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="n">
-        <v>1830410729</v>
+        <v>1869077178</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4014,19 +4014,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.1091</v>
+        <v>1</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45796.82476561343</v>
+        <v>45819.67426902778</v>
       </c>
       <c r="G73" t="n">
-        <v>33.66</v>
+        <v>13.285</v>
       </c>
       <c r="H73" t="n">
-        <v>31.67</v>
+        <v>16.645</v>
       </c>
       <c r="I73" t="n">
-        <v>3.67</v>
+        <v>15.31</v>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
@@ -4043,18 +4043,18 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>-0.21</v>
+        <v>4.02</v>
       </c>
       <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="n">
-        <v>1727591551</v>
+        <v>1997498400</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4063,19 +4063,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>0.0507</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45743.77389555555</v>
+        <v>45898.65380736111</v>
       </c>
       <c r="G74" t="n">
-        <v>72.87</v>
+        <v>197.26</v>
       </c>
       <c r="H74" t="n">
-        <v>74.97</v>
+        <v>231.77</v>
       </c>
       <c r="I74" t="n">
-        <v>72.87</v>
+        <v>10</v>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
@@ -4092,18 +4092,18 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="n">
-        <v>1744916497</v>
+        <v>1867193336</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4115,16 +4115,16 @@
         <v>1</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>45751.74231563658</v>
+        <v>45818.80084483796</v>
       </c>
       <c r="G75" t="n">
-        <v>17.54</v>
+        <v>17.64</v>
       </c>
       <c r="H75" t="n">
-        <v>24.41</v>
+        <v>19.34</v>
       </c>
       <c r="I75" t="n">
-        <v>17.54</v>
+        <v>17.64</v>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
@@ -4141,18 +4141,18 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>6.87</v>
+        <v>1.7</v>
       </c>
       <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="n">
-        <v>1867193336</v>
+        <v>1631475148</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4161,19 +4161,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>0.2592</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>45818.80084483796</v>
+        <v>45685.83625201389</v>
       </c>
       <c r="G76" t="n">
-        <v>17.64</v>
+        <v>38.58</v>
       </c>
       <c r="H76" t="n">
-        <v>19.95</v>
+        <v>26.02</v>
       </c>
       <c r="I76" t="n">
-        <v>17.64</v>
+        <v>10</v>
       </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
@@ -4190,18 +4190,18 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>2.31</v>
+        <v>-3.26</v>
       </c>
       <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="n">
-        <v>1986476926</v>
+        <v>2042867331</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>JKS</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4210,19 +4210,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1</v>
+        <v>0.3941</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>45891.66490212963</v>
+        <v>45924.67994332176</v>
       </c>
       <c r="G77" t="n">
-        <v>34.44</v>
+        <v>25.37</v>
       </c>
       <c r="H77" t="n">
-        <v>49.16</v>
+        <v>23.11</v>
       </c>
       <c r="I77" t="n">
-        <v>34.44</v>
+        <v>10</v>
       </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
@@ -4239,18 +4239,18 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>14.72</v>
+        <v>-0.89</v>
       </c>
       <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="n">
-        <v>2091115227</v>
+        <v>2065634230</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4259,19 +4259,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.376</v>
+        <v>0.7849</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>45945.66604186343</v>
+        <v>45936.60990405093</v>
       </c>
       <c r="G78" t="n">
-        <v>26.59</v>
+        <v>16.28</v>
       </c>
       <c r="H78" t="n">
-        <v>26.35</v>
+        <v>16.645</v>
       </c>
       <c r="I78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
@@ -4288,18 +4288,18 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>-0.09</v>
+        <v>0.17</v>
       </c>
       <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="n">
-        <v>1563288050</v>
+        <v>1923256224</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4308,19 +4308,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.0626</v>
+        <v>0.6457000000000001</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>45630.85583428241</v>
+        <v>45853.65543140046</v>
       </c>
       <c r="G79" t="n">
-        <v>159.74</v>
+        <v>30.97</v>
       </c>
       <c r="H79" t="n">
-        <v>152.68</v>
+        <v>26.02</v>
       </c>
       <c r="I79" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
@@ -4337,18 +4337,18 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>-0.44</v>
+        <v>-3.2</v>
       </c>
       <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="n">
-        <v>1806980496</v>
+        <v>2047762508</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>BBAR</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4357,19 +4357,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>45783.83190503472</v>
+        <v>45926.65279332176</v>
       </c>
       <c r="G80" t="n">
-        <v>16.12</v>
+        <v>9.27</v>
       </c>
       <c r="H80" t="n">
-        <v>19.95</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>16.12</v>
+        <v>0.73</v>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
@@ -4386,18 +4386,18 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>3.83</v>
+        <v>0.01</v>
       </c>
       <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="n">
-        <v>2072487323</v>
+        <v>2091099618</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>BBAR</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4406,19 +4406,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.4062</v>
+        <v>0.0373</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>45938.67565716435</v>
+        <v>45945.66309922453</v>
       </c>
       <c r="G81" t="n">
-        <v>24.64</v>
+        <v>9.68</v>
       </c>
       <c r="H81" t="n">
-        <v>22.87</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>10.01</v>
+        <v>0.36</v>
       </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
@@ -4435,18 +4435,18 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>-0.72</v>
+        <v>-0.01</v>
       </c>
       <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="n">
-        <v>2042867331</v>
+        <v>1727591551</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>JKS</t>
+          <t>BND</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4455,19 +4455,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.3941</v>
+        <v>1</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>45924.67994332176</v>
+        <v>45743.77389555555</v>
       </c>
       <c r="G82" t="n">
-        <v>25.37</v>
+        <v>72.87</v>
       </c>
       <c r="H82" t="n">
-        <v>23.8</v>
+        <v>74.88</v>
       </c>
       <c r="I82" t="n">
-        <v>10</v>
+        <v>72.87</v>
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
@@ -4484,18 +4484,18 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>-0.62</v>
+        <v>2.01</v>
       </c>
       <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="n">
-        <v>2042971604</v>
+        <v>2080281858</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4504,19 +4504,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.3901</v>
+        <v>0.4547</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>45924.70406969907</v>
+        <v>45940.89146028935</v>
       </c>
       <c r="G83" t="n">
-        <v>25.66</v>
+        <v>21.99</v>
       </c>
       <c r="H83" t="n">
-        <v>22.87</v>
+        <v>22.51</v>
       </c>
       <c r="I83" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
@@ -4533,18 +4533,18 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>-1.09</v>
+        <v>0.24</v>
       </c>
       <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="n">
-        <v>1976499401</v>
+        <v>1867196288</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4553,19 +4553,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.8064</v>
+        <v>0.5568</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>45884.83731814815</v>
+        <v>45818.80209099537</v>
       </c>
       <c r="G84" t="n">
-        <v>49.6</v>
+        <v>41.99</v>
       </c>
       <c r="H84" t="n">
-        <v>47.7</v>
+        <v>56.8</v>
       </c>
       <c r="I84" t="n">
-        <v>40</v>
+        <v>23.38</v>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
@@ -4582,18 +4582,18 @@
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>-1.53</v>
+        <v>8.25</v>
       </c>
       <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="n">
-        <v>1997500170</v>
+        <v>1972092684</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>JKS</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4602,19 +4602,19 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.4466</v>
+        <v>1</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>45898.65406594907</v>
+        <v>45882.68269449074</v>
       </c>
       <c r="G85" t="n">
-        <v>22.39</v>
+        <v>18.8</v>
       </c>
       <c r="H85" t="n">
-        <v>23.8</v>
+        <v>19.75</v>
       </c>
       <c r="I85" t="n">
-        <v>10</v>
+        <v>18.8</v>
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
@@ -4631,18 +4631,18 @@
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>0.63</v>
+        <v>0.95</v>
       </c>
       <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="n">
-        <v>2080281129</v>
+        <v>1830410729</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>JKS</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4651,19 +4651,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.462</v>
+        <v>0.1091</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>45940.89117050926</v>
+        <v>45796.82476561343</v>
       </c>
       <c r="G86" t="n">
-        <v>21.73</v>
+        <v>33.66</v>
       </c>
       <c r="H86" t="n">
-        <v>23.8</v>
+        <v>31.63</v>
       </c>
       <c r="I86" t="n">
-        <v>10.04</v>
+        <v>3.67</v>
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
@@ -4680,18 +4680,18 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>0.96</v>
+        <v>-0.22</v>
       </c>
       <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="n">
-        <v>1882283184</v>
+        <v>1599448103</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4700,19 +4700,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.4835</v>
+        <v>0.2839</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>45826.76569390047</v>
+        <v>45663.73506711805</v>
       </c>
       <c r="G87" t="n">
-        <v>20.69</v>
+        <v>52.83</v>
       </c>
       <c r="H87" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="I87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
@@ -4729,18 +4729,18 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>1.12</v>
+        <v>3.45</v>
       </c>
       <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="n">
-        <v>1997498400</v>
+        <v>2045989132</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4749,16 +4749,16 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.0507</v>
+        <v>0.2034</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>45898.65380736111</v>
+        <v>45925.79891365741</v>
       </c>
       <c r="G88" t="n">
-        <v>197.26</v>
+        <v>49.16</v>
       </c>
       <c r="H88" t="n">
-        <v>237.16</v>
+        <v>48.43</v>
       </c>
       <c r="I88" t="n">
         <v>10</v>
@@ -4778,18 +4778,18 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>2.02</v>
+        <v>-0.15</v>
       </c>
       <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="n">
-        <v>1880443947</v>
+        <v>1806979127</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4798,19 +4798,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.1047</v>
+        <v>0.6361</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>45825.891695625</v>
+        <v>45783.83125244213</v>
       </c>
       <c r="G89" t="n">
-        <v>142.99</v>
+        <v>15.72</v>
       </c>
       <c r="H89" t="n">
-        <v>237.16</v>
+        <v>22.51</v>
       </c>
       <c r="I89" t="n">
-        <v>14.97</v>
+        <v>10</v>
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
@@ -4827,18 +4827,18 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>9.859999999999999</v>
+        <v>4.32</v>
       </c>
       <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="n">
-        <v>1843477272</v>
+        <v>2020498366</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>BBAR</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4850,16 +4850,16 @@
         <v>1</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>45804.66725678241</v>
+        <v>45911.68945292824</v>
       </c>
       <c r="G90" t="n">
-        <v>17.86</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="H90" t="n">
-        <v>19.95</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>17.86</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
@@ -4876,18 +4876,18 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>2.09</v>
+        <v>-0.5</v>
       </c>
       <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="n">
-        <v>2066994664</v>
+        <v>1867193304</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4896,19 +4896,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.067</v>
+        <v>0.1337</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>45936.87431893519</v>
+        <v>45818.8008296412</v>
       </c>
       <c r="G91" t="n">
-        <v>149.19</v>
+        <v>17.64</v>
       </c>
       <c r="H91" t="n">
-        <v>143.25</v>
+        <v>19.34</v>
       </c>
       <c r="I91" t="n">
-        <v>10</v>
+        <v>2.36</v>
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
@@ -4925,18 +4925,18 @@
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>-0.4</v>
+        <v>0.23</v>
       </c>
       <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="n">
-        <v>1830408508</v>
+        <v>2017778050</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4945,19 +4945,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.5793</v>
+        <v>0.3611</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>45796.82346997685</v>
+        <v>45910.64665976852</v>
       </c>
       <c r="G92" t="n">
-        <v>17.26</v>
+        <v>27.91</v>
       </c>
       <c r="H92" t="n">
-        <v>23</v>
+        <v>26.02</v>
       </c>
       <c r="I92" t="n">
-        <v>10</v>
+        <v>10.08</v>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
@@ -4974,18 +4974,18 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>3.32</v>
+        <v>-0.68</v>
       </c>
       <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="n">
-        <v>1923258184</v>
+        <v>1599431096</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4994,19 +4994,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.0298</v>
+        <v>0.1013</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>45853.6557568287</v>
+        <v>45663.73014731482</v>
       </c>
       <c r="G93" t="n">
-        <v>19.43</v>
+        <v>148.02</v>
       </c>
       <c r="H93" t="n">
-        <v>23</v>
+        <v>153.77</v>
       </c>
       <c r="I93" t="n">
-        <v>0.58</v>
+        <v>14.99</v>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
@@ -5023,18 +5023,18 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>0.11</v>
+        <v>0.59</v>
       </c>
       <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="n">
-        <v>1666461140</v>
+        <v>2091104996</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>BLX</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5043,19 +5043,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.2651</v>
+        <v>0.2189</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>45708.68207092593</v>
+        <v>45945.66391778935</v>
       </c>
       <c r="G94" t="n">
-        <v>37.7</v>
+        <v>45.76</v>
       </c>
       <c r="H94" t="n">
-        <v>26.35</v>
+        <v>44.72</v>
       </c>
       <c r="I94" t="n">
-        <v>9.99</v>
+        <v>10.02</v>
       </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
@@ -5072,18 +5072,18 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>-3</v>
+        <v>-0.23</v>
       </c>
       <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="n">
-        <v>2078907475</v>
+        <v>1923258184</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PHGP.L</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5092,19 +5092,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.0537</v>
+        <v>0.0298</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>45940.67644164352</v>
+        <v>45853.6557568287</v>
       </c>
       <c r="G95" t="n">
-        <v>278.84</v>
+        <v>19.43</v>
       </c>
       <c r="H95" t="n">
-        <v>295.87</v>
+        <v>22.51</v>
       </c>
       <c r="I95" t="n">
-        <v>19.99</v>
+        <v>0.58</v>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -5121,18 +5121,18 @@
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>1.24</v>
+        <v>0.09</v>
       </c>
       <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="n">
-        <v>2080281858</v>
+        <v>2060645660</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5141,19 +5141,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.4547</v>
+        <v>0.1027</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>45940.89146028935</v>
+        <v>45932.90186543982</v>
       </c>
       <c r="G96" t="n">
-        <v>21.99</v>
+        <v>97.43000000000001</v>
       </c>
       <c r="H96" t="n">
-        <v>23</v>
+        <v>97.06</v>
       </c>
       <c r="I96" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
@@ -5170,14 +5170,14 @@
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>0.46</v>
+        <v>-0.04</v>
       </c>
       <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="n">
-        <v>2045993574</v>
+        <v>1727574394</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -5190,19 +5190,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.5753</v>
+        <v>1</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>45925.80108013889</v>
+        <v>45743.76658678241</v>
       </c>
       <c r="G97" t="n">
-        <v>17.38</v>
+        <v>21.13</v>
       </c>
       <c r="H97" t="n">
-        <v>19.24</v>
+        <v>19.75</v>
       </c>
       <c r="I97" t="n">
-        <v>10</v>
+        <v>21.13</v>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
@@ -5219,18 +5219,18 @@
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>1.07</v>
+        <v>-1.38</v>
       </c>
       <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="n">
-        <v>2050990570</v>
+        <v>2045993574</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BLX</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5239,19 +5239,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.2121</v>
+        <v>0.5753</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>45929.65780017361</v>
+        <v>45925.80108013889</v>
       </c>
       <c r="G98" t="n">
-        <v>47</v>
+        <v>17.38</v>
       </c>
       <c r="H98" t="n">
-        <v>44.62</v>
+        <v>19.75</v>
       </c>
       <c r="I98" t="n">
-        <v>9.970000000000001</v>
+        <v>10</v>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
@@ -5268,18 +5268,18 @@
         <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>-0.51</v>
+        <v>1.36</v>
       </c>
       <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="n">
-        <v>1981010841</v>
+        <v>2078838036</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>JKS</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5288,19 +5288,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.0425</v>
+        <v>0.43</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>45888.84617734954</v>
+        <v>45940.66691300926</v>
       </c>
       <c r="G99" t="n">
-        <v>235.53</v>
+        <v>23.37</v>
       </c>
       <c r="H99" t="n">
-        <v>300.11</v>
+        <v>23.11</v>
       </c>
       <c r="I99" t="n">
-        <v>10.01</v>
+        <v>10.05</v>
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
@@ -5317,14 +5317,14 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>2.74</v>
+        <v>-0.11</v>
       </c>
       <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="n">
-        <v>1880442840</v>
+        <v>2066990620</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -5337,19 +5337,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.2535</v>
+        <v>0.1541</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>45825.89113450232</v>
+        <v>45936.87171386574</v>
       </c>
       <c r="G100" t="n">
-        <v>59.15</v>
+        <v>64.88</v>
       </c>
       <c r="H100" t="n">
-        <v>64.26000000000001</v>
+        <v>65</v>
       </c>
       <c r="I100" t="n">
-        <v>14.99</v>
+        <v>10</v>
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
@@ -5366,18 +5366,18 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>1.3</v>
+        <v>0.02</v>
       </c>
       <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="n">
-        <v>1993382859</v>
+        <v>1880446729</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5386,19 +5386,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.0779</v>
+        <v>0.0772</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>45896.66809304398</v>
+        <v>45825.89315055555</v>
       </c>
       <c r="G101" t="n">
-        <v>128.25</v>
+        <v>129.62</v>
       </c>
       <c r="H101" t="n">
-        <v>120.39</v>
+        <v>153.77</v>
       </c>
       <c r="I101" t="n">
-        <v>9.99</v>
+        <v>10.01</v>
       </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -5415,18 +5415,18 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>-0.61</v>
+        <v>1.86</v>
       </c>
       <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="n">
-        <v>1754304266</v>
+        <v>1880443947</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5435,19 +5435,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.7137</v>
+        <v>0.1047</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>45755.88055112268</v>
+        <v>45825.891695625</v>
       </c>
       <c r="G102" t="n">
-        <v>14</v>
+        <v>142.99</v>
       </c>
       <c r="H102" t="n">
-        <v>23</v>
+        <v>231.77</v>
       </c>
       <c r="I102" t="n">
-        <v>9.99</v>
+        <v>14.97</v>
       </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
@@ -5464,18 +5464,18 @@
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>6.43</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="n">
-        <v>1997561527</v>
+        <v>2091123728</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>SQM</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5484,19 +5484,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.1498</v>
+        <v>0.4406</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>45898.65748991898</v>
+        <v>45945.66748809028</v>
       </c>
       <c r="G103" t="n">
-        <v>66.73</v>
+        <v>45.28</v>
       </c>
       <c r="H103" t="n">
-        <v>64.26000000000001</v>
+        <v>43.69</v>
       </c>
       <c r="I103" t="n">
-        <v>10</v>
+        <v>19.95</v>
       </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
@@ -5513,18 +5513,18 @@
         <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>-0.37</v>
+        <v>-0.7</v>
       </c>
       <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="n">
-        <v>1843469729</v>
+        <v>2050990570</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>BLX</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5533,19 +5533,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.0423</v>
+        <v>0.2121</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>45804.66615450232</v>
+        <v>45929.65780017361</v>
       </c>
       <c r="G104" t="n">
-        <v>156.9</v>
+        <v>47</v>
       </c>
       <c r="H104" t="n">
-        <v>237.16</v>
+        <v>44.72</v>
       </c>
       <c r="I104" t="n">
-        <v>6.64</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
@@ -5562,18 +5562,18 @@
         <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>3.39</v>
+        <v>-0.48</v>
       </c>
       <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="n">
-        <v>1867194722</v>
+        <v>2099890750</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5582,19 +5582,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1</v>
+        <v>0.1038</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>45818.80135700232</v>
+        <v>45947.69026060185</v>
       </c>
       <c r="G105" t="n">
-        <v>21.27</v>
+        <v>96.38</v>
       </c>
       <c r="H105" t="n">
-        <v>19.24</v>
+        <v>97.06</v>
       </c>
       <c r="I105" t="n">
-        <v>21.27</v>
+        <v>10</v>
       </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
@@ -5611,18 +5611,18 @@
         <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>-2.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="n">
-        <v>1926287328</v>
+        <v>1983186744</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5631,16 +5631,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.5476</v>
+        <v>0.3162</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>45854.82177967593</v>
+        <v>45889.85904239583</v>
       </c>
       <c r="G106" t="n">
-        <v>18.26</v>
+        <v>31.61</v>
       </c>
       <c r="H106" t="n">
-        <v>23</v>
+        <v>26.02</v>
       </c>
       <c r="I106" t="n">
         <v>10</v>
@@ -5660,18 +5660,18 @@
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>2.59</v>
+        <v>-1.77</v>
       </c>
       <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="n">
-        <v>1923259795</v>
+        <v>1867197360</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5680,19 +5680,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.4424</v>
+        <v>0.0765</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>45853.65609353009</v>
+        <v>45818.80265583334</v>
       </c>
       <c r="G107" t="n">
-        <v>22.59</v>
+        <v>131.96</v>
       </c>
       <c r="H107" t="n">
-        <v>24.41</v>
+        <v>153.77</v>
       </c>
       <c r="I107" t="n">
-        <v>9.99</v>
+        <v>10.09</v>
       </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
@@ -5709,18 +5709,18 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.67</v>
       </c>
       <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="n">
-        <v>1642762235</v>
+        <v>2017852950</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5729,19 +5729,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.1572</v>
+        <v>1</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>45692.86612574074</v>
+        <v>45910.65507498843</v>
       </c>
       <c r="G108" t="n">
-        <v>127.16</v>
+        <v>37.44</v>
       </c>
       <c r="H108" t="n">
-        <v>120.39</v>
+        <v>46.95</v>
       </c>
       <c r="I108" t="n">
-        <v>19.99</v>
+        <v>37.44</v>
       </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
@@ -5758,18 +5758,18 @@
         <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>-1.06</v>
+        <v>9.51</v>
       </c>
       <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="n">
-        <v>2065642904</v>
+        <v>1642762235</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>IAPD.AS</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5778,19 +5778,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.1572</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>45936.61247836806</v>
+        <v>45692.86612574074</v>
       </c>
       <c r="G109" t="n">
-        <v>22.935</v>
+        <v>127.16</v>
       </c>
       <c r="H109" t="n">
-        <v>23.005</v>
+        <v>121.13</v>
       </c>
       <c r="I109" t="n">
-        <v>15</v>
+        <v>19.99</v>
       </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
@@ -5807,18 +5807,18 @@
         <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>-0.12</v>
+        <v>-0.95</v>
       </c>
       <c r="Q109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="n">
-        <v>2045990228</v>
+        <v>1666461140</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5827,19 +5827,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.0839</v>
+        <v>0.2651</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>45925.79958348379</v>
+        <v>45708.68207092593</v>
       </c>
       <c r="G110" t="n">
-        <v>36.75</v>
+        <v>37.7</v>
       </c>
       <c r="H110" t="n">
-        <v>41.28</v>
+        <v>26.02</v>
       </c>
       <c r="I110" t="n">
-        <v>3.08</v>
+        <v>9.99</v>
       </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
@@ -5856,18 +5856,18 @@
         <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>0.38</v>
+        <v>-3.09</v>
       </c>
       <c r="Q110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="n">
-        <v>1666459270</v>
+        <v>1744879358</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5876,19 +5876,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.5636</v>
+        <v>0.0247</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>45708.68166530092</v>
+        <v>45751.73925940973</v>
       </c>
       <c r="G111" t="n">
-        <v>17.18</v>
+        <v>148.09</v>
       </c>
       <c r="H111" t="n">
-        <v>24.41</v>
+        <v>295.11</v>
       </c>
       <c r="I111" t="n">
-        <v>9.68</v>
+        <v>3.66</v>
       </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
@@ -5905,18 +5905,18 @@
         <v>0</v>
       </c>
       <c r="P111" t="n">
-        <v>4.08</v>
+        <v>3.63</v>
       </c>
       <c r="Q111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="n">
-        <v>2047825292</v>
+        <v>2042956616</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>BLX</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5925,19 +5925,19 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.3157</v>
+        <v>0.1592</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>45926.66222740741</v>
+        <v>45924.69943638889</v>
       </c>
       <c r="G112" t="n">
-        <v>47.56</v>
+        <v>62.88</v>
       </c>
       <c r="H112" t="n">
-        <v>44.62</v>
+        <v>61.52</v>
       </c>
       <c r="I112" t="n">
-        <v>15.01</v>
+        <v>10.01</v>
       </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
@@ -5954,18 +5954,18 @@
         <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>-0.92</v>
+        <v>-0.22</v>
       </c>
       <c r="Q112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="n">
-        <v>2066990620</v>
+        <v>1495551484</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5974,19 +5974,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.1541</v>
+        <v>0.1914</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>45936.87171386574</v>
+        <v>45580.70648087963</v>
       </c>
       <c r="G113" t="n">
-        <v>64.88</v>
+        <v>135.82</v>
       </c>
       <c r="H113" t="n">
-        <v>64.26000000000001</v>
+        <v>121.13</v>
       </c>
       <c r="I113" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
@@ -6003,18 +6003,18 @@
         <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>-0.1</v>
+        <v>-2.82</v>
       </c>
       <c r="Q113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="n">
-        <v>1824475555</v>
+        <v>1923259795</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6023,19 +6023,19 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1</v>
+        <v>0.4424</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>45792.64702015046</v>
+        <v>45853.65609353009</v>
       </c>
       <c r="G114" t="n">
-        <v>21.66</v>
+        <v>22.59</v>
       </c>
       <c r="H114" t="n">
-        <v>19.24</v>
+        <v>24.06</v>
       </c>
       <c r="I114" t="n">
-        <v>21.66</v>
+        <v>9.99</v>
       </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
@@ -6052,18 +6052,18 @@
         <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>-2.42</v>
+        <v>0.65</v>
       </c>
       <c r="Q114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="n">
-        <v>2020498309</v>
+        <v>2050937088</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>BBAR</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6072,19 +6072,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.0131</v>
+        <v>0.0984</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>45911.68944190972</v>
+        <v>45929.65204666667</v>
       </c>
       <c r="G115" t="n">
-        <v>9.890000000000001</v>
+        <v>86.06999999999999</v>
       </c>
       <c r="H115" t="n">
-        <v>9.49</v>
+        <v>81.605</v>
       </c>
       <c r="I115" t="n">
-        <v>0.13</v>
+        <v>10</v>
       </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
@@ -6101,18 +6101,18 @@
         <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>-0.01</v>
+        <v>-0.68</v>
       </c>
       <c r="Q115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="n">
-        <v>2017778050</v>
+        <v>1744767540</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6121,19 +6121,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.3611</v>
+        <v>0.643</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>45910.64665976852</v>
+        <v>45751.72316712963</v>
       </c>
       <c r="G116" t="n">
-        <v>27.91</v>
+        <v>15.55</v>
       </c>
       <c r="H116" t="n">
-        <v>26.35</v>
+        <v>22.51</v>
       </c>
       <c r="I116" t="n">
-        <v>10.08</v>
+        <v>10</v>
       </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
@@ -6150,18 +6150,18 @@
         <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>-0.57</v>
+        <v>4.47</v>
       </c>
       <c r="Q116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="n">
-        <v>1621495187</v>
+        <v>2076201130</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6170,19 +6170,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.2318</v>
+        <v>0.499</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>45678.83178196759</v>
+        <v>45939.75708394676</v>
       </c>
       <c r="G117" t="n">
-        <v>43.27</v>
+        <v>20.04</v>
       </c>
       <c r="H117" t="n">
-        <v>26.35</v>
+        <v>19.34</v>
       </c>
       <c r="I117" t="n">
-        <v>10.03</v>
+        <v>10</v>
       </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
@@ -6199,18 +6199,18 @@
         <v>0</v>
       </c>
       <c r="P117" t="n">
-        <v>-3.92</v>
+        <v>-0.35</v>
       </c>
       <c r="Q117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="n">
-        <v>1880441651</v>
+        <v>1754304266</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6219,19 +6219,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1</v>
+        <v>0.7137</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>45825.89055887731</v>
+        <v>45755.88055112268</v>
       </c>
       <c r="G118" t="n">
-        <v>21.21</v>
+        <v>14</v>
       </c>
       <c r="H118" t="n">
-        <v>19.24</v>
+        <v>22.51</v>
       </c>
       <c r="I118" t="n">
-        <v>21.21</v>
+        <v>9.99</v>
       </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
@@ -6248,18 +6248,18 @@
         <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>-1.97</v>
+        <v>6.08</v>
       </c>
       <c r="Q118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="n">
-        <v>1989207013</v>
+        <v>1880441651</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>JKS</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6268,19 +6268,19 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.4133</v>
+        <v>1</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>45894.65354606482</v>
+        <v>45825.89055887731</v>
       </c>
       <c r="G119" t="n">
-        <v>24.19</v>
+        <v>21.21</v>
       </c>
       <c r="H119" t="n">
-        <v>23.8</v>
+        <v>19.75</v>
       </c>
       <c r="I119" t="n">
-        <v>10</v>
+        <v>21.21</v>
       </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
@@ -6297,7 +6297,7 @@
         <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>-0.16</v>
+        <v>-1.46</v>
       </c>
       <c r="Q119" t="inlineStr"/>
     </row>
@@ -6326,7 +6326,7 @@
         <v>86.41</v>
       </c>
       <c r="H120" t="n">
-        <v>84.605</v>
+        <v>81.605</v>
       </c>
       <c r="I120" t="n">
         <v>9.99</v>
@@ -6346,18 +6346,18 @@
         <v>0</v>
       </c>
       <c r="P120" t="n">
-        <v>-0.27</v>
+        <v>-0.61</v>
       </c>
       <c r="Q120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="n">
-        <v>1869077157</v>
+        <v>1976499401</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6366,19 +6366,19 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.3061</v>
+        <v>0.8064</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>45819.6742621412</v>
+        <v>45884.83731814815</v>
       </c>
       <c r="G121" t="n">
-        <v>13.285</v>
+        <v>49.6</v>
       </c>
       <c r="H121" t="n">
-        <v>15.685</v>
+        <v>48.43</v>
       </c>
       <c r="I121" t="n">
-        <v>4.69</v>
+        <v>40</v>
       </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
@@ -6395,18 +6395,18 @@
         <v>0</v>
       </c>
       <c r="P121" t="n">
-        <v>0.88</v>
+        <v>-0.95</v>
       </c>
       <c r="Q121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="n">
-        <v>1867193304</v>
+        <v>1843474191</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6415,19 +6415,19 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.1337</v>
+        <v>0.9372</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>45818.8008296412</v>
+        <v>45804.66699503472</v>
       </c>
       <c r="G122" t="n">
-        <v>17.64</v>
+        <v>21.33</v>
       </c>
       <c r="H122" t="n">
-        <v>19.95</v>
+        <v>24.06</v>
       </c>
       <c r="I122" t="n">
-        <v>2.36</v>
+        <v>19.99</v>
       </c>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
@@ -6444,18 +6444,18 @@
         <v>0</v>
       </c>
       <c r="P122" t="n">
-        <v>0.31</v>
+        <v>2.56</v>
       </c>
       <c r="Q122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="n">
-        <v>1923246263</v>
+        <v>1993382859</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6464,19 +6464,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1</v>
+        <v>0.0779</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>45853.6538128125</v>
+        <v>45896.66809304398</v>
       </c>
       <c r="G123" t="n">
-        <v>21.17</v>
+        <v>128.25</v>
       </c>
       <c r="H123" t="n">
-        <v>19.24</v>
+        <v>121.13</v>
       </c>
       <c r="I123" t="n">
-        <v>21.17</v>
+        <v>9.99</v>
       </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
@@ -6493,18 +6493,18 @@
         <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>-1.93</v>
+        <v>-0.55</v>
       </c>
       <c r="Q123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="n">
-        <v>1559803221</v>
+        <v>1845429956</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6513,19 +6513,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.092</v>
+        <v>0.4821</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>45628.85951927083</v>
+        <v>45805.66180811343</v>
       </c>
       <c r="G124" t="n">
-        <v>162.85</v>
+        <v>13.275</v>
       </c>
       <c r="H124" t="n">
-        <v>152.68</v>
+        <v>16.645</v>
       </c>
       <c r="I124" t="n">
-        <v>14.98</v>
+        <v>7.28</v>
       </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
@@ -6542,18 +6542,18 @@
         <v>0</v>
       </c>
       <c r="P124" t="n">
-        <v>-0.93</v>
+        <v>2.04</v>
       </c>
       <c r="Q124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="n">
-        <v>1644788775</v>
+        <v>1635194117</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6562,19 +6562,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.2479</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>45693.85093391204</v>
+        <v>45687.85228493056</v>
       </c>
       <c r="G125" t="n">
-        <v>144.94</v>
+        <v>40.33</v>
       </c>
       <c r="H125" t="n">
-        <v>152.68</v>
+        <v>26.02</v>
       </c>
       <c r="I125" t="n">
-        <v>10.99</v>
+        <v>10</v>
       </c>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
@@ -6591,18 +6591,18 @@
         <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>0.58</v>
+        <v>-3.55</v>
       </c>
       <c r="Q125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="n">
-        <v>2091093343</v>
+        <v>2035163256</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6611,19 +6611,19 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.2366</v>
+        <v>0.0951</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>45945.66190688658</v>
+        <v>45919.66675122685</v>
       </c>
       <c r="G126" t="n">
-        <v>42.25</v>
+        <v>88.91</v>
       </c>
       <c r="H126" t="n">
-        <v>41.02</v>
+        <v>81.605</v>
       </c>
       <c r="I126" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
@@ -6640,18 +6640,18 @@
         <v>0</v>
       </c>
       <c r="P126" t="n">
-        <v>-0.29</v>
+        <v>-0.98</v>
       </c>
       <c r="Q126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="n">
-        <v>2072501999</v>
+        <v>2045991969</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6660,19 +6660,19 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.0121</v>
+        <v>0.4928</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>45938.67873797454</v>
+        <v>45925.80038483796</v>
       </c>
       <c r="G127" t="n">
-        <v>844.9</v>
+        <v>20.29</v>
       </c>
       <c r="H127" t="n">
-        <v>877.2</v>
+        <v>19.34</v>
       </c>
       <c r="I127" t="n">
-        <v>11.95</v>
+        <v>10</v>
       </c>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
@@ -6689,18 +6689,18 @@
         <v>0</v>
       </c>
       <c r="P127" t="n">
-        <v>0.37</v>
+        <v>-0.47</v>
       </c>
       <c r="Q127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="n">
-        <v>2045991969</v>
+        <v>2099892569</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6709,19 +6709,19 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.4928</v>
+        <v>0.1057</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>45925.80038483796</v>
+        <v>45947.69061754629</v>
       </c>
       <c r="G128" t="n">
-        <v>20.29</v>
+        <v>80.62</v>
       </c>
       <c r="H128" t="n">
-        <v>19.95</v>
+        <v>81.605</v>
       </c>
       <c r="I128" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
@@ -6738,18 +6738,18 @@
         <v>0</v>
       </c>
       <c r="P128" t="n">
-        <v>-0.17</v>
+        <v>0.03</v>
       </c>
       <c r="Q128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="n">
-        <v>1680993370</v>
+        <v>1923246263</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6761,16 +6761,16 @@
         <v>1</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>45716.85638861111</v>
+        <v>45853.6538128125</v>
       </c>
       <c r="G129" t="n">
-        <v>44.49</v>
+        <v>21.17</v>
       </c>
       <c r="H129" t="n">
-        <v>54.52</v>
+        <v>19.75</v>
       </c>
       <c r="I129" t="n">
-        <v>44.49</v>
+        <v>21.17</v>
       </c>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
@@ -6787,7 +6787,7 @@
         <v>0</v>
       </c>
       <c r="P129" t="n">
-        <v>10.03</v>
+        <v>-1.42</v>
       </c>
       <c r="Q129" t="inlineStr"/>
     </row>
@@ -6816,7 +6816,7 @@
         <v>30.91</v>
       </c>
       <c r="H130" t="n">
-        <v>31.67</v>
+        <v>31.63</v>
       </c>
       <c r="I130" t="n">
         <v>10.01</v>
@@ -6836,18 +6836,18 @@
         <v>0</v>
       </c>
       <c r="P130" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="Q130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="n">
-        <v>2066988146</v>
+        <v>1727563010</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6856,19 +6856,19 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.102</v>
+        <v>1</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>45936.870276875</v>
+        <v>45743.76106726852</v>
       </c>
       <c r="G131" t="n">
-        <v>98.06</v>
+        <v>46.11</v>
       </c>
       <c r="H131" t="n">
-        <v>96.20999999999999</v>
+        <v>54.39</v>
       </c>
       <c r="I131" t="n">
-        <v>10</v>
+        <v>46.11</v>
       </c>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
@@ -6885,18 +6885,18 @@
         <v>0</v>
       </c>
       <c r="P131" t="n">
-        <v>-0.19</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="Q131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="n">
-        <v>2020498366</v>
+        <v>2045990228</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>BBAR</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6905,19 +6905,19 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1</v>
+        <v>0.0839</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>45911.68945292824</v>
+        <v>45925.79958348379</v>
       </c>
       <c r="G132" t="n">
-        <v>9.880000000000001</v>
+        <v>36.75</v>
       </c>
       <c r="H132" t="n">
-        <v>9.49</v>
+        <v>42.12</v>
       </c>
       <c r="I132" t="n">
-        <v>9.880000000000001</v>
+        <v>3.08</v>
       </c>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
@@ -6934,14 +6934,14 @@
         <v>0</v>
       </c>
       <c r="P132" t="n">
-        <v>-0.39</v>
+        <v>0.45</v>
       </c>
       <c r="Q132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="n">
-        <v>2027639997</v>
+        <v>1824482557</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -6954,19 +6954,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.1558</v>
+        <v>0.2641</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>45916.65703747685</v>
+        <v>45792.64805195602</v>
       </c>
       <c r="G133" t="n">
-        <v>64.18000000000001</v>
+        <v>56.78</v>
       </c>
       <c r="H133" t="n">
-        <v>64.26000000000001</v>
+        <v>65</v>
       </c>
       <c r="I133" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
@@ -6983,18 +6983,18 @@
         <v>0</v>
       </c>
       <c r="P133" t="n">
-        <v>0.01</v>
+        <v>2.17</v>
       </c>
       <c r="Q133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="n">
-        <v>1358151307</v>
+        <v>2072501999</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -7003,19 +7003,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.1081</v>
+        <v>0.0121</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>45460.88529052083</v>
+        <v>45938.67873797454</v>
       </c>
       <c r="G134" t="n">
-        <v>165.93</v>
+        <v>844.9</v>
       </c>
       <c r="H134" t="n">
-        <v>152.68</v>
+        <v>875.4</v>
       </c>
       <c r="I134" t="n">
-        <v>17.94</v>
+        <v>11.95</v>
       </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
@@ -7032,18 +7032,18 @@
         <v>0</v>
       </c>
       <c r="P134" t="n">
-        <v>-1.43</v>
+        <v>0.35</v>
       </c>
       <c r="Q134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="n">
-        <v>2091123728</v>
+        <v>2002503461</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SQM</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7052,19 +7052,19 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.4406</v>
+        <v>0.0439</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>45945.66748809028</v>
+        <v>45902.65623520833</v>
       </c>
       <c r="G135" t="n">
-        <v>45.28</v>
+        <v>227.95</v>
       </c>
       <c r="H135" t="n">
-        <v>44.38</v>
+        <v>295.11</v>
       </c>
       <c r="I135" t="n">
-        <v>19.95</v>
+        <v>10.01</v>
       </c>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
@@ -7081,18 +7081,18 @@
         <v>0</v>
       </c>
       <c r="P135" t="n">
-        <v>-0.4</v>
+        <v>2.95</v>
       </c>
       <c r="Q135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="n">
-        <v>1883977086</v>
+        <v>1559803221</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7101,19 +7101,19 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1</v>
+        <v>0.092</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>45827.66106613426</v>
+        <v>45628.85951927083</v>
       </c>
       <c r="G136" t="n">
-        <v>12.875</v>
+        <v>162.85</v>
       </c>
       <c r="H136" t="n">
-        <v>15.685</v>
+        <v>153.77</v>
       </c>
       <c r="I136" t="n">
-        <v>14.86</v>
+        <v>14.98</v>
       </c>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
@@ -7130,18 +7130,18 @@
         <v>0</v>
       </c>
       <c r="P136" t="n">
-        <v>3.35</v>
+        <v>-0.83</v>
       </c>
       <c r="Q136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="n">
-        <v>1993444707</v>
+        <v>1984829391</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>BBAR</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7150,19 +7150,19 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.8051</v>
+        <v>0.0512</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>45896.6743321875</v>
+        <v>45890.71798858796</v>
       </c>
       <c r="G137" t="n">
-        <v>12.42</v>
+        <v>195.52</v>
       </c>
       <c r="H137" t="n">
-        <v>9.49</v>
+        <v>231.77</v>
       </c>
       <c r="I137" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
@@ -7179,18 +7179,18 @@
         <v>0</v>
       </c>
       <c r="P137" t="n">
-        <v>-2.36</v>
+        <v>1.86</v>
       </c>
       <c r="Q137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="n">
-        <v>2066989908</v>
+        <v>1796453499</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7199,19 +7199,19 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.3946</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>45936.87125002315</v>
+        <v>45777.64668229167</v>
       </c>
       <c r="G138" t="n">
-        <v>25.34</v>
+        <v>15.57</v>
       </c>
       <c r="H138" t="n">
-        <v>24.41</v>
+        <v>19.34</v>
       </c>
       <c r="I138" t="n">
-        <v>10</v>
+        <v>8.01</v>
       </c>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
@@ -7228,18 +7228,18 @@
         <v>0</v>
       </c>
       <c r="P138" t="n">
-        <v>-0.37</v>
+        <v>1.94</v>
       </c>
       <c r="Q138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="n">
-        <v>1888686062</v>
+        <v>1997552824</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7248,19 +7248,19 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.2903</v>
+        <v>0.0429</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>45831.64964792824</v>
+        <v>45898.65627293981</v>
       </c>
       <c r="G139" t="n">
-        <v>34.36</v>
+        <v>233.17</v>
       </c>
       <c r="H139" t="n">
-        <v>26.35</v>
+        <v>295.11</v>
       </c>
       <c r="I139" t="n">
-        <v>9.970000000000001</v>
+        <v>10</v>
       </c>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
@@ -7277,18 +7277,18 @@
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>-2.32</v>
+        <v>2.66</v>
       </c>
       <c r="Q139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="n">
-        <v>1867458993</v>
+        <v>1867462173</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7297,19 +7297,19 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.3417</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>45818.90699613426</v>
+        <v>45818.90866184028</v>
       </c>
       <c r="G140" t="n">
-        <v>58.53</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="H140" t="n">
-        <v>64.26000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="I140" t="n">
-        <v>20</v>
+        <v>0.65</v>
       </c>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
@@ -7326,18 +7326,18 @@
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>1.96</v>
+        <v>0.17</v>
       </c>
       <c r="Q140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="n">
-        <v>1983186744</v>
+        <v>2017777441</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -7346,16 +7346,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.3162</v>
+        <v>0.4582</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>45889.85904239583</v>
+        <v>45910.64656457176</v>
       </c>
       <c r="G141" t="n">
-        <v>31.61</v>
+        <v>21.82</v>
       </c>
       <c r="H141" t="n">
-        <v>26.35</v>
+        <v>22.51</v>
       </c>
       <c r="I141" t="n">
         <v>10</v>
@@ -7375,18 +7375,18 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>-1.67</v>
+        <v>0.31</v>
       </c>
       <c r="Q141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="n">
-        <v>1923250768</v>
+        <v>1653137218</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7395,19 +7395,19 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.87</v>
+        <v>0.277</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>45853.65447396991</v>
+        <v>45699.85152199074</v>
       </c>
       <c r="G142" t="n">
-        <v>12.76</v>
+        <v>36.1</v>
       </c>
       <c r="H142" t="n">
-        <v>15.685</v>
+        <v>26.02</v>
       </c>
       <c r="I142" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
@@ -7424,18 +7424,18 @@
         <v>0</v>
       </c>
       <c r="P142" t="n">
-        <v>2.84</v>
+        <v>-2.79</v>
       </c>
       <c r="Q142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="n">
-        <v>1796453499</v>
+        <v>1923271589</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -7444,19 +7444,19 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.4478</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>45777.64668229167</v>
+        <v>45853.65794861111</v>
       </c>
       <c r="G143" t="n">
-        <v>15.57</v>
+        <v>44.66</v>
       </c>
       <c r="H143" t="n">
-        <v>19.95</v>
+        <v>56.8</v>
       </c>
       <c r="I143" t="n">
-        <v>8.01</v>
+        <v>20</v>
       </c>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
@@ -7473,18 +7473,18 @@
         <v>0</v>
       </c>
       <c r="P143" t="n">
-        <v>2.26</v>
+        <v>5.44</v>
       </c>
       <c r="Q143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="n">
-        <v>2079414382</v>
+        <v>2047814173</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>IAPD.AS</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7493,19 +7493,19 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.0351</v>
+        <v>0.5688</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>45940.73297075232</v>
+        <v>45926.6592943287</v>
       </c>
       <c r="G144" t="n">
-        <v>285.2</v>
+        <v>22.46</v>
       </c>
       <c r="H144" t="n">
-        <v>300.11</v>
+        <v>22.975</v>
       </c>
       <c r="I144" t="n">
-        <v>10.01</v>
+        <v>15</v>
       </c>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
@@ -7522,18 +7522,18 @@
         <v>0</v>
       </c>
       <c r="P144" t="n">
-        <v>0.52</v>
+        <v>0.17</v>
       </c>
       <c r="Q144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="n">
-        <v>2050937088</v>
+        <v>1680993370</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>BTCE.DE</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -7542,19 +7542,19 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.0984</v>
+        <v>1</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>45929.65204666667</v>
+        <v>45716.85638861111</v>
       </c>
       <c r="G145" t="n">
-        <v>86.06999999999999</v>
+        <v>44.49</v>
       </c>
       <c r="H145" t="n">
-        <v>84.605</v>
+        <v>54.39</v>
       </c>
       <c r="I145" t="n">
-        <v>10</v>
+        <v>44.49</v>
       </c>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
@@ -7571,7 +7571,7 @@
         <v>0</v>
       </c>
       <c r="P145" t="n">
-        <v>-0.34</v>
+        <v>9.9</v>
       </c>
       <c r="Q145" t="inlineStr"/>
     </row>
@@ -7600,7 +7600,7 @@
         <v>42.2</v>
       </c>
       <c r="H146" t="n">
-        <v>49.16</v>
+        <v>46.95</v>
       </c>
       <c r="I146" t="n">
         <v>42.2</v>
@@ -7620,18 +7620,18 @@
         <v>0</v>
       </c>
       <c r="P146" t="n">
-        <v>6.96</v>
+        <v>4.75</v>
       </c>
       <c r="Q146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="n">
-        <v>1824482557</v>
+        <v>2080269311</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -7640,19 +7640,19 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.2641</v>
+        <v>1</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>45792.64805195602</v>
+        <v>45940.886384375</v>
       </c>
       <c r="G147" t="n">
-        <v>56.78</v>
+        <v>52.53</v>
       </c>
       <c r="H147" t="n">
-        <v>64.26000000000001</v>
+        <v>54.39</v>
       </c>
       <c r="I147" t="n">
-        <v>15</v>
+        <v>52.53</v>
       </c>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
@@ -7669,18 +7669,18 @@
         <v>0</v>
       </c>
       <c r="P147" t="n">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="Q147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="n">
-        <v>1744767540</v>
+        <v>2072487323</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7689,19 +7689,19 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.643</v>
+        <v>0.4062</v>
       </c>
       <c r="F148" s="2" t="n">
-        <v>45751.72316712963</v>
+        <v>45938.67565716435</v>
       </c>
       <c r="G148" t="n">
-        <v>15.55</v>
+        <v>24.64</v>
       </c>
       <c r="H148" t="n">
-        <v>23</v>
+        <v>23.11</v>
       </c>
       <c r="I148" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
@@ -7718,18 +7718,18 @@
         <v>0</v>
       </c>
       <c r="P148" t="n">
-        <v>4.79</v>
+        <v>-0.62</v>
       </c>
       <c r="Q148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="n">
-        <v>2002501482</v>
+        <v>2091099733</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>BBAR</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7738,19 +7738,19 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.0526</v>
+        <v>1</v>
       </c>
       <c r="F149" s="2" t="n">
-        <v>45902.65588916666</v>
+        <v>45945.6631174537</v>
       </c>
       <c r="G149" t="n">
-        <v>190.17</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="H149" t="n">
-        <v>237.16</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I149" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
@@ -7767,18 +7767,18 @@
         <v>0</v>
       </c>
       <c r="P149" t="n">
-        <v>2.47</v>
+        <v>-0.24</v>
       </c>
       <c r="Q149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="n">
-        <v>2002503461</v>
+        <v>1880442840</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7787,19 +7787,19 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.0439</v>
+        <v>0.2535</v>
       </c>
       <c r="F150" s="2" t="n">
-        <v>45902.65623520833</v>
+        <v>45825.89113450232</v>
       </c>
       <c r="G150" t="n">
-        <v>227.95</v>
+        <v>59.15</v>
       </c>
       <c r="H150" t="n">
-        <v>300.11</v>
+        <v>65</v>
       </c>
       <c r="I150" t="n">
-        <v>10.01</v>
+        <v>14.99</v>
       </c>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
@@ -7816,18 +7816,18 @@
         <v>0</v>
       </c>
       <c r="P150" t="n">
-        <v>3.16</v>
+        <v>1.49</v>
       </c>
       <c r="Q150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="n">
-        <v>1727574394</v>
+        <v>1563288050</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7836,19 +7836,19 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1</v>
+        <v>0.0626</v>
       </c>
       <c r="F151" s="2" t="n">
-        <v>45743.76658678241</v>
+        <v>45630.85583428241</v>
       </c>
       <c r="G151" t="n">
-        <v>21.13</v>
+        <v>159.74</v>
       </c>
       <c r="H151" t="n">
-        <v>19.24</v>
+        <v>153.77</v>
       </c>
       <c r="I151" t="n">
-        <v>21.13</v>
+        <v>10</v>
       </c>
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
@@ -7865,18 +7865,18 @@
         <v>0</v>
       </c>
       <c r="P151" t="n">
-        <v>-1.89</v>
+        <v>-0.37</v>
       </c>
       <c r="Q151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="n">
-        <v>1843474191</v>
+        <v>1824475555</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7885,19 +7885,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.9372</v>
+        <v>1</v>
       </c>
       <c r="F152" s="2" t="n">
-        <v>45804.66699503472</v>
+        <v>45792.64702015046</v>
       </c>
       <c r="G152" t="n">
-        <v>21.33</v>
+        <v>21.66</v>
       </c>
       <c r="H152" t="n">
-        <v>24.41</v>
+        <v>19.75</v>
       </c>
       <c r="I152" t="n">
-        <v>19.99</v>
+        <v>21.66</v>
       </c>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
@@ -7914,18 +7914,18 @@
         <v>0</v>
       </c>
       <c r="P152" t="n">
-        <v>2.89</v>
+        <v>-1.91</v>
       </c>
       <c r="Q152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="n">
-        <v>1928218937</v>
+        <v>2047758738</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7934,19 +7934,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1</v>
+        <v>0.0365</v>
       </c>
       <c r="F153" s="2" t="n">
-        <v>45855.75970359953</v>
+        <v>45926.65183609954</v>
       </c>
       <c r="G153" t="n">
-        <v>20.24</v>
+        <v>274.22</v>
       </c>
       <c r="H153" t="n">
-        <v>19.24</v>
+        <v>295.11</v>
       </c>
       <c r="I153" t="n">
-        <v>20.24</v>
+        <v>10.01</v>
       </c>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
@@ -7963,18 +7963,18 @@
         <v>0</v>
       </c>
       <c r="P153" t="n">
-        <v>-1</v>
+        <v>0.76</v>
       </c>
       <c r="Q153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="n">
-        <v>1895465445</v>
+        <v>2002501482</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7983,16 +7983,16 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.2987</v>
+        <v>0.0526</v>
       </c>
       <c r="F154" s="2" t="n">
-        <v>45834.6539484375</v>
+        <v>45902.65588916666</v>
       </c>
       <c r="G154" t="n">
-        <v>33.47</v>
+        <v>190.17</v>
       </c>
       <c r="H154" t="n">
-        <v>26.35</v>
+        <v>231.77</v>
       </c>
       <c r="I154" t="n">
         <v>10</v>
@@ -8012,18 +8012,18 @@
         <v>0</v>
       </c>
       <c r="P154" t="n">
-        <v>-2.13</v>
+        <v>2.19</v>
       </c>
       <c r="Q154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="n">
-        <v>1923256224</v>
+        <v>1867194722</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -8032,19 +8032,19 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.6457000000000001</v>
+        <v>1</v>
       </c>
       <c r="F155" s="2" t="n">
-        <v>45853.65543140046</v>
+        <v>45818.80135700232</v>
       </c>
       <c r="G155" t="n">
-        <v>30.97</v>
+        <v>21.27</v>
       </c>
       <c r="H155" t="n">
-        <v>26.35</v>
+        <v>19.75</v>
       </c>
       <c r="I155" t="n">
-        <v>20</v>
+        <v>21.27</v>
       </c>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
@@ -8061,18 +8061,18 @@
         <v>0</v>
       </c>
       <c r="P155" t="n">
-        <v>-2.99</v>
+        <v>-1.52</v>
       </c>
       <c r="Q155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="n">
-        <v>1806979127</v>
+        <v>1997485943</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -8081,16 +8081,16 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.6361</v>
+        <v>0.5157</v>
       </c>
       <c r="F156" s="2" t="n">
-        <v>45783.83125244213</v>
+        <v>45898.65185685185</v>
       </c>
       <c r="G156" t="n">
-        <v>15.72</v>
+        <v>19.39</v>
       </c>
       <c r="H156" t="n">
-        <v>23</v>
+        <v>19.34</v>
       </c>
       <c r="I156" t="n">
         <v>10</v>
@@ -8110,18 +8110,18 @@
         <v>0</v>
       </c>
       <c r="P156" t="n">
-        <v>4.63</v>
+        <v>-0.03</v>
       </c>
       <c r="Q156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="n">
-        <v>2065818035</v>
+        <v>1806980496</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>JKS</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -8130,19 +8130,19 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.3984</v>
+        <v>1</v>
       </c>
       <c r="F157" s="2" t="n">
-        <v>45936.64826241898</v>
+        <v>45783.83190503472</v>
       </c>
       <c r="G157" t="n">
-        <v>25.1</v>
+        <v>16.12</v>
       </c>
       <c r="H157" t="n">
-        <v>23.8</v>
+        <v>19.34</v>
       </c>
       <c r="I157" t="n">
-        <v>10</v>
+        <v>16.12</v>
       </c>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
@@ -8159,18 +8159,18 @@
         <v>0</v>
       </c>
       <c r="P157" t="n">
-        <v>-0.52</v>
+        <v>3.22</v>
       </c>
       <c r="Q157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="n">
-        <v>1867196288</v>
+        <v>1644788775</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -8179,19 +8179,19 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.5568</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="F158" s="2" t="n">
-        <v>45818.80209099537</v>
+        <v>45693.85093391204</v>
       </c>
       <c r="G158" t="n">
-        <v>41.99</v>
+        <v>144.94</v>
       </c>
       <c r="H158" t="n">
-        <v>56.33</v>
+        <v>153.77</v>
       </c>
       <c r="I158" t="n">
-        <v>23.38</v>
+        <v>10.99</v>
       </c>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
@@ -8208,18 +8208,18 @@
         <v>0</v>
       </c>
       <c r="P158" t="n">
-        <v>7.98</v>
+        <v>0.67</v>
       </c>
       <c r="Q158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="n">
-        <v>2060620530</v>
+        <v>2025662892</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>BLX</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -8228,19 +8228,19 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.2207</v>
+        <v>0.8196</v>
       </c>
       <c r="F159" s="2" t="n">
-        <v>45932.89856876157</v>
+        <v>45915.72913914352</v>
       </c>
       <c r="G159" t="n">
-        <v>45.28</v>
+        <v>24.39</v>
       </c>
       <c r="H159" t="n">
-        <v>44.62</v>
+        <v>23.11</v>
       </c>
       <c r="I159" t="n">
-        <v>9.99</v>
+        <v>19.99</v>
       </c>
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
@@ -8257,18 +8257,18 @@
         <v>0</v>
       </c>
       <c r="P159" t="n">
-        <v>-0.14</v>
+        <v>-1.05</v>
       </c>
       <c r="Q159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="n">
-        <v>2048501554</v>
+        <v>2042971604</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>JKS</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -8277,19 +8277,19 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.4118</v>
+        <v>0.3901</v>
       </c>
       <c r="F160" s="2" t="n">
-        <v>45926.83927949074</v>
+        <v>45924.70406969907</v>
       </c>
       <c r="G160" t="n">
-        <v>24.28</v>
+        <v>25.66</v>
       </c>
       <c r="H160" t="n">
-        <v>23.8</v>
+        <v>23.11</v>
       </c>
       <c r="I160" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
@@ -8306,18 +8306,18 @@
         <v>0</v>
       </c>
       <c r="P160" t="n">
-        <v>-0.2</v>
+        <v>-0.99</v>
       </c>
       <c r="Q160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="n">
-        <v>2047758738</v>
+        <v>1928218937</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -8326,19 +8326,19 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.0365</v>
+        <v>1</v>
       </c>
       <c r="F161" s="2" t="n">
-        <v>45926.65183609954</v>
+        <v>45855.75970359953</v>
       </c>
       <c r="G161" t="n">
-        <v>274.22</v>
+        <v>20.24</v>
       </c>
       <c r="H161" t="n">
-        <v>300.11</v>
+        <v>19.75</v>
       </c>
       <c r="I161" t="n">
-        <v>10.01</v>
+        <v>20.24</v>
       </c>
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
@@ -8355,18 +8355,18 @@
         <v>0</v>
       </c>
       <c r="P161" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.49</v>
       </c>
       <c r="Q161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="n">
-        <v>1824476420</v>
+        <v>1989207013</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>JKS</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -8375,19 +8375,19 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.1548</v>
+        <v>0.4133</v>
       </c>
       <c r="F162" s="2" t="n">
-        <v>45792.64714148148</v>
+        <v>45894.65354606482</v>
       </c>
       <c r="G162" t="n">
-        <v>129.17</v>
+        <v>24.19</v>
       </c>
       <c r="H162" t="n">
-        <v>152.68</v>
+        <v>23.11</v>
       </c>
       <c r="I162" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
@@ -8404,18 +8404,18 @@
         <v>0</v>
       </c>
       <c r="P162" t="n">
-        <v>3.63</v>
+        <v>-0.45</v>
       </c>
       <c r="Q162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="n">
-        <v>2095264263</v>
+        <v>2060624552</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>SQM</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -8424,19 +8424,19 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.2252</v>
+        <v>0.1676</v>
       </c>
       <c r="F163" s="2" t="n">
-        <v>45946.74280237268</v>
+        <v>45932.90130990741</v>
       </c>
       <c r="G163" t="n">
-        <v>44.39</v>
+        <v>59.7</v>
       </c>
       <c r="H163" t="n">
-        <v>44.38</v>
+        <v>61.52</v>
       </c>
       <c r="I163" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
@@ -8453,27 +8453,45 @@
         <v>0</v>
       </c>
       <c r="P163" t="n">
-        <v>-0.01</v>
+        <v>0.3</v>
       </c>
       <c r="Q163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr"/>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr"/>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
+      <c r="B164" t="n">
+        <v>1744930699</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>BND</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>1</v>
+      </c>
+      <c r="F164" s="2" t="n">
+        <v>45751.74534789352</v>
+      </c>
+      <c r="G164" t="n">
+        <v>74.13</v>
+      </c>
+      <c r="H164" t="n">
+        <v>74.88</v>
+      </c>
+      <c r="I164" t="n">
+        <v>74.13</v>
+      </c>
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
       <c r="M164" t="n">
         <v>0</v>
       </c>
@@ -8484,9 +8502,89 @@
         <v>0</v>
       </c>
       <c r="P164" t="n">
-        <v>158.27</v>
+        <v>0.75</v>
       </c>
       <c r="Q164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="n">
+        <v>2079414382</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>45940.73297075232</v>
+      </c>
+      <c r="G165" t="n">
+        <v>285.2</v>
+      </c>
+      <c r="H165" t="n">
+        <v>295.11</v>
+      </c>
+      <c r="I165" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Q165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" t="n">
+        <v>149.79</v>
+      </c>
+      <c r="Q166" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Stock Selection/OPEN POSITION.xlsx
+++ b/Stock Selection/OPEN POSITION.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q166"/>
+  <dimension ref="A1:Q206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,11 +522,11 @@
     <row r="2">
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="n">
-        <v>1883977044</v>
+        <v>2187239539</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>CSIQ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.345</v>
+        <v>0.4638</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45827.66105774305</v>
+        <v>45982.64886502315</v>
       </c>
       <c r="G2" t="n">
-        <v>12.88</v>
+        <v>21.53</v>
       </c>
       <c r="H2" t="n">
-        <v>16.645</v>
+        <v>24.89</v>
       </c>
       <c r="I2" t="n">
-        <v>5.13</v>
+        <v>9.99</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -564,18 +564,18 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="n">
-        <v>1882283184</v>
+        <v>2173074049</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -584,19 +584,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4835</v>
+        <v>0.1162</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45826.76569390047</v>
+        <v>45978.53673059028</v>
       </c>
       <c r="G3" t="n">
-        <v>20.69</v>
+        <v>73.77</v>
       </c>
       <c r="H3" t="n">
-        <v>22.51</v>
+        <v>67.745</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -613,18 +613,18 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.88</v>
+        <v>-0.96</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="n">
-        <v>2091105918</v>
+        <v>2099890750</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>IAPD.AS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -633,19 +633,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5535</v>
+        <v>0.1038</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45945.66408168981</v>
+        <v>45947.69026060185</v>
       </c>
       <c r="G4" t="n">
-        <v>23.185</v>
+        <v>96.38</v>
       </c>
       <c r="H4" t="n">
-        <v>22.975</v>
+        <v>99.8</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -662,18 +662,18 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.23</v>
+        <v>0.36</v>
       </c>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="n">
-        <v>1986476926</v>
+        <v>2050937088</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0.0984</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45891.66490212963</v>
+        <v>45929.65204666667</v>
       </c>
       <c r="G5" t="n">
-        <v>34.44</v>
+        <v>86.06999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>46.95</v>
+        <v>67.745</v>
       </c>
       <c r="I5" t="n">
-        <v>34.44</v>
+        <v>10</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -711,18 +711,18 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>12.51</v>
+        <v>-2.36</v>
       </c>
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="n">
-        <v>1843477152</v>
+        <v>1882283184</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.1198</v>
+        <v>0.4835</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45804.66724922453</v>
+        <v>45826.76569390047</v>
       </c>
       <c r="G6" t="n">
-        <v>17.86</v>
+        <v>20.69</v>
       </c>
       <c r="H6" t="n">
-        <v>19.34</v>
+        <v>24.43</v>
       </c>
       <c r="I6" t="n">
-        <v>2.14</v>
+        <v>10</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -760,18 +760,18 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.18</v>
+        <v>1.81</v>
       </c>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="n">
-        <v>1993444707</v>
+        <v>2045991969</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BBAR</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -780,16 +780,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.8051</v>
+        <v>0.4928</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45896.6743321875</v>
+        <v>45925.80038483796</v>
       </c>
       <c r="G7" t="n">
-        <v>12.42</v>
+        <v>20.29</v>
       </c>
       <c r="H7" t="n">
-        <v>9.380000000000001</v>
+        <v>21.12</v>
       </c>
       <c r="I7" t="n">
         <v>10</v>
@@ -809,18 +809,18 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.45</v>
+        <v>0.41</v>
       </c>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="n">
-        <v>1867458993</v>
+        <v>1978487977</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.3417</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45818.90699613426</v>
+        <v>45887.66311905093</v>
       </c>
       <c r="G8" t="n">
-        <v>58.53</v>
+        <v>127.06</v>
       </c>
       <c r="H8" t="n">
-        <v>65</v>
+        <v>105.97</v>
       </c>
       <c r="I8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -858,18 +858,18 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.21</v>
+        <v>-1.66</v>
       </c>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="n">
-        <v>2065818035</v>
+        <v>2035163256</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JKS</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -878,19 +878,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.3984</v>
+        <v>0.0951</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45936.64826241898</v>
+        <v>45919.66675122685</v>
       </c>
       <c r="G9" t="n">
-        <v>25.1</v>
+        <v>88.91</v>
       </c>
       <c r="H9" t="n">
-        <v>23.11</v>
+        <v>67.745</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -907,18 +907,18 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.79</v>
+        <v>-2.6</v>
       </c>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="n">
-        <v>1644796307</v>
+        <v>2152897258</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0.2516</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45693.85501710648</v>
+        <v>45968.67371078704</v>
       </c>
       <c r="G10" t="n">
-        <v>20.36</v>
+        <v>39.73</v>
       </c>
       <c r="H10" t="n">
-        <v>19.75</v>
+        <v>26.41</v>
       </c>
       <c r="I10" t="n">
-        <v>20.36</v>
+        <v>10</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -956,18 +956,18 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.61</v>
+        <v>-3.36</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="n">
-        <v>2091064900</v>
+        <v>2108027380</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>VALE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -976,19 +976,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.4294</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45945.66049490741</v>
+        <v>45951.66337512732</v>
       </c>
       <c r="G11" t="n">
-        <v>23.32</v>
+        <v>11.26</v>
       </c>
       <c r="H11" t="n">
-        <v>23.11</v>
+        <v>12.08</v>
       </c>
       <c r="I11" t="n">
-        <v>10.01</v>
+        <v>11.26</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -1005,18 +1005,18 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.09</v>
+        <v>0.82</v>
       </c>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
-        <v>1701100027</v>
+        <v>2170741178</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>WEN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1025,19 +1025,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.5043</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>45727.87202070602</v>
+        <v>45975.82252663194</v>
       </c>
       <c r="G12" t="n">
-        <v>19.2</v>
+        <v>8.59</v>
       </c>
       <c r="H12" t="n">
-        <v>22.51</v>
+        <v>7.91</v>
       </c>
       <c r="I12" t="n">
-        <v>9.68</v>
+        <v>8.59</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -1054,18 +1054,18 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.67</v>
+        <v>-0.68</v>
       </c>
       <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="n">
-        <v>2025661832</v>
+        <v>2191689046</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>WEN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1074,19 +1074,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.3235</v>
+        <v>0.2406</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>45915.72870862269</v>
+        <v>45985.81108717593</v>
       </c>
       <c r="G13" t="n">
-        <v>61.81</v>
+        <v>8.06</v>
       </c>
       <c r="H13" t="n">
-        <v>61.52</v>
+        <v>7.91</v>
       </c>
       <c r="I13" t="n">
-        <v>20</v>
+        <v>1.94</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -1103,18 +1103,18 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="n">
-        <v>1461331124</v>
+        <v>2170735067</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>CIG</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.3752</v>
+        <v>9</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>45553.65374138889</v>
+        <v>45975.8204810301</v>
       </c>
       <c r="G14" t="n">
-        <v>50.99</v>
+        <v>2.13</v>
       </c>
       <c r="H14" t="n">
-        <v>65</v>
+        <v>2.03</v>
       </c>
       <c r="I14" t="n">
-        <v>19.13</v>
+        <v>19.17</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -1152,18 +1152,18 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>5.26</v>
+        <v>-0.9</v>
       </c>
       <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="n">
-        <v>1923224670</v>
+        <v>2149012387</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>SGLD.L</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1172,19 +1172,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.2583</v>
+        <v>0.0259</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>45853.65359685185</v>
+        <v>45967.53095938657</v>
       </c>
       <c r="G15" t="n">
-        <v>58.05</v>
+        <v>386.71</v>
       </c>
       <c r="H15" t="n">
-        <v>65</v>
+        <v>393.97</v>
       </c>
       <c r="I15" t="n">
-        <v>14.99</v>
+        <v>10.02</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1201,18 +1201,18 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8</v>
+        <v>0.18</v>
       </c>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="n">
-        <v>2047825292</v>
+        <v>1662993636</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BLX</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.3157</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>45926.66222740741</v>
+        <v>45706.87026833333</v>
       </c>
       <c r="G16" t="n">
-        <v>47.56</v>
+        <v>20.65</v>
       </c>
       <c r="H16" t="n">
-        <v>44.72</v>
+        <v>17.52</v>
       </c>
       <c r="I16" t="n">
-        <v>15.01</v>
+        <v>20.65</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1250,18 +1250,18 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.89</v>
+        <v>-3.13</v>
       </c>
       <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="n">
-        <v>1806980482</v>
+        <v>1923256224</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1270,19 +1270,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.2406</v>
+        <v>0.6457000000000001</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>45783.83189613426</v>
+        <v>45853.65543140046</v>
       </c>
       <c r="G17" t="n">
-        <v>16.12</v>
+        <v>30.97</v>
       </c>
       <c r="H17" t="n">
-        <v>19.34</v>
+        <v>35.22</v>
       </c>
       <c r="I17" t="n">
-        <v>3.88</v>
+        <v>20</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1299,18 +1299,18 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.77</v>
+        <v>2.74</v>
       </c>
       <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="n">
-        <v>1744916497</v>
+        <v>2130416860</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1319,19 +1319,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45751.74231563658</v>
+        <v>45959.75112017361</v>
       </c>
       <c r="G18" t="n">
-        <v>17.54</v>
+        <v>18.34</v>
       </c>
       <c r="H18" t="n">
-        <v>24.06</v>
+        <v>17.52</v>
       </c>
       <c r="I18" t="n">
-        <v>17.54</v>
+        <v>9.99</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1348,14 +1348,14 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>6.52</v>
+        <v>-0.44</v>
       </c>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="n">
-        <v>2078840482</v>
+        <v>2060619876</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1368,16 +1368,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.4336</v>
+        <v>0.4178</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45940.66718949074</v>
+        <v>45932.89807736111</v>
       </c>
       <c r="G19" t="n">
-        <v>23.06</v>
+        <v>23.93</v>
       </c>
       <c r="H19" t="n">
-        <v>22.51</v>
+        <v>24.43</v>
       </c>
       <c r="I19" t="n">
         <v>10</v>
@@ -1397,18 +1397,18 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.24</v>
+        <v>0.21</v>
       </c>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="n">
-        <v>2078907475</v>
+        <v>2159083247</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PHGP.L</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1417,19 +1417,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.0537</v>
+        <v>1</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45940.67644164352</v>
+        <v>45972.55637631944</v>
       </c>
       <c r="G20" t="n">
-        <v>278.84</v>
+        <v>9.842000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>294.76</v>
+        <v>9.787000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>19.99</v>
+        <v>9.84</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1446,18 +1446,18 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.17</v>
+        <v>-0.05</v>
       </c>
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="n">
-        <v>1888700382</v>
+        <v>1843477152</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1466,19 +1466,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0.1198</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45831.65144708334</v>
+        <v>45804.66724922453</v>
       </c>
       <c r="G21" t="n">
-        <v>47.58</v>
+        <v>17.86</v>
       </c>
       <c r="H21" t="n">
-        <v>54.39</v>
+        <v>21.12</v>
       </c>
       <c r="I21" t="n">
-        <v>47.58</v>
+        <v>2.14</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1495,18 +1495,18 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>6.81</v>
+        <v>0.39</v>
       </c>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="n">
-        <v>2091086432</v>
+        <v>2187233945</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1515,19 +1515,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.1657</v>
+        <v>0.6067</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>45945.66072645834</v>
+        <v>45982.64814206018</v>
       </c>
       <c r="G22" t="n">
-        <v>60.4</v>
+        <v>24.72</v>
       </c>
       <c r="H22" t="n">
-        <v>61.52</v>
+        <v>24.9</v>
       </c>
       <c r="I22" t="n">
-        <v>10.01</v>
+        <v>15</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -1544,18 +1544,18 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="n">
-        <v>1978487977</v>
+        <v>2174828409</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>BVN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.6564</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>45887.66311905093</v>
+        <v>45978.88198976852</v>
       </c>
       <c r="G23" t="n">
-        <v>127.06</v>
+        <v>22.85</v>
       </c>
       <c r="H23" t="n">
-        <v>121.13</v>
+        <v>23.65</v>
       </c>
       <c r="I23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -1593,18 +1593,18 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.47</v>
+        <v>0.52</v>
       </c>
       <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="n">
-        <v>1843469729</v>
+        <v>2091063412</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.0423</v>
+        <v>0.4089</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45804.66615450232</v>
+        <v>45945.66023149306</v>
       </c>
       <c r="G24" t="n">
-        <v>156.9</v>
+        <v>24.44</v>
       </c>
       <c r="H24" t="n">
-        <v>231.77</v>
+        <v>24.9</v>
       </c>
       <c r="I24" t="n">
-        <v>6.64</v>
+        <v>9.99</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1642,18 +1642,18 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>3.16</v>
+        <v>0.19</v>
       </c>
       <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="n">
-        <v>2020498309</v>
+        <v>2107033904</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BBAR</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1662,19 +1662,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.0131</v>
+        <v>0.1028</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>45911.68944190972</v>
+        <v>45951.49965023148</v>
       </c>
       <c r="G25" t="n">
-        <v>9.890000000000001</v>
+        <v>83.205</v>
       </c>
       <c r="H25" t="n">
-        <v>9.380000000000001</v>
+        <v>67.745</v>
       </c>
       <c r="I25" t="n">
-        <v>0.13</v>
+        <v>9.99</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -1691,18 +1691,18 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.01</v>
+        <v>-2</v>
       </c>
       <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="n">
-        <v>1845429980</v>
+        <v>2050990570</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>BLX</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1711,19 +1711,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0.2121</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>45805.66181400463</v>
+        <v>45929.65780017361</v>
       </c>
       <c r="G26" t="n">
-        <v>13.27</v>
+        <v>47</v>
       </c>
       <c r="H26" t="n">
-        <v>16.645</v>
+        <v>44.25</v>
       </c>
       <c r="I26" t="n">
-        <v>15.09</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -1740,18 +1740,18 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>4.24</v>
+        <v>-0.58</v>
       </c>
       <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="n">
-        <v>1997562259</v>
+        <v>1888700382</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1760,19 +1760,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.6323</v>
+        <v>1</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>45898.65762083334</v>
+        <v>45831.65144708334</v>
       </c>
       <c r="G27" t="n">
-        <v>23.72</v>
+        <v>47.58</v>
       </c>
       <c r="H27" t="n">
-        <v>24.06</v>
+        <v>53.62</v>
       </c>
       <c r="I27" t="n">
-        <v>15</v>
+        <v>47.58</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -1789,18 +1789,18 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.21</v>
+        <v>6.04</v>
       </c>
       <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="n">
-        <v>2035164705</v>
+        <v>1599448103</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PHGP.L</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1809,19 +1809,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.032</v>
+        <v>0.2839</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>45919.6670447338</v>
+        <v>45663.73506711805</v>
       </c>
       <c r="G28" t="n">
-        <v>252.81</v>
+        <v>52.83</v>
       </c>
       <c r="H28" t="n">
-        <v>294.76</v>
+        <v>57.2</v>
       </c>
       <c r="I28" t="n">
-        <v>10.97</v>
+        <v>15</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -1838,18 +1838,18 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="n">
-        <v>1923250768</v>
+        <v>2017778050</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1858,19 +1858,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.87</v>
+        <v>0.3611</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>45853.65447396991</v>
+        <v>45910.64665976852</v>
       </c>
       <c r="G29" t="n">
-        <v>12.76</v>
+        <v>27.91</v>
       </c>
       <c r="H29" t="n">
-        <v>16.645</v>
+        <v>35.22</v>
       </c>
       <c r="I29" t="n">
-        <v>13</v>
+        <v>10.08</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -1887,18 +1887,18 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.82</v>
+        <v>2.64</v>
       </c>
       <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="n">
-        <v>2047762608</v>
+        <v>2165969833</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BBAR</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1910,16 +1910,16 @@
         <v>1</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45926.65281253472</v>
+        <v>45974.6734078588</v>
       </c>
       <c r="G30" t="n">
-        <v>9.27</v>
+        <v>9.849</v>
       </c>
       <c r="H30" t="n">
-        <v>9.380000000000001</v>
+        <v>9.787000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>9.27</v>
+        <v>9.85</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -1936,18 +1936,18 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0.11</v>
+        <v>-0.06</v>
       </c>
       <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="n">
-        <v>1830408508</v>
+        <v>1895465445</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1956,19 +1956,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.5793</v>
+        <v>0.2935</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45796.82346997685</v>
+        <v>45834.6539484375</v>
       </c>
       <c r="G31" t="n">
-        <v>17.26</v>
+        <v>33.47</v>
       </c>
       <c r="H31" t="n">
-        <v>22.51</v>
+        <v>35.22</v>
       </c>
       <c r="I31" t="n">
-        <v>10</v>
+        <v>9.82</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1985,18 +1985,18 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>3.04</v>
+        <v>0.51</v>
       </c>
       <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="n">
-        <v>2060620530</v>
+        <v>2109456088</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BLX</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2005,16 +2005,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.2207</v>
+        <v>0.2449</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45932.89856876157</v>
+        <v>45951.87487259259</v>
       </c>
       <c r="G32" t="n">
-        <v>45.28</v>
+        <v>40.81</v>
       </c>
       <c r="H32" t="n">
-        <v>44.72</v>
+        <v>41.51</v>
       </c>
       <c r="I32" t="n">
         <v>9.99</v>
@@ -2034,18 +2034,18 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>-0.12</v>
+        <v>0.18</v>
       </c>
       <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="n">
-        <v>2071864157</v>
+        <v>2165928440</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PHGP.L</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2054,19 +2054,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.0291</v>
+        <v>0.1087</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45938.58107210648</v>
+        <v>45974.67012341435</v>
       </c>
       <c r="G33" t="n">
-        <v>280.19</v>
+        <v>78.675</v>
       </c>
       <c r="H33" t="n">
-        <v>294.76</v>
+        <v>67.745</v>
       </c>
       <c r="I33" t="n">
-        <v>10.99</v>
+        <v>10</v>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -2083,18 +2083,18 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.48</v>
+        <v>-1.56</v>
       </c>
       <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="n">
-        <v>2091063412</v>
+        <v>2123985838</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2103,19 +2103,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.4089</v>
+        <v>0.3526</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45945.66023149306</v>
+        <v>45957.79493891204</v>
       </c>
       <c r="G34" t="n">
-        <v>24.44</v>
+        <v>42.53</v>
       </c>
       <c r="H34" t="n">
-        <v>24.06</v>
+        <v>46.62</v>
       </c>
       <c r="I34" t="n">
-        <v>9.99</v>
+        <v>15</v>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
@@ -2132,18 +2132,18 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>-0.15</v>
+        <v>1.44</v>
       </c>
       <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="n">
-        <v>2066994664</v>
+        <v>2153543105</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2152,16 +2152,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.067</v>
+        <v>0.0357</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>45936.87431893519</v>
+        <v>45968.7666778125</v>
       </c>
       <c r="G35" t="n">
-        <v>149.19</v>
+        <v>280.23</v>
       </c>
       <c r="H35" t="n">
-        <v>145.14</v>
+        <v>284.69</v>
       </c>
       <c r="I35" t="n">
         <v>10</v>
@@ -2181,18 +2181,18 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>-0.28</v>
+        <v>0.16</v>
       </c>
       <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="n">
-        <v>1883977086</v>
+        <v>2108073307</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2204,16 +2204,16 @@
         <v>1</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45827.66106613426</v>
+        <v>45951.66712166667</v>
       </c>
       <c r="G36" t="n">
-        <v>12.875</v>
+        <v>44.37</v>
       </c>
       <c r="H36" t="n">
-        <v>16.645</v>
+        <v>46.62</v>
       </c>
       <c r="I36" t="n">
-        <v>14.86</v>
+        <v>44.37</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -2230,18 +2230,18 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>4.47</v>
+        <v>2.25</v>
       </c>
       <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
-        <v>1582723120</v>
+        <v>1806979127</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2250,19 +2250,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.3755</v>
+        <v>0.6361</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>45645.89511640046</v>
+        <v>45783.83125244213</v>
       </c>
       <c r="G37" t="n">
-        <v>53.26</v>
+        <v>15.72</v>
       </c>
       <c r="H37" t="n">
-        <v>65</v>
+        <v>24.43</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
@@ -2279,18 +2279,18 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>4.41</v>
+        <v>5.54</v>
       </c>
       <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>1824476420</v>
+        <v>1923259795</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2299,19 +2299,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.1548</v>
+        <v>0.4424</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45792.64714148148</v>
+        <v>45853.65609353009</v>
       </c>
       <c r="G38" t="n">
-        <v>129.17</v>
+        <v>22.59</v>
       </c>
       <c r="H38" t="n">
-        <v>153.77</v>
+        <v>24.9</v>
       </c>
       <c r="I38" t="n">
-        <v>20</v>
+        <v>9.99</v>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
@@ -2328,18 +2328,18 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
-        <v>2065642904</v>
+        <v>2147671330</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IAPD.AS</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2348,19 +2348,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.175</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45936.61247836806</v>
+        <v>45966.7445521412</v>
       </c>
       <c r="G39" t="n">
-        <v>22.935</v>
+        <v>57.17</v>
       </c>
       <c r="H39" t="n">
-        <v>22.975</v>
+        <v>57.2</v>
       </c>
       <c r="I39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -2377,18 +2377,18 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>-0.14</v>
+        <v>0.01</v>
       </c>
       <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="n">
-        <v>1806977521</v>
+        <v>2072487323</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2397,19 +2397,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.3367</v>
+        <v>0.4062</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>45783.8305750463</v>
+        <v>45938.67565716435</v>
       </c>
       <c r="G40" t="n">
-        <v>29.7</v>
+        <v>24.64</v>
       </c>
       <c r="H40" t="n">
-        <v>26.02</v>
+        <v>22.68</v>
       </c>
       <c r="I40" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
@@ -2426,18 +2426,18 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>-1.24</v>
+        <v>-0.8</v>
       </c>
       <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="n">
-        <v>1997561527</v>
+        <v>2143958200</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>UEC</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2446,19 +2446,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.1498</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45898.65748991898</v>
+        <v>45965.64886045139</v>
       </c>
       <c r="G41" t="n">
-        <v>66.73</v>
+        <v>13.28</v>
       </c>
       <c r="H41" t="n">
-        <v>65</v>
+        <v>12.11</v>
       </c>
       <c r="I41" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
@@ -2475,18 +2475,18 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>-0.26</v>
+        <v>-0.89</v>
       </c>
       <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="n">
-        <v>1843477272</v>
+        <v>1869077178</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2495,19 +2495,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0.0001</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>45804.66725678241</v>
+        <v>45819.67426902778</v>
       </c>
       <c r="G42" t="n">
-        <v>17.86</v>
+        <v>13.285</v>
       </c>
       <c r="H42" t="n">
-        <v>19.34</v>
+        <v>18.02</v>
       </c>
       <c r="I42" t="n">
-        <v>17.86</v>
+        <v>0</v>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -2524,18 +2524,18 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="n">
-        <v>1997500170</v>
+        <v>2187232967</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>JKS</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2544,19 +2544,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.4466</v>
+        <v>0.7221</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>45898.65406594907</v>
+        <v>45982.64800082176</v>
       </c>
       <c r="G43" t="n">
-        <v>22.39</v>
+        <v>20.76</v>
       </c>
       <c r="H43" t="n">
-        <v>23.11</v>
+        <v>21.12</v>
       </c>
       <c r="I43" t="n">
-        <v>10</v>
+        <v>14.99</v>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -2573,18 +2573,18 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
-        <v>1599455288</v>
+        <v>2174585592</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>WEN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2593,19 +2593,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.2195</v>
+        <v>1</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45663.73750263889</v>
+        <v>45978.84634915509</v>
       </c>
       <c r="G44" t="n">
-        <v>45.55</v>
+        <v>8.42</v>
       </c>
       <c r="H44" t="n">
-        <v>26.02</v>
+        <v>7.91</v>
       </c>
       <c r="I44" t="n">
-        <v>10</v>
+        <v>8.42</v>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -2622,18 +2622,18 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>-4.29</v>
+        <v>-0.51</v>
       </c>
       <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>2029950407</v>
+        <v>2091064900</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PHGP.L</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2642,19 +2642,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.1453</v>
+        <v>0.4294</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>45917.66293982639</v>
+        <v>45945.66049490741</v>
       </c>
       <c r="G45" t="n">
-        <v>250.56</v>
+        <v>23.32</v>
       </c>
       <c r="H45" t="n">
-        <v>294.76</v>
+        <v>22.68</v>
       </c>
       <c r="I45" t="n">
-        <v>49.99</v>
+        <v>10.01</v>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -2671,18 +2671,18 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>7.27</v>
+        <v>-0.27</v>
       </c>
       <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>2027639997</v>
+        <v>2060624552</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2691,19 +2691,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.1558</v>
+        <v>0.1676</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>45916.65703747685</v>
+        <v>45932.90130990741</v>
       </c>
       <c r="G46" t="n">
-        <v>64.18000000000001</v>
+        <v>59.7</v>
       </c>
       <c r="H46" t="n">
-        <v>65</v>
+        <v>64.41</v>
       </c>
       <c r="I46" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -2720,18 +2720,18 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.13</v>
+        <v>0.79</v>
       </c>
       <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>1926287328</v>
+        <v>2048539334</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2740,19 +2740,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.5476</v>
+        <v>1</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>45854.82177967593</v>
+        <v>45926.85025574074</v>
       </c>
       <c r="G47" t="n">
-        <v>18.26</v>
+        <v>42.2</v>
       </c>
       <c r="H47" t="n">
-        <v>22.51</v>
+        <v>46.62</v>
       </c>
       <c r="I47" t="n">
-        <v>10</v>
+        <v>42.2</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -2769,18 +2769,18 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.33</v>
+        <v>4.42</v>
       </c>
       <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>1995249699</v>
+        <v>1997485943</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BTCE.DE</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2789,19 +2789,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.3888</v>
+        <v>0.5157</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>45897.61086020833</v>
+        <v>45898.65185685185</v>
       </c>
       <c r="G48" t="n">
-        <v>87.16500000000001</v>
+        <v>19.39</v>
       </c>
       <c r="H48" t="n">
-        <v>81.605</v>
+        <v>21.12</v>
       </c>
       <c r="I48" t="n">
-        <v>39.77</v>
+        <v>10</v>
       </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -2818,18 +2818,18 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>-2.92</v>
+        <v>0.89</v>
       </c>
       <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
-        <v>2060619876</v>
+        <v>2045993574</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2838,16 +2838,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.4178</v>
+        <v>0.5753</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45932.89807736111</v>
+        <v>45925.80108013889</v>
       </c>
       <c r="G49" t="n">
-        <v>23.93</v>
+        <v>17.38</v>
       </c>
       <c r="H49" t="n">
-        <v>22.51</v>
+        <v>17.52</v>
       </c>
       <c r="I49" t="n">
         <v>10</v>
@@ -2867,18 +2867,18 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>-0.6</v>
+        <v>0.08</v>
       </c>
       <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
-        <v>2080281129</v>
+        <v>1867194722</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>JKS</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.462</v>
+        <v>1</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>45940.89117050926</v>
+        <v>45818.80135700232</v>
       </c>
       <c r="G50" t="n">
-        <v>21.73</v>
+        <v>21.27</v>
       </c>
       <c r="H50" t="n">
-        <v>23.11</v>
+        <v>17.52</v>
       </c>
       <c r="I50" t="n">
-        <v>10.04</v>
+        <v>21.27</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -2916,18 +2916,18 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0.64</v>
+        <v>-3.75</v>
       </c>
       <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>2066988146</v>
+        <v>1976499401</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2936,19 +2936,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.102</v>
+        <v>0.8064</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>45936.870276875</v>
+        <v>45884.83731814815</v>
       </c>
       <c r="G51" t="n">
-        <v>98.06</v>
+        <v>49.6</v>
       </c>
       <c r="H51" t="n">
-        <v>97.06</v>
+        <v>46.96</v>
       </c>
       <c r="I51" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -2965,18 +2965,18 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>-0.1</v>
+        <v>-2.13</v>
       </c>
       <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
-        <v>1895465445</v>
+        <v>2126266618</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>SGLD.L</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2985,16 +2985,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.2987</v>
+        <v>0.0264</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>45834.6539484375</v>
+        <v>45958.59687736111</v>
       </c>
       <c r="G52" t="n">
-        <v>33.47</v>
+        <v>378.7</v>
       </c>
       <c r="H52" t="n">
-        <v>26.02</v>
+        <v>393.97</v>
       </c>
       <c r="I52" t="n">
         <v>10</v>
@@ -3014,18 +3014,18 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>-2.23</v>
+        <v>0.4</v>
       </c>
       <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="n">
-        <v>1754302454</v>
+        <v>2166275422</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3034,19 +3034,19 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.3673</v>
+        <v>0.0355</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>45755.88025324074</v>
+        <v>45974.71278471065</v>
       </c>
       <c r="G53" t="n">
-        <v>27.17</v>
+        <v>281.58</v>
       </c>
       <c r="H53" t="n">
-        <v>26.02</v>
+        <v>284.69</v>
       </c>
       <c r="I53" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
@@ -3063,18 +3063,18 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>-0.42</v>
+        <v>0.11</v>
       </c>
       <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="n">
-        <v>2091093343</v>
+        <v>2109456461</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3083,16 +3083,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.2366</v>
+        <v>0.2053</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>45945.66190688658</v>
+        <v>45951.8750978125</v>
       </c>
       <c r="G54" t="n">
-        <v>42.25</v>
+        <v>48.7</v>
       </c>
       <c r="H54" t="n">
-        <v>40.9</v>
+        <v>46.96</v>
       </c>
       <c r="I54" t="n">
         <v>10</v>
@@ -3112,18 +3112,18 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>-0.32</v>
+        <v>-0.36</v>
       </c>
       <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="n">
-        <v>1981010841</v>
+        <v>2157051356</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>WEN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3132,19 +3132,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.0425</v>
+        <v>1</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>45888.84617734954</v>
+        <v>45971.69033096065</v>
       </c>
       <c r="G55" t="n">
-        <v>235.53</v>
+        <v>8.6</v>
       </c>
       <c r="H55" t="n">
-        <v>295.11</v>
+        <v>7.91</v>
       </c>
       <c r="I55" t="n">
-        <v>10.01</v>
+        <v>8.6</v>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
@@ -3161,18 +3161,18 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.53</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="n">
-        <v>2048501554</v>
+        <v>2132998553</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>JKS</t>
+          <t>G.MI</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3181,19 +3181,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.4118</v>
+        <v>0.5187</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>45926.83927949074</v>
+        <v>45960.54250372685</v>
       </c>
       <c r="G56" t="n">
-        <v>24.28</v>
+        <v>33.09</v>
       </c>
       <c r="H56" t="n">
-        <v>23.11</v>
+        <v>33.21</v>
       </c>
       <c r="I56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
@@ -3210,18 +3210,18 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>-0.48</v>
+        <v>-0.25</v>
       </c>
       <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="n">
-        <v>1869077157</v>
+        <v>1843474191</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3230,19 +3230,19 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.3061</v>
+        <v>0.9372</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45819.6742621412</v>
+        <v>45804.66699503472</v>
       </c>
       <c r="G57" t="n">
-        <v>13.285</v>
+        <v>21.33</v>
       </c>
       <c r="H57" t="n">
-        <v>16.645</v>
+        <v>24.9</v>
       </c>
       <c r="I57" t="n">
-        <v>4.69</v>
+        <v>19.99</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
@@ -3259,18 +3259,18 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>1.23</v>
+        <v>3.35</v>
       </c>
       <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
-        <v>2000138014</v>
+        <v>1461331124</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BTCE.DE</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3279,19 +3279,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.1017</v>
+        <v>0.3752</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45901.57795706019</v>
+        <v>45553.65374138889</v>
       </c>
       <c r="G58" t="n">
-        <v>83.47499999999999</v>
+        <v>50.99</v>
       </c>
       <c r="H58" t="n">
-        <v>81.605</v>
+        <v>57.2</v>
       </c>
       <c r="I58" t="n">
-        <v>10</v>
+        <v>19.13</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
@@ -3308,18 +3308,18 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>-0.36</v>
+        <v>2.33</v>
       </c>
       <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="n">
-        <v>2095264263</v>
+        <v>1923246263</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SQM</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3328,19 +3328,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.2252</v>
+        <v>1</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>45946.74280237268</v>
+        <v>45853.6538128125</v>
       </c>
       <c r="G59" t="n">
-        <v>44.39</v>
+        <v>21.17</v>
       </c>
       <c r="H59" t="n">
-        <v>43.69</v>
+        <v>17.52</v>
       </c>
       <c r="I59" t="n">
-        <v>10</v>
+        <v>21.17</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
@@ -3357,18 +3357,18 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>-0.16</v>
+        <v>-3.65</v>
       </c>
       <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="n">
-        <v>1621495187</v>
+        <v>2130418359</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3377,19 +3377,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.2318</v>
+        <v>0.0716</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45678.83178196759</v>
+        <v>45959.75166957176</v>
       </c>
       <c r="G60" t="n">
-        <v>43.27</v>
+        <v>139.74</v>
       </c>
       <c r="H60" t="n">
-        <v>26.02</v>
+        <v>150.97</v>
       </c>
       <c r="I60" t="n">
-        <v>10.03</v>
+        <v>10.01</v>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
@@ -3406,18 +3406,18 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>-4</v>
+        <v>0.8</v>
       </c>
       <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="n">
-        <v>2042979139</v>
+        <v>2191689080</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>WEN</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3426,19 +3426,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.3128</v>
+        <v>1</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>45924.70564383102</v>
+        <v>45985.81110582176</v>
       </c>
       <c r="G61" t="n">
-        <v>32</v>
+        <v>8.06</v>
       </c>
       <c r="H61" t="n">
-        <v>31.63</v>
+        <v>7.91</v>
       </c>
       <c r="I61" t="n">
-        <v>10.01</v>
+        <v>8.06</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
@@ -3455,18 +3455,18 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>-0.12</v>
+        <v>-0.15</v>
       </c>
       <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="n">
-        <v>1666459270</v>
+        <v>1995249699</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3475,19 +3475,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.5636</v>
+        <v>0.3888</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>45708.68166530092</v>
+        <v>45897.61086020833</v>
       </c>
       <c r="G62" t="n">
-        <v>17.18</v>
+        <v>87.16500000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>24.06</v>
+        <v>67.745</v>
       </c>
       <c r="I62" t="n">
-        <v>9.68</v>
+        <v>39.77</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
@@ -3504,18 +3504,18 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>3.88</v>
+        <v>-9.56</v>
       </c>
       <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="n">
-        <v>1662993636</v>
+        <v>2130239989</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>EXXW.DE</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3524,19 +3524,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>0.6221</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>45706.87026833333</v>
+        <v>45959.70656982639</v>
       </c>
       <c r="G63" t="n">
-        <v>20.65</v>
+        <v>27.425</v>
       </c>
       <c r="H63" t="n">
-        <v>19.75</v>
+        <v>27.525</v>
       </c>
       <c r="I63" t="n">
-        <v>20.65</v>
+        <v>20</v>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
@@ -3553,18 +3553,18 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>-0.9</v>
+        <v>-0.37</v>
       </c>
       <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="n">
-        <v>1517510856</v>
+        <v>2133516483</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3573,16 +3573,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.0602</v>
+        <v>0.1748</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>45597.61014849537</v>
+        <v>45960.62396875</v>
       </c>
       <c r="G64" t="n">
-        <v>166.03</v>
+        <v>57.18</v>
       </c>
       <c r="H64" t="n">
-        <v>153.77</v>
+        <v>57.2</v>
       </c>
       <c r="I64" t="n">
         <v>10</v>
@@ -3602,18 +3602,18 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>-0.74</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="n">
-        <v>1923258249</v>
+        <v>2177450098</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>EXXW.DE</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3622,19 +3622,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>0.4714</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>45853.65576626157</v>
+        <v>45979.70481835648</v>
       </c>
       <c r="G65" t="n">
-        <v>19.41</v>
+        <v>27.305</v>
       </c>
       <c r="H65" t="n">
-        <v>22.51</v>
+        <v>27.525</v>
       </c>
       <c r="I65" t="n">
-        <v>19.41</v>
+        <v>15</v>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
@@ -3651,18 +3651,18 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>3.1</v>
+        <v>-0.12</v>
       </c>
       <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="n">
-        <v>2060617471</v>
+        <v>2186918766</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>EXXW.DE</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3671,19 +3671,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.2255</v>
+        <v>0.3179</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>45932.89647650463</v>
+        <v>45982.58088385416</v>
       </c>
       <c r="G66" t="n">
-        <v>44.35</v>
+        <v>27.18</v>
       </c>
       <c r="H66" t="n">
-        <v>40.9</v>
+        <v>27.525</v>
       </c>
       <c r="I66" t="n">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
@@ -3700,18 +3700,18 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>-0.78</v>
+        <v>0.02</v>
       </c>
       <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="n">
-        <v>1744916452</v>
+        <v>2076201130</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3720,19 +3720,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.4245</v>
+        <v>0.499</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>45751.74230173611</v>
+        <v>45939.75708394676</v>
       </c>
       <c r="G67" t="n">
-        <v>17.54</v>
+        <v>20.04</v>
       </c>
       <c r="H67" t="n">
-        <v>24.06</v>
+        <v>21.12</v>
       </c>
       <c r="I67" t="n">
-        <v>7.45</v>
+        <v>10</v>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
@@ -3749,18 +3749,18 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>2.76</v>
+        <v>0.54</v>
       </c>
       <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="n">
-        <v>2066989908</v>
+        <v>2080269311</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3769,19 +3769,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.3946</v>
+        <v>1</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>45936.87125002315</v>
+        <v>45940.886384375</v>
       </c>
       <c r="G68" t="n">
-        <v>25.34</v>
+        <v>52.53</v>
       </c>
       <c r="H68" t="n">
-        <v>24.06</v>
+        <v>53.62</v>
       </c>
       <c r="I68" t="n">
-        <v>10</v>
+        <v>52.53</v>
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
@@ -3798,18 +3798,18 @@
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>-0.51</v>
+        <v>1.09</v>
       </c>
       <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="n">
-        <v>1358151307</v>
+        <v>1883977086</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3818,19 +3818,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.1081</v>
+        <v>1</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>45460.88529052083</v>
+        <v>45827.66106613426</v>
       </c>
       <c r="G69" t="n">
-        <v>165.93</v>
+        <v>12.875</v>
       </c>
       <c r="H69" t="n">
-        <v>153.77</v>
+        <v>18.02</v>
       </c>
       <c r="I69" t="n">
-        <v>17.94</v>
+        <v>14.86</v>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
@@ -3847,18 +3847,18 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>-1.31</v>
+        <v>5.8</v>
       </c>
       <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="n">
-        <v>1888686062</v>
+        <v>2045989132</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3867,19 +3867,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.2903</v>
+        <v>0.2034</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>45831.64964792824</v>
+        <v>45925.79891365741</v>
       </c>
       <c r="G70" t="n">
-        <v>34.36</v>
+        <v>49.16</v>
       </c>
       <c r="H70" t="n">
-        <v>26.02</v>
+        <v>46.96</v>
       </c>
       <c r="I70" t="n">
-        <v>9.970000000000001</v>
+        <v>10</v>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
@@ -3896,18 +3896,18 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>-2.42</v>
+        <v>-0.45</v>
       </c>
       <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="n">
-        <v>2091115227</v>
+        <v>1824482557</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3916,19 +3916,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.376</v>
+        <v>0.2641</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>45945.66604186343</v>
+        <v>45792.64805195602</v>
       </c>
       <c r="G71" t="n">
-        <v>26.59</v>
+        <v>56.78</v>
       </c>
       <c r="H71" t="n">
-        <v>26.02</v>
+        <v>57.2</v>
       </c>
       <c r="I71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
@@ -3945,18 +3945,18 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>-0.22</v>
+        <v>0.11</v>
       </c>
       <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="n">
-        <v>1982273555</v>
+        <v>2108071782</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>SGLD.L</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3965,19 +3965,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.0439</v>
+        <v>0.0497</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>45889.64957444445</v>
+        <v>45951.66693487269</v>
       </c>
       <c r="G72" t="n">
-        <v>228</v>
+        <v>402.15</v>
       </c>
       <c r="H72" t="n">
-        <v>295.11</v>
+        <v>393.97</v>
       </c>
       <c r="I72" t="n">
-        <v>10.01</v>
+        <v>19.99</v>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -3994,18 +3994,18 @@
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>2.95</v>
+        <v>-0.41</v>
       </c>
       <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="n">
-        <v>1869077178</v>
+        <v>2166279633</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>UEC</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4014,19 +4014,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>0.8532</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45819.67426902778</v>
+        <v>45974.71368689815</v>
       </c>
       <c r="G73" t="n">
-        <v>13.285</v>
+        <v>11.71</v>
       </c>
       <c r="H73" t="n">
-        <v>16.645</v>
+        <v>12.11</v>
       </c>
       <c r="I73" t="n">
-        <v>15.31</v>
+        <v>9.99</v>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
@@ -4043,18 +4043,18 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>4.02</v>
+        <v>0.34</v>
       </c>
       <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="n">
-        <v>1997498400</v>
+        <v>1796453499</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4063,19 +4063,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.0507</v>
+        <v>0.0146</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45898.65380736111</v>
+        <v>45777.64668229167</v>
       </c>
       <c r="G74" t="n">
-        <v>197.26</v>
+        <v>15.57</v>
       </c>
       <c r="H74" t="n">
-        <v>231.77</v>
+        <v>21.12</v>
       </c>
       <c r="I74" t="n">
-        <v>10</v>
+        <v>0.23</v>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
@@ -4092,18 +4092,18 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>1.75</v>
+        <v>0.08</v>
       </c>
       <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="n">
-        <v>1867193336</v>
+        <v>2170017941</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>EXXW.DE</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4112,19 +4112,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>0.4625</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>45818.80084483796</v>
+        <v>45975.68838484953</v>
       </c>
       <c r="G75" t="n">
-        <v>17.64</v>
+        <v>27.76</v>
       </c>
       <c r="H75" t="n">
-        <v>19.34</v>
+        <v>27.525</v>
       </c>
       <c r="I75" t="n">
-        <v>17.64</v>
+        <v>14.99</v>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
@@ -4141,18 +4141,18 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>1.7</v>
+        <v>-0.39</v>
       </c>
       <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="n">
-        <v>1631475148</v>
+        <v>2166284132</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4161,16 +4161,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.2592</v>
+        <v>0.0916</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>45685.83625201389</v>
+        <v>45974.7148656713</v>
       </c>
       <c r="G76" t="n">
-        <v>38.58</v>
+        <v>109.19</v>
       </c>
       <c r="H76" t="n">
-        <v>26.02</v>
+        <v>105.97</v>
       </c>
       <c r="I76" t="n">
         <v>10</v>
@@ -4190,18 +4190,18 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>-3.26</v>
+        <v>-0.29</v>
       </c>
       <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="n">
-        <v>2042867331</v>
+        <v>2080281858</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>JKS</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4210,16 +4210,16 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.3941</v>
+        <v>0.4547</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>45924.67994332176</v>
+        <v>45940.89146028935</v>
       </c>
       <c r="G77" t="n">
-        <v>25.37</v>
+        <v>21.99</v>
       </c>
       <c r="H77" t="n">
-        <v>23.11</v>
+        <v>24.43</v>
       </c>
       <c r="I77" t="n">
         <v>10</v>
@@ -4239,18 +4239,18 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>-0.89</v>
+        <v>1.11</v>
       </c>
       <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="n">
-        <v>2065634230</v>
+        <v>2137053932</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>EXXW.DE</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4259,19 +4259,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.7849</v>
+        <v>0.6311</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>45936.60990405093</v>
+        <v>45961.6854628125</v>
       </c>
       <c r="G78" t="n">
-        <v>16.28</v>
+        <v>27.345</v>
       </c>
       <c r="H78" t="n">
-        <v>16.645</v>
+        <v>27.525</v>
       </c>
       <c r="I78" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
@@ -4288,18 +4288,18 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>0.17</v>
+        <v>-0.08</v>
       </c>
       <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="n">
-        <v>1923256224</v>
+        <v>1727574394</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4308,19 +4308,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.6457000000000001</v>
+        <v>1</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>45853.65543140046</v>
+        <v>45743.76658678241</v>
       </c>
       <c r="G79" t="n">
-        <v>30.97</v>
+        <v>21.13</v>
       </c>
       <c r="H79" t="n">
-        <v>26.02</v>
+        <v>17.52</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>21.13</v>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
@@ -4337,18 +4337,18 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>-3.2</v>
+        <v>-3.61</v>
       </c>
       <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="n">
-        <v>2047762508</v>
+        <v>1867193304</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BBAR</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4357,19 +4357,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.1337</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>45926.65279332176</v>
+        <v>45818.8008296412</v>
       </c>
       <c r="G80" t="n">
-        <v>9.27</v>
+        <v>17.64</v>
       </c>
       <c r="H80" t="n">
-        <v>9.380000000000001</v>
+        <v>21.12</v>
       </c>
       <c r="I80" t="n">
-        <v>0.73</v>
+        <v>2.36</v>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
@@ -4386,18 +4386,18 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>0.01</v>
+        <v>0.46</v>
       </c>
       <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="n">
-        <v>2091099618</v>
+        <v>2147235946</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BBAR</t>
+          <t>CIG</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4406,19 +4406,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.0373</v>
+        <v>9</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>45945.66309922453</v>
+        <v>45966.65399990741</v>
       </c>
       <c r="G81" t="n">
-        <v>9.68</v>
+        <v>2.16</v>
       </c>
       <c r="H81" t="n">
-        <v>9.380000000000001</v>
+        <v>2.03</v>
       </c>
       <c r="I81" t="n">
-        <v>0.36</v>
+        <v>19.44</v>
       </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
@@ -4435,18 +4435,18 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>-0.01</v>
+        <v>-1.17</v>
       </c>
       <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="n">
-        <v>1727591551</v>
+        <v>2143342728</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4455,19 +4455,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0.1064</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>45743.77389555555</v>
+        <v>45965.52168108796</v>
       </c>
       <c r="G82" t="n">
-        <v>72.87</v>
+        <v>81.22499999999999</v>
       </c>
       <c r="H82" t="n">
-        <v>74.88</v>
+        <v>67.745</v>
       </c>
       <c r="I82" t="n">
-        <v>72.87</v>
+        <v>9.99</v>
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
@@ -4484,18 +4484,18 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>2.01</v>
+        <v>-1.72</v>
       </c>
       <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="n">
-        <v>2080281858</v>
+        <v>2177445750</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>JKS</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4504,19 +4504,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.4547</v>
+        <v>0.3465</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>45940.89146028935</v>
+        <v>45979.70378568287</v>
       </c>
       <c r="G83" t="n">
-        <v>21.99</v>
+        <v>29</v>
       </c>
       <c r="H83" t="n">
-        <v>22.51</v>
+        <v>25.68</v>
       </c>
       <c r="I83" t="n">
-        <v>10</v>
+        <v>10.05</v>
       </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
@@ -4533,18 +4533,18 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>0.24</v>
+        <v>-1.15</v>
       </c>
       <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="n">
-        <v>1867196288</v>
+        <v>1744916497</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4553,19 +4553,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.5568</v>
+        <v>1</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>45818.80209099537</v>
+        <v>45751.74231563658</v>
       </c>
       <c r="G84" t="n">
-        <v>41.99</v>
+        <v>17.54</v>
       </c>
       <c r="H84" t="n">
-        <v>56.8</v>
+        <v>24.9</v>
       </c>
       <c r="I84" t="n">
-        <v>23.38</v>
+        <v>17.54</v>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
@@ -4582,18 +4582,18 @@
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>8.25</v>
+        <v>7.36</v>
       </c>
       <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="n">
-        <v>1972092684</v>
+        <v>2174225044</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>SEDG</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4602,19 +4602,19 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>0.2948</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>45882.68269449074</v>
+        <v>45978.7566997338</v>
       </c>
       <c r="G85" t="n">
-        <v>18.8</v>
+        <v>33.92</v>
       </c>
       <c r="H85" t="n">
-        <v>19.75</v>
+        <v>34.47</v>
       </c>
       <c r="I85" t="n">
-        <v>18.8</v>
+        <v>10</v>
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
@@ -4631,18 +4631,18 @@
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>0.95</v>
+        <v>0.16</v>
       </c>
       <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="n">
-        <v>1830410729</v>
+        <v>2099892569</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4651,19 +4651,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.1091</v>
+        <v>0.1057</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>45796.82476561343</v>
+        <v>45947.69061754629</v>
       </c>
       <c r="G86" t="n">
-        <v>33.66</v>
+        <v>80.62</v>
       </c>
       <c r="H86" t="n">
-        <v>31.63</v>
+        <v>67.745</v>
       </c>
       <c r="I86" t="n">
-        <v>3.67</v>
+        <v>9.99</v>
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
@@ -4680,18 +4680,18 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>-0.22</v>
+        <v>-1.78</v>
       </c>
       <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="n">
-        <v>1599448103</v>
+        <v>2078840482</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4700,19 +4700,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.2839</v>
+        <v>0.4336</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>45663.73506711805</v>
+        <v>45940.66718949074</v>
       </c>
       <c r="G87" t="n">
-        <v>52.83</v>
+        <v>23.06</v>
       </c>
       <c r="H87" t="n">
-        <v>65</v>
+        <v>24.43</v>
       </c>
       <c r="I87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
@@ -4729,18 +4729,18 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>3.45</v>
+        <v>0.59</v>
       </c>
       <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="n">
-        <v>2045989132</v>
+        <v>1883977044</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4749,19 +4749,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.2034</v>
+        <v>0.345</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>45925.79891365741</v>
+        <v>45827.66105774305</v>
       </c>
       <c r="G88" t="n">
-        <v>49.16</v>
+        <v>12.88</v>
       </c>
       <c r="H88" t="n">
-        <v>48.43</v>
+        <v>18.02</v>
       </c>
       <c r="I88" t="n">
-        <v>10</v>
+        <v>5.13</v>
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
@@ -4778,18 +4778,18 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>-0.15</v>
+        <v>2</v>
       </c>
       <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="n">
-        <v>1806979127</v>
+        <v>1582723120</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4798,19 +4798,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.6361</v>
+        <v>0.3755</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>45783.83125244213</v>
+        <v>45645.89511640046</v>
       </c>
       <c r="G89" t="n">
-        <v>15.72</v>
+        <v>53.26</v>
       </c>
       <c r="H89" t="n">
-        <v>22.51</v>
+        <v>57.2</v>
       </c>
       <c r="I89" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
@@ -4827,18 +4827,18 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>4.32</v>
+        <v>1.48</v>
       </c>
       <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="n">
-        <v>2020498366</v>
+        <v>2017852950</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BBAR</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4850,16 +4850,16 @@
         <v>1</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>45911.68945292824</v>
+        <v>45910.65507498843</v>
       </c>
       <c r="G90" t="n">
-        <v>9.880000000000001</v>
+        <v>37.44</v>
       </c>
       <c r="H90" t="n">
-        <v>9.380000000000001</v>
+        <v>46.62</v>
       </c>
       <c r="I90" t="n">
-        <v>9.880000000000001</v>
+        <v>37.44</v>
       </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
@@ -4876,18 +4876,18 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>-0.5</v>
+        <v>9.18</v>
       </c>
       <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="n">
-        <v>1867193304</v>
+        <v>2025662892</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4896,19 +4896,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.1337</v>
+        <v>0.8196</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>45818.8008296412</v>
+        <v>45915.72913914352</v>
       </c>
       <c r="G91" t="n">
-        <v>17.64</v>
+        <v>24.39</v>
       </c>
       <c r="H91" t="n">
-        <v>19.34</v>
+        <v>22.68</v>
       </c>
       <c r="I91" t="n">
-        <v>2.36</v>
+        <v>19.99</v>
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
@@ -4925,18 +4925,18 @@
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>0.23</v>
+        <v>-1.4</v>
       </c>
       <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="n">
-        <v>2017778050</v>
+        <v>2159520127</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>UEC</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4945,19 +4945,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.3611</v>
+        <v>0.8077</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>45910.64665976852</v>
+        <v>45972.65953206018</v>
       </c>
       <c r="G92" t="n">
-        <v>27.91</v>
+        <v>12.38</v>
       </c>
       <c r="H92" t="n">
-        <v>26.02</v>
+        <v>12.11</v>
       </c>
       <c r="I92" t="n">
-        <v>10.08</v>
+        <v>10</v>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
@@ -4974,18 +4974,18 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>-0.68</v>
+        <v>-0.22</v>
       </c>
       <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="n">
-        <v>1599431096</v>
+        <v>2126323625</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4994,19 +4994,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.1013</v>
+        <v>0.0519</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>45663.73014731482</v>
+        <v>45958.60738418982</v>
       </c>
       <c r="G93" t="n">
-        <v>148.02</v>
+        <v>192.64</v>
       </c>
       <c r="H93" t="n">
-        <v>153.77</v>
+        <v>175.09</v>
       </c>
       <c r="I93" t="n">
-        <v>14.99</v>
+        <v>10</v>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
@@ -5023,18 +5023,18 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>0.59</v>
+        <v>-0.91</v>
       </c>
       <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="n">
-        <v>2091104996</v>
+        <v>2165942793</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BLX</t>
+          <t>EXXW.DE</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5043,19 +5043,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.2189</v>
+        <v>0.4599</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>45945.66391778935</v>
+        <v>45974.67230265046</v>
       </c>
       <c r="G94" t="n">
-        <v>45.76</v>
+        <v>27.915</v>
       </c>
       <c r="H94" t="n">
-        <v>44.72</v>
+        <v>27.525</v>
       </c>
       <c r="I94" t="n">
-        <v>10.02</v>
+        <v>15</v>
       </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
@@ -5072,18 +5072,18 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>-0.23</v>
+        <v>-0.48</v>
       </c>
       <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="n">
-        <v>1923258184</v>
+        <v>2091093343</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5092,19 +5092,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.0298</v>
+        <v>0.2366</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>45853.6557568287</v>
+        <v>45945.66190688658</v>
       </c>
       <c r="G95" t="n">
-        <v>19.43</v>
+        <v>42.25</v>
       </c>
       <c r="H95" t="n">
-        <v>22.51</v>
+        <v>41.51</v>
       </c>
       <c r="I95" t="n">
-        <v>0.58</v>
+        <v>10</v>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -5121,18 +5121,18 @@
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>0.09</v>
+        <v>-0.18</v>
       </c>
       <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="n">
-        <v>2060645660</v>
+        <v>2153585683</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>CIG</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5141,19 +5141,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.1027</v>
+        <v>9</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>45932.90186543982</v>
+        <v>45968.77361017361</v>
       </c>
       <c r="G96" t="n">
-        <v>97.43000000000001</v>
+        <v>2.16</v>
       </c>
       <c r="H96" t="n">
-        <v>97.06</v>
+        <v>2.03</v>
       </c>
       <c r="I96" t="n">
-        <v>10.01</v>
+        <v>19.44</v>
       </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
@@ -5170,18 +5170,18 @@
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>-0.04</v>
+        <v>-1.17</v>
       </c>
       <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="n">
-        <v>1727574394</v>
+        <v>2141396087</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5190,19 +5190,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>0.2409</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>45743.76658678241</v>
+        <v>45964.7920094213</v>
       </c>
       <c r="G97" t="n">
-        <v>21.13</v>
+        <v>41.51</v>
       </c>
       <c r="H97" t="n">
-        <v>19.75</v>
+        <v>26.41</v>
       </c>
       <c r="I97" t="n">
-        <v>21.13</v>
+        <v>10</v>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
@@ -5219,18 +5219,18 @@
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>-1.38</v>
+        <v>-3.64</v>
       </c>
       <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="n">
-        <v>2045993574</v>
+        <v>1806980482</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5239,19 +5239,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.5753</v>
+        <v>0.2406</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>45925.80108013889</v>
+        <v>45783.83189613426</v>
       </c>
       <c r="G98" t="n">
-        <v>17.38</v>
+        <v>16.12</v>
       </c>
       <c r="H98" t="n">
-        <v>19.75</v>
+        <v>21.12</v>
       </c>
       <c r="I98" t="n">
-        <v>10</v>
+        <v>3.88</v>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
@@ -5268,18 +5268,18 @@
         <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="n">
-        <v>2078838036</v>
+        <v>1923258184</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>JKS</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5288,19 +5288,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.43</v>
+        <v>0.0298</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>45940.66691300926</v>
+        <v>45853.6557568287</v>
       </c>
       <c r="G99" t="n">
-        <v>23.37</v>
+        <v>19.43</v>
       </c>
       <c r="H99" t="n">
-        <v>23.11</v>
+        <v>24.43</v>
       </c>
       <c r="I99" t="n">
-        <v>10.05</v>
+        <v>0.58</v>
       </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
@@ -5317,18 +5317,18 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>-0.11</v>
+        <v>0.15</v>
       </c>
       <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="n">
-        <v>2066990620</v>
+        <v>2130236780</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5337,19 +5337,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.1541</v>
+        <v>2</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>45936.87171386574</v>
+        <v>45959.70575767361</v>
       </c>
       <c r="G100" t="n">
-        <v>64.88</v>
+        <v>9.920999999999999</v>
       </c>
       <c r="H100" t="n">
-        <v>65</v>
+        <v>9.787000000000001</v>
       </c>
       <c r="I100" t="n">
-        <v>10</v>
+        <v>19.84</v>
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
@@ -5366,18 +5366,18 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>0.02</v>
+        <v>-0.27</v>
       </c>
       <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="n">
-        <v>1880446729</v>
+        <v>2071864157</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>PHGP.L</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5386,19 +5386,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.0772</v>
+        <v>0.0291</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>45825.89315055555</v>
+        <v>45938.58107210648</v>
       </c>
       <c r="G101" t="n">
-        <v>129.62</v>
+        <v>280.19</v>
       </c>
       <c r="H101" t="n">
-        <v>153.77</v>
+        <v>290.47</v>
       </c>
       <c r="I101" t="n">
-        <v>10.01</v>
+        <v>10.99</v>
       </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -5415,18 +5415,18 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>1.86</v>
+        <v>0.04</v>
       </c>
       <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="n">
-        <v>1880443947</v>
+        <v>2130236742</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5435,19 +5435,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.1047</v>
+        <v>0.0151</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>45825.891695625</v>
+        <v>45959.70574188657</v>
       </c>
       <c r="G102" t="n">
-        <v>142.99</v>
+        <v>9.920999999999999</v>
       </c>
       <c r="H102" t="n">
-        <v>231.77</v>
+        <v>9.787000000000001</v>
       </c>
       <c r="I102" t="n">
-        <v>14.97</v>
+        <v>0.15</v>
       </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
@@ -5464,18 +5464,18 @@
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="n">
-        <v>2091123728</v>
+        <v>2174222935</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SQM</t>
+          <t>VIST</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5484,19 +5484,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.4406</v>
+        <v>0.2016</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>45945.66748809028</v>
+        <v>45978.75555864583</v>
       </c>
       <c r="G103" t="n">
-        <v>45.28</v>
+        <v>49.6</v>
       </c>
       <c r="H103" t="n">
-        <v>43.69</v>
+        <v>48.27</v>
       </c>
       <c r="I103" t="n">
-        <v>19.95</v>
+        <v>10</v>
       </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
@@ -5513,18 +5513,18 @@
         <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>-0.7</v>
+        <v>-0.27</v>
       </c>
       <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="n">
-        <v>2050990570</v>
+        <v>2187248452</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BLX</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5533,19 +5533,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.2121</v>
+        <v>0.3344</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>45929.65780017361</v>
+        <v>45982.65039924769</v>
       </c>
       <c r="G104" t="n">
-        <v>47</v>
+        <v>44.85</v>
       </c>
       <c r="H104" t="n">
-        <v>44.72</v>
+        <v>46.62</v>
       </c>
       <c r="I104" t="n">
-        <v>9.970000000000001</v>
+        <v>15</v>
       </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
@@ -5562,18 +5562,18 @@
         <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>-0.48</v>
+        <v>0.59</v>
       </c>
       <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="n">
-        <v>2099890750</v>
+        <v>2191690048</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5582,16 +5582,16 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.1038</v>
+        <v>0.3824</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>45947.69026060185</v>
+        <v>45985.81166753472</v>
       </c>
       <c r="G105" t="n">
-        <v>96.38</v>
+        <v>26.15</v>
       </c>
       <c r="H105" t="n">
-        <v>97.06</v>
+        <v>26.41</v>
       </c>
       <c r="I105" t="n">
         <v>10</v>
@@ -5611,18 +5611,18 @@
         <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="n">
-        <v>1983186744</v>
+        <v>2174585539</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>WEN</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5631,19 +5631,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.3162</v>
+        <v>0.1876</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>45889.85904239583</v>
+        <v>45978.84633431713</v>
       </c>
       <c r="G106" t="n">
-        <v>31.61</v>
+        <v>8.42</v>
       </c>
       <c r="H106" t="n">
-        <v>26.02</v>
+        <v>7.91</v>
       </c>
       <c r="I106" t="n">
-        <v>10</v>
+        <v>1.58</v>
       </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
@@ -5660,18 +5660,18 @@
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>-1.77</v>
+        <v>-0.1</v>
       </c>
       <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="n">
-        <v>1867197360</v>
+        <v>2091104996</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>BLX</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5680,19 +5680,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.0765</v>
+        <v>0.2189</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>45818.80265583334</v>
+        <v>45945.66391778935</v>
       </c>
       <c r="G107" t="n">
-        <v>131.96</v>
+        <v>45.76</v>
       </c>
       <c r="H107" t="n">
-        <v>153.77</v>
+        <v>44.25</v>
       </c>
       <c r="I107" t="n">
-        <v>10.09</v>
+        <v>10.02</v>
       </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
@@ -5709,18 +5709,18 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>1.67</v>
+        <v>-0.33</v>
       </c>
       <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="n">
-        <v>2017852950</v>
+        <v>2066989908</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5729,19 +5729,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1</v>
+        <v>0.3946</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>45910.65507498843</v>
+        <v>45936.87125002315</v>
       </c>
       <c r="G108" t="n">
-        <v>37.44</v>
+        <v>25.34</v>
       </c>
       <c r="H108" t="n">
-        <v>46.95</v>
+        <v>24.9</v>
       </c>
       <c r="I108" t="n">
-        <v>37.44</v>
+        <v>10</v>
       </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
@@ -5758,18 +5758,18 @@
         <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>9.51</v>
+        <v>-0.17</v>
       </c>
       <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="n">
-        <v>1642762235</v>
+        <v>1867462173</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5778,19 +5778,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.1572</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>45692.86612574074</v>
+        <v>45818.90866184028</v>
       </c>
       <c r="G109" t="n">
-        <v>127.16</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="H109" t="n">
-        <v>121.13</v>
+        <v>99.8</v>
       </c>
       <c r="I109" t="n">
-        <v>19.99</v>
+        <v>0.65</v>
       </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
@@ -5807,18 +5807,18 @@
         <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>-0.95</v>
+        <v>0.19</v>
       </c>
       <c r="Q109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="n">
-        <v>1666461140</v>
+        <v>2066988146</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5827,19 +5827,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.2651</v>
+        <v>0.102</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>45708.68207092593</v>
+        <v>45936.870276875</v>
       </c>
       <c r="G110" t="n">
-        <v>37.7</v>
+        <v>98.06</v>
       </c>
       <c r="H110" t="n">
-        <v>26.02</v>
+        <v>99.8</v>
       </c>
       <c r="I110" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
@@ -5856,18 +5856,18 @@
         <v>0</v>
       </c>
       <c r="P110" t="n">
-        <v>-3.09</v>
+        <v>0.18</v>
       </c>
       <c r="Q110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="n">
-        <v>1744879358</v>
+        <v>1997561527</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5876,19 +5876,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.0247</v>
+        <v>0.1498</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>45751.73925940973</v>
+        <v>45898.65748991898</v>
       </c>
       <c r="G111" t="n">
-        <v>148.09</v>
+        <v>66.73</v>
       </c>
       <c r="H111" t="n">
-        <v>295.11</v>
+        <v>57.2</v>
       </c>
       <c r="I111" t="n">
-        <v>3.66</v>
+        <v>10</v>
       </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
@@ -5905,7 +5905,7 @@
         <v>0</v>
       </c>
       <c r="P111" t="n">
-        <v>3.63</v>
+        <v>-1.43</v>
       </c>
       <c r="Q111" t="inlineStr"/>
     </row>
@@ -5934,7 +5934,7 @@
         <v>62.88</v>
       </c>
       <c r="H112" t="n">
-        <v>61.52</v>
+        <v>64.41</v>
       </c>
       <c r="I112" t="n">
         <v>10.01</v>
@@ -5954,18 +5954,18 @@
         <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>-0.22</v>
+        <v>0.24</v>
       </c>
       <c r="Q112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="n">
-        <v>1495551484</v>
+        <v>1972092684</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5974,19 +5974,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.1914</v>
+        <v>1</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>45580.70648087963</v>
+        <v>45882.68269449074</v>
       </c>
       <c r="G113" t="n">
-        <v>135.82</v>
+        <v>18.8</v>
       </c>
       <c r="H113" t="n">
-        <v>121.13</v>
+        <v>17.52</v>
       </c>
       <c r="I113" t="n">
-        <v>26</v>
+        <v>18.8</v>
       </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
@@ -6003,18 +6003,18 @@
         <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>-2.82</v>
+        <v>-1.28</v>
       </c>
       <c r="Q113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="n">
-        <v>1923259795</v>
+        <v>2108027255</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>VALE</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6023,19 +6023,19 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.4424</v>
+        <v>0.3321</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>45853.65609353009</v>
+        <v>45951.66335608796</v>
       </c>
       <c r="G114" t="n">
-        <v>22.59</v>
+        <v>11.27</v>
       </c>
       <c r="H114" t="n">
-        <v>24.06</v>
+        <v>12.08</v>
       </c>
       <c r="I114" t="n">
-        <v>9.99</v>
+        <v>3.74</v>
       </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
@@ -6052,18 +6052,18 @@
         <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>0.65</v>
+        <v>0.27</v>
       </c>
       <c r="Q114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="n">
-        <v>2050937088</v>
+        <v>1880441651</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>BTCE.DE</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6072,19 +6072,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.0984</v>
+        <v>1</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>45929.65204666667</v>
+        <v>45825.89055887731</v>
       </c>
       <c r="G115" t="n">
-        <v>86.06999999999999</v>
+        <v>21.21</v>
       </c>
       <c r="H115" t="n">
-        <v>81.605</v>
+        <v>17.52</v>
       </c>
       <c r="I115" t="n">
-        <v>10</v>
+        <v>21.21</v>
       </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
@@ -6101,18 +6101,18 @@
         <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>-0.68</v>
+        <v>-3.69</v>
       </c>
       <c r="Q115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="n">
-        <v>1744767540</v>
+        <v>2165851289</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6121,16 +6121,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.643</v>
+        <v>0.2121</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>45751.72316712963</v>
+        <v>45974.6615252662</v>
       </c>
       <c r="G116" t="n">
-        <v>15.55</v>
+        <v>47.14</v>
       </c>
       <c r="H116" t="n">
-        <v>22.51</v>
+        <v>46.96</v>
       </c>
       <c r="I116" t="n">
         <v>10</v>
@@ -6150,18 +6150,18 @@
         <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>4.47</v>
+        <v>-0.04</v>
       </c>
       <c r="Q116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="n">
-        <v>2076201130</v>
+        <v>2132991984</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6170,16 +6170,16 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.499</v>
+        <v>0.101</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>45939.75708394676</v>
+        <v>45960.53958806713</v>
       </c>
       <c r="G117" t="n">
-        <v>20.04</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H117" t="n">
-        <v>19.34</v>
+        <v>67.745</v>
       </c>
       <c r="I117" t="n">
         <v>10</v>
@@ -6199,18 +6199,18 @@
         <v>0</v>
       </c>
       <c r="P117" t="n">
-        <v>-0.35</v>
+        <v>-2.15</v>
       </c>
       <c r="Q117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="n">
-        <v>1754304266</v>
+        <v>2165969654</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6219,19 +6219,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.7137</v>
+        <v>0.5229</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>45755.88055112268</v>
+        <v>45974.67338539352</v>
       </c>
       <c r="G118" t="n">
-        <v>14</v>
+        <v>9.849</v>
       </c>
       <c r="H118" t="n">
-        <v>22.51</v>
+        <v>9.787000000000001</v>
       </c>
       <c r="I118" t="n">
-        <v>9.99</v>
+        <v>5.15</v>
       </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
@@ -6248,18 +6248,18 @@
         <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>6.08</v>
+        <v>-0.03</v>
       </c>
       <c r="Q118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="n">
-        <v>1880441651</v>
+        <v>2103482409</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6268,19 +6268,19 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>45825.89055887731</v>
+        <v>45950.57414493056</v>
       </c>
       <c r="G119" t="n">
-        <v>21.21</v>
+        <v>85.38</v>
       </c>
       <c r="H119" t="n">
-        <v>19.75</v>
+        <v>67.745</v>
       </c>
       <c r="I119" t="n">
-        <v>21.21</v>
+        <v>9.99</v>
       </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
@@ -6297,18 +6297,18 @@
         <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>-1.46</v>
+        <v>-2.22</v>
       </c>
       <c r="Q119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="n">
-        <v>2091302201</v>
+        <v>1642762235</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>BTCE.DE</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6317,19 +6317,19 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.099</v>
+        <v>0.1572</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>45945.68849447917</v>
+        <v>45692.86612574074</v>
       </c>
       <c r="G120" t="n">
-        <v>86.41</v>
+        <v>127.16</v>
       </c>
       <c r="H120" t="n">
-        <v>81.605</v>
+        <v>105.97</v>
       </c>
       <c r="I120" t="n">
-        <v>9.99</v>
+        <v>19.99</v>
       </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
@@ -6346,18 +6346,18 @@
         <v>0</v>
       </c>
       <c r="P120" t="n">
-        <v>-0.61</v>
+        <v>-3.33</v>
       </c>
       <c r="Q120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="n">
-        <v>1976499401</v>
+        <v>1923250768</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6366,19 +6366,19 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.8064</v>
+        <v>0.87</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>45884.83731814815</v>
+        <v>45853.65447396991</v>
       </c>
       <c r="G121" t="n">
-        <v>49.6</v>
+        <v>12.76</v>
       </c>
       <c r="H121" t="n">
-        <v>48.43</v>
+        <v>18.02</v>
       </c>
       <c r="I121" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
@@ -6395,18 +6395,18 @@
         <v>0</v>
       </c>
       <c r="P121" t="n">
-        <v>-0.95</v>
+        <v>4.98</v>
       </c>
       <c r="Q121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="n">
-        <v>1843474191</v>
+        <v>2130244352</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6415,19 +6415,19 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.9372</v>
+        <v>0.0857</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>45804.66699503472</v>
+        <v>45959.70758293982</v>
       </c>
       <c r="G122" t="n">
-        <v>21.33</v>
+        <v>116.75</v>
       </c>
       <c r="H122" t="n">
-        <v>24.06</v>
+        <v>105.97</v>
       </c>
       <c r="I122" t="n">
-        <v>19.99</v>
+        <v>10.01</v>
       </c>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
@@ -6444,18 +6444,18 @@
         <v>0</v>
       </c>
       <c r="P122" t="n">
-        <v>2.56</v>
+        <v>-0.93</v>
       </c>
       <c r="Q122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="n">
-        <v>1993382859</v>
+        <v>1830408508</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6464,19 +6464,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.0779</v>
+        <v>0.5793</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>45896.66809304398</v>
+        <v>45796.82346997685</v>
       </c>
       <c r="G123" t="n">
-        <v>128.25</v>
+        <v>17.26</v>
       </c>
       <c r="H123" t="n">
-        <v>121.13</v>
+        <v>24.43</v>
       </c>
       <c r="I123" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
@@ -6493,18 +6493,18 @@
         <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>-0.55</v>
+        <v>4.15</v>
       </c>
       <c r="Q123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="n">
-        <v>1845429956</v>
+        <v>2141394559</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>UEC</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6513,19 +6513,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.4821</v>
+        <v>0.7027</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>45805.66180811343</v>
+        <v>45964.79105378472</v>
       </c>
       <c r="G124" t="n">
-        <v>13.275</v>
+        <v>14.23</v>
       </c>
       <c r="H124" t="n">
-        <v>16.645</v>
+        <v>12.11</v>
       </c>
       <c r="I124" t="n">
-        <v>7.28</v>
+        <v>10</v>
       </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
@@ -6542,18 +6542,18 @@
         <v>0</v>
       </c>
       <c r="P124" t="n">
-        <v>2.04</v>
+        <v>-1.49</v>
       </c>
       <c r="Q124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="n">
-        <v>1635194117</v>
+        <v>2174832705</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6562,19 +6562,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.2479</v>
+        <v>0.3314</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>45687.85228493056</v>
+        <v>45978.88314283565</v>
       </c>
       <c r="G125" t="n">
-        <v>40.33</v>
+        <v>45.26</v>
       </c>
       <c r="H125" t="n">
-        <v>26.02</v>
+        <v>46.62</v>
       </c>
       <c r="I125" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
@@ -6591,14 +6591,14 @@
         <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>-3.55</v>
+        <v>0.45</v>
       </c>
       <c r="Q125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="n">
-        <v>2035163256</v>
+        <v>2176491048</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -6611,16 +6611,16 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.0951</v>
+        <v>0.1216</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>45919.66675122685</v>
+        <v>45979.56363978009</v>
       </c>
       <c r="G126" t="n">
-        <v>88.91</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="H126" t="n">
-        <v>81.605</v>
+        <v>67.745</v>
       </c>
       <c r="I126" t="n">
         <v>9.99</v>
@@ -6640,18 +6640,18 @@
         <v>0</v>
       </c>
       <c r="P126" t="n">
-        <v>-0.98</v>
+        <v>-0.54</v>
       </c>
       <c r="Q126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="n">
-        <v>2045991969</v>
+        <v>2174826426</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>VALE</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6660,16 +6660,16 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.4928</v>
+        <v>0.8183</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>45925.80038483796</v>
+        <v>45978.8814528125</v>
       </c>
       <c r="G127" t="n">
-        <v>20.29</v>
+        <v>12.22</v>
       </c>
       <c r="H127" t="n">
-        <v>19.34</v>
+        <v>12.08</v>
       </c>
       <c r="I127" t="n">
         <v>10</v>
@@ -6689,18 +6689,18 @@
         <v>0</v>
       </c>
       <c r="P127" t="n">
-        <v>-0.47</v>
+        <v>-0.11</v>
       </c>
       <c r="Q127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="n">
-        <v>2099892569</v>
+        <v>2079414382</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BTCE.DE</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6709,19 +6709,19 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.1057</v>
+        <v>0.0351</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>45947.69061754629</v>
+        <v>45940.73297075232</v>
       </c>
       <c r="G128" t="n">
-        <v>80.62</v>
+        <v>285.2</v>
       </c>
       <c r="H128" t="n">
-        <v>81.605</v>
+        <v>284.69</v>
       </c>
       <c r="I128" t="n">
-        <v>9.99</v>
+        <v>10.01</v>
       </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
@@ -6738,18 +6738,18 @@
         <v>0</v>
       </c>
       <c r="P128" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="Q128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="n">
-        <v>1923246263</v>
+        <v>2065634230</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6758,19 +6758,19 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1</v>
+        <v>0.7849</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>45853.6538128125</v>
+        <v>45936.60990405093</v>
       </c>
       <c r="G129" t="n">
-        <v>21.17</v>
+        <v>16.28</v>
       </c>
       <c r="H129" t="n">
-        <v>19.75</v>
+        <v>18.02</v>
       </c>
       <c r="I129" t="n">
-        <v>21.17</v>
+        <v>15</v>
       </c>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
@@ -6787,18 +6787,18 @@
         <v>0</v>
       </c>
       <c r="P129" t="n">
-        <v>-1.42</v>
+        <v>1.22</v>
       </c>
       <c r="Q129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="n">
-        <v>2050940197</v>
+        <v>2017777441</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6807,19 +6807,19 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.3238</v>
+        <v>0.4582</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>45929.65257815972</v>
+        <v>45910.64656457176</v>
       </c>
       <c r="G130" t="n">
-        <v>30.91</v>
+        <v>21.82</v>
       </c>
       <c r="H130" t="n">
-        <v>31.63</v>
+        <v>24.43</v>
       </c>
       <c r="I130" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
@@ -6836,18 +6836,18 @@
         <v>0</v>
       </c>
       <c r="P130" t="n">
-        <v>0.23</v>
+        <v>1.19</v>
       </c>
       <c r="Q130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="n">
-        <v>1727563010</v>
+        <v>2042971604</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6856,19 +6856,19 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1</v>
+        <v>0.3901</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>45743.76106726852</v>
+        <v>45924.70406969907</v>
       </c>
       <c r="G131" t="n">
-        <v>46.11</v>
+        <v>25.66</v>
       </c>
       <c r="H131" t="n">
-        <v>54.39</v>
+        <v>22.68</v>
       </c>
       <c r="I131" t="n">
-        <v>46.11</v>
+        <v>10.01</v>
       </c>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
@@ -6885,18 +6885,18 @@
         <v>0</v>
       </c>
       <c r="P131" t="n">
-        <v>8.279999999999999</v>
+        <v>-1.16</v>
       </c>
       <c r="Q131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="n">
-        <v>2045990228</v>
+        <v>1983186744</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6905,19 +6905,19 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.0839</v>
+        <v>0.3162</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>45925.79958348379</v>
+        <v>45889.85904239583</v>
       </c>
       <c r="G132" t="n">
-        <v>36.75</v>
+        <v>31.61</v>
       </c>
       <c r="H132" t="n">
-        <v>42.12</v>
+        <v>35.22</v>
       </c>
       <c r="I132" t="n">
-        <v>3.08</v>
+        <v>10</v>
       </c>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
@@ -6934,18 +6934,18 @@
         <v>0</v>
       </c>
       <c r="P132" t="n">
-        <v>0.45</v>
+        <v>1.14</v>
       </c>
       <c r="Q132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="n">
-        <v>1824482557</v>
+        <v>2109293021</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6954,19 +6954,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.2641</v>
+        <v>0.4208</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>45792.64805195602</v>
+        <v>45951.83135178241</v>
       </c>
       <c r="G133" t="n">
-        <v>56.78</v>
+        <v>23.75</v>
       </c>
       <c r="H133" t="n">
-        <v>65</v>
+        <v>24.9</v>
       </c>
       <c r="I133" t="n">
-        <v>15</v>
+        <v>9.99</v>
       </c>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
@@ -6983,18 +6983,18 @@
         <v>0</v>
       </c>
       <c r="P133" t="n">
-        <v>2.17</v>
+        <v>0.49</v>
       </c>
       <c r="Q133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="n">
-        <v>2072501999</v>
+        <v>2169093277</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -7003,19 +7003,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.0121</v>
+        <v>0.1164</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>45938.67873797454</v>
+        <v>45975.57876332176</v>
       </c>
       <c r="G134" t="n">
-        <v>844.9</v>
+        <v>73.37</v>
       </c>
       <c r="H134" t="n">
-        <v>875.4</v>
+        <v>67.745</v>
       </c>
       <c r="I134" t="n">
-        <v>11.95</v>
+        <v>10</v>
       </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
@@ -7032,18 +7032,18 @@
         <v>0</v>
       </c>
       <c r="P134" t="n">
-        <v>0.35</v>
+        <v>-0.96</v>
       </c>
       <c r="Q134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="n">
-        <v>2002503461</v>
+        <v>2112359590</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>SGLD.L</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7052,16 +7052,16 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.0439</v>
+        <v>0.0255</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>45902.65623520833</v>
+        <v>45952.66207533565</v>
       </c>
       <c r="G135" t="n">
-        <v>227.95</v>
+        <v>392.65</v>
       </c>
       <c r="H135" t="n">
-        <v>295.11</v>
+        <v>393.97</v>
       </c>
       <c r="I135" t="n">
         <v>10.01</v>
@@ -7081,18 +7081,18 @@
         <v>0</v>
       </c>
       <c r="P135" t="n">
-        <v>2.95</v>
+        <v>0.04</v>
       </c>
       <c r="Q135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="n">
-        <v>1559803221</v>
+        <v>2066990620</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7101,19 +7101,19 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.092</v>
+        <v>0.1541</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>45628.85951927083</v>
+        <v>45936.87171386574</v>
       </c>
       <c r="G136" t="n">
-        <v>162.85</v>
+        <v>64.88</v>
       </c>
       <c r="H136" t="n">
-        <v>153.77</v>
+        <v>57.2</v>
       </c>
       <c r="I136" t="n">
-        <v>14.98</v>
+        <v>10</v>
       </c>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
@@ -7130,18 +7130,18 @@
         <v>0</v>
       </c>
       <c r="P136" t="n">
-        <v>-0.83</v>
+        <v>-1.19</v>
       </c>
       <c r="Q136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="n">
-        <v>1984829391</v>
+        <v>2157051303</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>WEN</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7150,19 +7150,19 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.0512</v>
+        <v>0.1627</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>45890.71798858796</v>
+        <v>45971.69031855324</v>
       </c>
       <c r="G137" t="n">
-        <v>195.52</v>
+        <v>8.6</v>
       </c>
       <c r="H137" t="n">
-        <v>231.77</v>
+        <v>7.91</v>
       </c>
       <c r="I137" t="n">
-        <v>10.01</v>
+        <v>1.4</v>
       </c>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
@@ -7179,18 +7179,18 @@
         <v>0</v>
       </c>
       <c r="P137" t="n">
-        <v>1.86</v>
+        <v>-0.11</v>
       </c>
       <c r="Q137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="n">
-        <v>1796453499</v>
+        <v>1867458993</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7199,19 +7199,19 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.3417</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>45777.64668229167</v>
+        <v>45818.90699613426</v>
       </c>
       <c r="G138" t="n">
-        <v>15.57</v>
+        <v>58.53</v>
       </c>
       <c r="H138" t="n">
-        <v>19.34</v>
+        <v>57.2</v>
       </c>
       <c r="I138" t="n">
-        <v>8.01</v>
+        <v>20</v>
       </c>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
@@ -7228,18 +7228,18 @@
         <v>0</v>
       </c>
       <c r="P138" t="n">
-        <v>1.94</v>
+        <v>-0.45</v>
       </c>
       <c r="Q138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="n">
-        <v>1997552824</v>
+        <v>1923224670</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7248,19 +7248,19 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.0429</v>
+        <v>0.2583</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>45898.65627293981</v>
+        <v>45853.65359685185</v>
       </c>
       <c r="G139" t="n">
-        <v>233.17</v>
+        <v>58.05</v>
       </c>
       <c r="H139" t="n">
-        <v>295.11</v>
+        <v>57.2</v>
       </c>
       <c r="I139" t="n">
-        <v>10</v>
+        <v>14.99</v>
       </c>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
@@ -7277,18 +7277,18 @@
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>2.66</v>
+        <v>-0.22</v>
       </c>
       <c r="Q139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="n">
-        <v>1867462173</v>
+        <v>2134206350</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7297,19 +7297,19 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0521</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>45818.90866184028</v>
+        <v>45960.73897074074</v>
       </c>
       <c r="G140" t="n">
-        <v>77.93000000000001</v>
+        <v>192.07</v>
       </c>
       <c r="H140" t="n">
-        <v>97.06</v>
+        <v>175.09</v>
       </c>
       <c r="I140" t="n">
-        <v>0.65</v>
+        <v>10.01</v>
       </c>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
@@ -7326,18 +7326,18 @@
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>0.17</v>
+        <v>-0.89</v>
       </c>
       <c r="Q140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="n">
-        <v>2017777441</v>
+        <v>1727563010</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -7346,19 +7346,19 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.4582</v>
+        <v>1</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>45910.64656457176</v>
+        <v>45743.76106726852</v>
       </c>
       <c r="G141" t="n">
-        <v>21.82</v>
+        <v>46.11</v>
       </c>
       <c r="H141" t="n">
-        <v>22.51</v>
+        <v>53.62</v>
       </c>
       <c r="I141" t="n">
-        <v>10</v>
+        <v>46.11</v>
       </c>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
@@ -7375,18 +7375,18 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>0.31</v>
+        <v>7.51</v>
       </c>
       <c r="Q141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="n">
-        <v>1653137218</v>
+        <v>2134088809</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7395,16 +7395,16 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.277</v>
+        <v>0.103</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>45699.85152199074</v>
+        <v>45960.70532193287</v>
       </c>
       <c r="G142" t="n">
-        <v>36.1</v>
+        <v>83.545</v>
       </c>
       <c r="H142" t="n">
-        <v>26.02</v>
+        <v>67.745</v>
       </c>
       <c r="I142" t="n">
         <v>10</v>
@@ -7424,18 +7424,18 @@
         <v>0</v>
       </c>
       <c r="P142" t="n">
-        <v>-2.79</v>
+        <v>-2</v>
       </c>
       <c r="Q142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="n">
-        <v>1923271589</v>
+        <v>2149911198</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>UEC</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -7444,19 +7444,19 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.4478</v>
+        <v>0.8045</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>45853.65794861111</v>
+        <v>45967.69368804398</v>
       </c>
       <c r="G143" t="n">
-        <v>44.66</v>
+        <v>12.43</v>
       </c>
       <c r="H143" t="n">
-        <v>56.8</v>
+        <v>12.11</v>
       </c>
       <c r="I143" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
@@ -7473,18 +7473,18 @@
         <v>0</v>
       </c>
       <c r="P143" t="n">
-        <v>5.44</v>
+        <v>-0.26</v>
       </c>
       <c r="Q143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="n">
-        <v>2047814173</v>
+        <v>2107043621</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>IAPD.AS</t>
+          <t>SGLD.L</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7493,19 +7493,19 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.5688</v>
+        <v>0.0487</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>45926.6592943287</v>
+        <v>45951.50373594907</v>
       </c>
       <c r="G144" t="n">
-        <v>22.46</v>
+        <v>410.41</v>
       </c>
       <c r="H144" t="n">
-        <v>22.975</v>
+        <v>393.97</v>
       </c>
       <c r="I144" t="n">
-        <v>15</v>
+        <v>19.99</v>
       </c>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
@@ -7522,18 +7522,18 @@
         <v>0</v>
       </c>
       <c r="P144" t="n">
-        <v>0.17</v>
+        <v>-0.8</v>
       </c>
       <c r="Q144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="n">
-        <v>1680993370</v>
+        <v>2174225418</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>CSIQ</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -7542,19 +7542,19 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1</v>
+        <v>0.3427</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>45716.85638861111</v>
+        <v>45978.75694429398</v>
       </c>
       <c r="G145" t="n">
-        <v>44.49</v>
+        <v>29.18</v>
       </c>
       <c r="H145" t="n">
-        <v>54.39</v>
+        <v>24.89</v>
       </c>
       <c r="I145" t="n">
-        <v>44.49</v>
+        <v>10</v>
       </c>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
@@ -7571,18 +7571,18 @@
         <v>0</v>
       </c>
       <c r="P145" t="n">
-        <v>9.9</v>
+        <v>-1.47</v>
       </c>
       <c r="Q145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="n">
-        <v>2048539334</v>
+        <v>2187245584</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7591,19 +7591,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1</v>
+        <v>0.0367</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>45926.85025574074</v>
+        <v>45982.64992649305</v>
       </c>
       <c r="G146" t="n">
-        <v>42.2</v>
+        <v>272.9</v>
       </c>
       <c r="H146" t="n">
-        <v>46.95</v>
+        <v>284.69</v>
       </c>
       <c r="I146" t="n">
-        <v>42.2</v>
+        <v>10.02</v>
       </c>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
@@ -7620,18 +7620,18 @@
         <v>0</v>
       </c>
       <c r="P146" t="n">
-        <v>4.75</v>
+        <v>0.43</v>
       </c>
       <c r="Q146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="n">
-        <v>2080269311</v>
+        <v>2091302201</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -7640,19 +7640,19 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1</v>
+        <v>0.099</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>45940.886384375</v>
+        <v>45945.68849447917</v>
       </c>
       <c r="G147" t="n">
-        <v>52.53</v>
+        <v>86.41</v>
       </c>
       <c r="H147" t="n">
-        <v>54.39</v>
+        <v>67.745</v>
       </c>
       <c r="I147" t="n">
-        <v>52.53</v>
+        <v>9.99</v>
       </c>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
@@ -7669,18 +7669,18 @@
         <v>0</v>
       </c>
       <c r="P147" t="n">
-        <v>1.86</v>
+        <v>-2.3</v>
       </c>
       <c r="Q147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="n">
-        <v>2072487323</v>
+        <v>2060617471</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7689,19 +7689,19 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.4062</v>
+        <v>0.2255</v>
       </c>
       <c r="F148" s="2" t="n">
-        <v>45938.67565716435</v>
+        <v>45932.89647650463</v>
       </c>
       <c r="G148" t="n">
-        <v>24.64</v>
+        <v>44.35</v>
       </c>
       <c r="H148" t="n">
-        <v>23.11</v>
+        <v>41.51</v>
       </c>
       <c r="I148" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
@@ -7718,18 +7718,18 @@
         <v>0</v>
       </c>
       <c r="P148" t="n">
-        <v>-0.62</v>
+        <v>-0.64</v>
       </c>
       <c r="Q148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="n">
-        <v>2091099733</v>
+        <v>1880442840</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>BBAR</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7738,19 +7738,19 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1</v>
+        <v>0.2535</v>
       </c>
       <c r="F149" s="2" t="n">
-        <v>45945.6631174537</v>
+        <v>45825.89113450232</v>
       </c>
       <c r="G149" t="n">
-        <v>9.619999999999999</v>
+        <v>59.15</v>
       </c>
       <c r="H149" t="n">
-        <v>9.380000000000001</v>
+        <v>57.2</v>
       </c>
       <c r="I149" t="n">
-        <v>9.619999999999999</v>
+        <v>14.99</v>
       </c>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
@@ -7767,14 +7767,14 @@
         <v>0</v>
       </c>
       <c r="P149" t="n">
-        <v>-0.24</v>
+        <v>-0.49</v>
       </c>
       <c r="Q149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="n">
-        <v>1880442840</v>
+        <v>2027639997</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -7787,19 +7787,19 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.2535</v>
+        <v>0.1558</v>
       </c>
       <c r="F150" s="2" t="n">
-        <v>45825.89113450232</v>
+        <v>45916.65703747685</v>
       </c>
       <c r="G150" t="n">
-        <v>59.15</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="H150" t="n">
-        <v>65</v>
+        <v>57.2</v>
       </c>
       <c r="I150" t="n">
-        <v>14.99</v>
+        <v>10</v>
       </c>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
@@ -7816,18 +7816,18 @@
         <v>0</v>
       </c>
       <c r="P150" t="n">
-        <v>1.49</v>
+        <v>-1.09</v>
       </c>
       <c r="Q150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="n">
-        <v>1563288050</v>
+        <v>2000138014</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>BTCE.DE</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7836,16 +7836,16 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.0626</v>
+        <v>0.1017</v>
       </c>
       <c r="F151" s="2" t="n">
-        <v>45630.85583428241</v>
+        <v>45901.57795706019</v>
       </c>
       <c r="G151" t="n">
-        <v>159.74</v>
+        <v>83.47499999999999</v>
       </c>
       <c r="H151" t="n">
-        <v>153.77</v>
+        <v>67.745</v>
       </c>
       <c r="I151" t="n">
         <v>10</v>
@@ -7865,18 +7865,18 @@
         <v>0</v>
       </c>
       <c r="P151" t="n">
-        <v>-0.37</v>
+        <v>-2.1</v>
       </c>
       <c r="Q151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="n">
-        <v>1824475555</v>
+        <v>2025661832</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7885,19 +7885,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1</v>
+        <v>0.3235</v>
       </c>
       <c r="F152" s="2" t="n">
-        <v>45792.64702015046</v>
+        <v>45915.72870862269</v>
       </c>
       <c r="G152" t="n">
-        <v>21.66</v>
+        <v>61.81</v>
       </c>
       <c r="H152" t="n">
-        <v>19.75</v>
+        <v>64.41</v>
       </c>
       <c r="I152" t="n">
-        <v>21.66</v>
+        <v>20</v>
       </c>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
@@ -7914,18 +7914,18 @@
         <v>0</v>
       </c>
       <c r="P152" t="n">
-        <v>-1.91</v>
+        <v>0.84</v>
       </c>
       <c r="Q152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="n">
-        <v>2047758738</v>
+        <v>2170741154</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>WEN</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7934,19 +7934,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.0365</v>
+        <v>0.1627</v>
       </c>
       <c r="F153" s="2" t="n">
-        <v>45926.65183609954</v>
+        <v>45975.82251121528</v>
       </c>
       <c r="G153" t="n">
-        <v>274.22</v>
+        <v>8.59</v>
       </c>
       <c r="H153" t="n">
-        <v>295.11</v>
+        <v>7.91</v>
       </c>
       <c r="I153" t="n">
-        <v>10.01</v>
+        <v>1.4</v>
       </c>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
@@ -7963,18 +7963,18 @@
         <v>0</v>
       </c>
       <c r="P153" t="n">
-        <v>0.76</v>
+        <v>-0.11</v>
       </c>
       <c r="Q153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="n">
-        <v>2002501482</v>
+        <v>2109288256</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>CIB</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7983,19 +7983,19 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.0526</v>
+        <v>0.3653</v>
       </c>
       <c r="F154" s="2" t="n">
-        <v>45902.65588916666</v>
+        <v>45951.82931385416</v>
       </c>
       <c r="G154" t="n">
-        <v>190.17</v>
+        <v>54.74</v>
       </c>
       <c r="H154" t="n">
-        <v>231.77</v>
+        <v>60.33</v>
       </c>
       <c r="I154" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
@@ -8012,18 +8012,18 @@
         <v>0</v>
       </c>
       <c r="P154" t="n">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="Q154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="n">
-        <v>1867194722</v>
+        <v>2170960662</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -8032,19 +8032,19 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1</v>
+        <v>0.4606</v>
       </c>
       <c r="F155" s="2" t="n">
-        <v>45818.80135700232</v>
+        <v>45975.89401422453</v>
       </c>
       <c r="G155" t="n">
-        <v>21.27</v>
+        <v>21.7</v>
       </c>
       <c r="H155" t="n">
-        <v>19.75</v>
+        <v>21.12</v>
       </c>
       <c r="I155" t="n">
-        <v>21.27</v>
+        <v>10</v>
       </c>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
@@ -8061,18 +8061,18 @@
         <v>0</v>
       </c>
       <c r="P155" t="n">
-        <v>-1.52</v>
+        <v>-0.27</v>
       </c>
       <c r="Q155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="n">
-        <v>1997485943</v>
+        <v>2163341970</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -8081,19 +8081,19 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.5157</v>
+        <v>0.2567</v>
       </c>
       <c r="F156" s="2" t="n">
-        <v>45898.65185685185</v>
+        <v>45973.79644112269</v>
       </c>
       <c r="G156" t="n">
-        <v>19.39</v>
+        <v>58.43</v>
       </c>
       <c r="H156" t="n">
-        <v>19.34</v>
+        <v>57.2</v>
       </c>
       <c r="I156" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
@@ -8110,18 +8110,18 @@
         <v>0</v>
       </c>
       <c r="P156" t="n">
-        <v>-0.03</v>
+        <v>-0.32</v>
       </c>
       <c r="Q156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="n">
-        <v>1806980496</v>
+        <v>2130243116</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -8130,19 +8130,19 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1</v>
+        <v>0.2137</v>
       </c>
       <c r="F157" s="2" t="n">
-        <v>45783.83190503472</v>
+        <v>45959.70735681713</v>
       </c>
       <c r="G157" t="n">
-        <v>16.12</v>
+        <v>46.8</v>
       </c>
       <c r="H157" t="n">
-        <v>19.34</v>
+        <v>46.96</v>
       </c>
       <c r="I157" t="n">
-        <v>16.12</v>
+        <v>10</v>
       </c>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
@@ -8159,18 +8159,18 @@
         <v>0</v>
       </c>
       <c r="P157" t="n">
-        <v>3.22</v>
+        <v>0.04</v>
       </c>
       <c r="Q157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="n">
-        <v>1644788775</v>
+        <v>1806980496</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -8179,19 +8179,19 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.07580000000000001</v>
+        <v>1</v>
       </c>
       <c r="F158" s="2" t="n">
-        <v>45693.85093391204</v>
+        <v>45783.83190503472</v>
       </c>
       <c r="G158" t="n">
-        <v>144.94</v>
+        <v>16.12</v>
       </c>
       <c r="H158" t="n">
-        <v>153.77</v>
+        <v>21.12</v>
       </c>
       <c r="I158" t="n">
-        <v>10.99</v>
+        <v>16.12</v>
       </c>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
@@ -8208,18 +8208,18 @@
         <v>0</v>
       </c>
       <c r="P158" t="n">
-        <v>0.67</v>
+        <v>5</v>
       </c>
       <c r="Q158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="n">
-        <v>2025662892</v>
+        <v>1923258249</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -8228,19 +8228,19 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.8196</v>
+        <v>1</v>
       </c>
       <c r="F159" s="2" t="n">
-        <v>45915.72913914352</v>
+        <v>45853.65576626157</v>
       </c>
       <c r="G159" t="n">
-        <v>24.39</v>
+        <v>19.41</v>
       </c>
       <c r="H159" t="n">
-        <v>23.11</v>
+        <v>24.43</v>
       </c>
       <c r="I159" t="n">
-        <v>19.99</v>
+        <v>19.41</v>
       </c>
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
@@ -8257,18 +8257,18 @@
         <v>0</v>
       </c>
       <c r="P159" t="n">
-        <v>-1.05</v>
+        <v>5.02</v>
       </c>
       <c r="Q159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="n">
-        <v>2042971604</v>
+        <v>2141582221</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -8277,16 +8277,16 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.3901</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="F160" s="2" t="n">
-        <v>45924.70406969907</v>
+        <v>45964.83888591435</v>
       </c>
       <c r="G160" t="n">
-        <v>25.66</v>
+        <v>102.97</v>
       </c>
       <c r="H160" t="n">
-        <v>23.11</v>
+        <v>104.89</v>
       </c>
       <c r="I160" t="n">
         <v>10.01</v>
@@ -8306,18 +8306,18 @@
         <v>0</v>
       </c>
       <c r="P160" t="n">
-        <v>-0.99</v>
+        <v>0.19</v>
       </c>
       <c r="Q160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="n">
-        <v>1928218937</v>
+        <v>2060620530</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>BLX</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -8326,19 +8326,19 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1</v>
+        <v>0.2207</v>
       </c>
       <c r="F161" s="2" t="n">
-        <v>45855.75970359953</v>
+        <v>45932.89856876157</v>
       </c>
       <c r="G161" t="n">
-        <v>20.24</v>
+        <v>45.28</v>
       </c>
       <c r="H161" t="n">
-        <v>19.75</v>
+        <v>44.25</v>
       </c>
       <c r="I161" t="n">
-        <v>20.24</v>
+        <v>9.99</v>
       </c>
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
@@ -8355,18 +8355,18 @@
         <v>0</v>
       </c>
       <c r="P161" t="n">
-        <v>-0.49</v>
+        <v>-0.22</v>
       </c>
       <c r="Q161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="n">
-        <v>1989207013</v>
+        <v>2159083184</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>JKS</t>
+          <t>NDIA.L</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -8375,19 +8375,19 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.4133</v>
+        <v>0.0159</v>
       </c>
       <c r="F162" s="2" t="n">
-        <v>45894.65354606482</v>
+        <v>45972.55636200232</v>
       </c>
       <c r="G162" t="n">
-        <v>24.19</v>
+        <v>9.842000000000001</v>
       </c>
       <c r="H162" t="n">
-        <v>23.11</v>
+        <v>9.787000000000001</v>
       </c>
       <c r="I162" t="n">
-        <v>10</v>
+        <v>0.16</v>
       </c>
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
@@ -8404,18 +8404,18 @@
         <v>0</v>
       </c>
       <c r="P162" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="Q162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="n">
-        <v>2060624552</v>
+        <v>2177446291</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>CSIQ</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -8424,19 +8424,19 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.1676</v>
+        <v>0.3769</v>
       </c>
       <c r="F163" s="2" t="n">
-        <v>45932.90130990741</v>
+        <v>45979.70391243055</v>
       </c>
       <c r="G163" t="n">
-        <v>59.7</v>
+        <v>26.53</v>
       </c>
       <c r="H163" t="n">
-        <v>61.52</v>
+        <v>24.89</v>
       </c>
       <c r="I163" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
@@ -8453,18 +8453,18 @@
         <v>0</v>
       </c>
       <c r="P163" t="n">
-        <v>0.3</v>
+        <v>-0.62</v>
       </c>
       <c r="Q163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="n">
-        <v>1744930699</v>
+        <v>1867193336</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -8476,16 +8476,16 @@
         <v>1</v>
       </c>
       <c r="F164" s="2" t="n">
-        <v>45751.74534789352</v>
+        <v>45818.80084483796</v>
       </c>
       <c r="G164" t="n">
-        <v>74.13</v>
+        <v>17.64</v>
       </c>
       <c r="H164" t="n">
-        <v>74.88</v>
+        <v>21.12</v>
       </c>
       <c r="I164" t="n">
-        <v>74.13</v>
+        <v>17.64</v>
       </c>
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
@@ -8502,18 +8502,18 @@
         <v>0</v>
       </c>
       <c r="P164" t="n">
-        <v>0.75</v>
+        <v>3.48</v>
       </c>
       <c r="Q164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="n">
-        <v>2079414382</v>
+        <v>2173747681</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>CSIQ</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -8522,19 +8522,19 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.0351</v>
+        <v>0.3363</v>
       </c>
       <c r="F165" s="2" t="n">
-        <v>45940.73297075232</v>
+        <v>45978.66955163195</v>
       </c>
       <c r="G165" t="n">
-        <v>285.2</v>
+        <v>29.74</v>
       </c>
       <c r="H165" t="n">
-        <v>295.11</v>
+        <v>24.89</v>
       </c>
       <c r="I165" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
@@ -8551,27 +8551,45 @@
         <v>0</v>
       </c>
       <c r="P165" t="n">
-        <v>0.35</v>
+        <v>-1.63</v>
       </c>
       <c r="Q165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr"/>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr"/>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
+      <c r="B166" t="n">
+        <v>2091115227</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>YPF</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="F166" s="2" t="n">
+        <v>45945.66604186343</v>
+      </c>
+      <c r="G166" t="n">
+        <v>26.59</v>
+      </c>
+      <c r="H166" t="n">
+        <v>35.22</v>
+      </c>
+      <c r="I166" t="n">
+        <v>10</v>
+      </c>
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
       <c r="M166" t="n">
         <v>0</v>
       </c>
@@ -8582,9 +8600,1951 @@
         <v>0</v>
       </c>
       <c r="P166" t="n">
-        <v>149.79</v>
+        <v>3.24</v>
       </c>
       <c r="Q166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+      <c r="B167" t="n">
+        <v>1744916452</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ING</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>0.4245</v>
+      </c>
+      <c r="F167" s="2" t="n">
+        <v>45751.74230173611</v>
+      </c>
+      <c r="G167" t="n">
+        <v>17.54</v>
+      </c>
+      <c r="H167" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I167" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="Q167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+      <c r="B168" t="n">
+        <v>2047825292</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>BLX</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="F168" s="2" t="n">
+        <v>45926.66222740741</v>
+      </c>
+      <c r="G168" t="n">
+        <v>47.56</v>
+      </c>
+      <c r="H168" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="I168" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="Q168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+      <c r="B169" t="n">
+        <v>2078907475</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>PHGP.L</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="F169" s="2" t="n">
+        <v>45940.67644164352</v>
+      </c>
+      <c r="G169" t="n">
+        <v>278.84</v>
+      </c>
+      <c r="H169" t="n">
+        <v>290.47</v>
+      </c>
+      <c r="I169" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Q169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" t="n">
+        <v>1993382859</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>INGR</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>0.0779</v>
+      </c>
+      <c r="F170" s="2" t="n">
+        <v>45896.66809304398</v>
+      </c>
+      <c r="G170" t="n">
+        <v>128.25</v>
+      </c>
+      <c r="H170" t="n">
+        <v>105.97</v>
+      </c>
+      <c r="I170" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="Q170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr"/>
+      <c r="B171" t="n">
+        <v>1701100027</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>0.5043</v>
+      </c>
+      <c r="F171" s="2" t="n">
+        <v>45727.87202070602</v>
+      </c>
+      <c r="G171" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H171" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="I171" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" t="n">
+        <v>0</v>
+      </c>
+      <c r="N171" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr"/>
+      <c r="B172" t="n">
+        <v>1754304266</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>0.7137</v>
+      </c>
+      <c r="F172" s="2" t="n">
+        <v>45755.88055112268</v>
+      </c>
+      <c r="G172" t="n">
+        <v>14</v>
+      </c>
+      <c r="H172" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="I172" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" t="n">
+        <v>0</v>
+      </c>
+      <c r="N172" t="n">
+        <v>0</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="Q172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr"/>
+      <c r="B173" t="n">
+        <v>2152947951</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>UEC</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>0.8532</v>
+      </c>
+      <c r="F173" s="2" t="n">
+        <v>45968.67567004629</v>
+      </c>
+      <c r="G173" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="H173" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="I173" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" t="n">
+        <v>0</v>
+      </c>
+      <c r="N173" t="n">
+        <v>0</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="Q173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr"/>
+      <c r="B174" t="n">
+        <v>2109457833</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>INGR</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>0.0829</v>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>45951.87555299768</v>
+      </c>
+      <c r="G174" t="n">
+        <v>120.74</v>
+      </c>
+      <c r="H174" t="n">
+        <v>105.97</v>
+      </c>
+      <c r="I174" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" t="n">
+        <v>0</v>
+      </c>
+      <c r="N174" t="n">
+        <v>0</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="Q174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr"/>
+      <c r="B175" t="n">
+        <v>2170959882</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="F175" s="2" t="n">
+        <v>45975.89367650463</v>
+      </c>
+      <c r="G175" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="H175" t="n">
+        <v>46.62</v>
+      </c>
+      <c r="I175" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" t="n">
+        <v>0</v>
+      </c>
+      <c r="N175" t="n">
+        <v>0</v>
+      </c>
+      <c r="O175" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr"/>
+      <c r="B176" t="n">
+        <v>2109292501</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>VST</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>0.0531</v>
+      </c>
+      <c r="F176" s="2" t="n">
+        <v>45951.83110900463</v>
+      </c>
+      <c r="G176" t="n">
+        <v>188.28</v>
+      </c>
+      <c r="H176" t="n">
+        <v>175.09</v>
+      </c>
+      <c r="I176" t="n">
+        <v>10</v>
+      </c>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" t="n">
+        <v>0</v>
+      </c>
+      <c r="N176" t="n">
+        <v>0</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
+      <c r="P176" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="Q176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr"/>
+      <c r="B177" t="n">
+        <v>2153544118</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>0.1016</v>
+      </c>
+      <c r="F177" s="2" t="n">
+        <v>45968.76700783565</v>
+      </c>
+      <c r="G177" t="n">
+        <v>98.42</v>
+      </c>
+      <c r="H177" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="I177" t="n">
+        <v>10</v>
+      </c>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Q177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr"/>
+      <c r="B178" t="n">
+        <v>2129638702</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>BLX</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>0.2304</v>
+      </c>
+      <c r="F178" s="2" t="n">
+        <v>45959.61074027778</v>
+      </c>
+      <c r="G178" t="n">
+        <v>43.39</v>
+      </c>
+      <c r="H178" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="I178" t="n">
+        <v>10</v>
+      </c>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" t="n">
+        <v>0</v>
+      </c>
+      <c r="N178" t="n">
+        <v>0</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr"/>
+      <c r="B179" t="n">
+        <v>1644796307</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>ACI</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>1</v>
+      </c>
+      <c r="F179" s="2" t="n">
+        <v>45693.85501710648</v>
+      </c>
+      <c r="G179" t="n">
+        <v>20.36</v>
+      </c>
+      <c r="H179" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="I179" t="n">
+        <v>20.36</v>
+      </c>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" t="n">
+        <v>0</v>
+      </c>
+      <c r="N179" t="n">
+        <v>0</v>
+      </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" t="n">
+        <v>-2.84</v>
+      </c>
+      <c r="Q179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr"/>
+      <c r="B180" t="n">
+        <v>1928218937</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>ACI</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>1</v>
+      </c>
+      <c r="F180" s="2" t="n">
+        <v>45855.75970359953</v>
+      </c>
+      <c r="G180" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="H180" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="I180" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" t="n">
+        <v>-2.72</v>
+      </c>
+      <c r="Q180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr"/>
+      <c r="B181" t="n">
+        <v>2136575297</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>SYY</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>0.1352</v>
+      </c>
+      <c r="F181" s="2" t="n">
+        <v>45961.60931016204</v>
+      </c>
+      <c r="G181" t="n">
+        <v>73.95999999999999</v>
+      </c>
+      <c r="H181" t="n">
+        <v>74.64</v>
+      </c>
+      <c r="I181" t="n">
+        <v>10</v>
+      </c>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Q181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr"/>
+      <c r="B182" t="n">
+        <v>2047758738</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>0.0344</v>
+      </c>
+      <c r="F182" s="2" t="n">
+        <v>45926.65183609954</v>
+      </c>
+      <c r="G182" t="n">
+        <v>274.22</v>
+      </c>
+      <c r="H182" t="n">
+        <v>284.69</v>
+      </c>
+      <c r="I182" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" t="n">
+        <v>0</v>
+      </c>
+      <c r="N182" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Q182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr"/>
+      <c r="B183" t="n">
+        <v>2146877942</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>BTCE.DE</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="F183" s="2" t="n">
+        <v>45966.57708880787</v>
+      </c>
+      <c r="G183" t="n">
+        <v>80.13</v>
+      </c>
+      <c r="H183" t="n">
+        <v>67.745</v>
+      </c>
+      <c r="I183" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" t="n">
+        <v>0</v>
+      </c>
+      <c r="N183" t="n">
+        <v>0</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="P183" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="Q183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr"/>
+      <c r="B184" t="n">
+        <v>1923271589</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="F184" s="2" t="n">
+        <v>45853.65794861111</v>
+      </c>
+      <c r="G184" t="n">
+        <v>44.66</v>
+      </c>
+      <c r="H184" t="n">
+        <v>60.33</v>
+      </c>
+      <c r="I184" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="n">
+        <v>0</v>
+      </c>
+      <c r="M184" t="n">
+        <v>0</v>
+      </c>
+      <c r="N184" t="n">
+        <v>0</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="P184" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr"/>
+      <c r="B185" t="n">
+        <v>2035164705</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>PHGP.L</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>0.0273</v>
+      </c>
+      <c r="F185" s="2" t="n">
+        <v>45919.6670447338</v>
+      </c>
+      <c r="G185" t="n">
+        <v>252.81</v>
+      </c>
+      <c r="H185" t="n">
+        <v>290.47</v>
+      </c>
+      <c r="I185" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="n">
+        <v>0</v>
+      </c>
+      <c r="M185" t="n">
+        <v>0</v>
+      </c>
+      <c r="N185" t="n">
+        <v>0</v>
+      </c>
+      <c r="O185" t="n">
+        <v>0</v>
+      </c>
+      <c r="P185" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="Q185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr"/>
+      <c r="B186" t="n">
+        <v>2174833927</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="F186" s="2" t="n">
+        <v>45978.88350326389</v>
+      </c>
+      <c r="G186" t="n">
+        <v>24.16</v>
+      </c>
+      <c r="H186" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="I186" t="n">
+        <v>10</v>
+      </c>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="n">
+        <v>0</v>
+      </c>
+      <c r="M186" t="n">
+        <v>0</v>
+      </c>
+      <c r="N186" t="n">
+        <v>0</v>
+      </c>
+      <c r="O186" t="n">
+        <v>0</v>
+      </c>
+      <c r="P186" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr"/>
+      <c r="B187" t="n">
+        <v>2091086432</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>TTE</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>0.1657</v>
+      </c>
+      <c r="F187" s="2" t="n">
+        <v>45945.66072645834</v>
+      </c>
+      <c r="G187" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="H187" t="n">
+        <v>64.41</v>
+      </c>
+      <c r="I187" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="n">
+        <v>0</v>
+      </c>
+      <c r="M187" t="n">
+        <v>0</v>
+      </c>
+      <c r="N187" t="n">
+        <v>0</v>
+      </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+      <c r="P187" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="Q187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr"/>
+      <c r="B188" t="n">
+        <v>2060645660</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>0.1027</v>
+      </c>
+      <c r="F188" s="2" t="n">
+        <v>45932.90186543982</v>
+      </c>
+      <c r="G188" t="n">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="H188" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="I188" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="n">
+        <v>0</v>
+      </c>
+      <c r="M188" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" t="n">
+        <v>0</v>
+      </c>
+      <c r="O188" t="n">
+        <v>0</v>
+      </c>
+      <c r="P188" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Q188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr"/>
+      <c r="B189" t="n">
+        <v>1997562259</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>ING</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>0.6323</v>
+      </c>
+      <c r="F189" s="2" t="n">
+        <v>45898.65762083334</v>
+      </c>
+      <c r="G189" t="n">
+        <v>23.72</v>
+      </c>
+      <c r="H189" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I189" t="n">
+        <v>15</v>
+      </c>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="n">
+        <v>0</v>
+      </c>
+      <c r="M189" t="n">
+        <v>0</v>
+      </c>
+      <c r="N189" t="n">
+        <v>0</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
+      <c r="P189" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="Q189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr"/>
+      <c r="B190" t="n">
+        <v>1666459270</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>ING</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>0.5636</v>
+      </c>
+      <c r="F190" s="2" t="n">
+        <v>45708.68166530092</v>
+      </c>
+      <c r="G190" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="H190" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="I190" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="n">
+        <v>0</v>
+      </c>
+      <c r="M190" t="n">
+        <v>0</v>
+      </c>
+      <c r="N190" t="n">
+        <v>0</v>
+      </c>
+      <c r="O190" t="n">
+        <v>0</v>
+      </c>
+      <c r="P190" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="Q190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr"/>
+      <c r="B191" t="n">
+        <v>1824475555</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>ACI</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>1</v>
+      </c>
+      <c r="F191" s="2" t="n">
+        <v>45792.64702015046</v>
+      </c>
+      <c r="G191" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="H191" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="I191" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="n">
+        <v>0</v>
+      </c>
+      <c r="M191" t="n">
+        <v>0</v>
+      </c>
+      <c r="N191" t="n">
+        <v>0</v>
+      </c>
+      <c r="O191" t="n">
+        <v>0</v>
+      </c>
+      <c r="P191" t="n">
+        <v>-4.14</v>
+      </c>
+      <c r="Q191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr"/>
+      <c r="B192" t="n">
+        <v>2066994664</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>YUM</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="F192" s="2" t="n">
+        <v>45936.87431893519</v>
+      </c>
+      <c r="G192" t="n">
+        <v>149.19</v>
+      </c>
+      <c r="H192" t="n">
+        <v>150.97</v>
+      </c>
+      <c r="I192" t="n">
+        <v>10</v>
+      </c>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" t="n">
+        <v>0</v>
+      </c>
+      <c r="N192" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0</v>
+      </c>
+      <c r="P192" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr"/>
+      <c r="B193" t="n">
+        <v>2132992616</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>SGLD.L</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>0.0261</v>
+      </c>
+      <c r="F193" s="2" t="n">
+        <v>45960.53984946759</v>
+      </c>
+      <c r="G193" t="n">
+        <v>382.78</v>
+      </c>
+      <c r="H193" t="n">
+        <v>393.97</v>
+      </c>
+      <c r="I193" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" t="n">
+        <v>0</v>
+      </c>
+      <c r="N193" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" t="n">
+        <v>0</v>
+      </c>
+      <c r="P193" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="Q193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr"/>
+      <c r="B194" t="n">
+        <v>1843477272</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>BCS</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>1</v>
+      </c>
+      <c r="F194" s="2" t="n">
+        <v>45804.66725678241</v>
+      </c>
+      <c r="G194" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="H194" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="I194" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="n">
+        <v>0</v>
+      </c>
+      <c r="M194" t="n">
+        <v>0</v>
+      </c>
+      <c r="N194" t="n">
+        <v>0</v>
+      </c>
+      <c r="O194" t="n">
+        <v>0</v>
+      </c>
+      <c r="P194" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="Q194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr"/>
+      <c r="B195" t="n">
+        <v>2153557711</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>0.1727</v>
+      </c>
+      <c r="F195" s="2" t="n">
+        <v>45968.77076890046</v>
+      </c>
+      <c r="G195" t="n">
+        <v>57.95</v>
+      </c>
+      <c r="H195" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="I195" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="n">
+        <v>0</v>
+      </c>
+      <c r="M195" t="n">
+        <v>0</v>
+      </c>
+      <c r="N195" t="n">
+        <v>0</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0</v>
+      </c>
+      <c r="P195" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="Q195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr"/>
+      <c r="B196" t="n">
+        <v>2113305906</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>0.0345</v>
+      </c>
+      <c r="F196" s="2" t="n">
+        <v>45952.79000163195</v>
+      </c>
+      <c r="G196" t="n">
+        <v>289.79</v>
+      </c>
+      <c r="H196" t="n">
+        <v>284.69</v>
+      </c>
+      <c r="I196" t="n">
+        <v>10</v>
+      </c>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="n">
+        <v>0</v>
+      </c>
+      <c r="M196" t="n">
+        <v>0</v>
+      </c>
+      <c r="N196" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" t="n">
+        <v>0</v>
+      </c>
+      <c r="P196" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="Q196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr"/>
+      <c r="B197" t="n">
+        <v>2157053130</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>BVN</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>0.4249</v>
+      </c>
+      <c r="F197" s="2" t="n">
+        <v>45971.69071640047</v>
+      </c>
+      <c r="G197" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="H197" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="I197" t="n">
+        <v>10</v>
+      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="n">
+        <v>0</v>
+      </c>
+      <c r="M197" t="n">
+        <v>0</v>
+      </c>
+      <c r="N197" t="n">
+        <v>0</v>
+      </c>
+      <c r="O197" t="n">
+        <v>0</v>
+      </c>
+      <c r="P197" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr"/>
+      <c r="B198" t="n">
+        <v>2112194266</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>YPF</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="F198" s="2" t="n">
+        <v>45952.6478500926</v>
+      </c>
+      <c r="G198" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="H198" t="n">
+        <v>35.22</v>
+      </c>
+      <c r="I198" t="n">
+        <v>10</v>
+      </c>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="n">
+        <v>0</v>
+      </c>
+      <c r="M198" t="n">
+        <v>0</v>
+      </c>
+      <c r="N198" t="n">
+        <v>0</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
+      <c r="P198" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="Q198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr"/>
+      <c r="B199" t="n">
+        <v>1495551484</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>INGR</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>0.1914</v>
+      </c>
+      <c r="F199" s="2" t="n">
+        <v>45580.70648087963</v>
+      </c>
+      <c r="G199" t="n">
+        <v>135.82</v>
+      </c>
+      <c r="H199" t="n">
+        <v>105.97</v>
+      </c>
+      <c r="I199" t="n">
+        <v>26</v>
+      </c>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="n">
+        <v>0</v>
+      </c>
+      <c r="M199" t="n">
+        <v>0</v>
+      </c>
+      <c r="N199" t="n">
+        <v>0</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0</v>
+      </c>
+      <c r="P199" t="n">
+        <v>-5.72</v>
+      </c>
+      <c r="Q199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr"/>
+      <c r="B200" t="n">
+        <v>1926287328</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>0.5476</v>
+      </c>
+      <c r="F200" s="2" t="n">
+        <v>45854.82177967593</v>
+      </c>
+      <c r="G200" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="H200" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="I200" t="n">
+        <v>10</v>
+      </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="n">
+        <v>0</v>
+      </c>
+      <c r="M200" t="n">
+        <v>0</v>
+      </c>
+      <c r="N200" t="n">
+        <v>0</v>
+      </c>
+      <c r="O200" t="n">
+        <v>0</v>
+      </c>
+      <c r="P200" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="Q200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr"/>
+      <c r="B201" t="n">
+        <v>2139719001</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>BTCE.DE</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="F201" s="2" t="n">
+        <v>45964.47419064815</v>
+      </c>
+      <c r="G201" t="n">
+        <v>83.705</v>
+      </c>
+      <c r="H201" t="n">
+        <v>67.745</v>
+      </c>
+      <c r="I201" t="n">
+        <v>10</v>
+      </c>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="n">
+        <v>0</v>
+      </c>
+      <c r="M201" t="n">
+        <v>0</v>
+      </c>
+      <c r="N201" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" t="n">
+        <v>0</v>
+      </c>
+      <c r="P201" t="n">
+        <v>-1.98</v>
+      </c>
+      <c r="Q201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr"/>
+      <c r="B202" t="n">
+        <v>1680993370</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>VWO</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>1</v>
+      </c>
+      <c r="F202" s="2" t="n">
+        <v>45716.85638861111</v>
+      </c>
+      <c r="G202" t="n">
+        <v>44.49</v>
+      </c>
+      <c r="H202" t="n">
+        <v>53.62</v>
+      </c>
+      <c r="I202" t="n">
+        <v>44.49</v>
+      </c>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="n">
+        <v>0</v>
+      </c>
+      <c r="M202" t="n">
+        <v>0</v>
+      </c>
+      <c r="N202" t="n">
+        <v>0</v>
+      </c>
+      <c r="O202" t="n">
+        <v>0</v>
+      </c>
+      <c r="P202" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="Q202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr"/>
+      <c r="B203" t="n">
+        <v>1744767540</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="F203" s="2" t="n">
+        <v>45751.72316712963</v>
+      </c>
+      <c r="G203" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="H203" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="I203" t="n">
+        <v>10</v>
+      </c>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="n">
+        <v>0</v>
+      </c>
+      <c r="M203" t="n">
+        <v>0</v>
+      </c>
+      <c r="N203" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
+      <c r="P203" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="Q203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr"/>
+      <c r="B204" t="n">
+        <v>2141393361</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>0.1776</v>
+      </c>
+      <c r="F204" s="2" t="n">
+        <v>45964.79022641203</v>
+      </c>
+      <c r="G204" t="n">
+        <v>56.35</v>
+      </c>
+      <c r="H204" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="I204" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="n">
+        <v>0</v>
+      </c>
+      <c r="M204" t="n">
+        <v>0</v>
+      </c>
+      <c r="N204" t="n">
+        <v>0</v>
+      </c>
+      <c r="O204" t="n">
+        <v>0</v>
+      </c>
+      <c r="P204" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr"/>
+      <c r="B205" t="n">
+        <v>2134209002</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>0.0494</v>
+      </c>
+      <c r="F205" s="2" t="n">
+        <v>45960.73994237268</v>
+      </c>
+      <c r="G205" t="n">
+        <v>202.61</v>
+      </c>
+      <c r="H205" t="n">
+        <v>188.61</v>
+      </c>
+      <c r="I205" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="n">
+        <v>0</v>
+      </c>
+      <c r="M205" t="n">
+        <v>0</v>
+      </c>
+      <c r="N205" t="n">
+        <v>0</v>
+      </c>
+      <c r="O205" t="n">
+        <v>0</v>
+      </c>
+      <c r="P205" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="Q205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr"/>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="n">
+        <v>0</v>
+      </c>
+      <c r="N206" t="n">
+        <v>0</v>
+      </c>
+      <c r="O206" t="n">
+        <v>0</v>
+      </c>
+      <c r="P206" t="n">
+        <v>41.46</v>
+      </c>
+      <c r="Q206" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
